--- a/moabiz/data/real_estate_datastore.xlsx
+++ b/moabiz/data/real_estate_datastore.xlsx
@@ -5783,7 +5783,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
@@ -5803,22 +5803,22 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
@@ -5828,62 +5828,62 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>미츠쿄 1AP 사사노다이</t>
+          <t>에스포와르 크로스 카스카베</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>三ツ境1AP 新築アパート</t>
+          <t>エスポワール クロス カスカベ</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t>가나가와현 요코하마시 아사히구 사사노다이 2-149-3 / 神奈川県横浜市旭区笹野台2丁目149番3</t>
+          <t>埼玉県春日部市粕壁東3丁目3-36</t>
         </is>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t>神奈川県横浜市旭区笹野台2丁目149番3、231番102</t>
+          <t>埼玉県春日部市粕壁東三丁目1750-2, 1750-4, 1750-5, 1751-1 (4필지 합계 314.98㎡)</t>
         </is>
       </c>
       <c r="N12" s="0" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=가나가와현 요코하마시 아사히구 사사노다이 2-149-3 / 神奈川県横浜市旭区笹野台2丁目149番3</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%98%A5%E6%97%A5%E9%83%A8%E5%B8%82%E7%B2%95%E5%A3%81%E6%9D%B13-3-36</t>
         </is>
       </c>
       <c r="O12" s="0" t="inlineStr">
         <is>
-          <t>134700000</t>
+          <t>80000000</t>
         </is>
       </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
-          <t>13,470만 엔</t>
+          <t>8,000만 엔</t>
         </is>
       </c>
       <c r="Q12" s="0" t="inlineStr">
         <is>
-          <t>세금포함 (건물분 확인완료)</t>
+          <t>세포함 (税込 / 1층 점포·건물분 소비세 내역 확인 요망)</t>
         </is>
       </c>
       <c r="R12" s="0" t="inlineStr">
         <is>
-          <t>중개 (媒介)</t>
+          <t>중개 (仲介: 株式会社リブライフマーケティング)</t>
         </is>
       </c>
       <c r="S12" s="0" t="inlineStr">
         <is>
-          <t>현황인도 (계약부적합책임 면책 조건 확인)</t>
+          <t>상담 (相談 / 현 소유자 도쿄도 네리마구 거주 개인 — 계약부적합책임 면책 유무 확인 필요)</t>
         </is>
       </c>
       <c r="T12" s="0" t="inlineStr">
         <is>
-          <t>397.71</t>
+          <t>314.98</t>
         </is>
       </c>
       <c r="U12" s="0" t="inlineStr">
         <is>
-          <t>120.31</t>
+          <t>95.28</t>
         </is>
       </c>
       <c r="V12" s="0" t="inlineStr">
@@ -5893,414 +5893,414 @@
       </c>
       <c r="W12" s="0" t="inlineStr">
         <is>
-          <t>택지 (宅地)</t>
+          <t>택지 (宅地 — 4필지 모두 공부·현황 택지 및 소규모주택용지 1/6 감면 특례 적용 완료)</t>
         </is>
       </c>
       <c r="X12" s="0" t="inlineStr">
         <is>
-          <t>평탄지 (일부 지형 실사완료)</t>
+          <t>평탄지 · 3방 각지 (平坦地・三方角地)</t>
         </is>
       </c>
       <c r="Y12" s="0" t="inlineStr">
         <is>
-          <t>시가지화구역</t>
+          <t>시가화구역 (市街化区域)</t>
         </is>
       </c>
       <c r="Z12" s="0" t="inlineStr">
         <is>
-          <t>第一種低層住居専用地域 / 第1種高度地区 (建ぺい率40% / 容積率80%)</t>
+          <t>상업지역 (商業地域)</t>
         </is>
       </c>
       <c r="AA12" s="0" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AB12" s="0" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="AC12" s="0" t="inlineStr">
         <is>
-          <t>[추정치 적용]</t>
+          <t>47.67</t>
         </is>
       </c>
       <c r="AD12" s="0" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>89.66</t>
         </is>
       </c>
       <c r="AE12" s="0" t="inlineStr">
         <is>
-          <t>준방화지역 / 법22조구역</t>
+          <t>법 제22조·제23조 구역 (法第22・23条区域)</t>
         </is>
       </c>
       <c r="AF12" s="0" t="inlineStr">
         <is>
-          <t>南西側 幅員約4.0m (公道・私道) 接道 (セットバック部分0.29㎡含む)</t>
+          <t>남측 공도(学校どおり) 폭원 약 16.1m 접도 (서측 공원교도리·북동측 도로 포함 실질 3방 각지)</t>
         </is>
       </c>
       <c r="AG12" s="0" t="inlineStr">
         <is>
-          <t>공도 접도 (사도부담 없음)</t>
+          <t>없음 (공도 3면 접도)</t>
         </is>
       </c>
       <c r="AH12" s="0" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>S_HEAVY</t>
         </is>
       </c>
       <c r="AI12" s="0" t="inlineStr">
         <is>
-          <t>목조 지상 2층 (열화대책등급 3급 취득)</t>
+          <t>철골조 육지붕 2층 건 (鉄骨造 陸屋根 2階建)</t>
         </is>
       </c>
       <c r="AJ12" s="0" t="inlineStr">
         <is>
-          <t>令和8年(2026年)11月末引渡予定 (新築・建築中)</t>
+          <t>2014년 6월 (平成26年6月)</t>
         </is>
       </c>
       <c r="AK12" s="0" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AL12" s="0" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AM12" s="0" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AN12" s="0" t="inlineStr">
         <is>
-          <t>242.07</t>
+          <t>282.41</t>
         </is>
       </c>
       <c r="AO12" s="0" t="inlineStr">
         <is>
-          <t>242.07</t>
+          <t>282.41</t>
         </is>
       </c>
       <c r="AP12" s="0" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ12" s="0" t="inlineStr">
+        <is>
+          <t>총 5호: 1층 점포 1실(ITTO 개별지도학원 87.72㎡) + 주거 4호(2LDK 60.87㎡×2호 + 1LDK 35.70㎡×2호, 주거 과세면적 합계 194.69㎡)</t>
+        </is>
+      </c>
+      <c r="AR12" s="0" t="inlineStr">
+        <is>
+          <t>부지 내 평면 자주식 주차장 다수(5~6대분 이상) 및 주기장 완비 (개별 계약 대수·요금 렌트롤 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AS12" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] 2014년 6월 신축으로 구비 확실시되나 사본 징구 필요</t>
+        </is>
+      </c>
+      <c r="AT12" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] 준공검사필증(検査済証) 사본 징구 필요 (은행 25년 융자 심사 필수)</t>
+        </is>
+      </c>
+      <c r="AU12" s="0" t="inlineStr">
+        <is>
+          <t>도시가스 (都市ガス)</t>
+        </is>
+      </c>
+      <c r="AV12" s="0" t="inlineStr">
+        <is>
+          <t>공영수도 (公営水道) · 공공하수 (公共下水 — 정화조 유지비 없음)</t>
+        </is>
+      </c>
+      <c r="AW12" s="0" t="inlineStr">
+        <is>
+          <t>없음 (지상 2층 건 — EV 보수비 절감)</t>
+        </is>
+      </c>
+      <c r="AX12" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] 2014년 6월 신축 후 12.3년 경과 — 육지붕 방수 탑코트 및 외벽 실링 수선 이력 확인 필요</t>
+        </is>
+      </c>
+      <c r="AY12" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ12" s="0" t="inlineStr">
+        <is>
+          <t>5844000</t>
+        </is>
+      </c>
+      <c r="BA12" s="0" t="inlineStr">
+        <is>
+          <t>5844000</t>
+        </is>
+      </c>
+      <c r="BB12" s="0" t="inlineStr">
+        <is>
+          <t>7.31</t>
+        </is>
+      </c>
+      <c r="BC12" s="0" t="inlineStr">
+        <is>
+          <t>7.31</t>
+        </is>
+      </c>
+      <c r="BD12" s="0" t="inlineStr">
+        <is>
+          <t>431300</t>
+        </is>
+      </c>
+      <c r="BE12" s="0" t="inlineStr">
+        <is>
+          <t>1312400</t>
+        </is>
+      </c>
+      <c r="BF12" s="0" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="BG12" s="0" t="inlineStr">
+        <is>
+          <t>4531600</t>
+        </is>
+      </c>
+      <c r="BH12" s="0" t="inlineStr">
+        <is>
+          <t>5.66</t>
+        </is>
+      </c>
+      <c r="BI12" s="0" t="inlineStr">
+        <is>
+          <t>98000</t>
+        </is>
+      </c>
+      <c r="BJ12" s="0" t="inlineStr">
+        <is>
+          <t>30868040</t>
+        </is>
+      </c>
+      <c r="BK12" s="0" t="inlineStr">
+        <is>
+          <t>43258567</t>
+        </is>
+      </c>
+      <c r="BL12" s="0" t="inlineStr">
+        <is>
+          <t>92.66</t>
+        </is>
+      </c>
+      <c r="BM12" s="0" t="inlineStr">
+        <is>
+          <t>25008141</t>
+        </is>
+      </c>
+      <c r="BN12" s="0" t="inlineStr">
+        <is>
+          <t>22273671</t>
+        </is>
+      </c>
+      <c r="BO12" s="0" t="inlineStr">
+        <is>
+          <t>431300</t>
+        </is>
+      </c>
+      <c r="BP12" s="0" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="BQ12" s="0" t="inlineStr">
+        <is>
+          <t>68000000</t>
+        </is>
+      </c>
+      <c r="BR12" s="0" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BS12" s="0" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BT12" s="0" t="inlineStr">
+        <is>
+          <t>3538654</t>
+        </is>
+      </c>
+      <c r="BU12" s="0" t="inlineStr">
+        <is>
+          <t>992946</t>
+        </is>
+      </c>
+      <c r="BV12" s="0" t="inlineStr">
+        <is>
+          <t>256329</t>
+        </is>
+      </c>
+      <c r="BW12" s="0" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="BX12" s="0" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="BY12" s="0" t="inlineStr">
+        <is>
+          <t>83.01</t>
+        </is>
+      </c>
+      <c r="BZ12" s="0" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="CA12" s="0" t="inlineStr">
+        <is>
+          <t>18766000</t>
+        </is>
+      </c>
+      <c r="CB12" s="0" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="CC12" s="0" t="inlineStr">
+        <is>
+          <t>도부 스카이트리라인·도부 어반파크라인 『카스카베(春日部)』역 도보 9분 (2노선 급행 정차역)</t>
+        </is>
+      </c>
+      <c r="CD12" s="0" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AQ12" s="0" t="inlineStr">
-        <is>
-          <t>총 9세대</t>
-        </is>
-      </c>
-      <c r="AR12" s="0" t="inlineStr">
-        <is>
-          <t>부대 주차장 현황 본문 참조</t>
-        </is>
-      </c>
-      <c r="AS12" s="0" t="inlineStr">
-        <is>
-          <t>유 (건축확인대장 확인)</t>
-        </is>
-      </c>
-      <c r="AT12" s="0" t="inlineStr">
-        <is>
-          <t>[미수집 - 중개사 확인필요]</t>
-        </is>
-      </c>
-      <c r="AU12" s="0" t="inlineStr">
-        <is>
-          <t>公営水道 / 公共下水 / 都市ガス / 無料WIFI完備</t>
-        </is>
-      </c>
-      <c r="AV12" s="0" t="inlineStr">
-        <is>
-          <t>公営水道 / 公共下水 / 都市ガス / 無料WIFI完備</t>
-        </is>
-      </c>
-      <c r="AW12" s="0" t="inlineStr">
-        <is>
-          <t>무 (저층 유지비 절감형)</t>
-        </is>
-      </c>
-      <c r="AX12" s="0" t="inlineStr">
-        <is>
-          <t>[미수집 - 수선이력서 징구 필수]</t>
-        </is>
-      </c>
-      <c r="AY12" s="0" t="inlineStr">
+      <c r="CE12" s="0" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AZ12" s="0" t="inlineStr">
-        <is>
-          <t>8760000</t>
-        </is>
-      </c>
-      <c r="BA12" s="0" t="inlineStr">
-        <is>
-          <t>8760000</t>
-        </is>
-      </c>
-      <c r="BB12" s="0" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="BC12" s="0" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="BD12" s="0" t="inlineStr">
-        <is>
-          <t>850500</t>
-        </is>
-      </c>
-      <c r="BE12" s="0" t="inlineStr">
-        <is>
-          <t>1890000</t>
-        </is>
-      </c>
-      <c r="BF12" s="0" t="inlineStr">
-        <is>
-          <t>21.58</t>
-        </is>
-      </c>
-      <c r="BG12" s="0" t="inlineStr">
-        <is>
-          <t>6870000</t>
-        </is>
-      </c>
-      <c r="BH12" s="0" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="BI12" s="0" t="inlineStr">
-        <is>
-          <t>189861</t>
-        </is>
-      </c>
-      <c r="BJ12" s="0" t="inlineStr">
-        <is>
-          <t>75509800</t>
-        </is>
-      </c>
-      <c r="BK12" s="0" t="inlineStr">
-        <is>
-          <t>43572600</t>
-        </is>
-      </c>
-      <c r="BL12" s="0" t="inlineStr">
-        <is>
-          <t>88.41</t>
-        </is>
-      </c>
-      <c r="BM12" s="0" t="inlineStr">
-        <is>
-          <t>47145000</t>
-        </is>
-      </c>
-      <c r="BN12" s="0" t="inlineStr">
-        <is>
-          <t>29634000</t>
-        </is>
-      </c>
-      <c r="BO12" s="0" t="inlineStr">
-        <is>
-          <t>808,200 (추정치 적용)</t>
-        </is>
-      </c>
-      <c r="BP12" s="0" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="BQ12" s="0" t="inlineStr">
-        <is>
-          <t>114495000</t>
-        </is>
-      </c>
-      <c r="BR12" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="BS12" s="0" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BT12" s="0" t="inlineStr">
-        <is>
-          <t>5287219</t>
-        </is>
-      </c>
-      <c r="BU12" s="0" t="inlineStr">
-        <is>
-          <t>1582781</t>
-        </is>
-      </c>
-      <c r="BV12" s="0" t="inlineStr">
-        <is>
-          <t>1266225</t>
-        </is>
-      </c>
-      <c r="BW12" s="0" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="BX12" s="0" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="BY12" s="0" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="BZ12" s="0" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="CA12" s="0" t="inlineStr">
-        <is>
-          <t>31497300</t>
-        </is>
-      </c>
-      <c r="CB12" s="0" t="inlineStr">
-        <is>
-          <t>5.03</t>
-        </is>
-      </c>
-      <c r="CC12" s="0" t="inlineStr">
-        <is>
-          <t>최기역 도보 실측완료 (본문 9장 참조)</t>
-        </is>
-      </c>
-      <c r="CD12" s="0" t="inlineStr">
-        <is>
-          <t>개요서 도보시간 확인완료</t>
-        </is>
-      </c>
-      <c r="CE12" s="0" t="inlineStr">
-        <is>
-          <t>구글맵 실측 도보시간 검증완료</t>
-        </is>
-      </c>
       <c r="CF12" s="0" t="inlineStr">
         <is>
-          <t>실측거리 확인완료</t>
+          <t>720</t>
         </is>
       </c>
       <c r="CG12" s="0" t="inlineStr">
         <is>
-          <t>경사도·보행동선 스트리트뷰 실사완료</t>
+          <t>완전 평탄지 (표고 7.5m, 공원교도리·학교도리 직선 간선도로 동선, 카스카베 소학교 교차점 코너)</t>
         </is>
       </c>
       <c r="CH12" s="0" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=가나가와현 요코하마시 아사히구 사사노다이 2-149-3 / 神奈川県横浜市旭区笹野台2丁目149番3</t>
+          <t>https://www.google.com/maps/dir/%E6%98%A5%E6%97%A5%E9%83%A8%E9%A7%85/%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%98%A5%E6%97%A5%E9%83%A8%E5%B8%82%E7%B2%95%E5%A3%81%E6%9D%B13-3-36/</t>
         </is>
       </c>
       <c r="CI12" s="0" t="inlineStr">
         <is>
-          <t>지자체 침수 하저드맵 대조완료</t>
+          <t>카스카베시 홍수 해저드맵(L2 최대강우) 침수심 0.5m~3.0m 미만 상정 구역 (수도권 외곽방수로 인접 / 화재보험 수재 특약 필수 반영 완료)</t>
         </is>
       </c>
       <c r="CJ12" s="0" t="inlineStr">
         <is>
-          <t>토사재해 경계구역 대조완료</t>
+          <t>해당 없음 (평지 상업지역 — 토사재해 경계구역 외)</t>
         </is>
       </c>
       <c r="CK12" s="0" t="inlineStr">
         <is>
-          <t>https://www.homes.co.jp/archive/</t>
+          <t>https://www.homes.co.jp/archive/b-40030480/</t>
         </is>
       </c>
       <c r="CL12" s="0" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>90</t>
         </is>
       </c>
       <c r="CM12" s="0" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="CN12" s="0" t="inlineStr">
         <is>
-          <t>240000</t>
+          <t>192000</t>
         </is>
       </c>
       <c r="CO12" s="0" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CP12" s="0" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CQ12" s="0" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CR12" s="0" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="CS12" s="0" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CT12" s="0" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CU12" s="0" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CV12" s="0" t="inlineStr">
         <is>
-          <t>조건부 추천</t>
+          <t>A- 등급 (25.3/30) — 상업지역(400%) 3방 각지 95.3평 + 2014년식 철골조 + R8 과세명세서 실사 완료(고도세 43.1만엔, 단품 상환연수 21.9년). 7,300만~7,500만 엔 네고 및 렌트롤 검증 조건부 적극 추천</t>
         </is>
       </c>
       <c r="CW12" s="0" t="inlineStr">
         <is>
-          <t>recommend</t>
+          <t>적합 (우량 매수 검토)</t>
         </is>
       </c>
       <c r="CX12" s="0" t="inlineStr">
         <is>
-          <t>적합 (우량 편입 대상 - 120.3평 토지 담보력·열화3급 30년 융자·LTV -41.7%p 대폭 개선)</t>
+          <t>적합 (우량 편입 대상 - 5대 핵심 지표 전방위 개선: 통합 ICR 0.9→1.0배 돌파, 상환연수 24.1→23.6년 단축, Tax LTV -27.2%p 감축)</t>
         </is>
       </c>
       <c r="CY12" s="0" t="inlineStr">
         <is>
-          <t>적합 (우량 투자 대상 - 120.3평 대형 택지·열화3급 30년 융자·광폭 26.9㎡×9실)</t>
+          <t>우량 매수 검토 (25.3 / 30점 — 채무상환연수 21.9년·ICR 1.9배·국세청 적산비율 92.7%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
@@ -6319,378 +6319,390 @@
         </is>
       </c>
       <c r="E13" s="0">
-        <v>65.7</v>
+        <v>94.3</v>
       </c>
       <c r="F13" s="0">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G13" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="0">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>FULL_DD (정밀실사완료)</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>미츠쿄 1AP 사사노다이 (三ツ境1AP)</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>三ツ境1AP（横浜市旭区笹野台）</t>
+        </is>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
+        <is>
+          <t>神奈川県横浜市旭区笹野台2丁目19-5</t>
+        </is>
+      </c>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>神奈川県横浜市旭区笹野台二丁目149番3、231番102</t>
+        </is>
+      </c>
+      <c r="N13" s="0" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
+        </is>
+      </c>
+      <c r="O13" s="0">
+        <v>134700000</v>
+      </c>
+      <c r="P13" s="0" t="inlineStr">
+        <is>
+          <t>1억 3,470만 엔</t>
+        </is>
+      </c>
+      <c r="Q13" s="0" t="inlineStr">
+        <is>
+          <t>세금포함 (건물 소비세 포함 확인완료)</t>
+        </is>
+      </c>
+      <c r="R13" s="0" t="inlineStr">
+        <is>
+          <t>중개 (媒介 · 무브업)</t>
+        </is>
+      </c>
+      <c r="S13" s="0" t="inlineStr">
+        <is>
+          <t>2026년 12월 말 준공 / 2027년 1월 신축 인도 (계약금 보전조치 불요 범위)</t>
+        </is>
+      </c>
+      <c r="T13" s="0">
+        <v>397.71</v>
+      </c>
+      <c r="U13" s="0">
+        <v>120.3</v>
+      </c>
+      <c r="V13" s="0" t="inlineStr">
+        <is>
+          <t>소유권 (所有権)</t>
+        </is>
+      </c>
+      <c r="W13" s="0" t="inlineStr">
+        <is>
+          <t>택지 (宅地 · 등기 399.56㎡ / 확정측량 유효 397.42㎡ + 후퇴 0.29㎡)</t>
+        </is>
+      </c>
+      <c r="X13" s="0" t="inlineStr">
+        <is>
+          <t>고대(高台) 평탄지 (주변 대비 4.0~4.69m 단차 · 동·북측 기존 간지블록 옹벽 98.84㎡ 검사필증 없음 / 7.0m 파일 시공으로 벼랑조례 안식각 45° 대응)</t>
+        </is>
+      </c>
+      <c r="Y13" s="0" t="inlineStr">
+        <is>
+          <t>시가지화구역 (市街化区域)</t>
+        </is>
+      </c>
+      <c r="Z13" s="0" t="inlineStr">
+        <is>
+          <t>제1종 저층주거전용지역 · 제1종 고도지구</t>
+        </is>
+      </c>
+      <c r="AA13" s="0">
+        <v>40.0</v>
+      </c>
+      <c r="AB13" s="0">
+        <v>80.0</v>
+      </c>
+      <c r="AC13" s="0">
+        <v>39.57</v>
+      </c>
+      <c r="AD13" s="0">
+        <v>60.92</v>
+      </c>
+      <c r="AE13" s="0" t="inlineStr">
+        <is>
+          <t>법22조구역 · 목조 준내화구조(準耐火構造)</t>
+        </is>
+      </c>
+      <c r="AF13" s="0" t="inlineStr">
+        <is>
+          <t>남서측 폭원 3.92~4.50m 요코하마시 공도(下川井第402号線, 일부 계단) 및 서측 폭원 4.00~5.50m 요코하마시 공도(下川井第398号線) 접도</t>
+        </is>
+      </c>
+      <c r="AG13" s="0" t="inlineStr">
+        <is>
+          <t>없음 (등기부 지번 231-1 요코하마시 소유 공중용도로 및 인정노선도 100% 공도 검증완료)</t>
+        </is>
+      </c>
+      <c r="AH13" s="0" t="inlineStr">
+        <is>
+          <t>WOOD</t>
+        </is>
+      </c>
+      <c r="AI13" s="0" t="inlineStr">
+        <is>
+          <t>목조 준내화구조 지상 2층건 (RC베타기초+7.00m 기초파일 / 설계·건설 열화대책등급 3급)</t>
+        </is>
+      </c>
+      <c r="AJ13" s="0" t="inlineStr">
+        <is>
+          <t>2026년 12월 말 준공 예정 (2027년 1월 인도 예정)</t>
+        </is>
+      </c>
+      <c r="AK13" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="AL13" s="0">
+        <v>22</v>
+      </c>
+      <c r="AM13" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="AN13" s="0">
+        <v>242.07</v>
+      </c>
+      <c r="AO13" s="0">
+        <v>242.07</v>
+      </c>
+      <c r="AP13" s="0">
         <v>9</v>
       </c>
-      <c r="I13" s="0" t="inlineStr">
-        <is>
-          <t>PARTIAL_DD (일부서류입수)</t>
-        </is>
-      </c>
-      <c r="J13" s="0" t="inlineStr">
-        <is>
-          <t>에스포와르 크로스 카스카베</t>
-        </is>
-      </c>
-      <c r="K13" s="0" t="inlineStr">
-        <is>
-          <t>エスポワール クロス カスカベ</t>
-        </is>
-      </c>
-      <c r="L13" s="0" t="inlineStr">
-        <is>
-          <t>埼玉県春日部市粕壁東3丁目3-36</t>
-        </is>
-      </c>
-      <c r="M13" s="0" t="inlineStr">
-        <is>
-          <t>埼玉県春日部市粕壁東三丁目1750-2, 1750-4, 1750-5, 1751-1 (4필지 합계 314.98㎡)</t>
-        </is>
-      </c>
-      <c r="N13" s="0" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%98%A5%E6%97%A5%E9%83%A8%E5%B8%82%E7%B2%95%E5%A3%81%E6%9D%B13-3-36</t>
-        </is>
-      </c>
-      <c r="O13" s="0">
-        <v>80000000</v>
-      </c>
-      <c r="P13" s="0" t="inlineStr">
-        <is>
-          <t>8,000만 엔</t>
-        </is>
-      </c>
-      <c r="Q13" s="0" t="inlineStr">
-        <is>
-          <t>세포함 (税込 / 1층 점포·건물분 소비세 내역 확인 요망)</t>
-        </is>
-      </c>
-      <c r="R13" s="0" t="inlineStr">
-        <is>
-          <t>중개 (仲介: 株式会社リブライフマーケティング)</t>
-        </is>
-      </c>
-      <c r="S13" s="0" t="inlineStr">
-        <is>
-          <t>상담 (相談 / 현 소유자 도쿄도 네리마구 거주 개인 — 계약부적합책임 면책 유무 확인 필요)</t>
-        </is>
-      </c>
-      <c r="T13" s="0">
-        <v>314.98</v>
-      </c>
-      <c r="U13" s="0">
-        <v>95.28</v>
-      </c>
-      <c r="V13" s="0" t="inlineStr">
-        <is>
-          <t>소유권 (所有権)</t>
-        </is>
-      </c>
-      <c r="W13" s="0" t="inlineStr">
-        <is>
-          <t>택지 (宅地 — 4필지 모두 공부·현황 택지 및 소규모주택용지 1/6 감면 특례 적용 완료)</t>
-        </is>
-      </c>
-      <c r="X13" s="0" t="inlineStr">
-        <is>
-          <t>평탄지 · 3방 각지 (平坦地・三方角地)</t>
-        </is>
-      </c>
-      <c r="Y13" s="0" t="inlineStr">
-        <is>
-          <t>시가화구역 (市街化区域)</t>
-        </is>
-      </c>
-      <c r="Z13" s="0" t="inlineStr">
-        <is>
-          <t>상업지역 (商業地域)</t>
-        </is>
-      </c>
-      <c r="AA13" s="0">
-        <v>80.0</v>
-      </c>
-      <c r="AB13" s="0">
-        <v>400.0</v>
-      </c>
-      <c r="AC13" s="0">
-        <v>47.67</v>
-      </c>
-      <c r="AD13" s="0">
-        <v>89.66</v>
-      </c>
-      <c r="AE13" s="0" t="inlineStr">
-        <is>
-          <t>법 제22조·제23조 구역 (法第22・23条区域)</t>
-        </is>
-      </c>
-      <c r="AF13" s="0" t="inlineStr">
-        <is>
-          <t>남측 공도(学校どおり) 폭원 약 16.1m 접도 (서측 공원교도리·북동측 도로 포함 실질 3방 각지)</t>
-        </is>
-      </c>
-      <c r="AG13" s="0" t="inlineStr">
-        <is>
-          <t>없음 (공도 3면 접도)</t>
-        </is>
-      </c>
-      <c r="AH13" s="0" t="inlineStr">
-        <is>
-          <t>S_HEAVY</t>
-        </is>
-      </c>
-      <c r="AI13" s="0" t="inlineStr">
-        <is>
-          <t>철골조 육지붕 2층 건 (鉄骨造 陸屋根 2階建)</t>
-        </is>
-      </c>
-      <c r="AJ13" s="0" t="inlineStr">
-        <is>
-          <t>2014년 6월 (平成26年6月)</t>
-        </is>
-      </c>
-      <c r="AK13" s="0">
-        <v>12.3</v>
-      </c>
-      <c r="AL13" s="0">
-        <v>34</v>
-      </c>
-      <c r="AM13" s="0">
-        <v>21.7</v>
-      </c>
-      <c r="AN13" s="0">
-        <v>282.41</v>
-      </c>
-      <c r="AO13" s="0">
-        <v>282.41</v>
-      </c>
-      <c r="AP13" s="0">
-        <v>5</v>
-      </c>
       <c r="AQ13" s="0" t="inlineStr">
         <is>
-          <t>총 5호: 1층 점포 1실(ITTO 개별지도학원 87.72㎡) + 주거 4호(2LDK 60.87㎡×2호 + 1LDK 35.70㎡×2호, 주거 과세면적 합계 194.69㎡)</t>
+          <t>전 9세대 1LDK(26.89㎡: LDK8.0+양실5.5, 2인입주 가능) + 5세대(105, 201~204호) 로프트 4.82㎡</t>
         </is>
       </c>
       <c r="AR13" s="0" t="inlineStr">
         <is>
-          <t>부지 내 평면 자주식 주차장 다수(5~6대분 이상) 및 주기장 완비 (개별 계약 대수·요금 렌트롤 확인 필요)</t>
-        </is>
-      </c>
-      <c r="AS13" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] 2014년 6월 신축으로 구비 확실시되나 사본 징구 필요</t>
-        </is>
-      </c>
-      <c r="AT13" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] 준공검사필증(検査済証) 사본 징구 필요 (은행 25년 융자 심사 필수)</t>
+          <t>없음 (전면도로 계단 직전까지 차량 접근 가능)</t>
+        </is>
+      </c>
+      <c r="AS13" s="0" t="inlineStr">
+        <is>
+          <t>유 (제26UDI1K건00271호, R8.6.18 교부 확인필증 사본 완비)</t>
+        </is>
+      </c>
+      <c r="AT13" s="0" t="inlineStr">
+        <is>
+          <t>신축 건축중 (2026.12 말 준공 시 건축물 검사필증 및 건설주택성능평가서 열화3급 교부 예정 / 단, 기존 옹벽은 검사필증 없음)</t>
         </is>
       </c>
       <c r="AU13" s="0" t="inlineStr">
         <is>
-          <t>도시가스 (都市ガス)</t>
+          <t>도시가스 (都市ガス 완비)</t>
         </is>
       </c>
       <c r="AV13" s="0" t="inlineStr">
         <is>
-          <t>공영수도 (公営水道) · 공공하수 (公共下水 — 정화조 유지비 없음)</t>
+          <t>공영수도·공공하수·무료WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정 확인완료)</t>
         </is>
       </c>
       <c r="AW13" s="0" t="inlineStr">
         <is>
-          <t>없음 (지상 2층 건 — EV 보수비 절감)</t>
-        </is>
-      </c>
-      <c r="AX13" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] 2014년 6월 신축 후 12.3년 경과 — 육지붕 방수 탑코트 및 외벽 실링 수선 이력 확인 필요</t>
+          <t>무 (2층 저층형)</t>
+        </is>
+      </c>
+      <c r="AX13" s="0" t="inlineStr">
+        <is>
+          <t>신축 완공 예정 (RC베타기초+7.0m 기초파일 시공 / 동·북측 기존 간지블록 옹벽 98.84㎡는 보강계획 없음 확인)</t>
         </is>
       </c>
       <c r="AY13" s="0">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ13" s="0">
-        <v>5844000</v>
+        <v>8760000</v>
       </c>
       <c r="BA13" s="0">
-        <v>5844000</v>
+        <v>8760000</v>
       </c>
       <c r="BB13" s="0">
-        <v>7.31</v>
+        <v>6.5</v>
       </c>
       <c r="BC13" s="0">
-        <v>7.31</v>
+        <v>6.5</v>
       </c>
       <c r="BD13" s="0">
-        <v>431300</v>
+        <v>1130040</v>
       </c>
       <c r="BE13" s="0">
-        <v>1312400</v>
+        <v>1890040</v>
       </c>
       <c r="BF13" s="0">
-        <v>22.46</v>
+        <v>21.58</v>
       </c>
       <c r="BG13" s="0">
-        <v>4531600</v>
+        <v>6869960</v>
       </c>
       <c r="BH13" s="0">
-        <v>5.66</v>
+        <v>5.1</v>
       </c>
       <c r="BI13" s="0">
-        <v>98000</v>
+        <v>190000</v>
       </c>
       <c r="BJ13" s="0">
-        <v>30868040</v>
+        <v>75509800</v>
       </c>
       <c r="BK13" s="0">
-        <v>43258567</v>
+        <v>43572600</v>
       </c>
       <c r="BL13" s="0">
-        <v>92.66</v>
+        <v>88.41</v>
       </c>
       <c r="BM13" s="0">
-        <v>25008141</v>
+        <v>36985271</v>
       </c>
       <c r="BN13" s="0">
-        <v>22273671</v>
-      </c>
-      <c r="BO13" s="0">
-        <v>431300</v>
+        <v>26627700</v>
+      </c>
+      <c r="BO13" s="0" t="inlineStr">
+        <is>
+          <t>573,283엔 (R8 토지 공과증명서 주택특례 약 12.3만 엔 + 건물 오카다상 확인 약 45만 엔 추정)</t>
+        </is>
       </c>
       <c r="BP13" s="0">
         <v>85.0</v>
       </c>
       <c r="BQ13" s="0">
-        <v>68000000</v>
+        <v>114495000</v>
       </c>
       <c r="BR13" s="0">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BS13" s="0">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BT13" s="0">
-        <v>3538654</v>
+        <v>5287219</v>
       </c>
       <c r="BU13" s="0">
-        <v>992946</v>
+        <v>1582741</v>
       </c>
       <c r="BV13" s="0">
-        <v>256329</v>
+        <v>1246795</v>
       </c>
       <c r="BW13" s="0">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BX13" s="0">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="BY13" s="0">
-        <v>83.01</v>
+        <v>81.93</v>
       </c>
       <c r="BZ13" s="0">
-        <v>0.8</v>
+        <v>1.63</v>
       </c>
       <c r="CA13" s="0">
-        <v>18766000</v>
+        <v>31497300</v>
       </c>
       <c r="CB13" s="0">
-        <v>5.29</v>
+        <v>5.03</v>
       </c>
       <c r="CC13" s="0" t="inlineStr">
         <is>
-          <t>도부 스카이트리라인·도부 어반파크라인 『카스카베(春日部)』역 도보 9분 (2노선 급행 정차역)</t>
-        </is>
-      </c>
-      <c r="CD13" s="0">
-        <v>9</v>
-      </c>
-      <c r="CE13" s="0">
-        <v>9</v>
-      </c>
-      <c r="CF13" s="0">
-        <v>720</v>
+          <t>소테츠 본선(급행 정차) 「미츠쿄(三ツ境)」역 구글맵 실측 도보 10분 (약 720m, 마이소쿠 표기 7분)</t>
+        </is>
+      </c>
+      <c r="CD13" s="0" t="inlineStr">
+        <is>
+          <t>도보 7분 (마이소쿠 표기)</t>
+        </is>
+      </c>
+      <c r="CE13" s="0" t="inlineStr">
+        <is>
+          <t>실측 도보 10분 (구글맵 및 오카다상 현장 확인완료)</t>
+        </is>
+      </c>
+      <c r="CF13" s="0" t="inlineStr">
+        <is>
+          <t>720m (구글맵 실측완료)</t>
+        </is>
       </c>
       <c r="CG13" s="0" t="inlineStr">
         <is>
-          <t>완전 평탄지 (표고 7.5m, 공원교도리·학교도리 직선 간선도로 동선, 카스카베 소학교 교차점 코너)</t>
+          <t>사사노다이 상점가 경유 후 남서측 전면도로(下川井第402号線) 진입부에 계단 구간 및 부지 고저차(4.0~4.69m) 존재 확인완료</t>
         </is>
       </c>
       <c r="CH13" s="0" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/%E6%98%A5%E6%97%A5%E9%83%A8%E9%A7%85/%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%98%A5%E6%97%A5%E9%83%A8%E5%B8%82%E7%B2%95%E5%A3%81%E6%9D%B13-3-36/</t>
+          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
         </is>
       </c>
       <c r="CI13" s="0" t="inlineStr">
         <is>
-          <t>카스카베시 홍수 해저드맵(L2 최대강우) 침수심 0.5m~3.0m 미만 상정 구역 (수도권 외곽방수로 인접 / 화재보험 수재 특약 필수 반영 완료)</t>
+          <t>고대(高台) 입지로 홍수·내수 침수 해저드 해당 없음 (교차검증 완료)</t>
         </is>
       </c>
       <c r="CJ13" s="0" t="inlineStr">
         <is>
-          <t>해당 없음 (평지 상업지역 — 토사재해 경계구역 외)</t>
+          <t>부지 북서측 모서리 옹벽 부분(가측량도 약 4.69㎡)이 토사재해경계구역(옐로우존/잠정 레드존 경계)에 일부 저촉 확인완료 (건물 본체는 2m 이격되어 구역 외)</t>
         </is>
       </c>
       <c r="CK13" s="0" t="inlineStr">
         <is>
-          <t>https://www.homes.co.jp/archive/b-40030480/</t>
-        </is>
-      </c>
-      <c r="CL13" s="0">
-        <v>90</v>
-      </c>
-      <c r="CM13" s="0">
-        <v>2.9</v>
+          <t>https://www.homes.co.jp/archive/b-36020804/</t>
+        </is>
+      </c>
+      <c r="CL13" s="0" t="inlineStr">
+        <is>
+          <t>30~45일 (REINS 근린 성약 50건 및 일 피오레 사사노다이 교차검증 완료)</t>
+        </is>
+      </c>
+      <c r="CM13" s="0" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
       <c r="CN13" s="0">
-        <v>192000</v>
+        <v>0</v>
       </c>
       <c r="CO13" s="0">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="CP13" s="0">
-        <v>4.0</v>
+        <v>3.5</v>
       </c>
       <c r="CQ13" s="0">
-        <v>4.2</v>
+        <v>3.0</v>
       </c>
       <c r="CR13" s="0">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="CS13" s="0">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="CT13" s="0">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="CU13" s="0">
-        <v>25.3</v>
+        <v>19.5</v>
       </c>
       <c r="CV13" s="0" t="inlineStr">
         <is>
-          <t>A- 등급 (25.3/30) — 상업지역(400%) 3방 각지 95.3평 + 2014년식 철골조 + R8 과세명세서 실사 완료(고도세 43.1만엔, 단품 상환연수 21.9년). 7,300만~7,500만 엔 네고 및 렌트롤 검증 조건부 적극 추천</t>
+          <t>조건부 검토</t>
         </is>
       </c>
       <c r="CW13" s="0" t="inlineStr">
         <is>
-          <t>적합 (우량 매수 검토)</t>
+          <t>review</t>
         </is>
       </c>
       <c r="CX13" s="0" t="inlineStr">
         <is>
-          <t>적합 (우량 편입 대상 - 5대 핵심 지표 전방위 개선: 통합 ICR 0.9→1.0배 돌파, 상환연수 24.1→23.6년 단축, Tax LTV -27.2%p 감축)</t>
+          <t>적합 / 조건부 편입 (ICR 1.05배 돌파·LTV -15.6%p 개선 / 단, 미검사 옹벽·토사재해 저촉 반영 1.24억 네고 필수)</t>
         </is>
       </c>
       <c r="CY13" s="0" t="inlineStr">
         <is>
-          <t>우량 매수 검토 (25.3 / 30점 — 채무상환연수 21.9년·ICR 1.9배·국세청 적산비율 92.7%)</t>
+          <t>적합 / 조건부 검토 (120.3평 택지·1LDK+로프트·열화3급 30년 융자 우수하나 기존 옹벽·임대료 상단 리스크 반영 지값 협상 필수)</t>
         </is>
       </c>
     </row>
@@ -17318,27 +17330,27 @@
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>101호</t>
+          <t>1F 점포</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>점포 (교습소·학원)</t>
         </is>
       </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="F123" s="0" t="inlineStr">
@@ -17346,24 +17358,24 @@
           <t>입주중</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G123" s="0" t="inlineStr">
+        <is>
+          <t>법인 프랜차이즈 (ITTO個別指導学院 春日部東校)</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>10.0</t>
         </is>
       </c>
       <c r="J123" s="0" t="inlineStr">
         <is>
-          <t>960000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="K123" s="0" t="inlineStr">
@@ -17373,59 +17385,59 @@
       </c>
       <c r="L123" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="M123" s="0" t="inlineStr">
         <is>
-          <t>960000</t>
+          <t>192000</t>
         </is>
       </c>
       <c r="N123" s="0" t="inlineStr">
         <is>
-          <t>960000</t>
+          <t>195000</t>
         </is>
       </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="P123" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>90</t>
         </is>
       </c>
       <c r="Q123" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>[과세명세서 면적 87.72㎡ VERIFIED / 월세는 총수입 역산 추정치 — 계약서·렌트롤 필수 징구]</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>102호</t>
+          <t>101호</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>2LDK (남향)</t>
         </is>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="F124" s="0" t="inlineStr">
@@ -17433,86 +17445,86 @@
           <t>입주중</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G124" s="0" t="inlineStr">
+        <is>
+          <t>개인 (패밀리 장기거주 추정)</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>8.0</t>
         </is>
       </c>
       <c r="J124" s="0" t="inlineStr">
         <is>
-          <t>936000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="K124" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="M124" s="0" t="inlineStr">
         <is>
-          <t>936000</t>
+          <t>86000</t>
         </is>
       </c>
       <c r="N124" s="0" t="inlineStr">
         <is>
-          <t>936000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="P124" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>45</t>
         </is>
       </c>
       <c r="Q124" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>[201호 동타입 기준 추정 — 준공 이후 온라인 공실 이력 없음]</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>103호</t>
+          <t>201호</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>2LDK (남향)</t>
         </is>
       </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="F125" s="0" t="inlineStr">
@@ -17520,86 +17532,86 @@
           <t>입주중</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
+      <c r="G125" s="0" t="inlineStr">
+        <is>
+          <t>개인 (패밀리)</t>
+        </is>
+      </c>
+      <c r="H125" s="0" t="inlineStr">
+        <is>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="I125" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>5.3</t>
         </is>
       </c>
       <c r="J125" s="0" t="inlineStr">
         <is>
-          <t>936000</t>
+          <t>85000</t>
         </is>
       </c>
       <c r="K125" s="0" t="inlineStr">
         <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="L125" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L125" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M125" s="0" t="inlineStr">
         <is>
-          <t>936000</t>
+          <t>87000</t>
         </is>
       </c>
       <c r="N125" s="0" t="inlineStr">
         <is>
-          <t>936000</t>
+          <t>92000</t>
         </is>
       </c>
       <c r="O125" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="P125" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>45</t>
         </is>
       </c>
       <c r="Q125" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>[HOME'S u-33279661 실측 확인: 2021년 5월~6월 모집(DOM 45일), 월 85,000엔]</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>104호</t>
+          <t>202호</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK (북동향)</t>
         </is>
       </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="F126" s="0" t="inlineStr">
@@ -17607,86 +17619,86 @@
           <t>입주중</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
+      <c r="G126" s="0" t="inlineStr">
+        <is>
+          <t>개인 (단신/신혼)</t>
+        </is>
+      </c>
+      <c r="H126" s="0" t="inlineStr">
+        <is>
+          <t>2018-11</t>
         </is>
       </c>
       <c r="I126" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>7.8</t>
         </is>
       </c>
       <c r="J126" s="0" t="inlineStr">
         <is>
-          <t>936000</t>
+          <t>59000</t>
         </is>
       </c>
       <c r="K126" s="0" t="inlineStr">
         <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="L126" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L126" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M126" s="0" t="inlineStr">
         <is>
-          <t>936000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="N126" s="0" t="inlineStr">
         <is>
-          <t>936000</t>
+          <t>63000</t>
         </is>
       </c>
       <c r="O126" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="P126" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>135</t>
         </is>
       </c>
       <c r="Q126" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>[HOME'S u-33279663 실측 확인: 2018년 7월~11월 모집(DOM 135일), 월 59,000엔]</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>105호</t>
+          <t>203호</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK (북동향)</t>
         </is>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="F127" s="0" t="inlineStr">
@@ -17694,59 +17706,59 @@
           <t>입주중</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G127" s="0" t="inlineStr">
+        <is>
+          <t>개인 (장기거주 추정)</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
       <c r="I127" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>8.0</t>
         </is>
       </c>
       <c r="J127" s="0" t="inlineStr">
         <is>
-          <t>960000</t>
+          <t>59000</t>
         </is>
       </c>
       <c r="K127" s="0" t="inlineStr">
         <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="L127" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L127" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M127" s="0" t="inlineStr">
         <is>
-          <t>960000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="N127" s="0" t="inlineStr">
         <is>
-          <t>960000</t>
+          <t>63000</t>
         </is>
       </c>
       <c r="O127" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="P127" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>90</t>
         </is>
       </c>
       <c r="Q127" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>[202호 동타입 대칭 설계 기준 추정 — 준공 이후 온라인 공실 이력 없음]</t>
         </is>
       </c>
     </row>
@@ -17758,82 +17770,68 @@
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>201호</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="E128" s="0" t="inlineStr">
-        <is>
-          <t>26.89</t>
-        </is>
+          <t>1LDK (LDK8.0+양실5.5)</t>
+        </is>
+      </c>
+      <c r="E128" s="0">
+        <v>26.89</v>
       </c>
       <c r="F128" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
+          <t>신축모집예정(2026.12준공)</t>
+        </is>
+      </c>
+      <c r="G128" s="0" t="inlineStr">
+        <is>
+          <t>신축 2인입주가능(1LDK)</t>
+        </is>
+      </c>
+      <c r="H128" s="0" t="inlineStr">
+        <is>
+          <t>2026.12 준공예정</t>
         </is>
       </c>
       <c r="I128" s="0" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J128" s="0" t="inlineStr">
-        <is>
-          <t>1020000</t>
-        </is>
-      </c>
-      <c r="K128" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L128" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M128" s="0" t="inlineStr">
-        <is>
-          <t>1020000</t>
-        </is>
-      </c>
-      <c r="N128" s="0" t="inlineStr">
-        <is>
-          <t>1020000</t>
-        </is>
-      </c>
-      <c r="O128" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J128" s="0">
+        <v>80000</v>
+      </c>
+      <c r="K128" s="0">
+        <v>0</v>
+      </c>
+      <c r="L128" s="0">
+        <v>0</v>
+      </c>
+      <c r="M128" s="0">
+        <v>80000</v>
+      </c>
+      <c r="N128" s="0">
+        <v>78000</v>
+      </c>
+      <c r="O128" s="0">
+        <v>0</v>
       </c>
       <c r="P128" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>30~45</t>
         </is>
       </c>
       <c r="Q128" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>1F 서측 각실 · 2면채광 · 1F 수동셔터 · 무료WiFi 포함</t>
         </is>
       </c>
     </row>
@@ -17845,82 +17843,68 @@
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>202호</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="E129" s="0" t="inlineStr">
-        <is>
-          <t>26.89</t>
-        </is>
+          <t>1LDK (LDK8.0+양실5.5)</t>
+        </is>
+      </c>
+      <c r="E129" s="0">
+        <v>26.89</v>
       </c>
       <c r="F129" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
+          <t>신축모집예정(2026.12준공)</t>
+        </is>
+      </c>
+      <c r="G129" s="0" t="inlineStr">
+        <is>
+          <t>신축 2인입주가능(1LDK)</t>
+        </is>
+      </c>
+      <c r="H129" s="0" t="inlineStr">
+        <is>
+          <t>2026.12 준공예정</t>
         </is>
       </c>
       <c r="I129" s="0" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J129" s="0" t="inlineStr">
-        <is>
-          <t>996000</t>
-        </is>
-      </c>
-      <c r="K129" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L129" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M129" s="0" t="inlineStr">
-        <is>
-          <t>996000</t>
-        </is>
-      </c>
-      <c r="N129" s="0" t="inlineStr">
-        <is>
-          <t>996000</t>
-        </is>
-      </c>
-      <c r="O129" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J129" s="0">
+        <v>78000</v>
+      </c>
+      <c r="K129" s="0">
+        <v>0</v>
+      </c>
+      <c r="L129" s="0">
+        <v>0</v>
+      </c>
+      <c r="M129" s="0">
+        <v>78000</v>
+      </c>
+      <c r="N129" s="0">
+        <v>76000</v>
+      </c>
+      <c r="O129" s="0">
+        <v>0</v>
       </c>
       <c r="P129" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>30~45</t>
         </is>
       </c>
       <c r="Q129" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>1F 중실 · UB1014 · IH2구 키친(W1200) · 수동셔터</t>
         </is>
       </c>
     </row>
@@ -17932,82 +17916,68 @@
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>203호</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="E130" s="0" t="inlineStr">
-        <is>
-          <t>26.89</t>
-        </is>
+          <t>1LDK (LDK8.0+양실5.5)</t>
+        </is>
+      </c>
+      <c r="E130" s="0">
+        <v>26.89</v>
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
+          <t>신축모집예정(2026.12준공)</t>
+        </is>
+      </c>
+      <c r="G130" s="0" t="inlineStr">
+        <is>
+          <t>신축 2인입주가능(1LDK)</t>
+        </is>
+      </c>
+      <c r="H130" s="0" t="inlineStr">
+        <is>
+          <t>2026.12 준공예정</t>
         </is>
       </c>
       <c r="I130" s="0" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J130" s="0" t="inlineStr">
-        <is>
-          <t>996000</t>
-        </is>
-      </c>
-      <c r="K130" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L130" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M130" s="0" t="inlineStr">
-        <is>
-          <t>996000</t>
-        </is>
-      </c>
-      <c r="N130" s="0" t="inlineStr">
-        <is>
-          <t>996000</t>
-        </is>
-      </c>
-      <c r="O130" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J130" s="0">
+        <v>78000</v>
+      </c>
+      <c r="K130" s="0">
+        <v>0</v>
+      </c>
+      <c r="L130" s="0">
+        <v>0</v>
+      </c>
+      <c r="M130" s="0">
+        <v>78000</v>
+      </c>
+      <c r="N130" s="0">
+        <v>76000</v>
+      </c>
+      <c r="O130" s="0">
+        <v>0</v>
       </c>
       <c r="P130" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>30~45</t>
         </is>
       </c>
       <c r="Q130" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>1F 중실 · 차음경계벽 천장속 밀실시공 · 무료WiFi</t>
         </is>
       </c>
     </row>
@@ -18019,94 +17989,80 @@
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>204호</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="E131" s="0" t="inlineStr">
-        <is>
-          <t>26.89</t>
-        </is>
+          <t>1LDK (LDK8.0+양실5.5)</t>
+        </is>
+      </c>
+      <c r="E131" s="0">
+        <v>26.89</v>
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
+          <t>신축모집예정(2026.12준공)</t>
+        </is>
+      </c>
+      <c r="G131" s="0" t="inlineStr">
+        <is>
+          <t>신축 2인입주가능(1LDK)</t>
+        </is>
+      </c>
+      <c r="H131" s="0" t="inlineStr">
+        <is>
+          <t>2026.12 준공예정</t>
         </is>
       </c>
       <c r="I131" s="0" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J131" s="0" t="inlineStr">
-        <is>
-          <t>1020000</t>
-        </is>
-      </c>
-      <c r="K131" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L131" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M131" s="0" t="inlineStr">
-        <is>
-          <t>1020000</t>
-        </is>
-      </c>
-      <c r="N131" s="0" t="inlineStr">
-        <is>
-          <t>1020000</t>
-        </is>
-      </c>
-      <c r="O131" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J131" s="0">
+        <v>78000</v>
+      </c>
+      <c r="K131" s="0">
+        <v>0</v>
+      </c>
+      <c r="L131" s="0">
+        <v>0</v>
+      </c>
+      <c r="M131" s="0">
+        <v>78000</v>
+      </c>
+      <c r="N131" s="0">
+        <v>76000</v>
+      </c>
+      <c r="O131" s="0">
+        <v>0</v>
       </c>
       <c r="P131" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>30~45</t>
         </is>
       </c>
       <c r="Q131" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>1F 중실 · 수동셔터 · 무료WiFi 포함</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>1F 점포</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -18116,135 +18072,143 @@
       </c>
       <c r="D132" s="0" t="inlineStr">
         <is>
-          <t>점포 (교습소·학원)</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E132" s="0">
-        <v>87.72</v>
+        <v>26.89</v>
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>법인 프랜차이즈 (ITTO個別指導学院 春日部東校)</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="I132" s="0">
-        <v>10.0</v>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
+        </is>
+      </c>
+      <c r="H132" s="0" t="inlineStr">
+        <is>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I132" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J132" s="0">
-        <v>180000</v>
+        <v>80000</v>
       </c>
       <c r="K132" s="0">
         <v>0</v>
       </c>
       <c r="L132" s="0">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="M132" s="0">
-        <v>192000</v>
+        <v>80000</v>
       </c>
       <c r="N132" s="0">
-        <v>195000</v>
+        <v>80000</v>
       </c>
       <c r="O132" s="0">
-        <v>3000</v>
-      </c>
-      <c r="P132" s="0">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="P132" s="0" t="inlineStr">
+        <is>
+          <t>25~35</t>
+        </is>
       </c>
       <c r="Q132" s="0" t="inlineStr">
         <is>
-          <t>[과세명세서 면적 87.72㎡ VERIFIED / 월세는 총수입 역산 추정치 — 계약서·렌트롤 필수 징구]</t>
+          <t>1F 동측 단층부 각실 + 4.82㎡ 대형 로프트(실사용 31.71㎡, 2,523엔/㎡)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>101호</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
         <is>
-          <t>2LDK (남향)</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E133" s="0">
-        <v>60.87</v>
+        <v>26.89</v>
       </c>
       <c r="F133" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>개인 (패밀리 장기거주 추정)</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="I133" s="0">
-        <v>8.0</v>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
+        </is>
+      </c>
+      <c r="H133" s="0" t="inlineStr">
+        <is>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I133" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J133" s="0">
-        <v>80000</v>
+        <v>85000</v>
       </c>
       <c r="K133" s="0">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L133" s="0">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M133" s="0">
-        <v>86000</v>
+        <v>85000</v>
       </c>
       <c r="N133" s="0">
-        <v>90000</v>
+        <v>82000</v>
       </c>
       <c r="O133" s="0">
-        <v>4000</v>
-      </c>
-      <c r="P133" s="0">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="P133" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q133" s="0" t="inlineStr">
         <is>
-          <t>[201호 동타입 기준 추정 — 준공 이후 온라인 공실 이력 없음]</t>
+          <t>2F 최상층 서측 각실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>201호</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -18254,66 +18218,70 @@
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
-          <t>2LDK (남향)</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E134" s="0">
-        <v>60.87</v>
+        <v>26.89</v>
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>개인 (패밀리)</t>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
         <is>
-          <t>2021-06</t>
-        </is>
-      </c>
-      <c r="I134" s="0">
-        <v>5.3</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I134" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J134" s="0">
-        <v>85000</v>
+        <v>83000</v>
       </c>
       <c r="K134" s="0">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L134" s="0">
         <v>0</v>
       </c>
       <c r="M134" s="0">
-        <v>87000</v>
+        <v>83000</v>
       </c>
       <c r="N134" s="0">
-        <v>92000</v>
+        <v>80000</v>
       </c>
       <c r="O134" s="0">
-        <v>5000</v>
-      </c>
-      <c r="P134" s="0">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="P134" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q134" s="0" t="inlineStr">
         <is>
-          <t>[HOME'S u-33279661 실측 확인: 2021년 5월~6월 모집(DOM 45일), 월 85,000엔]</t>
+          <t>2F 최상층 중실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>202호</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
@@ -18323,66 +18291,70 @@
       </c>
       <c r="D135" s="0" t="inlineStr">
         <is>
-          <t>1LDK (북동향)</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E135" s="0">
-        <v>35.7</v>
+        <v>26.89</v>
       </c>
       <c r="F135" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>개인 (단신/신혼)</t>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
         <is>
-          <t>2018-11</t>
-        </is>
-      </c>
-      <c r="I135" s="0">
-        <v>7.8</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I135" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J135" s="0">
-        <v>59000</v>
+        <v>83000</v>
       </c>
       <c r="K135" s="0">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L135" s="0">
         <v>0</v>
       </c>
       <c r="M135" s="0">
-        <v>61000</v>
+        <v>83000</v>
       </c>
       <c r="N135" s="0">
-        <v>63000</v>
+        <v>80000</v>
       </c>
       <c r="O135" s="0">
-        <v>2000</v>
-      </c>
-      <c r="P135" s="0">
-        <v>135</v>
+        <v>0</v>
+      </c>
+      <c r="P135" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q135" s="0" t="inlineStr">
         <is>
-          <t>[HOME'S u-33279663 실측 확인: 2018년 7월~11월 모집(DOM 135일), 월 59,000엔]</t>
+          <t>2F 최상층 중실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>203호</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
@@ -18392,54 +18364,58 @@
       </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
-          <t>1LDK (북동향)</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E136" s="0">
-        <v>35.7</v>
+        <v>26.89</v>
       </c>
       <c r="F136" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>개인 (장기거주 추정)</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="I136" s="0">
-        <v>8.0</v>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
+        </is>
+      </c>
+      <c r="H136" s="0" t="inlineStr">
+        <is>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I136" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J136" s="0">
-        <v>59000</v>
+        <v>85000</v>
       </c>
       <c r="K136" s="0">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L136" s="0">
         <v>0</v>
       </c>
       <c r="M136" s="0">
-        <v>61000</v>
+        <v>85000</v>
       </c>
       <c r="N136" s="0">
-        <v>63000</v>
+        <v>82000</v>
       </c>
       <c r="O136" s="0">
-        <v>2000</v>
-      </c>
-      <c r="P136" s="0">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="P136" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q136" s="0" t="inlineStr">
         <is>
-          <t>[202호 동타입 대칭 설계 기준 추정 — 준공 이후 온라인 공실 이력 없음]</t>
+          <t>2F 최상층 동측 각실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
         </is>
       </c>
     </row>
@@ -38460,7 +38436,7 @@
     <row r="352">
       <c r="A352" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B352" s="0" t="inlineStr">
@@ -38490,12 +38466,12 @@
       </c>
       <c r="G352" s="0" t="inlineStr">
         <is>
-          <t>미츠쿄 1AP 사사노다이</t>
+          <t>에스포와르 크로스 카스카베</t>
         </is>
       </c>
       <c r="H352" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I352" s="0" t="inlineStr">
@@ -38517,7 +38493,7 @@
     <row r="353">
       <c r="A353" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B353" s="0" t="inlineStr">
@@ -38547,12 +38523,12 @@
       </c>
       <c r="G353" s="0" t="inlineStr">
         <is>
-          <t>가나가와현 요코하마시 아사히구 사사노다이 2-149-3 / 神奈川県横浜市旭区笹野台2丁目149番3</t>
+          <t>埼玉県春日部市粕壁東3丁目3-36</t>
         </is>
       </c>
       <c r="H353" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I353" s="0" t="inlineStr">
@@ -38574,7 +38550,7 @@
     <row r="354">
       <c r="A354" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B354" s="0" t="inlineStr">
@@ -38604,12 +38580,12 @@
       </c>
       <c r="G354" s="0" t="inlineStr">
         <is>
-          <t>神奈川県横浜市旭区笹野台2丁目149番3、231番102</t>
+          <t>埼玉県春日部市粕壁東三丁目1750-2, 1750-4, 1750-5, 1751-1 (4필지 합계 314.98㎡)</t>
         </is>
       </c>
       <c r="H354" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I354" s="0" t="inlineStr">
@@ -38631,7 +38607,7 @@
     <row r="355">
       <c r="A355" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B355" s="0" t="inlineStr">
@@ -38661,12 +38637,12 @@
       </c>
       <c r="G355" s="0" t="inlineStr">
         <is>
-          <t>134700000</t>
+          <t>80000000</t>
         </is>
       </c>
       <c r="H355" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I355" s="0" t="inlineStr">
@@ -38686,66 +38662,66 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B356" s="0" t="inlineStr">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
         <is>
           <t>CHK_05</t>
         </is>
       </c>
-      <c r="C356" s="0" t="inlineStr">
+      <c r="C356" s="2" t="inlineStr">
         <is>
           <t>1.기본/가격</t>
         </is>
       </c>
-      <c r="D356" s="0" t="inlineStr">
+      <c r="D356" s="2" t="inlineStr">
         <is>
           <t>delivery_condition</t>
         </is>
       </c>
-      <c r="E356" s="0" t="inlineStr">
+      <c r="E356" s="2" t="inlineStr">
         <is>
           <t>인도조건 및 계약부적합책임 면책 여부</t>
         </is>
       </c>
-      <c r="F356" s="0" t="inlineStr">
+      <c r="F356" s="2" t="inlineStr">
         <is>
           <t>引渡条件・契約不適合免責</t>
         </is>
       </c>
-      <c r="G356" s="0" t="inlineStr">
-        <is>
-          <t>현황인도 (계약부적합책임 면책 조건 확인)</t>
-        </is>
-      </c>
-      <c r="H356" s="0" t="inlineStr">
-        <is>
-          <t>COLLECTED</t>
-        </is>
-      </c>
-      <c r="I356" s="0" t="inlineStr">
-        <is>
-          <t>물건개요서</t>
-        </is>
-      </c>
-      <c r="J356" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K356" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>상담 (相談 / 현 소유자 도쿄도 네리마구 거주 개인 — 계약부적합책임 면책 유무 확인 필요)</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>현황인도 및 계약부적합책임 면책 특약 유무</t>
+        </is>
+      </c>
+      <c r="K356" s="2" t="inlineStr">
+        <is>
+          <t>現況渡し・契約不適合責任免責特約の有無</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B357" s="0" t="inlineStr">
@@ -38775,12 +38751,12 @@
       </c>
       <c r="G357" s="0" t="inlineStr">
         <is>
-          <t>397.71</t>
+          <t>314.98</t>
         </is>
       </c>
       <c r="H357" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I357" s="0" t="inlineStr">
@@ -38802,7 +38778,7 @@
     <row r="358">
       <c r="A358" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B358" s="0" t="inlineStr">
@@ -38837,7 +38813,7 @@
       </c>
       <c r="H358" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I358" s="0" t="inlineStr">
@@ -38859,7 +38835,7 @@
     <row r="359">
       <c r="A359" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B359" s="0" t="inlineStr">
@@ -38889,12 +38865,12 @@
       </c>
       <c r="G359" s="0" t="inlineStr">
         <is>
-          <t>第一種低層住居専用地域 / 第1種高度地区 (建ぺい率40% / 容積率80%)</t>
+          <t>상업지역 (商業地域)</t>
         </is>
       </c>
       <c r="H359" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I359" s="0" t="inlineStr">
@@ -38916,7 +38892,7 @@
     <row r="360">
       <c r="A360" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B360" s="0" t="inlineStr">
@@ -38946,12 +38922,12 @@
       </c>
       <c r="G360" s="0" t="inlineStr">
         <is>
-          <t>南西側 幅員約4.0m (公道・私道) 接道 (セットバック部分0.29㎡含む)</t>
+          <t>남측 공도(学校どおり) 폭원 약 16.1m 접도 (서측 공원교도리·북동측 도로 포함 실질 3방 각지)</t>
         </is>
       </c>
       <c r="H360" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I360" s="0" t="inlineStr">
@@ -38973,7 +38949,7 @@
     <row r="361">
       <c r="A361" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B361" s="0" t="inlineStr">
@@ -39003,12 +38979,12 @@
       </c>
       <c r="G361" s="0" t="inlineStr">
         <is>
-          <t>공도 접도 (사도부담 없음)</t>
+          <t>없음 (공도 3면 접도)</t>
         </is>
       </c>
       <c r="H361" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I361" s="0" t="inlineStr">
@@ -39030,7 +39006,7 @@
     <row r="362">
       <c r="A362" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B362" s="0" t="inlineStr">
@@ -39060,12 +39036,12 @@
       </c>
       <c r="G362" s="0" t="inlineStr">
         <is>
-          <t>목조 지상 2층 (열화대책등급 3급 취득)</t>
+          <t>철골조 육지붕 2층 건 (鉄骨造 陸屋根 2階建)</t>
         </is>
       </c>
       <c r="H362" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I362" s="0" t="inlineStr">
@@ -39087,7 +39063,7 @@
     <row r="363">
       <c r="A363" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B363" s="0" t="inlineStr">
@@ -39117,12 +39093,12 @@
       </c>
       <c r="G363" s="0" t="inlineStr">
         <is>
-          <t>令和8年(2026年)11月末引渡予定 (新築・建築中)</t>
+          <t>2014년 6월 (平成26年6月)</t>
         </is>
       </c>
       <c r="H363" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I363" s="0" t="inlineStr">
@@ -39144,7 +39120,7 @@
     <row r="364">
       <c r="A364" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B364" s="0" t="inlineStr">
@@ -39174,12 +39150,12 @@
       </c>
       <c r="G364" s="0" t="inlineStr">
         <is>
-          <t>242.07</t>
+          <t>282.41</t>
         </is>
       </c>
       <c r="H364" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I364" s="0" t="inlineStr">
@@ -39199,66 +39175,66 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B365" s="0" t="inlineStr">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
         <is>
           <t>CHK_14</t>
         </is>
       </c>
-      <c r="C365" s="0" t="inlineStr">
+      <c r="C365" s="2" t="inlineStr">
         <is>
           <t>3.건물/적법</t>
         </is>
       </c>
-      <c r="D365" s="0" t="inlineStr">
+      <c r="D365" s="2" t="inlineStr">
         <is>
           <t>has_confirm_cert</t>
         </is>
       </c>
-      <c r="E365" s="0" t="inlineStr">
+      <c r="E365" s="2" t="inlineStr">
         <is>
           <t>건축확인필증(確認済証) 및 대장 유무</t>
         </is>
       </c>
-      <c r="F365" s="0" t="inlineStr">
+      <c r="F365" s="2" t="inlineStr">
         <is>
           <t>建築確認済証・台帳記載事項証明</t>
         </is>
       </c>
-      <c r="G365" s="0" t="inlineStr">
-        <is>
-          <t>유 (건축확인대장 확인)</t>
-        </is>
-      </c>
-      <c r="H365" s="0" t="inlineStr">
-        <is>
-          <t>COLLECTED</t>
-        </is>
-      </c>
-      <c r="I365" s="0" t="inlineStr">
-        <is>
-          <t>건축확인대장</t>
-        </is>
-      </c>
-      <c r="J365" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K365" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>건축확인필증 또는 대장기재사항증명서 사본 요청</t>
+        </is>
+      </c>
+      <c r="K365" s="2" t="inlineStr">
+        <is>
+          <t>建築確認済証または台帳記載事項証明書の写しのご共有</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -39315,7 +39291,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -39372,7 +39348,7 @@
     <row r="368">
       <c r="A368" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B368" s="0" t="inlineStr">
@@ -39402,7 +39378,7 @@
       </c>
       <c r="G368" s="0" t="inlineStr">
         <is>
-          <t>8760000</t>
+          <t>5844000</t>
         </is>
       </c>
       <c r="H368" s="0" t="inlineStr">
@@ -39427,66 +39403,66 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B369" s="0" t="inlineStr">
+      <c r="A369" s="3" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="inlineStr">
         <is>
           <t>CHK_18</t>
         </is>
       </c>
-      <c r="C369" s="0" t="inlineStr">
+      <c r="C369" s="3" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D369" s="0" t="inlineStr">
+      <c r="D369" s="3" t="inlineStr">
         <is>
           <t>unit_composition</t>
         </is>
       </c>
-      <c r="E369" s="0" t="inlineStr">
+      <c r="E369" s="3" t="inlineStr">
         <is>
           <t>호실별 전유면적(㎡) 및 평형 타입</t>
         </is>
       </c>
-      <c r="F369" s="0" t="inlineStr">
+      <c r="F369" s="3" t="inlineStr">
         <is>
           <t>各戸専有面積・間取り</t>
         </is>
       </c>
-      <c r="G369" s="0" t="inlineStr">
-        <is>
-          <t>총 9세대</t>
-        </is>
-      </c>
-      <c r="H369" s="0" t="inlineStr">
-        <is>
-          <t>COLLECTED</t>
-        </is>
-      </c>
-      <c r="I369" s="0" t="inlineStr">
-        <is>
-          <t>렌트롤/도면</t>
-        </is>
-      </c>
-      <c r="J369" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K369" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G369" s="3" t="inlineStr">
+        <is>
+          <t>총 5호: 1층 점포 1실(ITTO 개별지도학원 87.72㎡) + 주거 4호(2LDK 60.87㎡×2호 + 1LDK 35.70㎡×2호, 주거 과세면적 합계 194.69㎡)</t>
+        </is>
+      </c>
+      <c r="H369" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I369" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J369" s="3" t="inlineStr">
+        <is>
+          <t>호실별 정확한 전유면적(㎡) 및 평면도(間取り図) 요청</t>
+        </is>
+      </c>
+      <c r="K369" s="3" t="inlineStr">
+        <is>
+          <t>各戸の正確な専有面積（㎡）および間取り図のご共有</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -39516,7 +39492,7 @@
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>[미수집 - 계약시작일 미기재]</t>
+          <t>전수/일부 확인 (5실)</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
@@ -39541,180 +39517,180 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B371" s="2" t="inlineStr">
+      <c r="A371" s="3" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
         <is>
           <t>CHK_20</t>
         </is>
       </c>
-      <c r="C371" s="2" t="inlineStr">
+      <c r="C371" s="3" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D371" s="2" t="inlineStr">
+      <c r="D371" s="3" t="inlineStr">
         <is>
           <t>rent_roll_tenant_types</t>
         </is>
       </c>
-      <c r="E371" s="2" t="inlineStr">
+      <c r="E371" s="3" t="inlineStr">
         <is>
           <t>호실별 입주자 속성(법인/직장인/학생/보증회사)</t>
         </is>
       </c>
-      <c r="F371" s="2" t="inlineStr">
+      <c r="F371" s="3" t="inlineStr">
         <is>
           <t>入居者属性・保証会社加入状況</t>
         </is>
       </c>
-      <c r="G371" s="2" t="inlineStr">
-        <is>
-          <t>[미수집 - 입주자속성 미기재]</t>
-        </is>
-      </c>
-      <c r="H371" s="2" t="inlineStr">
+      <c r="G371" s="3" t="inlineStr">
+        <is>
+          <t>속성 확인 (5실)</t>
+        </is>
+      </c>
+      <c r="H371" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I371" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J371" s="3" t="inlineStr">
+        <is>
+          <t>호실별 입주자 속성(법인/개인) 및 임대보증회사 가입 유무 확인</t>
+        </is>
+      </c>
+      <c r="K371" s="3" t="inlineStr">
+        <is>
+          <t>各戸の入居者属性（法人・社会人・学生等）および保証会社加入状況のご教示</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>CHK_21</t>
+        </is>
+      </c>
+      <c r="C372" s="3" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>parking_info</t>
+        </is>
+      </c>
+      <c r="E372" s="3" t="inlineStr">
+        <is>
+          <t>주차장·자판기·안테나 등 부대수입 계약현황</t>
+        </is>
+      </c>
+      <c r="F372" s="3" t="inlineStr">
+        <is>
+          <t>駐車場・付帯収入の契約状況</t>
+        </is>
+      </c>
+      <c r="G372" s="3" t="inlineStr">
+        <is>
+          <t>부지 내 평면 자주식 주차장 다수(5~6대분 이상) 및 주기장 완비 (개별 계약 대수·요금 렌트롤 확인 필요)</t>
+        </is>
+      </c>
+      <c r="H372" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I372" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J372" s="3" t="inlineStr">
+        <is>
+          <t>주차장 총 구획수, 현재 계약 대수 및 월 사용료 확인</t>
+        </is>
+      </c>
+      <c r="K372" s="3" t="inlineStr">
+        <is>
+          <t>駐車場区画数・契約台数およびその他付帯収入（自販機・アンテナ等）の内訳</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>CHK_22</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>disclosed_opex_yen</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>PM 관리위탁비 및 정기청소비 실비</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>PM管理委託費・定期清掃費</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>431300</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="I371" s="2" t="inlineStr">
+      <c r="I373" s="2" t="inlineStr">
         <is>
           <t>미수령 (중개사 요청 필요)</t>
         </is>
       </c>
-      <c r="J371" s="2" t="inlineStr">
-        <is>
-          <t>호실별 입주자 속성(법인/개인) 및 임대보증회사 가입 유무 확인</t>
-        </is>
-      </c>
-      <c r="K371" s="2" t="inlineStr">
-        <is>
-          <t>各戸の入居者属性（法人・社会人・学生等）および保証会社加入状況のご教示</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B372" s="0" t="inlineStr">
-        <is>
-          <t>CHK_21</t>
-        </is>
-      </c>
-      <c r="C372" s="0" t="inlineStr">
-        <is>
-          <t>4.렌트롤</t>
-        </is>
-      </c>
-      <c r="D372" s="0" t="inlineStr">
-        <is>
-          <t>parking_info</t>
-        </is>
-      </c>
-      <c r="E372" s="0" t="inlineStr">
-        <is>
-          <t>주차장·자판기·안테나 등 부대수입 계약현황</t>
-        </is>
-      </c>
-      <c r="F372" s="0" t="inlineStr">
-        <is>
-          <t>駐車場・付帯収入の契約状況</t>
-        </is>
-      </c>
-      <c r="G372" s="0" t="inlineStr">
-        <is>
-          <t>부대 주차장 현황 본문 참조</t>
-        </is>
-      </c>
-      <c r="H372" s="0" t="inlineStr">
-        <is>
-          <t>COLLECTED</t>
-        </is>
-      </c>
-      <c r="I372" s="0" t="inlineStr">
-        <is>
-          <t>렌트롤/개요서</t>
-        </is>
-      </c>
-      <c r="J372" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K372" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B373" s="0" t="inlineStr">
-        <is>
-          <t>CHK_22</t>
-        </is>
-      </c>
-      <c r="C373" s="0" t="inlineStr">
-        <is>
-          <t>5.경비/세금</t>
-        </is>
-      </c>
-      <c r="D373" s="0" t="inlineStr">
-        <is>
-          <t>disclosed_opex_yen</t>
-        </is>
-      </c>
-      <c r="E373" s="0" t="inlineStr">
-        <is>
-          <t>PM 관리위탁비 및 정기청소비 실비</t>
-        </is>
-      </c>
-      <c r="F373" s="0" t="inlineStr">
-        <is>
-          <t>PM管理委託費・定期清掃費</t>
-        </is>
-      </c>
-      <c r="G373" s="0" t="inlineStr">
-        <is>
-          <t>850500</t>
-        </is>
-      </c>
-      <c r="H373" s="0" t="inlineStr">
-        <is>
-          <t>COLLECTED</t>
-        </is>
-      </c>
-      <c r="I373" s="0" t="inlineStr">
-        <is>
-          <t>런닝코스트 명세</t>
-        </is>
-      </c>
-      <c r="J373" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K373" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>현재 위탁 중인 PM 관리수수료율 및 정기청소비 월액 확인</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="inlineStr">
+        <is>
+          <t>現行のPM管理委託料率および定期清掃費等のランニングコスト明細のご共有</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B374" s="0" t="inlineStr">
@@ -39744,12 +39720,12 @@
       </c>
       <c r="G374" s="0" t="inlineStr">
         <is>
-          <t>公営水道 / 公共下水 / 都市ガス / 無料WIFI完備</t>
+          <t>공영수도 (公営水道) · 공공하수 (公共下水 — 정화조 유지비 없음)</t>
         </is>
       </c>
       <c r="H374" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I374" s="0" t="inlineStr">
@@ -39771,7 +39747,7 @@
     <row r="375">
       <c r="A375" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B375" s="0" t="inlineStr">
@@ -39801,12 +39777,12 @@
       </c>
       <c r="G375" s="0" t="inlineStr">
         <is>
-          <t>47145000</t>
+          <t>25008141</t>
         </is>
       </c>
       <c r="H375" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I375" s="0" t="inlineStr">
@@ -39828,7 +39804,7 @@
     <row r="376">
       <c r="A376" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B376" s="0" t="inlineStr">
@@ -39858,12 +39834,12 @@
       </c>
       <c r="G376" s="0" t="inlineStr">
         <is>
-          <t>29634000</t>
+          <t>22273671</t>
         </is>
       </c>
       <c r="H376" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I376" s="0" t="inlineStr">
@@ -39883,237 +39859,237 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="3" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B377" s="3" t="inlineStr">
+      <c r="A377" s="0" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B377" s="0" t="inlineStr">
         <is>
           <t>CHK_26</t>
         </is>
       </c>
-      <c r="C377" s="3" t="inlineStr">
+      <c r="C377" s="0" t="inlineStr">
         <is>
           <t>5.경비/세금</t>
         </is>
       </c>
-      <c r="D377" s="3" t="inlineStr">
+      <c r="D377" s="0" t="inlineStr">
         <is>
           <t>fixed_tax_annual_yen</t>
         </is>
       </c>
-      <c r="E377" s="3" t="inlineStr">
+      <c r="E377" s="0" t="inlineStr">
         <is>
           <t>고정자산세·도시계획세 연간 실납부세액</t>
         </is>
       </c>
-      <c r="F377" s="3" t="inlineStr">
+      <c r="F377" s="0" t="inlineStr">
         <is>
           <t>固都税 年間納付税額</t>
         </is>
       </c>
-      <c r="G377" s="3" t="inlineStr">
-        <is>
-          <t>808,200 (추정치 적용)</t>
-        </is>
-      </c>
-      <c r="H377" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I377" s="3" t="inlineStr">
-        <is>
-          <t>표준산식 역산 추정</t>
-        </is>
-      </c>
-      <c r="J377" s="3" t="inlineStr">
-        <is>
-          <t>고정자산세·도시계획세 연간 납부세액 확정치 확인</t>
-        </is>
-      </c>
-      <c r="K377" s="3" t="inlineStr">
-        <is>
-          <t>固定資産税・都市計画税の年間納付税額（確定値）のご教示</t>
+      <c r="G377" s="0" t="inlineStr">
+        <is>
+          <t>431300</t>
+        </is>
+      </c>
+      <c r="H377" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I377" s="0" t="inlineStr">
+        <is>
+          <t>과세명세서</t>
+        </is>
+      </c>
+      <c r="J377" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K377" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B378" s="0" t="inlineStr">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
         <is>
           <t>CHK_27</t>
         </is>
       </c>
-      <c r="C378" s="0" t="inlineStr">
+      <c r="C378" s="2" t="inlineStr">
         <is>
           <t>6.등기/내력</t>
         </is>
       </c>
-      <c r="D378" s="0" t="inlineStr">
+      <c r="D378" s="2" t="inlineStr">
         <is>
           <t>registry_owner_match</t>
         </is>
       </c>
-      <c r="E378" s="0" t="inlineStr">
+      <c r="E378" s="2" t="inlineStr">
         <is>
           <t>토지·건물 등기부 소유자 일치 여부</t>
         </is>
       </c>
-      <c r="F378" s="0" t="inlineStr">
+      <c r="F378" s="2" t="inlineStr">
         <is>
           <t>土地・建物登記簿の所有者一致</t>
         </is>
       </c>
-      <c r="G378" s="0" t="inlineStr">
-        <is>
-          <t>[등기부 원장 확인완료]</t>
-        </is>
-      </c>
-      <c r="H378" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I378" s="0" t="inlineStr">
-        <is>
-          <t>등기사항전부증명서</t>
-        </is>
-      </c>
-      <c r="J378" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K378" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 등기부 미수령]</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>토지 및 건물 등기사항전부증명서(전부사항) 사본 요청</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="inlineStr">
+        <is>
+          <t>土地・建物の全部事項証明書（登記簿謄本）のご共有</t>
         </is>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B379" s="0" t="inlineStr">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
         <is>
           <t>CHK_28</t>
         </is>
       </c>
-      <c r="C379" s="0" t="inlineStr">
+      <c r="C379" s="2" t="inlineStr">
         <is>
           <t>6.등기/내력</t>
         </is>
       </c>
-      <c r="D379" s="0" t="inlineStr">
+      <c r="D379" s="2" t="inlineStr">
         <is>
           <t>registry_history_갑구</t>
         </is>
       </c>
-      <c r="E379" s="0" t="inlineStr">
+      <c r="E379" s="2" t="inlineStr">
         <is>
           <t>과거 소유권 변천내력(갑구) 및 매각동기</t>
         </is>
       </c>
-      <c r="F379" s="0" t="inlineStr">
+      <c r="F379" s="2" t="inlineStr">
         <is>
           <t>所有権移転履歴・売却理由</t>
         </is>
       </c>
-      <c r="G379" s="0" t="inlineStr">
-        <is>
-          <t>[등기부 원장 확인완료]</t>
-        </is>
-      </c>
-      <c r="H379" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I379" s="0" t="inlineStr">
-        <is>
-          <t>등기부 갑구/중개사</t>
-        </is>
-      </c>
-      <c r="J379" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K379" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 등기부 미수령]</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>현 소유자의 취득 경위 및 금번 매각 사유 확인</t>
+        </is>
+      </c>
+      <c r="K379" s="2" t="inlineStr">
+        <is>
+          <t>現所有者様の取得経緯および今回のご売却理由のご教示</t>
         </is>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B380" s="0" t="inlineStr">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>espoir-cross-kasukabe</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
         <is>
           <t>CHK_29</t>
         </is>
       </c>
-      <c r="C380" s="0" t="inlineStr">
+      <c r="C380" s="2" t="inlineStr">
         <is>
           <t>6.등기/내력</t>
         </is>
       </c>
-      <c r="D380" s="0" t="inlineStr">
+      <c r="D380" s="2" t="inlineStr">
         <is>
           <t>registry_liens_을구</t>
         </is>
       </c>
-      <c r="E380" s="0" t="inlineStr">
+      <c r="E380" s="2" t="inlineStr">
         <is>
           <t>담보권·근저당·압류·지역권 유무(을구)</t>
         </is>
       </c>
-      <c r="F380" s="0" t="inlineStr">
+      <c r="F380" s="2" t="inlineStr">
         <is>
           <t>抵当権・地役権等の権利関係</t>
         </is>
       </c>
-      <c r="G380" s="0" t="inlineStr">
-        <is>
-          <t>[등기부 원장 확인완료]</t>
-        </is>
-      </c>
-      <c r="H380" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I380" s="0" t="inlineStr">
-        <is>
-          <t>등기부 을구</t>
-        </is>
-      </c>
-      <c r="J380" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K380" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 등기부 미수령]</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>등기부 을구 권리관계 및 말소 조건 확인</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="inlineStr">
+        <is>
+          <t>登記簿乙区の権利関係および引渡時抹消条件の確認</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B381" s="0" t="inlineStr">
@@ -40143,12 +40119,12 @@
       </c>
       <c r="G381" s="0" t="inlineStr">
         <is>
-          <t>189861</t>
+          <t>98000</t>
         </is>
       </c>
       <c r="H381" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I381" s="0" t="inlineStr">
@@ -40170,7 +40146,7 @@
     <row r="382">
       <c r="A382" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B382" s="0" t="inlineStr">
@@ -40200,7 +40176,7 @@
       </c>
       <c r="G382" s="0" t="inlineStr">
         <is>
-          <t>구글맵 실측 도보시간 검증완료</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H382" s="0" t="inlineStr">
@@ -40227,7 +40203,7 @@
     <row r="383">
       <c r="A383" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B383" s="0" t="inlineStr">
@@ -40257,12 +40233,12 @@
       </c>
       <c r="G383" s="0" t="inlineStr">
         <is>
-          <t>경사도·보행동선 스트리트뷰 실사완료</t>
+          <t>완전 평탄지 (표고 7.5m, 공원교도리·학교도리 직선 간선도로 동선, 카스카베 소학교 교차점 코너)</t>
         </is>
       </c>
       <c r="H383" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I383" s="0" t="inlineStr">
@@ -40284,7 +40260,7 @@
     <row r="384">
       <c r="A384" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B384" s="0" t="inlineStr">
@@ -40314,12 +40290,12 @@
       </c>
       <c r="G384" s="0" t="inlineStr">
         <is>
-          <t>지자체 침수 하저드맵 대조완료</t>
+          <t>카스카베시 홍수 해저드맵(L2 최대강우) 침수심 0.5m~3.0m 미만 상정 구역 (수도권 외곽방수로 인접 / 화재보험 수재 특약 필수 반영 완료)</t>
         </is>
       </c>
       <c r="H384" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I384" s="0" t="inlineStr">
@@ -40341,7 +40317,7 @@
     <row r="385">
       <c r="A385" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B385" s="0" t="inlineStr">
@@ -40371,12 +40347,12 @@
       </c>
       <c r="G385" s="0" t="inlineStr">
         <is>
-          <t>토사재해 경계구역 대조완료</t>
+          <t>해당 없음 (평지 상업지역 — 토사재해 경계구역 외)</t>
         </is>
       </c>
       <c r="H385" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I385" s="0" t="inlineStr">
@@ -40398,7 +40374,7 @@
     <row r="386">
       <c r="A386" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B386" s="0" t="inlineStr">
@@ -40428,12 +40404,12 @@
       </c>
       <c r="G386" s="0" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H386" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I386" s="0" t="inlineStr">
@@ -40455,7 +40431,7 @@
     <row r="387">
       <c r="A387" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B387" s="0" t="inlineStr">
@@ -40485,7 +40461,7 @@
       </c>
       <c r="G387" s="0" t="inlineStr">
         <is>
-          <t>에스포와르 크로스 카스카베</t>
+          <t>미츠쿄 1AP 사사노다이 (三ツ境1AP)</t>
         </is>
       </c>
       <c r="H387" s="0" t="inlineStr">
@@ -40512,7 +40488,7 @@
     <row r="388">
       <c r="A388" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B388" s="0" t="inlineStr">
@@ -40542,7 +40518,7 @@
       </c>
       <c r="G388" s="0" t="inlineStr">
         <is>
-          <t>埼玉県春日部市粕壁東3丁目3-36</t>
+          <t>神奈川県横浜市旭区笹野台2丁目19-5</t>
         </is>
       </c>
       <c r="H388" s="0" t="inlineStr">
@@ -40569,7 +40545,7 @@
     <row r="389">
       <c r="A389" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B389" s="0" t="inlineStr">
@@ -40599,7 +40575,7 @@
       </c>
       <c r="G389" s="0" t="inlineStr">
         <is>
-          <t>埼玉県春日部市粕壁東三丁目1750-2, 1750-4, 1750-5, 1751-1 (4필지 합계 314.98㎡)</t>
+          <t>神奈川県横浜市旭区笹野台二丁目149番3、231番102</t>
         </is>
       </c>
       <c r="H389" s="0" t="inlineStr">
@@ -40626,7 +40602,7 @@
     <row r="390">
       <c r="A390" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B390" s="0" t="inlineStr">
@@ -40656,7 +40632,7 @@
       </c>
       <c r="G390" s="0" t="inlineStr">
         <is>
-          <t>80000000</t>
+          <t>134700000</t>
         </is>
       </c>
       <c r="H390" s="0" t="inlineStr">
@@ -40681,66 +40657,66 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B391" s="2" t="inlineStr">
+      <c r="A391" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B391" s="0" t="inlineStr">
         <is>
           <t>CHK_05</t>
         </is>
       </c>
-      <c r="C391" s="2" t="inlineStr">
+      <c r="C391" s="0" t="inlineStr">
         <is>
           <t>1.기본/가격</t>
         </is>
       </c>
-      <c r="D391" s="2" t="inlineStr">
+      <c r="D391" s="0" t="inlineStr">
         <is>
           <t>delivery_condition</t>
         </is>
       </c>
-      <c r="E391" s="2" t="inlineStr">
+      <c r="E391" s="0" t="inlineStr">
         <is>
           <t>인도조건 및 계약부적합책임 면책 여부</t>
         </is>
       </c>
-      <c r="F391" s="2" t="inlineStr">
+      <c r="F391" s="0" t="inlineStr">
         <is>
           <t>引渡条件・契約不適合免責</t>
         </is>
       </c>
-      <c r="G391" s="2" t="inlineStr">
-        <is>
-          <t>상담 (相談 / 현 소유자 도쿄도 네리마구 거주 개인 — 계약부적합책임 면책 유무 확인 필요)</t>
-        </is>
-      </c>
-      <c r="H391" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I391" s="2" t="inlineStr">
-        <is>
-          <t>미수령 (중개사 요청 필요)</t>
-        </is>
-      </c>
-      <c r="J391" s="2" t="inlineStr">
-        <is>
-          <t>현황인도 및 계약부적합책임 면책 특약 유무</t>
-        </is>
-      </c>
-      <c r="K391" s="2" t="inlineStr">
-        <is>
-          <t>現況渡し・契約不適合責任免責特約の有無</t>
+      <c r="G391" s="0" t="inlineStr">
+        <is>
+          <t>2026년 12월 말 준공 / 2027년 1월 신축 인도 (계약금 보전조치 불요 범위)</t>
+        </is>
+      </c>
+      <c r="H391" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I391" s="0" t="inlineStr">
+        <is>
+          <t>물건개요서</t>
+        </is>
+      </c>
+      <c r="J391" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K391" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B392" s="0" t="inlineStr">
@@ -40770,7 +40746,7 @@
       </c>
       <c r="G392" s="0" t="inlineStr">
         <is>
-          <t>314.98</t>
+          <t>397.71</t>
         </is>
       </c>
       <c r="H392" s="0" t="inlineStr">
@@ -40797,7 +40773,7 @@
     <row r="393">
       <c r="A393" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B393" s="0" t="inlineStr">
@@ -40854,7 +40830,7 @@
     <row r="394">
       <c r="A394" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B394" s="0" t="inlineStr">
@@ -40884,7 +40860,7 @@
       </c>
       <c r="G394" s="0" t="inlineStr">
         <is>
-          <t>상업지역 (商業地域)</t>
+          <t>제1종 저층주거전용지역 · 제1종 고도지구</t>
         </is>
       </c>
       <c r="H394" s="0" t="inlineStr">
@@ -40911,7 +40887,7 @@
     <row r="395">
       <c r="A395" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B395" s="0" t="inlineStr">
@@ -40941,7 +40917,7 @@
       </c>
       <c r="G395" s="0" t="inlineStr">
         <is>
-          <t>남측 공도(学校どおり) 폭원 약 16.1m 접도 (서측 공원교도리·북동측 도로 포함 실질 3방 각지)</t>
+          <t>남서측 폭원 3.92~4.50m 요코하마시 공도(下川井第402号線, 일부 계단) 및 서측 폭원 4.00~5.50m 요코하마시 공도(下川井第398号線) 접도</t>
         </is>
       </c>
       <c r="H395" s="0" t="inlineStr">
@@ -40968,7 +40944,7 @@
     <row r="396">
       <c r="A396" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B396" s="0" t="inlineStr">
@@ -40998,7 +40974,7 @@
       </c>
       <c r="G396" s="0" t="inlineStr">
         <is>
-          <t>없음 (공도 3면 접도)</t>
+          <t>없음 (등기부 지번 231-1 요코하마시 소유 공중용도로 및 인정노선도 100% 공도 검증완료)</t>
         </is>
       </c>
       <c r="H396" s="0" t="inlineStr">
@@ -41025,7 +41001,7 @@
     <row r="397">
       <c r="A397" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B397" s="0" t="inlineStr">
@@ -41055,7 +41031,7 @@
       </c>
       <c r="G397" s="0" t="inlineStr">
         <is>
-          <t>철골조 육지붕 2층 건 (鉄骨造 陸屋根 2階建)</t>
+          <t>목조 준내화구조 지상 2층건 (RC베타기초+7.00m 기초파일 / 설계·건설 열화대책등급 3급)</t>
         </is>
       </c>
       <c r="H397" s="0" t="inlineStr">
@@ -41082,7 +41058,7 @@
     <row r="398">
       <c r="A398" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B398" s="0" t="inlineStr">
@@ -41112,7 +41088,7 @@
       </c>
       <c r="G398" s="0" t="inlineStr">
         <is>
-          <t>2014년 6월 (平成26年6月)</t>
+          <t>2026년 12월 말 준공 예정 (2027년 1월 인도 예정)</t>
         </is>
       </c>
       <c r="H398" s="0" t="inlineStr">
@@ -41139,7 +41115,7 @@
     <row r="399">
       <c r="A399" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B399" s="0" t="inlineStr">
@@ -41169,7 +41145,7 @@
       </c>
       <c r="G399" s="0" t="inlineStr">
         <is>
-          <t>282.41</t>
+          <t>242.07</t>
         </is>
       </c>
       <c r="H399" s="0" t="inlineStr">
@@ -41194,522 +41170,522 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B400" s="2" t="inlineStr">
+      <c r="A400" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B400" s="0" t="inlineStr">
         <is>
           <t>CHK_14</t>
         </is>
       </c>
-      <c r="C400" s="2" t="inlineStr">
+      <c r="C400" s="0" t="inlineStr">
         <is>
           <t>3.건물/적법</t>
         </is>
       </c>
-      <c r="D400" s="2" t="inlineStr">
+      <c r="D400" s="0" t="inlineStr">
         <is>
           <t>has_confirm_cert</t>
         </is>
       </c>
-      <c r="E400" s="2" t="inlineStr">
+      <c r="E400" s="0" t="inlineStr">
         <is>
           <t>건축확인필증(確認済証) 및 대장 유무</t>
         </is>
       </c>
-      <c r="F400" s="2" t="inlineStr">
+      <c r="F400" s="0" t="inlineStr">
         <is>
           <t>建築確認済証・台帳記載事項証明</t>
         </is>
       </c>
-      <c r="G400" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="H400" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I400" s="2" t="inlineStr">
-        <is>
-          <t>미수령 (중개사 요청 필요)</t>
-        </is>
-      </c>
-      <c r="J400" s="2" t="inlineStr">
-        <is>
-          <t>건축확인필증 또는 대장기재사항증명서 사본 요청</t>
-        </is>
-      </c>
-      <c r="K400" s="2" t="inlineStr">
-        <is>
-          <t>建築確認済証または台帳記載事項証明書の写しのご共有</t>
+      <c r="G400" s="0" t="inlineStr">
+        <is>
+          <t>유 (제26UDI1K건00271호, R8.6.18 교부 확인필증 사본 완비)</t>
+        </is>
+      </c>
+      <c r="H400" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I400" s="0" t="inlineStr">
+        <is>
+          <t>건축확인대장</t>
+        </is>
+      </c>
+      <c r="J400" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K400" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B401" s="2" t="inlineStr">
+      <c r="A401" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B401" s="0" t="inlineStr">
         <is>
           <t>CHK_15</t>
         </is>
       </c>
-      <c r="C401" s="2" t="inlineStr">
+      <c r="C401" s="0" t="inlineStr">
         <is>
           <t>3.건물/적법</t>
         </is>
       </c>
-      <c r="D401" s="2" t="inlineStr">
+      <c r="D401" s="0" t="inlineStr">
         <is>
           <t>has_inspection_cert</t>
         </is>
       </c>
-      <c r="E401" s="2" t="inlineStr">
+      <c r="E401" s="0" t="inlineStr">
         <is>
           <t>준공검사필증(検査済証) 취득 여부</t>
         </is>
       </c>
-      <c r="F401" s="2" t="inlineStr">
+      <c r="F401" s="0" t="inlineStr">
         <is>
           <t>検査済証の有無</t>
         </is>
       </c>
-      <c r="G401" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="H401" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I401" s="2" t="inlineStr">
-        <is>
-          <t>미수령 (중개사 요청 필요)</t>
-        </is>
-      </c>
-      <c r="J401" s="2" t="inlineStr">
-        <is>
-          <t>준공검사필증(検査済証) 교부 유무 및 번호 확인 (은행융자 필수)</t>
-        </is>
-      </c>
-      <c r="K401" s="2" t="inlineStr">
-        <is>
-          <t>検査済証の有無および交付番号のご確認（融資審査上必須）</t>
+      <c r="G401" s="0" t="inlineStr">
+        <is>
+          <t>신축 건축중 (2026.12 말 준공 시 건축물 검사필증 및 건설주택성능평가서 열화3급 교부 예정 / 단, 기존 옹벽은 검사필증 없음)</t>
+        </is>
+      </c>
+      <c r="H401" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I401" s="0" t="inlineStr">
+        <is>
+          <t>검사필증/대장</t>
+        </is>
+      </c>
+      <c r="J401" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K401" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B402" s="2" t="inlineStr">
+      <c r="A402" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B402" s="0" t="inlineStr">
         <is>
           <t>CHK_16</t>
         </is>
       </c>
-      <c r="C402" s="2" t="inlineStr">
+      <c r="C402" s="0" t="inlineStr">
         <is>
           <t>3.건물/적법</t>
         </is>
       </c>
-      <c r="D402" s="2" t="inlineStr">
+      <c r="D402" s="0" t="inlineStr">
         <is>
           <t>repair_history_summary</t>
         </is>
       </c>
-      <c r="E402" s="2" t="inlineStr">
+      <c r="E402" s="0" t="inlineStr">
         <is>
           <t>외벽도장·옥상방수 등 대규모 수선이력</t>
         </is>
       </c>
-      <c r="F402" s="2" t="inlineStr">
+      <c r="F402" s="0" t="inlineStr">
         <is>
           <t>大規模修繕履歴（外壁・屋上防水）</t>
         </is>
       </c>
-      <c r="G402" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="H402" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I402" s="2" t="inlineStr">
-        <is>
-          <t>미수령 (중개사 요청 필요)</t>
-        </is>
-      </c>
-      <c r="J402" s="2" t="inlineStr">
-        <is>
-          <t>과거 외벽도장·옥상방수·급배수관 수선이력서 및 견적서 요청</t>
-        </is>
-      </c>
-      <c r="K402" s="2" t="inlineStr">
-        <is>
-          <t>過去の外壁塗装・屋上防水・設備等の修繕履歴一覧のご共有</t>
+      <c r="G402" s="0" t="inlineStr">
+        <is>
+          <t>신축 완공 예정 (RC베타기초+7.0m 기초파일 시공 / 동·북측 기존 간지블록 옹벽 98.84㎡는 보강계획 없음 확인)</t>
+        </is>
+      </c>
+      <c r="H402" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I402" s="0" t="inlineStr">
+        <is>
+          <t>수선이력서</t>
+        </is>
+      </c>
+      <c r="J402" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K402" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="0" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B403" s="0" t="inlineStr">
+      <c r="A403" s="3" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
         <is>
           <t>CHK_17</t>
         </is>
       </c>
-      <c r="C403" s="0" t="inlineStr">
+      <c r="C403" s="3" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D403" s="0" t="inlineStr">
+      <c r="D403" s="3" t="inlineStr">
         <is>
           <t>full_annual_income_yen</t>
         </is>
       </c>
-      <c r="E403" s="0" t="inlineStr">
+      <c r="E403" s="3" t="inlineStr">
         <is>
           <t>호실별 월 차임 및 공익비 내역</t>
         </is>
       </c>
-      <c r="F403" s="0" t="inlineStr">
+      <c r="F403" s="3" t="inlineStr">
         <is>
           <t>各戸賃料・共益費一覧</t>
         </is>
       </c>
-      <c r="G403" s="0" t="inlineStr">
-        <is>
-          <t>5844000</t>
-        </is>
-      </c>
-      <c r="H403" s="0" t="inlineStr">
-        <is>
-          <t>COLLECTED</t>
-        </is>
-      </c>
-      <c r="I403" s="0" t="inlineStr">
-        <is>
-          <t>렌트롤</t>
-        </is>
-      </c>
-      <c r="J403" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K403" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G403" s="3" t="inlineStr">
+        <is>
+          <t>8760000</t>
+        </is>
+      </c>
+      <c r="H403" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I403" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J403" s="3" t="inlineStr">
+        <is>
+          <t>최신 렌트롤(호실별 차임·공익비·보증금 명시본) 요청</t>
+        </is>
+      </c>
+      <c r="K403" s="3" t="inlineStr">
+        <is>
+          <t>最新のレントロール（各戸賃料・共益費・敷金明細）のご共有</t>
         </is>
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="3" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B404" s="3" t="inlineStr">
+      <c r="A404" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B404" s="0" t="inlineStr">
         <is>
           <t>CHK_18</t>
         </is>
       </c>
-      <c r="C404" s="3" t="inlineStr">
+      <c r="C404" s="0" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D404" s="3" t="inlineStr">
+      <c r="D404" s="0" t="inlineStr">
         <is>
           <t>unit_composition</t>
         </is>
       </c>
-      <c r="E404" s="3" t="inlineStr">
+      <c r="E404" s="0" t="inlineStr">
         <is>
           <t>호실별 전유면적(㎡) 및 평형 타입</t>
         </is>
       </c>
-      <c r="F404" s="3" t="inlineStr">
+      <c r="F404" s="0" t="inlineStr">
         <is>
           <t>各戸専有面積・間取り</t>
         </is>
       </c>
-      <c r="G404" s="3" t="inlineStr">
-        <is>
-          <t>총 5호: 1층 점포 1실(ITTO 개별지도학원 87.72㎡) + 주거 4호(2LDK 60.87㎡×2호 + 1LDK 35.70㎡×2호, 주거 과세면적 합계 194.69㎡)</t>
-        </is>
-      </c>
-      <c r="H404" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I404" s="3" t="inlineStr">
-        <is>
-          <t>표준산식 역산 추정</t>
-        </is>
-      </c>
-      <c r="J404" s="3" t="inlineStr">
-        <is>
-          <t>호실별 정확한 전유면적(㎡) 및 평면도(間取り図) 요청</t>
-        </is>
-      </c>
-      <c r="K404" s="3" t="inlineStr">
-        <is>
-          <t>各戸の正確な専有面積（㎡）および間取り図のご共有</t>
+      <c r="G404" s="0" t="inlineStr">
+        <is>
+          <t>전 9세대 1LDK(26.89㎡: LDK8.0+양실5.5, 2인입주 가능) + 5세대(105, 201~204호) 로프트 4.82㎡</t>
+        </is>
+      </c>
+      <c r="H404" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I404" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤/도면</t>
+        </is>
+      </c>
+      <c r="J404" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K404" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B405" s="2" t="inlineStr">
+      <c r="A405" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B405" s="0" t="inlineStr">
         <is>
           <t>CHK_19</t>
         </is>
       </c>
-      <c r="C405" s="2" t="inlineStr">
+      <c r="C405" s="0" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D405" s="2" t="inlineStr">
+      <c r="D405" s="0" t="inlineStr">
         <is>
           <t>rent_roll_contract_dates</t>
         </is>
       </c>
-      <c r="E405" s="2" t="inlineStr">
+      <c r="E405" s="0" t="inlineStr">
         <is>
           <t>호실별 계약시작일(契約始期) 및 갱신주기</t>
         </is>
       </c>
-      <c r="F405" s="2" t="inlineStr">
+      <c r="F405" s="0" t="inlineStr">
         <is>
           <t>各戸の契約始期・更新時期</t>
         </is>
       </c>
-      <c r="G405" s="2" t="inlineStr">
-        <is>
-          <t>전수/일부 확인 (5실)</t>
-        </is>
-      </c>
-      <c r="H405" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I405" s="2" t="inlineStr">
-        <is>
-          <t>미수령 (중개사 요청 필요)</t>
-        </is>
-      </c>
-      <c r="J405" s="2" t="inlineStr">
-        <is>
-          <t>렌트롤상 호실별 최초 계약시작일(입주일) 기재본 요청</t>
-        </is>
-      </c>
-      <c r="K405" s="2" t="inlineStr">
-        <is>
-          <t>レントロールにおける各戸の契約始期（入居年月）のご教示</t>
+      <c r="G405" s="0" t="inlineStr">
+        <is>
+          <t>전수/일부 확인 (9실)</t>
+        </is>
+      </c>
+      <c r="H405" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I405" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤 상세판</t>
+        </is>
+      </c>
+      <c r="J405" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K405" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="3" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B406" s="3" t="inlineStr">
+      <c r="A406" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B406" s="0" t="inlineStr">
         <is>
           <t>CHK_20</t>
         </is>
       </c>
-      <c r="C406" s="3" t="inlineStr">
+      <c r="C406" s="0" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D406" s="3" t="inlineStr">
+      <c r="D406" s="0" t="inlineStr">
         <is>
           <t>rent_roll_tenant_types</t>
         </is>
       </c>
-      <c r="E406" s="3" t="inlineStr">
+      <c r="E406" s="0" t="inlineStr">
         <is>
           <t>호실별 입주자 속성(법인/직장인/학생/보증회사)</t>
         </is>
       </c>
-      <c r="F406" s="3" t="inlineStr">
+      <c r="F406" s="0" t="inlineStr">
         <is>
           <t>入居者属性・保証会社加入状況</t>
         </is>
       </c>
-      <c r="G406" s="3" t="inlineStr">
-        <is>
-          <t>속성 확인 (5실)</t>
-        </is>
-      </c>
-      <c r="H406" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I406" s="3" t="inlineStr">
-        <is>
-          <t>표준산식 역산 추정</t>
-        </is>
-      </c>
-      <c r="J406" s="3" t="inlineStr">
-        <is>
-          <t>호실별 입주자 속성(법인/개인) 및 임대보증회사 가입 유무 확인</t>
-        </is>
-      </c>
-      <c r="K406" s="3" t="inlineStr">
-        <is>
-          <t>各戸の入居者属性（法人・社会人・学生等）および保証会社加入状況のご教示</t>
+      <c r="G406" s="0" t="inlineStr">
+        <is>
+          <t>속성 확인 (9실)</t>
+        </is>
+      </c>
+      <c r="H406" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I406" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤 상세판</t>
+        </is>
+      </c>
+      <c r="J406" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K406" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="3" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B407" s="3" t="inlineStr">
+      <c r="A407" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B407" s="0" t="inlineStr">
         <is>
           <t>CHK_21</t>
         </is>
       </c>
-      <c r="C407" s="3" t="inlineStr">
+      <c r="C407" s="0" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D407" s="3" t="inlineStr">
+      <c r="D407" s="0" t="inlineStr">
         <is>
           <t>parking_info</t>
         </is>
       </c>
-      <c r="E407" s="3" t="inlineStr">
+      <c r="E407" s="0" t="inlineStr">
         <is>
           <t>주차장·자판기·안테나 등 부대수입 계약현황</t>
         </is>
       </c>
-      <c r="F407" s="3" t="inlineStr">
+      <c r="F407" s="0" t="inlineStr">
         <is>
           <t>駐車場・付帯収入の契約状況</t>
         </is>
       </c>
-      <c r="G407" s="3" t="inlineStr">
-        <is>
-          <t>부지 내 평면 자주식 주차장 다수(5~6대분 이상) 및 주기장 완비 (개별 계약 대수·요금 렌트롤 확인 필요)</t>
-        </is>
-      </c>
-      <c r="H407" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I407" s="3" t="inlineStr">
-        <is>
-          <t>표준산식 역산 추정</t>
-        </is>
-      </c>
-      <c r="J407" s="3" t="inlineStr">
-        <is>
-          <t>주차장 총 구획수, 현재 계약 대수 및 월 사용료 확인</t>
-        </is>
-      </c>
-      <c r="K407" s="3" t="inlineStr">
-        <is>
-          <t>駐車場区画数・契約台数およびその他付帯収入（自販機・アンテナ等）の内訳</t>
+      <c r="G407" s="0" t="inlineStr">
+        <is>
+          <t>없음 (전면도로 계단 직전까지 차량 접근 가능)</t>
+        </is>
+      </c>
+      <c r="H407" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I407" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤/개요서</t>
+        </is>
+      </c>
+      <c r="J407" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K407" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B408" s="2" t="inlineStr">
+      <c r="A408" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B408" s="0" t="inlineStr">
         <is>
           <t>CHK_22</t>
         </is>
       </c>
-      <c r="C408" s="2" t="inlineStr">
+      <c r="C408" s="0" t="inlineStr">
         <is>
           <t>5.경비/세금</t>
         </is>
       </c>
-      <c r="D408" s="2" t="inlineStr">
+      <c r="D408" s="0" t="inlineStr">
         <is>
           <t>disclosed_opex_yen</t>
         </is>
       </c>
-      <c r="E408" s="2" t="inlineStr">
+      <c r="E408" s="0" t="inlineStr">
         <is>
           <t>PM 관리위탁비 및 정기청소비 실비</t>
         </is>
       </c>
-      <c r="F408" s="2" t="inlineStr">
+      <c r="F408" s="0" t="inlineStr">
         <is>
           <t>PM管理委託費・定期清掃費</t>
         </is>
       </c>
-      <c r="G408" s="2" t="inlineStr">
-        <is>
-          <t>431300</t>
-        </is>
-      </c>
-      <c r="H408" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I408" s="2" t="inlineStr">
-        <is>
-          <t>미수령 (중개사 요청 필요)</t>
-        </is>
-      </c>
-      <c r="J408" s="2" t="inlineStr">
-        <is>
-          <t>현재 위탁 중인 PM 관리수수료율 및 정기청소비 월액 확인</t>
-        </is>
-      </c>
-      <c r="K408" s="2" t="inlineStr">
-        <is>
-          <t>現行のPM管理委託料率および定期清掃費等のランニングコスト明細のご共有</t>
+      <c r="G408" s="0" t="inlineStr">
+        <is>
+          <t>1130040</t>
+        </is>
+      </c>
+      <c r="H408" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I408" s="0" t="inlineStr">
+        <is>
+          <t>런닝코스트 명세</t>
+        </is>
+      </c>
+      <c r="J408" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K408" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B409" s="0" t="inlineStr">
@@ -41739,7 +41715,7 @@
       </c>
       <c r="G409" s="0" t="inlineStr">
         <is>
-          <t>공영수도 (公営水道) · 공공하수 (公共下水 — 정화조 유지비 없음)</t>
+          <t>공영수도·공공하수·무료WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정 확인완료)</t>
         </is>
       </c>
       <c r="H409" s="0" t="inlineStr">
@@ -41766,7 +41742,7 @@
     <row r="410">
       <c r="A410" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B410" s="0" t="inlineStr">
@@ -41796,7 +41772,7 @@
       </c>
       <c r="G410" s="0" t="inlineStr">
         <is>
-          <t>25008141</t>
+          <t>36985271</t>
         </is>
       </c>
       <c r="H410" s="0" t="inlineStr">
@@ -41821,66 +41797,66 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="0" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B411" s="0" t="inlineStr">
+      <c r="A411" s="3" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="inlineStr">
         <is>
           <t>CHK_25</t>
         </is>
       </c>
-      <c r="C411" s="0" t="inlineStr">
+      <c r="C411" s="3" t="inlineStr">
         <is>
           <t>5.경비/세금</t>
         </is>
       </c>
-      <c r="D411" s="0" t="inlineStr">
+      <c r="D411" s="3" t="inlineStr">
         <is>
           <t>fixed_tax_bldg_eval_yen</t>
         </is>
       </c>
-      <c r="E411" s="0" t="inlineStr">
+      <c r="E411" s="3" t="inlineStr">
         <is>
           <t>고정자산세 건물 과세평가액</t>
         </is>
       </c>
-      <c r="F411" s="0" t="inlineStr">
+      <c r="F411" s="3" t="inlineStr">
         <is>
           <t>固定資産税評価額（建物）</t>
         </is>
       </c>
-      <c r="G411" s="0" t="inlineStr">
-        <is>
-          <t>22273671</t>
-        </is>
-      </c>
-      <c r="H411" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I411" s="0" t="inlineStr">
-        <is>
-          <t>과세명세서</t>
-        </is>
-      </c>
-      <c r="J411" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K411" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G411" s="3" t="inlineStr">
+        <is>
+          <t>26627700</t>
+        </is>
+      </c>
+      <c r="H411" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I411" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J411" s="3" t="inlineStr">
+        <is>
+          <t>최신 연도 고정자산세·도시계획세 과세명세서(건물 평가액) 사본 요청</t>
+        </is>
+      </c>
+      <c r="K411" s="3" t="inlineStr">
+        <is>
+          <t>最新年度の固定資産税・都市計画税課税明細書（建物評価額）の写しのご共有</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B412" s="0" t="inlineStr">
@@ -41910,7 +41886,7 @@
       </c>
       <c r="G412" s="0" t="inlineStr">
         <is>
-          <t>431300</t>
+          <t>573,283엔 (R8 토지 공과증명서 주택특례 약 12.3만 엔 + 건물 오카다상 확인 약 45만 엔 추정)</t>
         </is>
       </c>
       <c r="H412" s="0" t="inlineStr">
@@ -41935,180 +41911,180 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B413" s="2" t="inlineStr">
+      <c r="A413" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B413" s="0" t="inlineStr">
         <is>
           <t>CHK_27</t>
         </is>
       </c>
-      <c r="C413" s="2" t="inlineStr">
+      <c r="C413" s="0" t="inlineStr">
         <is>
           <t>6.등기/내력</t>
         </is>
       </c>
-      <c r="D413" s="2" t="inlineStr">
+      <c r="D413" s="0" t="inlineStr">
         <is>
           <t>registry_owner_match</t>
         </is>
       </c>
-      <c r="E413" s="2" t="inlineStr">
+      <c r="E413" s="0" t="inlineStr">
         <is>
           <t>토지·건물 등기부 소유자 일치 여부</t>
         </is>
       </c>
-      <c r="F413" s="2" t="inlineStr">
+      <c r="F413" s="0" t="inlineStr">
         <is>
           <t>土地・建物登記簿の所有者一致</t>
         </is>
       </c>
-      <c r="G413" s="2" t="inlineStr">
-        <is>
-          <t>[미수집 - 등기부 미수령]</t>
-        </is>
-      </c>
-      <c r="H413" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I413" s="2" t="inlineStr">
-        <is>
-          <t>미수령 (중개사 요청 필요)</t>
-        </is>
-      </c>
-      <c r="J413" s="2" t="inlineStr">
-        <is>
-          <t>토지 및 건물 등기사항전부증명서(전부사항) 사본 요청</t>
-        </is>
-      </c>
-      <c r="K413" s="2" t="inlineStr">
-        <is>
-          <t>土地・建物の全部事項証明書（登記簿謄本）のご共有</t>
+      <c r="G413" s="0" t="inlineStr">
+        <is>
+          <t>검증완료: 야오키상사 주식회사(ヤオキ商事株式会社, R7.6.27 매매 취득, 149-3 및 231-102 2필지 일치)</t>
+        </is>
+      </c>
+      <c r="H413" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I413" s="0" t="inlineStr">
+        <is>
+          <t>등기사항전부증명서</t>
+        </is>
+      </c>
+      <c r="J413" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K413" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B414" s="2" t="inlineStr">
+      <c r="A414" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B414" s="0" t="inlineStr">
         <is>
           <t>CHK_28</t>
         </is>
       </c>
-      <c r="C414" s="2" t="inlineStr">
+      <c r="C414" s="0" t="inlineStr">
         <is>
           <t>6.등기/내력</t>
         </is>
       </c>
-      <c r="D414" s="2" t="inlineStr">
+      <c r="D414" s="0" t="inlineStr">
         <is>
           <t>registry_history_갑구</t>
         </is>
       </c>
-      <c r="E414" s="2" t="inlineStr">
+      <c r="E414" s="0" t="inlineStr">
         <is>
           <t>과거 소유권 변천내력(갑구) 및 매각동기</t>
         </is>
       </c>
-      <c r="F414" s="2" t="inlineStr">
+      <c r="F414" s="0" t="inlineStr">
         <is>
           <t>所有権移転履歴・売却理由</t>
         </is>
       </c>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>[미수집 - 등기부 미수령]</t>
-        </is>
-      </c>
-      <c r="H414" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I414" s="2" t="inlineStr">
-        <is>
-          <t>미수령 (중개사 요청 필요)</t>
-        </is>
-      </c>
-      <c r="J414" s="2" t="inlineStr">
-        <is>
-          <t>현 소유자의 취득 경위 및 금번 매각 사유 확인</t>
-        </is>
-      </c>
-      <c r="K414" s="2" t="inlineStr">
-        <is>
-          <t>現所有者様の取得経緯および今回のご売却理由のご教示</t>
+      <c r="G414" s="0" t="inlineStr">
+        <is>
+          <t>검증완료: S32/S57 개인취득 → H9 상속 → H15 매매 → R7.6.27 야오키상사(주) 신축분양 목적 매입</t>
+        </is>
+      </c>
+      <c r="H414" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I414" s="0" t="inlineStr">
+        <is>
+          <t>등기부 갑구/중개사</t>
+        </is>
+      </c>
+      <c r="J414" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K414" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B415" s="2" t="inlineStr">
+      <c r="A415" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B415" s="0" t="inlineStr">
         <is>
           <t>CHK_29</t>
         </is>
       </c>
-      <c r="C415" s="2" t="inlineStr">
+      <c r="C415" s="0" t="inlineStr">
         <is>
           <t>6.등기/내력</t>
         </is>
       </c>
-      <c r="D415" s="2" t="inlineStr">
+      <c r="D415" s="0" t="inlineStr">
         <is>
           <t>registry_liens_을구</t>
         </is>
       </c>
-      <c r="E415" s="2" t="inlineStr">
+      <c r="E415" s="0" t="inlineStr">
         <is>
           <t>담보권·근저당·압류·지역권 유무(을구)</t>
         </is>
       </c>
-      <c r="F415" s="2" t="inlineStr">
+      <c r="F415" s="0" t="inlineStr">
         <is>
           <t>抵当権・地役権等の権利関係</t>
         </is>
       </c>
-      <c r="G415" s="2" t="inlineStr">
-        <is>
-          <t>[미수집 - 등기부 미수령]</t>
-        </is>
-      </c>
-      <c r="H415" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I415" s="2" t="inlineStr">
-        <is>
-          <t>미수령 (중개사 요청 필요)</t>
-        </is>
-      </c>
-      <c r="J415" s="2" t="inlineStr">
-        <is>
-          <t>등기부 을구 권리관계 및 말소 조건 확인</t>
-        </is>
-      </c>
-      <c r="K415" s="2" t="inlineStr">
-        <is>
-          <t>登記簿乙区の権利関係および引渡時抹消条件の確認</t>
+      <c r="G415" s="0" t="inlineStr">
+        <is>
+          <t>검증완료: R7.6.27 카와사키신용금고(登戸支店) 채권액 7,700만 엔·금리 연 3.050% 공동담보 근저당 설정 (인도 시 말소 조건)</t>
+        </is>
+      </c>
+      <c r="H415" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I415" s="0" t="inlineStr">
+        <is>
+          <t>등기부 을구</t>
+        </is>
+      </c>
+      <c r="J415" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K415" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B416" s="0" t="inlineStr">
@@ -42138,7 +42114,7 @@
       </c>
       <c r="G416" s="0" t="inlineStr">
         <is>
-          <t>98000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="H416" s="0" t="inlineStr">
@@ -42165,7 +42141,7 @@
     <row r="417">
       <c r="A417" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B417" s="0" t="inlineStr">
@@ -42195,7 +42171,7 @@
       </c>
       <c r="G417" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>실측 도보 10분 (구글맵 및 오카다상 현장 확인완료)</t>
         </is>
       </c>
       <c r="H417" s="0" t="inlineStr">
@@ -42222,7 +42198,7 @@
     <row r="418">
       <c r="A418" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B418" s="0" t="inlineStr">
@@ -42252,7 +42228,7 @@
       </c>
       <c r="G418" s="0" t="inlineStr">
         <is>
-          <t>완전 평탄지 (표고 7.5m, 공원교도리·학교도리 직선 간선도로 동선, 카스카베 소학교 교차점 코너)</t>
+          <t>사사노다이 상점가 경유 후 남서측 전면도로(下川井第402号線) 진입부에 계단 구간 및 부지 고저차(4.0~4.69m) 존재 확인완료</t>
         </is>
       </c>
       <c r="H418" s="0" t="inlineStr">
@@ -42279,7 +42255,7 @@
     <row r="419">
       <c r="A419" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B419" s="0" t="inlineStr">
@@ -42309,7 +42285,7 @@
       </c>
       <c r="G419" s="0" t="inlineStr">
         <is>
-          <t>카스카베시 홍수 해저드맵(L2 최대강우) 침수심 0.5m~3.0m 미만 상정 구역 (수도권 외곽방수로 인접 / 화재보험 수재 특약 필수 반영 완료)</t>
+          <t>고대(高台) 입지로 홍수·내수 침수 해저드 해당 없음 (교차검증 완료)</t>
         </is>
       </c>
       <c r="H419" s="0" t="inlineStr">
@@ -42336,7 +42312,7 @@
     <row r="420">
       <c r="A420" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B420" s="0" t="inlineStr">
@@ -42366,7 +42342,7 @@
       </c>
       <c r="G420" s="0" t="inlineStr">
         <is>
-          <t>해당 없음 (평지 상업지역 — 토사재해 경계구역 외)</t>
+          <t>부지 북서측 모서리 옹벽 부분(가측량도 약 4.69㎡)이 토사재해경계구역(옐로우존/잠정 레드존 경계)에 일부 저촉 확인완료 (건물 본체는 2m 이격되어 구역 외)</t>
         </is>
       </c>
       <c r="H420" s="0" t="inlineStr">
@@ -42393,7 +42369,7 @@
     <row r="421">
       <c r="A421" s="0" t="inlineStr">
         <is>
-          <t>espoir-cross-kasukabe</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B421" s="0" t="inlineStr">
@@ -42423,7 +42399,7 @@
       </c>
       <c r="G421" s="0" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30~45일 (REINS 근린 성약 50건 및 일 피오레 사사노다이 교차검증 완료)</t>
         </is>
       </c>
       <c r="H421" s="0" t="inlineStr">
@@ -51438,7 +51414,7 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>espoir-cross-kasukabe</t>
         </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
@@ -51448,847 +51424,15 @@
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>에그제큐티브 서머리 (Executive Summary)</t>
+          <t>1. 투자 하이라이트 및 핵심 요약 (Executive Summary)</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>エグゼクティブ・サマリー (Executive Summary)</t>
+          <t>1. 投資ハイライトおよびエグゼクティブ・サマリー</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr">
-        <is>
-          <t>본 보고서는 가나가와현 요코하마시 아사히구 사사노다이 2초메(神奈川県横浜市旭区笹野台2丁目149番3、231番102)에 신축 중인 1동 수익형 목조 2층 공동주택 **「미츠쿄 1AP 사사노다이 신축 아파트 (三ツ境1AP 新築アパート)」**(총 9세대: 1층 5세대, 2층 4세대)의 매입 타당성을 검토하기 위해 작성된 기관 투자자 및 자산운용사 수준의 정밀 실사(Due Diligence) 보고서입니다.
-본 물건은 소테츠 본선(相鉄本線, **급행·통근급행 정차역** 및 JR·도큐 직통선 연결) **「미츠쿄(三ツ境)」역 도보 7분**(실측 약 550m, 역 북측 사사노다이 상점가를 경유하는 평탄·완만한 생활 밀착형 동선)의 준역세권에 위치합니다. 무엇보다 본 물건의 가장 강력한 투자 매력은 다음의 **4대 구조적 경쟁 우위(Structural Moats)**에 있습니다:
-1. **약 120.3평(397.71㎡)의 압도적 토지 면적 및 공적 적산 비율 88.4%(공시지가 기준 110.4%)의 강력한 하방 담보력**:
-   - 일반 신축 목조 아파트가 50~70평 토지에 협소 원룸을 빽빽하게 채워 토지 적산비율이 25~35%에 불과한 것과 달리(제1매물 카와시마초: 토지 71.1평, 토지 적산비율 28.2%), 본 물건은 제1종 저층주거전용지역(건폐율 40% / 용적률 80%) 내 **397.71㎡(120.30평, 유효부지 397.42㎡)**의 광활한 정형 택지를 확보하고 있습니다.
-   - 노선가(추정 19.0만 엔/㎡) 기준 **토지 적산가액만 7,551.0만 엔(매매가의 56.06%)**에 달하며, 국세청 표준 건물 적산(242.07㎡ × 18만 엔/㎡ = 4,357.3만 엔)을 합산한 **표준 총 적산가액은 1억 1,908.2만 엔(매매가 대비 88.41%)**, 공시지가(24.0만 엔/㎡) 및 신축 원가 기준 시 **1억 4,863.6만 엔(매매가 대비 110.35%)**으로 매매가를 상회합니다.
-2. **『설계주택성능평가 열화대책등급 3급 취득 완료』 및 『건설주택성능평가 열화대책등급 3급 취득 예정』의 더블 인증 (최장 30~35년 융자 100% 적격)**:
-   - 개요서 및 건축확인필증(제26UDI1K건00271호, 2026년 6월 18일 교부) 검증 결과, 이미 **설계주택성능평가서상 최고 등급인 『열화대책등급 3급(劣化対策等級3級)』을 정식 취득 완료**하였으며 준공 시 건설주택성능평가 3급까지 취득 예정입니다. 이에 따라 대다수 금융기관에서 **목조 신축 최장 30년~35년 장기 저리 융자(금리 2.0~2.5%)**를 이견 없이 승인받을 수 있어, 30년 융자(LTV 85%, 금리 2.3%) 시 **만실 세전 CF +158.3만 엔/년(월 +13.2만 엔), DSCR 1.30배, 손익분기 가동률 81.93%(허용 공실 1.63실/9실)**의 안정적 현금흐름을 창출합니다.
-3. **세대당 평균 연면적 26.89㎡(약 25.5~27.5㎡급 1K/1DK/1LDK 상당)의 광폭 평면 및 무료 WIFI·도시가스 완비**:
-   - 연면적 242.07㎡(73.22평)에 단 9세대만 배치하여 **세대당 평균 면적이 26.89㎡**에 달합니다. 이는 제1매물(카와시마초: 세대당 18.54㎡)보다 **세대당 면적이 +45.0% 더 넓은** 설계로, 재택근무 사회인·성인 단신자·신혼/동거 수요까지 흡수할 수 있으며, **㎡당 월 임대료 단가는 3,016엔/㎡**로 카와시마초(3,435엔/㎡)보다 오히려 **12.2% 저렴**하여 임대 경쟁력과 장기 정착성이 월등히 뛰어납니다.
-4. **법인 결산서(모아비즈 4기 기준) 편입 시 전 재무지표의 비약적 개선**:
-   - 본 물건을 법인 결산서에 편입할 경우(안정화 가동률 93%, 30년 융자 기준), 법인 합산 **세전 당기순이익이 372.2만 엔 → 657.4만 엔(+76.6% 급증)**, **세후 잉여 CF가 81.1만 엔 → 132.9만 엔(+63.8% 증가)**으로 확대되며, 기존 법인의 취약점이었던 **이자보상배율(ICR)이 0.90배 → 1.04배로 단숨에 1.0배를 돌파**하고, **고정자산세 평가 기준 LTV는 261.08% → 219.39%(▲41.69%p 대폭 개선)**로 낮아져 차기 추가 대출 한도를 크게 넓혀줍니다.
-다만, 계약 전 반드시 검증·보완해야 할 **3대 리스크 및 실사 과제**는 다음과 같습니다:
-1. **남서측 폭원 약 4.0m 도로의 『공도·사도(公道・私道) 혼재』에 따른 사도 지분 및 통행·굴착 승낙 확인**: 본 부지(149번3, 231번102의 2필지)가 접하는 남서측 4m 도로가 공도와 사도로 구성되어 있으므로, 사도 구간의 건축기준법상 도로 종별(42조 1항 2호 개발도로·3호 기존도로·5호 위치지정도로 또는 2항 도로) 및 사도 공유지분·무상 굴착승낙서 유무를 확인해야 합니다.
-2. **매매가격(1억 3,470만 엔) 내 토지·건물 가액 배분 비율 미기재**: 개요서상 총액(13,470만 엔, 소비세 포함)만 표기되어 있고 토지·건물 내역이 기재되어 있지 않습니다. 120.3평의 높은 토지 가치를 감안하더라도 감가상각 절세 효과를 극대화하기 위해 매도자(야오키상사)와의 매매계약서 작성 시 **건물 비중을 합리적 범위 내(예: 건물 5,500만~6,050만 엔[41~45%], 토지 7,420만~7,970만 엔[55~59%])로 협의 확정**해야 합니다.
-3. **표면수익률 6.50%(실질 Cap Rate 5.10%)의 호가 수준**: 토지 가치와 열화 3급 가치를 반영하여 호가 수익률이 6.50%로 책정되어 있으므로, **1억 2,600만 ~ 1억 2,900만 엔(표면 6.79% ~ 6.95%, Cap Rate 5.33% ~ 5.45%)**을 목표로 지값 협상을 진행할 경우 수익성과 자산가치를 동시에 극대화할 수 있습니다.
-결론적으로 본 물건은 동시에 검토한 2개 매물 중 **압도적 우위를 점하는 최우선 추천 매물**이며, 남서측 도로 권리 확인 및 토지·건물 가액 배분 협의, 1.26억~1.29억 엔 지값 협상을 전제로 한 **【조건부 추천 / 우량 편입 대상 (Conditional Recommendation: 22.5 / 30점)】**으로 최종 판정합니다.
----
-### 주요 지표 요약 (Key Metrics)
-| 항목 | 수치 | 비고 |
-| :--- | ---: | :--- |
-| **매매가격 (物件価格)** | **13,470.0만 엔** | 소비세 포함 (토지 7,947.3만[59.0%] / 건물 5,522.7만[41.0%] 표준안 기준) |
-| **현황 연간수입 (現況年収入)** | **0.0만 엔** | 신축 건축 중 (2026년 6월 확인필증 교부 ~ **2026년 11월 말 인도 예정**) |
-| **만실 상정 연간수입 (満室想定年収入)** | **876.0만 엔** | 월 730,000엔 (전 9세대, 세대당 평균 **81,111엔/월**, 공익비 포함) |
-| **만실 상정 표면수익률 (満室想定利回り)** | **6.50%** | 개요서 표기 6.50%(876만 ÷ 13,470만 = 6.503%)와 완벽 일치 |
-| **토지 공적 적산가액 (路線価積算)** | **7,551.0만 엔** | 유효부지 **397.42㎡(120.22평)** × 노선가 추정 19.0만 엔/㎡ (**매매가의 56.06%!**) |
-| **건물 표준 적산가액 (建物積算)** | **4,357.3만 엔** | 242.07㎡ × 18만 엔/㎡ × 신축(22/22년) → **합산 적산 11,908.2만 엔 (88.41%!)** |
-| **실질 연간경비 (実質年間経費, OPEX)** | **189.0만 엔** | 고도세(58만) + PM·청소·무료WIFI(68만) + 보험·원상복구·수선충당(63만, **경비율 21.58%**) |
-| **순영업소득 (純営業収益, NOI)** | **687.0만 엔** | 만실 기준 실질 OPEX 공제 후 (93% 가동 기준 시 622.6만 엔) |
-| **실질 Cap Rate (NOI 利回り)** | **5.10%** | 호가 1억 3,470만 엔 기준 (1억 2,700만 엔 네고 시 **5.41%**) |
-| **차입금 상정 (融資金, LTV 85%)** | **11,449.5만 엔** | **열화대책등급 3급 확정** 기반 **30년 융자** (금리 2.3% 원리금균등 상정) |
-| **연간 원리금상환액 (ADS, 30년/2.3%)** | **528.7만 엔** | 월 440,582엔 (35년 융자 승인 시 연 **476.3만 엔**으로 추가 경감) |
-| **연간 캐시플로 (세전 CF, 30년 상환)** | **158.3만 엔** | 세전 CF 수익률 1.18% (1.27억 네고 시 **+188.5만 엔 / 1.48%**) |
-| **부채상환배율 (DSCR)** | **1.30배** | 만실 기준 **1.30배** (결산서 기준 1.52배)로 안전기준(1.20배) 안정적 상회 |
-| **손익분기 가동률 (損益分岐稼働率)** | **81.93%** | 허용 공실 수: **1.63실 / 전체 9실** (9실 중 7.4실 가동 시 흑자 유지) |
-| **초기 필요 자기자금 (Equity)** | **3,149.7만 엔** | 두금(2,020.5만) + 제비용(1,129.2만, 소비세 환급 전 보수적 기준) |
-| **자기자본수익률 (CCR)** | **5.03%** | 만실 세전 CF 기준 (1.27억 엔 네고 시 **6.35%**, 35년 융자 시 **6.68%**) |
-| **잠재 임대료 증액 여지 (賃上げ余地)** | **연 0 ~ 10.8만 엔** | ㎡당 단가(3,016엔/㎡)가 합리적이어서 장기 임대료 하방 경직성 매우 우수 |
----
-### 1.2 결산서 디자인형 판정 (Output &amp; Key Metrics)
-#### 【A. 외부 공개용 표준 양식 (External Dossier)】
-&gt; ※ 본 분석은 법인의 재무 건전성 및 금융기관 추가 여신 한도 극대화를 위해, 본 부동산 단품 취득 시(안정화 가동률 93%, LTV 85%, 금리 2.3%, 열화대책 3급 기반 30년 상환 기준) 법인 결산서(손익계산서 및 대차대조표)에 미치는 핵심 재무 지표를 정밀 검증한 결과입니다.
-| 항목 (Key Metrics) | 검증대상 부동산 (단품 실적) | 지표 정의 및 결산서 디자인상의 의미 (Description &amp; Financial Significance) |
-| :--- | :---: | :--- |
-| **1. 장부상 세전순이익** | **약 285.2만 엔** | 안정화 가동(93%) 영업수익에서 관리운영비, 초년도 지급이자(259.9만) 및 신축 목조 감가상각비(22년 상각, 연 251.0만)를 차감한 회계상 순이익. **대규모 흑자 결산 기여.** |
-| **2. 세전 현금흐름 (Pre-tax CF)** | **123.1만 엔 (0.91%)** | 안정화 가동(93%) 시 원리금상환(ADS 528.7만) 차감 후 잔여 현금흐름 (**만실 100% 가동 시 158.3만 엔 / 1.18%**). |
-| **3. 추정 법인세액 (25% 과세 가정)** | **약 71.3만 엔** | 장부상 세전순이익(285.2만)에 대한 법인세 추정액. 신축 22년 감가상각비(연 251.0만 엔)로 과세표준을 안정적으로 방어. |
-| **4. 세후 현금흐름 (Post-tax CF)** | **약 51.8만 엔 (0.38%)** | 93% 가동 및 법인세 납부 후에도 순증하는 세후 현금흐름 (만실 가동 시 세후 약 78.2만 엔, 1.27억 네고 시 만실 세후 약 101만 엔). |
-| **5. 채무상환년수 (Debt Coverage)** | **24.3년** | 차입금(1억 1,449.5만) ÷ (세후순이익 213.9만 + 감가상각비 251.0만). **융자 기간(30년)보다 5.7년 짧은 24.3년**으로 골든크로스($C \le B$) 완벽 달성. |
-| **6. 이자보상배율 (ICR)** | **1.51배 (NOI 기준 2.51배)** | 영업이익(393.3만) ÷ 지급이자(259.9만). 감가상각 후 영업이익 기준 **1.51배**의 우량한 이자 커버리지 확보. |
-| **7. 부채상환배율 (DSCR)** | **1.30배 (만실) / 1.52배 (결산기준)** | 실질 OPEX 전부 반영 시에도 1.30배, 결산서 경비 기준 **1.52배**로 금융기관 안전 기준(1.20배)을 크게 상회. |
-| **8. 담보평가 LTV (고정자산세 기준)** | **164.25%** | 차입금(1억 1,449.5만) ÷ 공적 과세평가액(토지 397.42㎡×0.7 + 건물 = **6,968.8만 엔**). **120.3평 대토지 보유로 신축 목조 중 이례적으로 낮은 우량 LTV 기록!** |
-| **9. 자기자본수익률 (CCR / Cash-on-Cash)**| **5.03% (만실 30년)** | 만실 세전 CF(158.3만) ÷ 초기 자기자본(3,149.7만). 1.27억 네고 시 **6.35%**로 상승. |
----
-#### 【B. 모아비즈 내부 전용 비교 착지 양식 (Moabiz Internal)】
-| 항목 (指標項目) | 검증대상 부동산 단품 | 모아비즈 4기 현재 (Col G) | 검증대상 부동산 매입후결산서 착지 예상 |
-| :--- | :---: | :---: | :---: |
-| **1. 帳簿上税引前当期純利益 (장부상 세전순이익)** | **¥2,851,692** | ¥3,722,450 | **¥6,574,142** (**+76.6% 급증**) |
-| **2. 税引前手残りCF (세전 잔여 현금흐름)** | **¥1,231,095** | ¥1,741,901 | **¥2,972,996** (**+70.7% 확대**) |
-| 　・**税引前CF利回り (세전 CF 수익률)** | **0.91%** | 0.65% | **0.74%** (+9bp 개선) |
-| 　・**推定法人税額 (추정 법인세액)** | **¥712,923** | ¥930,613 | **¥1,643,536** |
-| 　・**税引後手残りCF (세후 잔여 현금흐름)** | **¥518,172** | ¥811,289 | **¥1,329,461** (**+63.8% 확대**) |
-| 　・**税引後CF利回り (세후 CF 수익률)** | **0.38%** | 0.30% | **0.33%** (+3bp 개선) |
-| **3. 債務償還年数 (채무상환년수, 년)** | **24.3년** | 24.1년 | **24.2년** (**30년 이내 완벽 유지**) |
-| **4. 簡易 Cash Flow (=税引後CF)** | **¥518,172** | ¥811,289 | **¥1,329,461** (약 1.64배 확대) |
-| **5. ICR (이자보상배율, Interest Coverage Ratio)** | **1.51배** | 0.90배 | **1.04배** (**+0.14배 개선 · 1.0배 돌파 달성!**) |
-| **6. 負債返済割合 (DSCR / 부채상환배율)** | **1.52배** | 1.50배 | **1.51배** (**+0.01배 개선 · 초우량 유지**) |
-| **7. LTV (固定資産税評価額に基づく / 고정자산세 기준)**| **164.25%** | 261.08% | **219.39%** (**▲41.69%p 획기적 개선!**) |
-| **8. 投資額ROI (초기 투하자기자본 대비 ROI / CCR)** | **3.91% (93% 가동)** | 3.83% | **3.86%** (+3bp 개선, 만실 시 5.03%) |
-| **9. 法人貢献総合判定 (부동산 종합 투자 적격성 판정)** | **우량 기여 (전 지표 통과)** | 기준선 (ICR 0.9배, LTV 261% 취약) | **편입 적극 권장 (ICR 1.0배 돌파 &amp; LTV 41.7%p 개선)** |
----
-### 평가 서머리 (Evaluation Summary)
-| 평가축 | 판정 | 근거 |
-| :--- | :---: | :--- |
-| **가격 타당성** | **적정 ~ 소폭 협상 여지** | 호가 1억 3,470만 엔(표면 6.50%)은 **표준 적산가액(1억 1,908만 엔, 88.4%)** 및 **공시지가 적산(1억 4,864만 엔, 110.4%)**으로 뒷받침되어 자산가치 대비 타당성이 높음. 1.26억~1.29억 엔 네고 시 최상급 딜. |
-| **임대료 수준** | **합리적 (경쟁력 우수)** | 세대당 평균 26.89㎡에 월 7.8만~8.5만 엔(평균 8.11만 엔, **㎡당 3,016엔/㎡**)은 미츠쿄역 도보 7분·신축·무료 WIFI 조건 대비 매우 합리적이며 인근 구축(일 피오레, 축 11년) 성약 시세와도 부합. |
-| **수익의 질** | **우량 (광폭 9세대 구성)** | 18㎡ 협소 원룸이 아닌 약 26~27㎡급 여유로운 평면으로 성인 단신자·재택근무자·커플 수요의 장기 거주(평균 3.5~4.5년)가 기대됨. |
-| **건물 상태** | **최우량 (2026.11 신축 / 열화 3급)**| 야오키상사(창업 50년 이상 목조 기획 개발사) 공급, **설계주택성능평가 열화대책등급 3급 취득 완료 &amp; 건설주택성능평가 3급 예정**으로 최고 수준의 물리적·제도적 내구성 확보. |
-| **수익 구조** | **안정적 (DSCR 1.30배)** | 열화대책 3급을 통한 30년 장기 융자(금리 2.3%) 조달 시 만실 세전 CF +158.3만 엔, 손익분기 가동률 81.9%로 안정적 캐시플로 창출. |
-| **미래 가치** | **매우 우수 (120.3평 역세권 택지)**| 미츠쿄역(급행 정차) 도보 7분의 **120.3평(397.71㎡) 대토지**는 향후 15~20년 뒤 중고 수익형 매각뿐만 아니라 **호별 분양 신축 부지(3~4필지 분할 매각)로의 출구 전략(Land Exit)**까지 가능한 핵심 자산. |
-| **금융/대출** | **최우량 (열화 3급 더블 인증)** | 설계·건설주택성능평가서(열화대책등급 3급) 완비 및 높은 토지 담보평가(적산 88.4%) 덕분에 제1금융권·지방은행·신협 등에서 30~35년 풀레버리지에 가까운 우대 융자 심사 가능. |
----
-### 선행 확인 필수 5대 항목 (Top 5 Due Diligence Action Items)
-- [ ] **1. 남서측 폭원 약 4.0m 도로의 『공도·사도(公道・私道)』 구간별 건축기준법상 종별 및 사도 지분·통행굴착승낙서 확인**: 본 부지(`149-3`, `231-102`)가 접하는 남서측 도로 중 사도 부분의 소유권 지분이 매매대상에 포함되는지, 상하수도·도시가스 인입을 위한 무상 통행·굴착 승낙서가 완비되었는지 최우선 확인.
-- [ ] **2. 실시설계 도면 일식(배치도·각층 평면도·입면도), 토지 등기부등본(2필지) 및 확정측량도 징구**: 개요서와 건축확인필증(제26UDI1K건00271호) 외에 호실별 정확한 전유면적·간취(1K/1DK/1LDK) 도면과 부지 내 고저차·옹벽 유무를 확인하기 위한 설계도서를 매도자(야오키상사/무브업)로부터 수령.
-- [ ] **3. 매매계약서상 『토지·건물 가액 배분 비율(土地・建物売買代金内訳)』 협의 확정**: 법인의 연간 감가상각비(절세 효과)와 소비세 환급·부동산취득세에 직접 영향을 미치므로, 매도자 측과 건물 가액을 **약 5,500만~6,000만 엔(소비세 포함, 전체의 41~45%)** 수준으로 설정 가능한지 사전 협의.
-- [ ] **4. 『설계주택성능평가서(열화대책등급 3급)』 사본 수령 및 거래 금융기관 30~35년 융자 사전 타진**: 이미 취득 완료된 설계주택성능평가서 사본과 건축확인필증을 금융기관에 제출하여 **기간 30~35년, 금리 2.0~2.3%대**의 우대 조건 승인을 확보.
-- [ ] **5. 2026년 11월 말 준공 전 선행 임차인 모집(리싱) 개시 일정 및 무료 WIFI 월간 런닝코스트 확인**: 11월 말 인도에 맞춰 9~10월부터 선행 임차인 모집을 개시하여 인도 시점 만실(또는 초기 AD 매도자 부담)을 유도하고, 무료 인터넷(WIFI) 설비의 월 이용료(예상 월 1.0~1.3만 엔) 및 계약 승계 조건을 확인.
----</t>
-        </is>
-      </c>
-      <c r="F102" s="0" t="inlineStr">
-        <is>
-          <t>本レポートは、神奈川県横浜市旭区笹野台2丁目149番3、231番102に新築中の1棟収益木造2階建共同住宅 **「三ツ境1AP 新築アパート」**（全9戸：1階5戸、2階4戸）の取得妥当性を検証するため、機関投資家およびアセットマネジメント水準の基準に基づき作成された精密デューデリジェンス（DD）レポートです。
-本物件は、相鉄本線（**急行・通勤急行停車駅**、JR・東急直通線乗入）**「三ツ境」駅 徒歩7分**（実測約550m、駅北口の笹野台商店街を経由する平坦・緩やかな生活密着動線）の準駅近エリアに位置します。とりわけ本物件の最大の投資魅力は、以下の**4大構造的競争優位（Structural Moats）**にあります：
-1. **約120.3坪（397.71㎡）の圧倒的土地面積および公的積算比率88.4%（公示地価基準110.4%）の強固な下値担保力**:
-   - 一般的な新築木造アパートが50〜70坪の敷地に狭小ワンルームを詰め込み土地積算比率が25〜35%に留まるのに対し（第1物件・川島町：土地71.1坪、土地積算比率28.2%）、本物件は第一種低層住居専用地域（建蔽率40%／容積率80%）内の**397.71㎡（120.30坪、有効敷地397.42㎡）**という広大な宅地を確保しています。
-   - 路線価（推定19.0万円/㎡）基準で**土地積算評価額だけで7,551.0万円（売買価格の56.06%）**に達し、国税庁標準建物積算（242.07㎡ × 18万円/㎡ ＝ 4,357.3万円）を合算した**標準総積算価格は1億1,908.2万円（売買価格比88.41%）**、公示地価（24.0万円/㎡）および新築原価基準では**1億4,863.6万円（売買価格比110.35%）**と売出価格を上回ります。
-2. **『設計住宅性能評価 劣化対策等級3級 取得済』および『建設住宅性能評価 劣化対策等級3級 取得予定』のダブル評価書取得（最長30〜35年融資100%適格）**:
-   - 物件概要書および建築確認済証（第26UDI1K建00271号、令和8年6月18日交付）の検証により、既に**設計住宅性能評価書において最高等級である『劣化対策等級3級』を正式取得済**であり、竣工時には建設住宅性能評価3級も取得予定です。これにより大多数の金融機関で**木造新築最長30年〜35年の長期低利融資（金利2.0〜2.5%）**を確実に引き出すことができ、30年融資（LTV 85%、金利2.3%）時に**満室税引前CF +158.3万円/年（月+13.2万円）、DSCR 1.30倍、損益分岐稼働率81.93%（許容空室1.63戸/9戸）**の安定したキャッシュフローを創出します。
-3. **1戸あたり平均延床26.89㎡（専有約25.5〜27.5㎡級の広々1K/1DK/1LDK相当）および無料WIFI・都市ガス完備**:
-   - 延床面積242.07㎡（73.22坪）にわずか9戸のみをゆったりと配棟しており、**1戸あたり平均面積は26.89㎡**に達します。これは第1物件（川島町：1戸平均18.54㎡）より**住戸面積が+45.0%広く**、在宅勤務の社会人・単身者からカップル・新婚層まで幅広い需要を吸収できる上、**㎡あたり月額賃料単価は3,016円/㎡**と川島町（3,435円/㎡）よりむしろ**12.2%割安**であり、リーシング競争力と長期定着性に優れています。
-4. **法人決算書（モアビズ4期基準）編入時における全財務指標の飛躍的改善**:
-   - 本物件を法人決算書に編入した場合（安定稼働率93%、30年融資基準）、法人合算の**税引前当期純利益は372.2万円 → 657.4万円（+76.6%急増）**、**税引後手残りCFは81.1万円 → 132.9万円（+63.8%増加）**へ拡大し、既存法人の課題であった**利子負担率（ICR）が0.90倍 → 1.04倍へと一気に1.0倍を突破**、さらに**固定資産税評価基準LTVは261.08% → 219.39%（▲41.69%pの劇的改善）**へと大幅に良化し、次案件への追加与信枠を大きく広げます。
-ただし、契約前に必ず検証・補完すべき**3つのリスクおよびDD課題**は以下の通りです：
-1. **南西側幅員約4.0m道路の『公道・私道混在』に伴う私道持分および通行・掘削承諾の確認**: 本敷地（149番3、231番102の2筆）が接道する南西側4m道路が「公道・私道」で構成されているため、私道区間の建築基準法上の道路種別（42条1項2号開発道路・3号既存道路・5号位置指定道路または2項道路）および私道持分の有無・無償掘削承諾書の有無を確認する必要があります。
-2. **売買価格（1億3,470万円）における土地・建物価格内訳の未記載**: 物件概要書には総額（13,470万円、税込）のみが表記されており、土地・建物の内訳が記載されていません。120.3坪の高い土地価値を考慮しつつも、減価償却による節税効果を最大化するため、売主（ヤオキ商事）との売買契約書作成時に**建物比率を合理的範囲内（例：建物5,500万〜6,050万円［41〜45%］、土地7,420万〜7,970万円［55〜59%］）で協議確定**する必要があります。
-3. **表面利回り6.50%（実質Cap Rate 5.10%）の売出価格水準**: 高い土地価値と劣化対策3級のプレミアムを反映して表面6.50%で売り出されているため、**1億2,600万 〜 1億2,900万円（表面6.79% 〜 6.95%、Cap Rate 5.33% 〜 5.45%）**を目標に指値交渉を行うことで、収益性と資産価値を同時に極大化できます。
-結論として、本物件は同時検討した2物件の中で**圧倒的優位に立つ最優先推奨物件**であり、南西側道路の権利確認および土地・建物内訳協議、1.26億〜1.29億円への指値交渉を前提とした**【条件付推奨／優良編入対象（Conditional Recommendation：22.5 / 30点）】**と最終判定いたします。
----
-### 主要指標サマリー (Key Metrics)
-| 項目 | 数値 | 備考 |
-| :--- | ---: | :--- |
-| **売買価格 (物件価格)** | **13,470.0万円** | 消費税込（土地7,947.3万[59.0%] / 建物5,522.7万[41.0%]の標準配分基準） |
-| **現況年間収入** | **0.0万円** | 新築建築中（2026年6月確認済証交付 〜 **2026年11月末引渡予定**） |
-| **満室想定年間収入 (GPI)** | **876.0万円** | 月額730,000円（全9戸、1戸平均 **81,111円/月**、共益費込） |
-| **満室想定表面利回り** | **6.50%** | 物件概要書表記6.50%（876万 ÷ 13,470万 = 6.503%）と完全一致 |
-| **土地公的積算評価 (路線価)** | **7,551.0万円** | 有効敷地 **397.42㎡(120.22坪)** × 推定路線価19.0万円/㎡（**売買価格の56.06%！**） |
-| **建物標準積算評価** | **4,357.3万円** | 242.07㎡ × 18万円/㎡ × 新築(22/22年) → **合計積算11,908.2万円 (88.41%！)** |
-| **実質年間経費 (OPEX)** | **189.0万円** | 固都税(58万) + PM・清掃・無料WIFI(68万) + 保険・原状回復・修繕積立(63万、**経費率21.58%**) |
-| **純営業収益 (NOI)** | **687.0万円** | 満室基準の実質OPEX控除後（93%稼働基準時は622.6万円） |
-| **実質Cap Rate (NOI利回り)** | **5.10%** | 売出価格1億3,470万円基準（1億2,700万円指値時は**5.41%**） |
-| **借入金想定 (LTV 85%)** | **11,449.5万円** | **劣化対策等級3級確定**に基づく **30年融資**（金利2.3%元利均等想定） |
-| **年間元利返済額 (ADS, 30年/2.3%)** | **528.7万円** | 月額440,582円（35年融資承認時は年**476.3万円**へさらに軽減） |
-| **年間キャッシュフロー (税引前CF, 30年)** | **158.3万円** | 税引前CF利回り1.18%（1.27億指値時は**+188.5万円 / 1.48%**） |
-| **負債返済倍率 (DSCR)** | **1.30倍** | 満室基準 **1.30倍**（決算書基準1.52倍）で安全基準(1.20倍)を安定超過 |
-| **損益分岐稼働率 (BEP)** | **81.93%** | 許容空室数：**1.63戸 / 全9戸**（9戸中7.4戸稼働で黒字維持） |
-| **初期必要自己資金 (Equity)** | **3,149.7万円** | 頭金(2,020.5万) + 諸費用(1,129.2万、消費税還付前の保守的基準) |
-| **自己資本配当率 (CCR)** | **5.03%** | 満室税引前CF基準（1.27億円指値時は**6.35%**、35年融資時は**6.68%**） |
-| **潜在賃料増額余地** | **年0 〜 10.8万円** | ㎡単価(3,016円/㎡)が合理的であり長期的な賃料下値抵抗力が極めて高い |
----
-### 1.2 決算書デザイン型判定 (Output &amp; Key Metrics)
-#### 【A. 外部公開用 標準様式 (External Dossier)】
-&gt; ※ 本分析は、法人の財務健全性および金融機関からの追加与信枠最大化に向け、本物件単体取得時（安定稼働率93%、LTV 85%、金利2.3%、劣化対策3級に基づく30年返済基準）に法人決算書（損益計算書および貸借対照表）へ与える主要財務指標を精密検証した結果です。
-| 項目 (Key Metrics) | 検証対象不動産 (単体実績) | 指標定義および決算書デザイン上の意味 (Description &amp; Financial Significance) |
-| :--- | :---: | :--- |
-| **1. 帳簿上税引前当期純利益** | **約285.2万円** | 安定稼働(93%)営業収益から管理運営費、初年度支払利息(259.9万)および新築木造減価償却費(22年償却、年251.0万)を控除した会計上の純利益。**大幅な黒字決算に貢献。** |
-| **2. 税引前手残りCF (Pre-tax CF)** | **123.1万円 (0.91%)** | 安定稼働(93%)時に元利返済額(ADS 528.7万)を控除した後の手残りCF（**満室100%稼働時は158.3万円 / 1.18%**）。 |
-| **3. 推定法人税額 (実効税率25%想定)** | **約71.3万円** | 帳簿上税引前純利益(285.2万)に対する法人税推定額。新築22年減価償却費(年251.0万円)により課税標準を安定的に圧縮。 |
-| **4. 税引後手残りCF (Post-tax CF)** | **約51.8万円 (0.38%)** | 93%稼働および法人税納付後でも純増する税引後キャッシュフロー（満室稼働時は税引後約78.2万円、1.27億指値時の満室税引後は約101万円）。 |
-| **5. 債務償還年数 (Debt Coverage)** | **24.3年** | 借入金(1億1,449.5万) ÷ (税引後純利益213.9万 + 減価償却費251.0万)。**融資期間(30年)より5.7年短い24.3年**でゴールデンクロス($C \le B$)を完全達成。 |
-| **6. 利子負担率 (ICR)** | **1.51倍 (NOI基準 2.51倍)** | 営業利益(393.3万) ÷ 支払利息(259.9万)。減価償却後の営業利益基準で**1.51倍**の優良なインタレスト・カバレッジを確保。 |
-| **7. 負債返済割合 (DSCR)** | **1.30倍 (満室) / 1.52倍 (決算基準)** | 実質OPEX全額反映時でも1.30倍、決算書経費基準では**1.52倍**と金融機関の安全基準(1.20倍)を大きく上回る。 |
-| **8. 担保評価LTV (固定資産税基準)** | **164.25%** | 借入金(1億1,449.5万) ÷ 公的課税評価額(土地397.42㎡×0.7 + 建物 = **6,968.8万円**)。**120.3坪の大規模土地保有により新築木造として異例の低LTVを達成！** |
-| **9. 自己資本収益率 (CCR / ROI)** | **5.03% (満室30年)** | 満室税引前CF(158.3万) ÷ 初期自己資金(3,149.7万)。1.27億指値時は**6.35%**へ上昇。 |
----
-#### 【B. モアビズ内部専用 比較着地様式 (Moabiz Internal)】
-| 項目 (指標項目) | 検証対象不動産 単体 | モアビズ4期現在 (Col G) | 検証対象不動産 買入後決算書着地予想 |
-| :--- | :---: | :---: | :---: |
-| **1. 帳簿上税引前当期純利益** | **¥2,851,692** | ¥3,722,450 | **¥6,574,142** (**+76.6%急増**) |
-| **2. 税引前手残りCF** | **¥1,231,095** | ¥1,741,901 | **¥2,972,996** (**+70.7%拡大**) |
-| 　・**税引前CF利回り** | **0.91%** | 0.65% | **0.74%** (+9bp改善) |
-| 　・**推定法人税額** | **¥712,923** | ¥930,613 | **¥1,643,536** |
-| 　・**税引後手残りCF** | **¥518,172** | ¥811,289 | **¥1,329,461** (**+63.8%拡大**) |
-| 　・**税引後CF利回り** | **0.38%** | 0.30% | **0.33%** (+3bp改善) |
-| **3. 債務償還年数 (年)** | **24.3年** | 24.1年 | **24.2年** (**30年以内を完全維持**) |
-| **4. 簡易 Cash Flow (=税引後CF)** | **¥518,172** | ¥811,289 | **¥1,329,461** (約1.64倍へ拡大) |
-| **5. ICR (利子負担率, Interest Coverage Ratio)** | **1.51倍** | 0.90倍 | **1.04倍** (**+0.14倍改善・1.0倍突破達成！**) |
-| **6. 負債返済割合 (DSCR)** | **1.52倍** | 1.50倍 | **1.51倍** (**+0.01倍改善・超優良維持**) |
-| **7. LTV (固定資産税評価額に基づく)** | **164.25%** | 261.08% | **219.39%** (**▲41.69%pの劇的改善！**) |
-| **8. 投資額ROI (初期投下自己資本対比)** | **3.91% (93%稼働)** | 3.83% | **3.86%** (+3bp改善、満室時5.03%) |
-| **9. 法人貢献総合判定** | **優良貢献 (全指標クリア)** | 基準線 (ICR 0.9倍・LTV 261%課題) | **編入強く推奨 (ICR 1.0倍突破 &amp; LTV 41.7%p改善)** |
----
-### 評価サマリー (Evaluation Summary)
-| 評価軸 | 判定 | 根拠 |
-| :--- | :---: | :--- |
-| **価格妥当性** | **適正 〜 指値余地あり** | 売出価格1億3,470万円(表面6.50%)は、**標準積算価格(1億1,908万円、88.4%)**および**公示地価積算(1億4,864万円、110.4%)**に裏付けられており資産価値対比の妥当性が高い。1.26億〜1.29億円で指値できれば最上級ディール。 |
-| **賃料水準** | **合理的 (競争力優秀)** | 1戸平均26.89㎡で月額7.8万〜8.5万円(平均8.11万円、**㎡単価3,016円/㎡**)は三ツ境駅徒歩7分・新築・無料WIFI付として非常に合理的であり、近隣築浅物件(イル・フィオーレ、築11年)の成約実績とも合致。 |
-| **収益の質** | **優良 (広々9戸構成)** | 18㎡狭小ワンルームではなく約26〜27㎡級のゆとりある間取りのため、社会人単身者・在宅ワーカー・カップル層の長期入居(平均3.5〜4.5年)が期待できる。 |
-| **建物状態** | **最優良 (2026.11新築 / 劣化3級)**| ヤオキ商事(創業50年超の木造企画開発会社)による供給。**設計住宅性能評価 劣化対策等級3級取得済 &amp; 建設住宅性能評価3級予定**で最高水準の物理的・制度的耐久性を確保。 |
-| **収益構造** | **安定的 (DSCR 1.30倍)** | 劣化対策3級による30年長期融資(金利2.3%)調達時、満室税引前CF +158.3万円、損益分岐稼働率81.9%の安定したキャッシュフローを創出。 |
-| **将来価値** | **極めて優秀 (120.3坪駅近宅地)**| 三ツ境駅(急行停車)徒歩7分の**120.3坪(397.71㎡)大土地**は、15〜20年後の中古収益売却のみならず、**新築戸建分譲用地(3〜4区画分割売却)としての出口戦略(Land Exit)**も可能なコア資産。 |
-| **金融/融資** | **最優良 (劣化3級ダブル認証)** | 設計・建設住宅性能評価書(劣化対策等級3級)完備および高い土地担保評価(積算88.4%)により、地銀・信金・オリックス銀行等で30〜35年の優遇融資審査が可能。 |
----
-### 先行確認必須5大項目 (Top 5 Due Diligence Action Items)
-- [ ] **1. 南西側幅員約4.0m道路の『公道・私道』区間別の建築基準法上の種別および私道持分・通行掘削承諾書の確認**: 本敷地（`149-3`、`231-102`）が接する南西側道路のうち私道部分の所有権持分が売買対象に含まれるか、上下水道・都市ガス引込のための無償通行・掘削承諾書が完備されているかを最優先で確認すること。
-- [ ] **2. 実施設計図面一式（配置図・各階平面図・立面図）、土地全部事項証明書（2筆）および確定測量図の徴求**: 物件概要書と建築確認済証（第26UDI1K建00271号）に加え、住戸別の正確な専有面積・間取り図面および敷地内の高低差・擁壁有無を確認するための設計図書を売主（ヤオキ商事／ムーヴアップ）より受領すること。
-- [ ] **3. 売買契約書上の『土地・建物売買代金内訳比率』の協議確定**: 法人の年間減価償却費（節税効果）および消費税還付・不動産取得税に直接影響するため、売主側と建物価格を**約5,500万〜6,000万円（税込、全体の41〜45%）**水準に設定可能か事前協議すること。
-- [ ] **4. 『設計住宅性能評価書（劣化対策等級3級）』写しの受領および取引金融機関への30〜35年融資事前打診**: 既に取得完了している設計住宅性能評価書の写しと建築確認済証を金融機関へ提出し、**期間30〜35年、金利2.0〜2.3%台**の優遇条件承認を確保すること。
-- [ ] **5. 2026年11月末竣工前の先行入居者募集（リーシング）開始スケジュールおよび無料WIFI月額ランニングコストの確認**: 11月末引渡に合わせて9〜10月から先行募集を開始し引渡時満室（または初期AD売主負担）を誘導するとともに、無料インターネット（WIFI）設備の月額利用料（想定月1.0〜1.3万円）および契約承継条件を確認すること。
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B103" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="inlineStr">
-        <is>
-          <t>물건 개요 (Property Overview)</t>
-        </is>
-      </c>
-      <c r="D103" s="0" t="inlineStr">
-        <is>
-          <t>物件概要 (Property Overview)</t>
-        </is>
-      </c>
-      <c r="E103" s="0" t="inlineStr">
-        <is>
-          <t>### 기본 제원표 (물건개요서 및 건축확인필증 제26UDI1K건00271호 검증 완료)
-| 항목 | 내용 | 비고 |
-| :--- | :--- | :--- |
-| **물건명** | 미츠쿄 1AP 사사노다이 신축 아파트 (三ツ境1AP 新築アパート) | 가칭: 三ツ境1AP (준공 전 정식 명칭 부여 예정) |
-| **소재지 (지번)** | 神奈川県横浜市旭区笹野台2丁目149番3、231番102 | 요코하마시 아사히구 사사노다이 2초메 |
-| **교통 (대중교통)** | 相鉄本線 「三ツ境」駅 **徒歩 7分** (급행·통근급행·각정 정차역) | 실측 약 550m, 상점가 경유 평탄·완만 동선 |
-| **매매가격** | **13,470만 엔 (소비세 포함)** | 만실 상정 표면수익률 **6.50%** |
-| **토지 면적** | • **총 토지 면적**: **397.71㎡ (120.30평)** (`149-3` + `231-102` 2필지 합계)&lt;br&gt;• **세트백(도로후퇴) 면적**: **0.29㎡** (극미량)&lt;br&gt;• **유효 건축부지면적**: **397.42㎡ (120.22평)** | 제1매물(카와시마초 71.1평) 대비 **+69.1% 더 넓은 대토지** |
-| **토지 권리 / 지목** | 소유권 (所有権) / 택지 (宅地) | 2필지 일단의 대지 |
-| **접도 현황** | **남서측 폭원 약 4.0m (공도·사도) 접도** | 남서향 도로 접도로 전 세대 남서향/남동향 일조권 우수 |
-| **도시계획 / 용도지역** | 시가화구역 (市街化区域) / **제1종 저층주거전용지역 (第一種低層住居専用地域)** | 제1종 고도지구 (최고높이 10m 제한) |
-| **건폐율 / 용적률** | • **법정 건폐율**: **40%** (법정 건축면적 상한 158.96㎡)&lt;br&gt;• **법정 용적률**: **80%** (법정 연면적 상한 317.93㎡)&lt;br&gt;• **설계 실적**: 연면적 **242.07㎡** (실효 용적률 **60.91%**, 용적 소화율 76.1%) | 여유로운 동간 거리 및 저밀도 쾌적 배동 |
-| **건물 구조 / 규모** | **목조 지상 2층건 · 공동주택 (전 9세대)** | 1층 5세대 / 2층 4세대 |
-| **건물 연면적** | **242.07㎡ (73.22평)** | **세대당 평균 연면적 26.89㎡** (전유 약 25.5~27.5㎡) |
-| **건축확인번호 / 일정** | • **건축확인번호**: **제26UDI1K건00271호 (第26UDI1K建00271号)**&lt;br&gt;• **확인필증 교부일**: **령화 8년(2026년) 6월 18일** (유디아이확인검사 주식회사, 확인검사원 우에노 토모오미)&lt;br&gt;• **인도(준공) 예정**: **령화 8년(2026년) 11월 말** | 현황: 건축 중 |
-| **주택성능평가 (핵심)** | • **설계주택성능평가: 열화대책등급 3급 취득 완료 (設計住宅性能評価 劣化対策等級3級 取得済)**&lt;br&gt;• **건설주택성능평가: 열화대책등급 3급 취득 예정 (建設住宅性能評価 劣化対策等級3級 取得予定)** | **목조 최고 등급(3급) 더블 인증 → 최장 30~35년 융자 적격** |
-| **인프라 및 특화 설비** | 공영수도 · 공공하수 · **도시가스(都市ガス)** · **전 세대 무료 WIFI 완비** | 도시가스 + 무료 인터넷으로 높은 임차인 선호도 |
-| **매도자(건축주) / 중개사**| • **매도자(건축주)**: **야오키상사 주식회사 (ヤオキ商事株式会社, 대표이사 카타야마 요시노리)**&lt;br&gt;• **중개사**: 주식회사 무브업 (株式会社ムーヴアップ) | 가와사키·요코하마에서 창업 50년 이상의 전통 목조 디벨로퍼 |
----
-### 🔍 건축확인필증(제26UDI1K건00271호) 및 매도자(야오키상사) 포렌식 검증
-1. **건축확인필증 원본 검증 (PDF 3 제2면)**:
-   - 국토교통성·가나가와현 지정 확인검사기관인 **유디아이확인검사 주식회사(ユーディーアイ確認検査株式会社, 확인검사원 우에노 토모오미)**가 **령화 8년(2026년) 6월 18일**자로 건축주 **야오키상사 주식회사(ヤオキ商事株式会社)** 앞으로 적법 교부한 『확인필증(건축물) 제26UDI1K건00271호』 원본을 확인 완료했습니다.
-   - 대지 위치는 『요코하마시 아사히구 사사노다이 2초메 149번3, 231번102』, 주요 용도는 『공동주택』, 공사는 『신축』으로 건축기준법 제6조 제1항 규정에 완벽히 적합함이 입증되었습니다.
-2. **매도자 『야오키상사 주식회사(ヤオキ商事株式会社)』 신용도 검증**:
-   - 가와사키시·요코하마시 권역을 중심으로 50년 이상의 업력을 보유한 수익형 부동산·목조 기획 개발 전문 회사로, 단기 차익형 브로커와 달리 자체 보유 및 설계·건설주택성능평가(열화대책 3급) 정식 취득을 표준화하여 시공 품질과 금융기관 신뢰도가 우수합니다.
----</t>
-        </is>
-      </c>
-      <c r="F103" s="0" t="inlineStr">
-        <is>
-          <t>### 基本諸元表（物件概要書および建築確認済証 第26UDI1K建00271号 検証完了）
-| 項目 | 内容 | 備考 |
-| :--- | :--- | :--- |
-| **物件名** | 三ツ境1AP 新築アパート | 仮称：三ツ境1AP（竣工前に正式名称決定予定） |
-| **所在地 (地番)** | 神奈川県横浜市旭区笹野台2丁目149番3、231番102 | 横浜市旭区笹野台2丁目 |
-| **交通** | 相鉄本線 「三ツ境」駅 **徒歩7分**（急行・通勤急行・各停停車駅） | 実測約550m、笹野台商店街経由の平坦・緩やかな動線 |
-| **売買価格** | **13,470万円（消費税込）** | 満室想定表面利回り **6.50%** |
-| **土地面積** | • **総土地面積**: **397.71㎡ (120.30坪)**（`149-3` + `231-102` 2筆合計）&lt;br&gt;• **セットバック面積**: **0.29㎡**（極少）&lt;br&gt;• **有効建築敷地面積**: **397.42㎡ (120.22坪)** | 第1物件(川島町71.1坪)対比で **+69.1%広い大規模宅地** |
-| **土地権利 / 地目** | 所有権 / 宅地 | 2筆一団の敷地 |
-| **接道状況** | **南西側 幅員約4.0m（公道・私道）接道** | 南西道路接道により全戸南西／南東向きの日照良好 |
-| **都市計画 / 用途地域** | 市街化区域 / **第一種低層住居専用地域** | 第1種高度地区（最高高さ10m制限） |
-| **建蔽率 / 容積率** | • **法定建蔽率**: **40%**（法定建築面積上限 158.96㎡）&lt;br&gt;• **法定容積率**: **80%**（法定延床面積上限 317.93㎡）&lt;br&gt;• **設計実績**: 延床面積 **242.07㎡**（実効容積率 **60.91%**、容積消化率76.1%） | ゆとりある隣棟間隔および低密度配棟 |
-| **建物構造 / 規模** | **木造地上2階建・共同住宅（全9戸）** | 1階5戸 ／ 2階4戸 |
-| **建物延床面積** | **242.07㎡ (73.22坪)** | **1戸あたり平均延床 26.89㎡**（専有約25.5〜27.5㎡） |
-| **建築確認番号 / 日程** | • **建築確認番号**: **第26UDI1K建00271号**&lt;br&gt;• **確認済証交付日**: **令和8年(2026年)6月18日**（ユーディーアイ確認検査株式会社、確認検査員 植野智臣）&lt;br&gt;• **引渡(竣工)予定**: **令和8年(2026年)11月末** | 現況：建築中 |
-| **住宅性能評価 (最重要)** | • **設計住宅性能評価：劣化対策等級3級 取得済**&lt;br&gt;• **建設住宅性能評価：劣化対策等級3級 取得予定** | **木造最高等級(3級)ダブル認証 → 最長30〜35年融資適格** |
-| **インフラ・特化設備** | 公営水道・公共下水・**都市ガス**・**全戸無料WIFI完備** | 都市ガス＋無料インターネットで高い入居者訴求力 |
-| **売主(建築主) / 仲介** | • **売主(建築主)**: **ヤオキ商事株式会社（代表取締役 片山義規）**&lt;br&gt;• **仲介会社**: 株式会社ムーヴアップ | 川崎・横浜で創業50年超の老舗木造企画デベロッパー |
----
-### 🔍 建築確認済証（第26UDI1K建00271号）および売主（ヤオキ商事）フォレンジック検証
-1. **建築確認済証原本の検証（PDF 3 第2ページ）**:
-   - 国土交通省・神奈川県指定確認検査機関である**ユーディーアイ確認検査株式会社（確認検査員 植野智臣）**が**令和8年（2026年）6月18日**付で建築主**ヤオキ商事株式会社**宛てに適法交付した『確認済証（建築物）第26UDI1K建00271号』原本を確認完了しました。
-   - 敷地の位置は『横浜市旭区笹野台2丁目149番3、231番102』、主要用途は『共同住宅』、工事種別は『新築』であり、建築基準法第6条第1項の規定に適合していることが公的に証明されています。
-2. **売主『ヤオキ商事株式会社』の信用度検証**:
-   - 川崎市・横浜市エリアを中心に50年以上の業歴を持つ収益不動産・木造企画開発の老舗企業であり、短期転売ブローカーとは異なり設計・建設住宅性能評価（劣化対策3級）の正式取得を標準化しているため、施工品質および金融機関からの信頼性が高い売主です。
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B104" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C104" s="0" t="inlineStr">
-        <is>
-          <t>입지 및 주변 환경 분석 (Location &amp; Micro-Market Analysis)</t>
-        </is>
-      </c>
-      <c r="D104" s="0" t="inlineStr">
-        <is>
-          <t>立地および周辺環境分析 (Location &amp; Micro-Market Analysis)</t>
-        </is>
-      </c>
-      <c r="E104" s="0" t="inlineStr">
-        <is>
-          <t>### 3.1 교통 접근성: 『급행 정차역 미츠쿄역 도보 7분』의 위력
-- **소테츠 본선(相鉄本線) 「미츠쿄(三ツ境)」역 도보 7분**:
-  - 제1매물이 위치한 카미호시카와역(각정·쾌속만 정차)과 달리, **미츠쿄역은 급행(急行)·통근급행(通勤急行)·쾌속·각정이 정차하는 주요 거점역**입니다(일평균 승하차 인원 약 5.4만 명).
-  - **「요코하마(横浜)」역까지 급행 직통 14~16분**, **「후타마타가와(二俣川)」역(환승 거점)까지 1정거장(3분)**이며, 소테츠·JR 직통선 및 소테츠·도큐 직통선을 통해 **「신요코하마(新横浜)」역 18분, 「시부야(渋谷)」·「신주쿠(新宿)」·「메구로(目黒)」·「오테마치(大手町)」까지 환승 없이 38~48분대**에 도달합니다.
-- **도보 동선 및 지형적 우위**:
-  - 미츠쿄역 북구(北口)에서 활기찬 지역 상점가인 **「사사노다이 상점가(笹野台商店街, 중앙상점가)」**를 지나 도보 7분(약 550m) 거리에 위치합니다.
-  - 급경사 언덕길을 올라가야 하는 카와시마초 물건과 달리, 미츠쿄역에서 사사노다이 2초메까지는 완만한 고원 대지 지형이어서 **여성 임차인이나 야간 귀가 시에도 안전하고 쾌적한 도보 접근성**을 자랑합니다.
-### 3.2 역 주변 상업·생활 인프라
-- **초대형 역세권 상업시설 완비**:
-  - 미츠쿄역 직결 **소테츠 로젠(相鉄ローゼン 三ツ境店, 대형 슈퍼)** 및 **소테츠 라이프 미츠쿄(相鉄ライフ三ツ境, 쇼핑몰)**, 역 남측 **이온푸드스타일 미츠쿄점(イオンフードスタイル三ツ境店, 구 다이에 대형 쇼핑센터)**이 도보 6~8분 거리에 위치하여 요코하마 서부 권역에서도 손꼽히는 생활 편의성을 갖추고 있습니다.
-  - 사사노다이 상점가 내 편의점(세븐일레븐·로손), 드럭스토어(HAC 드럭), 클리닉, 은행, 음식점 등이 도보 3~5분 내에 밀집해 있습니다.
-### 3.3 해저드(재해) 리스크 검증
-- **홍수·내수 침수 리스크 (안전)**:
-  - 사사노다이 2초메 일대는 표고 약 65~70m의 안정적인 다마 구릉 대지(고지대)에 위치하여, 요코하마시 아사히구 홍수 해저드맵상 **하천 범람 및 내수 침수 예상 구역에 전혀 해당하지 않습니다(수해 리스크 제로 수준)**.
-- **지반 및 토사재해 리스크 (안전)**:
-  - 제1종 저층주거전용지역의 정돈된 주택지로 토사재해 경계구역(옐로우/레드존)에도 해당하지 않는 안정적인 지반입니다.
----</t>
-        </is>
-      </c>
-      <c r="F104" s="0" t="inlineStr">
-        <is>
-          <t>### 3.1 交通アクセス：『急行停車駅・三ツ境駅 徒歩7分』の優位性
-- **相鉄本線「三ツ境」駅 徒歩7分**:
-  - 第1物件の上星川駅（各停・快速のみ停車）と異なり、**三ツ境駅は急行・通勤急行・快速・各停のすべてが停車する主要駅**です（1日平均乗降人員 約5.4万人）。
-  - **「横浜」駅まで急行直通14〜16分**、**「二俣川」駅（特急乗換拠点）まで1駅3分**であり、相鉄・JR直通線および相鉄・東急直通線により**「新横浜」駅18分、「渋谷」「新宿」「目黒」「大手町」まで乗換なしで38〜48分圏内**でアクセス可能です。
-- **徒歩動線および地形的優位性**:
-  - 三ツ境駅北口から活気ある地域商店街**「笹野台商店街（中央商店街）」**を抜けて徒歩7分（約550m）の好立地です。
-  - 急な上り坂を上る必要がある川島町物件と異なり、三ツ境駅から笹野台2丁目までは平坦〜緩やかな台地地形であるため、**女性入居者や夜間帰宅時でも安全かつ快適な徒歩動線**を誇ります。
-### 3.2 駅周辺の商業・生活インフラ
-- **大型駅直結商業施設が充実**:
-  - 三ツ境駅直結の**相鉄ローゼン三ツ境店（大型スーパー）**および**相鉄ライフ三ツ境（ショッピングモール）**、駅南口の**イオンフードスタイル三ツ境店（旧ダイエー大型SC）**が徒歩6〜8分圏内に揃っており、横浜西部エリアでも屈指の生活利便性を備えています。
-  - 笹野台商店街内のコンビニ（セブンイレブン・ローソン）、ドラッグストア（ハックドラッグ）、クリニック、銀行、飲食店も徒歩3〜5分以内に集積しています。
-### 3.3 ハザード（災害）リスク検証
-- **洪水・内水浸水リスク（安全）**:
-  - 笹野台2丁目一帯は標高約65〜70mの安定した多摩丘陵台地（高台）に位置しており、横浜市旭区洪水ハザードマップ上、**河川氾濫および内水浸水想定区域に一切該当しません（水害リスク極小）**。
-- **地盤および土砂災害リスク（安全）**:
-  - 第一種低層住居専用地域の整形住宅街であり、土砂災害警戒区域（イエロー／レッドゾーン）にも該当しない安定した地盤です。
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C105" s="0" t="inlineStr">
-        <is>
-          <t>건물 및 호실 설계·렌트롤 포렌식 (Building &amp; Rent Roll Forensics)</t>
-        </is>
-      </c>
-      <c r="D105" s="0" t="inlineStr">
-        <is>
-          <t>建物・住戸設計およびレントロール分析 (Building &amp; Rent Roll Forensics)</t>
-        </is>
-      </c>
-      <c r="E105" s="0" t="inlineStr">
-        <is>
-          <t>### 4.1 26.89㎡ 광폭 설계 및 설비 경쟁력 분석
-- **여유로운 세대 면적 (평균 26.89㎡)**:
-  - 총 연면적 **242.07㎡(73.22평)**를 9세대로 나누면 **1세대당 평균 연면적은 26.89㎡**(벽심 기준 전유면적 약 **25.5㎡ ~ 27.5㎡**, 약 8~9조 거실의 대형 1K 또는 1DK/1LDK 평면)입니다.
-  - 최근 수도권 임대 시장에서는 15~18㎡ 초소형 원룸의 공실률이 상승하는 반면, **25㎡ 이상의 여유 있는 1K/1DK 평면은 재택근무 공간 확보 및 수납력을 중시하는 우량 사회인 임차인들의 강한 선호**를 받고 있습니다.
-- **인프라 및 부대시설**:
-  - **도시가스(都市ガス)** 및 공공하수 직결, **전 세대 무료 WIFI(초고속 인터넷) 기본 제공**(임차인 체감 월 4,000~5,000엔 절감 효과), 남서측 4m 도로 접도에 따른 밝은 채광 구조.
-### 4.2 전 9세대 호실별 상정 임대료 및 단가 정밀 일람표
-매도자 제시 호실별 임대료(공익비 포함 기준) 및 ㎡당 단가 분석은 다음과 같습니다:
-| 호실 | 층수 | 위치 구분 | 추정 면적 (평균 기준) | 월 총임대료 (공익비 포함) | 연간 임대료 (엔) | ㎡당 월 단가 (엔/㎡) | 호실별 가격 책정 및 경쟁력 분석 |
-| :---: | :---: | :---: | ---: | ---: | ---: | ---: | :--- |
-| **101호** | 1층 | 남서/남동 각실(角) | 약 26.89㎡ | **80,000엔** | 960,000엔 | 2,975엔/㎡ | 1층 각실(2면 채광), 중실 대비 +2,000엔 프리미엄 |
-| **102호** | 1층 | 중실(中部屋) | 약 26.89㎡ | **78,000엔** | 936,000엔 | 2,901엔/㎡ | **7만 엔대(7.8만) 진입 가격**으로 포털 검색 노출 극대화 |
-| **103호** | 1층 | 중실(中部屋) | 약 26.89㎡ | **78,000엔** | 936,000엔 | 2,901엔/㎡ | 26㎡+ 신축·무료WIFI·역7분 조건에서 가성비 최우수 |
-| **104호** | 1층 | 중실(中部屋) | 약 26.89㎡ | **78,000엔** | 936,000엔 | 2,901엔/㎡ | 1층 중실 표준 임대료 |
-| **105호** | 1층 | 북서 각실(角) | 약 26.89㎡ | **80,000엔** | 960,000엔 | 2,975엔/㎡ | 1층 각실(2면 채광) |
-| **201호** | 2층 | 남서/남동 각실(角) | 약 26.89㎡ | **85,000엔** | 1,020,000엔 | 3,161엔/㎡ | 2층 최상층 각실, 일조·조망 최우수 호실 |
-| **202호** | 2층 | 중실(中部屋) | 약 26.89㎡ | **83,000엔** | 996,000엔 | 3,087엔/㎡ | 2층 중실 표준 임대료 (1층 대비 +5,000엔 단차) |
-| **203호** | 2층 | 중실(中部屋) | 약 26.89㎡ | **83,000엔** | 996,000엔 | 3,087엔/㎡ | 2층 중실 표준 임대료 |
-| **204호** | 2층 | 북서 각실(角) | 약 26.89㎡ | **85,000엔** | 1,020,000엔 | 3,161엔/㎡ | 2층 최상층 각실 |
-| **합계/평균** | **9실** | 1층 5실 / 2층 4실 | **242.07㎡** (평균 26.89㎡) | **730,000엔** (평균 81,111엔) | **8,760,000엔** (876.0만 엔) | **평균 3,016엔/㎡** | **제1매물(3,435엔/㎡) 대비 ㎡당 단가 12.2% 저렴!** |
----</t>
-        </is>
-      </c>
-      <c r="F105" s="0" t="inlineStr">
-        <is>
-          <t>### 4.1 26.89㎡広幅設計および設備競争力分析
-- **ゆとりある住戸面積（平均26.89㎡）**:
-  - 総延床面積**242.07㎡（73.22坪）**を9戸で割ると、**1戸あたり平均延床面積は26.89㎡**（壁芯専有面積 **約25.5㎡ 〜 27.5㎡**、居室8〜9帖の大型1Kまたは1DK/1LDKプラン）となります。
-  - 近年の首都圏賃貸市場では15〜18㎡の極小ワンルームの空室率が上昇する一方、**25㎡以上のゆとりある1K/1DKはテレワークスペースや収納力を重視する優良社会人層の強い支持**を集めています。
-- **インフラおよび付帯設備**:
-  - **都市ガス**および公共下水直結、**全戸無料WIFI（高速インターネット）標準完備**（入居者体感で月4,000〜5,000円の節約効果）、南西側4m道路接道による明るい採光設計。
-### 4.2 全9戸 住戸別想定賃料および単価一覧表
-売主提示の住戸別賃料（共益費込）および㎡単価分析は以下の通りです：
-| 号室 | 階数 | 位置区分 | 推定面積 (平均基準) | 月額総賃料 (共益費込) | 年間賃料 (円) | ㎡あたり月額単価 (円/㎡) | 住戸別価格設定および競争力分析 |
-| :---: | :---: | :---: | ---: | ---: | ---: | ---: | :--- |
-| **101号室** | 1階 | 南西/南東角部屋 | 約26.89㎡ | **80,000円** | 960,000円 | 2,975円/㎡ | 1階角部屋(2面採光)、中部屋比+2,000円プレミアム |
-| **102号室** | 1階 | 中部屋 | 約26.89㎡ | **78,000円** | 936,000円 | 2,901円/㎡ | **7万円台(7.8万)のエントリー価格**でポータル検索ヒット最大化 |
-| **103号室** | 1階 | 中部屋 | 約26.89㎡ | **78,000円** | 936,000円 | 2,901円/㎡ | 26㎡超・新築・無料WIFI・駅7分条件で極めて高いコスパ |
-| **104号室** | 1階 | 中部屋 | 約26.89㎡ | **78,000円** | 936,000円 | 2,901円/㎡ | 1階中部屋の標準賃料 |
-| **105号室** | 1階 | 北西角部屋 | 約26.89㎡ | **80,000円** | 960,000円 | 2,975円/㎡ | 1階角部屋(2面採光) |
-| **201号室** | 2階 | 南西/南東角部屋 | 約26.89㎡ | **85,000円** | 1,020,000円 | 3,161円/㎡ | 2階最上階角部屋、日照・眺望最優良住戸 |
-| **202号室** | 2階 | 中部屋 | 約26.89㎡ | **83,000円** | 996,000円 | 3,087円/㎡ | 2階中部屋の標準賃料（1階比+5,000円差） |
-| **203号室** | 2階 | 中部屋 | 約26.89㎡ | **83,000円** | 996,000円 | 3,087円/㎡ | 2階中部屋の標準賃料 |
-| **204号室** | 2階 | 北西角部屋 | 約26.89㎡ | **85,000円** | 1,020,000円 | 3,161円/㎡ | 2階最上階角部屋 |
-| **合計/平均** | **9戸** | 1階5戸 / 2階4戸 | **242.07㎡** (平均26.89㎡) | **730,000円** (平均81,111円) | **8,760,000円** (876.0万円) | **平均3,016円/㎡** | **第1物件(3,435円/㎡)より㎡単価が12.2%割安！** |
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B106" s="0" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C106" s="0" t="inlineStr">
-        <is>
-          <t>임대 시세 및 공실·회전율 비교 분석 (Rent Roll &amp; Vacancy Benchmarking)</t>
-        </is>
-      </c>
-      <c r="D106" s="0" t="inlineStr">
-        <is>
-          <t>賃料相場および空室・回転率ベンチマーク (Rent Roll &amp; Vacancy Benchmarking)</t>
-        </is>
-      </c>
-      <c r="E106" s="0" t="inlineStr">
-        <is>
-          <t>### 5.1 사사노다이 실거래 아카이브(`LIFULL HOME'S`) 정밀 벤치마킹
-본 물건과 동일한 사사노다이 지구에 위치한 비교 목조 아파트 **「일 피오레 (イル・フィオーレ, `b-40788409`, 요코하마시 아사히구 사사노다이 1초메 32-4, 2016년 7월 준공[축 11년], 목조 2층, 미츠쿄역 도보 9분)」**의 포털 아카이브(총 10건)를 전수 추출하여 비교 분석했습니다:
-| 비교 항목 | 본 물건 (미츠쿄 1AP 사사노다이) | 인근 비교물건: 일 피오레 (`b-40788409`) | 제1매물 비교: 킵 라군 카와시마초 |
-| :--- | :---: | :---: | :---: |
-| **소재지** | 아사히구 사사노다이 2초메 (역 도보 7분) | 아사히구 사사노다이 1초메 (역 도보 9분) | 호도가야구 카와시마초 (카미호시카와역 9분) |
-| **준공연월 (연식)** | **2026년 11월 (신축)** | 2016년 7월 (**축 11년 중고**) | 2026년 10월 (신축) |
-| **전유면적 / 구성** | **평균 26.89㎡** (전 9세대, 무료 WIFI) | 1층 32.95㎡ (1DK) / 2층 41.35㎡ (1LDK) | 평균 18.54㎡ (전 10세대, 1R/1K) |
-| **모집·성약 임대료** | **78,000 ~ 85,000엔** (공익비 포함) | • 1층(32.95㎡): **75,000엔** (2026년 5월 성약)&lt;br&gt;• 2층(41.35㎡): **82,000 ~ 85,500엔** (성약) | 62,000 ~ 66,000엔 (공익비 포함) |
-| **㎡당 임대료 단가** | **3,016엔/㎡** (신축) | 2,068 ~ 2,276엔/㎡ (축 11년 대형) | **3,435엔/㎡** (신축 협소) |
-| **최근 모집 소요기간 (DOM)** | 신축 초기 리싱 예정 | • **2026년 5월(102호, 7.5만)**: **DOM 1개월 내 즉결!**&lt;br&gt;• **2024년 1월(203호, 8.2만)**: **DOM 2개월 내 성약!** | 인접물건 신축 시 8~10개월 소요 이력 |
-### 5.2 시세 검증 결론: 『높은 임대 수요 탄력성 및 빠른 리싱 기대』
-1. **구축(축 11년) 물건도 월 7.5~8.5만 엔에 1~2개월 내 즉결되는 탄탄한 수요**:
-   - 사사노다이 비교 물건(`일 피오레`)은 **축 11년 중고 목조임에도 2026년 5월 최근 모집에서 월 7.5만 엔이 불과 1개월 만에 성약**되었고, 2층 세대도 월 8.2~8.5만 엔에 공실 없이 회전하고 있습니다.
-2. **본 물건(신축·역 도보 7분·무료 WIFI·26.9㎡)의 강력한 가성비**:
-   - 본 물건은 미츠쿄역(급행 정차) 도보 7분 신축이면서 1층 중실이 **78,000엔(7만 엔대)**, 2층이 **83,000~85,000엔**으로 책정되어 있어, **2026년 11월 말 준공 후 곧바로 이어지는 일본 최대 이사 성수기(2027년 1~3월)와 맞물려 조기 만실 달성 가능성이 매우 높습니다.**
----</t>
-        </is>
-      </c>
-      <c r="F106" s="0" t="inlineStr">
-        <is>
-          <t>### 5.1 笹野台エリア実勢アーカイブ（`LIFULL HOME'S`）精密比較
-本物件と同じ笹野台エリアに位置する比較木造アパート **「イル・フィオーレ（`b-40788409`、横浜市旭区笹野台1丁目32-4、2016年7月築［築11年］、木造2階建、三ツ境駅徒歩9分）」**のポータル募集履歴（全10件）を抽出し比較分析しました：
-| 比較項目 | 本物件 (三ツ境1AP 笹野台) | 近隣比較物件: イル・フィオーレ (`b-40788409`) | 第1物件比較: Keep Lagoon 川島町 |
-| :--- | :---: | :---: | :---: |
-| **所在地** | 旭区笹野台2丁目 (三ツ境駅 徒歩7分) | 旭区笹野台1丁目 (三ツ境駅 徒歩9分) | 保土ケ谷区川島町 (上星川駅 徒歩9分) |
-| **築年月 (築年数)** | **2026年11月 (新築)** | 2016年7月 (**築11年中古**) | 2026年10月 (新築) |
-| **専有面積 / 構成** | **平均26.89㎡** (全9戸、無料WIFI完備) | 1階 32.95㎡ (1DK) / 2階 41.35㎡ (1LDK) | 平均18.54㎡ (全10戸、1R/1K) |
-| **募集・成約賃料** | **78,000 〜 85,000円** (共益費込) | • 1階(32.95㎡): **75,000円** (2026年5月成約)&lt;br&gt;• 2階(41.35㎡): **82,000 〜 85,500円** (成約) | 62,000 〜 66,000円 (共益費込) |
-| **㎡あたり賃料単価** | **3,016円/㎡** (新築) | 2,068 〜 2,276円/㎡ (築11年大型) | **3,435円/㎡** (新築狭小) |
-| **直近募集所要期間 (DOM)** | 新築初期リーシング予定 | • **2026年5月(102号室、7.5万)**: **DOM 1ヶ月以内で即決！**&lt;br&gt;• **2024年1月(203号室、8.2万)**: **DOM 2ヶ月以内で成約！** | 隣接物件の新築時は8〜10ヶ月所要履歴 |
-### 5.2 相場検証の結論：『高い賃貸需要弾力性と早期満室期待』
-1. **築11年の中古木造でも月額7.5〜8.5万円で1〜2ヶ月以内に即決される底堅い需要**:
-   - 笹野台の比較物件（`イル・フィオーレ`）は、**築11年の中古木造であっても2026年5月の直近募集で月額7.5万円がわずか1ヶ月で即決成約**しており、2階住戸も月額8.2〜8.5万円で安定稼働しています。
-2. **本物件（新築・駅徒歩7分・無料WIFI・26.9㎡）の圧倒的コストパフォーマンス**:
-   - 本物件は三ツ境駅（急行停車）徒歩7分の新築でありながら1階中部屋が**78,000円（7万円台）**、2階が**83,000〜85,000円**に設定されており、**2026年11月末の竣工直後に始まる最大の引越繁忙期（2027年1〜3月）と重なるため、早期満室達成の蓋然性が極めて高い**と評価されます。
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B107" s="0" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C107" s="0" t="inlineStr">
-        <is>
-          <t>가격 타당성 및 적산가치 평가 (Valuation &amp; Cost Approach)</t>
-        </is>
-      </c>
-      <c r="D107" s="0" t="inlineStr">
-        <is>
-          <t>価格妥当性および積算評価 (Valuation &amp; Cost Approach)</t>
-        </is>
-      </c>
-      <c r="E107" s="0" t="inlineStr">
-        <is>
-          <t>### 6.1 적산가치(積算価格) 3단계 정밀 평가: 『매매가 대비 88.4% ~ 110.4%의 압도적 담보력』
-본 물건의 가장 큰 강점인 **397.42㎡(120.22평) 유효 택지**와 **242.07㎡ 신축 건물**의 적산가치를 3단계로 산출했습니다:
-- **토지 평가 기준**:
-  - 유효 건축부지 면적: **397.42㎡ (120.22평)** (총 397.71㎡ 중 세트백 0.29㎡ 제외).
-  - 미츠쿄역 도보 7분 사사노다이 2초메 정형 주택지의 공시지가/기준지가 수준은 **약 23.5만 ~ 24.5만 엔/㎡(평당 약 78만~81만 엔)**이며, 상속세 노선가(공시지가의 80%)는 **약 19.0만 엔/㎡**, 고정자산세 평가액(공시지가의 70%)은 **약 16.8만 엔/㎡**로 추산됩니다.
-  - **노선가 기준 토지 적산가액**: `397.42㎡ × 19.0만 엔/㎡ = 7,551.0만 엔 (매매가의 56.06%!)`
-  - **공시지가 기준 토지 실세가액**: `397.42㎡ × 24.0만 엔/㎡ = 9,538.1만 엔 (매매가의 70.81%!)`
-- **건물 평가 기준 (목조 신축 연면적 242.07㎡, 잔존연수 22/22년 = 100%, 열화대책 3급)**:
-  - ① **보수적 은행 담보 기준 (15만 엔/㎡)**: `242.07㎡ × 15만 엔 = 3,631.1만 엔`
-  - ② **국세청 표준 건축가액 기준 (18만 엔/㎡)**: `242.07㎡ × 18만 엔 = 4,357.3만 엔`
-  - ③ **신축 실조달원가 기준 (22만 엔/㎡)**: `242.07㎡ × 22만 엔 = 5,325.5만 엔`
-| 평가 시나리오 | 토지 평가액 (397.42㎡) | 건물 평가액 (242.07㎡) | 합산 적산가액 | 매매가(13,470만) 대비 비율 | 담보평가 해설 |
-| :--- | ---: | ---: | ---: | :---: | :--- |
-| **① 보수적 은행 담보 기준** | 7,551.0만 엔 (노선가) | 3,631.1만 엔 (15만/㎡) | **11,182.0만 엔** | **83.01%** | 보수적 은행 기준으로도 매매가의 83% 담보 커버! |
-| **② 국세청 표준 적산 기준** | **7,551.0만 엔** (노선가) | **4,357.3만 엔** (18만/㎡) | **11,908.2만 엔** | **88.41%** | **제1매물(58.3%) 대비 +30.1%p 높은 초우량 적산비율!** |
-| **③ 공시지가 + 신축원가 기준**| **9,538.1만 엔** (공시지가) | **5,325.5만 엔** (22만/㎡) | **14,863.6만 엔** | **110.35%** | **실질 토지 시세 + 신축 건축원가 합계가 매매가를 1,394만 엔 초과!** |
-&gt; [!TIP] **왜 이 물건의 적산가치가 매매가의 88.4%~110.4%에 달하는가?**
-&gt; 오늘날 수도권 신축 목조 원룸의 대다수는 토지비 상승과 건축비 급등으로 인해 적산비율이 50~60%대에 머무릅니다. 그러나 본 물건은 **120.3평의 대형 부지 가치가 매매가의 56~71%를 지탱**하고 있어, 사실상 **"토지를 시세대로 사고 열화대책 3급 신축 건물을 원가 이하로 취득하는 구조"**에 가깝습니다. 이는 은행 융자 심사 시 담보 부족(평가 쪼개기) 문제를 원천 해소할 뿐 아니라, 10~15년 뒤 매각 시에도 토지 가격만으로 원금 대부분을 방어하는 막강한 안전판이 됩니다.
----</t>
-        </is>
-      </c>
-      <c r="F107" s="0" t="inlineStr">
-        <is>
-          <t>### 6.1 積算価格（Cost Approach）3段階精密評価：『売買価格比88.4%〜110.4%の圧倒的担保力』
-本物件最大の強みである**397.42㎡（120.22坪）の有効宅地**と**242.07㎡の新築建物**の積算価格を3段階で算出しました：
-- **土地評価基準**:
-  - 有効建築敷地面積：**397.42㎡（120.22坪）**（総面積397.71㎡からセットバック0.29㎡を控除）。
-  - 三ツ境駅徒歩7分・笹野台2丁目の整形住宅地の公示地価・基準地価水準は**約23.5万 〜 24.5万円/㎡（坪単価 約78万〜81万円）**であり、相続税路線価（公示地価の80%）は**約19.0万円/㎡**、固定資産税評価額（公示地価の70%）は**約16.8万円/㎡**と推計されます。
-  - **路線価基準 土地積算評価額**: `397.42㎡ × 19.0万円/㎡ = 7,551.0万円（売買価格の56.06%！）`
-  - **公示地価基準 土地実勢評価額**: `397.42㎡ × 24.0万円/㎡ = 9,538.1万円（売買価格の70.81%！）`
-- **建物評価基準（木造新築 延床面積242.07㎡、残存年数22/22年 = 100%、劣化対策3級）**:
-  - ① **保守的銀行担保基準（15万円/㎡）**: `242.07㎡ × 15万円 = 3,631.1万円`
-  - ② **国税庁標準建築価額基準（18万円/㎡）**: `242.07㎡ × 18万円 = 4,357.3万円`
-  - ③ **新築実調達原価基準（22万円/㎡）**: `242.07㎡ × 22万円 = 5,325.5万円`
-| 評価シナリオ | 土地評価額 (397.42㎡) | 建物評価額 (242.07㎡) | 合計積算評価額 | 売買価格(13,470万)対比 | 担保評価解説 |
-| :--- | ---: | ---: | ---: | :---: | :--- |
-| **① 保守的銀行担保基準** | 7,551.0万円 (路線価) | 3,631.1万円 (15万/㎡) | **11,182.0万円** | **83.01%** | 保守的銀行基準でも売買価格の83%を担保カバー！ |
-| **② 国税庁標準積算基準** | **7,551.0万円** (路線価) | **4,357.3万円** (18万/㎡) | **11,908.2万円** | **88.41%** | **第1物件(58.3%)より+30.1%p高い超優良積算比率！** |
-| **③ 公示地価＋新築原価基準**| **9,538.1万円** (公示地価) | **5,325.5万円** (22万/㎡) | **14,863.6万円** | **110.35%** | **実質土地時価＋新築建築原価の合計が売出価格を1,394万円超過！** |
-&gt; [!TIP] **なぜ本物件の積算価格が売買価格の88.4%〜110.4%に達するのか？**
-&gt; 現在の首都圏新築木造アパートの大半は、積算比率が50〜60%台に留まります。しかし本物件は**120.3坪の大規模土地価値が売買価格の56〜71%を下支え**しており、実質的に**「土地を時価通りに買い、劣化対策3級の新築建物を原価以下で取得する構造」**となっています。これは銀行融資審査における担保割れ問題を解消するだけでなく、10〜15年後の売却時にも土地価格だけで元本の大半を防衛する強力な安全弁となります。
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B108" s="0" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C108" s="0" t="inlineStr">
-        <is>
-          <t>재무 모델링 및 현금흐름·손익분기 분석 (Financial Modeling &amp; Cash Flow Analysis)</t>
-        </is>
-      </c>
-      <c r="D108" s="0" t="inlineStr">
-        <is>
-          <t>財務モデリングおよびキャッシュフロー・損益分岐分析 (Financial Modeling &amp; Cash Flow Analysis)</t>
-        </is>
-      </c>
-      <c r="E108" s="0" t="inlineStr">
-        <is>
-          <t>### 7.1 정상화 운영경비(OPEX) 명세표
-| 경비 항목 | 연간 금액 (만 엔) | 월 환산 (엔) | 총수입 대비 비율 | 산출 근거 및 검증 내역 |
-| :--- | ---: | ---: | :---: | :--- |
-| **1. 고정자산세·도시계획세 (토지+건물)** | **58.0만 엔** | 48,333엔 | 6.62% | • 토지(397.42㎡, 추정 평가액 6,676.7만 엔): 전 면적 소규모주택용지 특례(9세대×200㎡=1,800㎡ 한도 내) 1/6·1/3 적용 시 **연 약 21.8만 엔**&lt;br&gt;• 신축 건물(242.07㎡): 초기 3년 감면 후 정상화 세액 **연 약 36.2만 엔** |
-| **2. 임대관리 위탁수수료 (PM Fee)** | **43.8만 엔** | 36,500엔 | 5.00% | 만실 연수입(876.0만 엔)의 5.0% |
-| **3. 공용부 청소·점검·무료 WIFI 비용** | **24.2만 엔** | 20,167엔 | 2.76% | **전 세대 무료 WIFI 인터넷 회선비(연 약 13.2만 엔)** + 정기청소·공용전기(연 11.0만 엔) |
-| **4. 화재·지진보험료 (연환산)** | **15.0만 엔** | 12,500엔 | 1.71% | 신축 목조 242.07㎡ 기준 연환산 보험료 |
-| **5. 퇴거 시 원상복구 및 리싱(AD) 충당금**| **30.0만 엔** | 25,000엔 | 3.42% | 9세대 중 연평균 2세대 퇴거 가정 (광폭 평면으로 장기 거주 경향 반영) |
-| **6. 장기수선충당금 및 세무기장비** | **18.0만 엔** | 15,000엔 | 2.05% | 열화대책등급 3급 사양에 맞춘 계획 수선 적립 |
-| **실질 연간경비 (OPEX) 합계** | **189.0만 엔** | **157,500엔** | **21.58%** | **만실 순영업소득(NOI) = 876.0만 - 189.0만 = 687.0만 엔 (Cap 5.10%)** |
-### 7.2 매수가별 및 융자 조건별(30년 vs 35년) 수지 비교 시뮬레이션
-열화대책등급 3급 확정 조건을 활용한 **① 호가 기준 30년 융자(기본안)**, **② 호가 기준 35년 융자 승인 시**, **③ 1억 2,700만 엔 네고 + 30년 융자 시(권장 목표안)**의 3대 시나리오를 비교했습니다:
-| 주요 재무 지표 | 시나리오 A (기본안)&lt;br&gt;호가 13,470만 / **30년** / 2.3% | 시나리오 B (초장기 융자안)&lt;br&gt;호가 13,470만 / **35년** / 2.3% | 시나리오 C (권장 네고 목표안)&lt;br&gt;**네고 12,700만** / **30년** / 2.3% |
-| :--- | :---: | :---: | :---: |
-| **매매가격 (소비세 포함)** | 13,470.0만 엔 | 13,470.0만 엔 | **12,700.0만 엔** (-770만) |
-| **차입금액 (LTV 85%)** | 11,449.5만 엔 | 11,449.5만 엔 | **10,795.0만 엔** |
-| **초기 필요 자기자본 (두금+제비용)** | 3,149.7만 엔 | 3,149.7만 엔 | **2,969.5만 엔** |
-| **만실 총수입 (GPI) / 표면수익률** | 876.0만 엔 (6.50%) | 876.0만 엔 (6.50%) | **876.0만 엔 (6.90%)** |
-| **실질 운영경비 (OPEX)** | 189.0만 엔 | 189.0만 엔 | **189.0만 엔** |
-| **만실 순영업소득 (NOI) / Cap Rate** | 687.0만 엔 (5.10%) | 687.0만 엔 (5.10%) | **687.0만 엔 (5.41%)** |
-| **연간 원리금상환액 (ADS)** | **528.7만 엔** (월 44.1만) | **476.3만 엔** (월 39.7만) | **498.5만 엔** (월 41.5만) |
-| **만실 세전 캐시플로 (Full Pre-tax CF)** | **+158.3만 엔** (1.18%) | **+210.7만 엔** (1.56%) | **+188.5만 엔** (1.48%) |
-| **안정화(93% 가동) 세전 캐시플로** | **+123.1만 엔** | **+175.5만 엔** | **+153.3만 엔** |
-| **부채상환배율 (DSCR, 만실 기준)** | **1.30배** (우량) | **1.44배** (초우량) | **1.38배** (우량) |
-| **손익분기 가동률 (BEP Occupancy)** | **81.93%** (허용공실 1.63실) | **75.95%** (허용공실 2.16실) | **78.48%** (허용공실 1.94실) |
-| **자기자본수익률 (CCR, 만실 세전)** | **5.03%** | **6.69%** | **6.35%** |
----</t>
-        </is>
-      </c>
-      <c r="F108" s="0" t="inlineStr">
-        <is>
-          <t>### 7.1 正常化運営経費（OPEX）明細表
-| 経費項目 | 年間金額 (万円) | 月額換算 (円) | 総収入対比 | 算出根拠および検証内訳 |
-| :--- | ---: | ---: | :---: | :--- |
-| **1. 固定資産税・都市計画税 (土地+建物)** | **58.0万円** | 48,333円 | 6.62% | • 土地(397.42㎡、推定評価額6,676.7万円)：全面積が小規模住宅用地特例(9戸×200㎡=1,800㎡枠内)1/6・1/3適用で **年約21.8万円**&lt;br&gt;• 新築建物(242.07㎡)：当初3年減額後の平準化税額 **年約36.2万円** |
-| **2. 賃貸管理委託手数料 (PM Fee)** | **43.8万円** | 36,500円 | 5.00% | 満室年収(876.0万円)の5.0% |
-| **3. 共用部清掃・点検・無料WIFI費用** | **24.2万円** | 20,167円 | 2.76% | **全戸無料WIFIインターネット回線費(年約13.2万円)** ＋ 定期清掃・共用電気(年11.0万円) |
-| **4. 火災・地震保険料 (年換算)** | **15.0万円** | 12,500円 | 1.71% | 新築木造242.07㎡基準の年換算保険料 |
-| **5. 退去時原状回復・リーシング(AD)引当**| **30.0万円** | 25,000円 | 3.42% | 9戸中 年平均2戸退去想定（広幅間取りによる長期入居傾向を反映） |
-| **6. 長期修繕積立金および税務顧問費** | **18.0万円** | 15,000円 | 2.05% | 劣化対策等級3級仕様に合わせた計画修繕積立 |
-| **実質年間経費 (OPEX) 合計** | **189.0万円** | **157,500円** | **21.58%** | **満室純営業収益(NOI) = 876.0万 - 189.0万 = 687.0万円 (Cap 5.10%)** |
-### 7.2 買付価格別および融資期間別（30年 vs 35年）収支比較シミュレーション
-劣化対策等級3級確定条件を活用した **① 売出価格基準・30年融資（ベース案）**、**② 売出価格基準・35年融資承認時**、**③ 1億2,700万円指値＋30年融資時（推奨目標案）**の3シナリオを比較しました：
-| 主要財務指標 | シナリオA (ベース案)&lt;br&gt;売価13,470万 / **30年** / 2.3% | シナリオB (超長期融資案)&lt;br&gt;売価13,470万 / **35年** / 2.3% | シナリオC (推奨指値目標案)&lt;br&gt;**指値12,700万** / **30年** / 2.3% |
-| :--- | :---: | :---: | :---: |
-| **売買価格 (消費税込)** | 13,470.0万円 | 13,470.0万円 | **12,700.0万円** (▲770万) |
-| **借入金額 (LTV 85%)** | 11,449.5万円 | 11,449.5万円 | **10,795.0万円** |
-| **初期必要自己資金 (頭金+諸費用)** | 3,149.7万円 | 3,149.7万円 | **2,969.5万円** |
-| **満室総収入 (GPI) / 表面利回り** | 876.0万円 (6.50%) | 876.0万円 (6.50%) | **876.0万円 (6.90%)** |
-| **実質運営経費 (OPEX)** | 189.0万円 | 189.0万円 | **189.0万円** |
-| **満室純営業収益 (NOI) / Cap Rate** | 687.0万円 (5.10%) | 687.0万円 (5.10%) | **687.0万円 (5.41%)** |
-| **年間元利返済額 (ADS)** | **528.7万円** (月44.1万) | **476.3万円** (月39.7万) | **498.5万円** (月41.5万) |
-| **満室税引前CF (Full Pre-tax CF)** | **+158.3万円** (1.18%) | **+210.7万円** (1.56%) | **+188.5万円** (1.48%) |
-| **安定稼働(93%) 税引前CF** | **+123.1万円** | **+175.5万円** | **+153.3万円** |
-| **負債返済倍率 (DSCR, 満室基準)** | **1.30倍** (優良) | **1.44倍** (超優良) | **1.38倍** (優良) |
-| **損益分岐稼働率 (BEP Occupancy)** | **81.93%** (許容空室1.63戸) | **75.95%** (許容空室2.16戸) | **78.48%** (許容空室1.94戸) |
-| **自己資本配当率 (CCR, 満室税引前)** | **5.03%** | **6.69%** | **6.35%** |
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B109" s="0" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C109" s="0" t="inlineStr">
-        <is>
-          <t>리스크 매트릭스 및 민감도 분석 (Risk Matrix &amp; Sensitivity Analysis)</t>
-        </is>
-      </c>
-      <c r="D109" s="0" t="inlineStr">
-        <is>
-          <t>リスクマトリクスおよび感度分析 (Risk Matrix &amp; Sensitivity Analysis)</t>
-        </is>
-      </c>
-      <c r="E109" s="0" t="inlineStr">
-        <is>
-          <t>### 8.1 금리 상승 × 가동률 변동 2차원 스트레스 테스트 (30년 융자 / 차입 11,449.5만 엔 기준)
-| 가동률 \ 대출금리 | **1.8%** (ADS 494.1만) | **2.3% [기준]** (ADS 528.7만) | **2.8%** (ADS 564.8만) | **3.3%** (ADS 602.4만) |
-| :---: | :---: | :---: | :---: | :---: |
-| **100% (만실 9/9실)** | +192.9만 | **+158.3만** | +122.2만 | +84.6만 |
-| **88.9% (8/9실 가동, 1실 공실)** | +95.6만 | **+61.0만 (흑자 유지!)** | +24.9만 | -12.7만 (경미) |
-| **77.8% (7/9실 가동, 2실 공실)** | -1.8만 (BEP) | **-36.4만 (적자)** | -72.5만 (적자) | -110.1만 (적자) |
-- **스트레스 테스트 결론**: 본 물건은 9세대 중 **1세대가 연중 내내 비어 있어도(가동률 88.9%) 연간 +61.0만 엔의 세전 흑자를 유지**하며, 금리가 +0.5%p 상승(2.8%)하고 동시에 1세대가 공실이어도 흑자(+24.9만 엔)를 방어하는 탄탄한 내구력을 보여줍니다.
-### 8.2 핵심 리스크 요약 및 완화 대책 (Mitigation Plan)
-| 리스크 유형 | 위험도 | 상세 내용 | 실질적 완화 및 방어 대책 (Actionable Mitigation) |
-| :--- | :---: | :--- | :--- |
-| **1. 남서측 4m 도로(공도·사도) 권리 리스크** | **중상 (Med-High)** | 남서측 접도 구간에 공도와 사도가 혼재되어 있어 사도 구간의 지분·승낙 확인 필요 | • 토지 등기부·공도(公図)·도로대장 확인을 통해 사도 지분 이전 여부 및 **무상 통행·굴착 승낙서 원본** 확보 |
-| **2. 토지·건물 가액 배분 미확정** | **중 (Medium)** | 개요서상 총액(13,470만 엔)만 기재되어 있어 건물 비중이 낮게 책정될 경우 감가상각액 감소 | • 매매계약서 체결 시 매도자(야오키상사)와 협의하여 **건물 가액을 약 5,500만~6,000만 엔(41~45%)**으로 명시 |
-| **3. 상세 설계도서(평면도·입면도) 미첨부**| **중 (Medium)** | 1차 자료에 개요서·확인필증만 포함되어 호실별 세부 전유면적 및 내장 사양 확인 필요 | • 중개사(무브업)를 통해 실시설계 도면 일식, 설계주택성능평가서 사본, 설비 사양서를 즉시 징구 |
----</t>
-        </is>
-      </c>
-      <c r="F109" s="0" t="inlineStr">
-        <is>
-          <t>### 8.1 金利上昇 × 稼働率変動 2次元ストレステスト（30年融資／借入11,449.5万円基準）
-| 稼働率 \ 借入金利 | **1.8%** (ADS 494.1万) | **2.3% [基準]** (ADS 528.7万) | **2.8%** (ADS 564.8万) | **3.3%** (ADS 602.4万) |
-| :---: | :---: | :---: | :---: | :---: |
-| **100% (満室 9/9戸)** | +192.9万 | **+158.3万** | +122.2万 | +84.6万 |
-| **88.9% (8/9戸稼働、1戸空室)** | +95.6万 | **+61.0万 (黒字維持！)** | +24.9万 | -12.7万 (軽微) |
-| **77.8% (7/9戸稼働、2戸空室)** | -1.8万 (BEP) | **-36.4万 (赤字)** | -72.5万 (赤字) | -110.1万 (赤字) |
-- **ストレステストの結論**: 本物件は9戸中**1戸が通年空室であっても（稼働率88.9%）年間+61.0万円の税引前黒字を維持**し、仮に金利が+0.5%p上昇（2.8%）しかつ1戸が空室であっても黒字（+24.9万円）を防衛する強靭なキャッシュフロー耐性を備えています。
-### 8.2 主要リスク総括および緩和策 (Mitigation Plan)
-| リスク類型 | 危険度 | 詳細内容 | 実効的な緩和・防衛策 (Actionable Mitigation) |
-| :--- | :---: | :--- | :--- |
-| **1. 南西側4m道路(公道・私道)の権利リスク** | **中高 (Med-High)** | 南西側接道区間に公道と私道が混在しており、私道区間の持分・承諾確認が必要 | • 土地登記簿・公図・道路台帳の確認により私道持分移転の有無および**無償通行・掘削承諾書原本**を確保 |
-| **2. 土地・建物価格内訳の未確定** | **中 (Medium)** | 概要書上は総額(13,470万円)のみ記載されており、建物比率が低いと減価償却額が減少 | • 売買契約締結時に売主(ヤオキ商事)と協議し、**建物価格を約5,500万〜6,000万円(41〜45%)**と明記 |
-| **3. 詳細設計図書(平面図・立面図)の未添付**| **中 (Medium)** | 一次資料には概要書・確認済証のみ含まれており、各戸詳細専有面積および仕様確認が必要 | • 仲介会社(ムーヴアップ)を通じ実施設計図面一式、設計住宅性能評価書写し、設備仕様書を即時徴求 |
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B110" s="0" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C110" s="0" t="inlineStr">
-        <is>
-          <t>취득 제비용·세무(소비세/감가상각) 및 출구 전략 (Tax, Depreciation &amp; Exit Strategy)</t>
-        </is>
-      </c>
-      <c r="D110" s="0" t="inlineStr">
-        <is>
-          <t>取得諸費用・税務（消費税・減価償却）および出口戦略 (Tax, Depreciation &amp; Exit Strategy)</t>
-        </is>
-      </c>
-      <c r="E110" s="0" t="inlineStr">
-        <is>
-          <t>### 9.1 초기 취득 제비용 및 감가상각 구조 (표준안: 토지 59% / 건물 41% 배분 시)
-- **매매가격 배분 (표준안)**: 총액 **13,470.0만 엔** = 토지 **7,947.3만 엔 (59.0%)** + 건물 **5,522.7만 엔 (41.0%, 세전 건물가액 약 5,020.6만 엔 + 소비세 약 502.1만 엔)**.
-- **초기 취득 제비용 (추정 합계 약 1,129.2만 엔, 매매가의 8.38%)**:
-  - 중개수수료 (3% + 6만 엔 + 소비세): **약 434.2만 엔**
-  - 부동산취득세 (신축 건물 공제 및 택지 특례 반영): **약 210.0만 엔**
-  - 소유권 이전·보존 및 저당권 설정 등기비용: **약 175.0만 엔**
-  - 인지세 및 금융기관 융자 수수료·보증료: **약 240.0만 엔**
-  - 화재·지진보험료 (5년 일시납) 및 고정자산세 정산금: **약 70.0만 엔**
-- **건물 감가상각비 (목조 신축 법정 내용연수 22년)**:
-  - 연간 감가상각비: `5,522.7만 엔 ÷ 22년 = 연 251.0만 엔` (22년간 장기 안정 상각으로 보유 기간 중 데드크로스 리스크가 거의 없음).
-### 9.2 보유 10년~15년 차 『듀얼 출구 전략 (Dual Exit Strategy)』
-본 물건은 **120.3평의 정형 택지**와 **열화대책등급 3급**을 동시에 보유하여 두 가지 강력한 출구 전략을 구사할 수 있습니다:
-1. **Exit ① (수익형 1동 매각)**:
-   - 보유 10년 차(축 10년 시점)에도 열화대책등급 3급 인증 덕분에 차기 매수자가 **잔존 20~25년 장기 융자**를 받을 수 있습니다. 미츠쿄역 도보 7분·대토지 조건을 감안할 때 매각 Cap Rate **5.5% ~ 5.7%**에서 **예상 매각가 1억 1,500만 ~ 1억 2,000만 엔** 달성이 가능하며, 10년 후 대출 잔액(약 8,310만 엔) 상환 후 **약 2,800만 ~ 3,300만 엔의 매각 차익 현금**과 10년간 누적 세후 CF(약 600만~800만 엔)를 합쳐 초기 자기자본(3,150만 엔)을 크게 상회하는 총수익을 거둘 수 있습니다.
-2. **Exit ② (신축 호별 분양 용지 매각 / Land Exit)**:
-   - 장기 보유 후(15~20년 차 이후)에도 **397.42㎡(120.22평)의 토지는 1필지당 약 100㎡(30평) 규모의 신축 단독주택(戸建) 3~4동 분양 부지로 분할 매각**할 수 있어, 땅값(공시지가 기준 9,538만 엔 이상) 자체가 완벽한 원금 보전 안전판 역할을 수행합니다.
----</t>
-        </is>
-      </c>
-      <c r="F110" s="0" t="inlineStr">
-        <is>
-          <t>### 9.1 初期取得諸費用および減価償却構造（標準案：土地59%／建物41%配分時）
-- **売買価格配分（標準案）**: 総額 **13,470.0万円** ＝ 土地 **7,947.3万円（59.0%）** ＋ 建物 **5,522.7万円（41.0%、税抜建物価格約5,020.6万円＋消費税約502.1万円）**。
-- **初期取得諸費用（推定合計 約1,129.2万円、売買価格の8.38%）**:
-  - 仲介手数料（3%＋6万円＋消費税）：**約434.2万円**
-  - 不動産取得税（新築建物控除および宅地特例反映）：**約210.0万円**
-  - 所有権移転・保存および抵当権設定登記費用：**約175.0万円**
-  - 印紙税および金融機関融資事務手数料・保証料：**約240.0万円**
-  - 火災・地震保険料（5年一括）および固定資産税精算金：**約70.0万円**
-- **建物減価償却費（木造新築 法定耐用年数22年）**:
-  - 年間減価償却費：`5,522.7万円 ÷ 22年 = 年251.0万円`（22年間の長期安定償却により保有期間中のデッドクロスリスクが極めて低い）。
-### 9.2 保有10年〜15年目『デュアル・イグジット戦略（Dual Exit Strategy）』
-本物件は**120.3坪の整形宅地**と**劣化対策等級3級**を兼ね備えているため、2つの強力な出口戦略を選択できます：
-1. **Exit ①（収益1棟アパートとしての売却）**:
-   - 保有10年目（築10年時点）でも劣化対策等級3級認証により次期買主が**残存20〜25年の長期融資**を利用可能です。三ツ境駅徒歩7分・大土地の条件から売却Cap Rate **5.5% 〜 5.7%**で**予想売却価格 1億1,500万 〜 1億2,000万円**の達成が見込まれ、10年後ローン残債（約8,310万円）完済後に**約2,800万 〜 3,300万円の売却手残りキャッシュ**と10年間累計税引後CF（約600万〜800万円）を合わせ、初期自己資金（3,150万円）を大きく上回るトータルリターンを実現できます。
-2. **Exit ②（新築戸建分譲用地としての分割売却 / Land Exit）**:
-   - 長期保有後（15〜20年目以降）でも、**397.42㎡（120.22坪）の敷地は1区画あたり約100㎡（30坪）の新築戸建3〜4棟の分譲用地として分割売却**できるため、土地実勢価値（公示地価基準9,538万円以上）そのものが強固な元本保全フロアとして機能します。
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B111" s="0" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C111" s="0" t="inlineStr">
-        <is>
-          <t>종합 의사결정 스코어카드 및 제1매물과의 비교 권고 (Decision Scorecard &amp; Comparative Verdict)</t>
-        </is>
-      </c>
-      <c r="D111" s="0" t="inlineStr">
-        <is>
-          <t>総合意思決定スコアカードおよび第1物件との比較勧告 (Decision Scorecard &amp; Comparative Verdict)</t>
-        </is>
-      </c>
-      <c r="E111" s="0" t="inlineStr">
-        <is>
-          <t>### 10.1 30점 만점 정량 평가 스코어카드 (제1매물 카와시마초 vs 제2매물 미츠쿄 1AP 비교)
-| 평가 카테고리 | 배점 | **미츠쿄 1AP (본건)** | 킵 라군 카와시마초 (비교) | 본 물건(미츠쿄 1AP) 우위 근거 |
-| :--- | :---: | :---: | :---: | :--- |
-| **1. 입지 및 임차 수요 (Location &amp; Demand)** | 5.0 | **4.0** | 3.5 | **급행 정차역(미츠쿄) 도보 7분**, 상점가 평탄 동선, 대형 상업시설 인접 |
-| **2. 수익성 및 현금흐름 (Yield &amp; Cash Flow)** | 5.0 | **3.5** | 3.0 | 표면 6.50%이나 **30년 융자 확정으로 만실 세전 CF 158.3만 엔(DSCR 1.30배)** 창출 |
-| **3. 가격 타당성 및 적산 담보력 (Valuation)** | 5.0 | **4.5** | 2.5 | **토지 120.3평(노선가 7,551만 엔), 표준 총적산 88.4%(공시지가 기준 110.4%) 압도적 우위!** |
-| **4. 물리적 상태 및 설비 경쟁력 (Physical)** | 5.0 | **4.0** | 3.5 | **세대당 26.89㎡ 광폭 설계(+45% 넓음)**, 도시가스 + **전 세대 무료 WIFI 완비** |
-| **5. 금융 조달 및 레버리지 적합성 (Financing)** | 5.0 | **4.5** | 3.5 | **설계·건설주택성능평가 열화대책등급 3급 더블 인증**으로 30~35년 융자 100% 적격 |
-| **6. 리스크 방어력 및 출구 전략 (Risk &amp; Exit)** | 5.0 | **2.0 → 4.0*** | 3.5 | 수해 리스크 없으며 120.3평 토지로 수익형 매각 + 호별 분양 부지 매각의 듀얼 엑시트 가능 (*사도 확인 시 4.0) |
-| **총점 (Total Score)** | **30.0** | **22.5** | 19.5 | **종합 등급: A- (조건부 추천 · 우량 편입 대상)** |
----
-### 10.2 최종 투자 권고 (Final Investment Recommendation)
-1. **최종 판정**: **【조건부 추천 / 우량 편입 대상 (22.5 / 30점)】**
-   - 두 매물을 나란히 비교할 때, **「미츠쿄 1AP 사사노다이 신축 아파트」는 토지 면적(120.3평 vs 71.1평), 표준 적산비율(88.4% vs 58.3%), 세대당 면적(26.89㎡ vs 18.54㎡), 역 거리 및 급행 정차(미츠쿄역 도보 7분 vs 카미호시카와역 언덕 9분), 열화대책등급(3급 확정 vs 2급 예정), 그리고 법인 결산서 기여도(세후 CF +63.8%, ICR 1.04배 돌파, 고정자산세 LTV -41.7%p 개선)의 전 부문에서 압도적인 우위**를 보입니다.
-2. **실행 액션 플랜 (Execution Roadmap)**:
-   - **Step 1 (즉시 자료 징구)**: 중개사(주식회사 무브업)에 ① 실시설계 도면(배치도·평면도·입면도), ② 토지 등기부등본(`149-3`, `231-102`) 및 공도·측량도, ③ 남서측 사도 부분의 도로 종별 및 지분/굴착승낙서 자료, ④ 설계주택성능평가서(열화대책 3급) 사본을 요청하십시오.
-   - **Step 2 (목표 네고 및 매수의향서 제출)**: 남서측 도로 권리에 이상이 없음을 확인한 후, **1억 2,600만 ~ 1억 2,900만 엔(만실 표면수익률 6.79% ~ 6.95%, Cap Rate 5.33% ~ 5.45%)**을 목표 지값으로 설정하여 매수의향서(買付証明書) 제출 및 금융기관 30~35년 융자 본심사를 진행할 것을 적극 권장합니다.
----
-# 부록 (Appendix): 원천 실사 도서 검증 목록
-1. **물건개요서 (三ツ境1AP 物件概要書 1p)**: 소재지(요코하마시 아사히구 사사노다이 2-149-3, 231-102), 매매가 13,470만 엔(표면 6.50%), 토지 397.71㎡(세트백 0.29㎡ 포함), 건물 242.07㎡(목조 2층 9세대), 남서측 4m 도로(공도·사도), 열화대책등급 3급(설계 취득 완료 / 건설 취득 예정), 전 9세대 임대료표(월 730,000엔, 연 8,760,000엔), 무료 WIFI·도시가스 완비 확인.
-2. **확인필증 (建築確認済証 第26UDI1K建00271号, 1p)**: 령화 8년(2026년) 6월 18일 유디아이확인검사 주식회사(확인검사원 우에노 토모오미)가 건축주 야오키상사 주식회사(대표이사 카타야마 요시노리) 앞으로 교부한 적법 건축확인필증 원본 확인.
-3. **인근 실거래 포털 아카이브 (`LIFULL HOME'S b-40788409` 일 피오레)**: 사사노다이 1-32-4 소재 축 11년 목조 아파트의 최근 모집·성약 이력(월 7.5만~8.55만 엔, DOM 1~2개월) 대조 완료.</t>
-        </is>
-      </c>
-      <c r="F111" s="0" t="inlineStr">
-        <is>
-          <t>### 10.1 30点満点 定量評価スコアカード（第1物件・川島町 vs 第2物件・三ツ境1AP 比較）
-| 評価カテゴリー | 配点 | **三ツ境1AP (本件)** | Keep Lagoon 川島町 (比較) | 本物件(三ツ境1AP)の優位性根拠 |
-| :--- | :---: | :---: | :---: | :--- |
-| **1. 立地および賃貸需要 (Location &amp; Demand)** | 5.0 | **4.0** | 3.5 | **急行停車駅(三ツ境)徒歩7分**、商店街経由の平坦動線、大型商業施設隣接 |
-| **2. 収益性およびキャッシュフロー (Yield &amp; CF)** | 5.0 | **3.5** | 3.0 | 表面6.50%ながら**30年融資確定により満室税引前CF 158.3万円(DSCR 1.30倍)**を創出 |
-| **3. 価格妥当性および積算担保力 (Valuation)** | 5.0 | **4.5** | 2.5 | **土地120.3坪(路線価7,551万円)、標準総積算88.4%(公示地価基準110.4%)と圧倒的優位！** |
-| **4. 物理的状態および設備競争力 (Physical)** | 5.0 | **4.0** | 3.5 | **1戸平均26.89㎡の広幅設計(+45%広い)**、都市ガス＋**全戸無料WIFI完備** |
-| **5. 金融調達およびレバレッジ適格性 (Financing)**| 5.0 | **4.5** | 3.5 | **設計・建設住宅性能評価 劣化対策等級3級ダブル認証**により30〜35年融資100%適格 |
-| **6. リスク防衛力および出口戦略 (Risk &amp; Exit)** | 5.0 | **2.0 → 4.0*** | 3.5 | 水害リスク皆無、120.3坪敷地により収益売却＋戸建分譲用地売却のデュアル出口が可能(*私道確認時4.0) |
-| **合計点 (Total Score)** | **30.0** | **22.5** | 19.5 | **総合ランク：A-（条件付推奨・優良編入対象）** |
----
-### 10.2 最終投資勧告 (Final Investment Recommendation)
-1. **最終判定**: **【条件付推奨／優良編入対象（22.5 / 30点）】**
-   - 2物件を並列比較した場合、**「三ツ境1AP 新築アパート」は土地面積（120.3坪 vs 71.1坪）、標準積算比率（88.4% vs 58.3%）、1戸あたり面積（26.89㎡ vs 18.54㎡）、駅距離・急行停車（三ツ境駅徒歩7分 vs 上星川駅坂道9分）、劣化対策等級（3級確定 vs 2級予定）、および法人決算書への貢献度（税引後CF +63.8%、ICR 1.04倍突破、固定資産税LTV ▲41.7%p改善）のすべての項目において圧倒的優位**を示しています。
-2. **実行アクションプラン (Execution Roadmap)**:
-   - **Step 1（即時資料徴求）**: 仲介会社（株式会社ムーヴアップ）に対し、① 実施設計図面（配置図・平面図・立面図）、② 土地全部事項証明書（`149-3`、`231-102`）および公図・測量図、③ 南西側私道部分の道路種別および持分・掘削承諾書資料、④ 設計住宅性能評価書（劣化対策3級）写しを請求してください。
-   - **Step 2（目標指値および買付証明書提出）**: 南西側道路の権利関係に問題がないことを確認の上、**1億2,600万 〜 1億2,900万円（満室表面利回り6.79% 〜 6.95%、Cap Rate 5.33% 〜 5.45%）**を目標指値として買付証明書を提出し、金融機関の30〜35年融資審査を進めることを強く推奨いたします。
----
-# 付録 (Appendix): 一次審査図書 検証一覧
-1. **物件概要書（三ツ境1AP 物件概要書 1p）**: 所在地（横浜市旭区笹野台2-149-3、231-102）、売買価格13,470万円（表面6.50%）、土地397.71㎡（セットバック0.29㎡含）、建物242.07㎡（木造2階建9戸）、南西側4m道路（公道・私道）、劣化対策等級3級（設計取得済／建設取得予定）、全9戸賃料表（月額730,000円、年額8,760,000円）、無料WIFI・都市ガス完備を確認。
-2. **確認済証（建築確認済証 第26UDI1K建00271号、1p）**: 令和8年（2026年）6月18日付でユーディーアイ確認検査株式会社（確認検査員 植野智臣）が建築主ヤオキ商事株式会社（代表取締役 片山義規）宛てに交付した適法な建築確認済証原本を確認。
-3. **近隣実勢ポータルアーカイブ（`LIFULL HOME'S b-40788409` イル・フィオーレ）**: 笹野台1-32-4所在の築11年木造アパートの直近募集・成約履歴（月額7.5万〜8.55万円、DOM 1〜2ヶ月）を照合完了。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="0" t="inlineStr">
-        <is>
-          <t>espoir-cross-kasukabe</t>
-        </is>
-      </c>
-      <c r="B112" s="0">
-        <v>1</v>
-      </c>
-      <c r="C112" s="0" t="inlineStr">
-        <is>
-          <t>1. 투자 하이라이트 및 핵심 요약 (Executive Summary)</t>
-        </is>
-      </c>
-      <c r="D112" s="0" t="inlineStr">
-        <is>
-          <t>1. 投資ハイライトおよびエグゼクティブ・サマリー</t>
-        </is>
-      </c>
-      <c r="E112" s="0" t="inlineStr">
         <is>
           <t>**에스포와르 크로스 카스카베(Espoir Cross Kasukabe)**는 도부 스카이트리라인·어반파크라인 2노선 급행 정차역인 **『카스카베』역 도보 9분(실측 720m)**의 평탄한 상업지역(건폐율 80% / 용적률 400%) **3방 각지(314.98㎡ / 약 95.28평)**에 위치한 **2014년 6월 신축(축 12.3년) 철골조 2층 건 복합 수익 부동산(1층 학원 점포 1실 + 주거 4호, 총 5호)**입니다.
 - **매매가격**: ¥80,000,000 (만실 연수입 ¥5,844,000 / 표면수익률 **7.31%** / 실질 NOI **¥4,531,600 [Cap Rate 5.66%]**)
@@ -52296,7 +51440,7 @@
 - **3대 연수 골든크로스 달성**: 채무상환연수(**21.9년**) &lt; 감가상각연수(**24.0년**) &lt; 융자연수(**25.0년**)를 완벽히 충족하여 보유 기간 중 데드크로스가 발생하지 않습니다.</t>
         </is>
       </c>
-      <c r="F112" s="0" t="inlineStr">
+      <c r="F102" s="0" t="inlineStr">
         <is>
           <t>**エスポワール クロス カスカベ**は、東武スカイツリーライン・東武アーバンパークラインの2路線急行停車駅**『春日部』駅 徒歩9分（実測720m）**の商業地域（建蔽率80% / 容積率400%）・**三方角地（314.98㎡ / 約95.28坪）**に位置する、**2014年6月新築（築12.3年）鉄骨造2階建の複合収益不動産（1階学習塾店舗1室＋住居4戸、計5戸）**です。
 - **物件価格**: ¥80,000,000（満室年収入 ¥5,844,000 / 表面利回り **7.31%** / 実質NOI **¥4,531,600 [Cap Rate 5.66%]**）
@@ -52305,26 +51449,28 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="0" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
         <is>
           <t>espoir-cross-kasukabe</t>
         </is>
       </c>
-      <c r="B113" s="0">
-        <v>2</v>
-      </c>
-      <c r="C113" s="0" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
         <is>
           <t>2. 물건 개요 및 레이와 8년도 과세명세서 정밀 실사</t>
         </is>
       </c>
-      <c r="D113" s="0" t="inlineStr">
+      <c r="D103" s="0" t="inlineStr">
         <is>
           <t>2. 物件概要および令和8年度課税明細書の精査</t>
         </is>
       </c>
-      <c r="E113" s="0" t="inlineStr">
+      <c r="E103" s="0" t="inlineStr">
         <is>
           <t>### 토지 4필지 및 가옥 2구분 과세명세서 검증 내역
 - **토지 4필지 합계 (314.98㎡)**: `粕壁東三丁目 1750-2 (65.95㎡, ¥5,236,156)` + `1750-4 (161.98㎡, ¥12,860,564)` + `1750-5 (72.72㎡, ¥5,773,677)` + `1751-1 (14.33㎡, ¥1,137,744)` = **평가액 ¥25,008,141** (고자세 과세표준 ¥4,168,024 [1/6 특례], 도계세 과세표준 ¥8,336,049 [1/3 특례]).
@@ -52332,7 +51478,7 @@
 - **소유자 개인정보 보호**: 납세통지서상 소유자 성명 및 자택 주소(도쿄도 네리마구)는 개인정보 보호 원칙에 따라 비공개 마스킹 처리하였습니다.</t>
         </is>
       </c>
-      <c r="F113" s="0" t="inlineStr">
+      <c r="F103" s="0" t="inlineStr">
         <is>
           <t>### 土地4筆および家屋2区分の課税明細検証内訳
 - **土地4筆合計 (314.98㎡)**: `粕壁東三丁目 1750-2 (65.95㎡, ¥5,236,156)` + `1750-4 (161.98㎡, ¥12,860,564)` + `1750-5 (72.72㎡, ¥5,773,677)` + `1751-1 (14.33㎡, ¥1,137,744)` = **評価額 ¥25,008,141**（固税課税標準 ¥4,168,024 [1/6特例]、都計税課税標準 ¥8,336,049 [1/3特例]）。
@@ -52340,33 +51486,35 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="0" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
         <is>
           <t>espoir-cross-kasukabe</t>
         </is>
       </c>
-      <c r="B114" s="0">
-        <v>3</v>
-      </c>
-      <c r="C114" s="0" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
         <is>
           <t>3. 입지, 상권 및 카스카베역 고가화 재개발 호재 분석</t>
         </is>
       </c>
-      <c r="D114" s="0" t="inlineStr">
+      <c r="D104" s="0" t="inlineStr">
         <is>
           <t>3. 立地・商圏および春日部駅高架化再開発の恩恵</t>
         </is>
       </c>
-      <c r="E114" s="0" t="inlineStr">
+      <c r="E104" s="0" t="inlineStr">
         <is>
           <t>- **2노선 급행 정차역 도보 9분**: 도부 스카이트리라인(히비야선·한조몬선 직통, 키타센주 26분, 오테마치 48분) 및 도부 어반파크라인(오미야역 급행 16분) 이용 가능.
 - **카스카베역 부근 연속입체교차사업(철도 고가화)**: 총 사업비 약 650억 엔 이상을 투입하여 건널목 10개소를 제거하고 동서 시가지를 일체화하는 대규모 재개발이 진행 중이며, 본건이 위치한 동구 상업지역(용적률 400%)의 장기 지가 상승 모멘텀이 매우 강력합니다.
 - **카스카베 소학교 교차점 코너 입지**: 초등학교 바로 앞 폭 16.1m 학교도리 코너에 위치하여 1층 학원 테넌트(`ITTO個別指導学院 春日部東校`)의 입지 적합성이 최상급입니다.</t>
         </is>
       </c>
-      <c r="F114" s="0" t="inlineStr">
+      <c r="F104" s="0" t="inlineStr">
         <is>
           <t>- **2路線急行停車駅 徒歩9分**: 東武スカイツリーライン（日比谷線・半蔵門線直通：北千住26分、大手町48分）および東武アーバンパークライン（大宮駅へ急行16分）が利用可能。
 - **春日部駅付近連続立体交差事業（鉄道高架化）**: 総事業費約650億円超の鉄道高架化事業により踏切10箇所が除却され、東口商業地域（容積率400%）の資産価値向上が見込まれます。
@@ -52374,26 +51522,28 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="0" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
         <is>
           <t>espoir-cross-kasukabe</t>
         </is>
       </c>
-      <c r="B115" s="0">
-        <v>4</v>
-      </c>
-      <c r="C115" s="0" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
         <is>
           <t>4. 적산평가 및 토지·건물 담보가치 정밀 검증</t>
         </is>
       </c>
-      <c r="D115" s="0" t="inlineStr">
+      <c r="D105" s="0" t="inlineStr">
         <is>
           <t>4. 積算価格および土地・建物担保評価の検証</t>
         </is>
       </c>
-      <c r="E115" s="0" t="inlineStr">
+      <c r="E105" s="0" t="inlineStr">
         <is>
           <t>- **토지 적산평가**: 전면 노선가 `98,000엔/㎡ (98D)` × `314.98㎡` = **¥30,868,040** (상업지역 3방 각지 가산 반영 시 약 3,350만 엔, 공시지가 환산 약 3,859만 엔).
 - **건물 적산평가 시나리오 비교 (연면적 282.41㎡, 철골조 법정 34년, 잔존 21.7년)**:
@@ -52403,7 +51553,7 @@
   4. 현행 신축시세 기준 (320,000엔/㎡): 건물 5,767.8만 + 토지 3,086.8만 = **8,854.6만 엔 (110.7%)**</t>
         </is>
       </c>
-      <c r="F115" s="0" t="inlineStr">
+      <c r="F105" s="0" t="inlineStr">
         <is>
           <t>- **土地積算評価**: 前面路線価 `98,000円/㎡ (98D)` × `314.98㎡` = **¥30,868,040**（三方角地加算反映時は約3,350万円、実勢公示地価換算は約3,859万円）。
 - **建物積算評価シナリオ比較（延床282.41㎡、鉄骨造法定34年、残存21.7年）**:
@@ -52414,58 +51564,62 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="0" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="0" t="inlineStr">
         <is>
           <t>espoir-cross-kasukabe</t>
         </is>
       </c>
-      <c r="B116" s="0">
-        <v>5</v>
-      </c>
-      <c r="C116" s="0" t="inlineStr">
+      <c r="B106" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
         <is>
           <t>5. 렌트롤 포렌식 감사 및 공실·회전율(DOM) 분석</t>
         </is>
       </c>
-      <c r="D116" s="0" t="inlineStr">
+      <c r="D106" s="0" t="inlineStr">
         <is>
           <t>5. レントロール復元およびLIFULL HOME'S空室・回転率分析</t>
         </is>
       </c>
-      <c r="E116" s="0" t="inlineStr">
+      <c r="E106" s="0" t="inlineStr">
         <is>
           <t>- **5호실 면적·임대료 완벽 복원**: 과세명세서(`주택 194.69㎡` + `점포 87.72㎡`)와 LIFULL HOME'S 아카이브(`b-40030480`) 대조 결과, **1층 점포(ITTO 개별지도학원 87.72㎡, 월 약 19.2만엔 추정) + 101호(2LDK 60.87㎡, 월 약 8.6만엔) + 201호(2LDK 60.87㎡, 월 8.7만엔) + 202호·203호(1LDK 35.70㎡×2호, 각 월 6.1만엔)**로 총 월수입 **¥487,000(연 ¥5,844,000)**을 구성합니다.
 - **초저회전 장기 정착 입증**: 2014년 준공 이후 12년간 홈즈 모집 이력은 단 2회(2018년 1LDK [DOM 135일], 2021년 2LDK [DOM 45일])뿐이며, **2021년 6월 이후 5년 이상 공실 모집 0건**입니다.</t>
         </is>
       </c>
-      <c r="F116" s="0" t="inlineStr">
+      <c r="F106" s="0" t="inlineStr">
         <is>
           <t>- **全5戸の面積・賃料構成復元**: 課税明細書（`住宅 194.69㎡` ＋ `店舗 87.72㎡`）とLIFULL HOME'Sアーカイブ（`b-40030480`）の照合により、**1階店舗（ITTO個別指導学院 87.72㎡、月額約19.2万円推定）＋ 101号室（2LDK 60.87㎡、約8.6万円）＋ 201号室（2LDK 60.87㎡、8.7万円）＋ 202・203号室（1LDK 35.70㎡×2戸、各6.1万円）**で月額総収入 **¥487,000（年 ¥5,844,000）**を構成します。
 - **超低回転・長期定着の実証**: 2014年新築以降12年間でHOME'S募集履歴はわずか2回のみであり、**2021年6月以降は5年以上空室募集ゼロ**です。</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="0" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
         <is>
           <t>espoir-cross-kasukabe</t>
         </is>
       </c>
-      <c r="B117" s="0">
-        <v>6</v>
-      </c>
-      <c r="C117" s="0" t="inlineStr">
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
         <is>
           <t>6. 운영경비(OPEX) 정규화 및 순영업소득(NOI) 모델링</t>
         </is>
       </c>
-      <c r="D117" s="0" t="inlineStr">
+      <c r="D107" s="0" t="inlineStr">
         <is>
           <t>6. 運営経費(OPEX)の正規化および純営業収益(NOI)分析</t>
         </is>
       </c>
-      <c r="E117" s="0" t="inlineStr">
+      <c r="E107" s="0" t="inlineStr">
         <is>
           <t>- **실질 연간 운영경비(OPEX) ¥1,312,400 (경비율 22.46%)**:
   1. 고정자산세·도시계획세(R8 납세통지서 확정 실액): **¥431,300 (7.38%)**
@@ -52476,7 +51630,7 @@
 - **만실 시 순영업소득(NOI)**: **¥4,531,600 / 년 (Cap Rate 5.66%)**.</t>
         </is>
       </c>
-      <c r="F117" s="0" t="inlineStr">
+      <c r="F107" s="0" t="inlineStr">
         <is>
           <t>- **実質年間運営経費(OPEX) ¥1,312,400（経費率 22.46%）**:
   1. 固定資産税・都市計画税（令和8年度確定実額）: **¥431,300 (7.38%)**
@@ -52488,33 +51642,35 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="0" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
         <is>
           <t>espoir-cross-kasukabe</t>
         </is>
       </c>
-      <c r="B118" s="0">
-        <v>7</v>
-      </c>
-      <c r="C118" s="0" t="inlineStr">
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
         <is>
           <t>7. 금융 조달, 현금흐름(Cash Flow) 및 금리 스트레스 테스트</t>
         </is>
       </c>
-      <c r="D118" s="0" t="inlineStr">
+      <c r="D108" s="0" t="inlineStr">
         <is>
           <t>7. 資金調達・キャッシュフローおよび金利ストレステスト</t>
         </is>
       </c>
-      <c r="E118" s="0" t="inlineStr">
+      <c r="E108" s="0" t="inlineStr">
         <is>
           <t>- **표준 대출 조달**: 융자 **6,800만 엔 (LTV 85%)**, 금리 **2.20%**, 기간 **25년** → 연간 원리금상환액(ADS) **¥3,538,654 (월 ¥294,888)**.
 - **연간 세전 캐시플로우**: 만실 시 **¥992,946** (공실 5% 차감 안정화 시 **¥766,212**, 세후 CF **¥256,329**).
 - **금리·공실 스트레스 테스트**: 손익분기 가동률(BEP)은 **83.0%**이며, 금리가 **3.20%(+1.0%p)**로 상승하더라도 만실 기준 **+55.5만 엔**, 공실 5% 기준 **+32.8만 엔**의 흑자 현금흐름을 방어합니다.</t>
         </is>
       </c>
-      <c r="F118" s="0" t="inlineStr">
+      <c r="F108" s="0" t="inlineStr">
         <is>
           <t>- **標準融資条件**: 借入 **6,800万円 (LTV 85%)**、金利 **2.20%**、期間 **25年** → 年間元利返済額(ADS) **¥3,538,654（月額 ¥294,888）**。
 - **年間税引前CF**: 満室時 **¥992,946**（空室5%控除時 **¥766,212**、税引後CF **¥256,329**）。
@@ -52522,33 +51678,35 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="0" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
         <is>
           <t>espoir-cross-kasukabe</t>
         </is>
       </c>
-      <c r="B119" s="0">
-        <v>8</v>
-      </c>
-      <c r="C119" s="0" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
         <is>
           <t>8. 법인 결산서 적합성 및 10~15년차 출구(Exit) 시뮬레이션</t>
         </is>
       </c>
-      <c r="D119" s="0" t="inlineStr">
+      <c r="D109" s="0" t="inlineStr">
         <is>
           <t>8. 法人決算書適合性および10〜15年目イグジット分析</t>
         </is>
       </c>
-      <c r="E119" s="0" t="inlineStr">
+      <c r="E109" s="0" t="inlineStr">
         <is>
           <t>- **감가상각 및 세무 구조**: 과세명세서상 건물 평가액 비중이 **47.11%**에 달해 건물 취득원가 안분액(약 3,768.7만 엔)을 간이법 **24년**간 연간 **¥1,570,277**씩 정액 상각합니다.
 - **보유 10년차(2036년) 엑시트**: 10년간 대출 원금 **약 2,282.4만 엔**이 상환되어 잔채가 **¥45,175,589**로 감소합니다. 카스카베역 고가화 완공 프리미엄을 반영한 캡레이트(표면 7.5% / 매각가 약 7,118만 엔) 매각 시 **누적 세후 CF 포함 총 ¥26,360,715 현금 회수(순이익 +¥8.76M, ROI +49.8%)**가 기대됩니다.
 - **7,300만 엔 네고 시 효과**: 표면수익률 **8.01%**, 단품 채무상환연수 **18.9년**, 단품 세후 CF **연 ¥499,389(약 2배)**로 수익성이 극대화됩니다.</t>
         </is>
       </c>
-      <c r="F119" s="0" t="inlineStr">
+      <c r="F109" s="0" t="inlineStr">
         <is>
           <t>- **減価償却および税務構造**: 課税明細書上の建物評価比率が **47.11%** と高く、建物按分取得原価（約3,768.7万円）を簡便法 **24年** にわたり年間 **¥1,570,277** 定額償却します。
 - **保有10年目（2036年）イグジット**: 10年間で元金 **約2,282.4万円** が返済され残債は **¥45,175,589** へ減少。春日部駅高架化完了プレミアムを反映した利回り（表面7.5% / 売却額約7,118万円）での売却時、**累積税引後CF込みで総額 ¥26,360,715 の現金回収（純利益 +¥8.76M、ROI +49.8%）**が見込まれます。
@@ -52556,58 +51714,62 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="0" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
         <is>
           <t>espoir-cross-kasukabe</t>
         </is>
       </c>
-      <c r="B120" s="0">
-        <v>9</v>
-      </c>
-      <c r="C120" s="0" t="inlineStr">
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
         <is>
           <t>9. 재해(Hazard), 건물 엔지니어링 및 법적 리스크 정밀 진단</t>
         </is>
       </c>
-      <c r="D120" s="0" t="inlineStr">
+      <c r="D110" s="0" t="inlineStr">
         <is>
           <t>9. ハザード・建物エンジニアリングおよび法的リスク診断</t>
         </is>
       </c>
-      <c r="E120" s="0" t="inlineStr">
+      <c r="E110" s="0" t="inlineStr">
         <is>
           <t>- **홍수 해저드 및 보험 대책**: 카스카베시 홍수 해저드맵(L2 최대강우)상 침수심 0.5m~3.0m 미만 상정 구역에 위치하나, 인근 수도권 외곽방수로(G-Cans)의 배수 보호를 받으며 화재보험 가입 시 **수재(水災) 담보 특약(연 15만 엔 예산 반영 완료)**으로 재무 리스크를 헤지합니다.
 - **육지붕 방수 주기 점검**: 2014년 6월 신축 후 12.3년 경과 시점이므로 옥상 육지붕(陸屋根) 방수 탑코트 및 외벽 실링 보수 이력을 확인하고, 미실시 시 향후 수선비(약 150만~200만 엔)를 가격 네고 근거로 활용합니다.</t>
         </is>
       </c>
-      <c r="F120" s="0" t="inlineStr">
+      <c r="F110" s="0" t="inlineStr">
         <is>
           <t>- **洪水ハザードおよび保険対策**: 春日部市洪水ハザードマップ（L2最大降雨）では浸水深0.5m〜3.0m未満想定区域ですが、近隣の首都圏外郭放水路による治水効果が高く、火災保険の**水災補償特約付帯（年15万円予算計上済）**によりリスクをヘッジします。
 - **陸屋根防水周期の確認**: 2014年6月築（築12.3年）のため、屋上陸屋根防水トップコートおよび外壁シーリングの修繕履歴を確認し、未実施の場合は指値交渉材料（約150万〜200万円）として活用します。</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="0" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
         <is>
           <t>espoir-cross-kasukabe</t>
         </is>
       </c>
-      <c r="B121" s="0">
-        <v>10</v>
-      </c>
-      <c r="C121" s="0" t="inlineStr">
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
         <is>
           <t>10. 종합 의사결정 스코어카드 및 중개사 필수 질의서</t>
         </is>
       </c>
-      <c r="D121" s="0" t="inlineStr">
+      <c r="D111" s="0" t="inlineStr">
         <is>
           <t>10. 総合意思決定スコアカードおよび仲介会社への必須確認事項</t>
         </is>
       </c>
-      <c r="E121" s="0" t="inlineStr">
+      <c r="E111" s="0" t="inlineStr">
         <is>
           <t>- **종합 스코어**: **25.3 / 30.0점 (A- 등급: 우량 매수 검토 — 7,300만~7,500만 엔 지가 네고 추천)**
 - **중개사(株式会社リブライフマーケティング) 최우선 징구 서류 5선**:
@@ -52618,7 +51780,7 @@
   5. **과거 12년간 수선 이력(修繕履歴) 및 토지·건물 등기사항전부증명서**.</t>
         </is>
       </c>
-      <c r="F121" s="0" t="inlineStr">
+      <c r="F111" s="0" t="inlineStr">
         <is>
           <t>- **総合スコア**: **25.3 / 30.0点（ランク A-：優良買付検討 — 7,300万〜7,500万円への指値交渉推奨）**
 - **仲介会社（株式会社リブライフマーケティング）への最優先徴求資料5選**:
@@ -52627,6 +51789,578 @@
   3. **1階店舗（ITTO個別指導学院 春日部東校）賃貸借契約書写し**: 普通/定期借家の別、解約予告期間、原状回復特約。
   4. **建築確認済証および検査済証の写し**。
   5. **過去12年間の修繕履歴および土地・建物全部事項証明書**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B112" s="0">
+        <v>1</v>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>물건 기본 개요 (Property Overview)</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t>物件基本概要 (Property Overview)</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>![마이소쿠 및 건축확인필증](./assets/maisoku_overview.png)
+| 항목 | 세부 내용 (등기부·공과증명서·확정측량도·실시설계도 교차 검증 완료) |
+| :--- | :--- |
+| **물건명** | **미츠쿄 1AP 사사노다이 신축 아파트 (三ツ境1AP 新築一棟アパート)** |
+| **소재지 (지번 / 주거표시)** | **[지번]** 神奈川県横浜市旭区笹野台二丁目149番3、231番102&lt;br&gt;**[주거표시]** **神奈川県横浜市旭区笹野台2丁目19-5** (`35°28'12.8"N 139°30'02.6"E`) |
+| **교통 (구글맵 실측)** | 소테츠 본선(相鉄本線, 급행·통근급행 정차) **「미츠쿄(三ツ境)」역 도보 10분** (마이소쿠 표기 도보 7분 / 구글맵 실측 약 720m·도보 10분, 전면도로 진입부 계단 구간 존재) |
+| **매매가격 (호가)** | **1억 3,470만 엔 (¥134,700,000)** ※ 건물 소비세 포함 |
+| **목표 매수가 (네고 타겟)** | **1억 2,300만 ~ 1억 2,500만 엔** (표면 6.87~7.12% / 실질 NOI 5.50~5.59% — 미검사 옹벽 및 임대료 상단 리스크 반영) |
+| **토지 면적 (공부 vs 실측)** | **[등기부 지적]** 합계 **399.56㎡** (`149番3`: 386.62㎡ + `231番102`: 12.94㎡)&lt;br&gt;**[확정측량 실측]** 합계 **397.71㎡ (120.30평)** = **유효택지 397.42㎡ (120.22평)** (`149-3`: 384.52㎡ + `231-102`: 12.90㎡) + 잠정 후퇴부분(SB) **0.29㎡** |
+| **토지 권리 / 지목** | 소유권 (所有権) / 택지 (宅地) |
+| **도시계획 / 용도지역** | 시가지화구역 / **제1종 저층주거전용지역 (第一種低層住居専用地域)** · 제1종 고도지구 |
+| **건폐율 / 용적률** | 법정 건폐율 **40%** (실적 **39.57%** = 건축면적 `157.24㎡`) / 법정 용적률 **80%** (실적 **60.92%** = 연면적 `242.07㎡`) |
+| **접도 조건 (100% 공도 확인)** | **남서측 폭원 3.92~4.50m 요코하마시 공도(`下川井第402号線`, 지번 `231-1` 요코하마시 소유 공중용도로)** 및 **서측 폭원 4.00~5.50m 요코하마시 공도(`下川井第398号線`)** 접도&lt;br&gt;※ **사도 부담 없음(100% 공도)**, 단 `下川井第402号線`의 부지 전면 구간은 **계단(階段) 도로**임 (차량은 계단 직전까지 동·서 양방향 접근 가능) |
+| **건물 구조 / 규모** | **목조(木造) 준내화구조(準耐火構造) 지상 2층건** · 공동주택 **총 9세대** (1층 5세대, 2층 4세대)&lt;br&gt;**[기초 공법]** RC 베타기초(`地耐力 20kN/㎡`) + **길이 `7.00m` 기초 파일(`杭長 7.00m`)** (요코하마시 벼랑조례 안식각 45° 대응) |
+| **건물 면적 및 평면 구성** | **연면적 242.07㎡ (73.22평)** (1층 `134.48㎡`, 2층 `107.59㎡` / 최고높이 `8.10m`, 처마높이 `5.87m`)&lt;br&gt;• **전 9세대 `1LDK (26.89㎡)`**: `LDK 8.0帖(12.98㎡) + 洋室 5.5帖(8.94㎡)` (전 실 2인 입주 가능 설계)&lt;br&gt;• **5세대(`105, 201, 202, 203, 204호`) 대형 로프트(`4.82㎡ / 3.0帖`) 부착** (로프트 포함 실사용 면적 **31.71㎡**!) |
+| **건축확인번호 / 성능평가** | **제26UDI1K건00271호** (令和8年6月18日 교부 / UDI확인검사(주), 설계: 일급건축사사무소 스페이스팩토리ING)&lt;br&gt;• **설계주택성능평가서 『열화대책등급 3급(劣化対策等級3級)』 취득 완료**&lt;br&gt;• **건설주택성능평가서 『열화대책등급 3급』 준공 시 취득 예정** (최장 30~35년 장기 융자 적격) |
+| **준공 및 인도 예정일** | **2026년 12월 말 준공 예정 / 2027년 1월 인도 예정** (기존 11월 말에서 약 1개월 순연 확인) |
+| **매도자 / 프로젝트 금융** | **야오키상사 주식회사 (ヤオキ商事株式会社)** (카와사키시 타카츠구 소재 업력 50년 디벨로퍼)&lt;br&gt;• **[을구 근저당권]** 2025년 6월 27일 매수 시 **카와사키신용금고(川崎信用金庫 登戸支店) 차입금 7,700만 엔, 금리 연 3.050%** 근저당 설정 확인 |
+| **설비 및 특기사항** | 공영수도 · 공공하수 · **도시가스** · **전 세대 무료 WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정)** · 독립세면대 · UB1014 · IH 2구 시스템키친(W1200) · 실내물건걸이 · 1층 수동셔터 |
+---</t>
+        </is>
+      </c>
+      <c r="F112" s="0" t="inlineStr">
+        <is>
+          <t>![マイソクおよび建築確認済証](./assets/maisoku_overview.png)
+| 項目 | 詳細内容（登記簿・公課証明書・確定測量図・実施設計図 照合済） |
+| :--- | :--- |
+| **物件名** | **三ツ境1AP 新築一棟アパート** |
+| **所在地（地番 / 住居表示）** | **【地番】** 神奈川県横浜市旭区笹野台二丁目149番3、231番102&lt;br&gt;**【住居表示】** **神奈川県横浜市旭区笹野台2丁目19-5** (`35°28'12.8"N 139°30'02.6"E`) |
+| **交通（Googleマップ実測）** | 相鉄本線（急行・通勤急行停車）**「三ツ境」駅 徒歩10分**（マイソク表記：徒歩7分 / Googleマップ実測：約720m・徒歩10分、前面道路に階段区間あり） |
+| **売出価格** | **1億3,470万円 (¥134,700,000)** ※建物消費税込み |
+| **目標買付価格（指値）** | **1億2,300万 〜 1億2,500万円**（表面6.87〜7.12% / 実質NOI利回り5.50〜5.59% — 無検査擁壁・賃料上限リスク反映） |
+| **土地面積（公簿 vs 実測）** | **【登記簿地積】** 合計 **399.56㎡**（`149番3`: 386.62㎡ ＋ `231番102`: 12.94㎡）&lt;br&gt;**【確定測量実測】** 合計 **397.71㎡ (120.30坪)** ＝ **有効宅地 397.42㎡ (120.22坪)** ＋ 暫定後退部分(SB) **0.29㎡** |
+| **土地権利 / 地目** | 所有権 / 宅地 |
+| **都市計画 / 用途地域** | 市街化区域 / **第一種低層住居専用地域** ・ 第1種高度地区 |
+| **建蔽率 / 容積率** | 法定建蔽率 **40%**（実績 **39.57%** ＝ 建築面積 `157.24㎡`） / 法定容積率 **80%**（実績 **60.92%** ＝ 延床面積 `242.07㎡`） |
+| **接道条件（100%公道確定）** | **南西側 幅員3.92〜4.50m 横浜市公道（`下川井第402号線`、地番`231-1` 横浜市所有 公衆用道路）** および **西側 幅員4.00〜5.50m 横浜市公道（`下川井第398号線`）** 接道&lt;br&gt;※**私道負担なし（100%公道）**。ただし`下川井第402号線`の敷地前面区間は**階段道路**（車両は階段手前まで東西双方から進入可） |
+| **建物構造 / 規模** | **木造 準耐火構造 地上2階建** ・ 共同住宅 **全9戸**（1階5戸、2階4戸）&lt;br&gt;**【基礎工法】** RCベタ基礎（`地耐力 20kN/㎡`）＋ **長さ`7.00m`基礎杭（`杭長 7.00m`）**（横浜市がけ条例 安息角45°対応） |
+| **建物面積および間取り** | **延床面積 242.07㎡ (73.22坪)**（1階 `134.48㎡`、2階 `107.59㎡` / 最高高さ `8.10m`、最高軒高 `5.87m`）&lt;br&gt;• **全9戸 `1LDK (26.89㎡)`**：`LDK 8.0帖(12.98㎡) ＋ 洋室 5.5帖(8.94㎡)`（全室2人入居可能）&lt;br&gt;• **5戸（`105, 201, 202, 203, 204号室`）に大型ロフト（`4.82㎡ / 3.0帖`）付帯**（ロフト含む実使用面積 **31.71㎡**！） |
+| **建築確認番号 / 性能評価** | **第26UDI1K建00271号**（令和8年6月18日交付 / ユーディーアイ確認検査(株)、設計：一級建築士事務所スペースファクトリーING）&lt;br&gt;• **設計住宅性能評価書『劣化対策等級3級』取得済**&lt;br&gt;• **建設住宅性能評価書『劣化対策等級3級』竣工時取得予定**（最長30〜35年長期融資適格） |
+| **竣工および引渡予定日** | **2026年12月末竣工予定 / 2027年1月引渡予定**（当初11月末より約1ヶ月順延） |
+| **売主 / プロジェクト融資** | **ヤオキ商事株式会社**（川崎市高津区坂戸3-2-1 KSP西414）&lt;br&gt;• **【乙区抵当権】** 令和7年6月27日取得時に**川崎信用金庫（登戸支店）債権額7,700万円・利息年3.050%**の共同抵当権設定を確認 |
+| **設備および特記事項** | 公営水道 ・ 公共下水 ・ **都市ガス** ・ **全戸無料WiFi（オーナー負担：月額7,920円[税込]・10年縛り）** ・ 独立洗面台 ・ UB1014 ・ IH2口システムキッチン(W1200) ・ 室内物干 ・ 1階手動シャッター |
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B113" s="0">
+        <v>2</v>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>등기부등본(甲区·乙区)·공과증명서·건축도면 포렌식 실사 (Forensic Due Diligence)</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t>登記簿謄本・公課証明書・実施設計図フォレンジック調査 (Forensic Due Diligence)</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t>### 2.1 등기부등본(全部事項証明書) 권리관계 및 매도자 조달금리 분석
+`05_touhon_sokuryo_kouka.pdf` (1~6페이지) 등기부등본 전수 조사 결과:
+1. **갑구 (소유권 이력)**:
+   - 구 소유자 개인(1957년/1982년 취득 → 1997년 상속 → 2003년 매매)을 거쳐, **令和7年(2025년) 6월 27일 현 매도자인 『야오키상사 주식회사(ヤオキ商事株式会社)』가 매매로 소유권을 취득**했습니다.
+   - `149番3` 토지는 1983년(소화 58년) 지적 정정을 통해 `384.06㎡ → 386.62㎡`로 등기되었으며, `231番102` 토지는 `12.94㎡`로 등기되어 공부상 합계 면적은 **`399.56㎡`**입니다.
+2. **을구 (담보권 및 매도자 협상 레버리지 핵심 단서)**:
+   - 현 매도자(야오키상사)는 2025년 6월 27일 토지 취득과 동시에 **카와사키신용금고(川崎信用金庫 登戸支店)**로부터 **채권액 7,700만 엔(이자 연 3.050%, 손해금 연 14.50%)의 공동담보 저당권(목록 (イ)第5921号)**을 설정했습니다.
+   - **💡 협상 전략적 시사점**: 중개사(오카다상)에 따르면 매도자는 *"초기에는 가격 네고에 잘 응하지 않으나 안 팔리면 시기를 보아 가격을 내리는 스탠스"*입니다. 그러나 매도자는 현재 **연 3.05%라는 높은 프로젝트 조달금리(월 이자만 약 19.6만 엔)**를 부담하고 있으며, 공정이 당초 11월 말에서 **12월 말 준공(2027년 1월 인도)**으로 지연되었습니다. 따라서 연말 준공 시점까지 매수자가 확정되지 않을 경우 매도자의 이자 및 재고 보유 압박이 급증하므로, 이를 지렛대로 **1억 2,300만 ~ 1억 2,500만 엔** 선의 조건부 매수의향서(LOI) 타진이 매우 유효합니다.
+---
+### 2.2 🚨 최대 핵심 리스크: 기존 간지블록 옹벽(98.84㎡) &amp; 토사재해경계구역(Yellow/Red Zone) 정밀 진단
+![현황평면도 및 옹벽면적 산출도](./assets/retaining_wall_calc.png)
+![단면도 및 7.0m 기초파일 안식각 45도 시공도](./assets/section_piles.png)
+![가나가와현 토사재해 하저드맵](./assets/hazard_landslide.jpg)
+이번 2차 실사 자료(`현황평면도`, `옹벽면적도`, `실시설계 단면도`, `가측량도`, `오카다상 질의응답`)를 통해 밝혀진 가장 중요한 물리적·법적 팩트입니다.
+| 검증 항목 | 실사 확인 결과 (Hard Fact) | 투자 리스크 및 대응 방안 |
+| :--- | :--- | :--- |
+| **1. 지형 및 옹벽 규모** | • 부지 레벨(GL `12.14~12.26m`)이 북측·동측·남측 인접지 및 도로(`7.63~8.37m`)보다 **약 4.0m ~ 4.69m 높은 고대(高台) 지형**&lt;br&gt;• 옹벽 면적 산출도(`擁壁面積`)상 **총 7개 구간(①~⑦), 합계 면적 `98.84㎡`** (구간별 높이 `1.162m ~ 3.488m`, 단면도상 최대 단차 `4.690m`) | 높이 2m를 초과하는 대형 간지블록(間知ブロック) 옹벽이 부지 3면을 둘러싸고 있음 |
+| **2. 옹벽 소유권 및 유지관리 책임** | • **동측(東) 및 북측(北) 옹벽**: **매도자 소유 → 매수자(투자자)에게 소유권 및 유지보수 책임 승계!**&lt;br&gt;• **서측(西) 옹벽**: **서측 인접지 소유자 소유** (고저차 큰 노후 옹벽) | 동·북측 옹벽의 향후 균열·배부름 보수비 및 지진·호우로 인한 붕괴 시 인접 저지대 가옥에 대한 **민법상 공작물 배상책임(민법 717조)**이 매수자에게 귀속됨 |
+| **3. 축조시기 및 검사필증 유무** | • **축조시기 불명(築造時期不明) / 택지조성 및 공작물 검사필증 없음(検査済証なし)**&lt;br&gt;• 매도자 측의 **보강 공사나 재축조 계획 없음(補強・造り直し予定なし)**&lt;br&gt;• 단, 실시설계 배치도(`配置図`)상 일급건축사 육안 점검 결과 **『間知ブロック 亀裂、たわみ無し 水抜き穴あり 安全支障無し(균열·배부름 없음, 배수공 있음, 안전지장 없음)』**으로 기재됨 | 검사필증이 없는 구형 옹벽이므로, 향후 재건축 시에는 옹벽 재축조(수천만 엔 소요) 또는 벼랑조례 파일 재시공이 필요하며, 일부 보수적 시중은행(1금융권)에서 담보 평가를 감액할 수 있음 |
+| **4. 벼랑조례(がけ条例) 및 신축 허가 통과 비결** | • 요코하마시 건축기준조례 제4조(벼랑 부근의 건축물) 및 **『横浜市がけ関係小規模建築物技術指針』**에 의거하여, **옹벽 하단으로부터 45° 안식각(`安息角 45°`) 아래의 견고한 지지층까지 길이 `7.00m`의 기초 파일(`杭長 7.00m`)을 관입**하고 RC 베타기초를 얹는 공법을 채택!&lt;br&gt;• 또한 성토규제법(`盛土規制法`) 저촉을 피하기 위해 **성토 없음(`盛土無し`)**으로 설계하여 건축확인(`제26UDI1K건00271호`)을 적법 취득함 | **건물 본체의 구조적 안전성(침하·전도 방지)은 7.0m 파일 시공으로 확보**되었음. 준공 시 **『7.0m 파일 시공 보고서 및 지반조사 보고서』** 사본을 반드시 수령해야 함 |
+| **5. 토사재해경계구역 저촉 여부** | • 가나가와현 토사재해 포털 및 가측량도(`06_karisoku.pdf`) 확인 결과, **부지 북서측(北西) 모서리 옹벽 부분(약 4.69㎡ 삼각형 구간)이 토사재해경계구역(옐로우존 / 잠정 레드존 경계)에 일부 걸쳐 있음(かすっている)**을 매도자가 공식 확인함&lt;br&gt;• 건물 본체는 북측·서측 경계로부터 `2.00m` 이상 이격되어 있어 건물 자체는 구역 밖에 위치함 | 중요사항설명서(重説)에 토사재해경계구역(일부) 해당 사실이 기재되며, 화재·지진보험 가입 시 **시설소유관리자 배상책임보험(옹벽 손해 담보)** 특약을 반드시 추가해야 함 |
+---
+### 2.3 전면도로 공도(公道) 확인 및 계단 접근로 분석
+![요코하마시 인정노선도 하카와이 제402호선](./assets/road_map_402.png)
+![현황평면도 계단 및 레벨 상세](./assets/survey_topography.png)
+1. **사도(私道) 리스크 완전 해소**:
+   - 1차 분석 당시 마이소쿠에 `公道・私道`로 혼재 표기되어 있었으나, 이번에 수령한 **도로 등기부(`笹野台二丁目231番1`, 지목: 공중용도로, 소유자: `横浜市`)** 및 **요코하마시 인정노선도(`下川井第402号線` 폭원 4.00~4.50m, `下川井第398号線` 폭원 4.00~5.50m)**를 통해 **부지에 접한 모든 도로가 100% 요코하마시 공도(公道)**임이 확정되었습니다. 따라서 사도 지분 누락이나 굴착 승낙 거부 리스크는 **0%**입니다.
+2. **전면도로 계단(階段) 구간 유의사항**:
+   - 현황평면도(`survey_topography.png`)에서 확인되듯, 남서측 전면도로(`下川井第402号線`)의 부지 접도 구간 중 서측 절반은 **경사 계단(階段)**으로 되어 있습니다.
+   - 자동차는 계단 아래쪽(남동측)과 계단 위쪽(`下川井第398号線`, 북서측) 양방향에서 계단 바로 앞까지 진입할 수 있으나, 부지 내 주차장은 없으며 이사 차량 정차 시 계단 앞 도로를 이용해야 합니다.
+---
+### 2.4 건축 상세 도면(`1階・2階 平面詳細図`) 분석: 전 세대 `1LDK(26.89㎡)` + 5세대 `로프트(4.82㎡)`
+![1층 평면상세도](./assets/plan_1f.png)
+![2층 평면상세도](./assets/plan_2f.png)
+실시설계 평면상세도(`02_plans_elevations.pdf` 2~3p)를 통해 확인된 본 건물의 상품 스펙은 일반 신축 목조 원룸(14~18㎡)을 압도합니다:
+- **전 9세대 `1LDK` (`26.89㎡`) 표준 구성**:
+  - 전 호실이 **`LDK 8.0帖 (12.98㎡) + 洋室 5.5帖 (8.94㎡)`**으로 분리된 정통 **컴팩트 1LDK** 구조입니다(소방법상 각 실 수용인원 2명, 1인 가구 재택근무자 및 **신혼·동거 커플 2인 입주 가능**!).
+- **5개 호실(`105호`, `201~204호`) 대형 로프트(`4.82㎡`) 서비스 면적**:
+  - 2층 4개 호실(`201~204호`)뿐 아니라 **1층 동측 끝단 단층 구조인 `105호`에도 `2.65m × 1.82m = 4.82㎡ (약 3.0帖, 천장고 1.4m 이하, 이동식 사다리)` 로프트가 시공**됩니다!
+  - 즉, 9세대 중 5세대는 **실사용 면적이 `26.89㎡ + 4.82㎡ = 31.71㎡ (약 9.6평)`**에 달합니다.
+- **내화·차음·설비 사양**:
+  - **준내화구조(`準耐火構造`)**: 벽체 석고보드 `12.5+12.5mm` 양면 시공, 세대 간 차음 경계벽 천장 속까지 밀실 시공(`界壁遮音 天井裏まで達しせめる` + 글라스울 충전).
+  - **설비**: 시스템키친 `W1200` (`IH 2구 콘로 200V 3000W`), 유닛배스 `UB 1014`, 독립 세면화장대, 실내 빨래걸이(`室内物干`), 1층 전 창문 **방범용 수동 셔터(`手動シャッター`)**, 전 세대 **무료 WiFi**.
+---</t>
+        </is>
+      </c>
+      <c r="F113" s="0" t="inlineStr">
+        <is>
+          <t>### 2.1 登記簿謄本（甲区・乙区）の権利関係および売主の借入条件分析
+1. **甲区（所有権履歴）**：
+   - 旧個人所有者（昭和32年/57年取得→平成9年相続→平成15年売買）を経て、**令和7年（2025年）6月27日に現売主である『ヤオキ商事株式会社』が売買により取得**しています。
+2. **乙区（抵当権および指値交渉の強力なレバレッジ）**：
+   - 売主（ヤオキ商事）は令和7年6月27日付で**川崎信用金庫（登戸支店）より債権額7,700万円・金利年3.050%**のプロジェクト融資を借り入れています。
+   - **💡 指値交渉への示唆**：仲介担当者（岡田様）によれば「売主は当初は値下げに応じないが、売れなければ時期を見て価格を下げるスタンス」とのことですが、**年3.050%という高金利（月間利息だけで約19.6万円）**を負担しながら竣工が**2026年12月末（引渡2027年1月）**へ遅れているため、竣工前後のタイミングで**1億2,300万〜1億2,500万円**の指値買付を入れる交渉戦略が極めて有効です。
+---
+### 2.2 🚨 最大の重要リスク：既存間知ブロック擁壁（98.84㎡）＆土砂災害警戒区域の精密診断
+![擁壁面積算出図](./assets/retaining_wall_calc.png)
+![断面図および7.0m基礎杭・安息角45度施工図](./assets/section_piles.png)
+![神奈川県土砂災害ハザードマップ](./assets/hazard_landslide.jpg)
+| 検証項目 | 実査確認結果 (Hard Fact) | 投資リスクおよび対策 |
+| :--- | :--- | :--- |
+| **1. 高低差および擁壁規模** | • 敷地レベル（GL `12.14〜12.26m`）が北・東・南側の隣地および道路（`7.63〜8.37m`）より**約4.0m〜4.69m高い高台**&lt;br&gt;• 擁壁面積図（`擁壁面積`）上、**全7区間（①〜⑦）合計 `98.84㎡`**（高さ`1.162m〜3.488m`、断面図上の最大高低差`4.690m`） | 高さ2m超の間知ブロック擁壁が敷地を取り囲んでいる |
+| **2. 擁壁の所有権と管理責任** | • **東側および北側擁壁**：**売主所有 → 買主（投資家）へ所有権・維持管理責任が承継！**&lt;br&gt;• **西側擁壁**：**西側隣地所有者の所有**（高低差が大きい古い擁壁） | 東・北側擁壁の将来の補修費用および万一の崩壊時の**工作物責任（民法717条）**は買主負担となる |
+| **3. 築造時期・検査済証の有無** | • **築造時期不明・検査済証なし・補強や造り直し予定なし**&lt;br&gt;• ただし配置図（`配置図`）上の一級建築士による現況確認では**『間知ブロック 亀裂、たわみ無し 水抜き穴あり 安全支障無し』**と明記 | 検査済証のない既存擁壁のため、一部の都市銀行・地方銀行では担保評価が厳しくなる可能性あり |
+| **4. 横浜市がけ条例のクリア手法** | • **『横浜市がけ関係小規模建築物技術指針』**に基づき、**擁壁下端から安息角45°（`安息角 45°`）より深い支持層まで長さ`7.00m`の基礎杭（`杭長 7.00m`）を打設**してRCベタ基礎を支持！&lt;br&gt;• 盛土規制法に抵触しないよう**盛土無し（`盛土無し`）**で設計し、建築確認済証（`第26UDI1K建00271号`）を適法に取得 | **建物本体の構造安全性（沈下・倒壊防止）は7.0m杭によって確保済**。引渡時に必ず**『杭施工報告書・地盤調査報告書』**を受領すること |
+| **5. 土砂災害警戒区域への抵触** | • 神奈川県土砂災害情報ポータルおよび仮測量図（`06_karisoku.pdf`）にて、**敷地北西角の擁壁部分（約4.69㎡）が土砂災害警戒区域（イエローゾーン／暫定レッドゾーン境界）にかすっている**ことを売主も認識&lt;br&gt;• 建物本体は北・西境界から`2.00m`離隔しており区域外 | 重要事項説明書に記載される事項であり、火災・地震保険加入時に**施設所有者賠償責任特約**を必ず付帯すること |
+---
+### 2.3 前面道路の公道確定および階段アプローチの確認
+![横浜市認定路線図 下川井第402号線](./assets/road_map_402.png)
+![現況平面図 階段および高低差詳細](./assets/survey_topography.png)
+- **100%横浜市公道と確定**：道路登記簿（`笹野台二丁目231番1`、所有者：`横浜市`）および認定路線図（`下川井第402号線`・`下川井第398号線`）により、**接道する道路はすべて横浜市所有の公道**であることが証明されました。私道トラブルのリスクはありません。
+- **階段部分の注意点**：南西側`下川井第402号線`の敷地前面西側半分は**階段**となっています。車両は階段の上側・下側の両方から階段手前まで進入可能です。
+---
+### 2.4 実施設計平面詳細図：全9戸`1LDK（26.89㎡）`＋5戸`ロフト（4.82㎡）`
+![1階平面詳細図](./assets/plan_1f.png)
+![2階平面詳細図](./assets/plan_2f.png)
+- **全9戸が`1LDK（26.89㎡）`**：全戸が`LDK 8.0帖（12.98㎡）＋洋室 5.5帖（8.94㎡）`の1LDK設計（消防法上の収容人員：各室2名、カップル・新婚の2人入居に対応）。
+- **5戸（`105号室`、`201〜204号室`）に`4.82㎡（約3.0帖）`ロフト付帯**：2階4戸だけでなく**1階東端の下屋部分である`105号室`にも`4.82㎡`のロフトが設置**されており、ロフト含む実使用面積は**31.71㎡**に達します。
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B114" s="0">
+        <v>3</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>토지·건물 적산가격(積算価格) 및 령화 8년도 공과증명서(公課証明書) 정밀 평가</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t>令和8年度 公課証明書（固定資産税評価額）および積算価格検証</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>### 3.1 령화 8년도 고정자산세·도시계획세 공과증명서(令和8年度 公課証明書) 실측 내역
+요코하마시 아사히구청장이 2026년 4월 30일 발급한 공식 공과증명서(`05_touhon_sokuryo_kouka.pdf` 12~13p) 수치입니다:
+| 필지 (지번) | 등기 지적 | 확정측량 유효면적 | R8 고정자산세 평가액 (評価額) | ㎡당 평가단가 | R8 나대지 기준 세액 (고정+도계) | 신축 완공 후 소규모 주택용지 특례(1/6·1/3) 적용 시 연간 세액 |
+| :--- | :---: | :---: | :---: | :---: | :---: | :---: |
+| **笹野台二丁目149番3** | 386.62㎡ | 384.52㎡ (+SB 0.20㎡) | **¥35,787,480** | ¥92,565/㎡ | ¥397,154 | **약 ¥119,291** |
+| **笹野台二丁目231番102** | 12.94㎡ | 12.90㎡ (+SB 0.09㎡) | **¥1,197,791** | ¥92,565/㎡ | ¥13,291 | **약 ¥3,992** |
+| **토지 2필지 합계** | **399.56㎡** | **397.42㎡ (120.22평)** | **¥36,985,271** | **¥92,565/㎡** | ¥410,445 | **약 ¥123,283 / 년 (약 12.3만 엔)** |
+| **신축 건물 (추정)** | - | **242.07㎡ (73.22평)** | **약 ¥26,627,700** (11만/㎡) | ¥110,000/㎡ | - | **약 ¥450,000 / 년 (첫 3년은 감면으로 약 25만 엔)** |
+| **토지 + 건물 총계** | - | - | **¥63,612,971 (약 6,361만 엔)** | - | - | **정상화 시 약 ¥573,283 / 년 (약 57.3만 엔)** |
+&gt; [!TIP] **공과증명서 핵심 인사이트 (보유세 절감 vs 고저차 보정)**
+&gt; - **왜 토지 고정자산세 평가액이 `3,698.5만 엔(92,565엔/㎡)`인가?**: 사사노다이 2초메 표준 주택가의 상속세 노선가는 약 `190,000円/㎡`(공시지가 약 `240,000円/㎡`)이나, 본 필지는 **남서측 계단 도로 접도 및 4m 이상 고저차(옹벽)**가 존재하여 요코하마시 세무과에서 **지형·접도 감가 보정**을 대폭 반영했기 때문입니다.
+&gt; - **투자자 실익**: 토지 공적 평가액이 낮게 책정된 덕분에, 9세대 공동주택 준공 후 **소규모 주택용지 특례(200㎡×9호=1,800㎡까지 고정자산세 1/6, 도시계획세 1/3 감면)**가 적용되면 **120.3평 대토지의 연간 보유세가 불과 `12.3만 엔` 수준**으로 낮아져 현금흐름(NOI)을 강력하게 방어합니다!
+---
+### 3.2 적산가격(積算価格) 3대 시나리오 및 지형 보정(がけ地補正) 비교
+일반 평탄지 노선가(`190,000円/㎡`) 기준 적산과, 금융기관이 고저차·계단 접도 감가(**-20%, 실효 노선가 `152,000円/㎡`**)를 적용한 보수적 담보 적산을 병행 산출했습니다.
+| 평가 시나리오 | 토지 평가 기준 | 토지 적산가 | 건물 단가 (`242.07㎡`×22/22년) | 건물 적산가 | **합계 적산가격** | **호가(1.347억) 대비 비율** |
+| :--- | :--- | :---: | :---: | :---: | :---: | :---: |
+| **① 은행 엄격 담보 기준 (지형감가 -20%)** | 유효 `397.42㎡` × 15.2만 엔/㎡ | ¥60,407,840 | 150,000엔/㎡ | ¥36,310,500 | **¥96,718,340** | **71.80%** |
+| **② 금융기관 표준 기준 (노선가 원안+15만)** | 유효 `397.42㎡` × 19.0만 엔/㎡ | ¥75,509,800 | 150,000엔/㎡ | ¥36,310,500 | **¥111,820,300** | **83.01%** |
+| **③ 국세청 표준 적산 (노선가 원안+18만)** | 유효 `397.42㎡` × 19.0만 엔/㎡ | ¥75,509,800 | 180,000엔/㎡ | ¥43,572,600 | **¥119,082,400** | **88.41%** |
+| **④ 실세 공시지가 + 신축 재조달원가(22만)** | 유효 `397.42㎡` × 24.0만 엔/㎡ | ¥95,380,800 | 220,000엔/㎡ | ¥53,255,400 | **¥148,636,200** | **110.35%** |
+- 지형 감가(-20%)를 엄격히 반영하더라도 적산비율이 **71.80%(9,672만 엔)**를 상회하며, 표준 노선가 기준으로는 **83.01% ~ 88.41%**에 달합니다.
+---</t>
+        </is>
+      </c>
+      <c r="F114" s="0" t="inlineStr">
+        <is>
+          <t>### 3.1 令和8年度 固定資産・都市計画税 公課証明書（実測値）
+| 筆（地番） | 登記地積 | 確定測量有効面積 | R8 固定資産税評価額 | ㎡単価 | R8 更地時点年税額 | 完成後・小規模住宅用地特例（1/6・1/3）適用時の年税額 |
+| :--- | :---: | :---: | :---: | :---: | :---: | :---: |
+| **笹野台二丁目149番3** | 386.62㎡ | 384.52㎡ (+SB 0.20㎡) | **¥35,787,480** | ¥92,565/㎡ | ¥397,154 | **約 ¥119,291** |
+| **笹野台二丁目231番102** | 12.94㎡ | 12.90㎡ (+SB 0.09㎡) | **¥1,197,791** | ¥92,565/㎡ | ¥13,291 | **約 ¥3,992** |
+| **土地2筆 合計** | **399.56㎡** | **397.42㎡ (120.22坪)** | **¥36,985,271** | **¥92,565/㎡** | ¥410,445 | **約 ¥123,283 / 年（約12.3万円）** |
+| **新築建物（見込）** | - | **242.07㎡ (73.22坪)** | **約 ¥26,627,700** (11万/㎡) | ¥110,000/㎡ | - | **約 ¥450,000 / 年（当初3年間は軽減で約25万円）** |
+| **土地＋建物 総計** | - | - | **¥63,612,971（約6,361万円）** | - | - | **通常時 約 ¥573,283 / 年（約57.3万円）** |
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B115" s="0">
+        <v>4</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤 포렌식 및 REINS 근린 성약 50건(`03_comps_1R_1K.pdf`) 비교 검증</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t>レントロールおよびREINS近隣成約事例50件（`03_comps_1R_1K.pdf`）比較検証</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>### 4.1 호실별 상정 렌트롤 및 평면 스펙 (전 9세대)
+| 호실 | 층수 / 위치 | 상세 평면 (전유면적 + 로프트) | 상정 월임대료 (공익비·무료WiFi 포함) | 연간 임대료 | 전유 ㎡당 단가 | 로프트 포함(31.71㎡) 실효 ㎡단가 | 비고 |
+| :---: | :---: | :--- | :---: | :---: | :---: | :---: | :--- |
+| **101호** | 1F 서측 각실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥80,000** | ¥960,000 | 2,975엔/㎡ | 2,975엔/㎡ | 1층 남서·북서 2면 채광 각실, 수동셔터 |
+| **102호** | 1F 중실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥78,000** | ¥936,000 | 2,901엔/㎡ | 2,901엔/㎡ | 7만 엔대(7.8만) 진입 호실, 수동셔터 |
+| **103호** | 1F 중실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥78,000** | ¥936,000 | 2,901엔/㎡ | 2,901엔/㎡ | 7만 엔대(7.8만) 진입 호실, 수동셔터 |
+| **104호** | 1F 중실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥78,000** | ¥936,000 | 2,901엔/㎡ | 2,901엔/㎡ | 7만 엔대(7.8만) 진입 호실, 수동셔터 |
+| **105호** | 1F 동측 단층 각실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥80,000** | ¥960,000 | 2,975엔/㎡ | **2,523엔/㎡** | **1층 유일 로프트 부착** + 2면 채광 각실! |
+| **201호** | 2F 서측 각실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥85,000** | ¥1,020,000 | 3,161엔/㎡ | **2,681엔/㎡** | 최상층 각실 + 4.82㎡ 대형 로프트 |
+| **202호** | 2F 중실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥83,000** | ¥996,000 | 3,087엔/㎡ | **2,617엔/㎡** | 최상층 중실 + 4.82㎡ 대형 로프트 |
+| **203호** | 2F 중실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥83,000** | ¥996,000 | 3,087엔/㎡ | **2,617엔/㎡** | 최상층 중실 + 4.82㎡ 대형 로프트 |
+| **204호** | 2F 동측 각실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥85,000** | ¥1,020,000 | 3,161엔/㎡ | **2,681엔/㎡** | 최상층 각실 + 4.82㎡ 대형 로프트 |
+| **합계** | **전 9세대** | **전유 242.07㎡ (+로프트 24.10㎡ = 266.17㎡)** | **¥730,000 / 월** | **¥8,760,000 / 년** | **3,016엔/㎡** | **2,743엔/㎡** | **전 실 2인 입주 가능 1LDK + 무료 WiFi** |
+---
+### 4.2 REINS 근린 성약 사례 50건(`03_comps_1R_1K.pdf`) 대조 및 임대료 적정성 진단
+오카다상이 제공한 미츠쿄·키보가오카·세야역 주변 24~31㎡ 성약 데이터 50건 중 주요 경쟁 신축·축천 사례와의 비교표입니다:
+| 비교 물건명 (소재지) | 최기역 / 도보 | 준공연월 | 면적 / 타입 | 성약 임대료 + 관리비 = **월 총액** | ㎡당 단가 | 본건(`미츠쿄 1AP`) 대비 시사점 |
+| :--- | :--- | :---: | :---: | :---: | :---: | :--- |
+| **가칭 요코하마 미츠쿄 AP** (미츠쿄) | 미츠쿄역 **도보 3분** | **2025.06 (신축)** | 25.05㎡ / 1K | 6.9~7.4만 + 4,000엔 = **7.3~7.8만 엔** | 2,914~3,114엔 | 역 도보 3분 신축 1K가 7.3~7.8만 엔에 성약됨 (예금 1개월) |
+| **KOMA 미츠쿄** (사사노다이 1초메) | 미츠쿄역 **도보 7분** | 2021.12 (축4년) | 24.77㎡ / 1K | 6.6~6.7만 + 3,000엔 = **6.9~7.0만 엔** | 2,786~2,826엔 | 동일 사사노다이 권역 1K(축4년) 실세는 약 7.0만 엔 수준 |
+| **그린힐 키보가오카** (나카키보가오카) | 키보가오카역 **도보 4분** | **2025.07 (신축)** | 26.45㎡ / 1R | 7.3만 + 3,000엔 = **7.6만 엔** | 2,873엔 | 인접역 도보 4분 26.45㎡ 신축이 총 7.6만 엔에 성약 |
+| **트윈즈 요코하마 세야** (세야) | 세야역 **도보 5~6분** | **2024.10 (신축)** | 28.66㎡ / 1K | 8.0만 + 5,000엔 = **8.5만 엔** | 2,966엔 | 28.6㎡급 대형 평면은 8.5만 엔 성약 가능 입증 |
+| **일 피오레 사사노다이** (사사노다이 1초메) | 미츠쿄역 **도보 5분** | 2015.02 (축11년) | 28.56㎡ / 1K | 7.2만 + 3,000엔 = **7.5만 엔** | 2,626엔 | 사사노다이 28㎡급 기축은 평균 DOM 30일 내 안정 소화 |
+| **⭐ 본건: 미츠쿄 1AP** (사사노다이 2-19-5) | 미츠쿄역 **도보 10분** | **2026.12 (신축)** | **26.89㎡ `1LDK` (+로프트 4.82㎡×5실)** | **1F 7.8~8.0만 / 2F 8.3~8.5만** (무료WiFi 포함) | **3,016엔** (로프트 포함 2,743엔) | **1K가 아닌 『1LDK(2인 입주 가능)+로프트+무료WiFi』로 차별화했으나, 도보 10분 기준 지역 시세 최상단(Upper Bound)에 위치!** |
+&gt; [!IMPORTANT] **임대료 스트레스 테스트 결론**
+&gt; - 미츠쿄역 도보 3분 신축 1K(25㎡)가 7.3~7.8만 엔에 성약된 점을 감안할 때, 도보 10분(계단 접근)인 본건이 **1층 7.8~8.0만 엔 / 2층 8.3~8.5만 엔**을 달성하려면 반드시 포털(SUUMO/HOME'S) 등록 시 **『1K가 아닌 1LDK(2인 입주 가능) + 3조 대형 로프트 + 무료 WiFi 완비』** 카테고리로 노출시켜 **커플·동거 수요 및 광폭 재택근무 수요**를 타겟팅해야 합니다.
+&gt; - 만약 1인 가구 위주로 모집하여 **임대료를 -5% 인하(1층 7.4~7.6만 엔, 2층 7.9~8.1만 엔 → 연수입 832.2만 엔)**하더라도, **만실 NOI는 645.4만 엔(Cap 4.79%), 30년 융자 시 DSCR 1.22배, 세전 CF +116.7만 엔/년**으로 여전히 안정적인 흑자가 유지됩니다.
+---</t>
+        </is>
+      </c>
+      <c r="F115" s="0" t="inlineStr">
+        <is>
+          <t>### 4.1 REINS成約事例50件との比較
+- **仮称 横浜三ツ境アパート**（2025年6月新築、三ツ境駅**徒歩3分**、25.05㎡・1K）：成約賃料 **6.9〜7.4万円＋共益費4,000円＝計7.3〜7.8万円**（礼金1ヶ月）。
+- **KOMA三ツ境**（2021年12月築、笹野台1丁目、三ツ境駅**徒歩7分**、24.77㎡・1K）：成約賃料 **6.6〜6.7万円＋共益費3,000円＝計6.9〜7.0万円**。
+- **グリーンヒル希望ヶ丘**（2025年7月新築、希望ヶ丘駅**徒歩4分**、26.45㎡・1R）：成約賃料 **7.3万円＋共益費3,000円＝計7.6万円**。
+- **ツインズ横浜瀬谷**（2024年10月新築、瀬谷駅**徒歩5〜6分**、28.66㎡・1K）：成約賃料 **8.0万円＋共益費5,000円＝計8.5万円**。
+- **診断結論**：本物件（徒歩10分・階段あり）の想定賃料（1階7.8〜8.0万円、2階8.3〜8.5万円、無料WiFi込）は近隣相場の**上限（アッパーバウンド）**に位置します。ただし近隣事例がすべて「1R/1K」であるのに対し、本物件は**『1LDK（26.89㎡・2人入居可）＋大型ロフト4.82㎡（5戸）＋無料WiFi』**という明確な差別化要素を持つため、募集時は必ず「1LDK・二人入居可」としてポータル掲載する必要があります。万一賃料を**-5%引き下げ（年収入832.2万円）**た場合でも、**満室NOI 645.4万円・DSCR 1.22倍・税引前CF +116.7万円/年**と黒字を維持できます。
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B116" s="0">
+        <v>5</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>운영경비(OPEX) 정규화 및 현금흐름·손익분기(BEP) 모델링</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t>モアビズ4期 決算書着地シミュレーション（令和8年度公課証明書反映）</t>
+        </is>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>### 5.1 실질 운영경비(OPEX) 명세 (오카다상 확인 확정치 반영)
+| 경비 항목 | 연간 금액 (엔) |GPI 대비 비율 | 산출 근거 (2차 실사 검증 완료) |
+| :--- | :---: | :---: | :--- |
+| **1. 고정자산세·도시계획세 (보유세)** | **¥573,000** | 6.54% | **[토지]** R8 공과증명서(평가액 3,698.5만) 주택용지 특례(1/6·1/3) 적용 **¥123,000**&lt;br&gt;**[건물]** 오카다상 확인 목조 신축 평가 기준 **¥450,000** (※ 초기 3년간은 신축 감면으로 합계 약 37만 엔/년) |
+| **2. PM 임대관리 위탁수수료** | **¥438,000** | 5.00% | 만실 임대수입(876만 엔)의 5.0% |
+| **3. 전 세대 무료 WiFi 런닝코스트** | **¥95,040** | 1.08% | **오카다상 확인 확정치: 월 7,920엔(세금포함) × 12개월 (※ 10년 약정 조건)** |
+| **4. 공용부 전기·수도·정기청소·소방** | **¥144,000** | 1.64% | 공용등 전기·공용 수도·월 2회 순회청소 및 소방점검 (월 1.2만 엔) |
+| **5. 화재·지진보험 + 옹벽 배상책임특약** | **¥90,000** | 1.03% | **목조 준내화구조(`準耐火構造`) 할인 적용** + 시설소유관리자 배상책임특약(옹벽) |
+| **6. 퇴거 원상복구비·장기수선·옹벽점검 적립** | **¥550,000** | 6.28% | 퇴거 원상복구·AD 충당(연 25만) + 외벽·지붕·옹벽 배수공 유지적립(연 30만) |
+| **실질 운영경비 (Normalized OPEX) 합계** | **¥1,890,040** | **21.58%** | **만실 순영업소득 (NOI) = ¥6,869,960 (≒ ¥6,870,000, 실질 Cap Rate 5.10%)** |
+---
+### 5.2 금융 조달 및 매수가·임대료별 스트레스 테스트 (LTV 85%, 금리 2.3%, 기간 30년)
+설계·건설 주택성능평가 **열화대책등급 3급** 취득에 따른 **30년 원리금균등상환(금리 2.3%)** 기준 시나리오 비교입니다:
+| 구분 시나리오 | 매매가격 | 대출금액 (85%) | 연간 총수입 (GPI) | 실질 NOI | 연간 원리금 (ADS) | **만실 세전 CF** | **DSCR** | **손익분기 가동률 (허용공실)** |
+| :--- | :---: | :---: | :---: | :---: | :---: | :---: | :---: | :---: |
+| **① 기본안 (호가 1.347억 · 상정임대료)** | ¥134,700,000 | ¥114,495,000 | ¥8,760,000 | ¥6,870,000 | ¥5,287,219 | **+¥1,582,781** | **1.30배** | **81.93% (1.63실 / 9실)** |
+| **② 임대료 -5% 보수안 (호가 1.347억)** | ¥134,700,000 | ¥114,495,000 | ¥8,322,000 | ¥6,453,900 | ¥5,287,219 | **+¥1,166,681** | **1.22배** | **85.98% (1.26실 / 9실)** |
+| **③ 1차 네고안 (1.27억 · 상정임대료)** | ¥127,000,000 | ¥107,950,000 | ¥8,760,000 | ¥6,870,000 | ¥4,984,980 | **+¥1,885,020** | **1.38배** | **78.48% (1.94실 / 9실)** |
+| **④ 공격적 네고안 (1.24억 · 상정임대료)** | **¥124,000,000** | **¥105,400,000** | ¥8,760,000 | ¥6,870,000 | **¥4,867,225** | **+¥2,002,775** | **1.41배** | **77.14% (2.06실 / 9실)** |
+| **⑤ 공격적 네고 + 임대료 -5% 복합안** | **¥124,000,000** | **¥105,400,000** | ¥8,322,000 | ¥6,453,900 | **¥4,867,225** | **+¥1,586,675** | **1.33배** | **80.96% (1.71실 / 9실)** |
+---</t>
+        </is>
+      </c>
+      <c r="F116" s="0" t="inlineStr">
+        <is>
+          <t>| 決算書コア指標 | 本物件単体 (稼働93%) | モアビズ4期現在 | **取得後決算着地** | **1.24億指値時単体** | 財務貢献度および判定 |
+| :--- | :---: | :---: | :---: | :---: | :--- |
+| **固定資産税評価額 (土地+建物)** | **3,699万 + 2,663万 = 6,361万** | 7,186万 + 4,191万 = 1.138億 | **1.088億 + 6,853万 = 1.774億** | **6,361万円** | R8公課証明書実測値を100%反映 |
+| **1. 帳簿上税引前当期純利益** | **+¥2,955,270** | +¥3,722,450 | **+¥6,677,720 (+79.4%)** | **+¥3,384,100** | **法人黒字規模 +79.4%大幅増益！** |
+| **2. 税引前手残りCF (利回り)** | **+¥1,246,795 (0.93%)** | +¥1,741,901 (0.65%) | **+¥2,988,696 (+71.6%)** | **+¥1,666,550 (1.34%)** | 満室時は単体税引前CF +158.3万円 |
+| **3. 推定法人税額 (25%)** | ▲¥738,818 | ▲¥930,613 | **▲¥1,669,430** | ▲¥846,025 | 22年新築減価償却(年251万)節税 |
+| **4. 税引後手残りCF (利回り)** | **+¥507,977 (0.38%)** | +¥811,289 (0.30%) | **+¥1,319,266 (+62.6%)** | **+¥820,525 (0.66%)** | 法人税引後キャッシュ +62.6%純増 |
+| **5. 債務償還年数 (C)** | **24.2年** (融資30年以内) | 24.1年 | **24.2年** | **20.5年** | **単体24.2年 $\ll$ 融資30.0年 ゴールデンクロス！** |
+| **6. 利子支払倍率 (ICR)** | **1.54倍** | 0.90倍 | **1.05倍 (+0.15倍)** | **1.77倍** | **法人統合ICR 1.0倍突破達成！** |
+| **7. 負債返済余裕率 (DSCR)** | **1.53倍 (満室1.30倍)** | 1.50倍 | **1.51倍 (+0.01倍)** | **1.66倍 (満室1.41倍)** | **法人統合DSCR上昇に貢献！** |
+| **8. 固定資産税評価LTV** | **218.01%** (単純合算180.0%) | 261.08% | **245.45% (▲15.63%p改善)** | **200.69%** | **公課証明書基準でも法人LTV ▲15.63%p改善！** |
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B117" s="0">
+        <v>6</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>모아비즈 4기 결산서 디자인형 적합성 분석 (Moabiz Corporate Landing)</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="inlineStr">
+        <is>
+          <t>総合スコアカード（19.5 / 30点：条件付検討）および最終提言</t>
+        </is>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>**령화 8년도 공과증명서 실측 토지 평가액(`36,985,271円`)** 및 **건물 평가액(`26,627,700円`)**을 반영한 모아비즈 4기 결산서 착지 시뮬레이션(가동률 93% 보수적 기준, 결산 경비율 19.8%, 건물 비중 41%, 감가상각 22년 = 연 251.0만 엔) 결과입니다:
+| 핵심 결산 지표 | 본 물건 단품 (93% 가동) | 모아비즈 4기 현재 | **편입 후 결산서 착지** | **1.24억 네고 시 단품** | 재무적 기여도 및 판정 |
+| :--- | :---: | :---: | :---: | :---: | :--- |
+| **자산 총액 / 총 차입금** | 1.347억 / 1.145억 | 2.675억 / 2.407억 | **4.022억 / 3.552억** | 1.240억 / 1.054억 | 우량 신축 자산 편입으로 외형 확대 |
+| **고정자산세 평가액 (토지+건물)** | **3,699만 + 2,663만 = 6,361만** | 7,186만 + 4,191만 = 1.138억 | **1.088억 + 6,853만 = 1.774억** | **6,361만 엔** | R8 공과증명서 실측치 100% 반영 |
+| **1. 장부상 세전 당기순이익** | **+¥2,955,270** | +¥3,722,450 | **+¥6,677,720 (+79.4%)** | **+¥3,384,100** | **법인 흑자 규모 +79.4% 점프업!** |
+| **2. 세전 잔여 CF (수익률)** | **+¥1,246,795 (0.93%)** | +¥1,741,901 (0.65%) | **+¥2,988,696 (+71.6%)** | **+¥1,666,550 (1.34%)** | 만실 시 단품 세전 CF +158.3만 엔 |
+| **3. 추정 법인세액 (25%)** | ▲¥738,818 | ▲¥930,613 | **▲¥1,669,430** | ▲¥846,025 | 22년 신축 감가상각(연 251만) 절세 |
+| **4. 세후 잔여 CF (수익률)** | **+¥507,977 (0.38%)** | +¥811,289 (0.30%) | **+¥1,319,266 (+62.6%)** | **+¥820,525 (0.66%)** | 법인 세후 잉여현금 +62.6% 순증 |
+| **5. 채무상환연수 (C)** | **24.2년** (융자 30년 이내) | 24.1년 | **24.2년** | **20.5년** | **단품 24.2년 $\ll$ 융자 30.0년 골든크로스!** |
+| **6. 이자보상배율 (ICR)** | **1.54배** | 0.90배 | **1.05배 (+0.15배)** | **1.77배** | **법인 통합 ICR 1.0배 돌파 달성!** |
+| **7. 부채상환여유율 (DSCR)** | **1.53배 (만실 1.30배)** | 1.50배 | **1.51배 (+0.01배)** | **1.66배 (만실 1.41배)** | **법인 통합 DSCR 상승 기여!** |
+| **8. 고정자산세 평가 LTV** | **218.01%** (단순합산 180.0%) | 261.08% | **245.45% (▲15.63%p 개선)** | **200.69%** | **공과증명서 실측 기준으로도 법인 LTV ▲15.63%p 개선!** |
+---</t>
+        </is>
+      </c>
+      <c r="F117" s="0" t="inlineStr">
+        <is>
+          <t>| 評価項目 (配点) | 1次スコア | **2次確定スコア** | 評価根拠 |
+| :--- | :---: | :---: | :--- |
+| **1. 価格・積算価値 (5点)** | 4.0 | **3.5 / 5.0** | 120.3坪宅地（路線価標準積算88.4%）は優秀だが、公課証明書評価額（3,698.5万円）に表れた高低差・階段接道補正（-20%補正時71.8%）を反映 |
+| **2. 賃貸需要・立地 (5点)** | 4.0 | **3.5 / 5.0** | 全9戸`1LDK(26.89㎡)＋ロフト(5戸)`は強いが、実測徒歩10分および前面道路の階段区間を反映 |
+| **3. 賃料競争力 (5点)** | 3.5 | **3.0 / 5.0** | 近隣成約50件（徒歩3分新築1Kが7.3〜7.8万円）対比で想定賃料（7.8〜8.5万円）は上限水準のため、1LDK訴求と初期ADバッファが必要 |
+| **4. 出口戦略 (5点)** | 4.0 | **3.5 / 5.0** | 120.3坪の土地と劣化3級は強みだが、東・北側の無検査既存擁壁（98.84㎡）が将来売却時の審査ハードルとなり得る |
+| **5. CF・DSCR (5点)** | 3.5 | **3.5 / 5.0** | 劣化3級30年融資でDSCR 1.30倍、土地固都税特例（年12.3万円）により実質NOI 687万円（Cap 5.10%）を堅守 |
+| **6. 法的・物理的安定性 (5点)** | 3.5 | **2.5 / 5.0** | 前面道路100%公道確定および7.0m基礎杭（安息角45°対応）はプラスだが、**東・北側既存擁壁（98.84㎡）検査済証なし＆北西角の土砂災害警戒区域抵触**により減点 |
+| **合計スコア・総合判定** | 22.5 / 30 | **19.5 / 30点** | **【条件付検討（擁壁・賃料リスクを織り込んだ1.23〜1.25億円への指値交渉必須）】** |</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B118" s="0">
+        <v>7</v>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>35개 표준 실사 체크리스트 완결성 감사 (Data Collection Audit: 94.3% 완료!)</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="inlineStr">
+        <is>
+          <t>35標準DDチェックリスト監査 (94.3%完了)</t>
+        </is>
+      </c>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t>이번 `20260925 OKD 三ツ境` 구글 드라이브 폴더(11개 파일) 수령을 통해 **35개 표준 실사 항목 중 33개(94.3%)가 공식 공부 및 설계도서로 검증 완료(`VERIFIED`/`COLLECTED`)**되었습니다!
+| 구분 | 1차 분석 시점 (마이소쿠 단독) | **2차 업데이트 현시점 (드라이브 11종 반영 후)** | 주요 해결 내역 |
+| :--- | :---: | :---: | :--- |
+| **수집/검증 완료 (`VERIFIED`/`COLLECTED`)** | 23건 | **33건 (94.3%)** | ✅ 등기부등본(갑·을구), ✅ R8 공과증명서(토지 2필지), ✅ 확정측량도, ✅ 현황평면도·옹벽면적도, ✅ 실시설계도(배치·평면·입면·단면·7m파일), ✅ 인정노선도 2종, ✅ 토사재해 하저드맵, ✅ REINS 성약 50건, ✅ 무료 WiFi 비용(월 7,920엔)·준공일(12월 말) |
+| **추정 적용 (`ESTIMATED`)** | 9건 | **2건 (5.7%)** | ⚠️ 건물분 고정자산세 본칙 세액(준공 후 가옥조사 시 확정, 현재 오카다상 45만 엔 추정), ⚠️ 초기 리싱 달성 임대료 및 실제 AD(광고료)개월 수 |
+| **미수집 (`MISSING`)** | 3건 | **0건 (0.0%)** | (미수집 항목 전수 해소 완료!) |
+---</t>
+        </is>
+      </c>
+      <c r="F118" s="0" t="inlineStr">
+        <is>
+          <t>이번 `20260925 OKD 三ツ境` 구글 드라이브 폴더(11개 파일) 수령을 통해 **35개 표준 실사 항목 중 33개(94.3%)가 공식 공부 및 설계도서로 검증 완료(`VERIFIED`/`COLLECTED`)**되었습니다!
+| 구분 | 1차 분석 시점 (마이소쿠 단독) | **2차 업데이트 현시점 (드라이브 11종 반영 후)** | 주요 해결 내역 |
+| :--- | :---: | :---: | :--- |
+| **수집/검증 완료 (`VERIFIED`/`COLLECTED`)** | 23건 | **33건 (94.3%)** | ✅ 등기부등본(갑·을구), ✅ R8 공과증명서(토지 2필지), ✅ 확정측량도, ✅ 현황평면도·옹벽면적도, ✅ 실시설계도(배치·평면·입면·단면·7m파일), ✅ 인정노선도 2종, ✅ 토사재해 하저드맵, ✅ REINS 성약 50건, ✅ 무료 WiFi 비용(월 7,920엔)·준공일(12월 말) |
+| **추정 적용 (`ESTIMATED`)** | 9건 | **2건 (5.7%)** | ⚠️ 건물분 고정자산세 본칙 세액(준공 후 가옥조사 시 확정, 현재 오카다상 45만 엔 추정), ⚠️ 초기 리싱 달성 임대료 및 실제 AD(광고료)개월 수 |
+| **미수집 (`MISSING`)** | 3건 | **0건 (0.0%)** | (미수집 항목 전수 해소 완료!) |
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B119" s="0">
+        <v>8</v>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>종합 스코어카드 (30점 만점) 및 최종 의사결정 권고</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="inlineStr">
+        <is>
+          <t>総合スコアカード (19.5/30点) および提言</t>
+        </is>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t>| 평가 영역 (배점) | 1차 점수 | **2차 확정 점수** | 변경 사유 및 핵심 근거 |
+| :--- | :---: | :---: | :--- |
+| **1. 가격 및 적산가치 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 택지(표준 노선가 적산 88.4%)는 탁월하나, 공과증명서상 토지 평가액(3,698.5만 엔)에 반영된 고저차·계단 접도 감가(-20% 보정 시 적산 71.8%)를 반영하여 0.5점 조정 |
+| **2. 임차 수요 및 입지 (5점)** | 4.0 | **3.5 / 5.0** | 미츠쿄역 급행 정차 및 전 세대 `1LDK(26.89㎡)+로프트(5실)` 평면은 우수하나, 실측 도보 10분 및 남서측 전면도로 계단 구간 존재를 반영하여 0.5점 조정 |
+| **3. 임대료 경쟁력 (5점)** | 3.5 | **3.0 / 5.0** | REINS 성약 50건 대조 결과, 도보 3분 신축 1K(7.3~7.8만 엔) 대비 본건(7.8~8.5만 엔)은 1LDK+로프트 감안 시에도 지역 시세 상단에 해당하여 초기 리싱 버퍼 필요 |
+| **4. 출구 전략 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 토지 및 열화 3급은 장기 매각에 유리하나, 동·북측 미검사 기존 옹벽(98.84㎡)이 차기 매수자 실사 시 허들로 작용 가능 |
+| **5. 현금흐름 및 DSCR (5점)** | 3.5 | **3.5 / 5.0** | 열화 3급 30년 융자 시 DSCR 1.30배, 토지 보유세 특례(연 12.3만 엔) 덕분에 실질 NOI 687만 엔(Cap 5.10%) 견고 유지 |
+| **6. 법적·물리적 안정성 (5점)** | 3.5 | **2.5 / 5.0** | 전면도로 100% 공도 확정 및 건물 7.0m 파일 기초(안식각 45° 대응)는 긍정적이나, **동·북측 기존 옹벽(98.84㎡) 검사필증 부재 및 북서측 토사재해 구역 일부 저촉**으로 1.0점 감점 |
+| **총점 및 종합 등급** | 22.5 / 30 | **19.5 / 30점** | **【조건부 검토 (옹벽·임대료 리스크 반영 공격적 지값 필수)】** |
+### 🎯 매수 실행을 위한 4대 실전 액션 플랜
+1. **준공 시점(2026.12 말)을 활용한 공격적 지값(1.23억~1.25억 엔) 협상**:
+   - 매도자(야오키상사)가 카와사키신용금고로부터 **7,700만 엔을 연 3.05% 고금리**로 조달 중이며 준공이 12월 말(인도 2027년 1월)로 지연된 점을 활용하여, 미검사 기존 옹벽 리스크 인수 조건으로 **1억 2,300만 ~ 1억 2,500만 엔(수익률 7.0~7.1%)** 지값 협상을 추진하십시오.
+2. **『7.00m 기초 파일 시공보고서·지반조사서』 및 『건설주택성능평가서(열화 3급)』 징구 특약**:
+   - 잔금 결제(2027년 1월) 전 인도 서류 목록에 ① 벼랑조례 대응 **7.00m 파일 시공 사진·시공보고서**, ② **건설주택성능평가서(열화대책등급 3급)**, ③ **검사필증(건축물)**을 필수 조건으로 명시하십시오.
+3. **옹벽 배수공 정기 관리 및 시설소유관리자 배상책임보험 가입**:
+   - 동·북측 간지블록 옹벽(98.84㎡)의 수압 상승을 막기 위해 배수공(水抜き穴) 청소 및 균열 점검을 연 1회 실시하고, 화재·지진보험 가입 시 반드시 **옹벽 붕괴 배상책임 특약**을 부가하십시오.
+4. **포털 리싱 시 『1LDK(2인 입주 가능) + 4.82㎡ 로프트 + 무료 WiFi』 카테고리 등록 지시**:
+   - 일반 1R/1K 검색 필터가 아닌 **1DK/1LDK 및 2인 입주 가능(二人入居可) 필터**에 노출시켜 미츠쿄역 역세권 1K 신축(7.3~7.8만 엔)과의 단순 가격 경쟁을 피하고 2027년 1~3월 성수기 조기 만실을 달성하십시오.</t>
+        </is>
+      </c>
+      <c r="F119" s="0" t="inlineStr">
+        <is>
+          <t>| 평가 영역 (배점) | 1차 점수 | **2차 확정 점수** | 변경 사유 및 핵심 근거 |
+| :--- | :---: | :---: | :--- |
+| **1. 가격 및 적산가치 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 택지(표준 노선가 적산 88.4%)는 탁월하나, 공과증명서상 토지 평가액(3,698.5만 엔)에 반영된 고저차·계단 접도 감가(-20% 보정 시 적산 71.8%)를 반영하여 0.5점 조정 |
+| **2. 임차 수요 및 입지 (5점)** | 4.0 | **3.5 / 5.0** | 미츠쿄역 급행 정차 및 전 세대 `1LDK(26.89㎡)+로프트(5실)` 평면은 우수하나, 실측 도보 10분 및 남서측 전면도로 계단 구간 존재를 반영하여 0.5점 조정 |
+| **3. 임대료 경쟁력 (5점)** | 3.5 | **3.0 / 5.0** | REINS 성약 50건 대조 결과, 도보 3분 신축 1K(7.3~7.8만 엔) 대비 본건(7.8~8.5만 엔)은 1LDK+로프트 감안 시에도 지역 시세 상단에 해당하여 초기 리싱 버퍼 필요 |
+| **4. 출구 전략 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 토지 및 열화 3급은 장기 매각에 유리하나, 동·북측 미검사 기존 옹벽(98.84㎡)이 차기 매수자 실사 시 허들로 작용 가능 |
+| **5. 현금흐름 및 DSCR (5점)** | 3.5 | **3.5 / 5.0** | 열화 3급 30년 융자 시 DSCR 1.30배, 토지 보유세 특례(연 12.3만 엔) 덕분에 실질 NOI 687만 엔(Cap 5.10%) 견고 유지 |
+| **6. 법적·물리적 안정성 (5점)** | 3.5 | **2.5 / 5.0** | 전면도로 100% 공도 확정 및 건물 7.0m 파일 기초(안식각 45° 대응)는 긍정적이나, **동·북측 기존 옹벽(98.84㎡) 검사필증 부재 및 북서측 토사재해 구역 일부 저촉**으로 1.0점 감점 |
+| **총점 및 종합 등급** | 22.5 / 30 | **19.5 / 30점** | **【조건부 검토 (옹벽·임대료 리스크 반영 공격적 지값 필수)】** |
+### 🎯 매수 실행을 위한 4대 실전 액션 플랜
+1. **준공 시점(2026.12 말)을 활용한 공격적 지값(1.23억~1.25억 엔) 협상**:
+   - 매도자(야오키상사)가 카와사키신용금고로부터 **7,700만 엔을 연 3.05% 고금리**로 조달 중이며 준공이 12월 말(인도 2027년 1월)로 지연된 점을 활용하여, 미검사 기존 옹벽 리스크 인수 조건으로 **1억 2,300만 ~ 1억 2,500만 엔(수익률 7.0~7.1%)** 지값 협상을 추진하십시오.
+2. **『7.00m 기초 파일 시공보고서·지반조사서』 및 『건설주택성능평가서(열화 3급)』 징구 특약**:
+   - 잔금 결제(2027년 1월) 전 인도 서류 목록에 ① 벼랑조례 대응 **7.00m 파일 시공 사진·시공보고서**, ② **건설주택성능평가서(열화대책등급 3급)**, ③ **검사필증(건축물)**을 필수 조건으로 명시하십시오.
+3. **옹벽 배수공 정기 관리 및 시설소유관리자 배상책임보험 가입**:
+   - 동·북측 간지블록 옹벽(98.84㎡)의 수압 상승을 막기 위해 배수공(水抜き穴) 청소 및 균열 점검을 연 1회 실시하고, 화재·지진보험 가입 시 반드시 **옹벽 붕괴 배상책임 특약**을 부가하십시오.
+4. **포털 리싱 시 『1LDK(2인 입주 가능) + 4.82㎡ 로프트 + 무료 WiFi』 카테고리 등록 지시**:
+   - 일반 1R/1K 검색 필터가 아닌 **1DK/1LDK 및 2인 입주 가능(二人入居可) 필터**에 노출시켜 미츠쿄역 역세권 1K 신축(7.3~7.8만 엔)과의 단순 가격 경쟁을 피하고 2027년 1~3월 성수기 조기 만실을 달성하십시오.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B120" s="0">
+        <v>9</v>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>입지·도보 10분(계단 접도)·토사재해 하저드 검증</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="inlineStr">
+        <is>
+          <t>立地・実測徒歩10分(階段接道)・土砂災害検証</t>
+        </is>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t>챕터 9 상세 분석은 본문 참조</t>
+        </is>
+      </c>
+      <c r="F120" s="0" t="inlineStr">
+        <is>
+          <t>챕터 9 상세 분석은 본문 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B121" s="0">
+        <v>10</v>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>최종 투자 의사결정 요약</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t>最終投資意思決定サマリー</t>
+        </is>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>챕터 10 상세 분석은 본문 참조</t>
+        </is>
+      </c>
+      <c r="F121" s="0" t="inlineStr">
+        <is>
+          <t>챕터 10 상세 분석은 본문 참조</t>
         </is>
       </c>
     </row>

--- a/moabiz/data/real_estate_datastore.xlsx
+++ b/moabiz/data/real_estate_datastore.xlsx
@@ -6319,13 +6319,13 @@
         </is>
       </c>
       <c r="E13" s="0">
-        <v>97.1</v>
+        <v>91.4</v>
       </c>
       <c r="F13" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G13" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -40785,59 +40785,59 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="0" t="inlineStr">
+      <c r="A401" s="3" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B401" s="0" t="inlineStr">
+      <c r="B401" s="3" t="inlineStr">
         <is>
           <t>CHK_15</t>
         </is>
       </c>
-      <c r="C401" s="0" t="inlineStr">
+      <c r="C401" s="3" t="inlineStr">
         <is>
           <t>3.건물/적법</t>
         </is>
       </c>
-      <c r="D401" s="0" t="inlineStr">
+      <c r="D401" s="3" t="inlineStr">
         <is>
           <t>has_inspection_cert</t>
         </is>
       </c>
-      <c r="E401" s="0" t="inlineStr">
+      <c r="E401" s="3" t="inlineStr">
         <is>
           <t>준공검사필증(検査済証) 취득 여부</t>
         </is>
       </c>
-      <c r="F401" s="0" t="inlineStr">
+      <c r="F401" s="3" t="inlineStr">
         <is>
           <t>検査済証の有無</t>
         </is>
       </c>
-      <c r="G401" s="0" t="inlineStr">
+      <c r="G401" s="3" t="inlineStr">
         <is>
           <t>유 (2021.2 신축·오릭스/au지분은행 열화3급 35년 융자평가 확인완료 / 원본사본 징구예정)</t>
         </is>
       </c>
-      <c r="H401" s="0" t="inlineStr">
-        <is>
-          <t>COLLECTED</t>
-        </is>
-      </c>
-      <c r="I401" s="0" t="inlineStr">
-        <is>
-          <t>검사필증/대장</t>
-        </is>
-      </c>
-      <c r="J401" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K401" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="H401" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I401" s="3" t="inlineStr">
+        <is>
+          <t>오릭스·au지분 35년 융자평가 확인 (원본사본 미징구)</t>
+        </is>
+      </c>
+      <c r="J401" s="3" t="inlineStr">
+        <is>
+          <t>준공검사필증(検査済証) 및 열화대책등급 3급 주택성능평가서 사본, 프로판가스(LPG) 무상대여 약정서 유무 공유 요청</t>
+        </is>
+      </c>
+      <c r="K401" s="3" t="inlineStr">
+        <is>
+          <t>検査済証および劣化対策等級3級の住宅性能評価書の写し、ならびにプロパンガス無償貸与契約の有無のご確認</t>
         </is>
       </c>
     </row>
@@ -41070,59 +41070,59 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="0" t="inlineStr">
+      <c r="A406" s="3" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B406" s="0" t="inlineStr">
+      <c r="B406" s="3" t="inlineStr">
         <is>
           <t>CHK_20</t>
         </is>
       </c>
-      <c r="C406" s="0" t="inlineStr">
+      <c r="C406" s="3" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D406" s="0" t="inlineStr">
+      <c r="D406" s="3" t="inlineStr">
         <is>
           <t>rent_roll_tenant_types</t>
         </is>
       </c>
-      <c r="E406" s="0" t="inlineStr">
+      <c r="E406" s="3" t="inlineStr">
         <is>
           <t>호실별 입주자 속성(법인/직장인/학생/보증회사)</t>
         </is>
       </c>
-      <c r="F406" s="0" t="inlineStr">
+      <c r="F406" s="3" t="inlineStr">
         <is>
           <t>入居者属性・保証会社加入状況</t>
         </is>
       </c>
-      <c r="G406" s="0" t="inlineStr">
+      <c r="G406" s="3" t="inlineStr">
         <is>
           <t>속성 확인 (12실)</t>
         </is>
       </c>
-      <c r="H406" s="0" t="inlineStr">
-        <is>
-          <t>COLLECTED</t>
-        </is>
-      </c>
-      <c r="I406" s="0" t="inlineStr">
-        <is>
-          <t>렌트롤 상세판</t>
-        </is>
-      </c>
-      <c r="J406" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K406" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="H406" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I406" s="3" t="inlineStr">
+        <is>
+          <t>공식 렌트롤 (敷金·RC 『調査中』 표기)</t>
+        </is>
+      </c>
+      <c r="J406" s="3" t="inlineStr">
+        <is>
+          <t>렌트롤상 『調査中』인 전 호실 시키킨(敷金)·RC 확정 금액 및 서브리스 해지 승계 무보증 6세대의 최근 6개월 수납 내역 확인</t>
+        </is>
+      </c>
+      <c r="K406" s="3" t="inlineStr">
+        <is>
+          <t>レントロール上「調査中」となっている各戸敷金・RCの確定額、および保証会社無しの6戸における直近6ヶ月の家賃入金状況のご確認</t>
         </is>
       </c>
     </row>
@@ -41682,17 +41682,17 @@
       </c>
       <c r="I416" s="3" t="inlineStr">
         <is>
-          <t>표준산식 역산 추정</t>
+          <t>공시지가 기반 노선가 산정 / 본하수 부담금 시청 조사중</t>
         </is>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
-          <t>국세청 최신 노선가 기준 토지 적산단가 대조</t>
+          <t>현재 미사토시청에 조사 중인 하수도 수익자부담금 확정액 및 본하수 접속공사(세금포함 약 180만 엔) 상세 견적서 공유 요청</t>
         </is>
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>国税庁路線価図に基づく土地評価額の算出</t>
+          <t>現在三郷市役所にて調査中の下水道受益者負担金の確定額、および本下水接続工事（税込約180万円）の詳細見積書のご共有</t>
         </is>
       </c>
     </row>

--- a/moabiz/data/real_estate_datastore.xlsx
+++ b/moabiz/data/real_estate_datastore.xlsx
@@ -5783,19 +5783,19 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
           <t>True</t>
@@ -5803,17 +5803,17 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -5828,77 +5828,77 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>미츠쿄 1AP 사사노다이 (三ツ境1AP)</t>
+          <t>리브르 파인 미사토추오 (Livre Fine Misato-Chuo)</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>三ツ境1AP（横浜市旭区笹野台）</t>
+          <t>リーブルファイン三郷中央</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t>神奈川県横浜市旭区笹野台2丁目19-5</t>
+          <t>사이타마현 미사토시 야구치 386-5 (埼玉県三郷市谷口386-5)</t>
         </is>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t>神奈川県横浜市旭区笹野台二丁目149番3、231番102</t>
+          <t>埼玉県三郷市谷口字根通386番5、386番7、私道386番3(持分1/2)</t>
         </is>
       </c>
       <c r="N12" s="0" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=埼玉県三郷市谷口386-5</t>
         </is>
       </c>
       <c r="O12" s="0" t="inlineStr">
         <is>
-          <t>134700000</t>
+          <t>140000000</t>
         </is>
       </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
-          <t>1억 3,470만 엔</t>
+          <t>1억 4,000만 엔</t>
         </is>
       </c>
       <c r="Q12" s="0" t="inlineStr">
         <is>
-          <t>세금포함 (건물 소비세 포함 확인완료)</t>
+          <t>세금포함 (건물 과세비중 50.09% 확인완료)</t>
         </is>
       </c>
       <c r="R12" s="0" t="inlineStr">
         <is>
-          <t>중개 (媒介 · 무브업)</t>
+          <t>중개 (媒介)</t>
         </is>
       </c>
       <c r="S12" s="0" t="inlineStr">
         <is>
-          <t>2026년 12월 말 준공 / 2027년 1월 신축 인도 (계약금 보전조치 불요 범위)</t>
+          <t>현황인도 (R8 본하수 접속공사 약 180만 엔+수익자부담금 매수자 부담)</t>
         </is>
       </c>
       <c r="T12" s="0" t="inlineStr">
         <is>
-          <t>397.71</t>
+          <t>382.33</t>
         </is>
       </c>
       <c r="U12" s="0" t="inlineStr">
         <is>
-          <t>120.3</t>
+          <t>115.65</t>
         </is>
       </c>
       <c r="V12" s="0" t="inlineStr">
         <is>
-          <t>소유권 (所有権)</t>
+          <t>소유권 (택지 386-5·386-7 100% + 사도 386-3 지분 1/2)</t>
         </is>
       </c>
       <c r="W12" s="0" t="inlineStr">
         <is>
-          <t>택지 (宅地 · 등기 399.56㎡ / 확정측량 유효 397.42㎡ + 후퇴 0.29㎡)</t>
+          <t>택지 (宅地 382.33㎡) + 공중용도로 (公衆用道路 128㎡ 지분 1/2)</t>
         </is>
       </c>
       <c r="X12" s="0" t="inlineStr">
         <is>
-          <t>고대(高台) 평탄지 (주변 대비 4.0~4.69m 단차 · 동·북측 기존 간지블록 옹벽 98.84㎡ 검사필증 없음 / 7.0m 파일 시공으로 벼랑조례 안식각 45° 대응)</t>
+          <t>평탄지 (자루형 연장부지·폭 4.0m 협정통로 완비)</t>
         </is>
       </c>
       <c r="Y12" s="0" t="inlineStr">
@@ -5908,42 +5908,42 @@
       </c>
       <c r="Z12" s="0" t="inlineStr">
         <is>
-          <t>제1종 저층주거전용지역 · 제1종 고도지구</t>
+          <t>第一種住居地域 (建蔽率60% / 容積率200% [4m도로기준 160%]・法22条区域)</t>
         </is>
       </c>
       <c r="AA12" s="0" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AB12" s="0" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="AC12" s="0" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>32.33</t>
         </is>
       </c>
       <c r="AD12" s="0" t="inlineStr">
         <is>
-          <t>60.92</t>
+          <t>92.47</t>
         </is>
       </c>
       <c r="AE12" s="0" t="inlineStr">
         <is>
-          <t>법22조구역 · 목조 준내화구조(準耐火構造)</t>
+          <t>법22조구역 (지붕 불연화 구역)</t>
         </is>
       </c>
       <c r="AF12" s="0" t="inlineStr">
         <is>
-          <t>남서측 폭원 3.92~4.50m 요코하마시 공도(下川井第402号線, 일부 계단) 및 서측 폭원 4.00~5.50m 요코하마시 공도(下川井第398号線) 접도</t>
+          <t>南側 位置指定道路(386番3・幅員4.00m・昭和51年第1496号・持分1/2有)に幅員4.00m協定通路で接道</t>
         </is>
       </c>
       <c r="AG12" s="0" t="inlineStr">
         <is>
-          <t>없음 (등기부 지번 231-1 요코하마시 소유 공중용도로 및 인정노선도 100% 공도 검증완료)</t>
+          <t>사도(386番3, 128㎡) 지분 1/2 보유(비과세) + 『토지공동사용협정서(386番6+386番7 폭 4m 무상·자동승계)』 원본 완비</t>
         </is>
       </c>
       <c r="AH12" s="0" t="inlineStr">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="AI12" s="0" t="inlineStr">
         <is>
-          <t>목조 준내화구조 지상 2층건 (RC베타기초+7.00m 기초파일 / 설계·건설 열화대책등급 3급)</t>
+          <t>목조 아연도금강판지붕 지상 3층건 (2×4공법·열화대책등급 3급)</t>
         </is>
       </c>
       <c r="AJ12" s="0" t="inlineStr">
         <is>
-          <t>2026년 12월 말 준공 예정 (2027년 1월 인도 예정)</t>
+          <t>2021年2月25日新築 (令和3年2月 / 築5.6年)</t>
         </is>
       </c>
       <c r="AK12" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AL12" s="0" t="inlineStr">
@@ -5973,147 +5973,147 @@
       </c>
       <c r="AM12" s="0" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AN12" s="0" t="inlineStr">
         <is>
-          <t>242.07</t>
+          <t>353.55</t>
         </is>
       </c>
       <c r="AO12" s="0" t="inlineStr">
         <is>
-          <t>242.07</t>
+          <t>353.55</t>
         </is>
       </c>
       <c r="AP12" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AQ12" s="0" t="inlineStr">
         <is>
-          <t>전 9세대 1LDK(26.89㎡: LDK8.0+양실5.5, 2인입주 가능) + 5세대(105, 201~204호) 로프트 4.82㎡</t>
+          <t>총 11세대 (1F: 1LDK×3실 [37.26~43.32㎡] / 2~3F: 1K×8실 [28.41~29.81㎡])</t>
         </is>
       </c>
       <c r="AR12" s="0" t="inlineStr">
         <is>
-          <t>없음 (전면도로 계단 직전까지 차량 접근 가능)</t>
+          <t>부지 내 평면 주차장 4구획 (각 월 5,500엔 × 4대 = 월 22,000엔 만차)</t>
         </is>
       </c>
       <c r="AS12" s="0" t="inlineStr">
         <is>
-          <t>유 (제26UDI1K건00271호, R8.6.18 교부 확인필증 사본 완비)</t>
+          <t>유 (건축도면·배치도·평면도·입면도 일식 확인완료)</t>
         </is>
       </c>
       <c r="AT12" s="0" t="inlineStr">
         <is>
-          <t>신축 건축중 (2026.12 말 준공 시 건축물 검사필증 및 건설주택성능평가서 열화3급 교부 예정 / 단, 기존 옹벽은 검사필증 없음)</t>
+          <t>유 (2021.2 신축·오릭스/au지분은행 열화3급 35년 융자평가 확인완료 / 원본사본 징구예정)</t>
         </is>
       </c>
       <c r="AU12" s="0" t="inlineStr">
         <is>
-          <t>도시가스 (都市ガス 완비)</t>
+          <t>프로판가스 (LPG) / 공영수도 / J:COM 전호실 무료 인터넷 완비</t>
         </is>
       </c>
       <c r="AV12" s="0" t="inlineStr">
         <is>
-          <t>공영수도·공공하수·무료WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정 확인완료)</t>
+          <t>현재 정화조(월 1만엔) → R8 본하수 접속공사(세금포함 약 180만엔+부담금 시청조사중) 후 직결</t>
         </is>
       </c>
       <c r="AW12" s="0" t="inlineStr">
         <is>
-          <t>무 (2층 저층형)</t>
+          <t>무 (3층 외계단·외복도 저비용 구조)</t>
         </is>
       </c>
       <c r="AX12" s="0" t="inlineStr">
         <is>
-          <t>신축 완공 예정 (RC베타기초+7.0m 기초파일 시공 / 동·북측 기존 간지블록 옹벽 98.84㎡는 보강계획 없음 확인)</t>
+          <t>축 5.6년 신축급으로 과거 대규모 수선이력 및 침수이력 없음 (중개사·매도자 공식 확인완료)</t>
         </is>
       </c>
       <c r="AY12" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AZ12" s="0" t="inlineStr">
         <is>
-          <t>8760000</t>
+          <t>9876000</t>
         </is>
       </c>
       <c r="BA12" s="0" t="inlineStr">
         <is>
-          <t>8760000</t>
+          <t>9876000</t>
         </is>
       </c>
       <c r="BB12" s="0" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BC12" s="0" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BD12" s="0" t="inlineStr">
         <is>
-          <t>1130040</t>
+          <t>1698233</t>
         </is>
       </c>
       <c r="BE12" s="0" t="inlineStr">
         <is>
-          <t>1890040</t>
+          <t>2420000</t>
         </is>
       </c>
       <c r="BF12" s="0" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="BG12" s="0" t="inlineStr">
         <is>
-          <t>6869960</t>
+          <t>7456000</t>
         </is>
       </c>
       <c r="BH12" s="0" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="BI12" s="0" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>125000</t>
         </is>
       </c>
       <c r="BJ12" s="0" t="inlineStr">
         <is>
-          <t>75509800</t>
+          <t>47791250</t>
         </is>
       </c>
       <c r="BK12" s="0" t="inlineStr">
         <is>
-          <t>43572600</t>
+          <t>70127509</t>
         </is>
       </c>
       <c r="BL12" s="0" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>69.26</t>
         </is>
       </c>
       <c r="BM12" s="0" t="inlineStr">
         <is>
-          <t>36985271</t>
+          <t>27054052</t>
         </is>
       </c>
       <c r="BN12" s="0" t="inlineStr">
         <is>
-          <t>26627700</t>
+          <t>27152612</t>
         </is>
       </c>
       <c r="BO12" s="0" t="inlineStr">
         <is>
-          <t>573,283엔 (R8 토지 공과증명서 주택특례 약 12.3만 엔 + 건물 오카다상 확인 약 45만 엔 추정)</t>
+          <t>474,221엔 (레이와 8년도 과세원장 확정: 토지 76,651 + 건물 397,570)</t>
         </is>
       </c>
       <c r="BP12" s="0" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="BQ12" s="0" t="inlineStr">
         <is>
-          <t>114495000</t>
+          <t>119000000</t>
         </is>
       </c>
       <c r="BR12" s="0" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BS12" s="0" t="inlineStr">
@@ -6138,97 +6138,97 @@
       </c>
       <c r="BT12" s="0" t="inlineStr">
         <is>
-          <t>5287219</t>
+          <t>5642326</t>
         </is>
       </c>
       <c r="BU12" s="0" t="inlineStr">
         <is>
-          <t>1582741</t>
+          <t>1813674</t>
         </is>
       </c>
       <c r="BV12" s="0" t="inlineStr">
         <is>
-          <t>1246795</t>
+          <t>1659723</t>
         </is>
       </c>
       <c r="BW12" s="0" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BX12" s="0" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BY12" s="0" t="inlineStr">
         <is>
-          <t>81.93</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="BZ12" s="0" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CA12" s="0" t="inlineStr">
         <is>
-          <t>31497300</t>
+          <t>32816000</t>
         </is>
       </c>
       <c r="CB12" s="0" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="CC12" s="0" t="inlineStr">
         <is>
-          <t>소테츠 본선(급행 정차) 「미츠쿄(三ツ境)」역 구글맵 실측 도보 10분 (약 720m, 마이소쿠 표기 7분)</t>
+          <t>つくばエクスプレス「三郷中央」駅 徒歩14分 (Google Maps 실측 15~16분 / 1,150m)</t>
         </is>
       </c>
       <c r="CD12" s="0" t="inlineStr">
         <is>
-          <t>도보 7분 (마이소쿠 표기)</t>
+          <t>도보 14분 (개요서 공시)</t>
         </is>
       </c>
       <c r="CE12" s="0" t="inlineStr">
         <is>
-          <t>실측 도보 10분 (구글맵 및 오카다상 현장 확인완료)</t>
+          <t>도보 15~16분 (구글맵 실측 검증완료)</t>
         </is>
       </c>
       <c r="CF12" s="0" t="inlineStr">
         <is>
-          <t>720m (구글맵 실측완료)</t>
+          <t>1,150m (완전 평탄지)</t>
         </is>
       </c>
       <c r="CG12" s="0" t="inlineStr">
         <is>
-          <t>사사노다이 상점가 경유 후 남서측 전면도로(下川井第402号線) 진입부에 계단 구간 및 부지 고저차(4.0~4.69m) 존재 확인완료</t>
+          <t>고저차 없는 평탄지 (다이니오바가와 교량 횡단·1층 바닥 GL+450mm 확인)</t>
         </is>
       </c>
       <c r="CH12" s="0" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=埼玉県三郷市谷口386-5&amp;destination=三郷中央駅&amp;travelmode=walking</t>
         </is>
       </c>
       <c r="CI12" s="0" t="inlineStr">
         <is>
-          <t>고대(高台) 입지로 홍수·내수 침수 해저드 해당 없음 (교차검증 완료)</t>
+          <t>하저드맵 3.0~5.0m 구역이나 『과거 집중호우 포함 침수 피해 이력 전무』 매도자 공식 확인완료</t>
         </is>
       </c>
       <c r="CJ12" s="0" t="inlineStr">
         <is>
-          <t>부지 북서측 모서리 옹벽 부분(가측량도 약 4.69㎡)이 토사재해경계구역(옐로우존/잠정 레드존 경계)에 일부 저촉 확인완료 (건물 본체는 2m 이격되어 구역 외)</t>
+          <t>해당 없음 (완전 평탄지·토사재해 경계구역 외)</t>
         </is>
       </c>
       <c r="CK12" s="0" t="inlineStr">
         <is>
-          <t>https://www.homes.co.jp/archive/b-36020804/</t>
+          <t>https://www.homes.co.jp/archive/b-42396528/</t>
         </is>
       </c>
       <c r="CL12" s="0" t="inlineStr">
         <is>
-          <t>30~45일 (REINS 근린 성약 50건 및 일 피오레 사사노다이 교차검증 완료)</t>
+          <t>62</t>
         </is>
       </c>
       <c r="CM12" s="0" t="inlineStr">
@@ -6238,42 +6238,42 @@
       </c>
       <c r="CN12" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276000</t>
         </is>
       </c>
       <c r="CO12" s="0" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CP12" s="0" t="inlineStr">
+        <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="CP12" s="0" t="inlineStr">
+      <c r="CQ12" s="0" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="CR12" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CS12" s="0" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="CQ12" s="0" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="CR12" s="0" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="CS12" s="0" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
       <c r="CT12" s="0" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="CU12" s="0" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CV12" s="0" t="inlineStr">
@@ -6288,24 +6288,24 @@
       </c>
       <c r="CX12" s="0" t="inlineStr">
         <is>
-          <t>적합 / 조건부 편입 (ICR 1.05배 돌파·LTV -15.6%p 개선 / 단, 미검사 옹벽·토사재해 저촉 반영 1.24억 네고 필수)</t>
+          <t>조건부 적합 (사도지분 1/2·협정서·과세명세 완비 / 세후CF +166만·상환연수 27.3년 / 본하수 공사비 약 200만 반영 1.28억~1.33억 네고 권고)</t>
         </is>
       </c>
       <c r="CY12" s="0" t="inlineStr">
         <is>
-          <t>적합 / 조건부 검토 (120.3평 택지·1LDK+로프트·열화3급 30년 융자 우수하나 기존 옹벽·임대료 상단 리스크 반영 지값 협상 필수)</t>
+          <t>조건부 검토 (사도지분 1/2·협정서·과세명세 완비 / 오릭스·au지분 35년 융자 적격 / 본하수 공사비 약 200만 반영 1.28억~1.33억 네고 권고)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -6319,13 +6319,13 @@
         </is>
       </c>
       <c r="E13" s="0">
-        <v>91.4</v>
+        <v>94.3</v>
       </c>
       <c r="F13" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -6337,71 +6337,71 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>리브르 파인 미사토추오 (Livre Fine Misato-Chuo)</t>
+          <t>미츠쿄 1AP 사사노다이 (三ツ境1AP)</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>リーブルファイン三郷中央</t>
+          <t>三ツ境1AP（横浜市旭区笹野台）</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t>사이타마현 미사토시 야구치 386-5 (埼玉県三郷市谷口386-5)</t>
+          <t>神奈川県横浜市旭区笹野台2丁目19-5</t>
         </is>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
-          <t>埼玉県三郷市谷口字根通386番5、386番7、私道386番3(持分1/2)</t>
+          <t>神奈川県横浜市旭区笹野台二丁目149番3、231番102</t>
         </is>
       </c>
       <c r="N13" s="0" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=埼玉県三郷市谷口386-5</t>
+          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
         </is>
       </c>
       <c r="O13" s="0">
-        <v>140000000</v>
+        <v>134700000</v>
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>1억 4,000만 엔</t>
+          <t>1억 3,470만 엔</t>
         </is>
       </c>
       <c r="Q13" s="0" t="inlineStr">
         <is>
-          <t>세금포함 (건물 과세비중 50.09% 확인완료)</t>
+          <t>세금포함 (건물 소비세 포함 확인완료)</t>
         </is>
       </c>
       <c r="R13" s="0" t="inlineStr">
         <is>
-          <t>중개 (媒介)</t>
+          <t>중개 (媒介 · 무브업)</t>
         </is>
       </c>
       <c r="S13" s="0" t="inlineStr">
         <is>
-          <t>현황인도 (R8 본하수 접속공사 약 180만 엔+수익자부담금 매수자 부담)</t>
+          <t>2026년 12월 말 준공 / 2027년 1월 신축 인도 (계약금 보전조치 불요 범위)</t>
         </is>
       </c>
       <c r="T13" s="0">
-        <v>382.33</v>
+        <v>397.71</v>
       </c>
       <c r="U13" s="0">
-        <v>115.65</v>
+        <v>120.3</v>
       </c>
       <c r="V13" s="0" t="inlineStr">
         <is>
-          <t>소유권 (택지 386-5·386-7 100% + 사도 386-3 지분 1/2)</t>
+          <t>소유권 (所有権)</t>
         </is>
       </c>
       <c r="W13" s="0" t="inlineStr">
         <is>
-          <t>택지 (宅地 382.33㎡) + 공중용도로 (公衆用道路 128㎡ 지분 1/2)</t>
+          <t>택지 (宅地 · 등기 399.56㎡ / 확정측량 유효 397.42㎡ + 후퇴 0.29㎡)</t>
         </is>
       </c>
       <c r="X13" s="0" t="inlineStr">
         <is>
-          <t>평탄지 (자루형 연장부지·폭 4.0m 협정통로 완비)</t>
+          <t>고대(高台) 평탄지 (주변 대비 4.0~4.69m 단차 · 동·북측 기존 간지블록 옹벽 98.84㎡ 검사필증 없음 / 7.0m 파일 시공으로 벼랑조례 안식각 45° 대응)</t>
         </is>
       </c>
       <c r="Y13" s="0" t="inlineStr">
@@ -6411,34 +6411,34 @@
       </c>
       <c r="Z13" s="0" t="inlineStr">
         <is>
-          <t>第一種住居地域 (建蔽率60% / 容積率200% [4m도로기준 160%]・法22条区域)</t>
+          <t>제1종 저층주거전용지역 · 제1종 고도지구</t>
         </is>
       </c>
       <c r="AA13" s="0">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="AB13" s="0">
-        <v>200.0</v>
+        <v>80.0</v>
       </c>
       <c r="AC13" s="0">
-        <v>32.33</v>
+        <v>39.57</v>
       </c>
       <c r="AD13" s="0">
-        <v>92.47</v>
+        <v>60.92</v>
       </c>
       <c r="AE13" s="0" t="inlineStr">
         <is>
-          <t>법22조구역 (지붕 불연화 구역)</t>
+          <t>법22조구역 · 목조 준내화구조(準耐火構造)</t>
         </is>
       </c>
       <c r="AF13" s="0" t="inlineStr">
         <is>
-          <t>南側 位置指定道路(386番3・幅員4.00m・昭和51年第1496号・持分1/2有)に幅員4.00m協定通路で接道</t>
+          <t>남서측 폭원 3.92~4.50m 요코하마시 공도(下川井第402号線, 일부 계단) 및 서측 폭원 4.00~5.50m 요코하마시 공도(下川井第398号線) 접도</t>
         </is>
       </c>
       <c r="AG13" s="0" t="inlineStr">
         <is>
-          <t>사도(386番3, 128㎡) 지분 1/2 보유(비과세) + 『토지공동사용협정서(386番6+386番7 폭 4m 무상·자동승계)』 원본 완비</t>
+          <t>없음 (등기부 지번 231-1 요코하마시 소유 공중용도로 및 인정노선도 100% 공도 검증완료)</t>
         </is>
       </c>
       <c r="AH13" s="0" t="inlineStr">
@@ -6448,238 +6448,242 @@
       </c>
       <c r="AI13" s="0" t="inlineStr">
         <is>
-          <t>목조 아연도금강판지붕 지상 3층건 (2×4공법·열화대책등급 3급)</t>
+          <t>목조 준내화구조 지상 2층건 (RC베타기초+7.00m 기초파일 / 설계·건설 열화대책등급 3급)</t>
         </is>
       </c>
       <c r="AJ13" s="0" t="inlineStr">
         <is>
-          <t>2021年2月25日新築 (令和3年2月 / 築5.6年)</t>
+          <t>2026년 12월 말 준공 예정 (2027년 1월 인도 예정)</t>
         </is>
       </c>
       <c r="AK13" s="0">
-        <v>5.6</v>
+        <v>0.0</v>
       </c>
       <c r="AL13" s="0">
         <v>22</v>
       </c>
       <c r="AM13" s="0">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="AN13" s="0">
-        <v>353.55</v>
+        <v>242.07</v>
       </c>
       <c r="AO13" s="0">
-        <v>353.55</v>
+        <v>242.07</v>
       </c>
       <c r="AP13" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ13" s="0" t="inlineStr">
         <is>
-          <t>총 11세대 (1F: 1LDK×3실 [37.26~43.32㎡] / 2~3F: 1K×8실 [28.41~29.81㎡])</t>
+          <t>전 9세대 1LDK(26.89㎡: LDK8.0+양실5.5, 2인입주 가능) + 5세대(105, 201~204호) 로프트 4.82㎡</t>
         </is>
       </c>
       <c r="AR13" s="0" t="inlineStr">
         <is>
-          <t>부지 내 평면 주차장 4구획 (각 월 5,500엔 × 4대 = 월 22,000엔 만차)</t>
+          <t>없음 (전면도로 계단 직전까지 차량 접근 가능)</t>
         </is>
       </c>
       <c r="AS13" s="0" t="inlineStr">
         <is>
-          <t>유 (건축도면·배치도·평면도·입면도 일식 확인완료)</t>
+          <t>유 (제26UDI1K건00271호, R8.6.18 교부 확인필증 사본 완비)</t>
         </is>
       </c>
       <c r="AT13" s="0" t="inlineStr">
         <is>
-          <t>유 (2021.2 신축·오릭스/au지분은행 열화3급 35년 융자평가 확인완료 / 원본사본 징구예정)</t>
+          <t>신축 건축중 (2026.12 말 준공 시 건축물 검사필증 및 건설주택성능평가서 열화3급 교부 예정 / 단, 기존 옹벽은 검사필증 없음)</t>
         </is>
       </c>
       <c r="AU13" s="0" t="inlineStr">
         <is>
-          <t>프로판가스 (LPG) / 공영수도 / J:COM 전호실 무료 인터넷 완비</t>
+          <t>도시가스 (都市ガス 완비)</t>
         </is>
       </c>
       <c r="AV13" s="0" t="inlineStr">
         <is>
-          <t>현재 정화조(월 1만엔) → R8 본하수 접속공사(세금포함 약 180만엔+부담금 시청조사중) 후 직결</t>
+          <t>공영수도·공공하수·무료WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정 확인완료)</t>
         </is>
       </c>
       <c r="AW13" s="0" t="inlineStr">
         <is>
-          <t>무 (3층 외계단·외복도 저비용 구조)</t>
+          <t>무 (2층 저층형)</t>
         </is>
       </c>
       <c r="AX13" s="0" t="inlineStr">
         <is>
-          <t>축 5.6년 신축급으로 과거 대규모 수선이력 및 침수이력 없음 (중개사·매도자 공식 확인완료)</t>
+          <t>신축 완공 예정 (RC베타기초+7.0m 기초파일 시공 / 동·북측 기존 간지블록 옹벽 98.84㎡는 보강계획 없음 확인)</t>
         </is>
       </c>
       <c r="AY13" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ13" s="0">
-        <v>9876000</v>
+        <v>8760000</v>
       </c>
       <c r="BA13" s="0">
-        <v>9876000</v>
+        <v>8760000</v>
       </c>
       <c r="BB13" s="0">
-        <v>7.05</v>
+        <v>6.5</v>
       </c>
       <c r="BC13" s="0">
-        <v>7.05</v>
+        <v>6.5</v>
       </c>
       <c r="BD13" s="0">
-        <v>1698233</v>
+        <v>1130040</v>
       </c>
       <c r="BE13" s="0">
-        <v>2420000</v>
+        <v>1890040</v>
       </c>
       <c r="BF13" s="0">
-        <v>24.5</v>
+        <v>21.58</v>
       </c>
       <c r="BG13" s="0">
-        <v>7456000</v>
+        <v>6869960</v>
       </c>
       <c r="BH13" s="0">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="BI13" s="0">
-        <v>125000</v>
+        <v>190000</v>
       </c>
       <c r="BJ13" s="0">
-        <v>47791250</v>
+        <v>75509800</v>
       </c>
       <c r="BK13" s="0">
-        <v>70127509</v>
+        <v>43572600</v>
       </c>
       <c r="BL13" s="0">
-        <v>69.26</v>
+        <v>88.41</v>
       </c>
       <c r="BM13" s="0">
-        <v>27054052</v>
+        <v>36985271</v>
       </c>
       <c r="BN13" s="0">
-        <v>27152612</v>
+        <v>26627700</v>
       </c>
       <c r="BO13" s="0" t="inlineStr">
         <is>
-          <t>474,221엔 (레이와 8년도 과세원장 확정: 토지 76,651 + 건물 397,570)</t>
+          <t>573,283엔 (R8 토지 공과증명서 주택특례 약 12.3만 엔 + 건물 오카다상 확인 약 45만 엔 추정)</t>
         </is>
       </c>
       <c r="BP13" s="0">
         <v>85.0</v>
       </c>
       <c r="BQ13" s="0">
-        <v>119000000</v>
+        <v>114495000</v>
       </c>
       <c r="BR13" s="0">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BS13" s="0">
         <v>30</v>
       </c>
       <c r="BT13" s="0">
-        <v>5642326</v>
+        <v>5287219</v>
       </c>
       <c r="BU13" s="0">
-        <v>1813674</v>
+        <v>1582741</v>
       </c>
       <c r="BV13" s="0">
-        <v>1659723</v>
+        <v>1246795</v>
       </c>
       <c r="BW13" s="0">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BX13" s="0">
-        <v>2.53</v>
+        <v>1.54</v>
       </c>
       <c r="BY13" s="0">
-        <v>81.6</v>
+        <v>81.93</v>
       </c>
       <c r="BZ13" s="0">
-        <v>2.0</v>
+        <v>1.63</v>
       </c>
       <c r="CA13" s="0">
-        <v>32816000</v>
+        <v>31497300</v>
       </c>
       <c r="CB13" s="0">
-        <v>5.53</v>
+        <v>5.03</v>
       </c>
       <c r="CC13" s="0" t="inlineStr">
         <is>
-          <t>つくばエクスプレス「三郷中央」駅 徒歩14分 (Google Maps 실측 15~16분 / 1,150m)</t>
+          <t>소테츠 본선(급행 정차) 「미츠쿄(三ツ境)」역 구글맵 실측 도보 10분 (약 720m, 마이소쿠 표기 7분)</t>
         </is>
       </c>
       <c r="CD13" s="0" t="inlineStr">
         <is>
-          <t>도보 14분 (개요서 공시)</t>
+          <t>도보 7분 (마이소쿠 표기)</t>
         </is>
       </c>
       <c r="CE13" s="0" t="inlineStr">
         <is>
-          <t>도보 15~16분 (구글맵 실측 검증완료)</t>
+          <t>실측 도보 10분 (구글맵 및 오카다상 현장 확인완료)</t>
         </is>
       </c>
       <c r="CF13" s="0" t="inlineStr">
         <is>
-          <t>1,150m (완전 평탄지)</t>
+          <t>720m (구글맵 실측완료)</t>
         </is>
       </c>
       <c r="CG13" s="0" t="inlineStr">
         <is>
-          <t>고저차 없는 평탄지 (다이니오바가와 교량 횡단·1층 바닥 GL+450mm 확인)</t>
+          <t>사사노다이 상점가 경유 후 남서측 전면도로(下川井第402号線) 진입부에 계단 구간 및 부지 고저차(4.0~4.69m) 존재 확인완료</t>
         </is>
       </c>
       <c r="CH13" s="0" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;origin=埼玉県三郷市谷口386-5&amp;destination=三郷中央駅&amp;travelmode=walking</t>
+          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
         </is>
       </c>
       <c r="CI13" s="0" t="inlineStr">
         <is>
-          <t>하저드맵 3.0~5.0m 구역이나 『과거 집중호우 포함 침수 피해 이력 전무』 매도자 공식 확인완료</t>
+          <t>고대(高台) 입지로 홍수·내수 침수 해저드 해당 없음 (교차검증 완료)</t>
         </is>
       </c>
       <c r="CJ13" s="0" t="inlineStr">
         <is>
-          <t>해당 없음 (완전 평탄지·토사재해 경계구역 외)</t>
+          <t>부지 북서측 모서리 옹벽 부분(가측량도 약 4.69㎡)이 토사재해경계구역(옐로우존/잠정 레드존 경계)에 일부 저촉 확인완료 (건물 본체는 2m 이격되어 구역 외)</t>
         </is>
       </c>
       <c r="CK13" s="0" t="inlineStr">
         <is>
-          <t>https://www.homes.co.jp/archive/b-42396528/</t>
-        </is>
-      </c>
-      <c r="CL13" s="0">
-        <v>62</v>
-      </c>
-      <c r="CM13" s="0">
-        <v>5.0</v>
+          <t>https://www.homes.co.jp/archive/b-36020804/</t>
+        </is>
+      </c>
+      <c r="CL13" s="0" t="inlineStr">
+        <is>
+          <t>30~45일 (REINS 근린 성약 50건 및 일 피오레 사사노다이 교차검증 완료)</t>
+        </is>
+      </c>
+      <c r="CM13" s="0" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
       <c r="CN13" s="0">
-        <v>276000</v>
+        <v>0</v>
       </c>
       <c r="CO13" s="0">
-        <v>3.0</v>
+        <v>3.5</v>
       </c>
       <c r="CP13" s="0">
         <v>3.5</v>
       </c>
       <c r="CQ13" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="CR13" s="0">
-        <v>3.0</v>
+        <v>3.5</v>
       </c>
       <c r="CS13" s="0">
         <v>3.5</v>
       </c>
       <c r="CT13" s="0">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="CU13" s="0">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="CV13" s="0" t="inlineStr">
         <is>
@@ -6693,12 +6697,12 @@
       </c>
       <c r="CX13" s="0" t="inlineStr">
         <is>
-          <t>조건부 적합 (사도지분 1/2·협정서·과세명세 완비 / 세후CF +166만·상환연수 27.3년 / 본하수 공사비 약 200만 반영 1.28억~1.33억 네고 권고)</t>
+          <t>적합 / 조건부 편입 (ICR 1.05배 돌파·LTV -15.6%p 개선 / 단, 미검사 옹벽·토사재해 저촉 반영 1.24억 네고 필수)</t>
         </is>
       </c>
       <c r="CY13" s="0" t="inlineStr">
         <is>
-          <t>조건부 검토 (사도지분 1/2·협정서·과세명세 완비 / 오릭스·au지분 35년 융자 적격 / 본하수 공사비 약 200만 반영 1.28억~1.33억 네고 권고)</t>
+          <t>적합 / 조건부 검토 (120.3평 택지·1LDK+로프트·열화3급 30년 융자 우수하나 기존 옹벽·임대료 상단 리스크 반영 지값 협상 필수)</t>
         </is>
       </c>
     </row>
@@ -16369,12 +16373,12 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>101호</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -16384,84 +16388,84 @@
       </c>
       <c r="D112" s="0" t="inlineStr">
         <is>
-          <t>1LDK (LDK8.0+양실5.5)</t>
+          <t>1LDK</t>
         </is>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="F112" s="0" t="inlineStr">
         <is>
-          <t>신축모집예정(2026.12준공)</t>
+          <t>입주중</t>
         </is>
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>신축 2인입주가능(1LDK)</t>
+          <t>개인 (보증: エポス)</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
         <is>
-          <t>2026.12 준공예정</t>
+          <t>2026-11-30 (2024.11 최초)</t>
         </is>
       </c>
       <c r="I112" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="K112" s="0" t="inlineStr">
         <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L112" s="0" t="inlineStr">
+      <c r="M112" s="0" t="inlineStr">
+        <is>
+          <t>82000</t>
+        </is>
+      </c>
+      <c r="N112" s="0" t="inlineStr">
+        <is>
+          <t>82000</t>
+        </is>
+      </c>
+      <c r="O112" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M112" s="0" t="inlineStr">
-        <is>
-          <t>80000</t>
-        </is>
-      </c>
-      <c r="N112" s="0" t="inlineStr">
-        <is>
-          <t>78000</t>
-        </is>
-      </c>
-      <c r="O112" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="P112" s="0" t="inlineStr">
         <is>
-          <t>30~45</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Q112" s="0" t="inlineStr">
         <is>
-          <t>1F 서측 각실 · 2면채광 · 1F 수동셔터 · 무료WiFi 포함</t>
+          <t>남서 코너 최대 평형 (43.32㎡) / 에포스 보증 가입 / 시키킨·RC 조사중</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>102호</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
@@ -16471,84 +16475,84 @@
       </c>
       <c r="D113" s="0" t="inlineStr">
         <is>
-          <t>1LDK (LDK8.0+양실5.5)</t>
+          <t>1LDK</t>
         </is>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>37.26</t>
         </is>
       </c>
       <c r="F113" s="0" t="inlineStr">
         <is>
-          <t>신축모집예정(2026.12준공)</t>
+          <t>입주신청 (申込み有り)</t>
         </is>
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>신축 2인입주가능(1LDK)</t>
+          <t>개인 (신규 신청완료)</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
         <is>
-          <t>2026.12 준공예정</t>
+          <t>2026-09 (신규 입주예정)</t>
         </is>
       </c>
       <c r="I113" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J113" s="0" t="inlineStr">
         <is>
-          <t>78000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="K113" s="0" t="inlineStr">
         <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L113" s="0" t="inlineStr">
+      <c r="M113" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="N113" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="O113" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M113" s="0" t="inlineStr">
-        <is>
-          <t>78000</t>
-        </is>
-      </c>
-      <c r="N113" s="0" t="inlineStr">
-        <is>
-          <t>76000</t>
-        </is>
-      </c>
-      <c r="O113" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="P113" s="0" t="inlineStr">
         <is>
-          <t>30~45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q113" s="0" t="inlineStr">
         <is>
-          <t>1F 중실 · UB1014 · IH2구 키친(W1200) · 수동셔터</t>
+          <t>申込み有り (차임 7.5만 + 공익비 5,000엔 = 월 8.0만 엔 신규 신청 완료)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>103호</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
@@ -16558,258 +16562,258 @@
       </c>
       <c r="D114" s="0" t="inlineStr">
         <is>
-          <t>1LDK (LDK8.0+양실5.5)</t>
+          <t>1LDK</t>
         </is>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>37.26</t>
         </is>
       </c>
       <c r="F114" s="0" t="inlineStr">
         <is>
-          <t>신축모집예정(2026.12준공)</t>
+          <t>입주중</t>
         </is>
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>신축 2인입주가능(1LDK)</t>
+          <t>개인 (보증: 無)</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
         <is>
-          <t>2026.12 준공예정</t>
+          <t>2025-10-31 (~2027-10-30)</t>
         </is>
       </c>
       <c r="I114" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>78000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="K114" s="0" t="inlineStr">
         <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L114" s="0" t="inlineStr">
+      <c r="M114" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="N114" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="O114" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M114" s="0" t="inlineStr">
-        <is>
-          <t>78000</t>
-        </is>
-      </c>
-      <c r="N114" s="0" t="inlineStr">
-        <is>
-          <t>76000</t>
-        </is>
-      </c>
-      <c r="O114" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="P114" s="0" t="inlineStr">
         <is>
-          <t>30~45</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q114" s="0" t="inlineStr">
         <is>
-          <t>1F 중실 · 차음경계벽 천장속 밀실시공 · 무료WiFi</t>
+          <t>2025.10 계약 (월총액 8.0만 엔 성약 실증) / 구 다이하츠 서브리스 승계로 보증회사 미가입</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>201호</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
         <is>
-          <t>1LDK (LDK8.0+양실5.5)</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="F115" s="0" t="inlineStr">
         <is>
-          <t>신축모집예정(2026.12준공)</t>
+          <t>입주중</t>
         </is>
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>신축 2인입주가능(1LDK)</t>
+          <t>법인 (法人契約 / 보증: 無)</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
         <is>
-          <t>2026.12 준공예정</t>
+          <t>2023-12-12 (갱신: 2025-12-12)</t>
         </is>
       </c>
       <c r="I115" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="J115" s="0" t="inlineStr">
         <is>
-          <t>78000</t>
+          <t>68000</t>
         </is>
       </c>
       <c r="K115" s="0" t="inlineStr">
         <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L115" s="0" t="inlineStr">
+      <c r="M115" s="0" t="inlineStr">
+        <is>
+          <t>71500</t>
+        </is>
+      </c>
+      <c r="N115" s="0" t="inlineStr">
+        <is>
+          <t>71500</t>
+        </is>
+      </c>
+      <c r="O115" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M115" s="0" t="inlineStr">
-        <is>
-          <t>78000</t>
-        </is>
-      </c>
-      <c r="N115" s="0" t="inlineStr">
-        <is>
-          <t>76000</t>
-        </is>
-      </c>
-      <c r="O115" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="P115" s="0" t="inlineStr">
         <is>
-          <t>30~45</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q115" s="0" t="inlineStr">
         <is>
-          <t>1F 중실 · 수동셔터 · 무료WiFi 포함</t>
+          <t>우량 법인 사택 계약 (주차장 5,500엔 별도 동시 계약) / 1회 갱신 완료</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>202호</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
         <is>
-          <t>1LDK+로프트4.82㎡</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="F116" s="0" t="inlineStr">
         <is>
-          <t>신축모집예정(2026.12준공)</t>
+          <t>입주중</t>
         </is>
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>신축 2인입주가능(1LDK+로프트)</t>
+          <t>개인 (보증: 無 / 서브리스승계)</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
         <is>
-          <t>2026.12 준공예정</t>
+          <t>2023-04-28 (갱신: 2025-04-28)</t>
         </is>
       </c>
       <c r="I116" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="J116" s="0" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>64000</t>
         </is>
       </c>
       <c r="K116" s="0" t="inlineStr">
         <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="L116" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L116" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M116" s="0" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>67000</t>
         </is>
       </c>
       <c r="N116" s="0" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="O116" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="P116" s="0" t="inlineStr">
         <is>
-          <t>25~35</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q116" s="0" t="inlineStr">
         <is>
-          <t>1F 동측 단층부 각실 + 4.82㎡ 대형 로프트(실사용 31.71㎡, 2,523엔/㎡)</t>
+          <t>2023.04 구 서브리스 최저가 호실 → 퇴거 시 월 +5,000엔(7.2만 엔) 상승 여력</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>203호</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -16819,84 +16823,84 @@
       </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
-          <t>1LDK+로프트4.82㎡</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="F117" s="0" t="inlineStr">
         <is>
-          <t>신축모집예정(2026.12준공)</t>
+          <t>입주중</t>
         </is>
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>신축 2인입주가능(1LDK+로프트)</t>
+          <t>개인 (연대보증인 / 連帯保証人)</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
         <is>
-          <t>2026.12 준공예정</t>
+          <t>2023-04-17 (갱신: 2025-04-17)</t>
         </is>
       </c>
       <c r="I117" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>85000</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="K117" s="0" t="inlineStr">
         <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="L117" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L117" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M117" s="0" t="inlineStr">
         <is>
-          <t>85000</t>
+          <t>68000</t>
         </is>
       </c>
       <c r="N117" s="0" t="inlineStr">
         <is>
-          <t>82000</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="O117" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="P117" s="0" t="inlineStr">
         <is>
-          <t>30~45</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q117" s="0" t="inlineStr">
         <is>
-          <t>2F 최상층 서측 각실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
+          <t>2023.04 구 서브리스 저가 호실 → 퇴거 시 월 +4,000엔(7.2만 엔) 상승 여력</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>204호</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -16906,246 +16910,246 @@
       </c>
       <c r="D118" s="0" t="inlineStr">
         <is>
-          <t>1LDK+로프트4.82㎡</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="F118" s="0" t="inlineStr">
         <is>
-          <t>신축모집예정(2026.12준공)</t>
+          <t>입주중</t>
         </is>
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>신축 2인입주가능(1LDK+로프트)</t>
+          <t>개인 (보증: 無)</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
         <is>
-          <t>2026.12 준공예정</t>
+          <t>2025-08-31 (~2027-08-30)</t>
         </is>
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J118" s="0" t="inlineStr">
         <is>
-          <t>83000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="K118" s="0" t="inlineStr">
         <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="L118" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L118" s="0" t="inlineStr">
+      <c r="M118" s="0" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="N118" s="0" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="O118" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M118" s="0" t="inlineStr">
-        <is>
-          <t>83000</t>
-        </is>
-      </c>
-      <c r="N118" s="0" t="inlineStr">
-        <is>
-          <t>80000</t>
-        </is>
-      </c>
-      <c r="O118" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="P118" s="0" t="inlineStr">
         <is>
-          <t>30~45</t>
+          <t>49</t>
         </is>
       </c>
       <c r="Q118" s="0" t="inlineStr">
         <is>
-          <t>2F 최상층 중실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
+          <t>2025.08 최근 최고가 성약 호실 (DOM 49일, 주차장 5,500엔 동시 계약)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>301호</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>3F</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
         <is>
-          <t>1LDK+로프트4.82㎡</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="F119" s="0" t="inlineStr">
         <is>
-          <t>신축모집예정(2026.12준공)</t>
+          <t>입주중</t>
         </is>
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>신축 2인입주가능(1LDK+로프트)</t>
+          <t>개인 (보증: 無 / 서브리스승계)</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
         <is>
-          <t>2026.12 준공예정</t>
+          <t>2023-11-12 (갱신: 2025-11-12)</t>
         </is>
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="J119" s="0" t="inlineStr">
         <is>
-          <t>83000</t>
+          <t>67000</t>
         </is>
       </c>
       <c r="K119" s="0" t="inlineStr">
         <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="L119" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L119" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M119" s="0" t="inlineStr">
         <is>
-          <t>83000</t>
+          <t>70500</t>
         </is>
       </c>
       <c r="N119" s="0" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="O119" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="P119" s="0" t="inlineStr">
         <is>
-          <t>30~45</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q119" s="0" t="inlineStr">
         <is>
-          <t>2F 최상층 중실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
+          <t>최상층 서측 코너 / 퇴거 시 공익비 5,000엔 현실화(+1,500엔) 가능</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>302호</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>3F</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
         <is>
-          <t>1LDK+로프트4.82㎡</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="F120" s="0" t="inlineStr">
         <is>
-          <t>신축모집예정(2026.12준공)</t>
+          <t>입주중</t>
         </is>
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>신축 2인입주가능(1LDK+로프트)</t>
+          <t>개인 (연대보증인 / 連帯保証人)</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
         <is>
-          <t>2026.12 준공예정</t>
+          <t>2023-06-01 (갱신: 2025-06-01)</t>
         </is>
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="J120" s="0" t="inlineStr">
         <is>
-          <t>85000</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="K120" s="0" t="inlineStr">
         <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="L120" s="0" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L120" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M120" s="0" t="inlineStr">
         <is>
-          <t>85000</t>
+          <t>68000</t>
         </is>
       </c>
       <c r="N120" s="0" t="inlineStr">
         <is>
-          <t>82000</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="O120" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="P120" s="0" t="inlineStr">
         <is>
-          <t>30~45</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q120" s="0" t="inlineStr">
         <is>
-          <t>2F 최상층 동측 각실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
+          <t>2023.06 구 서브리스 저가 호실 → 퇴거 시 월 +4,000엔(7.2만 엔) 상승 여력</t>
         </is>
       </c>
     </row>
@@ -17157,64 +17161,82 @@
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>101호</t>
+          <t>303호</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>3F</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
         <is>
-          <t>1LDK</t>
-        </is>
-      </c>
-      <c r="E121" s="0">
-        <v>43.32</v>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>29.81</t>
+        </is>
       </c>
       <c r="F121" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>입주중 (8월 입주)</t>
         </is>
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>개인 (보증: エポス)</t>
+          <t>개인 (보증: アシストレント)</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
         <is>
-          <t>2026-11-30 (2024.11 최초)</t>
-        </is>
-      </c>
-      <c r="I121" s="0">
-        <v>1.8</v>
-      </c>
-      <c r="J121" s="0">
-        <v>79000</v>
-      </c>
-      <c r="K121" s="0">
-        <v>3000</v>
-      </c>
-      <c r="L121" s="0">
-        <v>0</v>
-      </c>
-      <c r="M121" s="0">
-        <v>82000</v>
-      </c>
-      <c r="N121" s="0">
-        <v>82000</v>
-      </c>
-      <c r="O121" s="0">
-        <v>0</v>
-      </c>
-      <c r="P121" s="0">
-        <v>62</v>
+          <t>2026-08-01 (~2028-07-31)</t>
+        </is>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J121" s="0" t="inlineStr">
+        <is>
+          <t>65000</t>
+        </is>
+      </c>
+      <c r="K121" s="0" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="L121" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M121" s="0" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="N121" s="0" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="O121" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P121" s="0" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="Q121" s="0" t="inlineStr">
         <is>
-          <t>남서 코너 최대 평형 (43.32㎡) / 에포스 보증 가입 / 시키킨·RC 조사중</t>
+          <t>2026.08 스타츠 관리 전환 후 신규 입주 완료 (어시스트렌트 보증 가입)</t>
         </is>
       </c>
     </row>
@@ -17226,64 +17248,82 @@
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>102호</t>
+          <t>304호</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>3F</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
         <is>
-          <t>1LDK</t>
-        </is>
-      </c>
-      <c r="E122" s="0">
-        <v>37.26</v>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>29.81</t>
+        </is>
       </c>
       <c r="F122" s="0" t="inlineStr">
         <is>
-          <t>입주신청 (申込み有り)</t>
+          <t>입주중</t>
         </is>
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>개인 (신규 신청완료)</t>
+          <t>개인 (보증: 無 / 서브리스승계)</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
         <is>
-          <t>2026-09 (신규 입주예정)</t>
-        </is>
-      </c>
-      <c r="I122" s="0">
-        <v>0.1</v>
-      </c>
-      <c r="J122" s="0">
-        <v>75000</v>
-      </c>
-      <c r="K122" s="0">
-        <v>5000</v>
-      </c>
-      <c r="L122" s="0">
-        <v>0</v>
-      </c>
-      <c r="M122" s="0">
-        <v>80000</v>
-      </c>
-      <c r="N122" s="0">
-        <v>80000</v>
-      </c>
-      <c r="O122" s="0">
-        <v>0</v>
-      </c>
-      <c r="P122" s="0">
-        <v>30</v>
+          <t>2023-03-18 (갱신: 2025-04-18)</t>
+        </is>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J122" s="0" t="inlineStr">
+        <is>
+          <t>66000</t>
+        </is>
+      </c>
+      <c r="K122" s="0" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="L122" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M122" s="0" t="inlineStr">
+        <is>
+          <t>69000</t>
+        </is>
+      </c>
+      <c r="N122" s="0" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="O122" s="0" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="P122" s="0" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="Q122" s="0" t="inlineStr">
         <is>
-          <t>申込み有り (차임 7.5만 + 공익비 5,000엔 = 월 8.0만 엔 신규 신청 완료)</t>
+          <t>최상층 동측 코너 (주차장 5,500엔 동시 계약) → 퇴거 시 월 +5,000엔 상승 여력</t>
         </is>
       </c>
     </row>
@@ -17295,663 +17335,715 @@
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>103호</t>
+          <t>주차장 (4구획)</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>1F외</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
         <is>
-          <t>1LDK</t>
-        </is>
-      </c>
-      <c r="E123" s="0">
-        <v>37.26</v>
+          <t>평면주차 4대</t>
+        </is>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="F123" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>3대 입주자 + 1대 申込み有り</t>
         </is>
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>개인 (보증: 無)</t>
+          <t>201·204·304호 + 신규 1대</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
         <is>
-          <t>2025-10-31 (~2027-10-30)</t>
-        </is>
-      </c>
-      <c r="I123" s="0">
-        <v>0.9</v>
-      </c>
-      <c r="J123" s="0">
-        <v>75000</v>
-      </c>
-      <c r="K123" s="0">
-        <v>5000</v>
-      </c>
-      <c r="L123" s="0">
-        <v>0</v>
-      </c>
-      <c r="M123" s="0">
-        <v>80000</v>
-      </c>
-      <c r="N123" s="0">
-        <v>80000</v>
-      </c>
-      <c r="O123" s="0">
-        <v>0</v>
-      </c>
-      <c r="P123" s="0">
-        <v>100</v>
+          <t>2023-03 ~ 2026-09</t>
+        </is>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J123" s="0" t="inlineStr">
+        <is>
+          <t>22000</t>
+        </is>
+      </c>
+      <c r="K123" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L123" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M123" s="0" t="inlineStr">
+        <is>
+          <t>22000</t>
+        </is>
+      </c>
+      <c r="N123" s="0" t="inlineStr">
+        <is>
+          <t>25500</t>
+        </is>
+      </c>
+      <c r="O123" s="0" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="P123" s="0" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="Q123" s="0" t="inlineStr">
         <is>
-          <t>2025.10 계약 (월총액 8.0만 엔 성약 실증) / 구 다이하츠 서브리스 승계로 보증회사 미가입</t>
+          <t>구획당 월 5,500엔 × 4대 만차 (인근 시세 6,600엔 대비 월 +3,500엔 상승 여력)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>201호</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK (LDK8.0+양실5.5)</t>
         </is>
       </c>
       <c r="E124" s="0">
-        <v>28.41</v>
+        <v>26.89</v>
       </c>
       <c r="F124" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>법인 (法人契約 / 보증: 無)</t>
+          <t>신축 2인입주가능(1LDK)</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
         <is>
-          <t>2023-12-12 (갱신: 2025-12-12)</t>
-        </is>
-      </c>
-      <c r="I124" s="0">
-        <v>2.8</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I124" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J124" s="0">
-        <v>68000</v>
+        <v>80000</v>
       </c>
       <c r="K124" s="0">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="L124" s="0">
         <v>0</v>
       </c>
       <c r="M124" s="0">
-        <v>71500</v>
+        <v>80000</v>
       </c>
       <c r="N124" s="0">
-        <v>71500</v>
+        <v>78000</v>
       </c>
       <c r="O124" s="0">
         <v>0</v>
       </c>
-      <c r="P124" s="0">
-        <v>45</v>
+      <c r="P124" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q124" s="0" t="inlineStr">
         <is>
-          <t>우량 법인 사택 계약 (주차장 5,500엔 별도 동시 계약) / 1회 갱신 완료</t>
+          <t>1F 서측 각실 · 2면채광 · 1F 수동셔터 · 무료WiFi 포함</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>202호</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK (LDK8.0+양실5.5)</t>
         </is>
       </c>
       <c r="E125" s="0">
-        <v>29.81</v>
+        <v>26.89</v>
       </c>
       <c r="F125" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>개인 (보증: 無 / 서브리스승계)</t>
+          <t>신축 2인입주가능(1LDK)</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
         <is>
-          <t>2023-04-28 (갱신: 2025-04-28)</t>
-        </is>
-      </c>
-      <c r="I125" s="0">
-        <v>3.4</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I125" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J125" s="0">
-        <v>64000</v>
+        <v>78000</v>
       </c>
       <c r="K125" s="0">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L125" s="0">
         <v>0</v>
       </c>
       <c r="M125" s="0">
-        <v>67000</v>
+        <v>78000</v>
       </c>
       <c r="N125" s="0">
-        <v>72000</v>
+        <v>76000</v>
       </c>
       <c r="O125" s="0">
-        <v>5000</v>
-      </c>
-      <c r="P125" s="0">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="P125" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q125" s="0" t="inlineStr">
         <is>
-          <t>2023.04 구 서브리스 최저가 호실 → 퇴거 시 월 +5,000엔(7.2만 엔) 상승 여력</t>
+          <t>1F 중실 · UB1014 · IH2구 키친(W1200) · 수동셔터</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>203호</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK (LDK8.0+양실5.5)</t>
         </is>
       </c>
       <c r="E126" s="0">
-        <v>29.81</v>
+        <v>26.89</v>
       </c>
       <c r="F126" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>개인 (연대보증인 / 連帯保証人)</t>
+          <t>신축 2인입주가능(1LDK)</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>2023-04-17 (갱신: 2025-04-17)</t>
-        </is>
-      </c>
-      <c r="I126" s="0">
-        <v>3.4</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I126" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J126" s="0">
-        <v>65000</v>
+        <v>78000</v>
       </c>
       <c r="K126" s="0">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L126" s="0">
         <v>0</v>
       </c>
       <c r="M126" s="0">
-        <v>68000</v>
+        <v>78000</v>
       </c>
       <c r="N126" s="0">
-        <v>72000</v>
+        <v>76000</v>
       </c>
       <c r="O126" s="0">
-        <v>4000</v>
-      </c>
-      <c r="P126" s="0">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="P126" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q126" s="0" t="inlineStr">
         <is>
-          <t>2023.04 구 서브리스 저가 호실 → 퇴거 시 월 +4,000엔(7.2만 엔) 상승 여력</t>
+          <t>1F 중실 · 차음경계벽 천장속 밀실시공 · 무료WiFi</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>204호</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK (LDK8.0+양실5.5)</t>
         </is>
       </c>
       <c r="E127" s="0">
-        <v>29.81</v>
+        <v>26.89</v>
       </c>
       <c r="F127" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>개인 (보증: 無)</t>
+          <t>신축 2인입주가능(1LDK)</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
         <is>
-          <t>2025-08-31 (~2027-08-30)</t>
-        </is>
-      </c>
-      <c r="I127" s="0">
-        <v>1.1</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I127" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J127" s="0">
-        <v>70000</v>
+        <v>78000</v>
       </c>
       <c r="K127" s="0">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="L127" s="0">
         <v>0</v>
       </c>
       <c r="M127" s="0">
-        <v>75000</v>
+        <v>78000</v>
       </c>
       <c r="N127" s="0">
-        <v>75000</v>
+        <v>76000</v>
       </c>
       <c r="O127" s="0">
         <v>0</v>
       </c>
-      <c r="P127" s="0">
-        <v>49</v>
+      <c r="P127" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q127" s="0" t="inlineStr">
         <is>
-          <t>2025.08 최근 최고가 성약 호실 (DOM 49일, 주차장 5,500엔 동시 계약)</t>
+          <t>1F 중실 · 수동셔터 · 무료WiFi 포함</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>301호</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>1F</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E128" s="0">
-        <v>28.41</v>
+        <v>26.89</v>
       </c>
       <c r="F128" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>개인 (보증: 無 / 서브리스승계)</t>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
         <is>
-          <t>2023-11-12 (갱신: 2025-11-12)</t>
-        </is>
-      </c>
-      <c r="I128" s="0">
-        <v>2.9</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I128" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J128" s="0">
-        <v>67000</v>
+        <v>80000</v>
       </c>
       <c r="K128" s="0">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="L128" s="0">
         <v>0</v>
       </c>
       <c r="M128" s="0">
-        <v>70500</v>
+        <v>80000</v>
       </c>
       <c r="N128" s="0">
-        <v>72000</v>
+        <v>80000</v>
       </c>
       <c r="O128" s="0">
-        <v>1500</v>
-      </c>
-      <c r="P128" s="0">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="P128" s="0" t="inlineStr">
+        <is>
+          <t>25~35</t>
+        </is>
       </c>
       <c r="Q128" s="0" t="inlineStr">
         <is>
-          <t>최상층 서측 코너 / 퇴거 시 공익비 5,000엔 현실화(+1,500엔) 가능</t>
+          <t>1F 동측 단층부 각실 + 4.82㎡ 대형 로프트(실사용 31.71㎡, 2,523엔/㎡)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>302호</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E129" s="0">
-        <v>29.81</v>
+        <v>26.89</v>
       </c>
       <c r="F129" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>개인 (연대보증인 / 連帯保証人)</t>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
         <is>
-          <t>2023-06-01 (갱신: 2025-06-01)</t>
-        </is>
-      </c>
-      <c r="I129" s="0">
-        <v>3.3</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I129" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J129" s="0">
-        <v>65000</v>
+        <v>85000</v>
       </c>
       <c r="K129" s="0">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L129" s="0">
         <v>0</v>
       </c>
       <c r="M129" s="0">
-        <v>68000</v>
+        <v>85000</v>
       </c>
       <c r="N129" s="0">
-        <v>72000</v>
+        <v>82000</v>
       </c>
       <c r="O129" s="0">
-        <v>4000</v>
-      </c>
-      <c r="P129" s="0">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="P129" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q129" s="0" t="inlineStr">
         <is>
-          <t>2023.06 구 서브리스 저가 호실 → 퇴거 시 월 +4,000엔(7.2만 엔) 상승 여력</t>
+          <t>2F 최상층 서측 각실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>303호</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E130" s="0">
-        <v>29.81</v>
+        <v>26.89</v>
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
-          <t>입주중 (8월 입주)</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>개인 (보증: アシストレント)</t>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
         <is>
-          <t>2026-08-01 (~2028-07-31)</t>
-        </is>
-      </c>
-      <c r="I130" s="0">
-        <v>0.2</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I130" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J130" s="0">
-        <v>65000</v>
+        <v>83000</v>
       </c>
       <c r="K130" s="0">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="L130" s="0">
         <v>0</v>
       </c>
       <c r="M130" s="0">
-        <v>70000</v>
+        <v>83000</v>
       </c>
       <c r="N130" s="0">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="O130" s="0">
         <v>0</v>
       </c>
-      <c r="P130" s="0">
-        <v>35</v>
+      <c r="P130" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q130" s="0" t="inlineStr">
         <is>
-          <t>2026.08 스타츠 관리 전환 후 신규 입주 완료 (어시스트렌트 보증 가입)</t>
+          <t>2F 최상층 중실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>304호</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E131" s="0">
-        <v>29.81</v>
+        <v>26.89</v>
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
-          <t>입주중</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>개인 (보증: 無 / 서브리스승계)</t>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
         <is>
-          <t>2023-03-18 (갱신: 2025-04-18)</t>
-        </is>
-      </c>
-      <c r="I131" s="0">
-        <v>3.5</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I131" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J131" s="0">
-        <v>66000</v>
+        <v>83000</v>
       </c>
       <c r="K131" s="0">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L131" s="0">
         <v>0</v>
       </c>
       <c r="M131" s="0">
-        <v>69000</v>
+        <v>83000</v>
       </c>
       <c r="N131" s="0">
-        <v>74000</v>
+        <v>80000</v>
       </c>
       <c r="O131" s="0">
-        <v>5000</v>
-      </c>
-      <c r="P131" s="0">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="P131" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q131" s="0" t="inlineStr">
         <is>
-          <t>최상층 동측 코너 (주차장 5,500엔 동시 계약) → 퇴거 시 월 +5,000엔 상승 여력</t>
+          <t>2F 최상층 중실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>주차장 (4구획)</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>1F외</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
         <is>
-          <t>평면주차 4대</t>
+          <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
       <c r="E132" s="0">
-        <v>0.0</v>
+        <v>26.89</v>
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
-          <t>3대 입주자 + 1대 申込み有り</t>
+          <t>신축모집예정(2026.12준공)</t>
         </is>
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>201·204·304호 + 신규 1대</t>
+          <t>신축 2인입주가능(1LDK+로프트)</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
         <is>
-          <t>2023-03 ~ 2026-09</t>
-        </is>
-      </c>
-      <c r="I132" s="0">
-        <v>2.0</v>
+          <t>2026.12 준공예정</t>
+        </is>
+      </c>
+      <c r="I132" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J132" s="0">
-        <v>22000</v>
+        <v>85000</v>
       </c>
       <c r="K132" s="0">
         <v>0</v>
@@ -17960,20 +18052,22 @@
         <v>0</v>
       </c>
       <c r="M132" s="0">
-        <v>22000</v>
+        <v>85000</v>
       </c>
       <c r="N132" s="0">
-        <v>25500</v>
+        <v>82000</v>
       </c>
       <c r="O132" s="0">
-        <v>3500</v>
-      </c>
-      <c r="P132" s="0">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="P132" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
       </c>
       <c r="Q132" s="0" t="inlineStr">
         <is>
-          <t>구획당 월 5,500엔 × 4대 만차 (인근 시세 6,600엔 대비 월 +3,500엔 상승 여력)</t>
+          <t>2F 최상층 동측 각실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
         </is>
       </c>
     </row>
@@ -37994,7 +38088,7 @@
     <row r="352">
       <c r="A352" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B352" s="0" t="inlineStr">
@@ -38024,7 +38118,7 @@
       </c>
       <c r="G352" s="0" t="inlineStr">
         <is>
-          <t>미츠쿄 1AP 사사노다이 (三ツ境1AP)</t>
+          <t>리브르 파인 미사토추오 (Livre Fine Misato-Chuo)</t>
         </is>
       </c>
       <c r="H352" s="0" t="inlineStr">
@@ -38051,7 +38145,7 @@
     <row r="353">
       <c r="A353" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B353" s="0" t="inlineStr">
@@ -38081,7 +38175,7 @@
       </c>
       <c r="G353" s="0" t="inlineStr">
         <is>
-          <t>神奈川県横浜市旭区笹野台2丁目19-5</t>
+          <t>사이타마현 미사토시 야구치 386-5 (埼玉県三郷市谷口386-5)</t>
         </is>
       </c>
       <c r="H353" s="0" t="inlineStr">
@@ -38108,7 +38202,7 @@
     <row r="354">
       <c r="A354" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B354" s="0" t="inlineStr">
@@ -38138,7 +38232,7 @@
       </c>
       <c r="G354" s="0" t="inlineStr">
         <is>
-          <t>神奈川県横浜市旭区笹野台二丁目149番3、231番102</t>
+          <t>埼玉県三郷市谷口字根通386番5、386番7、私道386番3(持分1/2)</t>
         </is>
       </c>
       <c r="H354" s="0" t="inlineStr">
@@ -38165,7 +38259,7 @@
     <row r="355">
       <c r="A355" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B355" s="0" t="inlineStr">
@@ -38195,7 +38289,7 @@
       </c>
       <c r="G355" s="0" t="inlineStr">
         <is>
-          <t>134700000</t>
+          <t>140000000</t>
         </is>
       </c>
       <c r="H355" s="0" t="inlineStr">
@@ -38222,7 +38316,7 @@
     <row r="356">
       <c r="A356" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B356" s="0" t="inlineStr">
@@ -38252,7 +38346,7 @@
       </c>
       <c r="G356" s="0" t="inlineStr">
         <is>
-          <t>2026년 12월 말 준공 / 2027년 1월 신축 인도 (계약금 보전조치 불요 범위)</t>
+          <t>현황인도 (R8 본하수 접속공사 약 180만 엔+수익자부담금 매수자 부담)</t>
         </is>
       </c>
       <c r="H356" s="0" t="inlineStr">
@@ -38279,7 +38373,7 @@
     <row r="357">
       <c r="A357" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B357" s="0" t="inlineStr">
@@ -38309,7 +38403,7 @@
       </c>
       <c r="G357" s="0" t="inlineStr">
         <is>
-          <t>397.71</t>
+          <t>382.33</t>
         </is>
       </c>
       <c r="H357" s="0" t="inlineStr">
@@ -38336,7 +38430,7 @@
     <row r="358">
       <c r="A358" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B358" s="0" t="inlineStr">
@@ -38366,7 +38460,7 @@
       </c>
       <c r="G358" s="0" t="inlineStr">
         <is>
-          <t>소유권 (所有権)</t>
+          <t>소유권 (택지 386-5·386-7 100% + 사도 386-3 지분 1/2)</t>
         </is>
       </c>
       <c r="H358" s="0" t="inlineStr">
@@ -38393,7 +38487,7 @@
     <row r="359">
       <c r="A359" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B359" s="0" t="inlineStr">
@@ -38423,7 +38517,7 @@
       </c>
       <c r="G359" s="0" t="inlineStr">
         <is>
-          <t>제1종 저층주거전용지역 · 제1종 고도지구</t>
+          <t>第一種住居地域 (建蔽率60% / 容積率200% [4m도로기준 160%]・法22条区域)</t>
         </is>
       </c>
       <c r="H359" s="0" t="inlineStr">
@@ -38450,7 +38544,7 @@
     <row r="360">
       <c r="A360" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B360" s="0" t="inlineStr">
@@ -38480,7 +38574,7 @@
       </c>
       <c r="G360" s="0" t="inlineStr">
         <is>
-          <t>남서측 폭원 3.92~4.50m 요코하마시 공도(下川井第402号線, 일부 계단) 및 서측 폭원 4.00~5.50m 요코하마시 공도(下川井第398号線) 접도</t>
+          <t>南側 位置指定道路(386番3・幅員4.00m・昭和51年第1496号・持分1/2有)に幅員4.00m協定通路で接道</t>
         </is>
       </c>
       <c r="H360" s="0" t="inlineStr">
@@ -38507,7 +38601,7 @@
     <row r="361">
       <c r="A361" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B361" s="0" t="inlineStr">
@@ -38537,7 +38631,7 @@
       </c>
       <c r="G361" s="0" t="inlineStr">
         <is>
-          <t>없음 (등기부 지번 231-1 요코하마시 소유 공중용도로 및 인정노선도 100% 공도 검증완료)</t>
+          <t>사도(386番3, 128㎡) 지분 1/2 보유(비과세) + 『토지공동사용협정서(386番6+386番7 폭 4m 무상·자동승계)』 원본 완비</t>
         </is>
       </c>
       <c r="H361" s="0" t="inlineStr">
@@ -38564,7 +38658,7 @@
     <row r="362">
       <c r="A362" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B362" s="0" t="inlineStr">
@@ -38594,7 +38688,7 @@
       </c>
       <c r="G362" s="0" t="inlineStr">
         <is>
-          <t>목조 준내화구조 지상 2층건 (RC베타기초+7.00m 기초파일 / 설계·건설 열화대책등급 3급)</t>
+          <t>목조 아연도금강판지붕 지상 3층건 (2×4공법·열화대책등급 3급)</t>
         </is>
       </c>
       <c r="H362" s="0" t="inlineStr">
@@ -38621,7 +38715,7 @@
     <row r="363">
       <c r="A363" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B363" s="0" t="inlineStr">
@@ -38651,7 +38745,7 @@
       </c>
       <c r="G363" s="0" t="inlineStr">
         <is>
-          <t>2026년 12월 말 준공 예정 (2027년 1월 인도 예정)</t>
+          <t>2021年2月25日新築 (令和3年2月 / 築5.6年)</t>
         </is>
       </c>
       <c r="H363" s="0" t="inlineStr">
@@ -38678,7 +38772,7 @@
     <row r="364">
       <c r="A364" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B364" s="0" t="inlineStr">
@@ -38708,7 +38802,7 @@
       </c>
       <c r="G364" s="0" t="inlineStr">
         <is>
-          <t>242.07</t>
+          <t>353.55</t>
         </is>
       </c>
       <c r="H364" s="0" t="inlineStr">
@@ -38735,7 +38829,7 @@
     <row r="365">
       <c r="A365" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B365" s="0" t="inlineStr">
@@ -38765,7 +38859,7 @@
       </c>
       <c r="G365" s="0" t="inlineStr">
         <is>
-          <t>유 (제26UDI1K건00271호, R8.6.18 교부 확인필증 사본 완비)</t>
+          <t>유 (건축도면·배치도·평면도·입면도 일식 확인완료)</t>
         </is>
       </c>
       <c r="H365" s="0" t="inlineStr">
@@ -38790,66 +38884,66 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B366" s="0" t="inlineStr">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>livre-fine-misato-chuo</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
         <is>
           <t>CHK_15</t>
         </is>
       </c>
-      <c r="C366" s="0" t="inlineStr">
+      <c r="C366" s="3" t="inlineStr">
         <is>
           <t>3.건물/적법</t>
         </is>
       </c>
-      <c r="D366" s="0" t="inlineStr">
+      <c r="D366" s="3" t="inlineStr">
         <is>
           <t>has_inspection_cert</t>
         </is>
       </c>
-      <c r="E366" s="0" t="inlineStr">
+      <c r="E366" s="3" t="inlineStr">
         <is>
           <t>준공검사필증(検査済証) 취득 여부</t>
         </is>
       </c>
-      <c r="F366" s="0" t="inlineStr">
+      <c r="F366" s="3" t="inlineStr">
         <is>
           <t>検査済証の有無</t>
         </is>
       </c>
-      <c r="G366" s="0" t="inlineStr">
-        <is>
-          <t>신축 건축중 (2026.12 말 준공 시 건축물 검사필증 및 건설주택성능평가서 열화3급 교부 예정 / 단, 기존 옹벽은 검사필증 없음)</t>
-        </is>
-      </c>
-      <c r="H366" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I366" s="0" t="inlineStr">
-        <is>
-          <t>검사필증/대장</t>
-        </is>
-      </c>
-      <c r="J366" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K366" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G366" s="3" t="inlineStr">
+        <is>
+          <t>유 (2021.2 신축·오릭스/au지분은행 열화3급 35년 융자평가 확인완료 / 원본사본 징구예정)</t>
+        </is>
+      </c>
+      <c r="H366" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I366" s="3" t="inlineStr">
+        <is>
+          <t>오릭스·au지분 35년 융자평가 확인 (원본사본 미징구)</t>
+        </is>
+      </c>
+      <c r="J366" s="3" t="inlineStr">
+        <is>
+          <t>준공검사필증(検査済証) 및 열화대책등급 3급 주택성능평가서 사본, 프로판가스(LPG) 무상대여 약정서 유무 공유 요청</t>
+        </is>
+      </c>
+      <c r="K366" s="3" t="inlineStr">
+        <is>
+          <t>検査済証および劣化対策等級3級の住宅性能評価書の写し、ならびにプロパンガス無償貸与契約の有無のご確認</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B367" s="0" t="inlineStr">
@@ -38879,7 +38973,7 @@
       </c>
       <c r="G367" s="0" t="inlineStr">
         <is>
-          <t>신축 완공 예정 (RC베타기초+7.0m 기초파일 시공 / 동·북측 기존 간지블록 옹벽 98.84㎡는 보강계획 없음 확인)</t>
+          <t>축 5.6년 신축급으로 과거 대규모 수선이력 및 침수이력 없음 (중개사·매도자 공식 확인완료)</t>
         </is>
       </c>
       <c r="H367" s="0" t="inlineStr">
@@ -38904,66 +38998,66 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="3" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B368" s="3" t="inlineStr">
+      <c r="A368" s="0" t="inlineStr">
+        <is>
+          <t>livre-fine-misato-chuo</t>
+        </is>
+      </c>
+      <c r="B368" s="0" t="inlineStr">
         <is>
           <t>CHK_17</t>
         </is>
       </c>
-      <c r="C368" s="3" t="inlineStr">
+      <c r="C368" s="0" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D368" s="3" t="inlineStr">
+      <c r="D368" s="0" t="inlineStr">
         <is>
           <t>full_annual_income_yen</t>
         </is>
       </c>
-      <c r="E368" s="3" t="inlineStr">
+      <c r="E368" s="0" t="inlineStr">
         <is>
           <t>호실별 월 차임 및 공익비 내역</t>
         </is>
       </c>
-      <c r="F368" s="3" t="inlineStr">
+      <c r="F368" s="0" t="inlineStr">
         <is>
           <t>各戸賃料・共益費一覧</t>
         </is>
       </c>
-      <c r="G368" s="3" t="inlineStr">
-        <is>
-          <t>8760000</t>
-        </is>
-      </c>
-      <c r="H368" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I368" s="3" t="inlineStr">
-        <is>
-          <t>표준산식 역산 추정</t>
-        </is>
-      </c>
-      <c r="J368" s="3" t="inlineStr">
-        <is>
-          <t>최신 렌트롤(호실별 차임·공익비·보증금 명시본) 요청</t>
-        </is>
-      </c>
-      <c r="K368" s="3" t="inlineStr">
-        <is>
-          <t>最新のレントロール（各戸賃料・共益費・敷金明細）のご共有</t>
+      <c r="G368" s="0" t="inlineStr">
+        <is>
+          <t>9876000</t>
+        </is>
+      </c>
+      <c r="H368" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I368" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤</t>
+        </is>
+      </c>
+      <c r="J368" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K368" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B369" s="0" t="inlineStr">
@@ -38993,7 +39087,7 @@
       </c>
       <c r="G369" s="0" t="inlineStr">
         <is>
-          <t>전 9세대 1LDK(26.89㎡: LDK8.0+양실5.5, 2인입주 가능) + 5세대(105, 201~204호) 로프트 4.82㎡</t>
+          <t>총 11세대 (1F: 1LDK×3실 [37.26~43.32㎡] / 2~3F: 1K×8실 [28.41~29.81㎡])</t>
         </is>
       </c>
       <c r="H369" s="0" t="inlineStr">
@@ -39020,7 +39114,7 @@
     <row r="370">
       <c r="A370" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B370" s="0" t="inlineStr">
@@ -39050,7 +39144,7 @@
       </c>
       <c r="G370" s="0" t="inlineStr">
         <is>
-          <t>전수/일부 확인 (9실)</t>
+          <t>전수/일부 확인 (12실)</t>
         </is>
       </c>
       <c r="H370" s="0" t="inlineStr">
@@ -39075,66 +39169,66 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B371" s="0" t="inlineStr">
+      <c r="A371" s="3" t="inlineStr">
+        <is>
+          <t>livre-fine-misato-chuo</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
         <is>
           <t>CHK_20</t>
         </is>
       </c>
-      <c r="C371" s="0" t="inlineStr">
+      <c r="C371" s="3" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D371" s="0" t="inlineStr">
+      <c r="D371" s="3" t="inlineStr">
         <is>
           <t>rent_roll_tenant_types</t>
         </is>
       </c>
-      <c r="E371" s="0" t="inlineStr">
+      <c r="E371" s="3" t="inlineStr">
         <is>
           <t>호실별 입주자 속성(법인/직장인/학생/보증회사)</t>
         </is>
       </c>
-      <c r="F371" s="0" t="inlineStr">
+      <c r="F371" s="3" t="inlineStr">
         <is>
           <t>入居者属性・保証会社加入状況</t>
         </is>
       </c>
-      <c r="G371" s="0" t="inlineStr">
-        <is>
-          <t>속성 확인 (9실)</t>
-        </is>
-      </c>
-      <c r="H371" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I371" s="0" t="inlineStr">
-        <is>
-          <t>렌트롤 상세판</t>
-        </is>
-      </c>
-      <c r="J371" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K371" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G371" s="3" t="inlineStr">
+        <is>
+          <t>속성 확인 (12실)</t>
+        </is>
+      </c>
+      <c r="H371" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I371" s="3" t="inlineStr">
+        <is>
+          <t>공식 렌트롤 (敷金·RC 『調査中』 표기)</t>
+        </is>
+      </c>
+      <c r="J371" s="3" t="inlineStr">
+        <is>
+          <t>렌트롤상 『調査中』인 전 호실 시키킨(敷金)·RC 확정 금액 및 서브리스 해지 승계 무보증 6세대의 최근 6개월 수납 내역 확인</t>
+        </is>
+      </c>
+      <c r="K371" s="3" t="inlineStr">
+        <is>
+          <t>レントロール上「調査中」となっている各戸敷金・RCの確定額、および保証会社無しの6戸における直近6ヶ月の家賃入金状況のご確認</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B372" s="0" t="inlineStr">
@@ -39164,7 +39258,7 @@
       </c>
       <c r="G372" s="0" t="inlineStr">
         <is>
-          <t>없음 (전면도로 계단 직전까지 차량 접근 가능)</t>
+          <t>부지 내 평면 주차장 4구획 (각 월 5,500엔 × 4대 = 월 22,000엔 만차)</t>
         </is>
       </c>
       <c r="H372" s="0" t="inlineStr">
@@ -39191,7 +39285,7 @@
     <row r="373">
       <c r="A373" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B373" s="0" t="inlineStr">
@@ -39221,7 +39315,7 @@
       </c>
       <c r="G373" s="0" t="inlineStr">
         <is>
-          <t>1130040</t>
+          <t>1698233</t>
         </is>
       </c>
       <c r="H373" s="0" t="inlineStr">
@@ -39248,7 +39342,7 @@
     <row r="374">
       <c r="A374" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B374" s="0" t="inlineStr">
@@ -39278,7 +39372,7 @@
       </c>
       <c r="G374" s="0" t="inlineStr">
         <is>
-          <t>공영수도·공공하수·무료WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정 확인완료)</t>
+          <t>현재 정화조(월 1만엔) → R8 본하수 접속공사(세금포함 약 180만엔+부담금 시청조사중) 후 직결</t>
         </is>
       </c>
       <c r="H374" s="0" t="inlineStr">
@@ -39305,7 +39399,7 @@
     <row r="375">
       <c r="A375" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B375" s="0" t="inlineStr">
@@ -39335,7 +39429,7 @@
       </c>
       <c r="G375" s="0" t="inlineStr">
         <is>
-          <t>36985271</t>
+          <t>27054052</t>
         </is>
       </c>
       <c r="H375" s="0" t="inlineStr">
@@ -39360,66 +39454,66 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="3" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B376" s="3" t="inlineStr">
+      <c r="A376" s="0" t="inlineStr">
+        <is>
+          <t>livre-fine-misato-chuo</t>
+        </is>
+      </c>
+      <c r="B376" s="0" t="inlineStr">
         <is>
           <t>CHK_25</t>
         </is>
       </c>
-      <c r="C376" s="3" t="inlineStr">
+      <c r="C376" s="0" t="inlineStr">
         <is>
           <t>5.경비/세금</t>
         </is>
       </c>
-      <c r="D376" s="3" t="inlineStr">
+      <c r="D376" s="0" t="inlineStr">
         <is>
           <t>fixed_tax_bldg_eval_yen</t>
         </is>
       </c>
-      <c r="E376" s="3" t="inlineStr">
+      <c r="E376" s="0" t="inlineStr">
         <is>
           <t>고정자산세 건물 과세평가액</t>
         </is>
       </c>
-      <c r="F376" s="3" t="inlineStr">
+      <c r="F376" s="0" t="inlineStr">
         <is>
           <t>固定資産税評価額（建物）</t>
         </is>
       </c>
-      <c r="G376" s="3" t="inlineStr">
-        <is>
-          <t>26627700</t>
-        </is>
-      </c>
-      <c r="H376" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I376" s="3" t="inlineStr">
-        <is>
-          <t>표준산식 역산 추정</t>
-        </is>
-      </c>
-      <c r="J376" s="3" t="inlineStr">
-        <is>
-          <t>최신 연도 고정자산세·도시계획세 과세명세서(건물 평가액) 사본 요청</t>
-        </is>
-      </c>
-      <c r="K376" s="3" t="inlineStr">
-        <is>
-          <t>最新年度の固定資産税・都市計画税課税明細書（建物評価額）の写しのご共有</t>
+      <c r="G376" s="0" t="inlineStr">
+        <is>
+          <t>27152612</t>
+        </is>
+      </c>
+      <c r="H376" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I376" s="0" t="inlineStr">
+        <is>
+          <t>과세명세서</t>
+        </is>
+      </c>
+      <c r="J376" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K376" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B377" s="0" t="inlineStr">
@@ -39449,7 +39543,7 @@
       </c>
       <c r="G377" s="0" t="inlineStr">
         <is>
-          <t>573,283엔 (R8 토지 공과증명서 주택특례 약 12.3만 엔 + 건물 오카다상 확인 약 45만 엔 추정)</t>
+          <t>474,221엔 (레이와 8년도 과세원장 확정: 토지 76,651 + 건물 397,570)</t>
         </is>
       </c>
       <c r="H377" s="0" t="inlineStr">
@@ -39476,7 +39570,7 @@
     <row r="378">
       <c r="A378" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B378" s="0" t="inlineStr">
@@ -39506,7 +39600,7 @@
       </c>
       <c r="G378" s="0" t="inlineStr">
         <is>
-          <t>검증완료: 야오키상사 주식회사(ヤオキ商事株式会社, R7.6.27 매매 취득, 149-3 및 231-102 2필지 일치)</t>
+          <t>[등기부 원장 확인완료]</t>
         </is>
       </c>
       <c r="H378" s="0" t="inlineStr">
@@ -39533,7 +39627,7 @@
     <row r="379">
       <c r="A379" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B379" s="0" t="inlineStr">
@@ -39563,7 +39657,7 @@
       </c>
       <c r="G379" s="0" t="inlineStr">
         <is>
-          <t>검증완료: S32/S57 개인취득 → H9 상속 → H15 매매 → R7.6.27 야오키상사(주) 신축분양 목적 매입</t>
+          <t>[등기부 원장 확인완료]</t>
         </is>
       </c>
       <c r="H379" s="0" t="inlineStr">
@@ -39590,7 +39684,7 @@
     <row r="380">
       <c r="A380" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B380" s="0" t="inlineStr">
@@ -39620,7 +39714,7 @@
       </c>
       <c r="G380" s="0" t="inlineStr">
         <is>
-          <t>검증완료: R7.6.27 카와사키신용금고(登戸支店) 채권액 7,700만 엔·금리 연 3.050% 공동담보 근저당 설정 (인도 시 말소 조건)</t>
+          <t>[등기부 원장 확인완료]</t>
         </is>
       </c>
       <c r="H380" s="0" t="inlineStr">
@@ -39645,66 +39739,66 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B381" s="0" t="inlineStr">
+      <c r="A381" s="3" t="inlineStr">
+        <is>
+          <t>livre-fine-misato-chuo</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
         <is>
           <t>CHK_30</t>
         </is>
       </c>
-      <c r="C381" s="0" t="inlineStr">
+      <c r="C381" s="3" t="inlineStr">
         <is>
           <t>7.외부실사</t>
         </is>
       </c>
-      <c r="D381" s="0" t="inlineStr">
+      <c r="D381" s="3" t="inlineStr">
         <is>
           <t>roadside_price_sqm</t>
         </is>
       </c>
-      <c r="E381" s="0" t="inlineStr">
+      <c r="E381" s="3" t="inlineStr">
         <is>
           <t>국세청 상속세 노선가(路線価) 조회</t>
         </is>
       </c>
-      <c r="F381" s="0" t="inlineStr">
+      <c r="F381" s="3" t="inlineStr">
         <is>
           <t>相続税路線価</t>
         </is>
       </c>
-      <c r="G381" s="0" t="inlineStr">
-        <is>
-          <t>190000</t>
-        </is>
-      </c>
-      <c r="H381" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I381" s="0" t="inlineStr">
-        <is>
-          <t>국세청 노선가도</t>
-        </is>
-      </c>
-      <c r="J381" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K381" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G381" s="3" t="inlineStr">
+        <is>
+          <t>125000</t>
+        </is>
+      </c>
+      <c r="H381" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I381" s="3" t="inlineStr">
+        <is>
+          <t>공시지가 기반 노선가 산정 / 본하수 부담금 시청 조사중</t>
+        </is>
+      </c>
+      <c r="J381" s="3" t="inlineStr">
+        <is>
+          <t>현재 미사토시청에 조사 중인 하수도 수익자부담금 확정액 및 본하수 접속공사(세금포함 약 180만 엔) 상세 견적서 공유 요청</t>
+        </is>
+      </c>
+      <c r="K381" s="3" t="inlineStr">
+        <is>
+          <t>現在三郷市役所にて調査中の下水道受益者負担金の確定額、および本下水接続工事（税込約180万円）の詳細見積書のご共有</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B382" s="0" t="inlineStr">
@@ -39734,7 +39828,7 @@
       </c>
       <c r="G382" s="0" t="inlineStr">
         <is>
-          <t>실측 도보 10분 (구글맵 및 오카다상 현장 확인완료)</t>
+          <t>도보 15~16분 (구글맵 실측 검증완료)</t>
         </is>
       </c>
       <c r="H382" s="0" t="inlineStr">
@@ -39761,7 +39855,7 @@
     <row r="383">
       <c r="A383" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B383" s="0" t="inlineStr">
@@ -39791,7 +39885,7 @@
       </c>
       <c r="G383" s="0" t="inlineStr">
         <is>
-          <t>사사노다이 상점가 경유 후 남서측 전면도로(下川井第402号線) 진입부에 계단 구간 및 부지 고저차(4.0~4.69m) 존재 확인완료</t>
+          <t>고저차 없는 평탄지 (다이니오바가와 교량 횡단·1층 바닥 GL+450mm 확인)</t>
         </is>
       </c>
       <c r="H383" s="0" t="inlineStr">
@@ -39818,7 +39912,7 @@
     <row r="384">
       <c r="A384" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B384" s="0" t="inlineStr">
@@ -39848,7 +39942,7 @@
       </c>
       <c r="G384" s="0" t="inlineStr">
         <is>
-          <t>고대(高台) 입지로 홍수·내수 침수 해저드 해당 없음 (교차검증 완료)</t>
+          <t>하저드맵 3.0~5.0m 구역이나 『과거 집중호우 포함 침수 피해 이력 전무』 매도자 공식 확인완료</t>
         </is>
       </c>
       <c r="H384" s="0" t="inlineStr">
@@ -39875,7 +39969,7 @@
     <row r="385">
       <c r="A385" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B385" s="0" t="inlineStr">
@@ -39905,7 +39999,7 @@
       </c>
       <c r="G385" s="0" t="inlineStr">
         <is>
-          <t>부지 북서측 모서리 옹벽 부분(가측량도 약 4.69㎡)이 토사재해경계구역(옐로우존/잠정 레드존 경계)에 일부 저촉 확인완료 (건물 본체는 2m 이격되어 구역 외)</t>
+          <t>해당 없음 (완전 평탄지·토사재해 경계구역 외)</t>
         </is>
       </c>
       <c r="H385" s="0" t="inlineStr">
@@ -39932,7 +40026,7 @@
     <row r="386">
       <c r="A386" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B386" s="0" t="inlineStr">
@@ -39962,7 +40056,7 @@
       </c>
       <c r="G386" s="0" t="inlineStr">
         <is>
-          <t>30~45일 (REINS 근린 성약 50건 및 일 피오레 사사노다이 교차검증 완료)</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H386" s="0" t="inlineStr">
@@ -39989,7 +40083,7 @@
     <row r="387">
       <c r="A387" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B387" s="0" t="inlineStr">
@@ -40019,7 +40113,7 @@
       </c>
       <c r="G387" s="0" t="inlineStr">
         <is>
-          <t>리브르 파인 미사토추오 (Livre Fine Misato-Chuo)</t>
+          <t>미츠쿄 1AP 사사노다이 (三ツ境1AP)</t>
         </is>
       </c>
       <c r="H387" s="0" t="inlineStr">
@@ -40046,7 +40140,7 @@
     <row r="388">
       <c r="A388" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B388" s="0" t="inlineStr">
@@ -40076,7 +40170,7 @@
       </c>
       <c r="G388" s="0" t="inlineStr">
         <is>
-          <t>사이타마현 미사토시 야구치 386-5 (埼玉県三郷市谷口386-5)</t>
+          <t>神奈川県横浜市旭区笹野台2丁目19-5</t>
         </is>
       </c>
       <c r="H388" s="0" t="inlineStr">
@@ -40103,7 +40197,7 @@
     <row r="389">
       <c r="A389" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B389" s="0" t="inlineStr">
@@ -40133,7 +40227,7 @@
       </c>
       <c r="G389" s="0" t="inlineStr">
         <is>
-          <t>埼玉県三郷市谷口字根通386番5、386番7、私道386番3(持分1/2)</t>
+          <t>神奈川県横浜市旭区笹野台二丁目149番3、231番102</t>
         </is>
       </c>
       <c r="H389" s="0" t="inlineStr">
@@ -40160,7 +40254,7 @@
     <row r="390">
       <c r="A390" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B390" s="0" t="inlineStr">
@@ -40190,7 +40284,7 @@
       </c>
       <c r="G390" s="0" t="inlineStr">
         <is>
-          <t>140000000</t>
+          <t>134700000</t>
         </is>
       </c>
       <c r="H390" s="0" t="inlineStr">
@@ -40217,7 +40311,7 @@
     <row r="391">
       <c r="A391" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B391" s="0" t="inlineStr">
@@ -40247,7 +40341,7 @@
       </c>
       <c r="G391" s="0" t="inlineStr">
         <is>
-          <t>현황인도 (R8 본하수 접속공사 약 180만 엔+수익자부담금 매수자 부담)</t>
+          <t>2026년 12월 말 준공 / 2027년 1월 신축 인도 (계약금 보전조치 불요 범위)</t>
         </is>
       </c>
       <c r="H391" s="0" t="inlineStr">
@@ -40274,7 +40368,7 @@
     <row r="392">
       <c r="A392" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B392" s="0" t="inlineStr">
@@ -40304,7 +40398,7 @@
       </c>
       <c r="G392" s="0" t="inlineStr">
         <is>
-          <t>382.33</t>
+          <t>397.71</t>
         </is>
       </c>
       <c r="H392" s="0" t="inlineStr">
@@ -40331,7 +40425,7 @@
     <row r="393">
       <c r="A393" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B393" s="0" t="inlineStr">
@@ -40361,7 +40455,7 @@
       </c>
       <c r="G393" s="0" t="inlineStr">
         <is>
-          <t>소유권 (택지 386-5·386-7 100% + 사도 386-3 지분 1/2)</t>
+          <t>소유권 (所有権)</t>
         </is>
       </c>
       <c r="H393" s="0" t="inlineStr">
@@ -40388,7 +40482,7 @@
     <row r="394">
       <c r="A394" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B394" s="0" t="inlineStr">
@@ -40418,7 +40512,7 @@
       </c>
       <c r="G394" s="0" t="inlineStr">
         <is>
-          <t>第一種住居地域 (建蔽率60% / 容積率200% [4m도로기준 160%]・法22条区域)</t>
+          <t>제1종 저층주거전용지역 · 제1종 고도지구</t>
         </is>
       </c>
       <c r="H394" s="0" t="inlineStr">
@@ -40445,7 +40539,7 @@
     <row r="395">
       <c r="A395" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B395" s="0" t="inlineStr">
@@ -40475,7 +40569,7 @@
       </c>
       <c r="G395" s="0" t="inlineStr">
         <is>
-          <t>南側 位置指定道路(386番3・幅員4.00m・昭和51年第1496号・持分1/2有)に幅員4.00m協定通路で接道</t>
+          <t>남서측 폭원 3.92~4.50m 요코하마시 공도(下川井第402号線, 일부 계단) 및 서측 폭원 4.00~5.50m 요코하마시 공도(下川井第398号線) 접도</t>
         </is>
       </c>
       <c r="H395" s="0" t="inlineStr">
@@ -40502,7 +40596,7 @@
     <row r="396">
       <c r="A396" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B396" s="0" t="inlineStr">
@@ -40532,7 +40626,7 @@
       </c>
       <c r="G396" s="0" t="inlineStr">
         <is>
-          <t>사도(386番3, 128㎡) 지분 1/2 보유(비과세) + 『토지공동사용협정서(386番6+386番7 폭 4m 무상·자동승계)』 원본 완비</t>
+          <t>없음 (등기부 지번 231-1 요코하마시 소유 공중용도로 및 인정노선도 100% 공도 검증완료)</t>
         </is>
       </c>
       <c r="H396" s="0" t="inlineStr">
@@ -40559,7 +40653,7 @@
     <row r="397">
       <c r="A397" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B397" s="0" t="inlineStr">
@@ -40589,7 +40683,7 @@
       </c>
       <c r="G397" s="0" t="inlineStr">
         <is>
-          <t>목조 아연도금강판지붕 지상 3층건 (2×4공법·열화대책등급 3급)</t>
+          <t>목조 준내화구조 지상 2층건 (RC베타기초+7.00m 기초파일 / 설계·건설 열화대책등급 3급)</t>
         </is>
       </c>
       <c r="H397" s="0" t="inlineStr">
@@ -40616,7 +40710,7 @@
     <row r="398">
       <c r="A398" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B398" s="0" t="inlineStr">
@@ -40646,7 +40740,7 @@
       </c>
       <c r="G398" s="0" t="inlineStr">
         <is>
-          <t>2021年2月25日新築 (令和3年2月 / 築5.6年)</t>
+          <t>2026년 12월 말 준공 예정 (2027년 1월 인도 예정)</t>
         </is>
       </c>
       <c r="H398" s="0" t="inlineStr">
@@ -40673,7 +40767,7 @@
     <row r="399">
       <c r="A399" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B399" s="0" t="inlineStr">
@@ -40703,7 +40797,7 @@
       </c>
       <c r="G399" s="0" t="inlineStr">
         <is>
-          <t>353.55</t>
+          <t>242.07</t>
         </is>
       </c>
       <c r="H399" s="0" t="inlineStr">
@@ -40730,7 +40824,7 @@
     <row r="400">
       <c r="A400" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B400" s="0" t="inlineStr">
@@ -40760,7 +40854,7 @@
       </c>
       <c r="G400" s="0" t="inlineStr">
         <is>
-          <t>유 (건축도면·배치도·평면도·입면도 일식 확인완료)</t>
+          <t>유 (제26UDI1K건00271호, R8.6.18 교부 확인필증 사본 완비)</t>
         </is>
       </c>
       <c r="H400" s="0" t="inlineStr">
@@ -40785,66 +40879,66 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="3" t="inlineStr">
-        <is>
-          <t>livre-fine-misato-chuo</t>
-        </is>
-      </c>
-      <c r="B401" s="3" t="inlineStr">
+      <c r="A401" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B401" s="0" t="inlineStr">
         <is>
           <t>CHK_15</t>
         </is>
       </c>
-      <c r="C401" s="3" t="inlineStr">
+      <c r="C401" s="0" t="inlineStr">
         <is>
           <t>3.건물/적법</t>
         </is>
       </c>
-      <c r="D401" s="3" t="inlineStr">
+      <c r="D401" s="0" t="inlineStr">
         <is>
           <t>has_inspection_cert</t>
         </is>
       </c>
-      <c r="E401" s="3" t="inlineStr">
+      <c r="E401" s="0" t="inlineStr">
         <is>
           <t>준공검사필증(検査済証) 취득 여부</t>
         </is>
       </c>
-      <c r="F401" s="3" t="inlineStr">
+      <c r="F401" s="0" t="inlineStr">
         <is>
           <t>検査済証の有無</t>
         </is>
       </c>
-      <c r="G401" s="3" t="inlineStr">
-        <is>
-          <t>유 (2021.2 신축·오릭스/au지분은행 열화3급 35년 융자평가 확인완료 / 원본사본 징구예정)</t>
-        </is>
-      </c>
-      <c r="H401" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I401" s="3" t="inlineStr">
-        <is>
-          <t>오릭스·au지분 35년 융자평가 확인 (원본사본 미징구)</t>
-        </is>
-      </c>
-      <c r="J401" s="3" t="inlineStr">
-        <is>
-          <t>준공검사필증(検査済証) 및 열화대책등급 3급 주택성능평가서 사본, 프로판가스(LPG) 무상대여 약정서 유무 공유 요청</t>
-        </is>
-      </c>
-      <c r="K401" s="3" t="inlineStr">
-        <is>
-          <t>検査済証および劣化対策等級3級の住宅性能評価書の写し、ならびにプロパンガス無償貸与契約の有無のご確認</t>
+      <c r="G401" s="0" t="inlineStr">
+        <is>
+          <t>신축 건축중 (2026.12 말 준공 시 건축물 검사필증 및 건설주택성능평가서 열화3급 교부 예정 / 단, 기존 옹벽은 검사필증 없음)</t>
+        </is>
+      </c>
+      <c r="H401" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I401" s="0" t="inlineStr">
+        <is>
+          <t>검사필증/대장</t>
+        </is>
+      </c>
+      <c r="J401" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K401" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B402" s="0" t="inlineStr">
@@ -40874,7 +40968,7 @@
       </c>
       <c r="G402" s="0" t="inlineStr">
         <is>
-          <t>축 5.6년 신축급으로 과거 대규모 수선이력 및 침수이력 없음 (중개사·매도자 공식 확인완료)</t>
+          <t>신축 완공 예정 (RC베타기초+7.0m 기초파일 시공 / 동·북측 기존 간지블록 옹벽 98.84㎡는 보강계획 없음 확인)</t>
         </is>
       </c>
       <c r="H402" s="0" t="inlineStr">
@@ -40899,66 +40993,66 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="0" t="inlineStr">
-        <is>
-          <t>livre-fine-misato-chuo</t>
-        </is>
-      </c>
-      <c r="B403" s="0" t="inlineStr">
+      <c r="A403" s="3" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
         <is>
           <t>CHK_17</t>
         </is>
       </c>
-      <c r="C403" s="0" t="inlineStr">
+      <c r="C403" s="3" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D403" s="0" t="inlineStr">
+      <c r="D403" s="3" t="inlineStr">
         <is>
           <t>full_annual_income_yen</t>
         </is>
       </c>
-      <c r="E403" s="0" t="inlineStr">
+      <c r="E403" s="3" t="inlineStr">
         <is>
           <t>호실별 월 차임 및 공익비 내역</t>
         </is>
       </c>
-      <c r="F403" s="0" t="inlineStr">
+      <c r="F403" s="3" t="inlineStr">
         <is>
           <t>各戸賃料・共益費一覧</t>
         </is>
       </c>
-      <c r="G403" s="0" t="inlineStr">
-        <is>
-          <t>9876000</t>
-        </is>
-      </c>
-      <c r="H403" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I403" s="0" t="inlineStr">
-        <is>
-          <t>렌트롤</t>
-        </is>
-      </c>
-      <c r="J403" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K403" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G403" s="3" t="inlineStr">
+        <is>
+          <t>8760000</t>
+        </is>
+      </c>
+      <c r="H403" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I403" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J403" s="3" t="inlineStr">
+        <is>
+          <t>최신 렌트롤(호실별 차임·공익비·보증금 명시본) 요청</t>
+        </is>
+      </c>
+      <c r="K403" s="3" t="inlineStr">
+        <is>
+          <t>最新のレントロール（各戸賃料・共益費・敷金明細）のご共有</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B404" s="0" t="inlineStr">
@@ -40988,7 +41082,7 @@
       </c>
       <c r="G404" s="0" t="inlineStr">
         <is>
-          <t>총 11세대 (1F: 1LDK×3실 [37.26~43.32㎡] / 2~3F: 1K×8실 [28.41~29.81㎡])</t>
+          <t>전 9세대 1LDK(26.89㎡: LDK8.0+양실5.5, 2인입주 가능) + 5세대(105, 201~204호) 로프트 4.82㎡</t>
         </is>
       </c>
       <c r="H404" s="0" t="inlineStr">
@@ -41015,7 +41109,7 @@
     <row r="405">
       <c r="A405" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B405" s="0" t="inlineStr">
@@ -41045,7 +41139,7 @@
       </c>
       <c r="G405" s="0" t="inlineStr">
         <is>
-          <t>전수/일부 확인 (12실)</t>
+          <t>전수/일부 확인 (9실)</t>
         </is>
       </c>
       <c r="H405" s="0" t="inlineStr">
@@ -41070,66 +41164,66 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="3" t="inlineStr">
-        <is>
-          <t>livre-fine-misato-chuo</t>
-        </is>
-      </c>
-      <c r="B406" s="3" t="inlineStr">
+      <c r="A406" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B406" s="0" t="inlineStr">
         <is>
           <t>CHK_20</t>
         </is>
       </c>
-      <c r="C406" s="3" t="inlineStr">
+      <c r="C406" s="0" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D406" s="3" t="inlineStr">
+      <c r="D406" s="0" t="inlineStr">
         <is>
           <t>rent_roll_tenant_types</t>
         </is>
       </c>
-      <c r="E406" s="3" t="inlineStr">
+      <c r="E406" s="0" t="inlineStr">
         <is>
           <t>호실별 입주자 속성(법인/직장인/학생/보증회사)</t>
         </is>
       </c>
-      <c r="F406" s="3" t="inlineStr">
+      <c r="F406" s="0" t="inlineStr">
         <is>
           <t>入居者属性・保証会社加入状況</t>
         </is>
       </c>
-      <c r="G406" s="3" t="inlineStr">
-        <is>
-          <t>속성 확인 (12실)</t>
-        </is>
-      </c>
-      <c r="H406" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I406" s="3" t="inlineStr">
-        <is>
-          <t>공식 렌트롤 (敷金·RC 『調査中』 표기)</t>
-        </is>
-      </c>
-      <c r="J406" s="3" t="inlineStr">
-        <is>
-          <t>렌트롤상 『調査中』인 전 호실 시키킨(敷金)·RC 확정 금액 및 서브리스 해지 승계 무보증 6세대의 최근 6개월 수납 내역 확인</t>
-        </is>
-      </c>
-      <c r="K406" s="3" t="inlineStr">
-        <is>
-          <t>レントロール上「調査中」となっている各戸敷金・RCの確定額、および保証会社無しの6戸における直近6ヶ月の家賃入金状況のご確認</t>
+      <c r="G406" s="0" t="inlineStr">
+        <is>
+          <t>속성 확인 (9실)</t>
+        </is>
+      </c>
+      <c r="H406" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I406" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤 상세판</t>
+        </is>
+      </c>
+      <c r="J406" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K406" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B407" s="0" t="inlineStr">
@@ -41159,7 +41253,7 @@
       </c>
       <c r="G407" s="0" t="inlineStr">
         <is>
-          <t>부지 내 평면 주차장 4구획 (각 월 5,500엔 × 4대 = 월 22,000엔 만차)</t>
+          <t>없음 (전면도로 계단 직전까지 차량 접근 가능)</t>
         </is>
       </c>
       <c r="H407" s="0" t="inlineStr">
@@ -41186,7 +41280,7 @@
     <row r="408">
       <c r="A408" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B408" s="0" t="inlineStr">
@@ -41216,7 +41310,7 @@
       </c>
       <c r="G408" s="0" t="inlineStr">
         <is>
-          <t>1698233</t>
+          <t>1130040</t>
         </is>
       </c>
       <c r="H408" s="0" t="inlineStr">
@@ -41243,7 +41337,7 @@
     <row r="409">
       <c r="A409" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B409" s="0" t="inlineStr">
@@ -41273,7 +41367,7 @@
       </c>
       <c r="G409" s="0" t="inlineStr">
         <is>
-          <t>현재 정화조(월 1만엔) → R8 본하수 접속공사(세금포함 약 180만엔+부담금 시청조사중) 후 직결</t>
+          <t>공영수도·공공하수·무료WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정 확인완료)</t>
         </is>
       </c>
       <c r="H409" s="0" t="inlineStr">
@@ -41300,7 +41394,7 @@
     <row r="410">
       <c r="A410" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B410" s="0" t="inlineStr">
@@ -41330,7 +41424,7 @@
       </c>
       <c r="G410" s="0" t="inlineStr">
         <is>
-          <t>27054052</t>
+          <t>36985271</t>
         </is>
       </c>
       <c r="H410" s="0" t="inlineStr">
@@ -41355,66 +41449,66 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="0" t="inlineStr">
-        <is>
-          <t>livre-fine-misato-chuo</t>
-        </is>
-      </c>
-      <c r="B411" s="0" t="inlineStr">
+      <c r="A411" s="3" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="inlineStr">
         <is>
           <t>CHK_25</t>
         </is>
       </c>
-      <c r="C411" s="0" t="inlineStr">
+      <c r="C411" s="3" t="inlineStr">
         <is>
           <t>5.경비/세금</t>
         </is>
       </c>
-      <c r="D411" s="0" t="inlineStr">
+      <c r="D411" s="3" t="inlineStr">
         <is>
           <t>fixed_tax_bldg_eval_yen</t>
         </is>
       </c>
-      <c r="E411" s="0" t="inlineStr">
+      <c r="E411" s="3" t="inlineStr">
         <is>
           <t>고정자산세 건물 과세평가액</t>
         </is>
       </c>
-      <c r="F411" s="0" t="inlineStr">
+      <c r="F411" s="3" t="inlineStr">
         <is>
           <t>固定資産税評価額（建物）</t>
         </is>
       </c>
-      <c r="G411" s="0" t="inlineStr">
-        <is>
-          <t>27152612</t>
-        </is>
-      </c>
-      <c r="H411" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I411" s="0" t="inlineStr">
-        <is>
-          <t>과세명세서</t>
-        </is>
-      </c>
-      <c r="J411" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K411" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="G411" s="3" t="inlineStr">
+        <is>
+          <t>26627700</t>
+        </is>
+      </c>
+      <c r="H411" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I411" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J411" s="3" t="inlineStr">
+        <is>
+          <t>최신 연도 고정자산세·도시계획세 과세명세서(건물 평가액) 사본 요청</t>
+        </is>
+      </c>
+      <c r="K411" s="3" t="inlineStr">
+        <is>
+          <t>最新年度の固定資産税・都市計画税課税明細書（建物評価額）の写しのご共有</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B412" s="0" t="inlineStr">
@@ -41444,7 +41538,7 @@
       </c>
       <c r="G412" s="0" t="inlineStr">
         <is>
-          <t>474,221엔 (레이와 8년도 과세원장 확정: 토지 76,651 + 건물 397,570)</t>
+          <t>573,283엔 (R8 토지 공과증명서 주택특례 약 12.3만 엔 + 건물 오카다상 확인 약 45만 엔 추정)</t>
         </is>
       </c>
       <c r="H412" s="0" t="inlineStr">
@@ -41471,7 +41565,7 @@
     <row r="413">
       <c r="A413" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B413" s="0" t="inlineStr">
@@ -41501,7 +41595,7 @@
       </c>
       <c r="G413" s="0" t="inlineStr">
         <is>
-          <t>[등기부 원장 확인완료]</t>
+          <t>검증완료: 야오키상사 주식회사(ヤオキ商事株式会社, R7.6.27 매매 취득, 149-3 및 231-102 2필지 일치)</t>
         </is>
       </c>
       <c r="H413" s="0" t="inlineStr">
@@ -41528,7 +41622,7 @@
     <row r="414">
       <c r="A414" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B414" s="0" t="inlineStr">
@@ -41558,7 +41652,7 @@
       </c>
       <c r="G414" s="0" t="inlineStr">
         <is>
-          <t>[등기부 원장 확인완료]</t>
+          <t>검증완료: S32/S57 개인취득 → H9 상속 → H15 매매 → R7.6.27 야오키상사(주) 신축분양 목적 매입</t>
         </is>
       </c>
       <c r="H414" s="0" t="inlineStr">
@@ -41585,7 +41679,7 @@
     <row r="415">
       <c r="A415" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B415" s="0" t="inlineStr">
@@ -41615,7 +41709,7 @@
       </c>
       <c r="G415" s="0" t="inlineStr">
         <is>
-          <t>[등기부 원장 확인완료]</t>
+          <t>검증완료: R7.6.27 카와사키신용금고(登戸支店) 채권액 7,700만 엔·금리 연 3.050% 공동담보 근저당 설정 (인도 시 말소 조건)</t>
         </is>
       </c>
       <c r="H415" s="0" t="inlineStr">
@@ -41640,66 +41734,66 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="3" t="inlineStr">
-        <is>
-          <t>livre-fine-misato-chuo</t>
-        </is>
-      </c>
-      <c r="B416" s="3" t="inlineStr">
+      <c r="A416" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B416" s="0" t="inlineStr">
         <is>
           <t>CHK_30</t>
         </is>
       </c>
-      <c r="C416" s="3" t="inlineStr">
+      <c r="C416" s="0" t="inlineStr">
         <is>
           <t>7.외부실사</t>
         </is>
       </c>
-      <c r="D416" s="3" t="inlineStr">
+      <c r="D416" s="0" t="inlineStr">
         <is>
           <t>roadside_price_sqm</t>
         </is>
       </c>
-      <c r="E416" s="3" t="inlineStr">
+      <c r="E416" s="0" t="inlineStr">
         <is>
           <t>국세청 상속세 노선가(路線価) 조회</t>
         </is>
       </c>
-      <c r="F416" s="3" t="inlineStr">
+      <c r="F416" s="0" t="inlineStr">
         <is>
           <t>相続税路線価</t>
         </is>
       </c>
-      <c r="G416" s="3" t="inlineStr">
-        <is>
-          <t>125000</t>
-        </is>
-      </c>
-      <c r="H416" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I416" s="3" t="inlineStr">
-        <is>
-          <t>공시지가 기반 노선가 산정 / 본하수 부담금 시청 조사중</t>
-        </is>
-      </c>
-      <c r="J416" s="3" t="inlineStr">
-        <is>
-          <t>현재 미사토시청에 조사 중인 하수도 수익자부담금 확정액 및 본하수 접속공사(세금포함 약 180만 엔) 상세 견적서 공유 요청</t>
-        </is>
-      </c>
-      <c r="K416" s="3" t="inlineStr">
-        <is>
-          <t>現在三郷市役所にて調査中の下水道受益者負担金の確定額、および本下水接続工事（税込約180万円）の詳細見積書のご共有</t>
+      <c r="G416" s="0" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
+      </c>
+      <c r="H416" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I416" s="0" t="inlineStr">
+        <is>
+          <t>국세청 노선가도</t>
+        </is>
+      </c>
+      <c r="J416" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K416" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B417" s="0" t="inlineStr">
@@ -41729,7 +41823,7 @@
       </c>
       <c r="G417" s="0" t="inlineStr">
         <is>
-          <t>도보 15~16분 (구글맵 실측 검증완료)</t>
+          <t>실측 도보 10분 (구글맵 및 오카다상 현장 확인완료)</t>
         </is>
       </c>
       <c r="H417" s="0" t="inlineStr">
@@ -41756,7 +41850,7 @@
     <row r="418">
       <c r="A418" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B418" s="0" t="inlineStr">
@@ -41786,7 +41880,7 @@
       </c>
       <c r="G418" s="0" t="inlineStr">
         <is>
-          <t>고저차 없는 평탄지 (다이니오바가와 교량 횡단·1층 바닥 GL+450mm 확인)</t>
+          <t>사사노다이 상점가 경유 후 남서측 전면도로(下川井第402号線) 진입부에 계단 구간 및 부지 고저차(4.0~4.69m) 존재 확인완료</t>
         </is>
       </c>
       <c r="H418" s="0" t="inlineStr">
@@ -41813,7 +41907,7 @@
     <row r="419">
       <c r="A419" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B419" s="0" t="inlineStr">
@@ -41843,7 +41937,7 @@
       </c>
       <c r="G419" s="0" t="inlineStr">
         <is>
-          <t>하저드맵 3.0~5.0m 구역이나 『과거 집중호우 포함 침수 피해 이력 전무』 매도자 공식 확인완료</t>
+          <t>고대(高台) 입지로 홍수·내수 침수 해저드 해당 없음 (교차검증 완료)</t>
         </is>
       </c>
       <c r="H419" s="0" t="inlineStr">
@@ -41870,7 +41964,7 @@
     <row r="420">
       <c r="A420" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B420" s="0" t="inlineStr">
@@ -41900,7 +41994,7 @@
       </c>
       <c r="G420" s="0" t="inlineStr">
         <is>
-          <t>해당 없음 (완전 평탄지·토사재해 경계구역 외)</t>
+          <t>부지 북서측 모서리 옹벽 부분(가측량도 약 4.69㎡)이 토사재해경계구역(옐로우존/잠정 레드존 경계)에 일부 저촉 확인완료 (건물 본체는 2m 이격되어 구역 외)</t>
         </is>
       </c>
       <c r="H420" s="0" t="inlineStr">
@@ -41927,7 +42021,7 @@
     <row r="421">
       <c r="A421" s="0" t="inlineStr">
         <is>
-          <t>livre-fine-misato-chuo</t>
+          <t>mitsukyo-1ap</t>
         </is>
       </c>
       <c r="B421" s="0" t="inlineStr">
@@ -41957,7 +42051,7 @@
       </c>
       <c r="G421" s="0" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>30~45일 (REINS 근린 성약 50건 및 일 피오레 사사노다이 교차검증 완료)</t>
         </is>
       </c>
       <c r="H421" s="0" t="inlineStr">
@@ -50234,7 +50328,7 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>mitsukyo-1ap</t>
+          <t>livre-fine-misato-chuo</t>
         </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
@@ -50244,605 +50338,15 @@
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>물건 기본 개요 (Property Overview)</t>
+          <t>에그제큐티브 서머리 (Executive Summary)</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>物件基本概要 (Property Overview)</t>
+          <t>エグゼクティブサマリー (Executive Summary)</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr">
-        <is>
-          <t>![마이소쿠 및 건축확인필증](./assets/maisoku_overview.png)
-| 항목 | 세부 내용 (등기부·공과증명서·확정측량도·실시설계도 교차 검증 완료) |
-| :--- | :--- |
-| **물건명** | **미츠쿄 1AP 사사노다이 신축 아파트 (三ツ境1AP 新築一棟アパート)** |
-| **소재지 (지번 / 주거표시)** | **[지번]** 神奈川県横浜市旭区笹野台二丁目149番3、231番102&lt;br&gt;**[주거표시]** **神奈川県横浜市旭区笹野台2丁目19-5** (`35°28'12.8"N 139°30'02.6"E`) |
-| **교통 (구글맵 실측)** | 소테츠 본선(相鉄本線, 급행·통근급행 정차) **「미츠쿄(三ツ境)」역 도보 10분** (마이소쿠 표기 도보 7분 / 구글맵 실측 약 720m·도보 10분, 전면도로 진입부 계단 구간 존재) |
-| **매매가격 (호가)** | **1억 3,470만 엔 (¥134,700,000)** ※ 건물 소비세 포함 |
-| **목표 매수가 (네고 타겟)** | **1억 2,300만 ~ 1억 2,500만 엔** (표면 6.87~7.12% / 실질 NOI 5.50~5.59% — 미검사 옹벽 및 임대료 상단 리스크 반영) |
-| **토지 면적 (공부 vs 실측)** | **[등기부 지적]** 합계 **399.56㎡** (`149番3`: 386.62㎡ + `231番102`: 12.94㎡)&lt;br&gt;**[확정측량 실측]** 합계 **397.71㎡ (120.30평)** = **유효택지 397.42㎡ (120.22평)** (`149-3`: 384.52㎡ + `231-102`: 12.90㎡) + 잠정 후퇴부분(SB) **0.29㎡** |
-| **토지 권리 / 지목** | 소유권 (所有権) / 택지 (宅地) |
-| **도시계획 / 용도지역** | 시가지화구역 / **제1종 저층주거전용지역 (第一種低層住居専用地域)** · 제1종 고도지구 |
-| **건폐율 / 용적률** | 법정 건폐율 **40%** (실적 **39.57%** = 건축면적 `157.24㎡`) / 법정 용적률 **80%** (실적 **60.92%** = 연면적 `242.07㎡`) |
-| **접도 조건 (100% 공도 확인)** | **남서측 폭원 3.92~4.50m 요코하마시 공도(`下川井第402号線`, 지번 `231-1` 요코하마시 소유 공중용도로)** 및 **서측 폭원 4.00~5.50m 요코하마시 공도(`下川井第398号線`)** 접도&lt;br&gt;※ **사도 부담 없음(100% 공도)**, 단 `下川井第402号線`의 부지 전면 구간은 **계단(階段) 도로**임 (차량은 계단 직전까지 동·서 양방향 접근 가능) |
-| **건물 구조 / 규모** | **목조(木造) 준내화구조(準耐火構造) 지상 2층건** · 공동주택 **총 9세대** (1층 5세대, 2층 4세대)&lt;br&gt;**[기초 공법]** RC 베타기초(`地耐力 20kN/㎡`) + **길이 `7.00m` 기초 파일(`杭長 7.00m`)** (요코하마시 벼랑조례 안식각 45° 대응) |
-| **건물 면적 및 평면 구성** | **연면적 242.07㎡ (73.22평)** (1층 `134.48㎡`, 2층 `107.59㎡` / 최고높이 `8.10m`, 처마높이 `5.87m`)&lt;br&gt;• **전 9세대 `1LDK (26.89㎡)`**: `LDK 8.0帖(12.98㎡) + 洋室 5.5帖(8.94㎡)` (전 실 2인 입주 가능 설계)&lt;br&gt;• **5세대(`105, 201, 202, 203, 204호`) 대형 로프트(`4.82㎡ / 3.0帖`) 부착** (로프트 포함 실사용 면적 **31.71㎡**!) |
-| **건축확인번호 / 성능평가** | **제26UDI1K건00271호** (令和8年6月18日 교부 / UDI확인검사(주), 설계: 일급건축사사무소 스페이스팩토리ING)&lt;br&gt;• **설계주택성능평가서 『열화대책등급 3급(劣化対策等級3級)』 취득 완료**&lt;br&gt;• **건설주택성능평가서 『열화대책등급 3급』 준공 시 취득 예정** (최장 30~35년 장기 융자 적격) |
-| **준공 및 인도 예정일** | **2026년 12월 말 준공 예정 / 2027년 1월 인도 예정** (기존 11월 말에서 약 1개월 순연 확인) |
-| **매도자 / 프로젝트 금융** | **야오키상사 주식회사 (ヤオキ商事株式会社)** (카와사키시 타카츠구 소재 업력 50년 디벨로퍼)&lt;br&gt;• **[을구 근저당권]** 2025년 6월 27일 매수 시 **카와사키신용금고(川崎信用金庫 登戸支店) 차입금 7,700만 엔, 금리 연 3.050%** 근저당 설정 확인 |
-| **설비 및 특기사항** | 공영수도 · 공공하수 · **도시가스** · **전 세대 무료 WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정)** · 독립세면대 · UB1014 · IH 2구 시스템키친(W1200) · 실내물건걸이 · 1층 수동셔터 |
----</t>
-        </is>
-      </c>
-      <c r="F102" s="0" t="inlineStr">
-        <is>
-          <t>![マイソクおよび建築確認済証](./assets/maisoku_overview.png)
-| 項目 | 詳細内容（登記簿・公課証明書・確定測量図・実施設計図 照合済） |
-| :--- | :--- |
-| **物件名** | **三ツ境1AP 新築一棟アパート** |
-| **所在地（地番 / 住居表示）** | **【地番】** 神奈川県横浜市旭区笹野台二丁目149番3、231番102&lt;br&gt;**【住居表示】** **神奈川県横浜市旭区笹野台2丁目19-5** (`35°28'12.8"N 139°30'02.6"E`) |
-| **交通（Googleマップ実測）** | 相鉄本線（急行・通勤急行停車）**「三ツ境」駅 徒歩10分**（マイソク表記：徒歩7分 / Googleマップ実測：約720m・徒歩10分、前面道路に階段区間あり） |
-| **売出価格** | **1億3,470万円 (¥134,700,000)** ※建物消費税込み |
-| **目標買付価格（指値）** | **1億2,300万 〜 1億2,500万円**（表面6.87〜7.12% / 実質NOI利回り5.50〜5.59% — 無検査擁壁・賃料上限リスク反映） |
-| **土地面積（公簿 vs 実測）** | **【登記簿地積】** 合計 **399.56㎡**（`149番3`: 386.62㎡ ＋ `231番102`: 12.94㎡）&lt;br&gt;**【確定測量実測】** 合計 **397.71㎡ (120.30坪)** ＝ **有効宅地 397.42㎡ (120.22坪)** ＋ 暫定後退部分(SB) **0.29㎡** |
-| **土地権利 / 地目** | 所有権 / 宅地 |
-| **都市計画 / 用途地域** | 市街化区域 / **第一種低層住居専用地域** ・ 第1種高度地区 |
-| **建蔽率 / 容積率** | 法定建蔽率 **40%**（実績 **39.57%** ＝ 建築面積 `157.24㎡`） / 法定容積率 **80%**（実績 **60.92%** ＝ 延床面積 `242.07㎡`） |
-| **接道条件（100%公道確定）** | **南西側 幅員3.92〜4.50m 横浜市公道（`下川井第402号線`、地番`231-1` 横浜市所有 公衆用道路）** および **西側 幅員4.00〜5.50m 横浜市公道（`下川井第398号線`）** 接道&lt;br&gt;※**私道負担なし（100%公道）**。ただし`下川井第402号線`の敷地前面区間は**階段道路**（車両は階段手前まで東西双方から進入可） |
-| **建物構造 / 規模** | **木造 準耐火構造 地上2階建** ・ 共同住宅 **全9戸**（1階5戸、2階4戸）&lt;br&gt;**【基礎工法】** RCベタ基礎（`地耐力 20kN/㎡`）＋ **長さ`7.00m`基礎杭（`杭長 7.00m`）**（横浜市がけ条例 安息角45°対応） |
-| **建物面積および間取り** | **延床面積 242.07㎡ (73.22坪)**（1階 `134.48㎡`、2階 `107.59㎡` / 最高高さ `8.10m`、最高軒高 `5.87m`）&lt;br&gt;• **全9戸 `1LDK (26.89㎡)`**：`LDK 8.0帖(12.98㎡) ＋ 洋室 5.5帖(8.94㎡)`（全室2人入居可能）&lt;br&gt;• **5戸（`105, 201, 202, 203, 204号室`）に大型ロフト（`4.82㎡ / 3.0帖`）付帯**（ロフト含む実使用面積 **31.71㎡**！） |
-| **建築確認番号 / 性能評価** | **第26UDI1K建00271号**（令和8年6月18日交付 / ユーディーアイ確認検査(株)、設計：一級建築士事務所スペースファクトリーING）&lt;br&gt;• **設計住宅性能評価書『劣化対策等級3級』取得済**&lt;br&gt;• **建設住宅性能評価書『劣化対策等級3級』竣工時取得予定**（最長30〜35年長期融資適格） |
-| **竣工および引渡予定日** | **2026年12月末竣工予定 / 2027年1月引渡予定**（当初11月末より約1ヶ月順延） |
-| **売主 / プロジェクト融資** | **ヤオキ商事株式会社**（川崎市高津区坂戸3-2-1 KSP西414）&lt;br&gt;• **【乙区抵当権】** 令和7年6月27日取得時に**川崎信用金庫（登戸支店）債権額7,700万円・利息年3.050%**の共同抵当権設定を確認 |
-| **設備および特記事項** | 公営水道 ・ 公共下水 ・ **都市ガス** ・ **全戸無料WiFi（オーナー負担：月額7,920円[税込]・10年縛り）** ・ 独立洗面台 ・ UB1014 ・ IH2口システムキッチン(W1200) ・ 室内物干 ・ 1階手動シャッター |
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B103" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="inlineStr">
-        <is>
-          <t>등기부등본(甲区·乙区)·공과증명서·건축도면 포렌식 실사 (Forensic Due Diligence)</t>
-        </is>
-      </c>
-      <c r="D103" s="0" t="inlineStr">
-        <is>
-          <t>登記簿謄本・公課証明書・実施設計図フォレンジック調査 (Forensic Due Diligence)</t>
-        </is>
-      </c>
-      <c r="E103" s="0" t="inlineStr">
-        <is>
-          <t>### 2.1 등기부등본(全部事項証明書) 권리관계 및 매도자 조달금리 분석
-`05_touhon_sokuryo_kouka.pdf` (1~6페이지) 등기부등본 전수 조사 결과:
-1. **갑구 (소유권 이력)**:
-   - 구 소유자 개인(1957년/1982년 취득 → 1997년 상속 → 2003년 매매)을 거쳐, **令和7年(2025년) 6월 27일 현 매도자인 『야오키상사 주식회사(ヤオキ商事株式会社)』가 매매로 소유권을 취득**했습니다.
-   - `149番3` 토지는 1983년(소화 58년) 지적 정정을 통해 `384.06㎡ → 386.62㎡`로 등기되었으며, `231番102` 토지는 `12.94㎡`로 등기되어 공부상 합계 면적은 **`399.56㎡`**입니다.
-2. **을구 (담보권 및 매도자 협상 레버리지 핵심 단서)**:
-   - 현 매도자(야오키상사)는 2025년 6월 27일 토지 취득과 동시에 **카와사키신용금고(川崎信用金庫 登戸支店)**로부터 **채권액 7,700만 엔(이자 연 3.050%, 손해금 연 14.50%)의 공동담보 저당권(목록 (イ)第5921号)**을 설정했습니다.
-   - **💡 협상 전략적 시사점**: 중개사(오카다상)에 따르면 매도자는 *"초기에는 가격 네고에 잘 응하지 않으나 안 팔리면 시기를 보아 가격을 내리는 스탠스"*입니다. 그러나 매도자는 현재 **연 3.05%라는 높은 프로젝트 조달금리(월 이자만 약 19.6만 엔)**를 부담하고 있으며, 공정이 당초 11월 말에서 **12월 말 준공(2027년 1월 인도)**으로 지연되었습니다. 따라서 연말 준공 시점까지 매수자가 확정되지 않을 경우 매도자의 이자 및 재고 보유 압박이 급증하므로, 이를 지렛대로 **1억 2,300만 ~ 1억 2,500만 엔** 선의 조건부 매수의향서(LOI) 타진이 매우 유효합니다.
----
-### 2.2 🚨 최대 핵심 리스크: 기존 간지블록 옹벽(98.84㎡) &amp; 토사재해경계구역(Yellow/Red Zone) 정밀 진단
-![현황평면도 및 옹벽면적 산출도](./assets/retaining_wall_calc.png)
-![단면도 및 7.0m 기초파일 안식각 45도 시공도](./assets/section_piles.png)
-![가나가와현 토사재해 하저드맵](./assets/hazard_landslide.jpg)
-이번 2차 실사 자료(`현황평면도`, `옹벽면적도`, `실시설계 단면도`, `가측량도`, `오카다상 질의응답`)를 통해 밝혀진 가장 중요한 물리적·법적 팩트입니다.
-| 검증 항목 | 실사 확인 결과 (Hard Fact) | 투자 리스크 및 대응 방안 |
-| :--- | :--- | :--- |
-| **1. 지형 및 옹벽 규모** | • 부지 레벨(GL `12.14~12.26m`)이 북측·동측·남측 인접지 및 도로(`7.63~8.37m`)보다 **약 4.0m ~ 4.69m 높은 고대(高台) 지형**&lt;br&gt;• 옹벽 면적 산출도(`擁壁面積`)상 **총 7개 구간(①~⑦), 합계 면적 `98.84㎡`** (구간별 높이 `1.162m ~ 3.488m`, 단면도상 최대 단차 `4.690m`) | 높이 2m를 초과하는 대형 간지블록(間知ブロック) 옹벽이 부지 3면을 둘러싸고 있음 |
-| **2. 옹벽 소유권 및 유지관리 책임** | • **동측(東) 및 북측(北) 옹벽**: **매도자 소유 → 매수자(투자자)에게 소유권 및 유지보수 책임 승계!**&lt;br&gt;• **서측(西) 옹벽**: **서측 인접지 소유자 소유** (고저차 큰 노후 옹벽) | 동·북측 옹벽의 향후 균열·배부름 보수비 및 지진·호우로 인한 붕괴 시 인접 저지대 가옥에 대한 **민법상 공작물 배상책임(민법 717조)**이 매수자에게 귀속됨 |
-| **3. 축조시기 및 검사필증 유무** | • **축조시기 불명(築造時期不明) / 택지조성 및 공작물 검사필증 없음(検査済証なし)**&lt;br&gt;• 매도자 측의 **보강 공사나 재축조 계획 없음(補強・造り直し予定なし)**&lt;br&gt;• 단, 실시설계 배치도(`配置図`)상 일급건축사 육안 점검 결과 **『間知ブロック 亀裂、たわみ無し 水抜き穴あり 安全支障無し(균열·배부름 없음, 배수공 있음, 안전지장 없음)』**으로 기재됨 | 검사필증이 없는 구형 옹벽이므로, 향후 재건축 시에는 옹벽 재축조(수천만 엔 소요) 또는 벼랑조례 파일 재시공이 필요하며, 일부 보수적 시중은행(1금융권)에서 담보 평가를 감액할 수 있음 |
-| **4. 벼랑조례(がけ条例) 및 신축 허가 통과 비결** | • 요코하마시 건축기준조례 제4조(벼랑 부근의 건축물) 및 **『横浜市がけ関係小規模建築物技術指針』**에 의거하여, **옹벽 하단으로부터 45° 안식각(`安息角 45°`) 아래의 견고한 지지층까지 길이 `7.00m`의 기초 파일(`杭長 7.00m`)을 관입**하고 RC 베타기초를 얹는 공법을 채택!&lt;br&gt;• 또한 성토규제법(`盛土規制法`) 저촉을 피하기 위해 **성토 없음(`盛土無し`)**으로 설계하여 건축확인(`제26UDI1K건00271호`)을 적법 취득함 | **건물 본체의 구조적 안전성(침하·전도 방지)은 7.0m 파일 시공으로 확보**되었음. 준공 시 **『7.0m 파일 시공 보고서 및 지반조사 보고서』** 사본을 반드시 수령해야 함 |
-| **5. 토사재해경계구역 저촉 여부** | • 가나가와현 토사재해 포털 및 가측량도(`06_karisoku.pdf`) 확인 결과, **부지 북서측(北西) 모서리 옹벽 부분(약 4.69㎡ 삼각형 구간)이 토사재해경계구역(옐로우존 / 잠정 레드존 경계)에 일부 걸쳐 있음(かすっている)**을 매도자가 공식 확인함&lt;br&gt;• 건물 본체는 북측·서측 경계로부터 `2.00m` 이상 이격되어 있어 건물 자체는 구역 밖에 위치함 | 중요사항설명서(重説)에 토사재해경계구역(일부) 해당 사실이 기재되며, 화재·지진보험 가입 시 **시설소유관리자 배상책임보험(옹벽 손해 담보)** 특약을 반드시 추가해야 함 |
----
-### 2.3 전면도로 공도(公道) 확인 및 계단 접근로 분석
-![요코하마시 인정노선도 하카와이 제402호선](./assets/road_map_402.png)
-![현황평면도 계단 및 레벨 상세](./assets/survey_topography.png)
-1. **사도(私道) 리스크 완전 해소**:
-   - 1차 분석 당시 마이소쿠에 `公道・私道`로 혼재 표기되어 있었으나, 이번에 수령한 **도로 등기부(`笹野台二丁目231番1`, 지목: 공중용도로, 소유자: `横浜市`)** 및 **요코하마시 인정노선도(`下川井第402号線` 폭원 4.00~4.50m, `下川井第398号線` 폭원 4.00~5.50m)**를 통해 **부지에 접한 모든 도로가 100% 요코하마시 공도(公道)**임이 확정되었습니다. 따라서 사도 지분 누락이나 굴착 승낙 거부 리스크는 **0%**입니다.
-2. **전면도로 계단(階段) 구간 유의사항**:
-   - 현황평면도(`survey_topography.png`)에서 확인되듯, 남서측 전면도로(`下川井第402号線`)의 부지 접도 구간 중 서측 절반은 **경사 계단(階段)**으로 되어 있습니다.
-   - 자동차는 계단 아래쪽(남동측)과 계단 위쪽(`下川井第398号線`, 북서측) 양방향에서 계단 바로 앞까지 진입할 수 있으나, 부지 내 주차장은 없으며 이사 차량 정차 시 계단 앞 도로를 이용해야 합니다.
----
-### 2.4 건축 상세 도면(`1階・2階 平面詳細図`) 분석: 전 세대 `1LDK(26.89㎡)` + 5세대 `로프트(4.82㎡)`
-![1층 평면상세도](./assets/plan_1f.png)
-![2층 평면상세도](./assets/plan_2f.png)
-실시설계 평면상세도(`02_plans_elevations.pdf` 2~3p)를 통해 확인된 본 건물의 상품 스펙은 일반 신축 목조 원룸(14~18㎡)을 압도합니다:
-- **전 9세대 `1LDK` (`26.89㎡`) 표준 구성**:
-  - 전 호실이 **`LDK 8.0帖 (12.98㎡) + 洋室 5.5帖 (8.94㎡)`**으로 분리된 정통 **컴팩트 1LDK** 구조입니다(소방법상 각 실 수용인원 2명, 1인 가구 재택근무자 및 **신혼·동거 커플 2인 입주 가능**!).
-- **5개 호실(`105호`, `201~204호`) 대형 로프트(`4.82㎡`) 서비스 면적**:
-  - 2층 4개 호실(`201~204호`)뿐 아니라 **1층 동측 끝단 단층 구조인 `105호`에도 `2.65m × 1.82m = 4.82㎡ (약 3.0帖, 천장고 1.4m 이하, 이동식 사다리)` 로프트가 시공**됩니다!
-  - 즉, 9세대 중 5세대는 **실사용 면적이 `26.89㎡ + 4.82㎡ = 31.71㎡ (약 9.6평)`**에 달합니다.
-- **내화·차음·설비 사양**:
-  - **준내화구조(`準耐火構造`)**: 벽체 석고보드 `12.5+12.5mm` 양면 시공, 세대 간 차음 경계벽 천장 속까지 밀실 시공(`界壁遮音 天井裏まで達しせめる` + 글라스울 충전).
-  - **설비**: 시스템키친 `W1200` (`IH 2구 콘로 200V 3000W`), 유닛배스 `UB 1014`, 독립 세면화장대, 실내 빨래걸이(`室内物干`), 1층 전 창문 **방범용 수동 셔터(`手動シャッター`)**, 전 세대 **무료 WiFi**.
----</t>
-        </is>
-      </c>
-      <c r="F103" s="0" t="inlineStr">
-        <is>
-          <t>### 2.1 登記簿謄本（甲区・乙区）の権利関係および売主の借入条件分析
-1. **甲区（所有権履歴）**：
-   - 旧個人所有者（昭和32年/57年取得→平成9年相続→平成15年売買）を経て、**令和7年（2025年）6月27日に現売主である『ヤオキ商事株式会社』が売買により取得**しています。
-2. **乙区（抵当権および指値交渉の強力なレバレッジ）**：
-   - 売主（ヤオキ商事）は令和7年6月27日付で**川崎信用金庫（登戸支店）より債権額7,700万円・金利年3.050%**のプロジェクト融資を借り入れています。
-   - **💡 指値交渉への示唆**：仲介担当者（岡田様）によれば「売主は当初は値下げに応じないが、売れなければ時期を見て価格を下げるスタンス」とのことですが、**年3.050%という高金利（月間利息だけで約19.6万円）**を負担しながら竣工が**2026年12月末（引渡2027年1月）**へ遅れているため、竣工前後のタイミングで**1億2,300万〜1億2,500万円**の指値買付を入れる交渉戦略が極めて有効です。
----
-### 2.2 🚨 最大の重要リスク：既存間知ブロック擁壁（98.84㎡）＆土砂災害警戒区域の精密診断
-![擁壁面積算出図](./assets/retaining_wall_calc.png)
-![断面図および7.0m基礎杭・安息角45度施工図](./assets/section_piles.png)
-![神奈川県土砂災害ハザードマップ](./assets/hazard_landslide.jpg)
-| 検証項目 | 実査確認結果 (Hard Fact) | 投資リスクおよび対策 |
-| :--- | :--- | :--- |
-| **1. 高低差および擁壁規模** | • 敷地レベル（GL `12.14〜12.26m`）が北・東・南側の隣地および道路（`7.63〜8.37m`）より**約4.0m〜4.69m高い高台**&lt;br&gt;• 擁壁面積図（`擁壁面積`）上、**全7区間（①〜⑦）合計 `98.84㎡`**（高さ`1.162m〜3.488m`、断面図上の最大高低差`4.690m`） | 高さ2m超の間知ブロック擁壁が敷地を取り囲んでいる |
-| **2. 擁壁の所有権と管理責任** | • **東側および北側擁壁**：**売主所有 → 買主（投資家）へ所有権・維持管理責任が承継！**&lt;br&gt;• **西側擁壁**：**西側隣地所有者の所有**（高低差が大きい古い擁壁） | 東・北側擁壁の将来の補修費用および万一の崩壊時の**工作物責任（民法717条）**は買主負担となる |
-| **3. 築造時期・検査済証の有無** | • **築造時期不明・検査済証なし・補強や造り直し予定なし**&lt;br&gt;• ただし配置図（`配置図`）上の一級建築士による現況確認では**『間知ブロック 亀裂、たわみ無し 水抜き穴あり 安全支障無し』**と明記 | 検査済証のない既存擁壁のため、一部の都市銀行・地方銀行では担保評価が厳しくなる可能性あり |
-| **4. 横浜市がけ条例のクリア手法** | • **『横浜市がけ関係小規模建築物技術指針』**に基づき、**擁壁下端から安息角45°（`安息角 45°`）より深い支持層まで長さ`7.00m`の基礎杭（`杭長 7.00m`）を打設**してRCベタ基礎を支持！&lt;br&gt;• 盛土規制法に抵触しないよう**盛土無し（`盛土無し`）**で設計し、建築確認済証（`第26UDI1K建00271号`）を適法に取得 | **建物本体の構造安全性（沈下・倒壊防止）は7.0m杭によって確保済**。引渡時に必ず**『杭施工報告書・地盤調査報告書』**を受領すること |
-| **5. 土砂災害警戒区域への抵触** | • 神奈川県土砂災害情報ポータルおよび仮測量図（`06_karisoku.pdf`）にて、**敷地北西角の擁壁部分（約4.69㎡）が土砂災害警戒区域（イエローゾーン／暫定レッドゾーン境界）にかすっている**ことを売主も認識&lt;br&gt;• 建物本体は北・西境界から`2.00m`離隔しており区域外 | 重要事項説明書に記載される事項であり、火災・地震保険加入時に**施設所有者賠償責任特約**を必ず付帯すること |
----
-### 2.3 前面道路の公道確定および階段アプローチの確認
-![横浜市認定路線図 下川井第402号線](./assets/road_map_402.png)
-![現況平面図 階段および高低差詳細](./assets/survey_topography.png)
-- **100%横浜市公道と確定**：道路登記簿（`笹野台二丁目231番1`、所有者：`横浜市`）および認定路線図（`下川井第402号線`・`下川井第398号線`）により、**接道する道路はすべて横浜市所有の公道**であることが証明されました。私道トラブルのリスクはありません。
-- **階段部分の注意点**：南西側`下川井第402号線`の敷地前面西側半分は**階段**となっています。車両は階段の上側・下側の両方から階段手前まで進入可能です。
----
-### 2.4 実施設計平面詳細図：全9戸`1LDK（26.89㎡）`＋5戸`ロフト（4.82㎡）`
-![1階平面詳細図](./assets/plan_1f.png)
-![2階平面詳細図](./assets/plan_2f.png)
-- **全9戸が`1LDK（26.89㎡）`**：全戸が`LDK 8.0帖（12.98㎡）＋洋室 5.5帖（8.94㎡）`の1LDK設計（消防法上の収容人員：各室2名、カップル・新婚の2人入居に対応）。
-- **5戸（`105号室`、`201〜204号室`）に`4.82㎡（約3.0帖）`ロフト付帯**：2階4戸だけでなく**1階東端の下屋部分である`105号室`にも`4.82㎡`のロフトが設置**されており、ロフト含む実使用面積は**31.71㎡**に達します。
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B104" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C104" s="0" t="inlineStr">
-        <is>
-          <t>토지·건물 적산가격(積算価格) 및 령화 8년도 공과증명서(公課証明書) 정밀 평가</t>
-        </is>
-      </c>
-      <c r="D104" s="0" t="inlineStr">
-        <is>
-          <t>令和8年度 公課証明書（固定資産税評価額）および積算価格検証</t>
-        </is>
-      </c>
-      <c r="E104" s="0" t="inlineStr">
-        <is>
-          <t>### 3.1 령화 8년도 고정자산세·도시계획세 공과증명서(令和8年度 公課証明書) 실측 내역
-요코하마시 아사히구청장이 2026년 4월 30일 발급한 공식 공과증명서(`05_touhon_sokuryo_kouka.pdf` 12~13p) 수치입니다:
-| 필지 (지번) | 등기 지적 | 확정측량 유효면적 | R8 고정자산세 평가액 (評価額) | ㎡당 평가단가 | R8 나대지 기준 세액 (고정+도계) | 신축 완공 후 소규모 주택용지 특례(1/6·1/3) 적용 시 연간 세액 |
-| :--- | :---: | :---: | :---: | :---: | :---: | :---: |
-| **笹野台二丁目149番3** | 386.62㎡ | 384.52㎡ (+SB 0.20㎡) | **¥35,787,480** | ¥92,565/㎡ | ¥397,154 | **약 ¥119,291** |
-| **笹野台二丁目231番102** | 12.94㎡ | 12.90㎡ (+SB 0.09㎡) | **¥1,197,791** | ¥92,565/㎡ | ¥13,291 | **약 ¥3,992** |
-| **토지 2필지 합계** | **399.56㎡** | **397.42㎡ (120.22평)** | **¥36,985,271** | **¥92,565/㎡** | ¥410,445 | **약 ¥123,283 / 년 (약 12.3만 엔)** |
-| **신축 건물 (추정)** | - | **242.07㎡ (73.22평)** | **약 ¥26,627,700** (11만/㎡) | ¥110,000/㎡ | - | **약 ¥450,000 / 년 (첫 3년은 감면으로 약 25만 엔)** |
-| **토지 + 건물 총계** | - | - | **¥63,612,971 (약 6,361만 엔)** | - | - | **정상화 시 약 ¥573,283 / 년 (약 57.3만 엔)** |
-&gt; [!TIP] **공과증명서 핵심 인사이트 (보유세 절감 vs 고저차 보정)**
-&gt; - **왜 토지 고정자산세 평가액이 `3,698.5만 엔(92,565엔/㎡)`인가?**: 사사노다이 2초메 표준 주택가의 상속세 노선가는 약 `190,000円/㎡`(공시지가 약 `240,000円/㎡`)이나, 본 필지는 **남서측 계단 도로 접도 및 4m 이상 고저차(옹벽)**가 존재하여 요코하마시 세무과에서 **지형·접도 감가 보정**을 대폭 반영했기 때문입니다.
-&gt; - **투자자 실익**: 토지 공적 평가액이 낮게 책정된 덕분에, 9세대 공동주택 준공 후 **소규모 주택용지 특례(200㎡×9호=1,800㎡까지 고정자산세 1/6, 도시계획세 1/3 감면)**가 적용되면 **120.3평 대토지의 연간 보유세가 불과 `12.3만 엔` 수준**으로 낮아져 현금흐름(NOI)을 강력하게 방어합니다!
----
-### 3.2 적산가격(積算価格) 3대 시나리오 및 지형 보정(がけ地補正) 비교
-일반 평탄지 노선가(`190,000円/㎡`) 기준 적산과, 금융기관이 고저차·계단 접도 감가(**-20%, 실효 노선가 `152,000円/㎡`**)를 적용한 보수적 담보 적산을 병행 산출했습니다.
-| 평가 시나리오 | 토지 평가 기준 | 토지 적산가 | 건물 단가 (`242.07㎡`×22/22년) | 건물 적산가 | **합계 적산가격** | **호가(1.347억) 대비 비율** |
-| :--- | :--- | :---: | :---: | :---: | :---: | :---: |
-| **① 은행 엄격 담보 기준 (지형감가 -20%)** | 유효 `397.42㎡` × 15.2만 엔/㎡ | ¥60,407,840 | 150,000엔/㎡ | ¥36,310,500 | **¥96,718,340** | **71.80%** |
-| **② 금융기관 표준 기준 (노선가 원안+15만)** | 유효 `397.42㎡` × 19.0만 엔/㎡ | ¥75,509,800 | 150,000엔/㎡ | ¥36,310,500 | **¥111,820,300** | **83.01%** |
-| **③ 국세청 표준 적산 (노선가 원안+18만)** | 유효 `397.42㎡` × 19.0만 엔/㎡ | ¥75,509,800 | 180,000엔/㎡ | ¥43,572,600 | **¥119,082,400** | **88.41%** |
-| **④ 실세 공시지가 + 신축 재조달원가(22만)** | 유효 `397.42㎡` × 24.0만 엔/㎡ | ¥95,380,800 | 220,000엔/㎡ | ¥53,255,400 | **¥148,636,200** | **110.35%** |
-- 지형 감가(-20%)를 엄격히 반영하더라도 적산비율이 **71.80%(9,672만 엔)**를 상회하며, 표준 노선가 기준으로는 **83.01% ~ 88.41%**에 달합니다.
----</t>
-        </is>
-      </c>
-      <c r="F104" s="0" t="inlineStr">
-        <is>
-          <t>### 3.1 令和8年度 固定資産・都市計画税 公課証明書（実測値）
-| 筆（地番） | 登記地積 | 確定測量有効面積 | R8 固定資産税評価額 | ㎡単価 | R8 更地時点年税額 | 完成後・小規模住宅用地特例（1/6・1/3）適用時の年税額 |
-| :--- | :---: | :---: | :---: | :---: | :---: | :---: |
-| **笹野台二丁目149番3** | 386.62㎡ | 384.52㎡ (+SB 0.20㎡) | **¥35,787,480** | ¥92,565/㎡ | ¥397,154 | **約 ¥119,291** |
-| **笹野台二丁目231番102** | 12.94㎡ | 12.90㎡ (+SB 0.09㎡) | **¥1,197,791** | ¥92,565/㎡ | ¥13,291 | **約 ¥3,992** |
-| **土地2筆 合計** | **399.56㎡** | **397.42㎡ (120.22坪)** | **¥36,985,271** | **¥92,565/㎡** | ¥410,445 | **約 ¥123,283 / 年（約12.3万円）** |
-| **新築建物（見込）** | - | **242.07㎡ (73.22坪)** | **約 ¥26,627,700** (11万/㎡) | ¥110,000/㎡ | - | **約 ¥450,000 / 年（当初3年間は軽減で約25万円）** |
-| **土地＋建物 総計** | - | - | **¥63,612,971（約6,361万円）** | - | - | **通常時 約 ¥573,283 / 年（約57.3万円）** |
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C105" s="0" t="inlineStr">
-        <is>
-          <t>렌트롤 포렌식 및 REINS 근린 성약 50건(`03_comps_1R_1K.pdf`) 비교 검증</t>
-        </is>
-      </c>
-      <c r="D105" s="0" t="inlineStr">
-        <is>
-          <t>レントロールおよびREINS近隣成約事例50件（`03_comps_1R_1K.pdf`）比較検証</t>
-        </is>
-      </c>
-      <c r="E105" s="0" t="inlineStr">
-        <is>
-          <t>### 4.1 호실별 상정 렌트롤 및 평면 스펙 (전 9세대)
-| 호실 | 층수 / 위치 | 상세 평면 (전유면적 + 로프트) | 상정 월임대료 (공익비·무료WiFi 포함) | 연간 임대료 | 전유 ㎡당 단가 | 로프트 포함(31.71㎡) 실효 ㎡단가 | 비고 |
-| :---: | :---: | :--- | :---: | :---: | :---: | :---: | :--- |
-| **101호** | 1F 서측 각실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥80,000** | ¥960,000 | 2,975엔/㎡ | 2,975엔/㎡ | 1층 남서·북서 2면 채광 각실, 수동셔터 |
-| **102호** | 1F 중실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥78,000** | ¥936,000 | 2,901엔/㎡ | 2,901엔/㎡ | 7만 엔대(7.8만) 진입 호실, 수동셔터 |
-| **103호** | 1F 중실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥78,000** | ¥936,000 | 2,901엔/㎡ | 2,901엔/㎡ | 7만 엔대(7.8만) 진입 호실, 수동셔터 |
-| **104호** | 1F 중실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥78,000** | ¥936,000 | 2,901엔/㎡ | 2,901엔/㎡ | 7만 엔대(7.8만) 진입 호실, 수동셔터 |
-| **105호** | 1F 동측 단층 각실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥80,000** | ¥960,000 | 2,975엔/㎡ | **2,523엔/㎡** | **1층 유일 로프트 부착** + 2면 채광 각실! |
-| **201호** | 2F 서측 각실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥85,000** | ¥1,020,000 | 3,161엔/㎡ | **2,681엔/㎡** | 최상층 각실 + 4.82㎡ 대형 로프트 |
-| **202호** | 2F 중실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥83,000** | ¥996,000 | 3,087엔/㎡ | **2,617엔/㎡** | 최상층 중실 + 4.82㎡ 대형 로프트 |
-| **203호** | 2F 중실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥83,000** | ¥996,000 | 3,087엔/㎡ | **2,617엔/㎡** | 최상층 중실 + 4.82㎡ 대형 로프트 |
-| **204호** | 2F 동측 각실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥85,000** | ¥1,020,000 | 3,161엔/㎡ | **2,681엔/㎡** | 최상층 각실 + 4.82㎡ 대형 로프트 |
-| **합계** | **전 9세대** | **전유 242.07㎡ (+로프트 24.10㎡ = 266.17㎡)** | **¥730,000 / 월** | **¥8,760,000 / 년** | **3,016엔/㎡** | **2,743엔/㎡** | **전 실 2인 입주 가능 1LDK + 무료 WiFi** |
----
-### 4.2 REINS 근린 성약 사례 50건(`03_comps_1R_1K.pdf`) 대조 및 임대료 적정성 진단
-오카다상이 제공한 미츠쿄·키보가오카·세야역 주변 24~31㎡ 성약 데이터 50건 중 주요 경쟁 신축·축천 사례와의 비교표입니다:
-| 비교 물건명 (소재지) | 최기역 / 도보 | 준공연월 | 면적 / 타입 | 성약 임대료 + 관리비 = **월 총액** | ㎡당 단가 | 본건(`미츠쿄 1AP`) 대비 시사점 |
-| :--- | :--- | :---: | :---: | :---: | :---: | :--- |
-| **가칭 요코하마 미츠쿄 AP** (미츠쿄) | 미츠쿄역 **도보 3분** | **2025.06 (신축)** | 25.05㎡ / 1K | 6.9~7.4만 + 4,000엔 = **7.3~7.8만 엔** | 2,914~3,114엔 | 역 도보 3분 신축 1K가 7.3~7.8만 엔에 성약됨 (예금 1개월) |
-| **KOMA 미츠쿄** (사사노다이 1초메) | 미츠쿄역 **도보 7분** | 2021.12 (축4년) | 24.77㎡ / 1K | 6.6~6.7만 + 3,000엔 = **6.9~7.0만 엔** | 2,786~2,826엔 | 동일 사사노다이 권역 1K(축4년) 실세는 약 7.0만 엔 수준 |
-| **그린힐 키보가오카** (나카키보가오카) | 키보가오카역 **도보 4분** | **2025.07 (신축)** | 26.45㎡ / 1R | 7.3만 + 3,000엔 = **7.6만 엔** | 2,873엔 | 인접역 도보 4분 26.45㎡ 신축이 총 7.6만 엔에 성약 |
-| **트윈즈 요코하마 세야** (세야) | 세야역 **도보 5~6분** | **2024.10 (신축)** | 28.66㎡ / 1K | 8.0만 + 5,000엔 = **8.5만 엔** | 2,966엔 | 28.6㎡급 대형 평면은 8.5만 엔 성약 가능 입증 |
-| **일 피오레 사사노다이** (사사노다이 1초메) | 미츠쿄역 **도보 5분** | 2015.02 (축11년) | 28.56㎡ / 1K | 7.2만 + 3,000엔 = **7.5만 엔** | 2,626엔 | 사사노다이 28㎡급 기축은 평균 DOM 30일 내 안정 소화 |
-| **⭐ 본건: 미츠쿄 1AP** (사사노다이 2-19-5) | 미츠쿄역 **도보 10분** | **2026.12 (신축)** | **26.89㎡ `1LDK` (+로프트 4.82㎡×5실)** | **1F 7.8~8.0만 / 2F 8.3~8.5만** (무료WiFi 포함) | **3,016엔** (로프트 포함 2,743엔) | **1K가 아닌 『1LDK(2인 입주 가능)+로프트+무료WiFi』로 차별화했으나, 도보 10분 기준 지역 시세 최상단(Upper Bound)에 위치!** |
-&gt; [!IMPORTANT] **임대료 스트레스 테스트 결론**
-&gt; - 미츠쿄역 도보 3분 신축 1K(25㎡)가 7.3~7.8만 엔에 성약된 점을 감안할 때, 도보 10분(계단 접근)인 본건이 **1층 7.8~8.0만 엔 / 2층 8.3~8.5만 엔**을 달성하려면 반드시 포털(SUUMO/HOME'S) 등록 시 **『1K가 아닌 1LDK(2인 입주 가능) + 3조 대형 로프트 + 무료 WiFi 완비』** 카테고리로 노출시켜 **커플·동거 수요 및 광폭 재택근무 수요**를 타겟팅해야 합니다.
-&gt; - 만약 1인 가구 위주로 모집하여 **임대료를 -5% 인하(1층 7.4~7.6만 엔, 2층 7.9~8.1만 엔 → 연수입 832.2만 엔)**하더라도, **만실 NOI는 645.4만 엔(Cap 4.79%), 30년 융자 시 DSCR 1.22배, 세전 CF +116.7만 엔/년**으로 여전히 안정적인 흑자가 유지됩니다.
----</t>
-        </is>
-      </c>
-      <c r="F105" s="0" t="inlineStr">
-        <is>
-          <t>### 4.1 REINS成約事例50件との比較
-- **仮称 横浜三ツ境アパート**（2025年6月新築、三ツ境駅**徒歩3分**、25.05㎡・1K）：成約賃料 **6.9〜7.4万円＋共益費4,000円＝計7.3〜7.8万円**（礼金1ヶ月）。
-- **KOMA三ツ境**（2021年12月築、笹野台1丁目、三ツ境駅**徒歩7分**、24.77㎡・1K）：成約賃料 **6.6〜6.7万円＋共益費3,000円＝計6.9〜7.0万円**。
-- **グリーンヒル希望ヶ丘**（2025年7月新築、希望ヶ丘駅**徒歩4分**、26.45㎡・1R）：成約賃料 **7.3万円＋共益費3,000円＝計7.6万円**。
-- **ツインズ横浜瀬谷**（2024年10月新築、瀬谷駅**徒歩5〜6分**、28.66㎡・1K）：成約賃料 **8.0万円＋共益費5,000円＝計8.5万円**。
-- **診断結論**：本物件（徒歩10分・階段あり）の想定賃料（1階7.8〜8.0万円、2階8.3〜8.5万円、無料WiFi込）は近隣相場の**上限（アッパーバウンド）**に位置します。ただし近隣事例がすべて「1R/1K」であるのに対し、本物件は**『1LDK（26.89㎡・2人入居可）＋大型ロフト4.82㎡（5戸）＋無料WiFi』**という明確な差別化要素を持つため、募集時は必ず「1LDK・二人入居可」としてポータル掲載する必要があります。万一賃料を**-5%引き下げ（年収入832.2万円）**た場合でも、**満室NOI 645.4万円・DSCR 1.22倍・税引前CF +116.7万円/年**と黒字を維持できます。
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B106" s="0" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C106" s="0" t="inlineStr">
-        <is>
-          <t>운영경비(OPEX) 정규화 및 현금흐름·손익분기(BEP) 모델링</t>
-        </is>
-      </c>
-      <c r="D106" s="0" t="inlineStr">
-        <is>
-          <t>モアビズ4期 決算書着地シミュレーション（令和8年度公課証明書反映）</t>
-        </is>
-      </c>
-      <c r="E106" s="0" t="inlineStr">
-        <is>
-          <t>### 5.1 실질 운영경비(OPEX) 명세 (오카다상 확인 확정치 반영)
-| 경비 항목 | 연간 금액 (엔) |GPI 대비 비율 | 산출 근거 (2차 실사 검증 완료) |
-| :--- | :---: | :---: | :--- |
-| **1. 고정자산세·도시계획세 (보유세)** | **¥573,000** | 6.54% | **[토지]** R8 공과증명서(평가액 3,698.5만) 주택용지 특례(1/6·1/3) 적용 **¥123,000**&lt;br&gt;**[건물]** 오카다상 확인 목조 신축 평가 기준 **¥450,000** (※ 초기 3년간은 신축 감면으로 합계 약 37만 엔/년) |
-| **2. PM 임대관리 위탁수수료** | **¥438,000** | 5.00% | 만실 임대수입(876만 엔)의 5.0% |
-| **3. 전 세대 무료 WiFi 런닝코스트** | **¥95,040** | 1.08% | **오카다상 확인 확정치: 월 7,920엔(세금포함) × 12개월 (※ 10년 약정 조건)** |
-| **4. 공용부 전기·수도·정기청소·소방** | **¥144,000** | 1.64% | 공용등 전기·공용 수도·월 2회 순회청소 및 소방점검 (월 1.2만 엔) |
-| **5. 화재·지진보험 + 옹벽 배상책임특약** | **¥90,000** | 1.03% | **목조 준내화구조(`準耐火構造`) 할인 적용** + 시설소유관리자 배상책임특약(옹벽) |
-| **6. 퇴거 원상복구비·장기수선·옹벽점검 적립** | **¥550,000** | 6.28% | 퇴거 원상복구·AD 충당(연 25만) + 외벽·지붕·옹벽 배수공 유지적립(연 30만) |
-| **실질 운영경비 (Normalized OPEX) 합계** | **¥1,890,040** | **21.58%** | **만실 순영업소득 (NOI) = ¥6,869,960 (≒ ¥6,870,000, 실질 Cap Rate 5.10%)** |
----
-### 5.2 금융 조달 및 매수가·임대료별 스트레스 테스트 (LTV 85%, 금리 2.3%, 기간 30년)
-설계·건설 주택성능평가 **열화대책등급 3급** 취득에 따른 **30년 원리금균등상환(금리 2.3%)** 기준 시나리오 비교입니다:
-| 구분 시나리오 | 매매가격 | 대출금액 (85%) | 연간 총수입 (GPI) | 실질 NOI | 연간 원리금 (ADS) | **만실 세전 CF** | **DSCR** | **손익분기 가동률 (허용공실)** |
-| :--- | :---: | :---: | :---: | :---: | :---: | :---: | :---: | :---: |
-| **① 기본안 (호가 1.347억 · 상정임대료)** | ¥134,700,000 | ¥114,495,000 | ¥8,760,000 | ¥6,870,000 | ¥5,287,219 | **+¥1,582,781** | **1.30배** | **81.93% (1.63실 / 9실)** |
-| **② 임대료 -5% 보수안 (호가 1.347억)** | ¥134,700,000 | ¥114,495,000 | ¥8,322,000 | ¥6,453,900 | ¥5,287,219 | **+¥1,166,681** | **1.22배** | **85.98% (1.26실 / 9실)** |
-| **③ 1차 네고안 (1.27억 · 상정임대료)** | ¥127,000,000 | ¥107,950,000 | ¥8,760,000 | ¥6,870,000 | ¥4,984,980 | **+¥1,885,020** | **1.38배** | **78.48% (1.94실 / 9실)** |
-| **④ 공격적 네고안 (1.24억 · 상정임대료)** | **¥124,000,000** | **¥105,400,000** | ¥8,760,000 | ¥6,870,000 | **¥4,867,225** | **+¥2,002,775** | **1.41배** | **77.14% (2.06실 / 9실)** |
-| **⑤ 공격적 네고 + 임대료 -5% 복합안** | **¥124,000,000** | **¥105,400,000** | ¥8,322,000 | ¥6,453,900 | **¥4,867,225** | **+¥1,586,675** | **1.33배** | **80.96% (1.71실 / 9실)** |
----</t>
-        </is>
-      </c>
-      <c r="F106" s="0" t="inlineStr">
-        <is>
-          <t>| 決算書コア指標 | 本物件単体 (稼働93%) | モアビズ4期現在 | **取得後決算着地** | **1.24億指値時単体** | 財務貢献度および判定 |
-| :--- | :---: | :---: | :---: | :---: | :--- |
-| **固定資産税評価額 (土地+建物)** | **3,699万 + 2,663万 = 6,361万** | 7,186万 + 4,191万 = 1.138億 | **1.088億 + 6,853万 = 1.774億** | **6,361万円** | R8公課証明書実測値を100%反映 |
-| **1. 帳簿上税引前当期純利益** | **+¥2,955,270** | +¥3,722,450 | **+¥6,677,720 (+79.4%)** | **+¥3,384,100** | **法人黒字規模 +79.4%大幅増益！** |
-| **2. 税引前手残りCF (利回り)** | **+¥1,246,795 (0.93%)** | +¥1,741,901 (0.65%) | **+¥2,988,696 (+71.6%)** | **+¥1,666,550 (1.34%)** | 満室時は単体税引前CF +158.3万円 |
-| **3. 推定法人税額 (25%)** | ▲¥738,818 | ▲¥930,613 | **▲¥1,669,430** | ▲¥846,025 | 22年新築減価償却(年251万)節税 |
-| **4. 税引後手残りCF (利回り)** | **+¥507,977 (0.38%)** | +¥811,289 (0.30%) | **+¥1,319,266 (+62.6%)** | **+¥820,525 (0.66%)** | 法人税引後キャッシュ +62.6%純増 |
-| **5. 債務償還年数 (C)** | **24.2年** (融資30年以内) | 24.1年 | **24.2年** | **20.5年** | **単体24.2年 $\ll$ 融資30.0年 ゴールデンクロス！** |
-| **6. 利子支払倍率 (ICR)** | **1.54倍** | 0.90倍 | **1.05倍 (+0.15倍)** | **1.77倍** | **法人統合ICR 1.0倍突破達成！** |
-| **7. 負債返済余裕率 (DSCR)** | **1.53倍 (満室1.30倍)** | 1.50倍 | **1.51倍 (+0.01倍)** | **1.66倍 (満室1.41倍)** | **法人統合DSCR上昇に貢献！** |
-| **8. 固定資産税評価LTV** | **218.01%** (単純合算180.0%) | 261.08% | **245.45% (▲15.63%p改善)** | **200.69%** | **公課証明書基準でも法人LTV ▲15.63%p改善！** |
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B107" s="0" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C107" s="0" t="inlineStr">
-        <is>
-          <t>모아비즈 4기 결산서 디자인형 적합성 분석 (Moabiz Corporate Landing)</t>
-        </is>
-      </c>
-      <c r="D107" s="0" t="inlineStr">
-        <is>
-          <t>総合スコアカード（19.5 / 30点：条件付検討）および最終提言</t>
-        </is>
-      </c>
-      <c r="E107" s="0" t="inlineStr">
-        <is>
-          <t>**령화 8년도 공과증명서 실측 토지 평가액(`36,985,271円`)** 및 **건물 평가액(`26,627,700円`)**을 반영한 모아비즈 4기 결산서 착지 시뮬레이션(가동률 93% 보수적 기준, 결산 경비율 19.8%, 건물 비중 41%, 감가상각 22년 = 연 251.0만 엔) 결과입니다:
-| 핵심 결산 지표 | 본 물건 단품 (93% 가동) | 모아비즈 4기 현재 | **편입 후 결산서 착지** | **1.24억 네고 시 단품** | 재무적 기여도 및 판정 |
-| :--- | :---: | :---: | :---: | :---: | :--- |
-| **자산 총액 / 총 차입금** | 1.347억 / 1.145억 | 2.675억 / 2.407억 | **4.022억 / 3.552억** | 1.240억 / 1.054억 | 우량 신축 자산 편입으로 외형 확대 |
-| **고정자산세 평가액 (토지+건물)** | **3,699만 + 2,663만 = 6,361만** | 7,186만 + 4,191만 = 1.138억 | **1.088억 + 6,853만 = 1.774억** | **6,361만 엔** | R8 공과증명서 실측치 100% 반영 |
-| **1. 장부상 세전 당기순이익** | **+¥2,955,270** | +¥3,722,450 | **+¥6,677,720 (+79.4%)** | **+¥3,384,100** | **법인 흑자 규모 +79.4% 점프업!** |
-| **2. 세전 잔여 CF (수익률)** | **+¥1,246,795 (0.93%)** | +¥1,741,901 (0.65%) | **+¥2,988,696 (+71.6%)** | **+¥1,666,550 (1.34%)** | 만실 시 단품 세전 CF +158.3만 엔 |
-| **3. 추정 법인세액 (25%)** | ▲¥738,818 | ▲¥930,613 | **▲¥1,669,430** | ▲¥846,025 | 22년 신축 감가상각(연 251만) 절세 |
-| **4. 세후 잔여 CF (수익률)** | **+¥507,977 (0.38%)** | +¥811,289 (0.30%) | **+¥1,319,266 (+62.6%)** | **+¥820,525 (0.66%)** | 법인 세후 잉여현금 +62.6% 순증 |
-| **5. 채무상환연수 (C)** | **24.2년** (융자 30년 이내) | 24.1년 | **24.2년** | **20.5년** | **단품 24.2년 $\ll$ 융자 30.0년 골든크로스!** |
-| **6. 이자보상배율 (ICR)** | **1.54배** | 0.90배 | **1.05배 (+0.15배)** | **1.77배** | **법인 통합 ICR 1.0배 돌파 달성!** |
-| **7. 부채상환여유율 (DSCR)** | **1.53배 (만실 1.30배)** | 1.50배 | **1.51배 (+0.01배)** | **1.66배 (만실 1.41배)** | **법인 통합 DSCR 상승 기여!** |
-| **8. 고정자산세 평가 LTV** | **218.01%** (단순합산 180.0%) | 261.08% | **245.45% (▲15.63%p 개선)** | **200.69%** | **공과증명서 실측 기준으로도 법인 LTV ▲15.63%p 개선!** |
----</t>
-        </is>
-      </c>
-      <c r="F107" s="0" t="inlineStr">
-        <is>
-          <t>| 評価項目 (配点) | 1次スコア | **2次確定スコア** | 評価根拠 |
-| :--- | :---: | :---: | :--- |
-| **1. 価格・積算価値 (5点)** | 4.0 | **3.5 / 5.0** | 120.3坪宅地（路線価標準積算88.4%）は優秀だが、公課証明書評価額（3,698.5万円）に表れた高低差・階段接道補正（-20%補正時71.8%）を反映 |
-| **2. 賃貸需要・立地 (5点)** | 4.0 | **3.5 / 5.0** | 全9戸`1LDK(26.89㎡)＋ロフト(5戸)`は強いが、実測徒歩10分および前面道路の階段区間を反映 |
-| **3. 賃料競争力 (5点)** | 3.5 | **3.0 / 5.0** | 近隣成約50件（徒歩3分新築1Kが7.3〜7.8万円）対比で想定賃料（7.8〜8.5万円）は上限水準のため、1LDK訴求と初期ADバッファが必要 |
-| **4. 出口戦略 (5点)** | 4.0 | **3.5 / 5.0** | 120.3坪の土地と劣化3級は強みだが、東・北側の無検査既存擁壁（98.84㎡）が将来売却時の審査ハードルとなり得る |
-| **5. CF・DSCR (5点)** | 3.5 | **3.5 / 5.0** | 劣化3級30年融資でDSCR 1.30倍、土地固都税特例（年12.3万円）により実質NOI 687万円（Cap 5.10%）を堅守 |
-| **6. 法的・物理的安定性 (5点)** | 3.5 | **2.5 / 5.0** | 前面道路100%公道確定および7.0m基礎杭（安息角45°対応）はプラスだが、**東・北側既存擁壁（98.84㎡）検査済証なし＆北西角の土砂災害警戒区域抵触**により減点 |
-| **合計スコア・総合判定** | 22.5 / 30 | **19.5 / 30点** | **【条件付検討（擁壁・賃料リスクを織り込んだ1.23〜1.25億円への指値交渉必須）】** |</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B108" s="0" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C108" s="0" t="inlineStr">
-        <is>
-          <t>35개 표준 실사 체크리스트 완결성 감사 (Data Collection Audit: 94.3% 완료!)</t>
-        </is>
-      </c>
-      <c r="D108" s="0" t="inlineStr">
-        <is>
-          <t>35標準DDチェックリスト監査 (94.3%完了)</t>
-        </is>
-      </c>
-      <c r="E108" s="0" t="inlineStr">
-        <is>
-          <t>이번 `20260925 OKD 三ツ境` 구글 드라이브 폴더(11개 파일) 수령을 통해 **35개 표준 실사 항목 중 33개(94.3%)가 공식 공부 및 설계도서로 검증 완료(`VERIFIED`/`COLLECTED`)**되었습니다!
-| 구분 | 1차 분석 시점 (마이소쿠 단독) | **2차 업데이트 현시점 (드라이브 11종 반영 후)** | 주요 해결 내역 |
-| :--- | :---: | :---: | :--- |
-| **수집/검증 완료 (`VERIFIED`/`COLLECTED`)** | 23건 | **33건 (94.3%)** | ✅ 등기부등본(갑·을구), ✅ R8 공과증명서(토지 2필지), ✅ 확정측량도, ✅ 현황평면도·옹벽면적도, ✅ 실시설계도(배치·평면·입면·단면·7m파일), ✅ 인정노선도 2종, ✅ 토사재해 하저드맵, ✅ REINS 성약 50건, ✅ 무료 WiFi 비용(월 7,920엔)·준공일(12월 말) |
-| **추정 적용 (`ESTIMATED`)** | 9건 | **2건 (5.7%)** | ⚠️ 건물분 고정자산세 본칙 세액(준공 후 가옥조사 시 확정, 현재 오카다상 45만 엔 추정), ⚠️ 초기 리싱 달성 임대료 및 실제 AD(광고료)개월 수 |
-| **미수집 (`MISSING`)** | 3건 | **0건 (0.0%)** | (미수집 항목 전수 해소 완료!) |
----</t>
-        </is>
-      </c>
-      <c r="F108" s="0" t="inlineStr">
-        <is>
-          <t>이번 `20260925 OKD 三ツ境` 구글 드라이브 폴더(11개 파일) 수령을 통해 **35개 표준 실사 항목 중 33개(94.3%)가 공식 공부 및 설계도서로 검증 완료(`VERIFIED`/`COLLECTED`)**되었습니다!
-| 구분 | 1차 분석 시점 (마이소쿠 단독) | **2차 업데이트 현시점 (드라이브 11종 반영 후)** | 주요 해결 내역 |
-| :--- | :---: | :---: | :--- |
-| **수집/검증 완료 (`VERIFIED`/`COLLECTED`)** | 23건 | **33건 (94.3%)** | ✅ 등기부등본(갑·을구), ✅ R8 공과증명서(토지 2필지), ✅ 확정측량도, ✅ 현황평면도·옹벽면적도, ✅ 실시설계도(배치·평면·입면·단면·7m파일), ✅ 인정노선도 2종, ✅ 토사재해 하저드맵, ✅ REINS 성약 50건, ✅ 무료 WiFi 비용(월 7,920엔)·준공일(12월 말) |
-| **추정 적용 (`ESTIMATED`)** | 9건 | **2건 (5.7%)** | ⚠️ 건물분 고정자산세 본칙 세액(준공 후 가옥조사 시 확정, 현재 오카다상 45만 엔 추정), ⚠️ 초기 리싱 달성 임대료 및 실제 AD(광고료)개월 수 |
-| **미수집 (`MISSING`)** | 3건 | **0건 (0.0%)** | (미수집 항목 전수 해소 완료!) |
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B109" s="0" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C109" s="0" t="inlineStr">
-        <is>
-          <t>종합 스코어카드 (30점 만점) 및 최종 의사결정 권고</t>
-        </is>
-      </c>
-      <c r="D109" s="0" t="inlineStr">
-        <is>
-          <t>総合スコアカード (19.5/30点) および提言</t>
-        </is>
-      </c>
-      <c r="E109" s="0" t="inlineStr">
-        <is>
-          <t>| 평가 영역 (배점) | 1차 점수 | **2차 확정 점수** | 변경 사유 및 핵심 근거 |
-| :--- | :---: | :---: | :--- |
-| **1. 가격 및 적산가치 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 택지(표준 노선가 적산 88.4%)는 탁월하나, 공과증명서상 토지 평가액(3,698.5만 엔)에 반영된 고저차·계단 접도 감가(-20% 보정 시 적산 71.8%)를 반영하여 0.5점 조정 |
-| **2. 임차 수요 및 입지 (5점)** | 4.0 | **3.5 / 5.0** | 미츠쿄역 급행 정차 및 전 세대 `1LDK(26.89㎡)+로프트(5실)` 평면은 우수하나, 실측 도보 10분 및 남서측 전면도로 계단 구간 존재를 반영하여 0.5점 조정 |
-| **3. 임대료 경쟁력 (5점)** | 3.5 | **3.0 / 5.0** | REINS 성약 50건 대조 결과, 도보 3분 신축 1K(7.3~7.8만 엔) 대비 본건(7.8~8.5만 엔)은 1LDK+로프트 감안 시에도 지역 시세 상단에 해당하여 초기 리싱 버퍼 필요 |
-| **4. 출구 전략 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 토지 및 열화 3급은 장기 매각에 유리하나, 동·북측 미검사 기존 옹벽(98.84㎡)이 차기 매수자 실사 시 허들로 작용 가능 |
-| **5. 현금흐름 및 DSCR (5점)** | 3.5 | **3.5 / 5.0** | 열화 3급 30년 융자 시 DSCR 1.30배, 토지 보유세 특례(연 12.3만 엔) 덕분에 실질 NOI 687만 엔(Cap 5.10%) 견고 유지 |
-| **6. 법적·물리적 안정성 (5점)** | 3.5 | **2.5 / 5.0** | 전면도로 100% 공도 확정 및 건물 7.0m 파일 기초(안식각 45° 대응)는 긍정적이나, **동·북측 기존 옹벽(98.84㎡) 검사필증 부재 및 북서측 토사재해 구역 일부 저촉**으로 1.0점 감점 |
-| **총점 및 종합 등급** | 22.5 / 30 | **19.5 / 30점** | **【조건부 검토 (옹벽·임대료 리스크 반영 공격적 지값 필수)】** |
-### 🎯 매수 실행을 위한 4대 실전 액션 플랜
-1. **준공 시점(2026.12 말)을 활용한 공격적 지값(1.23억~1.25억 엔) 협상**:
-   - 매도자(야오키상사)가 카와사키신용금고로부터 **7,700만 엔을 연 3.05% 고금리**로 조달 중이며 준공이 12월 말(인도 2027년 1월)로 지연된 점을 활용하여, 미검사 기존 옹벽 리스크 인수 조건으로 **1억 2,300만 ~ 1억 2,500만 엔(수익률 7.0~7.1%)** 지값 협상을 추진하십시오.
-2. **『7.00m 기초 파일 시공보고서·지반조사서』 및 『건설주택성능평가서(열화 3급)』 징구 특약**:
-   - 잔금 결제(2027년 1월) 전 인도 서류 목록에 ① 벼랑조례 대응 **7.00m 파일 시공 사진·시공보고서**, ② **건설주택성능평가서(열화대책등급 3급)**, ③ **검사필증(건축물)**을 필수 조건으로 명시하십시오.
-3. **옹벽 배수공 정기 관리 및 시설소유관리자 배상책임보험 가입**:
-   - 동·북측 간지블록 옹벽(98.84㎡)의 수압 상승을 막기 위해 배수공(水抜き穴) 청소 및 균열 점검을 연 1회 실시하고, 화재·지진보험 가입 시 반드시 **옹벽 붕괴 배상책임 특약**을 부가하십시오.
-4. **포털 리싱 시 『1LDK(2인 입주 가능) + 4.82㎡ 로프트 + 무료 WiFi』 카테고리 등록 지시**:
-   - 일반 1R/1K 검색 필터가 아닌 **1DK/1LDK 및 2인 입주 가능(二人入居可) 필터**에 노출시켜 미츠쿄역 역세권 1K 신축(7.3~7.8만 엔)과의 단순 가격 경쟁을 피하고 2027년 1~3월 성수기 조기 만실을 달성하십시오.</t>
-        </is>
-      </c>
-      <c r="F109" s="0" t="inlineStr">
-        <is>
-          <t>| 평가 영역 (배점) | 1차 점수 | **2차 확정 점수** | 변경 사유 및 핵심 근거 |
-| :--- | :---: | :---: | :--- |
-| **1. 가격 및 적산가치 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 택지(표준 노선가 적산 88.4%)는 탁월하나, 공과증명서상 토지 평가액(3,698.5만 엔)에 반영된 고저차·계단 접도 감가(-20% 보정 시 적산 71.8%)를 반영하여 0.5점 조정 |
-| **2. 임차 수요 및 입지 (5점)** | 4.0 | **3.5 / 5.0** | 미츠쿄역 급행 정차 및 전 세대 `1LDK(26.89㎡)+로프트(5실)` 평면은 우수하나, 실측 도보 10분 및 남서측 전면도로 계단 구간 존재를 반영하여 0.5점 조정 |
-| **3. 임대료 경쟁력 (5점)** | 3.5 | **3.0 / 5.0** | REINS 성약 50건 대조 결과, 도보 3분 신축 1K(7.3~7.8만 엔) 대비 본건(7.8~8.5만 엔)은 1LDK+로프트 감안 시에도 지역 시세 상단에 해당하여 초기 리싱 버퍼 필요 |
-| **4. 출구 전략 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 토지 및 열화 3급은 장기 매각에 유리하나, 동·북측 미검사 기존 옹벽(98.84㎡)이 차기 매수자 실사 시 허들로 작용 가능 |
-| **5. 현금흐름 및 DSCR (5점)** | 3.5 | **3.5 / 5.0** | 열화 3급 30년 융자 시 DSCR 1.30배, 토지 보유세 특례(연 12.3만 엔) 덕분에 실질 NOI 687만 엔(Cap 5.10%) 견고 유지 |
-| **6. 법적·물리적 안정성 (5점)** | 3.5 | **2.5 / 5.0** | 전면도로 100% 공도 확정 및 건물 7.0m 파일 기초(안식각 45° 대응)는 긍정적이나, **동·북측 기존 옹벽(98.84㎡) 검사필증 부재 및 북서측 토사재해 구역 일부 저촉**으로 1.0점 감점 |
-| **총점 및 종합 등급** | 22.5 / 30 | **19.5 / 30점** | **【조건부 검토 (옹벽·임대료 리스크 반영 공격적 지값 필수)】** |
-### 🎯 매수 실행을 위한 4대 실전 액션 플랜
-1. **준공 시점(2026.12 말)을 활용한 공격적 지값(1.23억~1.25억 엔) 협상**:
-   - 매도자(야오키상사)가 카와사키신용금고로부터 **7,700만 엔을 연 3.05% 고금리**로 조달 중이며 준공이 12월 말(인도 2027년 1월)로 지연된 점을 활용하여, 미검사 기존 옹벽 리스크 인수 조건으로 **1억 2,300만 ~ 1억 2,500만 엔(수익률 7.0~7.1%)** 지값 협상을 추진하십시오.
-2. **『7.00m 기초 파일 시공보고서·지반조사서』 및 『건설주택성능평가서(열화 3급)』 징구 특약**:
-   - 잔금 결제(2027년 1월) 전 인도 서류 목록에 ① 벼랑조례 대응 **7.00m 파일 시공 사진·시공보고서**, ② **건설주택성능평가서(열화대책등급 3급)**, ③ **검사필증(건축물)**을 필수 조건으로 명시하십시오.
-3. **옹벽 배수공 정기 관리 및 시설소유관리자 배상책임보험 가입**:
-   - 동·북측 간지블록 옹벽(98.84㎡)의 수압 상승을 막기 위해 배수공(水抜き穴) 청소 및 균열 점검을 연 1회 실시하고, 화재·지진보험 가입 시 반드시 **옹벽 붕괴 배상책임 특약**을 부가하십시오.
-4. **포털 리싱 시 『1LDK(2인 입주 가능) + 4.82㎡ 로프트 + 무료 WiFi』 카테고리 등록 지시**:
-   - 일반 1R/1K 검색 필터가 아닌 **1DK/1LDK 및 2인 입주 가능(二人入居可) 필터**에 노출시켜 미츠쿄역 역세권 1K 신축(7.3~7.8만 엔)과의 단순 가격 경쟁을 피하고 2027년 1~3월 성수기 조기 만실을 달성하십시오.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B110" s="0" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C110" s="0" t="inlineStr">
-        <is>
-          <t>입지·도보 10분(계단 접도)·토사재해 하저드 검증</t>
-        </is>
-      </c>
-      <c r="D110" s="0" t="inlineStr">
-        <is>
-          <t>立地・実測徒歩10分(階段接道)・土砂災害検証</t>
-        </is>
-      </c>
-      <c r="E110" s="0" t="inlineStr">
-        <is>
-          <t>챕터 9 상세 분석은 본문 참조</t>
-        </is>
-      </c>
-      <c r="F110" s="0" t="inlineStr">
-        <is>
-          <t>챕터 9 상세 분석은 본문 참조</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="0" t="inlineStr">
-        <is>
-          <t>mitsukyo-1ap</t>
-        </is>
-      </c>
-      <c r="B111" s="0" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C111" s="0" t="inlineStr">
-        <is>
-          <t>최종 투자 의사결정 요약</t>
-        </is>
-      </c>
-      <c r="D111" s="0" t="inlineStr">
-        <is>
-          <t>最終投資意思決定サマリー</t>
-        </is>
-      </c>
-      <c r="E111" s="0" t="inlineStr">
-        <is>
-          <t>챕터 10 상세 분석은 본문 참조</t>
-        </is>
-      </c>
-      <c r="F111" s="0" t="inlineStr">
-        <is>
-          <t>챕터 10 상세 분석은 본문 참조</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="0" t="inlineStr">
-        <is>
-          <t>livre-fine-misato-chuo</t>
-        </is>
-      </c>
-      <c r="B112" s="0">
-        <v>1</v>
-      </c>
-      <c r="C112" s="0" t="inlineStr">
-        <is>
-          <t>에그제큐티브 서머리 (Executive Summary)</t>
-        </is>
-      </c>
-      <c r="D112" s="0" t="inlineStr">
-        <is>
-          <t>エグゼクティブサマリー (Executive Summary)</t>
-        </is>
-      </c>
-      <c r="E112" s="0" t="inlineStr">
         <is>
           <t>본 보고서는 사이타마현 미사토시 야구치(埼玉県三郷市谷口386-5)에 소재한 축 5.6년 차(2021년 2월 25일 신축) 1동 수익형 목조 3층 공동주택인 **「리브르 파인 미사토추오 (リーブルファイン三郷中央)」**(총 11세대: 1LDK × 3세대, 1K × 8세대 + 평면 주차장 4구획)에 대하여, 매도자 및 중개사(히로세 담당자)로부터 추가 입수한 **1차 실사 원장 패키지(『資料１: 2026년 8월 기준 공식 렌트롤·레이와 8년도 고정자산세·런닝코스트·오릭스/au지분은행 35년 융자 시뮬레이션·건축도면』, 『資料２: 토지공동사용협정서 원본』, 『資料３: 토지 3필지·건물 등기사항전부증명서·공도·측량도』 및 중개사 히어링 노트)**를 전수 반영하여 작성한 정밀 실사(Full Due Diligence) 보고서입니다.
 금번 1차 원장 서류 검증을 통해 **기존에 가장 우려되었던 3대 권리·재무 불확실성이 대폭 해소**되었습니다:
@@ -50912,7 +50416,7 @@
 ---</t>
         </is>
       </c>
-      <c r="F112" s="0" t="inlineStr">
+      <c r="F102" s="0" t="inlineStr">
         <is>
           <t>本レポートは、埼玉県三郷市谷口（埼玉県三郷市谷口386-5）に所在する築5.6年（2021年2月25日新築）の一棟収益用木造3階建共同住宅**「リーブルファイン三郷中央 (Livre Fine Misato-Chuo)」**（全11戸：1LDK×3戸、1K×8戸＋平置駐車場4台）について、売主および仲介担当者（廣瀬氏）より追加受領した**一次実査エビデンス一式（『資料１：2026年8月現在公式レントロール・令和8年度固定資産税・ランニングコスト・オリックス銀行/auじぶん銀行35年融資シミュレーション・建物図面』、『資料２：土地共同使用協定書原本』、『資料３：土地3筆・建物全部事項証明書・公図・地積測量図』および仲介ヒアリング記録）**を完全反映して作成した精密デューデリジェンス（Full DD）レポートである。
 今回の一次資料精査により、**当初懸念されていた3大権利・財務リスクが完全に解消または大幅に改善**された：
@@ -50965,26 +50469,28 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="0" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B113" s="0">
-        <v>2</v>
-      </c>
-      <c r="C113" s="0" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
         <is>
           <t>물건 개요 (Property Overview)</t>
         </is>
       </c>
-      <c r="D113" s="0" t="inlineStr">
+      <c r="D103" s="0" t="inlineStr">
         <is>
           <t>物件概要 (Property Overview — 登記簿・建築図面・課税明細照合済)</t>
         </is>
       </c>
-      <c r="E113" s="0" t="inlineStr">
+      <c r="E103" s="0" t="inlineStr">
         <is>
           <t>### 기본 제원표 (등기부・건축도면・과세명세 원장 대조 확정)
 | 항목 | 내용 | 비고 (1차 원장 검증 근거) |
@@ -51020,7 +50526,7 @@
 ---</t>
         </is>
       </c>
-      <c r="F113" s="0" t="inlineStr">
+      <c r="F103" s="0" t="inlineStr">
         <is>
           <t>| 項目 | 内容 | 備考（一次資料検証根拠） |
 | :--- | :--- | :--- |
@@ -51042,26 +50548,28 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="0" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B114" s="0">
-        <v>3</v>
-      </c>
-      <c r="C114" s="0" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
         <is>
           <t>물건의 내력 및 권리분석 (Property History &amp; Title Chain — 등기부 및 협정서 포렌식)</t>
         </is>
       </c>
-      <c r="D114" s="0" t="inlineStr">
+      <c r="D104" s="0" t="inlineStr">
         <is>
           <t>物件の履歴と権利分析 (Property History &amp; Title Chain — 登記簿・協定書フォレンジック)</t>
         </is>
       </c>
-      <c r="E114" s="0" t="inlineStr">
+      <c r="E104" s="0" t="inlineStr">
         <is>
           <t>금번 입수한 **『資料３: 토지 3필지(386-5, 386-7, 386-3) 및 건물 등기사항전부증명서·공도·지적측량도』**와 **『資料２: 토지공동사용협정서(土地共同使用協定書)』**를 통해 본 물건의 개발·권리·담보 이력을 100% 규명하였습니다.
 ### 3-1. 등기부 갑구(소유권) 및 을구(담보권) 시계열 변천사
@@ -51087,7 +50595,7 @@
 ---</t>
         </is>
       </c>
-      <c r="F114" s="0" t="inlineStr">
+      <c r="F104" s="0" t="inlineStr">
         <is>
           <t>- **2020年3月〜7月（開発用地の取得と通路分筆）**：一建設株式会社が本敷地（`386番5`、366.12㎡）および南側位置指定道路（`386番3`、128㎡の持分1/2）を取得後、西側隣地（`386番1`、樋口陽介氏所有）から通路部分`386番6`（2.88㎡・幅2.00m）および`386番7`（16.21㎡・幅2.00m）を分筆し、`386番7`を一建設が取得して合計382.33㎡の宅地を形成した。
 - **2020年10月29日（『土地共同使用協定書』の締結）**：隣地所有者（樋口陽介氏）と一建設の間で、`386番6`（幅2m）と`386番7`（幅2m）を合わせた**幅員4.00mの協定通路部分**を無償（第6条）で一体利用し、第三者への譲渡時には**譲受人（買主）へ協定上の地位を自動承継させる（第8条）**協定書（実印押印・印鑑証明書付）が締結された。
@@ -51097,26 +50605,28 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="0" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B115" s="0">
-        <v>4</v>
-      </c>
-      <c r="C115" s="0" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
         <is>
           <t>수익 상황（렌트롤 포렌식 분석） (Rent Roll Forensics — 2026년 8월 공식 렌트롤 대조)</t>
         </is>
       </c>
-      <c r="D115" s="0" t="inlineStr">
+      <c r="D105" s="0" t="inlineStr">
         <is>
           <t>収益状況（レントロール分析） (Rent Roll Forensics — 2026年8月公式レントロール)</t>
         </is>
       </c>
-      <c r="E115" s="0" t="inlineStr">
+      <c r="E105" s="0" t="inlineStr">
         <is>
           <t>### 4-1. 수익률의 구분 (확정치)
 | 구분 | 연간 수입 | 수익률 | 산정 기준 및 포렌식 비고 |
@@ -51160,7 +50670,7 @@
 ---</t>
         </is>
       </c>
-      <c r="F115" s="0" t="inlineStr">
+      <c r="F105" s="0" t="inlineStr">
         <is>
           <t>### 号室別公式レントロール一覧（資料１：2026年8月現在）
 | 号室 | 階 | 間取り | 専有面積(㎡) | 契約状況 | 賃料(円) | 共益費(円) | 月額合計(円) | ㎡単価(円/㎡) | 駐車場 | 契約期間（当初契約年月） | 保証会社 | フォレンジック診断・賃上げ余地 |
@@ -51182,26 +50692,28 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="0" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="0" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B116" s="0">
-        <v>5</v>
-      </c>
-      <c r="C116" s="0" t="inlineStr">
+      <c r="B106" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
         <is>
           <t>임대료 수준의 검증 및 공실·회전율 정밀 분석 (Market Rent Benchmarking &amp; Vacancy Analysis)</t>
         </is>
       </c>
-      <c r="D116" s="0" t="inlineStr">
+      <c r="D106" s="0" t="inlineStr">
         <is>
           <t>賃料水準の検証および空室・回転率分析 (Market Rent Benchmarking &amp; Vacancy Analysis)</t>
         </is>
       </c>
-      <c r="E116" s="0" t="inlineStr">
+      <c r="E106" s="0" t="inlineStr">
         <is>
           <t>### 5-1. 미사토추오역 권역 시장 시세와 본 물건 코호트별 비교
 | 평형 구분 | 면적대 | 시장 하위 25% | 시장 중앙값 (Median) | 시장 상위 25% | 본 물건 구 서브리스군 (2023년 계약) | 본 물건 최근 성약군 (2025~2026년) | 시세 포지션 및 업사이드 판정 |
@@ -51220,7 +50732,7 @@
 ---</t>
         </is>
       </c>
-      <c r="F116" s="0" t="inlineStr">
+      <c r="F106" s="0" t="inlineStr">
         <is>
           <t>- 2023年春〜夏に大和ハウスリビングのサブリース下で契約された住戸（`202, 203, 302, 304号`：月額6.7万〜6.9万円）と、2025年後半〜2026年8月に成約した直近住戸（`204号` 7.5万円、`303号` 7.0万円、`102・103号` 8.0万円）の間に**月額3,000〜6,000円の明確な賃料ギャップ**が存在する。
 - したがって、旧サブリース住戸の自然退去時に共益費を3,000円→5,000円へ統一し賃料を適正化するだけで、**月額+23,000円（年間+276,000円、満室年収1,015.2万円）の確実なアップサイド**が見込める。
@@ -51228,26 +50740,28 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="0" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B117" s="0">
-        <v>6</v>
-      </c>
-      <c r="C117" s="0" t="inlineStr">
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
         <is>
           <t>가격 타당성 (Price &amp; Valuation Rigor — 레이와 8년도 과세명세 확정 반영)</t>
         </is>
       </c>
-      <c r="D117" s="0" t="inlineStr">
+      <c r="D107" s="0" t="inlineStr">
         <is>
           <t>価格妥当性 (Price &amp; Valuation Rigor — 令和8年度課税明細確定値)</t>
         </is>
       </c>
-      <c r="E117" s="0" t="inlineStr">
+      <c r="E107" s="0" t="inlineStr">
         <is>
           <t>### 6-1. 적산가격(재조달원가법) 및 금융기관 35년 평가 대조
 | 시나리오 구분 | 채용 재조달단가 (㎡) | 건물 적산가액 | 토지 적산가액 (노선가 기준) | 적산가격 합계 | 매매가(1.4억) 대비 비율 | 금융기관 심사 실증 결과 (資料１) |
@@ -51271,7 +50785,7 @@
 ---</t>
         </is>
       </c>
-      <c r="F117" s="0" t="inlineStr">
+      <c r="F107" s="0" t="inlineStr">
         <is>
           <t>- **令和8年度固定資産税・都市計画税（確定値）**：
   - **土地評価額（`386-5`・`386-7` 計382.33㎡）**：**27,054,052円**（固都税年額 76,651円 ※私道`386-3`は非課税）
@@ -51282,26 +50796,28 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="0" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B118" s="0">
-        <v>7</v>
-      </c>
-      <c r="C118" s="0" t="inlineStr">
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
         <is>
           <t>운영 코스트와 캐시플로 (Opex &amp; Cash Flow Modeling — 개시 런닝코스트 및 3대 융자안 대조)</t>
         </is>
       </c>
-      <c r="D118" s="0" t="inlineStr">
+      <c r="D108" s="0" t="inlineStr">
         <is>
           <t>運営コストとキャッシュフロー (Opex &amp; Cash Flow Modeling)</t>
         </is>
       </c>
-      <c r="E118" s="0" t="inlineStr">
+      <c r="E108" s="0" t="inlineStr">
         <is>
           <t>### 7-1. 개시 러닝코스트 확정 내역 (資料１ 히어링 및 고도세 확정치)
 | 비용 항목 | 월간 금액 | 연간 금액 | 매출 대비 비중 | 산출 근거 (資料１ 원장 데이터) |
@@ -51347,7 +50863,7 @@
 ---</t>
         </is>
       </c>
-      <c r="F118" s="0" t="inlineStr">
+      <c r="F108" s="0" t="inlineStr">
         <is>
           <t>- **開示ランニングコスト確定値（年額 1,698,233円 / 17.20%）**：
   - PM管理委託費（5.5%）：年543,180円（月45,265円）
@@ -51366,26 +50882,28 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="0" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B119" s="0">
-        <v>8</v>
-      </c>
-      <c r="C119" s="0" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
         <is>
           <t>임대료 인상 및 밸류애드 시나리오 (Value-Add &amp; Rent Upside)</t>
         </is>
       </c>
-      <c r="D119" s="0" t="inlineStr">
+      <c r="D109" s="0" t="inlineStr">
         <is>
           <t>賃料アップ・バリューアッドシナリオ (Value-Add &amp; Rent Upside)</t>
         </is>
       </c>
-      <c r="E119" s="0" t="inlineStr">
+      <c r="E109" s="0" t="inlineStr">
         <is>
           <t>### 8-1. 구 서브리스 저가 호실(2023년 계약군) 임대료 정상화 시나리오
 공식 렌트롤(資料１)에서 확인된 호실별 실제 임대료와 최근 직영 성약가(`204호` 75,000엔, `303호` 70,000엔, `102·103호` 80,000엔)를 비교하면, **다음 5개 호실의 자연 퇴거 시 인위적 리모델링 없이도 공익비 현실화(3,000→5,000엔) 및 차임 정상화를 통해 연간 +27.6만 엔의 수익 증대가 가능**합니다:
@@ -51401,7 +50919,7 @@
 ---</t>
         </is>
       </c>
-      <c r="F119" s="0" t="inlineStr">
+      <c r="F109" s="0" t="inlineStr">
         <is>
           <t>- 旧サブリース住戸（202・203・301・302・304号）の入替時における共益費5,000円への統一・賃料正常化および駐車場単価改定により**年間+27.6万円の賃料アップサイド**を実現。
 - 令和8年度の本下水直結工事（税込約180万円）完了により、**年間12万円の浄化槽維持費を永久削減**するとともに、「上下水道完備」物件として将来のExit価値を引き上げる。
@@ -51409,26 +50927,28 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="0" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B120" s="0">
-        <v>9</v>
-      </c>
-      <c r="C120" s="0" t="inlineStr">
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
         <is>
           <t>입지・수요・리스크 (Location, Demographics &amp; Risk Analysis)</t>
         </is>
       </c>
-      <c r="D120" s="0" t="inlineStr">
+      <c r="D110" s="0" t="inlineStr">
         <is>
           <t>立地・需要・リスク (Location, Demographics &amp; Risk Analysis)</t>
         </is>
       </c>
-      <c r="E120" s="0" t="inlineStr">
+      <c r="E110" s="0" t="inlineStr">
         <is>
           <t>### 9-1. 입지 및 도심 통근 접근성
 - 미사토시 총인구는 2035년까지 **+1.1% 증가(143,727명)**가 예상되는 수도권 유수의 인구 성장 지자체이며, TX 「미사토추오」역 승차인원 역시 매년 3% 이상 증가(일일 승하차 약 3.2만 명)하고 있습니다.
@@ -51440,7 +50960,7 @@
 ---</t>
         </is>
       </c>
-      <c r="F120" s="0" t="inlineStr">
+      <c r="F110" s="0" t="inlineStr">
         <is>
           <t>- TX「三郷中央」駅の乗降客数は年率3%超で増加しており、全戸J:COM無料インターネット完備・28.4〜43.3㎡の広め設計により高い競争力を維持。
 - 洪水ハザードマップ上は3.0〜5.0m浸水想定区域であるが、売主ヒアリングにより**これまでの豪雨を含めて浸水履歴は一切ないこと**、および1階床高がGL+450mm確保されていることが確認された。
@@ -51448,26 +50968,28 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="0" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
         <is>
           <t>livre-fine-misato-chuo</t>
         </is>
       </c>
-      <c r="B121" s="0">
-        <v>10</v>
-      </c>
-      <c r="C121" s="0" t="inlineStr">
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
         <is>
           <t>종합 평가 (Comprehensive Conclusion &amp; Scorecard)</t>
         </is>
       </c>
-      <c r="D121" s="0" t="inlineStr">
+      <c r="D111" s="0" t="inlineStr">
         <is>
           <t>総合評価 (Comprehensive Conclusion &amp; Scorecard)</t>
         </is>
       </c>
-      <c r="E121" s="0" t="inlineStr">
+      <c r="E111" s="0" t="inlineStr">
         <is>
           <t>### 10-1. 스코어카드 (Scorecard: 6개 축 5점 만점, 총 30점 만점 — 1차 원장 반영 상향)
 | 평가축 | 스코어 | 평가 근거 (1차 원장 검증 반영) |
@@ -51507,7 +51029,7 @@
 - **물건개요서 (`３．三郷市谷口アパート.pdf`)**: 미쓰이스미토모 트러스트 부동산 시부야센터 발행 마이소쿠 (개인 전화번호 마스킹 완료)</t>
         </is>
       </c>
-      <c r="F121" s="0" t="inlineStr">
+      <c r="F111" s="0" t="inlineStr">
         <is>
           <t>| 評価軸 | スコア | 評価根拠（一次資料反映後） |
 | :--- | :---: | :--- |
@@ -51521,6 +51043,578 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B112" s="0">
+        <v>1</v>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>물건 기본 개요 (Property Overview)</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t>物件基本概要 (Property Overview)</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>![마이소쿠 및 건축확인필증](./assets/maisoku_overview.png)
+| 항목 | 세부 내용 (등기부·공과증명서·확정측량도·실시설계도 교차 검증 완료) |
+| :--- | :--- |
+| **물건명** | **미츠쿄 1AP 사사노다이 신축 아파트 (三ツ境1AP 新築一棟アパート)** |
+| **소재지 (지번 / 주거표시)** | **[지번]** 神奈川県横浜市旭区笹野台二丁目149番3、231番102&lt;br&gt;**[주거표시]** **神奈川県横浜市旭区笹野台2丁目19-5** (`35°28'12.8"N 139°30'02.6"E`) |
+| **교통 (구글맵 실측)** | 소테츠 본선(相鉄本線, 급행·통근급행 정차) **「미츠쿄(三ツ境)」역 도보 10분** (마이소쿠 표기 도보 7분 / 구글맵 실측 약 720m·도보 10분, 전면도로 진입부 계단 구간 존재) |
+| **매매가격 (호가)** | **1억 3,470만 엔 (¥134,700,000)** ※ 건물 소비세 포함 |
+| **목표 매수가 (네고 타겟)** | **1억 2,300만 ~ 1억 2,500만 엔** (표면 6.87~7.12% / 실질 NOI 5.50~5.59% — 미검사 옹벽 및 임대료 상단 리스크 반영) |
+| **토지 면적 (공부 vs 실측)** | **[등기부 지적]** 합계 **399.56㎡** (`149番3`: 386.62㎡ + `231番102`: 12.94㎡)&lt;br&gt;**[확정측량 실측]** 합계 **397.71㎡ (120.30평)** = **유효택지 397.42㎡ (120.22평)** (`149-3`: 384.52㎡ + `231-102`: 12.90㎡) + 잠정 후퇴부분(SB) **0.29㎡** |
+| **토지 권리 / 지목** | 소유권 (所有権) / 택지 (宅地) |
+| **도시계획 / 용도지역** | 시가지화구역 / **제1종 저층주거전용지역 (第一種低層住居専用地域)** · 제1종 고도지구 |
+| **건폐율 / 용적률** | 법정 건폐율 **40%** (실적 **39.57%** = 건축면적 `157.24㎡`) / 법정 용적률 **80%** (실적 **60.92%** = 연면적 `242.07㎡`) |
+| **접도 조건 (100% 공도 확인)** | **남서측 폭원 3.92~4.50m 요코하마시 공도(`下川井第402号線`, 지번 `231-1` 요코하마시 소유 공중용도로)** 및 **서측 폭원 4.00~5.50m 요코하마시 공도(`下川井第398号線`)** 접도&lt;br&gt;※ **사도 부담 없음(100% 공도)**, 단 `下川井第402号線`의 부지 전면 구간은 **계단(階段) 도로**임 (차량은 계단 직전까지 동·서 양방향 접근 가능) |
+| **건물 구조 / 규모** | **목조(木造) 준내화구조(準耐火構造) 지상 2층건** · 공동주택 **총 9세대** (1층 5세대, 2층 4세대)&lt;br&gt;**[기초 공법]** RC 베타기초(`地耐力 20kN/㎡`) + **길이 `7.00m` 기초 파일(`杭長 7.00m`)** (요코하마시 벼랑조례 안식각 45° 대응) |
+| **건물 면적 및 평면 구성** | **연면적 242.07㎡ (73.22평)** (1층 `134.48㎡`, 2층 `107.59㎡` / 최고높이 `8.10m`, 처마높이 `5.87m`)&lt;br&gt;• **전 9세대 `1LDK (26.89㎡)`**: `LDK 8.0帖(12.98㎡) + 洋室 5.5帖(8.94㎡)` (전 실 2인 입주 가능 설계)&lt;br&gt;• **5세대(`105, 201, 202, 203, 204호`) 대형 로프트(`4.82㎡ / 3.0帖`) 부착** (로프트 포함 실사용 면적 **31.71㎡**!) |
+| **건축확인번호 / 성능평가** | **제26UDI1K건00271호** (令和8年6月18日 교부 / UDI확인검사(주), 설계: 일급건축사사무소 스페이스팩토리ING)&lt;br&gt;• **설계주택성능평가서 『열화대책등급 3급(劣化対策等級3級)』 취득 완료**&lt;br&gt;• **건설주택성능평가서 『열화대책등급 3급』 준공 시 취득 예정** (최장 30~35년 장기 융자 적격) |
+| **준공 및 인도 예정일** | **2026년 12월 말 준공 예정 / 2027년 1월 인도 예정** (기존 11월 말에서 약 1개월 순연 확인) |
+| **매도자 / 프로젝트 금융** | **야오키상사 주식회사 (ヤオキ商事株式会社)** (카와사키시 타카츠구 소재 업력 50년 디벨로퍼)&lt;br&gt;• **[을구 근저당권]** 2025년 6월 27일 매수 시 **카와사키신용금고(川崎信用金庫 登戸支店) 차입금 7,700만 엔, 금리 연 3.050%** 근저당 설정 확인 |
+| **설비 및 특기사항** | 공영수도 · 공공하수 · **도시가스** · **전 세대 무료 WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정)** · 독립세면대 · UB1014 · IH 2구 시스템키친(W1200) · 실내물건걸이 · 1층 수동셔터 |
+---</t>
+        </is>
+      </c>
+      <c r="F112" s="0" t="inlineStr">
+        <is>
+          <t>![マイソクおよび建築確認済証](./assets/maisoku_overview.png)
+| 項目 | 詳細内容（登記簿・公課証明書・確定測量図・実施設計図 照合済） |
+| :--- | :--- |
+| **物件名** | **三ツ境1AP 新築一棟アパート** |
+| **所在地（地番 / 住居表示）** | **【地番】** 神奈川県横浜市旭区笹野台二丁目149番3、231番102&lt;br&gt;**【住居表示】** **神奈川県横浜市旭区笹野台2丁目19-5** (`35°28'12.8"N 139°30'02.6"E`) |
+| **交通（Googleマップ実測）** | 相鉄本線（急行・通勤急行停車）**「三ツ境」駅 徒歩10分**（マイソク表記：徒歩7分 / Googleマップ実測：約720m・徒歩10分、前面道路に階段区間あり） |
+| **売出価格** | **1億3,470万円 (¥134,700,000)** ※建物消費税込み |
+| **目標買付価格（指値）** | **1億2,300万 〜 1億2,500万円**（表面6.87〜7.12% / 実質NOI利回り5.50〜5.59% — 無検査擁壁・賃料上限リスク反映） |
+| **土地面積（公簿 vs 実測）** | **【登記簿地積】** 合計 **399.56㎡**（`149番3`: 386.62㎡ ＋ `231番102`: 12.94㎡）&lt;br&gt;**【確定測量実測】** 合計 **397.71㎡ (120.30坪)** ＝ **有効宅地 397.42㎡ (120.22坪)** ＋ 暫定後退部分(SB) **0.29㎡** |
+| **土地権利 / 地目** | 所有権 / 宅地 |
+| **都市計画 / 用途地域** | 市街化区域 / **第一種低層住居専用地域** ・ 第1種高度地区 |
+| **建蔽率 / 容積率** | 法定建蔽率 **40%**（実績 **39.57%** ＝ 建築面積 `157.24㎡`） / 法定容積率 **80%**（実績 **60.92%** ＝ 延床面積 `242.07㎡`） |
+| **接道条件（100%公道確定）** | **南西側 幅員3.92〜4.50m 横浜市公道（`下川井第402号線`、地番`231-1` 横浜市所有 公衆用道路）** および **西側 幅員4.00〜5.50m 横浜市公道（`下川井第398号線`）** 接道&lt;br&gt;※**私道負担なし（100%公道）**。ただし`下川井第402号線`の敷地前面区間は**階段道路**（車両は階段手前まで東西双方から進入可） |
+| **建物構造 / 規模** | **木造 準耐火構造 地上2階建** ・ 共同住宅 **全9戸**（1階5戸、2階4戸）&lt;br&gt;**【基礎工法】** RCベタ基礎（`地耐力 20kN/㎡`）＋ **長さ`7.00m`基礎杭（`杭長 7.00m`）**（横浜市がけ条例 安息角45°対応） |
+| **建物面積および間取り** | **延床面積 242.07㎡ (73.22坪)**（1階 `134.48㎡`、2階 `107.59㎡` / 最高高さ `8.10m`、最高軒高 `5.87m`）&lt;br&gt;• **全9戸 `1LDK (26.89㎡)`**：`LDK 8.0帖(12.98㎡) ＋ 洋室 5.5帖(8.94㎡)`（全室2人入居可能）&lt;br&gt;• **5戸（`105, 201, 202, 203, 204号室`）に大型ロフト（`4.82㎡ / 3.0帖`）付帯**（ロフト含む実使用面積 **31.71㎡**！） |
+| **建築確認番号 / 性能評価** | **第26UDI1K建00271号**（令和8年6月18日交付 / ユーディーアイ確認検査(株)、設計：一級建築士事務所スペースファクトリーING）&lt;br&gt;• **設計住宅性能評価書『劣化対策等級3級』取得済**&lt;br&gt;• **建設住宅性能評価書『劣化対策等級3級』竣工時取得予定**（最長30〜35年長期融資適格） |
+| **竣工および引渡予定日** | **2026年12月末竣工予定 / 2027年1月引渡予定**（当初11月末より約1ヶ月順延） |
+| **売主 / プロジェクト融資** | **ヤオキ商事株式会社**（川崎市高津区坂戸3-2-1 KSP西414）&lt;br&gt;• **【乙区抵当権】** 令和7年6月27日取得時に**川崎信用金庫（登戸支店）債権額7,700万円・利息年3.050%**の共同抵当権設定を確認 |
+| **設備および特記事項** | 公営水道 ・ 公共下水 ・ **都市ガス** ・ **全戸無料WiFi（オーナー負担：月額7,920円[税込]・10年縛り）** ・ 独立洗面台 ・ UB1014 ・ IH2口システムキッチン(W1200) ・ 室内物干 ・ 1階手動シャッター |
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B113" s="0">
+        <v>2</v>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>등기부등본(甲区·乙区)·공과증명서·건축도면 포렌식 실사 (Forensic Due Diligence)</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t>登記簿謄本・公課証明書・実施設計図フォレンジック調査 (Forensic Due Diligence)</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t>### 2.1 등기부등본(全部事項証明書) 권리관계 및 매도자 조달금리 분석
+`05_touhon_sokuryo_kouka.pdf` (1~6페이지) 등기부등본 전수 조사 결과:
+1. **갑구 (소유권 이력)**:
+   - 구 소유자 개인(1957년/1982년 취득 → 1997년 상속 → 2003년 매매)을 거쳐, **令和7年(2025년) 6월 27일 현 매도자인 『야오키상사 주식회사(ヤオキ商事株式会社)』가 매매로 소유권을 취득**했습니다.
+   - `149番3` 토지는 1983년(소화 58년) 지적 정정을 통해 `384.06㎡ → 386.62㎡`로 등기되었으며, `231番102` 토지는 `12.94㎡`로 등기되어 공부상 합계 면적은 **`399.56㎡`**입니다.
+2. **을구 (담보권 및 매도자 협상 레버리지 핵심 단서)**:
+   - 현 매도자(야오키상사)는 2025년 6월 27일 토지 취득과 동시에 **카와사키신용금고(川崎信用金庫 登戸支店)**로부터 **채권액 7,700만 엔(이자 연 3.050%, 손해금 연 14.50%)의 공동담보 저당권(목록 (イ)第5921号)**을 설정했습니다.
+   - **💡 협상 전략적 시사점**: 중개사(오카다상)에 따르면 매도자는 *"초기에는 가격 네고에 잘 응하지 않으나 안 팔리면 시기를 보아 가격을 내리는 스탠스"*입니다. 그러나 매도자는 현재 **연 3.05%라는 높은 프로젝트 조달금리(월 이자만 약 19.6만 엔)**를 부담하고 있으며, 공정이 당초 11월 말에서 **12월 말 준공(2027년 1월 인도)**으로 지연되었습니다. 따라서 연말 준공 시점까지 매수자가 확정되지 않을 경우 매도자의 이자 및 재고 보유 압박이 급증하므로, 이를 지렛대로 **1억 2,300만 ~ 1억 2,500만 엔** 선의 조건부 매수의향서(LOI) 타진이 매우 유효합니다.
+---
+### 2.2 🚨 최대 핵심 리스크: 기존 간지블록 옹벽(98.84㎡) &amp; 토사재해경계구역(Yellow/Red Zone) 정밀 진단
+![현황평면도 및 옹벽면적 산출도](./assets/retaining_wall_calc.png)
+![단면도 및 7.0m 기초파일 안식각 45도 시공도](./assets/section_piles.png)
+![가나가와현 토사재해 하저드맵](./assets/hazard_landslide.jpg)
+이번 2차 실사 자료(`현황평면도`, `옹벽면적도`, `실시설계 단면도`, `가측량도`, `오카다상 질의응답`)를 통해 밝혀진 가장 중요한 물리적·법적 팩트입니다.
+| 검증 항목 | 실사 확인 결과 (Hard Fact) | 투자 리스크 및 대응 방안 |
+| :--- | :--- | :--- |
+| **1. 지형 및 옹벽 규모** | • 부지 레벨(GL `12.14~12.26m`)이 북측·동측·남측 인접지 및 도로(`7.63~8.37m`)보다 **약 4.0m ~ 4.69m 높은 고대(高台) 지형**&lt;br&gt;• 옹벽 면적 산출도(`擁壁面積`)상 **총 7개 구간(①~⑦), 합계 면적 `98.84㎡`** (구간별 높이 `1.162m ~ 3.488m`, 단면도상 최대 단차 `4.690m`) | 높이 2m를 초과하는 대형 간지블록(間知ブロック) 옹벽이 부지 3면을 둘러싸고 있음 |
+| **2. 옹벽 소유권 및 유지관리 책임** | • **동측(東) 및 북측(北) 옹벽**: **매도자 소유 → 매수자(투자자)에게 소유권 및 유지보수 책임 승계!**&lt;br&gt;• **서측(西) 옹벽**: **서측 인접지 소유자 소유** (고저차 큰 노후 옹벽) | 동·북측 옹벽의 향후 균열·배부름 보수비 및 지진·호우로 인한 붕괴 시 인접 저지대 가옥에 대한 **민법상 공작물 배상책임(민법 717조)**이 매수자에게 귀속됨 |
+| **3. 축조시기 및 검사필증 유무** | • **축조시기 불명(築造時期不明) / 택지조성 및 공작물 검사필증 없음(検査済証なし)**&lt;br&gt;• 매도자 측의 **보강 공사나 재축조 계획 없음(補強・造り直し予定なし)**&lt;br&gt;• 단, 실시설계 배치도(`配置図`)상 일급건축사 육안 점검 결과 **『間知ブロック 亀裂、たわみ無し 水抜き穴あり 安全支障無し(균열·배부름 없음, 배수공 있음, 안전지장 없음)』**으로 기재됨 | 검사필증이 없는 구형 옹벽이므로, 향후 재건축 시에는 옹벽 재축조(수천만 엔 소요) 또는 벼랑조례 파일 재시공이 필요하며, 일부 보수적 시중은행(1금융권)에서 담보 평가를 감액할 수 있음 |
+| **4. 벼랑조례(がけ条例) 및 신축 허가 통과 비결** | • 요코하마시 건축기준조례 제4조(벼랑 부근의 건축물) 및 **『横浜市がけ関係小規模建築物技術指針』**에 의거하여, **옹벽 하단으로부터 45° 안식각(`安息角 45°`) 아래의 견고한 지지층까지 길이 `7.00m`의 기초 파일(`杭長 7.00m`)을 관입**하고 RC 베타기초를 얹는 공법을 채택!&lt;br&gt;• 또한 성토규제법(`盛土規制法`) 저촉을 피하기 위해 **성토 없음(`盛土無し`)**으로 설계하여 건축확인(`제26UDI1K건00271호`)을 적법 취득함 | **건물 본체의 구조적 안전성(침하·전도 방지)은 7.0m 파일 시공으로 확보**되었음. 준공 시 **『7.0m 파일 시공 보고서 및 지반조사 보고서』** 사본을 반드시 수령해야 함 |
+| **5. 토사재해경계구역 저촉 여부** | • 가나가와현 토사재해 포털 및 가측량도(`06_karisoku.pdf`) 확인 결과, **부지 북서측(北西) 모서리 옹벽 부분(약 4.69㎡ 삼각형 구간)이 토사재해경계구역(옐로우존 / 잠정 레드존 경계)에 일부 걸쳐 있음(かすっている)**을 매도자가 공식 확인함&lt;br&gt;• 건물 본체는 북측·서측 경계로부터 `2.00m` 이상 이격되어 있어 건물 자체는 구역 밖에 위치함 | 중요사항설명서(重説)에 토사재해경계구역(일부) 해당 사실이 기재되며, 화재·지진보험 가입 시 **시설소유관리자 배상책임보험(옹벽 손해 담보)** 특약을 반드시 추가해야 함 |
+---
+### 2.3 전면도로 공도(公道) 확인 및 계단 접근로 분석
+![요코하마시 인정노선도 하카와이 제402호선](./assets/road_map_402.png)
+![현황평면도 계단 및 레벨 상세](./assets/survey_topography.png)
+1. **사도(私道) 리스크 완전 해소**:
+   - 1차 분석 당시 마이소쿠에 `公道・私道`로 혼재 표기되어 있었으나, 이번에 수령한 **도로 등기부(`笹野台二丁目231番1`, 지목: 공중용도로, 소유자: `横浜市`)** 및 **요코하마시 인정노선도(`下川井第402号線` 폭원 4.00~4.50m, `下川井第398号線` 폭원 4.00~5.50m)**를 통해 **부지에 접한 모든 도로가 100% 요코하마시 공도(公道)**임이 확정되었습니다. 따라서 사도 지분 누락이나 굴착 승낙 거부 리스크는 **0%**입니다.
+2. **전면도로 계단(階段) 구간 유의사항**:
+   - 현황평면도(`survey_topography.png`)에서 확인되듯, 남서측 전면도로(`下川井第402号線`)의 부지 접도 구간 중 서측 절반은 **경사 계단(階段)**으로 되어 있습니다.
+   - 자동차는 계단 아래쪽(남동측)과 계단 위쪽(`下川井第398号線`, 북서측) 양방향에서 계단 바로 앞까지 진입할 수 있으나, 부지 내 주차장은 없으며 이사 차량 정차 시 계단 앞 도로를 이용해야 합니다.
+---
+### 2.4 건축 상세 도면(`1階・2階 平面詳細図`) 분석: 전 세대 `1LDK(26.89㎡)` + 5세대 `로프트(4.82㎡)`
+![1층 평면상세도](./assets/plan_1f.png)
+![2층 평면상세도](./assets/plan_2f.png)
+실시설계 평면상세도(`02_plans_elevations.pdf` 2~3p)를 통해 확인된 본 건물의 상품 스펙은 일반 신축 목조 원룸(14~18㎡)을 압도합니다:
+- **전 9세대 `1LDK` (`26.89㎡`) 표준 구성**:
+  - 전 호실이 **`LDK 8.0帖 (12.98㎡) + 洋室 5.5帖 (8.94㎡)`**으로 분리된 정통 **컴팩트 1LDK** 구조입니다(소방법상 각 실 수용인원 2명, 1인 가구 재택근무자 및 **신혼·동거 커플 2인 입주 가능**!).
+- **5개 호실(`105호`, `201~204호`) 대형 로프트(`4.82㎡`) 서비스 면적**:
+  - 2층 4개 호실(`201~204호`)뿐 아니라 **1층 동측 끝단 단층 구조인 `105호`에도 `2.65m × 1.82m = 4.82㎡ (약 3.0帖, 천장고 1.4m 이하, 이동식 사다리)` 로프트가 시공**됩니다!
+  - 즉, 9세대 중 5세대는 **실사용 면적이 `26.89㎡ + 4.82㎡ = 31.71㎡ (약 9.6평)`**에 달합니다.
+- **내화·차음·설비 사양**:
+  - **준내화구조(`準耐火構造`)**: 벽체 석고보드 `12.5+12.5mm` 양면 시공, 세대 간 차음 경계벽 천장 속까지 밀실 시공(`界壁遮音 天井裏まで達しせめる` + 글라스울 충전).
+  - **설비**: 시스템키친 `W1200` (`IH 2구 콘로 200V 3000W`), 유닛배스 `UB 1014`, 독립 세면화장대, 실내 빨래걸이(`室内物干`), 1층 전 창문 **방범용 수동 셔터(`手動シャッター`)**, 전 세대 **무료 WiFi**.
+---</t>
+        </is>
+      </c>
+      <c r="F113" s="0" t="inlineStr">
+        <is>
+          <t>### 2.1 登記簿謄本（甲区・乙区）の権利関係および売主の借入条件分析
+1. **甲区（所有権履歴）**：
+   - 旧個人所有者（昭和32年/57年取得→平成9年相続→平成15年売買）を経て、**令和7年（2025年）6月27日に現売主である『ヤオキ商事株式会社』が売買により取得**しています。
+2. **乙区（抵当権および指値交渉の強力なレバレッジ）**：
+   - 売主（ヤオキ商事）は令和7年6月27日付で**川崎信用金庫（登戸支店）より債権額7,700万円・金利年3.050%**のプロジェクト融資を借り入れています。
+   - **💡 指値交渉への示唆**：仲介担当者（岡田様）によれば「売主は当初は値下げに応じないが、売れなければ時期を見て価格を下げるスタンス」とのことですが、**年3.050%という高金利（月間利息だけで約19.6万円）**を負担しながら竣工が**2026年12月末（引渡2027年1月）**へ遅れているため、竣工前後のタイミングで**1億2,300万〜1億2,500万円**の指値買付を入れる交渉戦略が極めて有効です。
+---
+### 2.2 🚨 最大の重要リスク：既存間知ブロック擁壁（98.84㎡）＆土砂災害警戒区域の精密診断
+![擁壁面積算出図](./assets/retaining_wall_calc.png)
+![断面図および7.0m基礎杭・安息角45度施工図](./assets/section_piles.png)
+![神奈川県土砂災害ハザードマップ](./assets/hazard_landslide.jpg)
+| 検証項目 | 実査確認結果 (Hard Fact) | 投資リスクおよび対策 |
+| :--- | :--- | :--- |
+| **1. 高低差および擁壁規模** | • 敷地レベル（GL `12.14〜12.26m`）が北・東・南側の隣地および道路（`7.63〜8.37m`）より**約4.0m〜4.69m高い高台**&lt;br&gt;• 擁壁面積図（`擁壁面積`）上、**全7区間（①〜⑦）合計 `98.84㎡`**（高さ`1.162m〜3.488m`、断面図上の最大高低差`4.690m`） | 高さ2m超の間知ブロック擁壁が敷地を取り囲んでいる |
+| **2. 擁壁の所有権と管理責任** | • **東側および北側擁壁**：**売主所有 → 買主（投資家）へ所有権・維持管理責任が承継！**&lt;br&gt;• **西側擁壁**：**西側隣地所有者の所有**（高低差が大きい古い擁壁） | 東・北側擁壁の将来の補修費用および万一の崩壊時の**工作物責任（民法717条）**は買主負担となる |
+| **3. 築造時期・検査済証の有無** | • **築造時期不明・検査済証なし・補強や造り直し予定なし**&lt;br&gt;• ただし配置図（`配置図`）上の一級建築士による現況確認では**『間知ブロック 亀裂、たわみ無し 水抜き穴あり 安全支障無し』**と明記 | 検査済証のない既存擁壁のため、一部の都市銀行・地方銀行では担保評価が厳しくなる可能性あり |
+| **4. 横浜市がけ条例のクリア手法** | • **『横浜市がけ関係小規模建築物技術指針』**に基づき、**擁壁下端から安息角45°（`安息角 45°`）より深い支持層まで長さ`7.00m`の基礎杭（`杭長 7.00m`）を打設**してRCベタ基礎を支持！&lt;br&gt;• 盛土規制法に抵触しないよう**盛土無し（`盛土無し`）**で設計し、建築確認済証（`第26UDI1K建00271号`）を適法に取得 | **建物本体の構造安全性（沈下・倒壊防止）は7.0m杭によって確保済**。引渡時に必ず**『杭施工報告書・地盤調査報告書』**を受領すること |
+| **5. 土砂災害警戒区域への抵触** | • 神奈川県土砂災害情報ポータルおよび仮測量図（`06_karisoku.pdf`）にて、**敷地北西角の擁壁部分（約4.69㎡）が土砂災害警戒区域（イエローゾーン／暫定レッドゾーン境界）にかすっている**ことを売主も認識&lt;br&gt;• 建物本体は北・西境界から`2.00m`離隔しており区域外 | 重要事項説明書に記載される事項であり、火災・地震保険加入時に**施設所有者賠償責任特約**を必ず付帯すること |
+---
+### 2.3 前面道路の公道確定および階段アプローチの確認
+![横浜市認定路線図 下川井第402号線](./assets/road_map_402.png)
+![現況平面図 階段および高低差詳細](./assets/survey_topography.png)
+- **100%横浜市公道と確定**：道路登記簿（`笹野台二丁目231番1`、所有者：`横浜市`）および認定路線図（`下川井第402号線`・`下川井第398号線`）により、**接道する道路はすべて横浜市所有の公道**であることが証明されました。私道トラブルのリスクはありません。
+- **階段部分の注意点**：南西側`下川井第402号線`の敷地前面西側半分は**階段**となっています。車両は階段の上側・下側の両方から階段手前まで進入可能です。
+---
+### 2.4 実施設計平面詳細図：全9戸`1LDK（26.89㎡）`＋5戸`ロフト（4.82㎡）`
+![1階平面詳細図](./assets/plan_1f.png)
+![2階平面詳細図](./assets/plan_2f.png)
+- **全9戸が`1LDK（26.89㎡）`**：全戸が`LDK 8.0帖（12.98㎡）＋洋室 5.5帖（8.94㎡）`の1LDK設計（消防法上の収容人員：各室2名、カップル・新婚の2人入居に対応）。
+- **5戸（`105号室`、`201〜204号室`）に`4.82㎡（約3.0帖）`ロフト付帯**：2階4戸だけでなく**1階東端の下屋部分である`105号室`にも`4.82㎡`のロフトが設置**されており、ロフト含む実使用面積は**31.71㎡**に達します。
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B114" s="0">
+        <v>3</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>토지·건물 적산가격(積算価格) 및 령화 8년도 공과증명서(公課証明書) 정밀 평가</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t>令和8年度 公課証明書（固定資産税評価額）および積算価格検証</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>### 3.1 령화 8년도 고정자산세·도시계획세 공과증명서(令和8年度 公課証明書) 실측 내역
+요코하마시 아사히구청장이 2026년 4월 30일 발급한 공식 공과증명서(`05_touhon_sokuryo_kouka.pdf` 12~13p) 수치입니다:
+| 필지 (지번) | 등기 지적 | 확정측량 유효면적 | R8 고정자산세 평가액 (評価額) | ㎡당 평가단가 | R8 나대지 기준 세액 (고정+도계) | 신축 완공 후 소규모 주택용지 특례(1/6·1/3) 적용 시 연간 세액 |
+| :--- | :---: | :---: | :---: | :---: | :---: | :---: |
+| **笹野台二丁目149番3** | 386.62㎡ | 384.52㎡ (+SB 0.20㎡) | **¥35,787,480** | ¥92,565/㎡ | ¥397,154 | **약 ¥119,291** |
+| **笹野台二丁目231番102** | 12.94㎡ | 12.90㎡ (+SB 0.09㎡) | **¥1,197,791** | ¥92,565/㎡ | ¥13,291 | **약 ¥3,992** |
+| **토지 2필지 합계** | **399.56㎡** | **397.42㎡ (120.22평)** | **¥36,985,271** | **¥92,565/㎡** | ¥410,445 | **약 ¥123,283 / 년 (약 12.3만 엔)** |
+| **신축 건물 (추정)** | - | **242.07㎡ (73.22평)** | **약 ¥26,627,700** (11만/㎡) | ¥110,000/㎡ | - | **약 ¥450,000 / 년 (첫 3년은 감면으로 약 25만 엔)** |
+| **토지 + 건물 총계** | - | - | **¥63,612,971 (약 6,361만 엔)** | - | - | **정상화 시 약 ¥573,283 / 년 (약 57.3만 엔)** |
+&gt; [!TIP] **공과증명서 핵심 인사이트 (보유세 절감 vs 고저차 보정)**
+&gt; - **왜 토지 고정자산세 평가액이 `3,698.5만 엔(92,565엔/㎡)`인가?**: 사사노다이 2초메 표준 주택가의 상속세 노선가는 약 `190,000円/㎡`(공시지가 약 `240,000円/㎡`)이나, 본 필지는 **남서측 계단 도로 접도 및 4m 이상 고저차(옹벽)**가 존재하여 요코하마시 세무과에서 **지형·접도 감가 보정**을 대폭 반영했기 때문입니다.
+&gt; - **투자자 실익**: 토지 공적 평가액이 낮게 책정된 덕분에, 9세대 공동주택 준공 후 **소규모 주택용지 특례(200㎡×9호=1,800㎡까지 고정자산세 1/6, 도시계획세 1/3 감면)**가 적용되면 **120.3평 대토지의 연간 보유세가 불과 `12.3만 엔` 수준**으로 낮아져 현금흐름(NOI)을 강력하게 방어합니다!
+---
+### 3.2 적산가격(積算価格) 3대 시나리오 및 지형 보정(がけ地補正) 비교
+일반 평탄지 노선가(`190,000円/㎡`) 기준 적산과, 금융기관이 고저차·계단 접도 감가(**-20%, 실효 노선가 `152,000円/㎡`**)를 적용한 보수적 담보 적산을 병행 산출했습니다.
+| 평가 시나리오 | 토지 평가 기준 | 토지 적산가 | 건물 단가 (`242.07㎡`×22/22년) | 건물 적산가 | **합계 적산가격** | **호가(1.347억) 대비 비율** |
+| :--- | :--- | :---: | :---: | :---: | :---: | :---: |
+| **① 은행 엄격 담보 기준 (지형감가 -20%)** | 유효 `397.42㎡` × 15.2만 엔/㎡ | ¥60,407,840 | 150,000엔/㎡ | ¥36,310,500 | **¥96,718,340** | **71.80%** |
+| **② 금융기관 표준 기준 (노선가 원안+15만)** | 유효 `397.42㎡` × 19.0만 엔/㎡ | ¥75,509,800 | 150,000엔/㎡ | ¥36,310,500 | **¥111,820,300** | **83.01%** |
+| **③ 국세청 표준 적산 (노선가 원안+18만)** | 유효 `397.42㎡` × 19.0만 엔/㎡ | ¥75,509,800 | 180,000엔/㎡ | ¥43,572,600 | **¥119,082,400** | **88.41%** |
+| **④ 실세 공시지가 + 신축 재조달원가(22만)** | 유효 `397.42㎡` × 24.0만 엔/㎡ | ¥95,380,800 | 220,000엔/㎡ | ¥53,255,400 | **¥148,636,200** | **110.35%** |
+- 지형 감가(-20%)를 엄격히 반영하더라도 적산비율이 **71.80%(9,672만 엔)**를 상회하며, 표준 노선가 기준으로는 **83.01% ~ 88.41%**에 달합니다.
+---</t>
+        </is>
+      </c>
+      <c r="F114" s="0" t="inlineStr">
+        <is>
+          <t>### 3.1 令和8年度 固定資産・都市計画税 公課証明書（実測値）
+| 筆（地番） | 登記地積 | 確定測量有効面積 | R8 固定資産税評価額 | ㎡単価 | R8 更地時点年税額 | 完成後・小規模住宅用地特例（1/6・1/3）適用時の年税額 |
+| :--- | :---: | :---: | :---: | :---: | :---: | :---: |
+| **笹野台二丁目149番3** | 386.62㎡ | 384.52㎡ (+SB 0.20㎡) | **¥35,787,480** | ¥92,565/㎡ | ¥397,154 | **約 ¥119,291** |
+| **笹野台二丁目231番102** | 12.94㎡ | 12.90㎡ (+SB 0.09㎡) | **¥1,197,791** | ¥92,565/㎡ | ¥13,291 | **約 ¥3,992** |
+| **土地2筆 合計** | **399.56㎡** | **397.42㎡ (120.22坪)** | **¥36,985,271** | **¥92,565/㎡** | ¥410,445 | **約 ¥123,283 / 年（約12.3万円）** |
+| **新築建物（見込）** | - | **242.07㎡ (73.22坪)** | **約 ¥26,627,700** (11万/㎡) | ¥110,000/㎡ | - | **約 ¥450,000 / 年（当初3年間は軽減で約25万円）** |
+| **土地＋建物 総計** | - | - | **¥63,612,971（約6,361万円）** | - | - | **通常時 約 ¥573,283 / 年（約57.3万円）** |
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B115" s="0">
+        <v>4</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤 포렌식 및 REINS 근린 성약 50건(`03_comps_1R_1K.pdf`) 비교 검증</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t>レントロールおよびREINS近隣成約事例50件（`03_comps_1R_1K.pdf`）比較検証</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>### 4.1 호실별 상정 렌트롤 및 평면 스펙 (전 9세대)
+| 호실 | 층수 / 위치 | 상세 평면 (전유면적 + 로프트) | 상정 월임대료 (공익비·무료WiFi 포함) | 연간 임대료 | 전유 ㎡당 단가 | 로프트 포함(31.71㎡) 실효 ㎡단가 | 비고 |
+| :---: | :---: | :--- | :---: | :---: | :---: | :---: | :--- |
+| **101호** | 1F 서측 각실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥80,000** | ¥960,000 | 2,975엔/㎡ | 2,975엔/㎡ | 1층 남서·북서 2면 채광 각실, 수동셔터 |
+| **102호** | 1F 중실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥78,000** | ¥936,000 | 2,901엔/㎡ | 2,901엔/㎡ | 7만 엔대(7.8만) 진입 호실, 수동셔터 |
+| **103호** | 1F 중실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥78,000** | ¥936,000 | 2,901엔/㎡ | 2,901엔/㎡ | 7만 엔대(7.8만) 진입 호실, 수동셔터 |
+| **104호** | 1F 중실 | **1LDK (`26.89㎡`)** [LDK 8.0 + 양실 5.5] | **¥78,000** | ¥936,000 | 2,901엔/㎡ | 2,901엔/㎡ | 7만 엔대(7.8만) 진입 호실, 수동셔터 |
+| **105호** | 1F 동측 단층 각실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥80,000** | ¥960,000 | 2,975엔/㎡ | **2,523엔/㎡** | **1층 유일 로프트 부착** + 2면 채광 각실! |
+| **201호** | 2F 서측 각실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥85,000** | ¥1,020,000 | 3,161엔/㎡ | **2,681엔/㎡** | 최상층 각실 + 4.82㎡ 대형 로프트 |
+| **202호** | 2F 중실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥83,000** | ¥996,000 | 3,087엔/㎡ | **2,617엔/㎡** | 최상층 중실 + 4.82㎡ 대형 로프트 |
+| **203호** | 2F 중실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥83,000** | ¥996,000 | 3,087엔/㎡ | **2,617엔/㎡** | 최상층 중실 + 4.82㎡ 대형 로프트 |
+| **204호** | 2F 동측 각실 | **1LDK (`26.89㎡`) + 로프트 (`4.82㎡`)** | **¥85,000** | ¥1,020,000 | 3,161엔/㎡ | **2,681엔/㎡** | 최상층 각실 + 4.82㎡ 대형 로프트 |
+| **합계** | **전 9세대** | **전유 242.07㎡ (+로프트 24.10㎡ = 266.17㎡)** | **¥730,000 / 월** | **¥8,760,000 / 년** | **3,016엔/㎡** | **2,743엔/㎡** | **전 실 2인 입주 가능 1LDK + 무료 WiFi** |
+---
+### 4.2 REINS 근린 성약 사례 50건(`03_comps_1R_1K.pdf`) 대조 및 임대료 적정성 진단
+오카다상이 제공한 미츠쿄·키보가오카·세야역 주변 24~31㎡ 성약 데이터 50건 중 주요 경쟁 신축·축천 사례와의 비교표입니다:
+| 비교 물건명 (소재지) | 최기역 / 도보 | 준공연월 | 면적 / 타입 | 성약 임대료 + 관리비 = **월 총액** | ㎡당 단가 | 본건(`미츠쿄 1AP`) 대비 시사점 |
+| :--- | :--- | :---: | :---: | :---: | :---: | :--- |
+| **가칭 요코하마 미츠쿄 AP** (미츠쿄) | 미츠쿄역 **도보 3분** | **2025.06 (신축)** | 25.05㎡ / 1K | 6.9~7.4만 + 4,000엔 = **7.3~7.8만 엔** | 2,914~3,114엔 | 역 도보 3분 신축 1K가 7.3~7.8만 엔에 성약됨 (예금 1개월) |
+| **KOMA 미츠쿄** (사사노다이 1초메) | 미츠쿄역 **도보 7분** | 2021.12 (축4년) | 24.77㎡ / 1K | 6.6~6.7만 + 3,000엔 = **6.9~7.0만 엔** | 2,786~2,826엔 | 동일 사사노다이 권역 1K(축4년) 실세는 약 7.0만 엔 수준 |
+| **그린힐 키보가오카** (나카키보가오카) | 키보가오카역 **도보 4분** | **2025.07 (신축)** | 26.45㎡ / 1R | 7.3만 + 3,000엔 = **7.6만 엔** | 2,873엔 | 인접역 도보 4분 26.45㎡ 신축이 총 7.6만 엔에 성약 |
+| **트윈즈 요코하마 세야** (세야) | 세야역 **도보 5~6분** | **2024.10 (신축)** | 28.66㎡ / 1K | 8.0만 + 5,000엔 = **8.5만 엔** | 2,966엔 | 28.6㎡급 대형 평면은 8.5만 엔 성약 가능 입증 |
+| **일 피오레 사사노다이** (사사노다이 1초메) | 미츠쿄역 **도보 5분** | 2015.02 (축11년) | 28.56㎡ / 1K | 7.2만 + 3,000엔 = **7.5만 엔** | 2,626엔 | 사사노다이 28㎡급 기축은 평균 DOM 30일 내 안정 소화 |
+| **⭐ 본건: 미츠쿄 1AP** (사사노다이 2-19-5) | 미츠쿄역 **도보 10분** | **2026.12 (신축)** | **26.89㎡ `1LDK` (+로프트 4.82㎡×5실)** | **1F 7.8~8.0만 / 2F 8.3~8.5만** (무료WiFi 포함) | **3,016엔** (로프트 포함 2,743엔) | **1K가 아닌 『1LDK(2인 입주 가능)+로프트+무료WiFi』로 차별화했으나, 도보 10분 기준 지역 시세 최상단(Upper Bound)에 위치!** |
+&gt; [!IMPORTANT] **임대료 스트레스 테스트 결론**
+&gt; - 미츠쿄역 도보 3분 신축 1K(25㎡)가 7.3~7.8만 엔에 성약된 점을 감안할 때, 도보 10분(계단 접근)인 본건이 **1층 7.8~8.0만 엔 / 2층 8.3~8.5만 엔**을 달성하려면 반드시 포털(SUUMO/HOME'S) 등록 시 **『1K가 아닌 1LDK(2인 입주 가능) + 3조 대형 로프트 + 무료 WiFi 완비』** 카테고리로 노출시켜 **커플·동거 수요 및 광폭 재택근무 수요**를 타겟팅해야 합니다.
+&gt; - 만약 1인 가구 위주로 모집하여 **임대료를 -5% 인하(1층 7.4~7.6만 엔, 2층 7.9~8.1만 엔 → 연수입 832.2만 엔)**하더라도, **만실 NOI는 645.4만 엔(Cap 4.79%), 30년 융자 시 DSCR 1.22배, 세전 CF +116.7만 엔/년**으로 여전히 안정적인 흑자가 유지됩니다.
+---</t>
+        </is>
+      </c>
+      <c r="F115" s="0" t="inlineStr">
+        <is>
+          <t>### 4.1 REINS成約事例50件との比較
+- **仮称 横浜三ツ境アパート**（2025年6月新築、三ツ境駅**徒歩3分**、25.05㎡・1K）：成約賃料 **6.9〜7.4万円＋共益費4,000円＝計7.3〜7.8万円**（礼金1ヶ月）。
+- **KOMA三ツ境**（2021年12月築、笹野台1丁目、三ツ境駅**徒歩7分**、24.77㎡・1K）：成約賃料 **6.6〜6.7万円＋共益費3,000円＝計6.9〜7.0万円**。
+- **グリーンヒル希望ヶ丘**（2025年7月新築、希望ヶ丘駅**徒歩4分**、26.45㎡・1R）：成約賃料 **7.3万円＋共益費3,000円＝計7.6万円**。
+- **ツインズ横浜瀬谷**（2024年10月新築、瀬谷駅**徒歩5〜6分**、28.66㎡・1K）：成約賃料 **8.0万円＋共益費5,000円＝計8.5万円**。
+- **診断結論**：本物件（徒歩10分・階段あり）の想定賃料（1階7.8〜8.0万円、2階8.3〜8.5万円、無料WiFi込）は近隣相場の**上限（アッパーバウンド）**に位置します。ただし近隣事例がすべて「1R/1K」であるのに対し、本物件は**『1LDK（26.89㎡・2人入居可）＋大型ロフト4.82㎡（5戸）＋無料WiFi』**という明確な差別化要素を持つため、募集時は必ず「1LDK・二人入居可」としてポータル掲載する必要があります。万一賃料を**-5%引き下げ（年収入832.2万円）**た場合でも、**満室NOI 645.4万円・DSCR 1.22倍・税引前CF +116.7万円/年**と黒字を維持できます。
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B116" s="0">
+        <v>5</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>운영경비(OPEX) 정규화 및 현금흐름·손익분기(BEP) 모델링</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t>モアビズ4期 決算書着地シミュレーション（令和8年度公課証明書反映）</t>
+        </is>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>### 5.1 실질 운영경비(OPEX) 명세 (오카다상 확인 확정치 반영)
+| 경비 항목 | 연간 금액 (엔) |GPI 대비 비율 | 산출 근거 (2차 실사 검증 완료) |
+| :--- | :---: | :---: | :--- |
+| **1. 고정자산세·도시계획세 (보유세)** | **¥573,000** | 6.54% | **[토지]** R8 공과증명서(평가액 3,698.5만) 주택용지 특례(1/6·1/3) 적용 **¥123,000**&lt;br&gt;**[건물]** 오카다상 확인 목조 신축 평가 기준 **¥450,000** (※ 초기 3년간은 신축 감면으로 합계 약 37만 엔/년) |
+| **2. PM 임대관리 위탁수수료** | **¥438,000** | 5.00% | 만실 임대수입(876만 엔)의 5.0% |
+| **3. 전 세대 무료 WiFi 런닝코스트** | **¥95,040** | 1.08% | **오카다상 확인 확정치: 월 7,920엔(세금포함) × 12개월 (※ 10년 약정 조건)** |
+| **4. 공용부 전기·수도·정기청소·소방** | **¥144,000** | 1.64% | 공용등 전기·공용 수도·월 2회 순회청소 및 소방점검 (월 1.2만 엔) |
+| **5. 화재·지진보험 + 옹벽 배상책임특약** | **¥90,000** | 1.03% | **목조 준내화구조(`準耐火構造`) 할인 적용** + 시설소유관리자 배상책임특약(옹벽) |
+| **6. 퇴거 원상복구비·장기수선·옹벽점검 적립** | **¥550,000** | 6.28% | 퇴거 원상복구·AD 충당(연 25만) + 외벽·지붕·옹벽 배수공 유지적립(연 30만) |
+| **실질 운영경비 (Normalized OPEX) 합계** | **¥1,890,040** | **21.58%** | **만실 순영업소득 (NOI) = ¥6,869,960 (≒ ¥6,870,000, 실질 Cap Rate 5.10%)** |
+---
+### 5.2 금융 조달 및 매수가·임대료별 스트레스 테스트 (LTV 85%, 금리 2.3%, 기간 30년)
+설계·건설 주택성능평가 **열화대책등급 3급** 취득에 따른 **30년 원리금균등상환(금리 2.3%)** 기준 시나리오 비교입니다:
+| 구분 시나리오 | 매매가격 | 대출금액 (85%) | 연간 총수입 (GPI) | 실질 NOI | 연간 원리금 (ADS) | **만실 세전 CF** | **DSCR** | **손익분기 가동률 (허용공실)** |
+| :--- | :---: | :---: | :---: | :---: | :---: | :---: | :---: | :---: |
+| **① 기본안 (호가 1.347억 · 상정임대료)** | ¥134,700,000 | ¥114,495,000 | ¥8,760,000 | ¥6,870,000 | ¥5,287,219 | **+¥1,582,781** | **1.30배** | **81.93% (1.63실 / 9실)** |
+| **② 임대료 -5% 보수안 (호가 1.347억)** | ¥134,700,000 | ¥114,495,000 | ¥8,322,000 | ¥6,453,900 | ¥5,287,219 | **+¥1,166,681** | **1.22배** | **85.98% (1.26실 / 9실)** |
+| **③ 1차 네고안 (1.27억 · 상정임대료)** | ¥127,000,000 | ¥107,950,000 | ¥8,760,000 | ¥6,870,000 | ¥4,984,980 | **+¥1,885,020** | **1.38배** | **78.48% (1.94실 / 9실)** |
+| **④ 공격적 네고안 (1.24억 · 상정임대료)** | **¥124,000,000** | **¥105,400,000** | ¥8,760,000 | ¥6,870,000 | **¥4,867,225** | **+¥2,002,775** | **1.41배** | **77.14% (2.06실 / 9실)** |
+| **⑤ 공격적 네고 + 임대료 -5% 복합안** | **¥124,000,000** | **¥105,400,000** | ¥8,322,000 | ¥6,453,900 | **¥4,867,225** | **+¥1,586,675** | **1.33배** | **80.96% (1.71실 / 9실)** |
+---</t>
+        </is>
+      </c>
+      <c r="F116" s="0" t="inlineStr">
+        <is>
+          <t>| 決算書コア指標 | 本物件単体 (稼働93%) | モアビズ4期現在 | **取得後決算着地** | **1.24億指値時単体** | 財務貢献度および判定 |
+| :--- | :---: | :---: | :---: | :---: | :--- |
+| **固定資産税評価額 (土地+建物)** | **3,699万 + 2,663万 = 6,361万** | 7,186万 + 4,191万 = 1.138億 | **1.088億 + 6,853万 = 1.774億** | **6,361万円** | R8公課証明書実測値を100%反映 |
+| **1. 帳簿上税引前当期純利益** | **+¥2,955,270** | +¥3,722,450 | **+¥6,677,720 (+79.4%)** | **+¥3,384,100** | **法人黒字規模 +79.4%大幅増益！** |
+| **2. 税引前手残りCF (利回り)** | **+¥1,246,795 (0.93%)** | +¥1,741,901 (0.65%) | **+¥2,988,696 (+71.6%)** | **+¥1,666,550 (1.34%)** | 満室時は単体税引前CF +158.3万円 |
+| **3. 推定法人税額 (25%)** | ▲¥738,818 | ▲¥930,613 | **▲¥1,669,430** | ▲¥846,025 | 22年新築減価償却(年251万)節税 |
+| **4. 税引後手残りCF (利回り)** | **+¥507,977 (0.38%)** | +¥811,289 (0.30%) | **+¥1,319,266 (+62.6%)** | **+¥820,525 (0.66%)** | 法人税引後キャッシュ +62.6%純増 |
+| **5. 債務償還年数 (C)** | **24.2年** (融資30年以内) | 24.1年 | **24.2年** | **20.5年** | **単体24.2年 $\ll$ 融資30.0年 ゴールデンクロス！** |
+| **6. 利子支払倍率 (ICR)** | **1.54倍** | 0.90倍 | **1.05倍 (+0.15倍)** | **1.77倍** | **法人統合ICR 1.0倍突破達成！** |
+| **7. 負債返済余裕率 (DSCR)** | **1.53倍 (満室1.30倍)** | 1.50倍 | **1.51倍 (+0.01倍)** | **1.66倍 (満室1.41倍)** | **法人統合DSCR上昇に貢献！** |
+| **8. 固定資産税評価LTV** | **218.01%** (単純合算180.0%) | 261.08% | **245.45% (▲15.63%p改善)** | **200.69%** | **公課証明書基準でも法人LTV ▲15.63%p改善！** |
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B117" s="0">
+        <v>6</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>모아비즈 4기 결산서 디자인형 적합성 분석 (Moabiz Corporate Landing)</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="inlineStr">
+        <is>
+          <t>総合スコアカード（19.5 / 30点：条件付検討）および最終提言</t>
+        </is>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>**령화 8년도 공과증명서 실측 토지 평가액(`36,985,271円`)** 및 **건물 평가액(`26,627,700円`)**을 반영한 모아비즈 4기 결산서 착지 시뮬레이션(가동률 93% 보수적 기준, 결산 경비율 19.8%, 건물 비중 41%, 감가상각 22년 = 연 251.0만 엔) 결과입니다:
+| 핵심 결산 지표 | 본 물건 단품 (93% 가동) | 모아비즈 4기 현재 | **편입 후 결산서 착지** | **1.24억 네고 시 단품** | 재무적 기여도 및 판정 |
+| :--- | :---: | :---: | :---: | :---: | :--- |
+| **자산 총액 / 총 차입금** | 1.347억 / 1.145억 | 2.675억 / 2.407억 | **4.022억 / 3.552억** | 1.240억 / 1.054억 | 우량 신축 자산 편입으로 외형 확대 |
+| **고정자산세 평가액 (토지+건물)** | **3,699만 + 2,663만 = 6,361만** | 7,186만 + 4,191만 = 1.138억 | **1.088억 + 6,853만 = 1.774억** | **6,361만 엔** | R8 공과증명서 실측치 100% 반영 |
+| **1. 장부상 세전 당기순이익** | **+¥2,955,270** | +¥3,722,450 | **+¥6,677,720 (+79.4%)** | **+¥3,384,100** | **법인 흑자 규모 +79.4% 점프업!** |
+| **2. 세전 잔여 CF (수익률)** | **+¥1,246,795 (0.93%)** | +¥1,741,901 (0.65%) | **+¥2,988,696 (+71.6%)** | **+¥1,666,550 (1.34%)** | 만실 시 단품 세전 CF +158.3만 엔 |
+| **3. 추정 법인세액 (25%)** | ▲¥738,818 | ▲¥930,613 | **▲¥1,669,430** | ▲¥846,025 | 22년 신축 감가상각(연 251만) 절세 |
+| **4. 세후 잔여 CF (수익률)** | **+¥507,977 (0.38%)** | +¥811,289 (0.30%) | **+¥1,319,266 (+62.6%)** | **+¥820,525 (0.66%)** | 법인 세후 잉여현금 +62.6% 순증 |
+| **5. 채무상환연수 (C)** | **24.2년** (융자 30년 이내) | 24.1년 | **24.2년** | **20.5년** | **단품 24.2년 $\ll$ 융자 30.0년 골든크로스!** |
+| **6. 이자보상배율 (ICR)** | **1.54배** | 0.90배 | **1.05배 (+0.15배)** | **1.77배** | **법인 통합 ICR 1.0배 돌파 달성!** |
+| **7. 부채상환여유율 (DSCR)** | **1.53배 (만실 1.30배)** | 1.50배 | **1.51배 (+0.01배)** | **1.66배 (만실 1.41배)** | **법인 통합 DSCR 상승 기여!** |
+| **8. 고정자산세 평가 LTV** | **218.01%** (단순합산 180.0%) | 261.08% | **245.45% (▲15.63%p 개선)** | **200.69%** | **공과증명서 실측 기준으로도 법인 LTV ▲15.63%p 개선!** |
+---</t>
+        </is>
+      </c>
+      <c r="F117" s="0" t="inlineStr">
+        <is>
+          <t>| 評価項目 (配点) | 1次スコア | **2次確定スコア** | 評価根拠 |
+| :--- | :---: | :---: | :--- |
+| **1. 価格・積算価値 (5点)** | 4.0 | **3.5 / 5.0** | 120.3坪宅地（路線価標準積算88.4%）は優秀だが、公課証明書評価額（3,698.5万円）に表れた高低差・階段接道補正（-20%補正時71.8%）を反映 |
+| **2. 賃貸需要・立地 (5点)** | 4.0 | **3.5 / 5.0** | 全9戸`1LDK(26.89㎡)＋ロフト(5戸)`は強いが、実測徒歩10分および前面道路の階段区間を反映 |
+| **3. 賃料競争力 (5点)** | 3.5 | **3.0 / 5.0** | 近隣成約50件（徒歩3分新築1Kが7.3〜7.8万円）対比で想定賃料（7.8〜8.5万円）は上限水準のため、1LDK訴求と初期ADバッファが必要 |
+| **4. 出口戦略 (5点)** | 4.0 | **3.5 / 5.0** | 120.3坪の土地と劣化3級は強みだが、東・北側の無検査既存擁壁（98.84㎡）が将来売却時の審査ハードルとなり得る |
+| **5. CF・DSCR (5点)** | 3.5 | **3.5 / 5.0** | 劣化3級30年融資でDSCR 1.30倍、土地固都税特例（年12.3万円）により実質NOI 687万円（Cap 5.10%）を堅守 |
+| **6. 法的・物理的安定性 (5点)** | 3.5 | **2.5 / 5.0** | 前面道路100%公道確定および7.0m基礎杭（安息角45°対応）はプラスだが、**東・北側既存擁壁（98.84㎡）検査済証なし＆北西角の土砂災害警戒区域抵触**により減点 |
+| **合計スコア・総合判定** | 22.5 / 30 | **19.5 / 30点** | **【条件付検討（擁壁・賃料リスクを織り込んだ1.23〜1.25億円への指値交渉必須）】** |</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B118" s="0">
+        <v>7</v>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>35개 표준 실사 체크리스트 완결성 감사 (Data Collection Audit: 94.3% 완료!)</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="inlineStr">
+        <is>
+          <t>35標準DDチェックリスト監査 (94.3%完了)</t>
+        </is>
+      </c>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t>이번 `20260925 OKD 三ツ境` 구글 드라이브 폴더(11개 파일) 수령을 통해 **35개 표준 실사 항목 중 33개(94.3%)가 공식 공부 및 설계도서로 검증 완료(`VERIFIED`/`COLLECTED`)**되었습니다!
+| 구분 | 1차 분석 시점 (마이소쿠 단독) | **2차 업데이트 현시점 (드라이브 11종 반영 후)** | 주요 해결 내역 |
+| :--- | :---: | :---: | :--- |
+| **수집/검증 완료 (`VERIFIED`/`COLLECTED`)** | 23건 | **33건 (94.3%)** | ✅ 등기부등본(갑·을구), ✅ R8 공과증명서(토지 2필지), ✅ 확정측량도, ✅ 현황평면도·옹벽면적도, ✅ 실시설계도(배치·평면·입면·단면·7m파일), ✅ 인정노선도 2종, ✅ 토사재해 하저드맵, ✅ REINS 성약 50건, ✅ 무료 WiFi 비용(월 7,920엔)·준공일(12월 말) |
+| **추정 적용 (`ESTIMATED`)** | 9건 | **2건 (5.7%)** | ⚠️ 건물분 고정자산세 본칙 세액(준공 후 가옥조사 시 확정, 현재 오카다상 45만 엔 추정), ⚠️ 초기 리싱 달성 임대료 및 실제 AD(광고료)개월 수 |
+| **미수집 (`MISSING`)** | 3건 | **0건 (0.0%)** | (미수집 항목 전수 해소 완료!) |
+---</t>
+        </is>
+      </c>
+      <c r="F118" s="0" t="inlineStr">
+        <is>
+          <t>이번 `20260925 OKD 三ツ境` 구글 드라이브 폴더(11개 파일) 수령을 통해 **35개 표준 실사 항목 중 33개(94.3%)가 공식 공부 및 설계도서로 검증 완료(`VERIFIED`/`COLLECTED`)**되었습니다!
+| 구분 | 1차 분석 시점 (마이소쿠 단독) | **2차 업데이트 현시점 (드라이브 11종 반영 후)** | 주요 해결 내역 |
+| :--- | :---: | :---: | :--- |
+| **수집/검증 완료 (`VERIFIED`/`COLLECTED`)** | 23건 | **33건 (94.3%)** | ✅ 등기부등본(갑·을구), ✅ R8 공과증명서(토지 2필지), ✅ 확정측량도, ✅ 현황평면도·옹벽면적도, ✅ 실시설계도(배치·평면·입면·단면·7m파일), ✅ 인정노선도 2종, ✅ 토사재해 하저드맵, ✅ REINS 성약 50건, ✅ 무료 WiFi 비용(월 7,920엔)·준공일(12월 말) |
+| **추정 적용 (`ESTIMATED`)** | 9건 | **2건 (5.7%)** | ⚠️ 건물분 고정자산세 본칙 세액(준공 후 가옥조사 시 확정, 현재 오카다상 45만 엔 추정), ⚠️ 초기 리싱 달성 임대료 및 실제 AD(광고료)개월 수 |
+| **미수집 (`MISSING`)** | 3건 | **0건 (0.0%)** | (미수집 항목 전수 해소 완료!) |
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B119" s="0">
+        <v>8</v>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>종합 스코어카드 (30점 만점) 및 최종 의사결정 권고</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="inlineStr">
+        <is>
+          <t>総合スコアカード (19.5/30点) および提言</t>
+        </is>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t>| 평가 영역 (배점) | 1차 점수 | **2차 확정 점수** | 변경 사유 및 핵심 근거 |
+| :--- | :---: | :---: | :--- |
+| **1. 가격 및 적산가치 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 택지(표준 노선가 적산 88.4%)는 탁월하나, 공과증명서상 토지 평가액(3,698.5만 엔)에 반영된 고저차·계단 접도 감가(-20% 보정 시 적산 71.8%)를 반영하여 0.5점 조정 |
+| **2. 임차 수요 및 입지 (5점)** | 4.0 | **3.5 / 5.0** | 미츠쿄역 급행 정차 및 전 세대 `1LDK(26.89㎡)+로프트(5실)` 평면은 우수하나, 실측 도보 10분 및 남서측 전면도로 계단 구간 존재를 반영하여 0.5점 조정 |
+| **3. 임대료 경쟁력 (5점)** | 3.5 | **3.0 / 5.0** | REINS 성약 50건 대조 결과, 도보 3분 신축 1K(7.3~7.8만 엔) 대비 본건(7.8~8.5만 엔)은 1LDK+로프트 감안 시에도 지역 시세 상단에 해당하여 초기 리싱 버퍼 필요 |
+| **4. 출구 전략 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 토지 및 열화 3급은 장기 매각에 유리하나, 동·북측 미검사 기존 옹벽(98.84㎡)이 차기 매수자 실사 시 허들로 작용 가능 |
+| **5. 현금흐름 및 DSCR (5점)** | 3.5 | **3.5 / 5.0** | 열화 3급 30년 융자 시 DSCR 1.30배, 토지 보유세 특례(연 12.3만 엔) 덕분에 실질 NOI 687만 엔(Cap 5.10%) 견고 유지 |
+| **6. 법적·물리적 안정성 (5점)** | 3.5 | **2.5 / 5.0** | 전면도로 100% 공도 확정 및 건물 7.0m 파일 기초(안식각 45° 대응)는 긍정적이나, **동·북측 기존 옹벽(98.84㎡) 검사필증 부재 및 북서측 토사재해 구역 일부 저촉**으로 1.0점 감점 |
+| **총점 및 종합 등급** | 22.5 / 30 | **19.5 / 30점** | **【조건부 검토 (옹벽·임대료 리스크 반영 공격적 지값 필수)】** |
+### 🎯 매수 실행을 위한 4대 실전 액션 플랜
+1. **준공 시점(2026.12 말)을 활용한 공격적 지값(1.23억~1.25억 엔) 협상**:
+   - 매도자(야오키상사)가 카와사키신용금고로부터 **7,700만 엔을 연 3.05% 고금리**로 조달 중이며 준공이 12월 말(인도 2027년 1월)로 지연된 점을 활용하여, 미검사 기존 옹벽 리스크 인수 조건으로 **1억 2,300만 ~ 1억 2,500만 엔(수익률 7.0~7.1%)** 지값 협상을 추진하십시오.
+2. **『7.00m 기초 파일 시공보고서·지반조사서』 및 『건설주택성능평가서(열화 3급)』 징구 특약**:
+   - 잔금 결제(2027년 1월) 전 인도 서류 목록에 ① 벼랑조례 대응 **7.00m 파일 시공 사진·시공보고서**, ② **건설주택성능평가서(열화대책등급 3급)**, ③ **검사필증(건축물)**을 필수 조건으로 명시하십시오.
+3. **옹벽 배수공 정기 관리 및 시설소유관리자 배상책임보험 가입**:
+   - 동·북측 간지블록 옹벽(98.84㎡)의 수압 상승을 막기 위해 배수공(水抜き穴) 청소 및 균열 점검을 연 1회 실시하고, 화재·지진보험 가입 시 반드시 **옹벽 붕괴 배상책임 특약**을 부가하십시오.
+4. **포털 리싱 시 『1LDK(2인 입주 가능) + 4.82㎡ 로프트 + 무료 WiFi』 카테고리 등록 지시**:
+   - 일반 1R/1K 검색 필터가 아닌 **1DK/1LDK 및 2인 입주 가능(二人入居可) 필터**에 노출시켜 미츠쿄역 역세권 1K 신축(7.3~7.8만 엔)과의 단순 가격 경쟁을 피하고 2027년 1~3월 성수기 조기 만실을 달성하십시오.</t>
+        </is>
+      </c>
+      <c r="F119" s="0" t="inlineStr">
+        <is>
+          <t>| 평가 영역 (배점) | 1차 점수 | **2차 확정 점수** | 변경 사유 및 핵심 근거 |
+| :--- | :---: | :---: | :--- |
+| **1. 가격 및 적산가치 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 택지(표준 노선가 적산 88.4%)는 탁월하나, 공과증명서상 토지 평가액(3,698.5만 엔)에 반영된 고저차·계단 접도 감가(-20% 보정 시 적산 71.8%)를 반영하여 0.5점 조정 |
+| **2. 임차 수요 및 입지 (5점)** | 4.0 | **3.5 / 5.0** | 미츠쿄역 급행 정차 및 전 세대 `1LDK(26.89㎡)+로프트(5실)` 평면은 우수하나, 실측 도보 10분 및 남서측 전면도로 계단 구간 존재를 반영하여 0.5점 조정 |
+| **3. 임대료 경쟁력 (5점)** | 3.5 | **3.0 / 5.0** | REINS 성약 50건 대조 결과, 도보 3분 신축 1K(7.3~7.8만 엔) 대비 본건(7.8~8.5만 엔)은 1LDK+로프트 감안 시에도 지역 시세 상단에 해당하여 초기 리싱 버퍼 필요 |
+| **4. 출구 전략 (5점)** | 4.0 | **3.5 / 5.0** | 120.3평 토지 및 열화 3급은 장기 매각에 유리하나, 동·북측 미검사 기존 옹벽(98.84㎡)이 차기 매수자 실사 시 허들로 작용 가능 |
+| **5. 현금흐름 및 DSCR (5점)** | 3.5 | **3.5 / 5.0** | 열화 3급 30년 융자 시 DSCR 1.30배, 토지 보유세 특례(연 12.3만 엔) 덕분에 실질 NOI 687만 엔(Cap 5.10%) 견고 유지 |
+| **6. 법적·물리적 안정성 (5점)** | 3.5 | **2.5 / 5.0** | 전면도로 100% 공도 확정 및 건물 7.0m 파일 기초(안식각 45° 대응)는 긍정적이나, **동·북측 기존 옹벽(98.84㎡) 검사필증 부재 및 북서측 토사재해 구역 일부 저촉**으로 1.0점 감점 |
+| **총점 및 종합 등급** | 22.5 / 30 | **19.5 / 30점** | **【조건부 검토 (옹벽·임대료 리스크 반영 공격적 지값 필수)】** |
+### 🎯 매수 실행을 위한 4대 실전 액션 플랜
+1. **준공 시점(2026.12 말)을 활용한 공격적 지값(1.23억~1.25억 엔) 협상**:
+   - 매도자(야오키상사)가 카와사키신용금고로부터 **7,700만 엔을 연 3.05% 고금리**로 조달 중이며 준공이 12월 말(인도 2027년 1월)로 지연된 점을 활용하여, 미검사 기존 옹벽 리스크 인수 조건으로 **1억 2,300만 ~ 1억 2,500만 엔(수익률 7.0~7.1%)** 지값 협상을 추진하십시오.
+2. **『7.00m 기초 파일 시공보고서·지반조사서』 및 『건설주택성능평가서(열화 3급)』 징구 특약**:
+   - 잔금 결제(2027년 1월) 전 인도 서류 목록에 ① 벼랑조례 대응 **7.00m 파일 시공 사진·시공보고서**, ② **건설주택성능평가서(열화대책등급 3급)**, ③ **검사필증(건축물)**을 필수 조건으로 명시하십시오.
+3. **옹벽 배수공 정기 관리 및 시설소유관리자 배상책임보험 가입**:
+   - 동·북측 간지블록 옹벽(98.84㎡)의 수압 상승을 막기 위해 배수공(水抜き穴) 청소 및 균열 점검을 연 1회 실시하고, 화재·지진보험 가입 시 반드시 **옹벽 붕괴 배상책임 특약**을 부가하십시오.
+4. **포털 리싱 시 『1LDK(2인 입주 가능) + 4.82㎡ 로프트 + 무료 WiFi』 카테고리 등록 지시**:
+   - 일반 1R/1K 검색 필터가 아닌 **1DK/1LDK 및 2인 입주 가능(二人入居可) 필터**에 노출시켜 미츠쿄역 역세권 1K 신축(7.3~7.8만 엔)과의 단순 가격 경쟁을 피하고 2027년 1~3월 성수기 조기 만실을 달성하십시오.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B120" s="0">
+        <v>9</v>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>입지·도보 10분(계단 접도)·토사재해 하저드 검증</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="inlineStr">
+        <is>
+          <t>立地・実測徒歩10分(階段接道)・土砂災害検証</t>
+        </is>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t>챕터 9 상세 분석은 본문 참조</t>
+        </is>
+      </c>
+      <c r="F120" s="0" t="inlineStr">
+        <is>
+          <t>챕터 9 상세 분석은 본문 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t>mitsukyo-1ap</t>
+        </is>
+      </c>
+      <c r="B121" s="0">
+        <v>10</v>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>최종 투자 의사결정 요약</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t>最終投資意思決定サマリー</t>
+        </is>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>챕터 10 상세 분석은 본문 참조</t>
+        </is>
+      </c>
+      <c r="F121" s="0" t="inlineStr">
+        <is>
+          <t>챕터 10 상세 분석은 본문 참조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/moabiz/data/real_estate_datastore.xlsx
+++ b/moabiz/data/real_estate_datastore.xlsx
@@ -6318,391 +6318,898 @@
           <t>True</t>
         </is>
       </c>
-      <c r="E13" s="0">
-        <v>94.3</v>
-      </c>
-      <c r="F13" s="0">
-        <v>33</v>
-      </c>
-      <c r="G13" s="0">
-        <v>2</v>
-      </c>
-      <c r="H13" s="0">
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>FULL_DD (정밀실사완료)</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>미츠쿄 1AP 사사노다이 (三ツ境1AP)</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>三ツ境1AP（横浜市旭区笹野台）</t>
+        </is>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
+        <is>
+          <t>神奈川県横浜市旭区笹野台2丁目19-5</t>
+        </is>
+      </c>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>神奈川県横浜市旭区笹野台二丁目149番3、231番102</t>
+        </is>
+      </c>
+      <c r="N13" s="0" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
+        </is>
+      </c>
+      <c r="O13" s="0" t="inlineStr">
+        <is>
+          <t>134700000</t>
+        </is>
+      </c>
+      <c r="P13" s="0" t="inlineStr">
+        <is>
+          <t>1억 3,470만 엔</t>
+        </is>
+      </c>
+      <c r="Q13" s="0" t="inlineStr">
+        <is>
+          <t>세금포함 (건물 소비세 포함 확인완료)</t>
+        </is>
+      </c>
+      <c r="R13" s="0" t="inlineStr">
+        <is>
+          <t>중개 (媒介 · 무브업)</t>
+        </is>
+      </c>
+      <c r="S13" s="0" t="inlineStr">
+        <is>
+          <t>2026년 12월 말 준공 / 2027년 1월 신축 인도 (계약금 보전조치 불요 범위)</t>
+        </is>
+      </c>
+      <c r="T13" s="0" t="inlineStr">
+        <is>
+          <t>397.71</t>
+        </is>
+      </c>
+      <c r="U13" s="0" t="inlineStr">
+        <is>
+          <t>120.3</t>
+        </is>
+      </c>
+      <c r="V13" s="0" t="inlineStr">
+        <is>
+          <t>소유권 (所有権)</t>
+        </is>
+      </c>
+      <c r="W13" s="0" t="inlineStr">
+        <is>
+          <t>택지 (宅地 · 등기 399.56㎡ / 확정측량 유효 397.42㎡ + 후퇴 0.29㎡)</t>
+        </is>
+      </c>
+      <c r="X13" s="0" t="inlineStr">
+        <is>
+          <t>고대(高台) 평탄지 (주변 대비 4.0~4.69m 단차 · 동·북측 기존 간지블록 옹벽 98.84㎡ 검사필증 없음 / 7.0m 파일 시공으로 벼랑조례 안식각 45° 대응)</t>
+        </is>
+      </c>
+      <c r="Y13" s="0" t="inlineStr">
+        <is>
+          <t>시가지화구역 (市街化区域)</t>
+        </is>
+      </c>
+      <c r="Z13" s="0" t="inlineStr">
+        <is>
+          <t>제1종 저층주거전용지역 · 제1종 고도지구</t>
+        </is>
+      </c>
+      <c r="AA13" s="0" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AB13" s="0" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="0" t="inlineStr">
+        <is>
+          <t>39.57</t>
+        </is>
+      </c>
+      <c r="AD13" s="0" t="inlineStr">
+        <is>
+          <t>60.92</t>
+        </is>
+      </c>
+      <c r="AE13" s="0" t="inlineStr">
+        <is>
+          <t>법22조구역 · 목조 준내화구조(準耐火構造)</t>
+        </is>
+      </c>
+      <c r="AF13" s="0" t="inlineStr">
+        <is>
+          <t>남서측 폭원 3.92~4.50m 요코하마시 공도(下川井第402号線, 일부 계단) 및 서측 폭원 4.00~5.50m 요코하마시 공도(下川井第398号線) 접도</t>
+        </is>
+      </c>
+      <c r="AG13" s="0" t="inlineStr">
+        <is>
+          <t>없음 (등기부 지번 231-1 요코하마시 소유 공중용도로 및 인정노선도 100% 공도 검증완료)</t>
+        </is>
+      </c>
+      <c r="AH13" s="0" t="inlineStr">
+        <is>
+          <t>WOOD</t>
+        </is>
+      </c>
+      <c r="AI13" s="0" t="inlineStr">
+        <is>
+          <t>목조 준내화구조 지상 2층건 (RC베타기초+7.00m 기초파일 / 설계·건설 열화대책등급 3급)</t>
+        </is>
+      </c>
+      <c r="AJ13" s="0" t="inlineStr">
+        <is>
+          <t>2026년 12월 말 준공 예정 (2027년 1월 인도 예정)</t>
+        </is>
+      </c>
+      <c r="AK13" s="0" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL13" s="0" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AM13" s="0" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AN13" s="0" t="inlineStr">
+        <is>
+          <t>242.07</t>
+        </is>
+      </c>
+      <c r="AO13" s="0" t="inlineStr">
+        <is>
+          <t>242.07</t>
+        </is>
+      </c>
+      <c r="AP13" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ13" s="0" t="inlineStr">
+        <is>
+          <t>전 9세대 1LDK(26.89㎡: LDK8.0+양실5.5, 2인입주 가능) + 5세대(105, 201~204호) 로프트 4.82㎡</t>
+        </is>
+      </c>
+      <c r="AR13" s="0" t="inlineStr">
+        <is>
+          <t>없음 (전면도로 계단 직전까지 차량 접근 가능)</t>
+        </is>
+      </c>
+      <c r="AS13" s="0" t="inlineStr">
+        <is>
+          <t>유 (제26UDI1K건00271호, R8.6.18 교부 확인필증 사본 완비)</t>
+        </is>
+      </c>
+      <c r="AT13" s="0" t="inlineStr">
+        <is>
+          <t>신축 건축중 (2026.12 말 준공 시 건축물 검사필증 및 건설주택성능평가서 열화3급 교부 예정 / 단, 기존 옹벽은 검사필증 없음)</t>
+        </is>
+      </c>
+      <c r="AU13" s="0" t="inlineStr">
+        <is>
+          <t>도시가스 (都市ガス 완비)</t>
+        </is>
+      </c>
+      <c r="AV13" s="0" t="inlineStr">
+        <is>
+          <t>공영수도·공공하수·무료WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정 확인완료)</t>
+        </is>
+      </c>
+      <c r="AW13" s="0" t="inlineStr">
+        <is>
+          <t>무 (2층 저층형)</t>
+        </is>
+      </c>
+      <c r="AX13" s="0" t="inlineStr">
+        <is>
+          <t>신축 완공 예정 (RC베타기초+7.0m 기초파일 시공 / 동·북측 기존 간지블록 옹벽 98.84㎡는 보강계획 없음 확인)</t>
+        </is>
+      </c>
+      <c r="AY13" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AZ13" s="0" t="inlineStr">
+        <is>
+          <t>8760000</t>
+        </is>
+      </c>
+      <c r="BA13" s="0" t="inlineStr">
+        <is>
+          <t>8760000</t>
+        </is>
+      </c>
+      <c r="BB13" s="0" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="BC13" s="0" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="BD13" s="0" t="inlineStr">
+        <is>
+          <t>1130040</t>
+        </is>
+      </c>
+      <c r="BE13" s="0" t="inlineStr">
+        <is>
+          <t>1890040</t>
+        </is>
+      </c>
+      <c r="BF13" s="0" t="inlineStr">
+        <is>
+          <t>21.58</t>
+        </is>
+      </c>
+      <c r="BG13" s="0" t="inlineStr">
+        <is>
+          <t>6869960</t>
+        </is>
+      </c>
+      <c r="BH13" s="0" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="BI13" s="0" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
+      </c>
+      <c r="BJ13" s="0" t="inlineStr">
+        <is>
+          <t>75509800</t>
+        </is>
+      </c>
+      <c r="BK13" s="0" t="inlineStr">
+        <is>
+          <t>43572600</t>
+        </is>
+      </c>
+      <c r="BL13" s="0" t="inlineStr">
+        <is>
+          <t>88.41</t>
+        </is>
+      </c>
+      <c r="BM13" s="0" t="inlineStr">
+        <is>
+          <t>36985271</t>
+        </is>
+      </c>
+      <c r="BN13" s="0" t="inlineStr">
+        <is>
+          <t>26627700</t>
+        </is>
+      </c>
+      <c r="BO13" s="0" t="inlineStr">
+        <is>
+          <t>573,283엔 (R8 토지 공과증명서 주택특례 약 12.3만 엔 + 건물 오카다상 확인 약 45만 엔 추정)</t>
+        </is>
+      </c>
+      <c r="BP13" s="0" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="BQ13" s="0" t="inlineStr">
+        <is>
+          <t>114495000</t>
+        </is>
+      </c>
+      <c r="BR13" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="BS13" s="0" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BT13" s="0" t="inlineStr">
+        <is>
+          <t>5287219</t>
+        </is>
+      </c>
+      <c r="BU13" s="0" t="inlineStr">
+        <is>
+          <t>1582741</t>
+        </is>
+      </c>
+      <c r="BV13" s="0" t="inlineStr">
+        <is>
+          <t>1246795</t>
+        </is>
+      </c>
+      <c r="BW13" s="0" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="BX13" s="0" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BY13" s="0" t="inlineStr">
+        <is>
+          <t>81.93</t>
+        </is>
+      </c>
+      <c r="BZ13" s="0" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="CA13" s="0" t="inlineStr">
+        <is>
+          <t>31497300</t>
+        </is>
+      </c>
+      <c r="CB13" s="0" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="CC13" s="0" t="inlineStr">
+        <is>
+          <t>소테츠 본선(급행 정차) 「미츠쿄(三ツ境)」역 구글맵 실측 도보 10분 (약 720m, 마이소쿠 표기 7분)</t>
+        </is>
+      </c>
+      <c r="CD13" s="0" t="inlineStr">
+        <is>
+          <t>도보 7분 (마이소쿠 표기)</t>
+        </is>
+      </c>
+      <c r="CE13" s="0" t="inlineStr">
+        <is>
+          <t>실측 도보 10분 (구글맵 및 오카다상 현장 확인완료)</t>
+        </is>
+      </c>
+      <c r="CF13" s="0" t="inlineStr">
+        <is>
+          <t>720m (구글맵 실측완료)</t>
+        </is>
+      </c>
+      <c r="CG13" s="0" t="inlineStr">
+        <is>
+          <t>사사노다이 상점가 경유 후 남서측 전면도로(下川井第402号線) 진입부에 계단 구간 및 부지 고저차(4.0~4.69m) 존재 확인완료</t>
+        </is>
+      </c>
+      <c r="CH13" s="0" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
+        </is>
+      </c>
+      <c r="CI13" s="0" t="inlineStr">
+        <is>
+          <t>고대(高台) 입지로 홍수·내수 침수 해저드 해당 없음 (교차검증 완료)</t>
+        </is>
+      </c>
+      <c r="CJ13" s="0" t="inlineStr">
+        <is>
+          <t>부지 북서측 모서리 옹벽 부분(가측량도 약 4.69㎡)이 토사재해경계구역(옐로우존/잠정 레드존 경계)에 일부 저촉 확인완료 (건물 본체는 2m 이격되어 구역 외)</t>
+        </is>
+      </c>
+      <c r="CK13" s="0" t="inlineStr">
+        <is>
+          <t>https://www.homes.co.jp/archive/b-36020804/</t>
+        </is>
+      </c>
+      <c r="CL13" s="0" t="inlineStr">
+        <is>
+          <t>30~45일 (REINS 근린 성약 50건 및 일 피오레 사사노다이 교차검증 완료)</t>
+        </is>
+      </c>
+      <c r="CM13" s="0" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="CN13" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO13" s="0" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="CP13" s="0" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="CQ13" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CR13" s="0" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="CS13" s="0" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="CT13" s="0" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="CU13" s="0" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CV13" s="0" t="inlineStr">
+        <is>
+          <t>조건부 검토</t>
+        </is>
+      </c>
+      <c r="CW13" s="0" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="CX13" s="0" t="inlineStr">
+        <is>
+          <t>적합 / 조건부 편입 (ICR 1.05배 돌파·LTV -15.6%p 개선 / 단, 미검사 옹벽·토사재해 저촉 반영 1.24억 네고 필수)</t>
+        </is>
+      </c>
+      <c r="CY13" s="0" t="inlineStr">
+        <is>
+          <t>적합 / 조건부 검토 (120.3평 택지·1LDK+로프트·열화3급 30년 융자 우수하나 기존 옹벽·임대료 상단 리스크 반영 지값 협상 필수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E14" s="0">
+        <v>51.4</v>
+      </c>
+      <c r="F14" s="0">
+        <v>18</v>
+      </c>
+      <c r="G14" s="0">
+        <v>5</v>
+      </c>
+      <c r="H14" s="0">
+        <v>12</v>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>MAISOKU_ONLY (마이소쿠단계)</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>시엘 블루 치바추오</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>Ciel Bleu 千葉中央</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t>千葉県千葉市中央区松波1丁目19-12</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (주거표시 千葉県千葉市中央区松波1丁目19-12 — 지번은 등기부 확인 필요)</t>
+        </is>
+      </c>
+      <c r="N14" s="0" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%E6%9D%BE%E6%B3%A21%E4%B8%81%E7%9B%AE19-12</t>
+        </is>
+      </c>
+      <c r="O14" s="0">
+        <v>222000000</v>
+      </c>
+      <c r="P14" s="0" t="inlineStr">
+        <is>
+          <t>2억 2,200만 엔</t>
+        </is>
+      </c>
+      <c r="Q14" s="0" t="inlineStr">
+        <is>
+          <t>비과세 (주거용 1K 16호 — 부지 내 주차장 등 과세매출 유무 확인 필요)</t>
+        </is>
+      </c>
+      <c r="R14" s="0" t="inlineStr">
+        <is>
+          <t>중개 (媒介)</t>
+        </is>
+      </c>
+      <c r="S14" s="0" t="inlineStr">
+        <is>
+          <t>상담 (相談 — 계약부적합책임 면책 특약 유무 확인 필요)</t>
+        </is>
+      </c>
+      <c r="T14" s="0">
+        <v>185.88</v>
+      </c>
+      <c r="U14" s="0">
+        <v>56.23</v>
+      </c>
+      <c r="V14" s="0" t="inlineStr">
+        <is>
+          <t>소유권 (所有権)</t>
+        </is>
+      </c>
+      <c r="W14" s="0" t="inlineStr">
+        <is>
+          <t>택지 (宅地 — 소규모주택용지 16호×200㎡ 한도 내 100% 1/6 감면 특례 대상)</t>
+        </is>
+      </c>
+      <c r="X14" s="0" t="inlineStr">
+        <is>
+          <t>평탄지 (平坦地)</t>
+        </is>
+      </c>
+      <c r="Y14" s="0" t="inlineStr">
+        <is>
+          <t>시가화구역 (市街化区域)</t>
+        </is>
+      </c>
+      <c r="Z14" s="0" t="inlineStr">
+        <is>
+          <t>제1종주거지역 (第一種住居地域)</t>
+        </is>
+      </c>
+      <c r="AA14" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="AB14" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="AC14" s="0">
+        <v>53.6</v>
+      </c>
+      <c r="AD14" s="0">
+        <v>193.56</v>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (준방화지역 또는 법22조구역 여부 건축확인대장 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (마이소쿠 접도 방향·폭원 미기재 — 도로대장 및 현지 실측 필요)</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (사도부담 유무 중요사항설명서 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AH14" s="0" t="inlineStr">
+        <is>
+          <t>S_HEAVY</t>
+        </is>
+      </c>
+      <c r="AI14" s="0" t="inlineStr">
+        <is>
+          <t>철골조 지상 4층 건 (鉄骨造 4階建)</t>
+        </is>
+      </c>
+      <c r="AJ14" s="0" t="inlineStr">
+        <is>
+          <t>2011년 2월 (平成23年2月)</t>
+        </is>
+      </c>
+      <c r="AK14" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="AL14" s="0">
+        <v>34</v>
+      </c>
+      <c r="AM14" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="AN14" s="0">
+        <v>359.79</v>
+      </c>
+      <c r="AO14" s="0">
+        <v>359.79</v>
+      </c>
+      <c r="AP14" s="0">
+        <v>16</v>
+      </c>
+      <c r="AQ14" s="0" t="inlineStr">
+        <is>
+          <t>전 호실 1K (24.16㎡) × 16호 (100% 단일 평형, 만실 가동 중)</t>
+        </is>
+      </c>
+      <c r="AR14" s="0" t="inlineStr">
+        <is>
+          <t>주륜장 완비 (駐輪場有 — 자동차 주차장 유무 및 수입 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AS14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (2011년 2월 준공으로 보유 확실시되나 사본 징구 필수)</t>
+        </is>
+      </c>
+      <c r="AT14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (준공검사필증 사본 및 철골 두께 4mm 초과 여부 확인 필수)</t>
+        </is>
+      </c>
+      <c r="AU14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (도시가스 vs 프로판가스 여부 확인 필수)</t>
+        </is>
+      </c>
+      <c r="AV14" s="0" t="inlineStr">
+        <is>
+          <t>공영수도 · 공공하수 (추정 — 중요사항설명서 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AW14" s="0" t="inlineStr">
+        <is>
+          <t>없음 (지상 4층 건 — EV 유지보수비 절감 장점 및 4층 임차 저항 양면성)</t>
+        </is>
+      </c>
+      <c r="AX14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (준공 15년차 — 외벽도장·옥상방수 1차 대규모 수선 실시 이력 확인 필수)</t>
+        </is>
+      </c>
+      <c r="AY14" s="0">
+        <v>16</v>
+      </c>
+      <c r="AZ14" s="0">
+        <v>14475600</v>
+      </c>
+      <c r="BA14" s="0">
+        <v>14475600</v>
+      </c>
+      <c r="BB14" s="0">
+        <v>6.52</v>
+      </c>
+      <c r="BC14" s="0">
+        <v>6.52</v>
+      </c>
+      <c r="BD14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="BE14" s="0">
+        <v>3201158</v>
+      </c>
+      <c r="BF14" s="0">
+        <v>22.11</v>
+      </c>
+      <c r="BG14" s="0">
+        <v>11274442</v>
+      </c>
+      <c r="BH14" s="0">
+        <v>5.08</v>
+      </c>
+      <c r="BI14" s="0">
+        <v>345000</v>
+      </c>
+      <c r="BJ14" s="0">
+        <v>64128600</v>
+      </c>
+      <c r="BK14" s="0">
+        <v>57738094</v>
+      </c>
+      <c r="BL14" s="0">
+        <v>54.89</v>
+      </c>
+      <c r="BM14" s="0">
+        <v>56112525</v>
+      </c>
+      <c r="BN14" s="0">
+        <v>37529761</v>
+      </c>
+      <c r="BO14" s="0">
+        <v>825000</v>
+      </c>
+      <c r="BP14" s="0">
+        <v>85.0</v>
+      </c>
+      <c r="BQ14" s="0">
+        <v>188700000</v>
+      </c>
+      <c r="BR14" s="0">
+        <v>2.5</v>
+      </c>
+      <c r="BS14" s="0">
+        <v>25</v>
+      </c>
+      <c r="BT14" s="0">
+        <v>10158477</v>
+      </c>
+      <c r="BU14" s="0">
+        <v>392185</v>
+      </c>
+      <c r="BV14" s="0">
+        <v>-70747</v>
+      </c>
+      <c r="BW14" s="0">
+        <v>1.04</v>
+      </c>
+      <c r="BX14" s="0">
+        <v>1.4</v>
+      </c>
+      <c r="BY14" s="0">
+        <v>92.29</v>
+      </c>
+      <c r="BZ14" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="CA14" s="0">
+        <v>49780664</v>
+      </c>
+      <c r="CB14" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="CC14" s="0" t="inlineStr">
+        <is>
+          <t>JR 소부본선 『치바(千葉)』역 도보 12분 · JR 주오·소부완행선 『니시치바(西千葉)』역 도보 13분 · 치바 도시 모노레일 『사쿠사베(作草部)』역 도보 13분</t>
+        </is>
+      </c>
+      <c r="CD14" s="0">
+        <v>12</v>
+      </c>
+      <c r="CE14" s="0">
+        <v>12</v>
+      </c>
+      <c r="CF14" s="0">
+        <v>960</v>
+      </c>
+      <c r="CG14" s="0" t="inlineStr">
+        <is>
+          <t>대체로 평탄한 주택·문교지구 동선 (치바역 북구~마츠나미 1초메 직선 접근)</t>
+        </is>
+      </c>
+      <c r="CH14" s="0" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/%E5%8D%83%E8%91%89%E9%A7%85/%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%E6%9D%BE%E6%B3%A21%E4%B8%81%E7%9B%AE19-12/</t>
+        </is>
+      </c>
+      <c r="CI14" s="0" t="inlineStr">
+        <is>
+          <t>치바시 홍수 해저드맵 하천범람 구역 외 (국지성 호우 시 내수침수 0.1~0.5m 가능성 확인 및 수재보험 특약 권장)</t>
+        </is>
+      </c>
+      <c r="CJ14" s="0" t="inlineStr">
+        <is>
+          <t>해당 없음 (평탄한 제1종주거지역 — 토사재해 경계구역 외)</t>
+        </is>
+      </c>
+      <c r="CK14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="CL14" s="0">
+        <v>60</v>
+      </c>
+      <c r="CM14" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="CN14" s="0">
         <v>0</v>
       </c>
-      <c r="I13" s="0" t="inlineStr">
-        <is>
-          <t>FULL_DD (정밀실사완료)</t>
-        </is>
-      </c>
-      <c r="J13" s="0" t="inlineStr">
-        <is>
-          <t>미츠쿄 1AP 사사노다이 (三ツ境1AP)</t>
-        </is>
-      </c>
-      <c r="K13" s="0" t="inlineStr">
-        <is>
-          <t>三ツ境1AP（横浜市旭区笹野台）</t>
-        </is>
-      </c>
-      <c r="L13" s="0" t="inlineStr">
-        <is>
-          <t>神奈川県横浜市旭区笹野台2丁目19-5</t>
-        </is>
-      </c>
-      <c r="M13" s="0" t="inlineStr">
-        <is>
-          <t>神奈川県横浜市旭区笹野台二丁目149番3、231番102</t>
-        </is>
-      </c>
-      <c r="N13" s="0" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
-        </is>
-      </c>
-      <c r="O13" s="0">
-        <v>134700000</v>
-      </c>
-      <c r="P13" s="0" t="inlineStr">
-        <is>
-          <t>1억 3,470만 엔</t>
-        </is>
-      </c>
-      <c r="Q13" s="0" t="inlineStr">
-        <is>
-          <t>세금포함 (건물 소비세 포함 확인완료)</t>
-        </is>
-      </c>
-      <c r="R13" s="0" t="inlineStr">
-        <is>
-          <t>중개 (媒介 · 무브업)</t>
-        </is>
-      </c>
-      <c r="S13" s="0" t="inlineStr">
-        <is>
-          <t>2026년 12월 말 준공 / 2027년 1월 신축 인도 (계약금 보전조치 불요 범위)</t>
-        </is>
-      </c>
-      <c r="T13" s="0">
-        <v>397.71</v>
-      </c>
-      <c r="U13" s="0">
-        <v>120.3</v>
-      </c>
-      <c r="V13" s="0" t="inlineStr">
-        <is>
-          <t>소유권 (所有権)</t>
-        </is>
-      </c>
-      <c r="W13" s="0" t="inlineStr">
-        <is>
-          <t>택지 (宅地 · 등기 399.56㎡ / 확정측량 유효 397.42㎡ + 후퇴 0.29㎡)</t>
-        </is>
-      </c>
-      <c r="X13" s="0" t="inlineStr">
-        <is>
-          <t>고대(高台) 평탄지 (주변 대비 4.0~4.69m 단차 · 동·북측 기존 간지블록 옹벽 98.84㎡ 검사필증 없음 / 7.0m 파일 시공으로 벼랑조례 안식각 45° 대응)</t>
-        </is>
-      </c>
-      <c r="Y13" s="0" t="inlineStr">
-        <is>
-          <t>시가지화구역 (市街化区域)</t>
-        </is>
-      </c>
-      <c r="Z13" s="0" t="inlineStr">
-        <is>
-          <t>제1종 저층주거전용지역 · 제1종 고도지구</t>
-        </is>
-      </c>
-      <c r="AA13" s="0">
-        <v>40.0</v>
-      </c>
-      <c r="AB13" s="0">
-        <v>80.0</v>
-      </c>
-      <c r="AC13" s="0">
-        <v>39.57</v>
-      </c>
-      <c r="AD13" s="0">
-        <v>60.92</v>
-      </c>
-      <c r="AE13" s="0" t="inlineStr">
-        <is>
-          <t>법22조구역 · 목조 준내화구조(準耐火構造)</t>
-        </is>
-      </c>
-      <c r="AF13" s="0" t="inlineStr">
-        <is>
-          <t>남서측 폭원 3.92~4.50m 요코하마시 공도(下川井第402号線, 일부 계단) 및 서측 폭원 4.00~5.50m 요코하마시 공도(下川井第398号線) 접도</t>
-        </is>
-      </c>
-      <c r="AG13" s="0" t="inlineStr">
-        <is>
-          <t>없음 (등기부 지번 231-1 요코하마시 소유 공중용도로 및 인정노선도 100% 공도 검증완료)</t>
-        </is>
-      </c>
-      <c r="AH13" s="0" t="inlineStr">
-        <is>
-          <t>WOOD</t>
-        </is>
-      </c>
-      <c r="AI13" s="0" t="inlineStr">
-        <is>
-          <t>목조 준내화구조 지상 2층건 (RC베타기초+7.00m 기초파일 / 설계·건설 열화대책등급 3급)</t>
-        </is>
-      </c>
-      <c r="AJ13" s="0" t="inlineStr">
-        <is>
-          <t>2026년 12월 말 준공 예정 (2027년 1월 인도 예정)</t>
-        </is>
-      </c>
-      <c r="AK13" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="AL13" s="0">
-        <v>22</v>
-      </c>
-      <c r="AM13" s="0">
-        <v>22.0</v>
-      </c>
-      <c r="AN13" s="0">
-        <v>242.07</v>
-      </c>
-      <c r="AO13" s="0">
-        <v>242.07</v>
-      </c>
-      <c r="AP13" s="0">
-        <v>9</v>
-      </c>
-      <c r="AQ13" s="0" t="inlineStr">
-        <is>
-          <t>전 9세대 1LDK(26.89㎡: LDK8.0+양실5.5, 2인입주 가능) + 5세대(105, 201~204호) 로프트 4.82㎡</t>
-        </is>
-      </c>
-      <c r="AR13" s="0" t="inlineStr">
-        <is>
-          <t>없음 (전면도로 계단 직전까지 차량 접근 가능)</t>
-        </is>
-      </c>
-      <c r="AS13" s="0" t="inlineStr">
-        <is>
-          <t>유 (제26UDI1K건00271호, R8.6.18 교부 확인필증 사본 완비)</t>
-        </is>
-      </c>
-      <c r="AT13" s="0" t="inlineStr">
-        <is>
-          <t>신축 건축중 (2026.12 말 준공 시 건축물 검사필증 및 건설주택성능평가서 열화3급 교부 예정 / 단, 기존 옹벽은 검사필증 없음)</t>
-        </is>
-      </c>
-      <c r="AU13" s="0" t="inlineStr">
-        <is>
-          <t>도시가스 (都市ガス 완비)</t>
-        </is>
-      </c>
-      <c r="AV13" s="0" t="inlineStr">
-        <is>
-          <t>공영수도·공공하수·무료WiFi (오너 부담 월 7,920엔[세금포함], 10년 약정 확인완료)</t>
-        </is>
-      </c>
-      <c r="AW13" s="0" t="inlineStr">
-        <is>
-          <t>무 (2층 저층형)</t>
-        </is>
-      </c>
-      <c r="AX13" s="0" t="inlineStr">
-        <is>
-          <t>신축 완공 예정 (RC베타기초+7.0m 기초파일 시공 / 동·북측 기존 간지블록 옹벽 98.84㎡는 보강계획 없음 확인)</t>
-        </is>
-      </c>
-      <c r="AY13" s="0">
-        <v>9</v>
-      </c>
-      <c r="AZ13" s="0">
-        <v>8760000</v>
-      </c>
-      <c r="BA13" s="0">
-        <v>8760000</v>
-      </c>
-      <c r="BB13" s="0">
-        <v>6.5</v>
-      </c>
-      <c r="BC13" s="0">
-        <v>6.5</v>
-      </c>
-      <c r="BD13" s="0">
-        <v>1130040</v>
-      </c>
-      <c r="BE13" s="0">
-        <v>1890040</v>
-      </c>
-      <c r="BF13" s="0">
-        <v>21.58</v>
-      </c>
-      <c r="BG13" s="0">
-        <v>6869960</v>
-      </c>
-      <c r="BH13" s="0">
-        <v>5.1</v>
-      </c>
-      <c r="BI13" s="0">
-        <v>190000</v>
-      </c>
-      <c r="BJ13" s="0">
-        <v>75509800</v>
-      </c>
-      <c r="BK13" s="0">
-        <v>43572600</v>
-      </c>
-      <c r="BL13" s="0">
-        <v>88.41</v>
-      </c>
-      <c r="BM13" s="0">
-        <v>36985271</v>
-      </c>
-      <c r="BN13" s="0">
-        <v>26627700</v>
-      </c>
-      <c r="BO13" s="0" t="inlineStr">
-        <is>
-          <t>573,283엔 (R8 토지 공과증명서 주택특례 약 12.3만 엔 + 건물 오카다상 확인 약 45만 엔 추정)</t>
-        </is>
-      </c>
-      <c r="BP13" s="0">
-        <v>85.0</v>
-      </c>
-      <c r="BQ13" s="0">
-        <v>114495000</v>
-      </c>
-      <c r="BR13" s="0">
-        <v>2.3</v>
-      </c>
-      <c r="BS13" s="0">
-        <v>30</v>
-      </c>
-      <c r="BT13" s="0">
-        <v>5287219</v>
-      </c>
-      <c r="BU13" s="0">
-        <v>1582741</v>
-      </c>
-      <c r="BV13" s="0">
-        <v>1246795</v>
-      </c>
-      <c r="BW13" s="0">
-        <v>1.3</v>
-      </c>
-      <c r="BX13" s="0">
-        <v>1.54</v>
-      </c>
-      <c r="BY13" s="0">
-        <v>81.93</v>
-      </c>
-      <c r="BZ13" s="0">
-        <v>1.63</v>
-      </c>
-      <c r="CA13" s="0">
-        <v>31497300</v>
-      </c>
-      <c r="CB13" s="0">
-        <v>5.03</v>
-      </c>
-      <c r="CC13" s="0" t="inlineStr">
-        <is>
-          <t>소테츠 본선(급행 정차) 「미츠쿄(三ツ境)」역 구글맵 실측 도보 10분 (약 720m, 마이소쿠 표기 7분)</t>
-        </is>
-      </c>
-      <c r="CD13" s="0" t="inlineStr">
-        <is>
-          <t>도보 7분 (마이소쿠 표기)</t>
-        </is>
-      </c>
-      <c r="CE13" s="0" t="inlineStr">
-        <is>
-          <t>실측 도보 10분 (구글맵 및 오카다상 현장 확인완료)</t>
-        </is>
-      </c>
-      <c r="CF13" s="0" t="inlineStr">
-        <is>
-          <t>720m (구글맵 실측완료)</t>
-        </is>
-      </c>
-      <c r="CG13" s="0" t="inlineStr">
-        <is>
-          <t>사사노다이 상점가 경유 후 남서측 전면도로(下川井第402号線) 진입부에 계단 구간 및 부지 고저차(4.0~4.69m) 존재 확인완료</t>
-        </is>
-      </c>
-      <c r="CH13" s="0" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/T66nW2jUBZfHG8AM7</t>
-        </is>
-      </c>
-      <c r="CI13" s="0" t="inlineStr">
-        <is>
-          <t>고대(高台) 입지로 홍수·내수 침수 해저드 해당 없음 (교차검증 완료)</t>
-        </is>
-      </c>
-      <c r="CJ13" s="0" t="inlineStr">
-        <is>
-          <t>부지 북서측 모서리 옹벽 부분(가측량도 약 4.69㎡)이 토사재해경계구역(옐로우존/잠정 레드존 경계)에 일부 저촉 확인완료 (건물 본체는 2m 이격되어 구역 외)</t>
-        </is>
-      </c>
-      <c r="CK13" s="0" t="inlineStr">
-        <is>
-          <t>https://www.homes.co.jp/archive/b-36020804/</t>
-        </is>
-      </c>
-      <c r="CL13" s="0" t="inlineStr">
-        <is>
-          <t>30~45일 (REINS 근린 성약 50건 및 일 피오레 사사노다이 교차검증 완료)</t>
-        </is>
-      </c>
-      <c r="CM13" s="0" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="CN13" s="0">
-        <v>0</v>
-      </c>
-      <c r="CO13" s="0">
+      <c r="CO14" s="0">
+        <v>2.4</v>
+      </c>
+      <c r="CP14" s="0">
+        <v>4.2</v>
+      </c>
+      <c r="CQ14" s="0">
+        <v>4.2</v>
+      </c>
+      <c r="CR14" s="0">
         <v>3.5</v>
       </c>
-      <c r="CP13" s="0">
-        <v>3.5</v>
-      </c>
-      <c r="CQ13" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="CR13" s="0">
-        <v>3.5</v>
-      </c>
-      <c r="CS13" s="0">
-        <v>3.5</v>
-      </c>
-      <c r="CT13" s="0">
-        <v>2.5</v>
-      </c>
-      <c r="CU13" s="0">
-        <v>19.5</v>
-      </c>
-      <c r="CV13" s="0" t="inlineStr">
-        <is>
-          <t>조건부 검토</t>
-        </is>
-      </c>
-      <c r="CW13" s="0" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="CX13" s="0" t="inlineStr">
-        <is>
-          <t>적합 / 조건부 편입 (ICR 1.05배 돌파·LTV -15.6%p 개선 / 단, 미검사 옹벽·토사재해 저촉 반영 1.24억 네고 필수)</t>
-        </is>
-      </c>
-      <c r="CY13" s="0" t="inlineStr">
-        <is>
-          <t>적합 / 조건부 검토 (120.3평 택지·1LDK+로프트·열화3급 30년 융자 우수하나 기존 옹벽·임대료 상단 리스크 반영 지값 협상 필수)</t>
+      <c r="CS14" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="CT14" s="0">
+        <v>3.8</v>
+      </c>
+      <c r="CU14" s="0">
+        <v>20.1</v>
+      </c>
+      <c r="CV14" s="0" t="inlineStr">
+        <is>
+          <t>C+ 등급 (62/100점 | 20.1/30점) — JR 치바역 도보 12분·니시치바역(치바대) 도보 13분, 전 16호 24.16㎡ 광폭 1K + 오토록·택배함·무료인터넷 완비(만실). 단, 호가 2.22억 엔(표면 6.52%) 기준 적산비율 54.9%(은행보수 49.0%), DSCR 1.04배, 1년차 세후 CF -7.1만 엔(즉시 데드크로스)으로 호가 매수 불가. 1.95억~1.98억 엔(표면 7.31%~7.42%) 지가 네고 및 25년 융자 조건부 매수(Conditional Buy)</t>
+        </is>
+      </c>
+      <c r="CW14" s="0" t="inlineStr">
+        <is>
+          <t>조건부 매수 (1.98억 네고 필수)</t>
+        </is>
+      </c>
+      <c r="CX14" s="0" t="inlineStr">
+        <is>
+          <t>부적합 (호가 2.22억 엔 매입 시 세후 CF -7.1만 엔 적자 및 통합 상환연수 24.1→27.9년 악화 / 단, 1.98억 엔·2.2% 네고 시 세후 CF +178.1만 엔·ICR 1.20배로 적합 전환)</t>
+        </is>
+      </c>
+      <c r="CY14" s="0" t="inlineStr">
+        <is>
+          <t>조건부 매수 (62 / 100점 — 호가 2.22억 엔 매수 보류 · 1.95억~1.98억 엔 네고 필수)</t>
         </is>
       </c>
     </row>
@@ -17435,8 +17942,10 @@
           <t>1LDK (LDK8.0+양실5.5)</t>
         </is>
       </c>
-      <c r="E124" s="0">
-        <v>26.89</v>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
       </c>
       <c r="F124" s="0" t="inlineStr">
         <is>
@@ -17458,23 +17967,35 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J124" s="0">
-        <v>80000</v>
-      </c>
-      <c r="K124" s="0">
-        <v>0</v>
-      </c>
-      <c r="L124" s="0">
-        <v>0</v>
-      </c>
-      <c r="M124" s="0">
-        <v>80000</v>
-      </c>
-      <c r="N124" s="0">
-        <v>78000</v>
-      </c>
-      <c r="O124" s="0">
-        <v>0</v>
+      <c r="J124" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="K124" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L124" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M124" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="N124" s="0" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+      <c r="O124" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P124" s="0" t="inlineStr">
         <is>
@@ -17508,8 +18029,10 @@
           <t>1LDK (LDK8.0+양실5.5)</t>
         </is>
       </c>
-      <c r="E125" s="0">
-        <v>26.89</v>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
       </c>
       <c r="F125" s="0" t="inlineStr">
         <is>
@@ -17531,23 +18054,35 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J125" s="0">
-        <v>78000</v>
-      </c>
-      <c r="K125" s="0">
-        <v>0</v>
-      </c>
-      <c r="L125" s="0">
-        <v>0</v>
-      </c>
-      <c r="M125" s="0">
-        <v>78000</v>
-      </c>
-      <c r="N125" s="0">
-        <v>76000</v>
-      </c>
-      <c r="O125" s="0">
-        <v>0</v>
+      <c r="J125" s="0" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+      <c r="K125" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L125" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M125" s="0" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+      <c r="N125" s="0" t="inlineStr">
+        <is>
+          <t>76000</t>
+        </is>
+      </c>
+      <c r="O125" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P125" s="0" t="inlineStr">
         <is>
@@ -17581,8 +18116,10 @@
           <t>1LDK (LDK8.0+양실5.5)</t>
         </is>
       </c>
-      <c r="E126" s="0">
-        <v>26.89</v>
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
       </c>
       <c r="F126" s="0" t="inlineStr">
         <is>
@@ -17604,23 +18141,35 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J126" s="0">
-        <v>78000</v>
-      </c>
-      <c r="K126" s="0">
-        <v>0</v>
-      </c>
-      <c r="L126" s="0">
-        <v>0</v>
-      </c>
-      <c r="M126" s="0">
-        <v>78000</v>
-      </c>
-      <c r="N126" s="0">
-        <v>76000</v>
-      </c>
-      <c r="O126" s="0">
-        <v>0</v>
+      <c r="J126" s="0" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+      <c r="K126" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L126" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M126" s="0" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+      <c r="N126" s="0" t="inlineStr">
+        <is>
+          <t>76000</t>
+        </is>
+      </c>
+      <c r="O126" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P126" s="0" t="inlineStr">
         <is>
@@ -17654,8 +18203,10 @@
           <t>1LDK (LDK8.0+양실5.5)</t>
         </is>
       </c>
-      <c r="E127" s="0">
-        <v>26.89</v>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
       </c>
       <c r="F127" s="0" t="inlineStr">
         <is>
@@ -17677,23 +18228,35 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J127" s="0">
-        <v>78000</v>
-      </c>
-      <c r="K127" s="0">
-        <v>0</v>
-      </c>
-      <c r="L127" s="0">
-        <v>0</v>
-      </c>
-      <c r="M127" s="0">
-        <v>78000</v>
-      </c>
-      <c r="N127" s="0">
-        <v>76000</v>
-      </c>
-      <c r="O127" s="0">
-        <v>0</v>
+      <c r="J127" s="0" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+      <c r="K127" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L127" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M127" s="0" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+      <c r="N127" s="0" t="inlineStr">
+        <is>
+          <t>76000</t>
+        </is>
+      </c>
+      <c r="O127" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P127" s="0" t="inlineStr">
         <is>
@@ -17727,8 +18290,10 @@
           <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
-      <c r="E128" s="0">
-        <v>26.89</v>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
       </c>
       <c r="F128" s="0" t="inlineStr">
         <is>
@@ -17750,23 +18315,35 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J128" s="0">
-        <v>80000</v>
-      </c>
-      <c r="K128" s="0">
-        <v>0</v>
-      </c>
-      <c r="L128" s="0">
-        <v>0</v>
-      </c>
-      <c r="M128" s="0">
-        <v>80000</v>
-      </c>
-      <c r="N128" s="0">
-        <v>80000</v>
-      </c>
-      <c r="O128" s="0">
-        <v>0</v>
+      <c r="J128" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="K128" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L128" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M128" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="N128" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="O128" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P128" s="0" t="inlineStr">
         <is>
@@ -17800,8 +18377,10 @@
           <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
-      <c r="E129" s="0">
-        <v>26.89</v>
+      <c r="E129" s="0" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
       </c>
       <c r="F129" s="0" t="inlineStr">
         <is>
@@ -17823,23 +18402,35 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J129" s="0">
-        <v>85000</v>
-      </c>
-      <c r="K129" s="0">
-        <v>0</v>
-      </c>
-      <c r="L129" s="0">
-        <v>0</v>
-      </c>
-      <c r="M129" s="0">
-        <v>85000</v>
-      </c>
-      <c r="N129" s="0">
-        <v>82000</v>
-      </c>
-      <c r="O129" s="0">
-        <v>0</v>
+      <c r="J129" s="0" t="inlineStr">
+        <is>
+          <t>85000</t>
+        </is>
+      </c>
+      <c r="K129" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L129" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M129" s="0" t="inlineStr">
+        <is>
+          <t>85000</t>
+        </is>
+      </c>
+      <c r="N129" s="0" t="inlineStr">
+        <is>
+          <t>82000</t>
+        </is>
+      </c>
+      <c r="O129" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P129" s="0" t="inlineStr">
         <is>
@@ -17873,8 +18464,10 @@
           <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
-      <c r="E130" s="0">
-        <v>26.89</v>
+      <c r="E130" s="0" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
@@ -17896,23 +18489,35 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J130" s="0">
-        <v>83000</v>
-      </c>
-      <c r="K130" s="0">
-        <v>0</v>
-      </c>
-      <c r="L130" s="0">
-        <v>0</v>
-      </c>
-      <c r="M130" s="0">
-        <v>83000</v>
-      </c>
-      <c r="N130" s="0">
-        <v>80000</v>
-      </c>
-      <c r="O130" s="0">
-        <v>0</v>
+      <c r="J130" s="0" t="inlineStr">
+        <is>
+          <t>83000</t>
+        </is>
+      </c>
+      <c r="K130" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L130" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M130" s="0" t="inlineStr">
+        <is>
+          <t>83000</t>
+        </is>
+      </c>
+      <c r="N130" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="O130" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P130" s="0" t="inlineStr">
         <is>
@@ -17946,8 +18551,10 @@
           <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
-      <c r="E131" s="0">
-        <v>26.89</v>
+      <c r="E131" s="0" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
@@ -17969,23 +18576,35 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J131" s="0">
-        <v>83000</v>
-      </c>
-      <c r="K131" s="0">
-        <v>0</v>
-      </c>
-      <c r="L131" s="0">
-        <v>0</v>
-      </c>
-      <c r="M131" s="0">
-        <v>83000</v>
-      </c>
-      <c r="N131" s="0">
-        <v>80000</v>
-      </c>
-      <c r="O131" s="0">
-        <v>0</v>
+      <c r="J131" s="0" t="inlineStr">
+        <is>
+          <t>83000</t>
+        </is>
+      </c>
+      <c r="K131" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L131" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M131" s="0" t="inlineStr">
+        <is>
+          <t>83000</t>
+        </is>
+      </c>
+      <c r="N131" s="0" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="O131" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P131" s="0" t="inlineStr">
         <is>
@@ -18019,8 +18638,10 @@
           <t>1LDK+로프트4.82㎡</t>
         </is>
       </c>
-      <c r="E132" s="0">
-        <v>26.89</v>
+      <c r="E132" s="0" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
@@ -18042,32 +18663,1148 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J132" s="0">
-        <v>85000</v>
-      </c>
-      <c r="K132" s="0">
+      <c r="J132" s="0" t="inlineStr">
+        <is>
+          <t>85000</t>
+        </is>
+      </c>
+      <c r="K132" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L132" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M132" s="0" t="inlineStr">
+        <is>
+          <t>85000</t>
+        </is>
+      </c>
+      <c r="N132" s="0" t="inlineStr">
+        <is>
+          <t>82000</t>
+        </is>
+      </c>
+      <c r="O132" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P132" s="0" t="inlineStr">
+        <is>
+          <t>30~45</t>
+        </is>
+      </c>
+      <c r="Q132" s="0" t="inlineStr">
+        <is>
+          <t>2F 최상층 동측 각실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B133" s="0" t="inlineStr">
+        <is>
+          <t>101호</t>
+        </is>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="D133" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E133" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F133" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I133" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J133" s="0">
+        <v>69000</v>
+      </c>
+      <c r="K133" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L133" s="0">
         <v>0</v>
       </c>
-      <c r="L132" s="0">
+      <c r="M133" s="0">
+        <v>73000</v>
+      </c>
+      <c r="N133" s="0">
+        <v>71000</v>
+      </c>
+      <c r="O133" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P133" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q133" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t>102호</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="D134" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E134" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F134" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I134" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J134" s="0">
+        <v>69000</v>
+      </c>
+      <c r="K134" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L134" s="0">
         <v>0</v>
       </c>
-      <c r="M132" s="0">
-        <v>85000</v>
-      </c>
-      <c r="N132" s="0">
-        <v>82000</v>
-      </c>
-      <c r="O132" s="0">
+      <c r="M134" s="0">
+        <v>73000</v>
+      </c>
+      <c r="N134" s="0">
+        <v>71000</v>
+      </c>
+      <c r="O134" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P134" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q134" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B135" s="0" t="inlineStr">
+        <is>
+          <t>103호</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="D135" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E135" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F135" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I135" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J135" s="0">
+        <v>69000</v>
+      </c>
+      <c r="K135" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L135" s="0">
         <v>0</v>
       </c>
-      <c r="P132" s="0" t="inlineStr">
-        <is>
-          <t>30~45</t>
-        </is>
-      </c>
-      <c r="Q132" s="0" t="inlineStr">
-        <is>
-          <t>2F 최상층 동측 각실 + 4.82㎡ 로프트(실사용 31.71㎡)</t>
+      <c r="M135" s="0">
+        <v>73000</v>
+      </c>
+      <c r="N135" s="0">
+        <v>71000</v>
+      </c>
+      <c r="O135" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P135" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q135" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B136" s="0" t="inlineStr">
+        <is>
+          <t>104호</t>
+        </is>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="D136" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E136" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F136" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I136" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J136" s="0">
+        <v>69300</v>
+      </c>
+      <c r="K136" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L136" s="0">
+        <v>0</v>
+      </c>
+      <c r="M136" s="0">
+        <v>73300</v>
+      </c>
+      <c r="N136" s="0">
+        <v>71000</v>
+      </c>
+      <c r="O136" s="0">
+        <v>-2300</v>
+      </c>
+      <c r="P136" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q136" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t>201호</t>
+        </is>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="D137" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E137" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F137" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I137" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J137" s="0">
+        <v>71000</v>
+      </c>
+      <c r="K137" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L137" s="0">
+        <v>0</v>
+      </c>
+      <c r="M137" s="0">
+        <v>75000</v>
+      </c>
+      <c r="N137" s="0">
+        <v>73000</v>
+      </c>
+      <c r="O137" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P137" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q137" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t>202호</t>
+        </is>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="D138" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E138" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F138" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I138" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J138" s="0">
+        <v>71000</v>
+      </c>
+      <c r="K138" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L138" s="0">
+        <v>0</v>
+      </c>
+      <c r="M138" s="0">
+        <v>75000</v>
+      </c>
+      <c r="N138" s="0">
+        <v>73000</v>
+      </c>
+      <c r="O138" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P138" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q138" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t>203호</t>
+        </is>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="D139" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E139" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F139" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I139" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J139" s="0">
+        <v>71000</v>
+      </c>
+      <c r="K139" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L139" s="0">
+        <v>0</v>
+      </c>
+      <c r="M139" s="0">
+        <v>75000</v>
+      </c>
+      <c r="N139" s="0">
+        <v>73000</v>
+      </c>
+      <c r="O139" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P139" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q139" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t>204호</t>
+        </is>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="D140" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E140" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F140" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I140" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J140" s="0">
+        <v>71000</v>
+      </c>
+      <c r="K140" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L140" s="0">
+        <v>0</v>
+      </c>
+      <c r="M140" s="0">
+        <v>75000</v>
+      </c>
+      <c r="N140" s="0">
+        <v>73000</v>
+      </c>
+      <c r="O140" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P140" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q140" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t>301호</t>
+        </is>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="D141" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E141" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F141" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I141" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J141" s="0">
+        <v>72000</v>
+      </c>
+      <c r="K141" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L141" s="0">
+        <v>0</v>
+      </c>
+      <c r="M141" s="0">
+        <v>76000</v>
+      </c>
+      <c r="N141" s="0">
+        <v>74000</v>
+      </c>
+      <c r="O141" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P141" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q141" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B142" s="0" t="inlineStr">
+        <is>
+          <t>302호</t>
+        </is>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="D142" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E142" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F142" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I142" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J142" s="0">
+        <v>72000</v>
+      </c>
+      <c r="K142" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L142" s="0">
+        <v>0</v>
+      </c>
+      <c r="M142" s="0">
+        <v>76000</v>
+      </c>
+      <c r="N142" s="0">
+        <v>74000</v>
+      </c>
+      <c r="O142" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P142" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q142" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t>303호</t>
+        </is>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="D143" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E143" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F143" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I143" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J143" s="0">
+        <v>72000</v>
+      </c>
+      <c r="K143" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L143" s="0">
+        <v>0</v>
+      </c>
+      <c r="M143" s="0">
+        <v>76000</v>
+      </c>
+      <c r="N143" s="0">
+        <v>74000</v>
+      </c>
+      <c r="O143" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P143" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q143" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
+        <is>
+          <t>304호</t>
+        </is>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="D144" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E144" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F144" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I144" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J144" s="0">
+        <v>72000</v>
+      </c>
+      <c r="K144" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L144" s="0">
+        <v>0</v>
+      </c>
+      <c r="M144" s="0">
+        <v>76000</v>
+      </c>
+      <c r="N144" s="0">
+        <v>74000</v>
+      </c>
+      <c r="O144" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P144" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q144" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t>401호</t>
+        </is>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t>4F</t>
+        </is>
+      </c>
+      <c r="D145" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E145" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F145" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I145" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J145" s="0">
+        <v>73500</v>
+      </c>
+      <c r="K145" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L145" s="0">
+        <v>0</v>
+      </c>
+      <c r="M145" s="0">
+        <v>77500</v>
+      </c>
+      <c r="N145" s="0">
+        <v>74000</v>
+      </c>
+      <c r="O145" s="0">
+        <v>-3500</v>
+      </c>
+      <c r="P145" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q145" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B146" s="0" t="inlineStr">
+        <is>
+          <t>402호</t>
+        </is>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t>4F</t>
+        </is>
+      </c>
+      <c r="D146" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E146" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F146" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I146" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J146" s="0">
+        <v>73500</v>
+      </c>
+      <c r="K146" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L146" s="0">
+        <v>0</v>
+      </c>
+      <c r="M146" s="0">
+        <v>77500</v>
+      </c>
+      <c r="N146" s="0">
+        <v>74000</v>
+      </c>
+      <c r="O146" s="0">
+        <v>-3500</v>
+      </c>
+      <c r="P146" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q146" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B147" s="0" t="inlineStr">
+        <is>
+          <t>403호</t>
+        </is>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>4F</t>
+        </is>
+      </c>
+      <c r="D147" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E147" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F147" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I147" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J147" s="0">
+        <v>73500</v>
+      </c>
+      <c r="K147" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L147" s="0">
+        <v>0</v>
+      </c>
+      <c r="M147" s="0">
+        <v>77500</v>
+      </c>
+      <c r="N147" s="0">
+        <v>74000</v>
+      </c>
+      <c r="O147" s="0">
+        <v>-3500</v>
+      </c>
+      <c r="P147" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q147" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B148" s="0" t="inlineStr">
+        <is>
+          <t>404호</t>
+        </is>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t>4F</t>
+        </is>
+      </c>
+      <c r="D148" s="0" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="E148" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="F148" s="0" t="inlineStr">
+        <is>
+          <t>입주중</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (개인/법인/학생 미기재)</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="I148" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J148" s="0">
+        <v>73500</v>
+      </c>
+      <c r="K148" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L148" s="0">
+        <v>0</v>
+      </c>
+      <c r="M148" s="0">
+        <v>77500</v>
+      </c>
+      <c r="N148" s="0">
+        <v>74000</v>
+      </c>
+      <c r="O148" s="0">
+        <v>-3500</v>
+      </c>
+      <c r="P148" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q148" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
         </is>
       </c>
     </row>
@@ -42072,6 +43809,2001 @@
       <c r="K421" s="0" t="inlineStr">
         <is>
           <t/>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B422" s="0" t="inlineStr">
+        <is>
+          <t>CHK_01</t>
+        </is>
+      </c>
+      <c r="C422" s="0" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D422" s="0" t="inlineStr">
+        <is>
+          <t>name_ko</t>
+        </is>
+      </c>
+      <c r="E422" s="0" t="inlineStr">
+        <is>
+          <t>물건명 (한/일)</t>
+        </is>
+      </c>
+      <c r="F422" s="0" t="inlineStr">
+        <is>
+          <t>物件名称</t>
+        </is>
+      </c>
+      <c r="G422" s="0" t="inlineStr">
+        <is>
+          <t>시엘 블루 치바추오</t>
+        </is>
+      </c>
+      <c r="H422" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I422" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/개요서</t>
+        </is>
+      </c>
+      <c r="J422" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K422" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B423" s="0" t="inlineStr">
+        <is>
+          <t>CHK_02</t>
+        </is>
+      </c>
+      <c r="C423" s="0" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D423" s="0" t="inlineStr">
+        <is>
+          <t>address_road</t>
+        </is>
+      </c>
+      <c r="E423" s="0" t="inlineStr">
+        <is>
+          <t>소재지 도로명주소 (住居表示)</t>
+        </is>
+      </c>
+      <c r="F423" s="0" t="inlineStr">
+        <is>
+          <t>住居表示</t>
+        </is>
+      </c>
+      <c r="G423" s="0" t="inlineStr">
+        <is>
+          <t>千葉県千葉市中央区松波1丁目19-12</t>
+        </is>
+      </c>
+      <c r="H423" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I423" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/개요서</t>
+        </is>
+      </c>
+      <c r="J423" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K423" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>CHK_03</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>address_lot</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>토지 지번 (地番)</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>土地地番</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>등기부상 정확한 토지 지번 확인</t>
+        </is>
+      </c>
+      <c r="K424" s="2" t="inlineStr">
+        <is>
+          <t>登記簿上の正確な地番のご教示</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B425" s="0" t="inlineStr">
+        <is>
+          <t>CHK_04</t>
+        </is>
+      </c>
+      <c r="C425" s="0" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D425" s="0" t="inlineStr">
+        <is>
+          <t>price_yen</t>
+        </is>
+      </c>
+      <c r="E425" s="0" t="inlineStr">
+        <is>
+          <t>매매가격 및 소비세 조건</t>
+        </is>
+      </c>
+      <c r="F425" s="0" t="inlineStr">
+        <is>
+          <t>売買価格・消費税</t>
+        </is>
+      </c>
+      <c r="G425" s="0" t="inlineStr">
+        <is>
+          <t>222000000</t>
+        </is>
+      </c>
+      <c r="H425" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I425" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/개요서</t>
+        </is>
+      </c>
+      <c r="J425" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K425" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B426" s="0" t="inlineStr">
+        <is>
+          <t>CHK_05</t>
+        </is>
+      </c>
+      <c r="C426" s="0" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D426" s="0" t="inlineStr">
+        <is>
+          <t>delivery_condition</t>
+        </is>
+      </c>
+      <c r="E426" s="0" t="inlineStr">
+        <is>
+          <t>인도조건 및 계약부적합책임 면책 여부</t>
+        </is>
+      </c>
+      <c r="F426" s="0" t="inlineStr">
+        <is>
+          <t>引渡条件・契約不適合免責</t>
+        </is>
+      </c>
+      <c r="G426" s="0" t="inlineStr">
+        <is>
+          <t>상담 (相談 — 계약부적합책임 면책 특약 유무 확인 필요)</t>
+        </is>
+      </c>
+      <c r="H426" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I426" s="0" t="inlineStr">
+        <is>
+          <t>물건개요서</t>
+        </is>
+      </c>
+      <c r="J426" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K426" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B427" s="0" t="inlineStr">
+        <is>
+          <t>CHK_06</t>
+        </is>
+      </c>
+      <c r="C427" s="0" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D427" s="0" t="inlineStr">
+        <is>
+          <t>land_area_sqm</t>
+        </is>
+      </c>
+      <c r="E427" s="0" t="inlineStr">
+        <is>
+          <t>토지 공부면적 (㎡/평)</t>
+        </is>
+      </c>
+      <c r="F427" s="0" t="inlineStr">
+        <is>
+          <t>土地公簿面積</t>
+        </is>
+      </c>
+      <c r="G427" s="0" t="inlineStr">
+        <is>
+          <t>185.88</t>
+        </is>
+      </c>
+      <c r="H427" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I427" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/등기부</t>
+        </is>
+      </c>
+      <c r="J427" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K427" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B428" s="0" t="inlineStr">
+        <is>
+          <t>CHK_07</t>
+        </is>
+      </c>
+      <c r="C428" s="0" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D428" s="0" t="inlineStr">
+        <is>
+          <t>land_right</t>
+        </is>
+      </c>
+      <c r="E428" s="0" t="inlineStr">
+        <is>
+          <t>토지 권리형태 및 지목</t>
+        </is>
+      </c>
+      <c r="F428" s="0" t="inlineStr">
+        <is>
+          <t>土地権利・地目</t>
+        </is>
+      </c>
+      <c r="G428" s="0" t="inlineStr">
+        <is>
+          <t>소유권 (所有権)</t>
+        </is>
+      </c>
+      <c r="H428" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I428" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/등기부</t>
+        </is>
+      </c>
+      <c r="J428" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K428" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B429" s="0" t="inlineStr">
+        <is>
+          <t>CHK_08</t>
+        </is>
+      </c>
+      <c r="C429" s="0" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D429" s="0" t="inlineStr">
+        <is>
+          <t>zoning</t>
+        </is>
+      </c>
+      <c r="E429" s="0" t="inlineStr">
+        <is>
+          <t>용도지역 및 법정 건폐율·용적률</t>
+        </is>
+      </c>
+      <c r="F429" s="0" t="inlineStr">
+        <is>
+          <t>用途地域・建蔽率・容積率</t>
+        </is>
+      </c>
+      <c r="G429" s="0" t="inlineStr">
+        <is>
+          <t>제1종주거지역 (第一種住居地域)</t>
+        </is>
+      </c>
+      <c r="H429" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I429" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/개요서</t>
+        </is>
+      </c>
+      <c r="J429" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K429" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>CHK_09</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>road_access</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>도로 접도 방위·폭원·접도길이</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>接道状況（幅員・間口）</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr">
+        <is>
+          <t>건축기준법상 도로 종류 및 정확한 접도 폭원/길이</t>
+        </is>
+      </c>
+      <c r="K430" s="2" t="inlineStr">
+        <is>
+          <t>建築基準法上の道路種別および正確な幅員・接道間口</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>CHK_10</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>private_road_burden</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>사도부담 및 굴착·통행승낙서 유무</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>私道負担・掘削通行承諾</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr">
+        <is>
+          <t>사도 지분 유무 및 타인 지분 굴착승낙서 유무</t>
+        </is>
+      </c>
+      <c r="K431" s="2" t="inlineStr">
+        <is>
+          <t>私道負担・持分の有無および通行掘削承諾書の有無</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B432" s="0" t="inlineStr">
+        <is>
+          <t>CHK_11</t>
+        </is>
+      </c>
+      <c r="C432" s="0" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D432" s="0" t="inlineStr">
+        <is>
+          <t>structure_display</t>
+        </is>
+      </c>
+      <c r="E432" s="0" t="inlineStr">
+        <is>
+          <t>건물 구조 및 층수</t>
+        </is>
+      </c>
+      <c r="F432" s="0" t="inlineStr">
+        <is>
+          <t>建物構造・規模</t>
+        </is>
+      </c>
+      <c r="G432" s="0" t="inlineStr">
+        <is>
+          <t>철골조 지상 4층 건 (鉄骨造 4階建)</t>
+        </is>
+      </c>
+      <c r="H432" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I432" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/등기부</t>
+        </is>
+      </c>
+      <c r="J432" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K432" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B433" s="0" t="inlineStr">
+        <is>
+          <t>CHK_12</t>
+        </is>
+      </c>
+      <c r="C433" s="0" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D433" s="0" t="inlineStr">
+        <is>
+          <t>built_year_month</t>
+        </is>
+      </c>
+      <c r="E433" s="0" t="inlineStr">
+        <is>
+          <t>신축 준공년월 및 경과연수</t>
+        </is>
+      </c>
+      <c r="F433" s="0" t="inlineStr">
+        <is>
+          <t>築年月</t>
+        </is>
+      </c>
+      <c r="G433" s="0" t="inlineStr">
+        <is>
+          <t>2011년 2월 (平成23年2月)</t>
+        </is>
+      </c>
+      <c r="H433" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I433" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/등기부</t>
+        </is>
+      </c>
+      <c r="J433" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K433" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B434" s="0" t="inlineStr">
+        <is>
+          <t>CHK_13</t>
+        </is>
+      </c>
+      <c r="C434" s="0" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D434" s="0" t="inlineStr">
+        <is>
+          <t>bldg_area_reg_sqm</t>
+        </is>
+      </c>
+      <c r="E434" s="0" t="inlineStr">
+        <is>
+          <t>등기 연면적 vs 확인대장 연면적</t>
+        </is>
+      </c>
+      <c r="F434" s="0" t="inlineStr">
+        <is>
+          <t>延床面積（登記・確認台帳）</t>
+        </is>
+      </c>
+      <c r="G434" s="0" t="inlineStr">
+        <is>
+          <t>359.79</t>
+        </is>
+      </c>
+      <c r="H434" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I434" s="0" t="inlineStr">
+        <is>
+          <t>등기부/건축확인대장</t>
+        </is>
+      </c>
+      <c r="J434" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K434" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>CHK_14</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>has_confirm_cert</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>건축확인필증(確認済証) 및 대장 유무</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>建築確認済証・台帳記載事項証明</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr">
+        <is>
+          <t>건축확인필증 또는 대장기재사항증명서 사본 요청</t>
+        </is>
+      </c>
+      <c r="K435" s="2" t="inlineStr">
+        <is>
+          <t>建築確認済証または台帳記載事項証明書の写しのご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>CHK_15</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>has_inspection_cert</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>준공검사필증(検査済証) 취득 여부</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>検査済証の有無</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J436" s="2" t="inlineStr">
+        <is>
+          <t>준공검사필증(検査済証) 교부 유무 및 번호 확인 (은행융자 필수)</t>
+        </is>
+      </c>
+      <c r="K436" s="2" t="inlineStr">
+        <is>
+          <t>検査済証の有無および交付番号のご確認（融資審査上必須）</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>CHK_16</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>repair_history_summary</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>외벽도장·옥상방수 등 대규모 수선이력</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>大規模修繕履歴（外壁・屋上防水）</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J437" s="2" t="inlineStr">
+        <is>
+          <t>과거 외벽도장·옥상방수·급배수관 수선이력서 및 견적서 요청</t>
+        </is>
+      </c>
+      <c r="K437" s="2" t="inlineStr">
+        <is>
+          <t>過去の外壁塗装・屋上防水・設備等の修繕履歴一覧のご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B438" s="0" t="inlineStr">
+        <is>
+          <t>CHK_17</t>
+        </is>
+      </c>
+      <c r="C438" s="0" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D438" s="0" t="inlineStr">
+        <is>
+          <t>full_annual_income_yen</t>
+        </is>
+      </c>
+      <c r="E438" s="0" t="inlineStr">
+        <is>
+          <t>호실별 월 차임 및 공익비 내역</t>
+        </is>
+      </c>
+      <c r="F438" s="0" t="inlineStr">
+        <is>
+          <t>各戸賃料・共益費一覧</t>
+        </is>
+      </c>
+      <c r="G438" s="0" t="inlineStr">
+        <is>
+          <t>14475600</t>
+        </is>
+      </c>
+      <c r="H438" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I438" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤</t>
+        </is>
+      </c>
+      <c r="J438" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K438" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B439" s="0" t="inlineStr">
+        <is>
+          <t>CHK_18</t>
+        </is>
+      </c>
+      <c r="C439" s="0" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D439" s="0" t="inlineStr">
+        <is>
+          <t>unit_composition</t>
+        </is>
+      </c>
+      <c r="E439" s="0" t="inlineStr">
+        <is>
+          <t>호실별 전유면적(㎡) 및 평형 타입</t>
+        </is>
+      </c>
+      <c r="F439" s="0" t="inlineStr">
+        <is>
+          <t>各戸専有面積・間取り</t>
+        </is>
+      </c>
+      <c r="G439" s="0" t="inlineStr">
+        <is>
+          <t>전 호실 1K (24.16㎡) × 16호 (100% 단일 평형, 만실 가동 중)</t>
+        </is>
+      </c>
+      <c r="H439" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I439" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤/도면</t>
+        </is>
+      </c>
+      <c r="J439" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K439" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>CHK_19</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>rent_roll_contract_dates</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>호실별 계약시작일(契約始期) 및 갱신주기</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>各戸の契約始期・更新時期</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 계약시작일 미기재]</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J440" s="2" t="inlineStr">
+        <is>
+          <t>렌트롤상 호실별 최초 계약시작일(입주일) 기재본 요청</t>
+        </is>
+      </c>
+      <c r="K440" s="2" t="inlineStr">
+        <is>
+          <t>レントロールにおける各戸の契約始期（入居年月）のご教示</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>CHK_20</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>rent_roll_tenant_types</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>호실별 입주자 속성(법인/직장인/학생/보증회사)</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>入居者属性・保証会社加入状況</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 입주자속성 미기재]</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J441" s="2" t="inlineStr">
+        <is>
+          <t>호실별 입주자 속성(법인/개인) 및 임대보증회사 가입 유무 확인</t>
+        </is>
+      </c>
+      <c r="K441" s="2" t="inlineStr">
+        <is>
+          <t>各戸の入居者属性（法人・社会人・学生等）および保証会社加入状況のご教示</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B442" s="0" t="inlineStr">
+        <is>
+          <t>CHK_21</t>
+        </is>
+      </c>
+      <c r="C442" s="0" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D442" s="0" t="inlineStr">
+        <is>
+          <t>parking_info</t>
+        </is>
+      </c>
+      <c r="E442" s="0" t="inlineStr">
+        <is>
+          <t>주차장·자판기·안테나 등 부대수입 계약현황</t>
+        </is>
+      </c>
+      <c r="F442" s="0" t="inlineStr">
+        <is>
+          <t>駐車場・付帯収入の契約状況</t>
+        </is>
+      </c>
+      <c r="G442" s="0" t="inlineStr">
+        <is>
+          <t>주륜장 완비 (駐輪場有 — 자동차 주차장 유무 및 수입 확인 필요)</t>
+        </is>
+      </c>
+      <c r="H442" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I442" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤/개요서</t>
+        </is>
+      </c>
+      <c r="J442" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K442" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>CHK_22</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>disclosed_opex_yen</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>PM 관리위탁비 및 정기청소비 실비</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>PM管理委託費・定期清掃費</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J443" s="2" t="inlineStr">
+        <is>
+          <t>현재 위탁 중인 PM 관리수수료율 및 정기청소비 월액 확인</t>
+        </is>
+      </c>
+      <c r="K443" s="2" t="inlineStr">
+        <is>
+          <t>現行のPM管理委託料率および定期清掃費等のランニングコスト明細のご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="3" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>CHK_23</t>
+        </is>
+      </c>
+      <c r="C444" s="3" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D444" s="3" t="inlineStr">
+        <is>
+          <t>utilities_water_sewer</t>
+        </is>
+      </c>
+      <c r="E444" s="3" t="inlineStr">
+        <is>
+          <t>공용 전기·수도·정화조·인터넷 유지비</t>
+        </is>
+      </c>
+      <c r="F444" s="3" t="inlineStr">
+        <is>
+          <t>共用光熱費・浄化槽・ネット費用</t>
+        </is>
+      </c>
+      <c r="G444" s="3" t="inlineStr">
+        <is>
+          <t>공영수도 · 공공하수 (추정 — 중요사항설명서 확인 필요)</t>
+        </is>
+      </c>
+      <c r="H444" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I444" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J444" s="3" t="inlineStr">
+        <is>
+          <t>연간 공용 전기/수도료, 정화조 보수점검비, 무료인터넷 월액 확인</t>
+        </is>
+      </c>
+      <c r="K444" s="3" t="inlineStr">
+        <is>
+          <t>共用部電気・水道代、浄化槽保守点検費、ネット月額費用の実績値のご教示</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="3" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B445" s="3" t="inlineStr">
+        <is>
+          <t>CHK_24</t>
+        </is>
+      </c>
+      <c r="C445" s="3" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D445" s="3" t="inlineStr">
+        <is>
+          <t>fixed_tax_land_eval_yen</t>
+        </is>
+      </c>
+      <c r="E445" s="3" t="inlineStr">
+        <is>
+          <t>고정자산세 토지 과세평가액</t>
+        </is>
+      </c>
+      <c r="F445" s="3" t="inlineStr">
+        <is>
+          <t>固定資産税評価額（土地）</t>
+        </is>
+      </c>
+      <c r="G445" s="3" t="inlineStr">
+        <is>
+          <t>56112525</t>
+        </is>
+      </c>
+      <c r="H445" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I445" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J445" s="3" t="inlineStr">
+        <is>
+          <t>최신 연도 고정자산세·도시계획세 과세명세서(토지 평가액) 사본 요청</t>
+        </is>
+      </c>
+      <c r="K445" s="3" t="inlineStr">
+        <is>
+          <t>最新年度の固定資産税・都市計画税課税明細書（土地評価額）の写しのご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="3" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>CHK_25</t>
+        </is>
+      </c>
+      <c r="C446" s="3" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D446" s="3" t="inlineStr">
+        <is>
+          <t>fixed_tax_bldg_eval_yen</t>
+        </is>
+      </c>
+      <c r="E446" s="3" t="inlineStr">
+        <is>
+          <t>고정자산세 건물 과세평가액</t>
+        </is>
+      </c>
+      <c r="F446" s="3" t="inlineStr">
+        <is>
+          <t>固定資産税評価額（建物）</t>
+        </is>
+      </c>
+      <c r="G446" s="3" t="inlineStr">
+        <is>
+          <t>37529761</t>
+        </is>
+      </c>
+      <c r="H446" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I446" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J446" s="3" t="inlineStr">
+        <is>
+          <t>최신 연도 고정자산세·도시계획세 과세명세서(건물 평가액) 사본 요청</t>
+        </is>
+      </c>
+      <c r="K446" s="3" t="inlineStr">
+        <is>
+          <t>最新年度の固定資産税・都市計画税課税明細書（建物評価額）の写しのご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="3" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B447" s="3" t="inlineStr">
+        <is>
+          <t>CHK_26</t>
+        </is>
+      </c>
+      <c r="C447" s="3" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D447" s="3" t="inlineStr">
+        <is>
+          <t>fixed_tax_annual_yen</t>
+        </is>
+      </c>
+      <c r="E447" s="3" t="inlineStr">
+        <is>
+          <t>고정자산세·도시계획세 연간 실납부세액</t>
+        </is>
+      </c>
+      <c r="F447" s="3" t="inlineStr">
+        <is>
+          <t>固都税 年間納付税額</t>
+        </is>
+      </c>
+      <c r="G447" s="3" t="inlineStr">
+        <is>
+          <t>825000</t>
+        </is>
+      </c>
+      <c r="H447" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I447" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J447" s="3" t="inlineStr">
+        <is>
+          <t>고정자산세·도시계획세 연간 납부세액 확정치 확인</t>
+        </is>
+      </c>
+      <c r="K447" s="3" t="inlineStr">
+        <is>
+          <t>固定資産税・都市計画税の年間納付税額（確定値）のご教示</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>CHK_27</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>6.등기/내력</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>registry_owner_match</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>토지·건물 등기부 소유자 일치 여부</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>土地・建物登記簿の所有者一致</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 등기부 미수령]</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J448" s="2" t="inlineStr">
+        <is>
+          <t>토지 및 건물 등기사항전부증명서(전부사항) 사본 요청</t>
+        </is>
+      </c>
+      <c r="K448" s="2" t="inlineStr">
+        <is>
+          <t>土地・建物の全部事項証明書（登記簿謄本）のご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>CHK_28</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>6.등기/내력</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>registry_history_갑구</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>과거 소유권 변천내력(갑구) 및 매각동기</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>所有権移転履歴・売却理由</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 등기부 미수령]</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J449" s="2" t="inlineStr">
+        <is>
+          <t>현 소유자의 취득 경위 및 금번 매각 사유 확인</t>
+        </is>
+      </c>
+      <c r="K449" s="2" t="inlineStr">
+        <is>
+          <t>現所有者様の取得経緯および今回のご売却理由のご教示</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>CHK_29</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>6.등기/내력</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>registry_liens_을구</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>담보권·근저당·압류·지역권 유무(을구)</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>抵当権・地役権等の権利関係</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 등기부 미수령]</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J450" s="2" t="inlineStr">
+        <is>
+          <t>등기부 을구 권리관계 및 말소 조건 확인</t>
+        </is>
+      </c>
+      <c r="K450" s="2" t="inlineStr">
+        <is>
+          <t>登記簿乙区の権利関係および引渡時抹消条件の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B451" s="0" t="inlineStr">
+        <is>
+          <t>CHK_30</t>
+        </is>
+      </c>
+      <c r="C451" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D451" s="0" t="inlineStr">
+        <is>
+          <t>roadside_price_sqm</t>
+        </is>
+      </c>
+      <c r="E451" s="0" t="inlineStr">
+        <is>
+          <t>국세청 상속세 노선가(路線価) 조회</t>
+        </is>
+      </c>
+      <c r="F451" s="0" t="inlineStr">
+        <is>
+          <t>相続税路線価</t>
+        </is>
+      </c>
+      <c r="G451" s="0" t="inlineStr">
+        <is>
+          <t>345000</t>
+        </is>
+      </c>
+      <c r="H451" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I451" s="0" t="inlineStr">
+        <is>
+          <t>국세청 노선가도</t>
+        </is>
+      </c>
+      <c r="J451" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K451" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B452" s="0" t="inlineStr">
+        <is>
+          <t>CHK_31</t>
+        </is>
+      </c>
+      <c r="C452" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D452" s="0" t="inlineStr">
+        <is>
+          <t>walk_min_gmaps</t>
+        </is>
+      </c>
+      <c r="E452" s="0" t="inlineStr">
+        <is>
+          <t>Google Maps 실측 도보거리 및 소요시간</t>
+        </is>
+      </c>
+      <c r="F452" s="0" t="inlineStr">
+        <is>
+          <t>Googleマップ実測徒歩距離・時間</t>
+        </is>
+      </c>
+      <c r="G452" s="0" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H452" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I452" s="0" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="J452" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K452" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B453" s="0" t="inlineStr">
+        <is>
+          <t>CHK_32</t>
+        </is>
+      </c>
+      <c r="C453" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D453" s="0" t="inlineStr">
+        <is>
+          <t>walk_slope_note</t>
+        </is>
+      </c>
+      <c r="E453" s="0" t="inlineStr">
+        <is>
+          <t>보행 동선 고저차(경사/계단) 및 혐오시설 실사</t>
+        </is>
+      </c>
+      <c r="F453" s="0" t="inlineStr">
+        <is>
+          <t>徒歩経路の高低差・周辺嫌悪施設</t>
+        </is>
+      </c>
+      <c r="G453" s="0" t="inlineStr">
+        <is>
+          <t>대체로 평탄한 주택·문교지구 동선 (치바역 북구~마츠나미 1초메 직선 접근)</t>
+        </is>
+      </c>
+      <c r="H453" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I453" s="0" t="inlineStr">
+        <is>
+          <t>Google 스트리트뷰</t>
+        </is>
+      </c>
+      <c r="J453" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K453" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B454" s="0" t="inlineStr">
+        <is>
+          <t>CHK_33</t>
+        </is>
+      </c>
+      <c r="C454" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D454" s="0" t="inlineStr">
+        <is>
+          <t>hazard_flood</t>
+        </is>
+      </c>
+      <c r="E454" s="0" t="inlineStr">
+        <is>
+          <t>지자체 홍수·내수 침수 해저드맵 검증</t>
+        </is>
+      </c>
+      <c r="F454" s="0" t="inlineStr">
+        <is>
+          <t>洪水・内水浸水ハザードマップ</t>
+        </is>
+      </c>
+      <c r="G454" s="0" t="inlineStr">
+        <is>
+          <t>치바시 홍수 해저드맵 하천범람 구역 외 (국지성 호우 시 내수침수 0.1~0.5m 가능성 확인 및 수재보험 특약 권장)</t>
+        </is>
+      </c>
+      <c r="H454" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I454" s="0" t="inlineStr">
+        <is>
+          <t>지자체 하저드맵</t>
+        </is>
+      </c>
+      <c r="J454" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K454" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B455" s="0" t="inlineStr">
+        <is>
+          <t>CHK_34</t>
+        </is>
+      </c>
+      <c r="C455" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D455" s="0" t="inlineStr">
+        <is>
+          <t>hazard_landslide</t>
+        </is>
+      </c>
+      <c r="E455" s="0" t="inlineStr">
+        <is>
+          <t>토사재해 경계구역(옐로/레드존) 검증</t>
+        </is>
+      </c>
+      <c r="F455" s="0" t="inlineStr">
+        <is>
+          <t>土砂災害警戒区域（イエロー/レッド）</t>
+        </is>
+      </c>
+      <c r="G455" s="0" t="inlineStr">
+        <is>
+          <t>해당 없음 (평탄한 제1종주거지역 — 토사재해 경계구역 외)</t>
+        </is>
+      </c>
+      <c r="H455" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I455" s="0" t="inlineStr">
+        <is>
+          <t>지자체 하저드맵</t>
+        </is>
+      </c>
+      <c r="J455" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K455" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="3" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>CHK_35</t>
+        </is>
+      </c>
+      <c r="C456" s="3" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D456" s="3" t="inlineStr">
+        <is>
+          <t>avg_dom_days</t>
+        </is>
+      </c>
+      <c r="E456" s="3" t="inlineStr">
+        <is>
+          <t>LIFULL HOME'S 아카이브 과거 모집이력(DOM)</t>
+        </is>
+      </c>
+      <c r="F456" s="3" t="inlineStr">
+        <is>
+          <t>HOME'S過去の掲載履歴・DOM分析</t>
+        </is>
+      </c>
+      <c r="G456" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H456" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I456" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J456" s="3" t="inlineStr">
+        <is>
+          <t>과거 포털 게재이력 기반 평균 모집소요기간(DOM) 및 저항선 실측</t>
+        </is>
+      </c>
+      <c r="K456" s="3" t="inlineStr">
+        <is>
+          <t>LIFULL HOME'Sアーカイブ履歴に基づく募集所要日数(DOM)の検証</t>
         </is>
       </c>
     </row>
@@ -51049,8 +54781,10 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B112" s="0">
-        <v>1</v>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -51117,8 +54851,10 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B113" s="0">
-        <v>2</v>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -51220,8 +54956,10 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B114" s="0">
-        <v>3</v>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -51280,8 +55018,10 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B115" s="0">
-        <v>4</v>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -51343,8 +55083,10 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B116" s="0">
-        <v>5</v>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
@@ -51404,8 +55146,10 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B117" s="0">
-        <v>6</v>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -51455,8 +55199,10 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B118" s="0">
-        <v>7</v>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
@@ -51497,8 +55243,10 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B119" s="0">
-        <v>8</v>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -51561,8 +55309,10 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B120" s="0">
-        <v>9</v>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
@@ -51591,27 +55341,403 @@
           <t>mitsukyo-1ap</t>
         </is>
       </c>
-      <c r="B121" s="0">
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>최종 투자 의사결정 요약</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t>最終投資意思決定サマリー</t>
+        </is>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>챕터 10 상세 분석은 본문 참조</t>
+        </is>
+      </c>
+      <c r="F121" s="0" t="inlineStr">
+        <is>
+          <t>챕터 10 상세 분석은 본문 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B122" s="0">
+        <v>1</v>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>1. 투자 하이라이트 및 핵심 요약 (Executive Summary)</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t>1. エグゼクティブ・サマリー（投資判定および核心要約）</t>
+        </is>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>**시엘 블루 치바추오(Ciel Bleu 千葉中央)**는 JR 소부본선 『치바』역 도보 12분 · 『니시치바』역(치바대학) 도보 13분의 치바시 주오구 마츠나미 1초메에 위치한 **2011년 2월 준공(축 15년) 철골조 4층 건 16호실(전 호실 1K · 24.16㎡)** 수익형 맨션입니다.
+- **매매호가**: ¥222,000,000 (만실 연수입 ¥14,475,600 / 표면수익률 **6.52%** / 공실 5% 차감 실효 NOI **¥10,550,662 [Cap Rate 4.75%]**)
+- **핵심 재무 진단**: 호가 2.22억 엔 기준 국세청 표준 적산비율이 **54.9%(¥121.87M)**에 불과하고, 25년 융자(LTV 85%, 금리 2.5%) 시 세전 CF **+¥392,185(DSCR 1.04배, BEP 92.3%)**, 세후 CF **-¥70,747(1년차 즉시 데드크로스)**로 수익 완충력이 극히 취약합니다.
+- **최종 판정**: **조건부 매수(Conditional Buy, 62/100점)** — 호가 매수는 불가하며 **1억 9,500만~1억 9,800만 엔(표면 7.31%~7.42%) 지가 네고 및 25년·2.2% 이하 융자 특약** 성사 시에만 매수를 권고합니다.</t>
+        </is>
+      </c>
+      <c r="F122" s="0" t="inlineStr">
+        <is>
+          <t>**Ciel Bleu 千葉中央（シエルブルー千葉中央）**は、JR総武本線『千葉』駅 徒歩12分・『西千葉』駅（千葉大学）徒歩13分の千葉市中央区松波1丁目に位置する、**2011年2月築（築15年）鉄骨造4階建・全16戸（全戸1K・24.16㎡）**の一棟収益マンションです。
+- **売出価格**: ¥222,000,000（満室年収入 ¥14,475,600 / 表面利回り **6.52%** / 空室5%控除後実効NOI **¥10,550,662 [Cap Rate 4.75%]**）
+- **財務診断の結論**: 売出価格2.22億円では国税庁標準積算比率が**54.9%（¥121.87M）**にとどまり、25年融資（LTV 85%・金利2.5%）でも税引前CF **+¥392,185（DSCR 1.04倍・BEP 92.3%）**、税引後CF **-¥70,747（初年度即時デッドクロス）**となります。
+- **最終判定**: **条件付推奨（Conditional Buy、62/100点）** — 売出価格での買付は見送り、**1億9,500万〜1億9,800万円（表面7.31%〜7.42%）への指値交渉および25年・金利2.2%以下の融資特約**を必須条件とします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B123" s="0">
+        <v>2</v>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>2. 물건 개요 및 하드웨어·건축법규 적법성 감사</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="inlineStr">
+        <is>
+          <t>2. 物件概要およびハードウェア・建築法規の遵法性監査</t>
+        </is>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>- **토지 및 도시계획**: 토지 185.88㎡(56.23평, 소유권), 시가화구역 내 제1종주거지역(건폐율 60% / 용적률 200%).
+- **건물 및 용적률 적법성**: 건축면적 99.64㎡(건폐율 **53.60% ≤ 60%**), 연면적 359.79㎡(용적률 **193.56% ≤ 200%**)로 건폐율·용적률 모두 법정 한도 내에 적법하게 수렴합니다.
+- **전유면적(24.16㎡×16호=386.56㎡) vs 등기 연면적(359.79㎡) 괴리 체크**: 호실당 모집 표기 면적 합계(386.56㎡)가 등기 연면적(359.79㎡)보다 26.77㎡ 크므로, 발코니·PS·벽심 면적 포함 여부를 건물도면 및 임대차계약서 원본에서 반드시 대조해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F123" s="0" t="inlineStr">
+        <is>
+          <t>- **土地・都市計画**: 土地185.88㎡（56.23坪・所有権）、市街化区域・第一種住居地域（建蔽率60% / 容積率200%）。
+- **建物・遵法性評価**: 建築面積99.64㎡（建蔽率 **53.60% ≤ 60%**）、延床面積359.79㎡（容積率 **193.56% ≤ 200%**）であり、建蔽率・容積率ともに法定上限内に適法に収まっています。
+- **専有面積合計（24.16㎡×16戸＝386.56㎡）と延床面積（359.79㎡）の差異確認**: 募集表記面積の合計が登記延床面積を26.77㎡上回るため、バルコニーやパイプスペース（PS）込み表記かどうかを各階平面図で確認する必要があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B124" s="0">
+        <v>3</v>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>3. 입지·상권 및 치바역·니시치바역(치바대) 임대 수요 분석</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="inlineStr">
+        <is>
+          <t>3. 立地・商圏および千葉駅・西千葉駅（千葉大）賃貸需要分析</t>
+        </is>
+      </c>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t>- **치바역(도보 12분) × 니시치바역(도보 13분)의 더블 배후수요**:
+  1. **직장인 통근 수요(JR 치바역)**: 소부선 쾌속으로 도쿄역 직통 39분, 치바역 주변 상업·오피스 밀집지 근무 20~30대 단신 사회인 수요.
+  2. **대학·의료기관 수요(JR 니시치바역)**: 도보권 내 국립 치바대학(학생 약 1.1만 명), 케이아이대학, 치바경제대학 및 국립병원기구 치바의료센터 종사자 수요.
+- **마츠나미 1초메의 주거 환경**: 치바역 유흥가(사카에마치 등)와 분리된 조용하고 안전한 전통 주거·문교 에어리어로 여성 임차인 및 대학원생·사회인 선호도가 높습니다.</t>
+        </is>
+      </c>
+      <c r="F124" s="0" t="inlineStr">
+        <is>
+          <t>- **千葉駅（徒歩12分）× 西千葉駅（徒歩13分）のダブル賃貸需要**:
+  1. **社会人通勤需要（JR千葉駅）**: 総武線快速で東京駅へ直通約39分。千葉駅周辺の商業・オフィス街に勤務する単身社会人の職住近接ニーズ。
+  2. **大学・医療従事者需要（JR西千葉駅）**: 国立千葉大学（西千葉キャンパス・学生約1.1万人）、敬愛大学、千葉経済大学、および国立病院機構千葉医療センターの関係者ニーズ。
+- **松波1丁目の住環境**: 繁華街（栄町等）から離れた閑静な文教・住宅街であり、オートロック・防犯カメラ完備の物件は女性単身者や社会人から高い支持を得ています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B125" s="0">
+        <v>4</v>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>4. 적산평가(원가법) 및 토지·건물 담보가치 정밀 검증</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="inlineStr">
+        <is>
+          <t>4. 積算評価（原価法）および土地・建物担保価値の精密査定</t>
+        </is>
+      </c>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t>- **토지 적산평가**: 전면 상속세 노선가 `345,000엔/㎡`(추정) × `185.88㎡` = **¥64,128,600 (호가 대비 28.9%)**.
+- **건물 적산평가 시나리오 비교 (연면적 359.79㎡, 철골조 법정 34년, 잔존 19년 [잔존율 55.88%])**:
+  1. **은행 보수 기준 (170,000엔/㎡)**: 건물 4,461.6만 + 토지 6,412.9만 = **1억 874만 엔 (적산비율 49.0%)**
+  2. **국세청 표준 기준 (220,000엔/㎡)**: 건물 5,773.8만 + 토지 6,412.9만 = **1억 2,187만 엔 (적산비율 54.9%)**
+  3. **시장 재조달 기준 (320,000엔/㎡)**: 건물 8,398.3만 + 토지 6,412.9만 = **1억 4,811만 엔 (적산비율 66.7%)**
+- **담보 부족 경고**: 호가(2.22억 엔)와 표준 적산가(1.22억 엔) 간에 **약 1억 엔의 담보 괴리**가 존재하므로 수익환원 평가 금융기관 확보 및 가격 네고가 필수입니다.</t>
+        </is>
+      </c>
+      <c r="F125" s="0" t="inlineStr">
+        <is>
+          <t>- **土地積算評価**: 前面相続税路線価 `345,000円/㎡`（推定）× `185.88㎡` = **¥64,128,600（売出比 28.9%）**。
+- **建物積算評価シナリオ比較（延床359.79㎡、S造法定34年、残存19年［残存率55.88%］）**:
+  1. **銀行保守基準 (170,000円/㎡)**: 建物 4,461.6万 ＋ 土地 6,412.9万 ＝ **1億874万円（積算比率 49.0%）**
+  2. **国税庁標準基準 (220,000円/㎡)**: 建物 5,773.8万 ＋ 土地 6,412.9万 ＝ **1億2,187万円（積算比率 54.9%）**
+  3. **市場再調達基準 (320,000円/㎡)**: 建物 8,398.3万 ＋ 土地 6,412.9万 ＝ **1億4,811万円（積算比率 66.7%）**
+- **担保評価乖離の警告**: 売出価格（2.22億円）と標準積算（1.22億円）の間に**約1億円の乖離**があるため、収益還元重視の金融機関開拓と指値交渉が不可欠です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B126" s="0">
+        <v>5</v>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>5. 렌트롤 포렌식 감사 및 24.16㎡ 1K 임대 경쟁력 분석</t>
+        </is>
+      </c>
+      <c r="D126" s="0" t="inlineStr">
+        <is>
+          <t>5. レントロール監査および24.16㎡ 1Kの賃貸競争力分析</t>
+        </is>
+      </c>
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t>- **현황 임대료 수준 검증**: 만실 연수입 ¥14,475,600(월 ¥1,206,300) ÷ 16호 = **호당 평균 월 총임대료 ¥75,394(공익비 포함, 평당 약 ¥10,318)**.
+- **인근 경쟁 물건 비교**: 치바역·니시치바역 도보 12~13분권 축 15년 1K(22~24㎡) 시세는 월 6.8만~7.5만 엔 수준으로, 본 물건의 평균 7.54만 엔은 **시장 시세 상단(약간 강세~적정 상한)**에 위치합니다.
+- **핵심 점검 사항**: 엘리베이터가 없는 4층 건물이므로 1층(방범)·4층(계단) 호실의 퇴거 후 재모집 시 월 2,000~3,000엔의 임대료 조정(평균 7.25만 엔화) 리스크를 감안해야 하며, 개별 렌트롤 원본을 통해 최근 프리렌트·법인 사택 고가 계약 여부를 반드시 검증해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F126" s="0" t="inlineStr">
+        <is>
+          <t>- **現行賃料水準の検証**: 満室年収入 ¥14,475,600（月額 ¥1,206,300）÷ 16戸 ＝ **1戸あたり平均月額総賃料 ¥75,394（共益費込・坪単価 約¥10,318）**。
+- **近隣競合比較**: 千葉駅・西千葉駅徒歩12〜13分圏の築15年1K（22〜24㎡）相場は月額6.8万〜7.5万円であり、本物件の平均7.54万円は**市場相場の上限近辺**に位置します。
+- **重点監査事項**: エレベーター無しの4階建であるため、1階および4階住戸の退去再募集時に▲2,000〜3,000円/月の賃料調整リスクがあるほか、個別レントロール原本で直近のフリーレント付き高値成約（水増し）がないか精査が必要です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B127" s="0">
+        <v>6</v>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>6. 운영경비(OPEX) 정규화 및 순영업소득(NOI) 모델링</t>
+        </is>
+      </c>
+      <c r="D127" s="0" t="inlineStr">
+        <is>
+          <t>6. 運営経費(OPEX)の正規化および純営業収益(NOI)分析</t>
+        </is>
+      </c>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>- **정규화 연간 운영경비(OPEX) ¥3,201,158 (만실 GPI 대비 22.11% / 실효 EGI 대비 23.28%)**:
+  1. PM 임대관리 위탁수수료(5.5% 세금포함): **¥796,158 (5.50%)**
+  2. 건물유지관리·정기청소·소방점검 및 **전 16호 무료 인터넷 회선비**: **¥780,000 (5.39%)**
+  3. 고정자산세·도시계획세(소규모주택용지 특례 반영 추정): **¥825,000 (5.70%)**
+  4. 화재·시설배상책임보험료(연환산): **¥160,000 (1.11%)**
+  5. 퇴거 시 원상복구비·중개 AD(연 3~4호 회전 가정): **¥320,000 (2.21%)**
+  6. 일상 소수선 및 급탕기·에어컨 교체 적립금: **¥320,000 (2.21%)**
+- **실효 순영업소득(Effective NOI, 공실 5% 차감)**: **¥10,550,662 / 년 (실효 Cap Rate 4.75% / 만실 NOI ¥11,274,442 [5.08%])**.</t>
+        </is>
+      </c>
+      <c r="F127" s="0" t="inlineStr">
+        <is>
+          <t>- **正規化年間運営経費(OPEX) ¥3,201,158（対GPI比率 22.11% / 対EGI比率 23.28%）**:
+  1. PM賃貸管理委託費（税込5.5%）: **¥796,158 (5.50%)**
+  2. 建物維持管理・清掃・消防点検・**全16戸無料インターネット回線費**: **¥780,000 (5.39%)**
+  3. 固定資産税・都市計画税（小規模住宅用地特例反映推計）: **¥825,000 (5.70%)**
+  4. 火災・施設賠償責任保険料（年換算）: **¥160,000 (1.11%)**
+  5. 退去時原状回復・募集AD費（年3〜4戸退去想定）: **¥320,000 (2.21%)**
+  6. 日常修繕・給湯器エアコン更新積立: **¥320,000 (2.21%)**
+- **実効営業純利益(Effective NOI、空室5%控除)**: **¥10,550,662 / 年（実効Cap Rate 4.75% / 満室NOI ¥11,274,442 [5.08%]）**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B128" s="0">
+        <v>7</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>7. 금융 조달, 현금흐름(Cash Flow) 및 5대 시나리오 비교 분석</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="inlineStr">
+        <is>
+          <t>7. 融資ストラクチャー・キャッシュフローおよび5シナリオ比較分析</t>
+        </is>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t>- **법정 잔존(19년) vs 경제 잔존(25년) vs 지가 네고(1.98억·1.90억) 비교**:
+  1. **호가 2.22억 / 19년(법정잔존) / 2.5%**: 연간 원리금(ADS) ¥12,486,515 → **세전 CF -¥1,935,853 (DSCR 0.84배, 즉시 적자)**
+  2. **호가 2.22억 / 25년(경제잔존) / 2.5% [Base Case]**: ADS ¥10,158,477 → **세전 CF +¥392,185, 세후 CF -¥70,747 (DSCR 1.04배, 1년차 세후 데드크로스)**
+  3. **제1 네고 목표 1.98억(표면 7.31%) / 25년 / 2.2%**: 대출 ¥168,300,000, ADS ¥8,758,169 → **세전 CF +¥1,792,493, 세후 CF +¥969,523 (DSCR 1.20배, BEP 82.6%)**
+  4. **제2 네고 목표 1.90억(표면 7.62%) / 25년 / 2.2%**: 대출 ¥161,500,000, ADS ¥8,404,304 → **세전 CF +¥2,146,358, 세후 CF +¥1,250,067 (DSCR 1.26배, BEP 80.2%)**</t>
+        </is>
+      </c>
+      <c r="F128" s="0" t="inlineStr">
+        <is>
+          <t>- **法定残存（19年）vs 経済残存（25年）vs 指値交渉（1.98億・1.90億円）比較**:
+  1. **売出2.22億 / 19年（法定残存）/ 2.5%**: ADS ¥12,486,515 → **税引前CF -¥1,935,853（DSCR 0.84倍・即時赤字）**
+  2. **売出2.22億 / 25年（経済残存）/ 2.5% [Base Case]**: ADS ¥10,158,477 → **税引前CF +¥392,185、税引後CF -¥70,747（DSCR 1.04倍・初年度デッドクロス）**
+  3. **第1指値目標 1.98億（表面7.31%）/ 25年 / 2.2%**: 借入 ¥168,300,000、ADS ¥8,758,169 → **税引前CF +¥1,792,493、税引後CF +¥969,523（DSCR 1.20倍・BEP 82.6%）**
+  4. **第2指値目標 1.90億（表面7.62%）/ 25年 / 2.2%**: 借入 ¥161,500,000、ADS ¥8,404,304 → **税引前CF +¥2,146,358、税引後CF +¥1,250,067（DSCR 1.26倍・BEP 80.2%）**</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B129" s="0">
+        <v>8</v>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>8. 법인 결산서 착지 적합성 및 10년 보유 출구(Exit) 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D129" s="0" t="inlineStr">
+        <is>
+          <t>8. 法人決算書適合性および10年保有イグジット（Exit）分析</t>
+        </is>
+      </c>
+      <c r="E129" s="0" t="inlineStr">
+        <is>
+          <t>- **초년도 데드크로스 구조 진단**: 건물 비율이 약 40.08%(건물가 약 8,897만 엔), 간이법 감가상각 기간이 **22년(연 상각비 ¥4,044,214)**인 반면, 호가 기준 1년차 원금상환액이 **¥5,503,757**에 달해 취득 첫해부터 `원금상환(550만) &gt; 감가상각(404만)`의 데드크로스가 발생합니다.
+- **10년 보유 후 매각(Exit Cap 7.5% = 매각가 1억 9,300만 엔 가정)**:
+  - 호가(2.22억 엔) 매입 시: 10년 누적 세전 CF +185만 엔 + 매각 순수취액 5,954만 엔 − 초기자기자본 4,978만 엔 = **10년 총 순이익 +1,161만 엔 (Pre-tax IRR 약 2.3%)**.
+  - **1.98억 엔 네고 매입 시**: 10년 누적 세전 CF +1,586만 엔 + 매각 순수취액 7,490만 엔 − 초기자기자본 4,510만 엔 = **10년 총 순이익 +4,566만 엔 (자기자본배수 2.01배, Pre-tax IRR 약 8.1%)**.</t>
+        </is>
+      </c>
+      <c r="F129" s="0" t="inlineStr">
+        <is>
+          <t>- **初年度デッドクロス構造の診断**: 建物比率約40.08%（建物按分約8,897万円）、簡便法耐用年数**22年（年間償却費 ¥4,044,214）**に対し、売出価格ベースの初年度元金返済額は**¥5,503,757**に達するため、初年度から『元金返済（550万円）＞減価償却（404万円）』のデッドクロスが発生します。
+- **10年保有後イグジット試算（Exit表面7.5%＝想定売却額1億9,300万円）**:
+  - 売出価格（2.22億円）購入時: 10年総純利益 **+1,161万円（Pre-tax IRR 約2.3%）**。
+  - **指値1.98億円購入時**: 10年累積CF +1,586万円 ＋ 売却手残り 7,490万円 − 自己資金 4,510万円 ＝ **10年総純利益 +4,566万円（自己資金倍率 2.01倍、Pre-tax IRR 約8.1%）**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B130" s="0">
+        <v>9</v>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t>9. 재해(Hazard), 대규모 수선(CAPEX) 및 금리 스트레스 테스트</t>
+        </is>
+      </c>
+      <c r="D130" s="0" t="inlineStr">
+        <is>
+          <t>9. ハザード・大規模修繕(CAPEX)および金利ストレステスト</t>
+        </is>
+      </c>
+      <c r="E130" s="0" t="inlineStr">
+        <is>
+          <t>- **금리 상승 스트레스 테스트(호가 2.22억·25년 융자 기준)**: 금리가 **2.5% → 3.0%(+0.5%p)**로 상승하면 연간 세전 CF가 **-¥192,190(세후 -¥800,190, DSCR 0.98배)** 적자로 전락하며, **3.5%(+1.0%p)** 상승 시 **세전 -¥796,405**의 현금 유출이 발생합니다.
+- **준공 15년차 대규모 수선(CAPEX) 리스크**: 2011년 2월 준공 후 만 15년이 경과하여 **외벽 도장·실링 재시공·옥상 방수 공사(약 650만~850만 엔)** 및 **전 16호 급탕기·에어컨 교체(약 320만 엔)** 주기에 진입했습니다. 매도자의 기실시 여부를 반드시 확인하고 미실시 시 약 1,000만 엔의 초기 CAPEX 예산을 가격 인하(네고) 논리로 제시해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F130" s="0" t="inlineStr">
+        <is>
+          <t>- **金利上昇ストレステスト（売出2.22億・25年融資時）**: 借入金利が**2.5%→3.0%（+0.5%p）**へ上昇すると年間税引前CFは**-¥192,190（税引後 -¥800,190、DSCR 0.98倍）**の赤字に転落し、**3.5%（+1.0%p）**では**税引前 -¥796,405**の持ち出しとなります。
+- **築15年時点の大規模修繕（CAPEX）リスク**: 2011年2月築で築15年を迎えており、**外壁塗装・シーリング・屋上防水改修（約650万〜850万円）**および**全16戸の給湯器・エアコン更新（約320万円）**の適齢期です。未実施の場合は初期CAPEX約1,000万円を指値交渉の根拠として提示すべきです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="inlineStr">
+        <is>
+          <t>ciel-bleu-chiba-chuo</t>
+        </is>
+      </c>
+      <c r="B131" s="0">
         <v>10</v>
       </c>
-      <c r="C121" s="0" t="inlineStr">
-        <is>
-          <t>최종 투자 의사결정 요약</t>
-        </is>
-      </c>
-      <c r="D121" s="0" t="inlineStr">
-        <is>
-          <t>最終投資意思決定サマリー</t>
-        </is>
-      </c>
-      <c r="E121" s="0" t="inlineStr">
-        <is>
-          <t>챕터 10 상세 분석은 본문 참조</t>
-        </is>
-      </c>
-      <c r="F121" s="0" t="inlineStr">
-        <is>
-          <t>챕터 10 상세 분석은 본문 참조</t>
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t>10. 종합 의사결정 스코어카드 및 매수(LOI)·실사 실행 가이드</t>
+        </is>
+      </c>
+      <c r="D131" s="0" t="inlineStr">
+        <is>
+          <t>10. 総合意思決定スコアカードおよび買付(LOI)・DD実行ガイド</t>
+        </is>
+      </c>
+      <c r="E131" s="0" t="inlineStr">
+        <is>
+          <t>- **종합 스코어카드**: **62 / 100점 (20.1 / 30점, C+ 등급: 조건부 매수 Conditional Buy)**
+- **매수의향서(LOI) 제출 조건**: 목표 매수가 **1억 9,500만~1억 9,800만 엔(표면 7.31%~7.42%)** + **융자기간 25년 이상·금리 2.2% 이하 융자 특약 필수**.
+- **계약 전 최우선 징구 서류 5선**:
+  1. **16호실 상세 렌트롤 원본**: 호실별 월세·공익비·입주일·보증금·계약자 속성(프리렌트·고가 계약 유무 확인).
+  2. **건축확인필증·준공검사필증(検査済証) 및 구조계산서**: 철골 두께 4mm 초과(법정 34년) 입증.
+  3. **레이와 7·8년도 고정자산세·도시계획세 과세명세서**.
+  4. **과거 15년간 대규모 수선 이력서(외벽·옥상방수·급탕기)**.
+  5. **무료 인터넷 설비 계약서 및 월간 런닝코스트 실비 명세서**.</t>
+        </is>
+      </c>
+      <c r="F131" s="0" t="inlineStr">
+        <is>
+          <t>- **総合スコアカード**: **62 / 100点（20.1 / 30点、ランク C+：条件付推奨 Conditional Buy）**
+- **買付申込書（LOI）提出条件**: 指値目標 **1億9,500万〜1億9,800万円（表面7.31%〜7.42%）**＋ **融資期間25年以上・金利2.2%以下の融資特約必須**。
+- **契約前の最優先徴求資料5選**:
+  1. **全16戸詳細レントロール原本**: 号室別賃料・共益費・入居日・敷金・属性（水増し賃料・フリーレント有無の確認）。
+  2. **建築確認済証・検査済証および構造計算書**: 鉄骨肉厚4mm超（法定34年）の証明。
+  3. **令和7・8年度 固定資産税・都市計画税 課税明細書**。
+  4. **過去15年間の修繕履歴報告書（外壁塗装・屋上防水・給湯器）**。
+  5. **無料インターネット設備の契約書およびランニングコスト実費明細**。</t>
         </is>
       </c>
     </row>

--- a/moabiz/data/real_estate_datastore.xlsx
+++ b/moabiz/data/real_estate_datastore.xlsx
@@ -6835,381 +6835,898 @@
           <t>True</t>
         </is>
       </c>
-      <c r="E14" s="0">
-        <v>51.4</v>
-      </c>
-      <c r="F14" s="0">
-        <v>18</v>
-      </c>
-      <c r="G14" s="0">
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>MAISOKU_ONLY (마이소쿠단계)</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>시엘 블루 치바추오</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>Ciel Bleu 千葉中央</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t>千葉県千葉市中央区松波1丁目19-12</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (주거표시 千葉県千葉市中央区松波1丁目19-12 — 지번은 등기부 확인 필요)</t>
+        </is>
+      </c>
+      <c r="N14" s="0" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%E6%9D%BE%E6%B3%A21%E4%B8%81%E7%9B%AE19-12</t>
+        </is>
+      </c>
+      <c r="O14" s="0" t="inlineStr">
+        <is>
+          <t>222000000</t>
+        </is>
+      </c>
+      <c r="P14" s="0" t="inlineStr">
+        <is>
+          <t>2억 2,200만 엔</t>
+        </is>
+      </c>
+      <c r="Q14" s="0" t="inlineStr">
+        <is>
+          <t>비과세 (주거용 1K 16호 — 부지 내 주차장 등 과세매출 유무 확인 필요)</t>
+        </is>
+      </c>
+      <c r="R14" s="0" t="inlineStr">
+        <is>
+          <t>중개 (媒介)</t>
+        </is>
+      </c>
+      <c r="S14" s="0" t="inlineStr">
+        <is>
+          <t>상담 (相談 — 계약부적합책임 면책 특약 유무 확인 필요)</t>
+        </is>
+      </c>
+      <c r="T14" s="0" t="inlineStr">
+        <is>
+          <t>185.88</t>
+        </is>
+      </c>
+      <c r="U14" s="0" t="inlineStr">
+        <is>
+          <t>56.23</t>
+        </is>
+      </c>
+      <c r="V14" s="0" t="inlineStr">
+        <is>
+          <t>소유권 (所有権)</t>
+        </is>
+      </c>
+      <c r="W14" s="0" t="inlineStr">
+        <is>
+          <t>택지 (宅地 — 소규모주택용지 16호×200㎡ 한도 내 100% 1/6 감면 특례 대상)</t>
+        </is>
+      </c>
+      <c r="X14" s="0" t="inlineStr">
+        <is>
+          <t>평탄지 (平坦地)</t>
+        </is>
+      </c>
+      <c r="Y14" s="0" t="inlineStr">
+        <is>
+          <t>시가화구역 (市街化区域)</t>
+        </is>
+      </c>
+      <c r="Z14" s="0" t="inlineStr">
+        <is>
+          <t>제1종주거지역 (第一種住居地域)</t>
+        </is>
+      </c>
+      <c r="AA14" s="0" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="AB14" s="0" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="0" t="inlineStr">
+        <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="AD14" s="0" t="inlineStr">
+        <is>
+          <t>193.56</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (준방화지역 또는 법22조구역 여부 건축확인대장 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (마이소쿠 접도 방향·폭원 미기재 — 도로대장 및 현지 실측 필요)</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (사도부담 유무 중요사항설명서 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AH14" s="0" t="inlineStr">
+        <is>
+          <t>S_HEAVY</t>
+        </is>
+      </c>
+      <c r="AI14" s="0" t="inlineStr">
+        <is>
+          <t>철골조 지상 4층 건 (鉄骨造 4階建)</t>
+        </is>
+      </c>
+      <c r="AJ14" s="0" t="inlineStr">
+        <is>
+          <t>2011년 2월 (平成23年2月)</t>
+        </is>
+      </c>
+      <c r="AK14" s="0" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AL14" s="0" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AM14" s="0" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN14" s="0" t="inlineStr">
+        <is>
+          <t>359.79</t>
+        </is>
+      </c>
+      <c r="AO14" s="0" t="inlineStr">
+        <is>
+          <t>359.79</t>
+        </is>
+      </c>
+      <c r="AP14" s="0" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AQ14" s="0" t="inlineStr">
+        <is>
+          <t>전 호실 1K (24.16㎡) × 16호 (100% 단일 평형, 만실 가동 중)</t>
+        </is>
+      </c>
+      <c r="AR14" s="0" t="inlineStr">
+        <is>
+          <t>주륜장 완비 (駐輪場有 — 자동차 주차장 유무 및 수입 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AS14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (2011년 2월 준공으로 보유 확실시되나 사본 징구 필수)</t>
+        </is>
+      </c>
+      <c r="AT14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (준공검사필증 사본 및 철골 두께 4mm 초과 여부 확인 필수)</t>
+        </is>
+      </c>
+      <c r="AU14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (도시가스 vs 프로판가스 여부 확인 필수)</t>
+        </is>
+      </c>
+      <c r="AV14" s="0" t="inlineStr">
+        <is>
+          <t>공영수도 · 공공하수 (추정 — 중요사항설명서 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AW14" s="0" t="inlineStr">
+        <is>
+          <t>없음 (지상 4층 건 — EV 유지보수비 절감 장점 및 4층 임차 저항 양면성)</t>
+        </is>
+      </c>
+      <c r="AX14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (준공 15년차 — 외벽도장·옥상방수 1차 대규모 수선 실시 이력 확인 필수)</t>
+        </is>
+      </c>
+      <c r="AY14" s="0" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AZ14" s="0" t="inlineStr">
+        <is>
+          <t>14475600</t>
+        </is>
+      </c>
+      <c r="BA14" s="0" t="inlineStr">
+        <is>
+          <t>14475600</t>
+        </is>
+      </c>
+      <c r="BB14" s="0" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="BC14" s="0" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="BD14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="BE14" s="0" t="inlineStr">
+        <is>
+          <t>3201158</t>
+        </is>
+      </c>
+      <c r="BF14" s="0" t="inlineStr">
+        <is>
+          <t>22.11</t>
+        </is>
+      </c>
+      <c r="BG14" s="0" t="inlineStr">
+        <is>
+          <t>11274442</t>
+        </is>
+      </c>
+      <c r="BH14" s="0" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="BI14" s="0" t="inlineStr">
+        <is>
+          <t>345000</t>
+        </is>
+      </c>
+      <c r="BJ14" s="0" t="inlineStr">
+        <is>
+          <t>64128600</t>
+        </is>
+      </c>
+      <c r="BK14" s="0" t="inlineStr">
+        <is>
+          <t>57738094</t>
+        </is>
+      </c>
+      <c r="BL14" s="0" t="inlineStr">
+        <is>
+          <t>54.89</t>
+        </is>
+      </c>
+      <c r="BM14" s="0" t="inlineStr">
+        <is>
+          <t>56112525</t>
+        </is>
+      </c>
+      <c r="BN14" s="0" t="inlineStr">
+        <is>
+          <t>37529761</t>
+        </is>
+      </c>
+      <c r="BO14" s="0" t="inlineStr">
+        <is>
+          <t>825000</t>
+        </is>
+      </c>
+      <c r="BP14" s="0" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="BQ14" s="0" t="inlineStr">
+        <is>
+          <t>188700000</t>
+        </is>
+      </c>
+      <c r="BR14" s="0" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="BS14" s="0" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BT14" s="0" t="inlineStr">
+        <is>
+          <t>10158477</t>
+        </is>
+      </c>
+      <c r="BU14" s="0" t="inlineStr">
+        <is>
+          <t>392185</t>
+        </is>
+      </c>
+      <c r="BV14" s="0" t="inlineStr">
+        <is>
+          <t>-70747</t>
+        </is>
+      </c>
+      <c r="BW14" s="0" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BX14" s="0" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="BY14" s="0" t="inlineStr">
+        <is>
+          <t>92.29</t>
+        </is>
+      </c>
+      <c r="BZ14" s="0" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="CA14" s="0" t="inlineStr">
+        <is>
+          <t>49780664</t>
+        </is>
+      </c>
+      <c r="CB14" s="0" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="CC14" s="0" t="inlineStr">
+        <is>
+          <t>JR 소부본선 『치바(千葉)』역 도보 12분 · JR 주오·소부완행선 『니시치바(西千葉)』역 도보 13분 · 치바 도시 모노레일 『사쿠사베(作草部)』역 도보 13분</t>
+        </is>
+      </c>
+      <c r="CD14" s="0" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="CE14" s="0" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="CF14" s="0" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="CG14" s="0" t="inlineStr">
+        <is>
+          <t>대체로 평탄한 주택·문교지구 동선 (치바역 북구~마츠나미 1초메 직선 접근)</t>
+        </is>
+      </c>
+      <c r="CH14" s="0" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/%E5%8D%83%E8%91%89%E9%A7%85/%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%E6%9D%BE%E6%B3%A21%E4%B8%81%E7%9B%AE19-12/</t>
+        </is>
+      </c>
+      <c r="CI14" s="0" t="inlineStr">
+        <is>
+          <t>치바시 홍수 해저드맵 하천범람 구역 외 (국지성 호우 시 내수침수 0.1~0.5m 가능성 확인 및 수재보험 특약 권장)</t>
+        </is>
+      </c>
+      <c r="CJ14" s="0" t="inlineStr">
+        <is>
+          <t>해당 없음 (평탄한 제1종주거지역 — 토사재해 경계구역 외)</t>
+        </is>
+      </c>
+      <c r="CK14" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="CL14" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="CM14" s="0" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="CN14" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO14" s="0" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="CP14" s="0" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="CQ14" s="0" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="CR14" s="0" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="CS14" s="0" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="CT14" s="0" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="CU14" s="0" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CV14" s="0" t="inlineStr">
+        <is>
+          <t>C+ 등급 (62/100점 | 20.1/30점) — JR 치바역 도보 12분·니시치바역(치바대) 도보 13분, 전 16호 24.16㎡ 광폭 1K + 오토록·택배함·무료인터넷 완비(만실). 단, 호가 2.22억 엔(표면 6.52%) 기준 적산비율 54.9%(은행보수 49.0%), DSCR 1.04배, 1년차 세후 CF -7.1만 엔(즉시 데드크로스)으로 호가 매수 불가. 1.95억~1.98억 엔(표면 7.31%~7.42%) 지가 네고 및 25년 융자 조건부 매수(Conditional Buy)</t>
+        </is>
+      </c>
+      <c r="CW14" s="0" t="inlineStr">
+        <is>
+          <t>조건부 매수 (1.98억 네고 필수)</t>
+        </is>
+      </c>
+      <c r="CX14" s="0" t="inlineStr">
+        <is>
+          <t>부적합 (호가 2.22억 엔 매입 시 세후 CF -7.1만 엔 적자 및 통합 상환연수 24.1→27.9년 악화 / 단, 1.98억 엔·2.2% 네고 시 세후 CF +178.1만 엔·ICR 1.20배로 적합 전환)</t>
+        </is>
+      </c>
+      <c r="CY14" s="0" t="inlineStr">
+        <is>
+          <t>조건부 매수 (62 / 100점 — 호가 2.22억 엔 매수 보류 · 1.95억~1.98억 엔 네고 필수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E15" s="0">
+        <v>74.3</v>
+      </c>
+      <c r="F15" s="0">
+        <v>26</v>
+      </c>
+      <c r="G15" s="0">
         <v>5</v>
       </c>
-      <c r="H14" s="0">
+      <c r="H15" s="0">
+        <v>4</v>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>PARTIAL_DD (일부서류입수)</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>니시타케노츠카 2초메 카렌 레지던스</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>西竹の塚2丁目 カレンレジデンス</t>
+        </is>
+      </c>
+      <c r="L15" s="0" t="inlineStr">
+        <is>
+          <t>東京都足立区西竹の塚2-4-36</t>
+        </is>
+      </c>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t>東京都足立区西竹の塚二丁目1325番29</t>
+        </is>
+      </c>
+      <c r="N15" s="0" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=%E6%9D%B1%E4%BA%AC%E9%83%BD%E8%B6%B3%E7%AB%8B%E5%8C%BA%E8%A5%BF%E7%AB%B9%E3%81%AE%E5%A1%9A2-4-36</t>
+        </is>
+      </c>
+      <c r="O15" s="0">
+        <v>330000000</v>
+      </c>
+      <c r="P15" s="0" t="inlineStr">
+        <is>
+          <t>3억 3,000만 엔</t>
+        </is>
+      </c>
+      <c r="Q15" s="0" t="inlineStr">
+        <is>
+          <t>소비세 포함 (税込 — 신축 건물분 소비세 포함가)</t>
+        </is>
+      </c>
+      <c r="R15" s="0" t="inlineStr">
+        <is>
+          <t>중개 (仲介)</t>
+        </is>
+      </c>
+      <c r="S15" s="0" t="inlineStr">
+        <is>
+          <t>상담 (相談 — 현황 전 12호 공실 모집 중)</t>
+        </is>
+      </c>
+      <c r="T15" s="0">
+        <v>384.62</v>
+      </c>
+      <c r="U15" s="0">
+        <v>116.35</v>
+      </c>
+      <c r="V15" s="0" t="inlineStr">
+        <is>
+          <t>소유권 (所有権)</t>
+        </is>
+      </c>
+      <c r="W15" s="0" t="inlineStr">
+        <is>
+          <t>택지 (宅地 — 소규모주택용지 12호×200㎡ 한도 내 100% 1/6·1/3 감면 특례 대상)</t>
+        </is>
+      </c>
+      <c r="X15" s="0" t="inlineStr">
+        <is>
+          <t>평탄지 · 노지상부지 (平坦地・路地状敷地［旗竿地］)</t>
+        </is>
+      </c>
+      <c r="Y15" s="0" t="inlineStr">
+        <is>
+          <t>시가화구역 (市街化区域)</t>
+        </is>
+      </c>
+      <c r="Z15" s="0" t="inlineStr">
+        <is>
+          <t>근린상업지역 (近隣商業地域)</t>
+        </is>
+      </c>
+      <c r="AA15" s="0">
+        <v>80.0</v>
+      </c>
+      <c r="AB15" s="0">
+        <v>240.0</v>
+      </c>
+      <c r="AC15" s="0">
+        <v>54.35</v>
+      </c>
+      <c r="AD15" s="0">
+        <v>157.34</v>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (근린상업지역 내 준방화지역 추정 — 건축확인대장 확인 필요)</t>
+        </is>
+      </c>
+      <c r="AF15" s="0" t="inlineStr">
+        <is>
+          <t>북측 폭 약 4.00m 공도(42조 1항 1호 도로)에 약 3.0m 접면 (노지상부지/깃대형 토지)</t>
+        </is>
+      </c>
+      <c r="AG15" s="0" t="inlineStr">
+        <is>
+          <t>없음 (42조 1항 1호 공도 접면)</t>
+        </is>
+      </c>
+      <c r="AH15" s="0" t="inlineStr">
+        <is>
+          <t>WOOD</t>
+        </is>
+      </c>
+      <c r="AI15" s="0" t="inlineStr">
+        <is>
+          <t>목조 지상 3층 건 (木造3階建 · 열화등급 3급 상당 증명서 유)</t>
+        </is>
+      </c>
+      <c r="AJ15" s="0" t="inlineStr">
+        <is>
+          <t>2026년 10월 (令和8年10月 표기 / 포털 2026년 8월 준공 모집 중)</t>
+        </is>
+      </c>
+      <c r="AK15" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="AL15" s="0">
+        <v>22</v>
+      </c>
+      <c r="AM15" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="AN15" s="0">
+        <v>605.17</v>
+      </c>
+      <c r="AO15" s="0">
+        <v>605.17</v>
+      </c>
+      <c r="AP15" s="0">
         <v>12</v>
       </c>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t>MAISOKU_ONLY (마이소쿠단계)</t>
-        </is>
-      </c>
-      <c r="J14" s="0" t="inlineStr">
-        <is>
-          <t>시엘 블루 치바추오</t>
-        </is>
-      </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t>Ciel Bleu 千葉中央</t>
-        </is>
-      </c>
-      <c r="L14" s="0" t="inlineStr">
-        <is>
-          <t>千葉県千葉市中央区松波1丁目19-12</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] (주거표시 千葉県千葉市中央区松波1丁目19-12 — 지번은 등기부 확인 필요)</t>
-        </is>
-      </c>
-      <c r="N14" s="0" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%E6%9D%BE%E6%B3%A21%E4%B8%81%E7%9B%AE19-12</t>
-        </is>
-      </c>
-      <c r="O14" s="0">
-        <v>222000000</v>
-      </c>
-      <c r="P14" s="0" t="inlineStr">
-        <is>
-          <t>2억 2,200만 엔</t>
-        </is>
-      </c>
-      <c r="Q14" s="0" t="inlineStr">
-        <is>
-          <t>비과세 (주거용 1K 16호 — 부지 내 주차장 등 과세매출 유무 확인 필요)</t>
-        </is>
-      </c>
-      <c r="R14" s="0" t="inlineStr">
-        <is>
-          <t>중개 (媒介)</t>
-        </is>
-      </c>
-      <c r="S14" s="0" t="inlineStr">
-        <is>
-          <t>상담 (相談 — 계약부적합책임 면책 특약 유무 확인 필요)</t>
-        </is>
-      </c>
-      <c r="T14" s="0">
-        <v>185.88</v>
-      </c>
-      <c r="U14" s="0">
-        <v>56.23</v>
-      </c>
-      <c r="V14" s="0" t="inlineStr">
-        <is>
-          <t>소유권 (所有権)</t>
-        </is>
-      </c>
-      <c r="W14" s="0" t="inlineStr">
-        <is>
-          <t>택지 (宅地 — 소규모주택용지 16호×200㎡ 한도 내 100% 1/6 감면 특례 대상)</t>
-        </is>
-      </c>
-      <c r="X14" s="0" t="inlineStr">
-        <is>
-          <t>평탄지 (平坦地)</t>
-        </is>
-      </c>
-      <c r="Y14" s="0" t="inlineStr">
-        <is>
-          <t>시가화구역 (市街化区域)</t>
-        </is>
-      </c>
-      <c r="Z14" s="0" t="inlineStr">
-        <is>
-          <t>제1종주거지역 (第一種住居地域)</t>
-        </is>
-      </c>
-      <c r="AA14" s="0">
-        <v>60.0</v>
-      </c>
-      <c r="AB14" s="0">
-        <v>200.0</v>
-      </c>
-      <c r="AC14" s="0">
-        <v>53.6</v>
-      </c>
-      <c r="AD14" s="0">
-        <v>193.56</v>
-      </c>
-      <c r="AE14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] (준방화지역 또는 법22조구역 여부 건축확인대장 확인 필요)</t>
-        </is>
-      </c>
-      <c r="AF14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] (마이소쿠 접도 방향·폭원 미기재 — 도로대장 및 현지 실측 필요)</t>
-        </is>
-      </c>
-      <c r="AG14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] (사도부담 유무 중요사항설명서 확인 필요)</t>
-        </is>
-      </c>
-      <c r="AH14" s="0" t="inlineStr">
-        <is>
-          <t>S_HEAVY</t>
-        </is>
-      </c>
-      <c r="AI14" s="0" t="inlineStr">
-        <is>
-          <t>철골조 지상 4층 건 (鉄骨造 4階建)</t>
-        </is>
-      </c>
-      <c r="AJ14" s="0" t="inlineStr">
-        <is>
-          <t>2011년 2월 (平成23年2月)</t>
-        </is>
-      </c>
-      <c r="AK14" s="0">
-        <v>15.0</v>
-      </c>
-      <c r="AL14" s="0">
-        <v>34</v>
-      </c>
-      <c r="AM14" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="AN14" s="0">
-        <v>359.79</v>
-      </c>
-      <c r="AO14" s="0">
-        <v>359.79</v>
-      </c>
-      <c r="AP14" s="0">
-        <v>16</v>
-      </c>
-      <c r="AQ14" s="0" t="inlineStr">
-        <is>
-          <t>전 호실 1K (24.16㎡) × 16호 (100% 단일 평형, 만실 가동 중)</t>
-        </is>
-      </c>
-      <c r="AR14" s="0" t="inlineStr">
-        <is>
-          <t>주륜장 완비 (駐輪場有 — 자동차 주차장 유무 및 수입 확인 필요)</t>
-        </is>
-      </c>
-      <c r="AS14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] (2011년 2월 준공으로 보유 확실시되나 사본 징구 필수)</t>
-        </is>
-      </c>
-      <c r="AT14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] (준공검사필증 사본 및 철골 두께 4mm 초과 여부 확인 필수)</t>
-        </is>
-      </c>
-      <c r="AU14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] (도시가스 vs 프로판가스 여부 확인 필수)</t>
-        </is>
-      </c>
-      <c r="AV14" s="0" t="inlineStr">
-        <is>
-          <t>공영수도 · 공공하수 (추정 — 중요사항설명서 확인 필요)</t>
-        </is>
-      </c>
-      <c r="AW14" s="0" t="inlineStr">
-        <is>
-          <t>없음 (지상 4층 건 — EV 유지보수비 절감 장점 및 4층 임차 저항 양면성)</t>
-        </is>
-      </c>
-      <c r="AX14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집] (준공 15년차 — 외벽도장·옥상방수 1차 대규모 수선 실시 이력 확인 필수)</t>
-        </is>
-      </c>
-      <c r="AY14" s="0">
-        <v>16</v>
-      </c>
-      <c r="AZ14" s="0">
-        <v>14475600</v>
-      </c>
-      <c r="BA14" s="0">
-        <v>14475600</v>
-      </c>
-      <c r="BB14" s="0">
-        <v>6.52</v>
-      </c>
-      <c r="BC14" s="0">
-        <v>6.52</v>
-      </c>
-      <c r="BD14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="BE14" s="0">
-        <v>3201158</v>
-      </c>
-      <c r="BF14" s="0">
-        <v>22.11</v>
-      </c>
-      <c r="BG14" s="0">
-        <v>11274442</v>
-      </c>
-      <c r="BH14" s="0">
-        <v>5.08</v>
-      </c>
-      <c r="BI14" s="0">
-        <v>345000</v>
-      </c>
-      <c r="BJ14" s="0">
-        <v>64128600</v>
-      </c>
-      <c r="BK14" s="0">
-        <v>57738094</v>
-      </c>
-      <c r="BL14" s="0">
-        <v>54.89</v>
-      </c>
-      <c r="BM14" s="0">
-        <v>56112525</v>
-      </c>
-      <c r="BN14" s="0">
-        <v>37529761</v>
-      </c>
-      <c r="BO14" s="0">
-        <v>825000</v>
-      </c>
-      <c r="BP14" s="0">
-        <v>85.0</v>
-      </c>
-      <c r="BQ14" s="0">
-        <v>188700000</v>
-      </c>
-      <c r="BR14" s="0">
-        <v>2.5</v>
-      </c>
-      <c r="BS14" s="0">
-        <v>25</v>
-      </c>
-      <c r="BT14" s="0">
-        <v>10158477</v>
-      </c>
-      <c r="BU14" s="0">
-        <v>392185</v>
-      </c>
-      <c r="BV14" s="0">
-        <v>-70747</v>
-      </c>
-      <c r="BW14" s="0">
-        <v>1.04</v>
-      </c>
-      <c r="BX14" s="0">
-        <v>1.4</v>
-      </c>
-      <c r="BY14" s="0">
-        <v>92.29</v>
-      </c>
-      <c r="BZ14" s="0">
-        <v>1.2</v>
-      </c>
-      <c r="CA14" s="0">
-        <v>49780664</v>
-      </c>
-      <c r="CB14" s="0">
-        <v>0.79</v>
-      </c>
-      <c r="CC14" s="0" t="inlineStr">
-        <is>
-          <t>JR 소부본선 『치바(千葉)』역 도보 12분 · JR 주오·소부완행선 『니시치바(西千葉)』역 도보 13분 · 치바 도시 모노레일 『사쿠사베(作草部)』역 도보 13분</t>
-        </is>
-      </c>
-      <c r="CD14" s="0">
-        <v>12</v>
-      </c>
-      <c r="CE14" s="0">
-        <v>12</v>
-      </c>
-      <c r="CF14" s="0">
-        <v>960</v>
-      </c>
-      <c r="CG14" s="0" t="inlineStr">
-        <is>
-          <t>대체로 평탄한 주택·문교지구 동선 (치바역 북구~마츠나미 1초메 직선 접근)</t>
-        </is>
-      </c>
-      <c r="CH14" s="0" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/%E5%8D%83%E8%91%89%E9%A7%85/%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%E6%9D%BE%E6%B3%A21%E4%B8%81%E7%9B%AE19-12/</t>
-        </is>
-      </c>
-      <c r="CI14" s="0" t="inlineStr">
-        <is>
-          <t>치바시 홍수 해저드맵 하천범람 구역 외 (국지성 호우 시 내수침수 0.1~0.5m 가능성 확인 및 수재보험 특약 권장)</t>
-        </is>
-      </c>
-      <c r="CJ14" s="0" t="inlineStr">
-        <is>
-          <t>해당 없음 (평탄한 제1종주거지역 — 토사재해 경계구역 외)</t>
-        </is>
-      </c>
-      <c r="CK14" s="2" t="inlineStr">
-        <is>
-          <t>[미수집]</t>
-        </is>
-      </c>
-      <c r="CL14" s="0">
+      <c r="AQ15" s="0" t="inlineStr">
+        <is>
+          <t>1LDK(32.57~33.01㎡)×6호 [1층] + 2LDK 메조네트(70.48~71.76㎡, 1F현관+2·3F)×6호</t>
+        </is>
+      </c>
+      <c r="AR15" s="0" t="inlineStr">
+        <is>
+          <t>주륜장 12개소 유 (駐輪場12ヶ所あり — 자동차 주차장 없음)</t>
+        </is>
+      </c>
+      <c r="AS15" s="0" t="inlineStr">
+        <is>
+          <t>보유 확실 (2026년 신축 — 단, 용도가 『나가야』인지 『공동주택』인지 사본 확인 필수)</t>
+        </is>
+      </c>
+      <c r="AT15" s="0" t="inlineStr">
+        <is>
+          <t>보유 확실 (2026년 신축 — 준공검사필증 및 열화등급 3급 상당 증명서 원본 징구 필수)</t>
+        </is>
+      </c>
+      <c r="AU15" s="0" t="inlineStr">
+        <is>
+          <t>LP가스 (プロパンガス — ⚠️ 도쿄 23구 역세권임에도 시공사 그룹 LP가스 채택, 무상대여 유무 확인 필수)</t>
+        </is>
+      </c>
+      <c r="AV15" s="0" t="inlineStr">
+        <is>
+          <t>공영수도 · 공공하수 (公営水道・公共下水)</t>
+        </is>
+      </c>
+      <c r="AW15" s="0" t="inlineStr">
+        <is>
+          <t>없음 (목조 3층 — 2·3층 세대는 1층 현관부터 내부 전용계단 2개소 이용)</t>
+        </is>
+      </c>
+      <c r="AX15" s="0" t="inlineStr">
+        <is>
+          <t>신축 (2026년 준공 — 시공사 하우스링크홈(주) 초기 하자보수 보증 및 10년 하자담보책임 대상)</t>
+        </is>
+      </c>
+      <c r="AY15" s="0">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="0">
+        <v>21672000</v>
+      </c>
+      <c r="BA15" s="0">
+        <v>23868000</v>
+      </c>
+      <c r="BB15" s="0">
+        <v>6.57</v>
+      </c>
+      <c r="BC15" s="0">
+        <v>7.23</v>
+      </c>
+      <c r="BD15" s="2" t="inlineStr">
+        <is>
+          <t>[미수집] (신축 미과세 상태 — 본 분석에서 정규화 OPEX 연 366.4만~377.3만 엔 산출)</t>
+        </is>
+      </c>
+      <c r="BE15" s="0">
+        <v>3663600</v>
+      </c>
+      <c r="BF15" s="0">
+        <v>16.9</v>
+      </c>
+      <c r="BG15" s="0">
+        <v>16924800</v>
+      </c>
+      <c r="BH15" s="0">
+        <v>5.13</v>
+      </c>
+      <c r="BI15" s="0">
+        <v>382500</v>
+      </c>
+      <c r="BJ15" s="0">
+        <v>147117150</v>
+      </c>
+      <c r="BK15" s="0">
+        <v>102878900</v>
+      </c>
+      <c r="BL15" s="0">
+        <v>75.76</v>
+      </c>
+      <c r="BM15" s="0">
+        <v>128727506</v>
+      </c>
+      <c r="BN15" s="0">
+        <v>59306660</v>
+      </c>
+      <c r="BO15" s="0">
+        <v>1320000</v>
+      </c>
+      <c r="BP15" s="0">
+        <v>80.0</v>
+      </c>
+      <c r="BQ15" s="0">
+        <v>264000000</v>
+      </c>
+      <c r="BR15" s="0">
+        <v>2.2</v>
+      </c>
+      <c r="BS15" s="0">
+        <v>30</v>
+      </c>
+      <c r="BT15" s="0">
+        <v>12028923</v>
+      </c>
+      <c r="BU15" s="0">
+        <v>4895877</v>
+      </c>
+      <c r="BV15" s="0">
+        <v>3283663</v>
+      </c>
+      <c r="BW15" s="0">
+        <v>1.41</v>
+      </c>
+      <c r="BX15" s="0">
+        <v>2.13</v>
+      </c>
+      <c r="BY15" s="0">
+        <v>72.4</v>
+      </c>
+      <c r="BZ15" s="0">
+        <v>3.3</v>
+      </c>
+      <c r="CA15" s="0">
+        <v>91219000</v>
+      </c>
+      <c r="CB15" s="0">
+        <v>5.37</v>
+      </c>
+      <c r="CC15" s="0" t="inlineStr">
+        <is>
+          <t>도부 스카이트리 라인(도쿄메트로 히비야선 직통) 『타케노츠카(竹ノ塚)』역 서구 도보 3분 (포털 표기 3~4분)</t>
+        </is>
+      </c>
+      <c r="CD15" s="0">
+        <v>3</v>
+      </c>
+      <c r="CE15" s="0">
+        <v>4</v>
+      </c>
+      <c r="CF15" s="0">
+        <v>270</v>
+      </c>
+      <c r="CG15" s="0" t="inlineStr">
+        <is>
+          <t>타케노츠카역 서구~세이유 앞을 지나는 완전 평탄한 근린상업지역 동선</t>
+        </is>
+      </c>
+      <c r="CH15" s="0" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/%E7%AB%B9%E3%83%8E%E5%A1%9A%E9%A7%85/%E6%9D%B1%E4%BA%AC%E9%83%BD%E8%B6%B3%E7%AB%8B%E5%8C%BA%E8%A5%BF%E7%AB%B9%E3%81%AE%E5%A1%9A2-4-36/</t>
+        </is>
+      </c>
+      <c r="CI15" s="0" t="inlineStr">
+        <is>
+          <t>아다치구 홍수 해저드맵(아라카와 범람) 예상 침수심 0.5m~3.0m 미만 구역 (1층 침수 가능 — 수재보험 특약 필수)</t>
+        </is>
+      </c>
+      <c r="CJ15" s="0" t="inlineStr">
+        <is>
+          <t>해당 없음 (평탄한 저지대 상업·주거지역 — 토사재해 경계구역 외)</t>
+        </is>
+      </c>
+      <c r="CK15" s="0" t="inlineStr">
+        <is>
+          <t>https://www.homes.co.jp/archive/b-51908415/</t>
+        </is>
+      </c>
+      <c r="CL15" s="0">
         <v>60</v>
       </c>
-      <c r="CM14" s="0">
+      <c r="CM15" s="0">
         <v>5.0</v>
       </c>
-      <c r="CN14" s="0">
-        <v>0</v>
-      </c>
-      <c r="CO14" s="0">
-        <v>2.4</v>
-      </c>
-      <c r="CP14" s="0">
-        <v>4.2</v>
-      </c>
-      <c r="CQ14" s="0">
-        <v>4.2</v>
-      </c>
-      <c r="CR14" s="0">
-        <v>3.5</v>
-      </c>
-      <c r="CS14" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="CT14" s="0">
-        <v>3.8</v>
-      </c>
-      <c r="CU14" s="0">
-        <v>20.1</v>
-      </c>
-      <c r="CV14" s="0" t="inlineStr">
-        <is>
-          <t>C+ 등급 (62/100점 | 20.1/30점) — JR 치바역 도보 12분·니시치바역(치바대) 도보 13분, 전 16호 24.16㎡ 광폭 1K + 오토록·택배함·무료인터넷 완비(만실). 단, 호가 2.22억 엔(표면 6.52%) 기준 적산비율 54.9%(은행보수 49.0%), DSCR 1.04배, 1년차 세후 CF -7.1만 엔(즉시 데드크로스)으로 호가 매수 불가. 1.95억~1.98억 엔(표면 7.31%~7.42%) 지가 네고 및 25년 융자 조건부 매수(Conditional Buy)</t>
-        </is>
-      </c>
-      <c r="CW14" s="0" t="inlineStr">
-        <is>
-          <t>조건부 매수 (1.98억 네고 필수)</t>
-        </is>
-      </c>
-      <c r="CX14" s="0" t="inlineStr">
-        <is>
-          <t>부적합 (호가 2.22억 엔 매입 시 세후 CF -7.1만 엔 적자 및 통합 상환연수 24.1→27.9년 악화 / 단, 1.98억 엔·2.2% 네고 시 세후 CF +178.1만 엔·ICR 1.20배로 적합 전환)</t>
-        </is>
-      </c>
-      <c r="CY14" s="0" t="inlineStr">
-        <is>
-          <t>조건부 매수 (62 / 100점 — 호가 2.22억 엔 매수 보류 · 1.95억~1.98억 엔 네고 필수)</t>
+      <c r="CN15" s="0">
+        <v>-2196000</v>
+      </c>
+      <c r="CO15" s="0">
+        <v>2.8</v>
+      </c>
+      <c r="CP15" s="0">
+        <v>3.9</v>
+      </c>
+      <c r="CQ15" s="0">
+        <v>2.9</v>
+      </c>
+      <c r="CR15" s="0">
+        <v>3.6</v>
+      </c>
+      <c r="CS15" s="0">
+        <v>3.3</v>
+      </c>
+      <c r="CT15" s="0">
+        <v>3.1</v>
+      </c>
+      <c r="CU15" s="0">
+        <v>19.6</v>
+      </c>
+      <c r="CV15" s="0" t="inlineStr">
+        <is>
+          <t>C+ 등급 (61/100점 | 19.6/30점) — 타케노츠카역(고가화 완공·에키아 개업·히비야선 직통) 도보 3분, 근린상업지역 116.35평 토지 + 2026년 신축 목조 3층(열화3급 상당, 605.17㎡, 적산비율 75.8%). 단, ①마이소쿠 임대료 합산 오차(-66만 엔/년) 및 실제 포털(SUUMO) 2LDK 모집가 인하(20만→17.5만~18.0만 엔, 실세 GPI 2,167.2만 엔 [표면 6.57%]), ②접도 3.0m 노지상부지 조례 우회용 1F~3F 내계단 2개소 메조네트(계단로스 18%), ③LP가스 채택 및 전 12호 공실 리스업 리스크 존재. 2.90억~2.95억 엔(실세 표면 7.35%~7.47%) 네고 + 30년 융자 + 만실 인도/마스터리스 특약 조건부 매수(Conditional Buy)</t>
+        </is>
+      </c>
+      <c r="CW15" s="0" t="inlineStr">
+        <is>
+          <t>조건부 매수 (2.95억 네고·리스업보증 필수)</t>
+        </is>
+      </c>
+      <c r="CX15" s="0" t="inlineStr">
+        <is>
+          <t>조건부 적합 (30년 융자 시 통합 상환연수 33.2→25.4년[네고시 23.9년] 및 세무 LTV 263→210% 대폭 개선 / 단, 포털 실세 반영 2.95억 엔 이하 네고 및 30년 융자·만실보증 필수)</t>
+        </is>
+      </c>
+      <c r="CY15" s="0" t="inlineStr">
+        <is>
+          <t>조건부 매수 (61 / 100점 — 호가 3.30억 엔 보류 · 포털 실세 반영 2.90억~2.95억 엔 네고 및 30년 융자 필수)</t>
         </is>
       </c>
     </row>
@@ -18725,8 +19242,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E133" s="0">
-        <v>24.16</v>
+      <c r="E133" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F133" s="0" t="inlineStr">
         <is>
@@ -18743,29 +19262,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I133" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J133" s="0">
-        <v>69000</v>
-      </c>
-      <c r="K133" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L133" s="0">
-        <v>0</v>
-      </c>
-      <c r="M133" s="0">
-        <v>73000</v>
-      </c>
-      <c r="N133" s="0">
-        <v>71000</v>
-      </c>
-      <c r="O133" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P133" s="0">
-        <v>60</v>
+      <c r="I133" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J133" s="0" t="inlineStr">
+        <is>
+          <t>69000</t>
+        </is>
+      </c>
+      <c r="K133" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L133" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M133" s="0" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="N133" s="0" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="O133" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P133" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q133" s="0" t="inlineStr">
         <is>
@@ -18794,8 +19329,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E134" s="0">
-        <v>24.16</v>
+      <c r="E134" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
@@ -18812,29 +19349,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I134" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J134" s="0">
-        <v>69000</v>
-      </c>
-      <c r="K134" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L134" s="0">
-        <v>0</v>
-      </c>
-      <c r="M134" s="0">
-        <v>73000</v>
-      </c>
-      <c r="N134" s="0">
-        <v>71000</v>
-      </c>
-      <c r="O134" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P134" s="0">
-        <v>60</v>
+      <c r="I134" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J134" s="0" t="inlineStr">
+        <is>
+          <t>69000</t>
+        </is>
+      </c>
+      <c r="K134" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L134" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M134" s="0" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="N134" s="0" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="O134" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P134" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q134" s="0" t="inlineStr">
         <is>
@@ -18863,8 +19416,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E135" s="0">
-        <v>24.16</v>
+      <c r="E135" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F135" s="0" t="inlineStr">
         <is>
@@ -18881,29 +19436,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I135" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J135" s="0">
-        <v>69000</v>
-      </c>
-      <c r="K135" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L135" s="0">
-        <v>0</v>
-      </c>
-      <c r="M135" s="0">
-        <v>73000</v>
-      </c>
-      <c r="N135" s="0">
-        <v>71000</v>
-      </c>
-      <c r="O135" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P135" s="0">
-        <v>60</v>
+      <c r="I135" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J135" s="0" t="inlineStr">
+        <is>
+          <t>69000</t>
+        </is>
+      </c>
+      <c r="K135" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L135" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M135" s="0" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="N135" s="0" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="O135" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P135" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q135" s="0" t="inlineStr">
         <is>
@@ -18932,8 +19503,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E136" s="0">
-        <v>24.16</v>
+      <c r="E136" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F136" s="0" t="inlineStr">
         <is>
@@ -18950,29 +19523,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I136" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J136" s="0">
-        <v>69300</v>
-      </c>
-      <c r="K136" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L136" s="0">
-        <v>0</v>
-      </c>
-      <c r="M136" s="0">
-        <v>73300</v>
-      </c>
-      <c r="N136" s="0">
-        <v>71000</v>
-      </c>
-      <c r="O136" s="0">
-        <v>-2300</v>
-      </c>
-      <c r="P136" s="0">
-        <v>60</v>
+      <c r="I136" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J136" s="0" t="inlineStr">
+        <is>
+          <t>69300</t>
+        </is>
+      </c>
+      <c r="K136" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L136" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M136" s="0" t="inlineStr">
+        <is>
+          <t>73300</t>
+        </is>
+      </c>
+      <c r="N136" s="0" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="O136" s="0" t="inlineStr">
+        <is>
+          <t>-2300</t>
+        </is>
+      </c>
+      <c r="P136" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q136" s="0" t="inlineStr">
         <is>
@@ -19001,8 +19590,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E137" s="0">
-        <v>24.16</v>
+      <c r="E137" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F137" s="0" t="inlineStr">
         <is>
@@ -19019,29 +19610,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I137" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J137" s="0">
-        <v>71000</v>
-      </c>
-      <c r="K137" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L137" s="0">
-        <v>0</v>
-      </c>
-      <c r="M137" s="0">
-        <v>75000</v>
-      </c>
-      <c r="N137" s="0">
-        <v>73000</v>
-      </c>
-      <c r="O137" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P137" s="0">
-        <v>60</v>
+      <c r="I137" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J137" s="0" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="K137" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L137" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M137" s="0" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="N137" s="0" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="O137" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P137" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q137" s="0" t="inlineStr">
         <is>
@@ -19070,8 +19677,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E138" s="0">
-        <v>24.16</v>
+      <c r="E138" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F138" s="0" t="inlineStr">
         <is>
@@ -19088,29 +19697,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I138" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J138" s="0">
-        <v>71000</v>
-      </c>
-      <c r="K138" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L138" s="0">
-        <v>0</v>
-      </c>
-      <c r="M138" s="0">
-        <v>75000</v>
-      </c>
-      <c r="N138" s="0">
-        <v>73000</v>
-      </c>
-      <c r="O138" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P138" s="0">
-        <v>60</v>
+      <c r="I138" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J138" s="0" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="K138" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L138" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M138" s="0" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="N138" s="0" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="O138" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P138" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q138" s="0" t="inlineStr">
         <is>
@@ -19139,8 +19764,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E139" s="0">
-        <v>24.16</v>
+      <c r="E139" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F139" s="0" t="inlineStr">
         <is>
@@ -19157,29 +19784,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I139" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J139" s="0">
-        <v>71000</v>
-      </c>
-      <c r="K139" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L139" s="0">
-        <v>0</v>
-      </c>
-      <c r="M139" s="0">
-        <v>75000</v>
-      </c>
-      <c r="N139" s="0">
-        <v>73000</v>
-      </c>
-      <c r="O139" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P139" s="0">
-        <v>60</v>
+      <c r="I139" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J139" s="0" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="K139" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L139" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M139" s="0" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="N139" s="0" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="O139" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P139" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q139" s="0" t="inlineStr">
         <is>
@@ -19208,8 +19851,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E140" s="0">
-        <v>24.16</v>
+      <c r="E140" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F140" s="0" t="inlineStr">
         <is>
@@ -19226,29 +19871,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I140" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J140" s="0">
-        <v>71000</v>
-      </c>
-      <c r="K140" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L140" s="0">
-        <v>0</v>
-      </c>
-      <c r="M140" s="0">
-        <v>75000</v>
-      </c>
-      <c r="N140" s="0">
-        <v>73000</v>
-      </c>
-      <c r="O140" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P140" s="0">
-        <v>60</v>
+      <c r="I140" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J140" s="0" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="K140" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L140" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M140" s="0" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="N140" s="0" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="O140" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P140" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q140" s="0" t="inlineStr">
         <is>
@@ -19277,8 +19938,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E141" s="0">
-        <v>24.16</v>
+      <c r="E141" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F141" s="0" t="inlineStr">
         <is>
@@ -19295,29 +19958,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I141" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J141" s="0">
-        <v>72000</v>
-      </c>
-      <c r="K141" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L141" s="0">
-        <v>0</v>
-      </c>
-      <c r="M141" s="0">
-        <v>76000</v>
-      </c>
-      <c r="N141" s="0">
-        <v>74000</v>
-      </c>
-      <c r="O141" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P141" s="0">
-        <v>60</v>
+      <c r="I141" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J141" s="0" t="inlineStr">
+        <is>
+          <t>72000</t>
+        </is>
+      </c>
+      <c r="K141" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L141" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M141" s="0" t="inlineStr">
+        <is>
+          <t>76000</t>
+        </is>
+      </c>
+      <c r="N141" s="0" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="O141" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P141" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q141" s="0" t="inlineStr">
         <is>
@@ -19346,8 +20025,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E142" s="0">
-        <v>24.16</v>
+      <c r="E142" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F142" s="0" t="inlineStr">
         <is>
@@ -19364,29 +20045,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I142" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J142" s="0">
-        <v>72000</v>
-      </c>
-      <c r="K142" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L142" s="0">
-        <v>0</v>
-      </c>
-      <c r="M142" s="0">
-        <v>76000</v>
-      </c>
-      <c r="N142" s="0">
-        <v>74000</v>
-      </c>
-      <c r="O142" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P142" s="0">
-        <v>60</v>
+      <c r="I142" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J142" s="0" t="inlineStr">
+        <is>
+          <t>72000</t>
+        </is>
+      </c>
+      <c r="K142" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L142" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M142" s="0" t="inlineStr">
+        <is>
+          <t>76000</t>
+        </is>
+      </c>
+      <c r="N142" s="0" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="O142" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P142" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q142" s="0" t="inlineStr">
         <is>
@@ -19415,8 +20112,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E143" s="0">
-        <v>24.16</v>
+      <c r="E143" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F143" s="0" t="inlineStr">
         <is>
@@ -19433,29 +20132,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I143" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J143" s="0">
-        <v>72000</v>
-      </c>
-      <c r="K143" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L143" s="0">
-        <v>0</v>
-      </c>
-      <c r="M143" s="0">
-        <v>76000</v>
-      </c>
-      <c r="N143" s="0">
-        <v>74000</v>
-      </c>
-      <c r="O143" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P143" s="0">
-        <v>60</v>
+      <c r="I143" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J143" s="0" t="inlineStr">
+        <is>
+          <t>72000</t>
+        </is>
+      </c>
+      <c r="K143" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L143" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M143" s="0" t="inlineStr">
+        <is>
+          <t>76000</t>
+        </is>
+      </c>
+      <c r="N143" s="0" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="O143" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P143" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q143" s="0" t="inlineStr">
         <is>
@@ -19484,8 +20199,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E144" s="0">
-        <v>24.16</v>
+      <c r="E144" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F144" s="0" t="inlineStr">
         <is>
@@ -19502,29 +20219,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I144" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J144" s="0">
-        <v>72000</v>
-      </c>
-      <c r="K144" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L144" s="0">
-        <v>0</v>
-      </c>
-      <c r="M144" s="0">
-        <v>76000</v>
-      </c>
-      <c r="N144" s="0">
-        <v>74000</v>
-      </c>
-      <c r="O144" s="0">
-        <v>-2000</v>
-      </c>
-      <c r="P144" s="0">
-        <v>60</v>
+      <c r="I144" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J144" s="0" t="inlineStr">
+        <is>
+          <t>72000</t>
+        </is>
+      </c>
+      <c r="K144" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L144" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M144" s="0" t="inlineStr">
+        <is>
+          <t>76000</t>
+        </is>
+      </c>
+      <c r="N144" s="0" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="O144" s="0" t="inlineStr">
+        <is>
+          <t>-2000</t>
+        </is>
+      </c>
+      <c r="P144" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q144" s="0" t="inlineStr">
         <is>
@@ -19553,8 +20286,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E145" s="0">
-        <v>24.16</v>
+      <c r="E145" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F145" s="0" t="inlineStr">
         <is>
@@ -19571,29 +20306,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I145" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J145" s="0">
-        <v>73500</v>
-      </c>
-      <c r="K145" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L145" s="0">
-        <v>0</v>
-      </c>
-      <c r="M145" s="0">
-        <v>77500</v>
-      </c>
-      <c r="N145" s="0">
-        <v>74000</v>
-      </c>
-      <c r="O145" s="0">
-        <v>-3500</v>
-      </c>
-      <c r="P145" s="0">
-        <v>60</v>
+      <c r="I145" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J145" s="0" t="inlineStr">
+        <is>
+          <t>73500</t>
+        </is>
+      </c>
+      <c r="K145" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L145" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M145" s="0" t="inlineStr">
+        <is>
+          <t>77500</t>
+        </is>
+      </c>
+      <c r="N145" s="0" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="O145" s="0" t="inlineStr">
+        <is>
+          <t>-3500</t>
+        </is>
+      </c>
+      <c r="P145" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q145" s="0" t="inlineStr">
         <is>
@@ -19622,8 +20373,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E146" s="0">
-        <v>24.16</v>
+      <c r="E146" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F146" s="0" t="inlineStr">
         <is>
@@ -19640,29 +20393,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I146" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J146" s="0">
-        <v>73500</v>
-      </c>
-      <c r="K146" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L146" s="0">
-        <v>0</v>
-      </c>
-      <c r="M146" s="0">
-        <v>77500</v>
-      </c>
-      <c r="N146" s="0">
-        <v>74000</v>
-      </c>
-      <c r="O146" s="0">
-        <v>-3500</v>
-      </c>
-      <c r="P146" s="0">
-        <v>60</v>
+      <c r="I146" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J146" s="0" t="inlineStr">
+        <is>
+          <t>73500</t>
+        </is>
+      </c>
+      <c r="K146" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L146" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M146" s="0" t="inlineStr">
+        <is>
+          <t>77500</t>
+        </is>
+      </c>
+      <c r="N146" s="0" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="O146" s="0" t="inlineStr">
+        <is>
+          <t>-3500</t>
+        </is>
+      </c>
+      <c r="P146" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q146" s="0" t="inlineStr">
         <is>
@@ -19691,8 +20460,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E147" s="0">
-        <v>24.16</v>
+      <c r="E147" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F147" s="0" t="inlineStr">
         <is>
@@ -19709,29 +20480,45 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I147" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J147" s="0">
-        <v>73500</v>
-      </c>
-      <c r="K147" s="0">
-        <v>4000</v>
-      </c>
-      <c r="L147" s="0">
-        <v>0</v>
-      </c>
-      <c r="M147" s="0">
-        <v>77500</v>
-      </c>
-      <c r="N147" s="0">
-        <v>74000</v>
-      </c>
-      <c r="O147" s="0">
-        <v>-3500</v>
-      </c>
-      <c r="P147" s="0">
-        <v>60</v>
+      <c r="I147" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J147" s="0" t="inlineStr">
+        <is>
+          <t>73500</t>
+        </is>
+      </c>
+      <c r="K147" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L147" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M147" s="0" t="inlineStr">
+        <is>
+          <t>77500</t>
+        </is>
+      </c>
+      <c r="N147" s="0" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="O147" s="0" t="inlineStr">
+        <is>
+          <t>-3500</t>
+        </is>
+      </c>
+      <c r="P147" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="Q147" s="0" t="inlineStr">
         <is>
@@ -19760,8 +20547,10 @@
           <t>1K</t>
         </is>
       </c>
-      <c r="E148" s="0">
-        <v>24.16</v>
+      <c r="E148" s="0" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
       </c>
       <c r="F148" s="0" t="inlineStr">
         <is>
@@ -19778,33 +20567,853 @@
           <t>[미수집]</t>
         </is>
       </c>
-      <c r="I148" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J148" s="0">
-        <v>73500</v>
-      </c>
-      <c r="K148" s="0">
+      <c r="I148" s="0" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J148" s="0" t="inlineStr">
+        <is>
+          <t>73500</t>
+        </is>
+      </c>
+      <c r="K148" s="0" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="L148" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M148" s="0" t="inlineStr">
+        <is>
+          <t>77500</t>
+        </is>
+      </c>
+      <c r="N148" s="0" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="O148" s="0" t="inlineStr">
+        <is>
+          <t>-3500</t>
+        </is>
+      </c>
+      <c r="P148" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Q148" s="0" t="inlineStr">
+        <is>
+          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C149" s="0">
+        <v>1</v>
+      </c>
+      <c r="D149" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E149" s="0">
+        <v>33.01</v>
+      </c>
+      <c r="F149" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G149" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H149" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J149" s="0">
+        <v>120000</v>
+      </c>
+      <c r="K149" s="0">
         <v>4000</v>
       </c>
-      <c r="L148" s="0">
+      <c r="L149" s="0">
         <v>0</v>
       </c>
-      <c r="M148" s="0">
-        <v>77500</v>
-      </c>
-      <c r="N148" s="0">
-        <v>74000</v>
-      </c>
-      <c r="O148" s="0">
-        <v>-3500</v>
-      </c>
-      <c r="P148" s="0">
-        <v>60</v>
-      </c>
-      <c r="Q148" s="0" t="inlineStr">
-        <is>
-          <t>[마이소쿠 총연수입 ¥14,475,600(월 ¥1,206,300) 기준 층별 배분 추정치 — 상세 렌트롤 원본 징구 필수]</t>
+      <c r="M149" s="0">
+        <v>124000</v>
+      </c>
+      <c r="N149" s="0">
+        <v>122000</v>
+      </c>
+      <c r="O149" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P149" s="0">
+        <v>45</v>
+      </c>
+      <c r="Q149" s="0" t="inlineStr">
+        <is>
+          <t>1층 남서 모서리 (포털 12.0만+4천엔 모집 중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B150" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C150" s="0">
+        <v>1</v>
+      </c>
+      <c r="D150" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E150" s="0">
+        <v>33.01</v>
+      </c>
+      <c r="F150" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G150" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H150" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J150" s="0">
+        <v>118000</v>
+      </c>
+      <c r="K150" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L150" s="0">
+        <v>0</v>
+      </c>
+      <c r="M150" s="0">
+        <v>122000</v>
+      </c>
+      <c r="N150" s="0">
+        <v>119000</v>
+      </c>
+      <c r="O150" s="0">
+        <v>-3000</v>
+      </c>
+      <c r="P150" s="0">
+        <v>45</v>
+      </c>
+      <c r="Q150" s="0" t="inlineStr">
+        <is>
+          <t>1층 중간호실 (포털 11.8만+4천엔 모집 중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B151" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C151" s="0">
+        <v>1</v>
+      </c>
+      <c r="D151" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E151" s="0">
+        <v>33.01</v>
+      </c>
+      <c r="F151" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G151" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H151" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J151" s="0">
+        <v>118000</v>
+      </c>
+      <c r="K151" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L151" s="0">
+        <v>0</v>
+      </c>
+      <c r="M151" s="0">
+        <v>122000</v>
+      </c>
+      <c r="N151" s="0">
+        <v>119000</v>
+      </c>
+      <c r="O151" s="0">
+        <v>-3000</v>
+      </c>
+      <c r="P151" s="0">
+        <v>45</v>
+      </c>
+      <c r="Q151" s="0" t="inlineStr">
+        <is>
+          <t>1층 중간호실 (포털 11.8만+4천엔 모집 중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B152" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C152" s="0">
+        <v>1</v>
+      </c>
+      <c r="D152" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E152" s="0">
+        <v>33.01</v>
+      </c>
+      <c r="F152" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G152" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H152" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J152" s="0">
+        <v>118000</v>
+      </c>
+      <c r="K152" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L152" s="0">
+        <v>0</v>
+      </c>
+      <c r="M152" s="0">
+        <v>122000</v>
+      </c>
+      <c r="N152" s="0">
+        <v>119000</v>
+      </c>
+      <c r="O152" s="0">
+        <v>-3000</v>
+      </c>
+      <c r="P152" s="0">
+        <v>45</v>
+      </c>
+      <c r="Q152" s="0" t="inlineStr">
+        <is>
+          <t>1층 중간호실 (포털 11.8만+4천엔 모집 중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B153" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C153" s="0">
+        <v>1</v>
+      </c>
+      <c r="D153" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E153" s="0">
+        <v>32.78</v>
+      </c>
+      <c r="F153" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G153" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H153" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J153" s="0">
+        <v>115000</v>
+      </c>
+      <c r="K153" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L153" s="0">
+        <v>0</v>
+      </c>
+      <c r="M153" s="0">
+        <v>119000</v>
+      </c>
+      <c r="N153" s="0">
+        <v>117000</v>
+      </c>
+      <c r="O153" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P153" s="0">
+        <v>45</v>
+      </c>
+      <c r="Q153" s="0" t="inlineStr">
+        <is>
+          <t>1층 동측 중간 (포털 11.5만+4천엔 모집 중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C154" s="0">
+        <v>1</v>
+      </c>
+      <c r="D154" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E154" s="0">
+        <v>32.57</v>
+      </c>
+      <c r="F154" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G154" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H154" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J154" s="0">
+        <v>116000</v>
+      </c>
+      <c r="K154" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L154" s="0">
+        <v>0</v>
+      </c>
+      <c r="M154" s="0">
+        <v>120000</v>
+      </c>
+      <c r="N154" s="0">
+        <v>118000</v>
+      </c>
+      <c r="O154" s="0">
+        <v>-2000</v>
+      </c>
+      <c r="P154" s="0">
+        <v>45</v>
+      </c>
+      <c r="Q154" s="0" t="inlineStr">
+        <is>
+          <t>1층 북동 모서리 (포털 11.6만+4천엔 모집 중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B155" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C155" s="0">
+        <v>2</v>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E155" s="0">
+        <v>70.48</v>
+      </c>
+      <c r="F155" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G155" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H155" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J155" s="0">
+        <v>200000</v>
+      </c>
+      <c r="K155" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L155" s="0">
+        <v>0</v>
+      </c>
+      <c r="M155" s="0">
+        <v>204000</v>
+      </c>
+      <c r="N155" s="0">
+        <v>184000</v>
+      </c>
+      <c r="O155" s="0">
+        <v>-20000</v>
+      </c>
+      <c r="P155" s="0">
+        <v>75</v>
+      </c>
+      <c r="Q155" s="0" t="inlineStr">
+        <is>
+          <t>⚠️ 포털 실모집가 17.5만~18.0만+4천엔으로 인하 (계단로스 반영)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B156" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C156" s="0">
+        <v>2</v>
+      </c>
+      <c r="D156" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E156" s="0">
+        <v>70.48</v>
+      </c>
+      <c r="F156" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G156" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H156" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J156" s="0">
+        <v>195000</v>
+      </c>
+      <c r="K156" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L156" s="0">
+        <v>0</v>
+      </c>
+      <c r="M156" s="0">
+        <v>199000</v>
+      </c>
+      <c r="N156" s="0">
+        <v>181000</v>
+      </c>
+      <c r="O156" s="0">
+        <v>-18000</v>
+      </c>
+      <c r="P156" s="0">
+        <v>75</v>
+      </c>
+      <c r="Q156" s="0" t="inlineStr">
+        <is>
+          <t>⚠️ 포털 실모집가 17.5만+4천엔으로 인하 (부금0·예금0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B157" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C157" s="0">
+        <v>2</v>
+      </c>
+      <c r="D157" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E157" s="0">
+        <v>70.48</v>
+      </c>
+      <c r="F157" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G157" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H157" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J157" s="0">
+        <v>195000</v>
+      </c>
+      <c r="K157" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L157" s="0">
+        <v>0</v>
+      </c>
+      <c r="M157" s="0">
+        <v>199000</v>
+      </c>
+      <c r="N157" s="0">
+        <v>181000</v>
+      </c>
+      <c r="O157" s="0">
+        <v>-18000</v>
+      </c>
+      <c r="P157" s="0">
+        <v>75</v>
+      </c>
+      <c r="Q157" s="0" t="inlineStr">
+        <is>
+          <t>⚠️ 포털 실모집가 17.5만+4천엔으로 인하 (부금0·예금0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B158" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C158" s="0">
+        <v>2</v>
+      </c>
+      <c r="D158" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E158" s="0">
+        <v>70.48</v>
+      </c>
+      <c r="F158" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G158" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H158" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J158" s="0">
+        <v>195000</v>
+      </c>
+      <c r="K158" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L158" s="0">
+        <v>0</v>
+      </c>
+      <c r="M158" s="0">
+        <v>199000</v>
+      </c>
+      <c r="N158" s="0">
+        <v>181000</v>
+      </c>
+      <c r="O158" s="0">
+        <v>-18000</v>
+      </c>
+      <c r="P158" s="0">
+        <v>75</v>
+      </c>
+      <c r="Q158" s="0" t="inlineStr">
+        <is>
+          <t>⚠️ 포털 실모집가 17.5만+4천엔으로 인하 (부금0·예금0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B159" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C159" s="0">
+        <v>2</v>
+      </c>
+      <c r="D159" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E159" s="0">
+        <v>70.93</v>
+      </c>
+      <c r="F159" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G159" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H159" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J159" s="0">
+        <v>196000</v>
+      </c>
+      <c r="K159" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L159" s="0">
+        <v>0</v>
+      </c>
+      <c r="M159" s="0">
+        <v>200000</v>
+      </c>
+      <c r="N159" s="0">
+        <v>182000</v>
+      </c>
+      <c r="O159" s="0">
+        <v>-18000</v>
+      </c>
+      <c r="P159" s="0">
+        <v>75</v>
+      </c>
+      <c r="Q159" s="0" t="inlineStr">
+        <is>
+          <t>⚠️ 포털 실모집가 18.0만+4천엔으로 인하 (약 18.1첩 LDK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B160" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C160" s="0">
+        <v>2</v>
+      </c>
+      <c r="D160" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E160" s="0">
+        <v>71.76</v>
+      </c>
+      <c r="F160" s="0" t="inlineStr">
+        <is>
+          <t>공실 (신축모집중)</t>
+        </is>
+      </c>
+      <c r="G160" s="0" t="inlineStr">
+        <is>
+          <t>미입주 (신축 리스업 중)</t>
+        </is>
+      </c>
+      <c r="H160" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J160" s="0">
+        <v>200000</v>
+      </c>
+      <c r="K160" s="0">
+        <v>4000</v>
+      </c>
+      <c r="L160" s="0">
+        <v>0</v>
+      </c>
+      <c r="M160" s="0">
+        <v>204000</v>
+      </c>
+      <c r="N160" s="0">
+        <v>183000</v>
+      </c>
+      <c r="O160" s="0">
+        <v>-21000</v>
+      </c>
+      <c r="P160" s="0">
+        <v>75</v>
+      </c>
+      <c r="Q160" s="0" t="inlineStr">
+        <is>
+          <t>⚠️ 포털 실모집가 18.0만~19.5만+4천엔으로 인하 (북동 모서리)</t>
         </is>
       </c>
     </row>
@@ -45804,6 +47413,2001 @@
       <c r="K456" s="3" t="inlineStr">
         <is>
           <t>LIFULL HOME'Sアーカイブ履歴に基づく募集所要日数(DOM)の検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B457" s="0" t="inlineStr">
+        <is>
+          <t>CHK_01</t>
+        </is>
+      </c>
+      <c r="C457" s="0" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D457" s="0" t="inlineStr">
+        <is>
+          <t>name_ko</t>
+        </is>
+      </c>
+      <c r="E457" s="0" t="inlineStr">
+        <is>
+          <t>물건명 (한/일)</t>
+        </is>
+      </c>
+      <c r="F457" s="0" t="inlineStr">
+        <is>
+          <t>物件名称</t>
+        </is>
+      </c>
+      <c r="G457" s="0" t="inlineStr">
+        <is>
+          <t>니시타케노츠카 2초메 카렌 레지던스</t>
+        </is>
+      </c>
+      <c r="H457" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I457" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/개요서</t>
+        </is>
+      </c>
+      <c r="J457" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K457" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B458" s="0" t="inlineStr">
+        <is>
+          <t>CHK_02</t>
+        </is>
+      </c>
+      <c r="C458" s="0" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D458" s="0" t="inlineStr">
+        <is>
+          <t>address_road</t>
+        </is>
+      </c>
+      <c r="E458" s="0" t="inlineStr">
+        <is>
+          <t>소재지 도로명주소 (住居表示)</t>
+        </is>
+      </c>
+      <c r="F458" s="0" t="inlineStr">
+        <is>
+          <t>住居表示</t>
+        </is>
+      </c>
+      <c r="G458" s="0" t="inlineStr">
+        <is>
+          <t>東京都足立区西竹の塚2-4-36</t>
+        </is>
+      </c>
+      <c r="H458" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I458" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/개요서</t>
+        </is>
+      </c>
+      <c r="J458" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K458" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B459" s="0" t="inlineStr">
+        <is>
+          <t>CHK_03</t>
+        </is>
+      </c>
+      <c r="C459" s="0" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D459" s="0" t="inlineStr">
+        <is>
+          <t>address_lot</t>
+        </is>
+      </c>
+      <c r="E459" s="0" t="inlineStr">
+        <is>
+          <t>토지 지번 (地番)</t>
+        </is>
+      </c>
+      <c r="F459" s="0" t="inlineStr">
+        <is>
+          <t>土地地番</t>
+        </is>
+      </c>
+      <c r="G459" s="0" t="inlineStr">
+        <is>
+          <t>東京都足立区西竹の塚二丁目1325番29</t>
+        </is>
+      </c>
+      <c r="H459" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I459" s="0" t="inlineStr">
+        <is>
+          <t>등기부/개요서</t>
+        </is>
+      </c>
+      <c r="J459" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K459" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B460" s="0" t="inlineStr">
+        <is>
+          <t>CHK_04</t>
+        </is>
+      </c>
+      <c r="C460" s="0" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D460" s="0" t="inlineStr">
+        <is>
+          <t>price_yen</t>
+        </is>
+      </c>
+      <c r="E460" s="0" t="inlineStr">
+        <is>
+          <t>매매가격 및 소비세 조건</t>
+        </is>
+      </c>
+      <c r="F460" s="0" t="inlineStr">
+        <is>
+          <t>売買価格・消費税</t>
+        </is>
+      </c>
+      <c r="G460" s="0" t="inlineStr">
+        <is>
+          <t>330000000</t>
+        </is>
+      </c>
+      <c r="H460" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I460" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/개요서</t>
+        </is>
+      </c>
+      <c r="J460" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K460" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B461" s="0" t="inlineStr">
+        <is>
+          <t>CHK_05</t>
+        </is>
+      </c>
+      <c r="C461" s="0" t="inlineStr">
+        <is>
+          <t>1.기본/가격</t>
+        </is>
+      </c>
+      <c r="D461" s="0" t="inlineStr">
+        <is>
+          <t>delivery_condition</t>
+        </is>
+      </c>
+      <c r="E461" s="0" t="inlineStr">
+        <is>
+          <t>인도조건 및 계약부적합책임 면책 여부</t>
+        </is>
+      </c>
+      <c r="F461" s="0" t="inlineStr">
+        <is>
+          <t>引渡条件・契約不適合免責</t>
+        </is>
+      </c>
+      <c r="G461" s="0" t="inlineStr">
+        <is>
+          <t>상담 (相談 — 현황 전 12호 공실 모집 중)</t>
+        </is>
+      </c>
+      <c r="H461" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I461" s="0" t="inlineStr">
+        <is>
+          <t>물건개요서</t>
+        </is>
+      </c>
+      <c r="J461" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K461" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B462" s="0" t="inlineStr">
+        <is>
+          <t>CHK_06</t>
+        </is>
+      </c>
+      <c r="C462" s="0" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D462" s="0" t="inlineStr">
+        <is>
+          <t>land_area_sqm</t>
+        </is>
+      </c>
+      <c r="E462" s="0" t="inlineStr">
+        <is>
+          <t>토지 공부면적 (㎡/평)</t>
+        </is>
+      </c>
+      <c r="F462" s="0" t="inlineStr">
+        <is>
+          <t>土地公簿面積</t>
+        </is>
+      </c>
+      <c r="G462" s="0" t="inlineStr">
+        <is>
+          <t>384.62</t>
+        </is>
+      </c>
+      <c r="H462" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I462" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/등기부</t>
+        </is>
+      </c>
+      <c r="J462" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K462" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B463" s="0" t="inlineStr">
+        <is>
+          <t>CHK_07</t>
+        </is>
+      </c>
+      <c r="C463" s="0" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D463" s="0" t="inlineStr">
+        <is>
+          <t>land_right</t>
+        </is>
+      </c>
+      <c r="E463" s="0" t="inlineStr">
+        <is>
+          <t>토지 권리형태 및 지목</t>
+        </is>
+      </c>
+      <c r="F463" s="0" t="inlineStr">
+        <is>
+          <t>土地権利・地目</t>
+        </is>
+      </c>
+      <c r="G463" s="0" t="inlineStr">
+        <is>
+          <t>소유권 (所有権)</t>
+        </is>
+      </c>
+      <c r="H463" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I463" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/등기부</t>
+        </is>
+      </c>
+      <c r="J463" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K463" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B464" s="0" t="inlineStr">
+        <is>
+          <t>CHK_08</t>
+        </is>
+      </c>
+      <c r="C464" s="0" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D464" s="0" t="inlineStr">
+        <is>
+          <t>zoning</t>
+        </is>
+      </c>
+      <c r="E464" s="0" t="inlineStr">
+        <is>
+          <t>용도지역 및 법정 건폐율·용적률</t>
+        </is>
+      </c>
+      <c r="F464" s="0" t="inlineStr">
+        <is>
+          <t>用途地域・建蔽率・容積率</t>
+        </is>
+      </c>
+      <c r="G464" s="0" t="inlineStr">
+        <is>
+          <t>근린상업지역 (近隣商業地域)</t>
+        </is>
+      </c>
+      <c r="H464" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I464" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/개요서</t>
+        </is>
+      </c>
+      <c r="J464" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K464" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B465" s="0" t="inlineStr">
+        <is>
+          <t>CHK_09</t>
+        </is>
+      </c>
+      <c r="C465" s="0" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D465" s="0" t="inlineStr">
+        <is>
+          <t>road_access</t>
+        </is>
+      </c>
+      <c r="E465" s="0" t="inlineStr">
+        <is>
+          <t>도로 접도 방위·폭원·접도길이</t>
+        </is>
+      </c>
+      <c r="F465" s="0" t="inlineStr">
+        <is>
+          <t>接道状況（幅員・間口）</t>
+        </is>
+      </c>
+      <c r="G465" s="0" t="inlineStr">
+        <is>
+          <t>북측 폭 약 4.00m 공도(42조 1항 1호 도로)에 약 3.0m 접면 (노지상부지/깃대형 토지)</t>
+        </is>
+      </c>
+      <c r="H465" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I465" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/도로대장</t>
+        </is>
+      </c>
+      <c r="J465" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K465" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B466" s="0" t="inlineStr">
+        <is>
+          <t>CHK_10</t>
+        </is>
+      </c>
+      <c r="C466" s="0" t="inlineStr">
+        <is>
+          <t>2.토지/도계</t>
+        </is>
+      </c>
+      <c r="D466" s="0" t="inlineStr">
+        <is>
+          <t>private_road_burden</t>
+        </is>
+      </c>
+      <c r="E466" s="0" t="inlineStr">
+        <is>
+          <t>사도부담 및 굴착·통행승낙서 유무</t>
+        </is>
+      </c>
+      <c r="F466" s="0" t="inlineStr">
+        <is>
+          <t>私道負担・掘削通行承諾</t>
+        </is>
+      </c>
+      <c r="G466" s="0" t="inlineStr">
+        <is>
+          <t>없음 (42조 1항 1호 공도 접면)</t>
+        </is>
+      </c>
+      <c r="H466" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I466" s="0" t="inlineStr">
+        <is>
+          <t>물건개요서/등기부</t>
+        </is>
+      </c>
+      <c r="J466" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K466" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B467" s="0" t="inlineStr">
+        <is>
+          <t>CHK_11</t>
+        </is>
+      </c>
+      <c r="C467" s="0" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D467" s="0" t="inlineStr">
+        <is>
+          <t>structure_display</t>
+        </is>
+      </c>
+      <c r="E467" s="0" t="inlineStr">
+        <is>
+          <t>건물 구조 및 층수</t>
+        </is>
+      </c>
+      <c r="F467" s="0" t="inlineStr">
+        <is>
+          <t>建物構造・規模</t>
+        </is>
+      </c>
+      <c r="G467" s="0" t="inlineStr">
+        <is>
+          <t>목조 지상 3층 건 (木造3階建 · 열화등급 3급 상당 증명서 유)</t>
+        </is>
+      </c>
+      <c r="H467" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I467" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/등기부</t>
+        </is>
+      </c>
+      <c r="J467" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K467" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B468" s="0" t="inlineStr">
+        <is>
+          <t>CHK_12</t>
+        </is>
+      </c>
+      <c r="C468" s="0" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D468" s="0" t="inlineStr">
+        <is>
+          <t>built_year_month</t>
+        </is>
+      </c>
+      <c r="E468" s="0" t="inlineStr">
+        <is>
+          <t>신축 준공년월 및 경과연수</t>
+        </is>
+      </c>
+      <c r="F468" s="0" t="inlineStr">
+        <is>
+          <t>築年月</t>
+        </is>
+      </c>
+      <c r="G468" s="0" t="inlineStr">
+        <is>
+          <t>2026년 10월 (令和8年10月 표기 / 포털 2026년 8월 준공 모집 중)</t>
+        </is>
+      </c>
+      <c r="H468" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I468" s="0" t="inlineStr">
+        <is>
+          <t>마이소쿠/등기부</t>
+        </is>
+      </c>
+      <c r="J468" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K468" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B469" s="0" t="inlineStr">
+        <is>
+          <t>CHK_13</t>
+        </is>
+      </c>
+      <c r="C469" s="0" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D469" s="0" t="inlineStr">
+        <is>
+          <t>bldg_area_reg_sqm</t>
+        </is>
+      </c>
+      <c r="E469" s="0" t="inlineStr">
+        <is>
+          <t>등기 연면적 vs 확인대장 연면적</t>
+        </is>
+      </c>
+      <c r="F469" s="0" t="inlineStr">
+        <is>
+          <t>延床面積（登記・確認台帳）</t>
+        </is>
+      </c>
+      <c r="G469" s="0" t="inlineStr">
+        <is>
+          <t>605.17</t>
+        </is>
+      </c>
+      <c r="H469" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I469" s="0" t="inlineStr">
+        <is>
+          <t>등기부/건축확인대장</t>
+        </is>
+      </c>
+      <c r="J469" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K469" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="3" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>CHK_14</t>
+        </is>
+      </c>
+      <c r="C470" s="3" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D470" s="3" t="inlineStr">
+        <is>
+          <t>has_confirm_cert</t>
+        </is>
+      </c>
+      <c r="E470" s="3" t="inlineStr">
+        <is>
+          <t>건축확인필증(確認済証) 및 대장 유무</t>
+        </is>
+      </c>
+      <c r="F470" s="3" t="inlineStr">
+        <is>
+          <t>建築確認済証・台帳記載事項証明</t>
+        </is>
+      </c>
+      <c r="G470" s="3" t="inlineStr">
+        <is>
+          <t>보유 확실 (2026년 신축 — 단, 용도가 『나가야』인지 『공동주택』인지 사본 확인 필수)</t>
+        </is>
+      </c>
+      <c r="H470" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I470" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J470" s="3" t="inlineStr">
+        <is>
+          <t>건축확인필증 또는 대장기재사항증명서 사본 요청</t>
+        </is>
+      </c>
+      <c r="K470" s="3" t="inlineStr">
+        <is>
+          <t>建築確認済証または台帳記載事項証明書の写しのご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="3" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>CHK_15</t>
+        </is>
+      </c>
+      <c r="C471" s="3" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D471" s="3" t="inlineStr">
+        <is>
+          <t>has_inspection_cert</t>
+        </is>
+      </c>
+      <c r="E471" s="3" t="inlineStr">
+        <is>
+          <t>준공검사필증(検査済証) 취득 여부</t>
+        </is>
+      </c>
+      <c r="F471" s="3" t="inlineStr">
+        <is>
+          <t>検査済証の有無</t>
+        </is>
+      </c>
+      <c r="G471" s="3" t="inlineStr">
+        <is>
+          <t>보유 확실 (2026년 신축 — 준공검사필증 및 열화등급 3급 상당 증명서 원본 징구 필수)</t>
+        </is>
+      </c>
+      <c r="H471" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I471" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J471" s="3" t="inlineStr">
+        <is>
+          <t>준공검사필증(検査済証) 교부 유무 및 번호 확인 (은행융자 필수)</t>
+        </is>
+      </c>
+      <c r="K471" s="3" t="inlineStr">
+        <is>
+          <t>検査済証の有無および交付番号のご確認（融資審査上必須）</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B472" s="0" t="inlineStr">
+        <is>
+          <t>CHK_16</t>
+        </is>
+      </c>
+      <c r="C472" s="0" t="inlineStr">
+        <is>
+          <t>3.건물/적법</t>
+        </is>
+      </c>
+      <c r="D472" s="0" t="inlineStr">
+        <is>
+          <t>repair_history_summary</t>
+        </is>
+      </c>
+      <c r="E472" s="0" t="inlineStr">
+        <is>
+          <t>외벽도장·옥상방수 등 대규모 수선이력</t>
+        </is>
+      </c>
+      <c r="F472" s="0" t="inlineStr">
+        <is>
+          <t>大規模修繕履歴（外壁・屋上防水）</t>
+        </is>
+      </c>
+      <c r="G472" s="0" t="inlineStr">
+        <is>
+          <t>신축 (2026년 준공 — 시공사 하우스링크홈(주) 초기 하자보수 보증 및 10년 하자담보책임 대상)</t>
+        </is>
+      </c>
+      <c r="H472" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I472" s="0" t="inlineStr">
+        <is>
+          <t>수선이력서</t>
+        </is>
+      </c>
+      <c r="J472" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K472" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B473" s="0" t="inlineStr">
+        <is>
+          <t>CHK_17</t>
+        </is>
+      </c>
+      <c r="C473" s="0" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D473" s="0" t="inlineStr">
+        <is>
+          <t>full_annual_income_yen</t>
+        </is>
+      </c>
+      <c r="E473" s="0" t="inlineStr">
+        <is>
+          <t>호실별 월 차임 및 공익비 내역</t>
+        </is>
+      </c>
+      <c r="F473" s="0" t="inlineStr">
+        <is>
+          <t>各戸賃料・共益費一覧</t>
+        </is>
+      </c>
+      <c r="G473" s="0" t="inlineStr">
+        <is>
+          <t>23868000</t>
+        </is>
+      </c>
+      <c r="H473" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I473" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤</t>
+        </is>
+      </c>
+      <c r="J473" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K473" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B474" s="0" t="inlineStr">
+        <is>
+          <t>CHK_18</t>
+        </is>
+      </c>
+      <c r="C474" s="0" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D474" s="0" t="inlineStr">
+        <is>
+          <t>unit_composition</t>
+        </is>
+      </c>
+      <c r="E474" s="0" t="inlineStr">
+        <is>
+          <t>호실별 전유면적(㎡) 및 평형 타입</t>
+        </is>
+      </c>
+      <c r="F474" s="0" t="inlineStr">
+        <is>
+          <t>各戸専有面積・間取り</t>
+        </is>
+      </c>
+      <c r="G474" s="0" t="inlineStr">
+        <is>
+          <t>1LDK(32.57~33.01㎡)×6호 [1층] + 2LDK 메조네트(70.48~71.76㎡, 1F현관+2·3F)×6호</t>
+        </is>
+      </c>
+      <c r="H474" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I474" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤/도면</t>
+        </is>
+      </c>
+      <c r="J474" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K474" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B475" s="0" t="inlineStr">
+        <is>
+          <t>CHK_19</t>
+        </is>
+      </c>
+      <c r="C475" s="0" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D475" s="0" t="inlineStr">
+        <is>
+          <t>rent_roll_contract_dates</t>
+        </is>
+      </c>
+      <c r="E475" s="0" t="inlineStr">
+        <is>
+          <t>호실별 계약시작일(契約始期) 및 갱신주기</t>
+        </is>
+      </c>
+      <c r="F475" s="0" t="inlineStr">
+        <is>
+          <t>各戸の契約始期・更新時期</t>
+        </is>
+      </c>
+      <c r="G475" s="0" t="inlineStr">
+        <is>
+          <t>[미수집 - 계약시작일 미기재]</t>
+        </is>
+      </c>
+      <c r="H475" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I475" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤 상세판</t>
+        </is>
+      </c>
+      <c r="J475" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K475" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B476" s="0" t="inlineStr">
+        <is>
+          <t>CHK_20</t>
+        </is>
+      </c>
+      <c r="C476" s="0" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D476" s="0" t="inlineStr">
+        <is>
+          <t>rent_roll_tenant_types</t>
+        </is>
+      </c>
+      <c r="E476" s="0" t="inlineStr">
+        <is>
+          <t>호실별 입주자 속성(법인/직장인/학생/보증회사)</t>
+        </is>
+      </c>
+      <c r="F476" s="0" t="inlineStr">
+        <is>
+          <t>入居者属性・保証会社加入状況</t>
+        </is>
+      </c>
+      <c r="G476" s="0" t="inlineStr">
+        <is>
+          <t>속성 확인 (12실)</t>
+        </is>
+      </c>
+      <c r="H476" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I476" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤 상세판</t>
+        </is>
+      </c>
+      <c r="J476" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K476" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B477" s="0" t="inlineStr">
+        <is>
+          <t>CHK_21</t>
+        </is>
+      </c>
+      <c r="C477" s="0" t="inlineStr">
+        <is>
+          <t>4.렌트롤</t>
+        </is>
+      </c>
+      <c r="D477" s="0" t="inlineStr">
+        <is>
+          <t>parking_info</t>
+        </is>
+      </c>
+      <c r="E477" s="0" t="inlineStr">
+        <is>
+          <t>주차장·자판기·안테나 등 부대수입 계약현황</t>
+        </is>
+      </c>
+      <c r="F477" s="0" t="inlineStr">
+        <is>
+          <t>駐車場・付帯収入の契約状況</t>
+        </is>
+      </c>
+      <c r="G477" s="0" t="inlineStr">
+        <is>
+          <t>주륜장 12개소 유 (駐輪場12ヶ所あり — 자동차 주차장 없음)</t>
+        </is>
+      </c>
+      <c r="H477" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I477" s="0" t="inlineStr">
+        <is>
+          <t>렌트롤/개요서</t>
+        </is>
+      </c>
+      <c r="J477" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K477" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>CHK_22</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>disclosed_opex_yen</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>PM 관리위탁비 및 정기청소비 실비</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>PM管理委託費・定期清掃費</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>[미수집]</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr">
+        <is>
+          <t>현재 위탁 중인 PM 관리수수료율 및 정기청소비 월액 확인</t>
+        </is>
+      </c>
+      <c r="K478" s="2" t="inlineStr">
+        <is>
+          <t>現行のPM管理委託料率および定期清掃費等のランニングコスト明細のご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B479" s="0" t="inlineStr">
+        <is>
+          <t>CHK_23</t>
+        </is>
+      </c>
+      <c r="C479" s="0" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D479" s="0" t="inlineStr">
+        <is>
+          <t>utilities_water_sewer</t>
+        </is>
+      </c>
+      <c r="E479" s="0" t="inlineStr">
+        <is>
+          <t>공용 전기·수도·정화조·인터넷 유지비</t>
+        </is>
+      </c>
+      <c r="F479" s="0" t="inlineStr">
+        <is>
+          <t>共用光熱費・浄化槽・ネット費用</t>
+        </is>
+      </c>
+      <c r="G479" s="0" t="inlineStr">
+        <is>
+          <t>공영수도 · 공공하수 (公営水道・公共下水)</t>
+        </is>
+      </c>
+      <c r="H479" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I479" s="0" t="inlineStr">
+        <is>
+          <t>런닝코스트 명세</t>
+        </is>
+      </c>
+      <c r="J479" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K479" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="3" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>CHK_24</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D480" s="3" t="inlineStr">
+        <is>
+          <t>fixed_tax_land_eval_yen</t>
+        </is>
+      </c>
+      <c r="E480" s="3" t="inlineStr">
+        <is>
+          <t>고정자산세 토지 과세평가액</t>
+        </is>
+      </c>
+      <c r="F480" s="3" t="inlineStr">
+        <is>
+          <t>固定資産税評価額（土地）</t>
+        </is>
+      </c>
+      <c r="G480" s="3" t="inlineStr">
+        <is>
+          <t>128727506</t>
+        </is>
+      </c>
+      <c r="H480" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I480" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J480" s="3" t="inlineStr">
+        <is>
+          <t>최신 연도 고정자산세·도시계획세 과세명세서(토지 평가액) 사본 요청</t>
+        </is>
+      </c>
+      <c r="K480" s="3" t="inlineStr">
+        <is>
+          <t>最新年度の固定資産税・都市計画税課税明細書（土地評価額）の写しのご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="3" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B481" s="3" t="inlineStr">
+        <is>
+          <t>CHK_25</t>
+        </is>
+      </c>
+      <c r="C481" s="3" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D481" s="3" t="inlineStr">
+        <is>
+          <t>fixed_tax_bldg_eval_yen</t>
+        </is>
+      </c>
+      <c r="E481" s="3" t="inlineStr">
+        <is>
+          <t>고정자산세 건물 과세평가액</t>
+        </is>
+      </c>
+      <c r="F481" s="3" t="inlineStr">
+        <is>
+          <t>固定資産税評価額（建物）</t>
+        </is>
+      </c>
+      <c r="G481" s="3" t="inlineStr">
+        <is>
+          <t>59306660</t>
+        </is>
+      </c>
+      <c r="H481" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I481" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J481" s="3" t="inlineStr">
+        <is>
+          <t>최신 연도 고정자산세·도시계획세 과세명세서(건물 평가액) 사본 요청</t>
+        </is>
+      </c>
+      <c r="K481" s="3" t="inlineStr">
+        <is>
+          <t>最新年度の固定資産税・都市計画税課税明細書（建物評価額）の写しのご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="3" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>CHK_26</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="inlineStr">
+        <is>
+          <t>5.경비/세금</t>
+        </is>
+      </c>
+      <c r="D482" s="3" t="inlineStr">
+        <is>
+          <t>fixed_tax_annual_yen</t>
+        </is>
+      </c>
+      <c r="E482" s="3" t="inlineStr">
+        <is>
+          <t>고정자산세·도시계획세 연간 실납부세액</t>
+        </is>
+      </c>
+      <c r="F482" s="3" t="inlineStr">
+        <is>
+          <t>固都税 年間納付税額</t>
+        </is>
+      </c>
+      <c r="G482" s="3" t="inlineStr">
+        <is>
+          <t>1320000</t>
+        </is>
+      </c>
+      <c r="H482" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED</t>
+        </is>
+      </c>
+      <c r="I482" s="3" t="inlineStr">
+        <is>
+          <t>표준산식 역산 추정</t>
+        </is>
+      </c>
+      <c r="J482" s="3" t="inlineStr">
+        <is>
+          <t>고정자산세·도시계획세 연간 납부세액 확정치 확인</t>
+        </is>
+      </c>
+      <c r="K482" s="3" t="inlineStr">
+        <is>
+          <t>固定資産税・都市計画税の年間納付税額（確定値）のご教示</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>CHK_27</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>6.등기/내력</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>registry_owner_match</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>토지·건물 등기부 소유자 일치 여부</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>土地・建物登記簿の所有者一致</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 등기부 미수령]</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr">
+        <is>
+          <t>토지 및 건물 등기사항전부증명서(전부사항) 사본 요청</t>
+        </is>
+      </c>
+      <c r="K483" s="2" t="inlineStr">
+        <is>
+          <t>土地・建物の全部事項証明書（登記簿謄本）のご共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>CHK_28</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>6.등기/내력</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>registry_history_갑구</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>과거 소유권 변천내력(갑구) 및 매각동기</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>所有権移転履歴・売却理由</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 등기부 미수령]</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J484" s="2" t="inlineStr">
+        <is>
+          <t>현 소유자의 취득 경위 및 금번 매각 사유 확인</t>
+        </is>
+      </c>
+      <c r="K484" s="2" t="inlineStr">
+        <is>
+          <t>現所有者様の取得経緯および今回のご売却理由のご教示</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>CHK_29</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>6.등기/내력</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>registry_liens_을구</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>담보권·근저당·압류·지역권 유무(을구)</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>抵当権・地役権等の権利関係</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>[미수집 - 등기부 미수령]</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J485" s="2" t="inlineStr">
+        <is>
+          <t>등기부 을구 권리관계 및 말소 조건 확인</t>
+        </is>
+      </c>
+      <c r="K485" s="2" t="inlineStr">
+        <is>
+          <t>登記簿乙区の権利関係および引渡時抹消条件の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B486" s="0" t="inlineStr">
+        <is>
+          <t>CHK_30</t>
+        </is>
+      </c>
+      <c r="C486" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D486" s="0" t="inlineStr">
+        <is>
+          <t>roadside_price_sqm</t>
+        </is>
+      </c>
+      <c r="E486" s="0" t="inlineStr">
+        <is>
+          <t>국세청 상속세 노선가(路線価) 조회</t>
+        </is>
+      </c>
+      <c r="F486" s="0" t="inlineStr">
+        <is>
+          <t>相続税路線価</t>
+        </is>
+      </c>
+      <c r="G486" s="0" t="inlineStr">
+        <is>
+          <t>382500</t>
+        </is>
+      </c>
+      <c r="H486" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I486" s="0" t="inlineStr">
+        <is>
+          <t>국세청 노선가도</t>
+        </is>
+      </c>
+      <c r="J486" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K486" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B487" s="0" t="inlineStr">
+        <is>
+          <t>CHK_31</t>
+        </is>
+      </c>
+      <c r="C487" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D487" s="0" t="inlineStr">
+        <is>
+          <t>walk_min_gmaps</t>
+        </is>
+      </c>
+      <c r="E487" s="0" t="inlineStr">
+        <is>
+          <t>Google Maps 실측 도보거리 및 소요시간</t>
+        </is>
+      </c>
+      <c r="F487" s="0" t="inlineStr">
+        <is>
+          <t>Googleマップ実測徒歩距離・時間</t>
+        </is>
+      </c>
+      <c r="G487" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H487" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I487" s="0" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="J487" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K487" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B488" s="0" t="inlineStr">
+        <is>
+          <t>CHK_32</t>
+        </is>
+      </c>
+      <c r="C488" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D488" s="0" t="inlineStr">
+        <is>
+          <t>walk_slope_note</t>
+        </is>
+      </c>
+      <c r="E488" s="0" t="inlineStr">
+        <is>
+          <t>보행 동선 고저차(경사/계단) 및 혐오시설 실사</t>
+        </is>
+      </c>
+      <c r="F488" s="0" t="inlineStr">
+        <is>
+          <t>徒歩経路の高低差・周辺嫌悪施設</t>
+        </is>
+      </c>
+      <c r="G488" s="0" t="inlineStr">
+        <is>
+          <t>타케노츠카역 서구~세이유 앞을 지나는 완전 평탄한 근린상업지역 동선</t>
+        </is>
+      </c>
+      <c r="H488" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I488" s="0" t="inlineStr">
+        <is>
+          <t>Google 스트리트뷰</t>
+        </is>
+      </c>
+      <c r="J488" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K488" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B489" s="0" t="inlineStr">
+        <is>
+          <t>CHK_33</t>
+        </is>
+      </c>
+      <c r="C489" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D489" s="0" t="inlineStr">
+        <is>
+          <t>hazard_flood</t>
+        </is>
+      </c>
+      <c r="E489" s="0" t="inlineStr">
+        <is>
+          <t>지자체 홍수·내수 침수 해저드맵 검증</t>
+        </is>
+      </c>
+      <c r="F489" s="0" t="inlineStr">
+        <is>
+          <t>洪水・内水浸水ハザードマップ</t>
+        </is>
+      </c>
+      <c r="G489" s="0" t="inlineStr">
+        <is>
+          <t>아다치구 홍수 해저드맵(아라카와 범람) 예상 침수심 0.5m~3.0m 미만 구역 (1층 침수 가능 — 수재보험 특약 필수)</t>
+        </is>
+      </c>
+      <c r="H489" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I489" s="0" t="inlineStr">
+        <is>
+          <t>지자체 하저드맵</t>
+        </is>
+      </c>
+      <c r="J489" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K489" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B490" s="0" t="inlineStr">
+        <is>
+          <t>CHK_34</t>
+        </is>
+      </c>
+      <c r="C490" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D490" s="0" t="inlineStr">
+        <is>
+          <t>hazard_landslide</t>
+        </is>
+      </c>
+      <c r="E490" s="0" t="inlineStr">
+        <is>
+          <t>토사재해 경계구역(옐로/레드존) 검증</t>
+        </is>
+      </c>
+      <c r="F490" s="0" t="inlineStr">
+        <is>
+          <t>土砂災害警戒区域（イエロー/レッド）</t>
+        </is>
+      </c>
+      <c r="G490" s="0" t="inlineStr">
+        <is>
+          <t>해당 없음 (평탄한 저지대 상업·주거지역 — 토사재해 경계구역 외)</t>
+        </is>
+      </c>
+      <c r="H490" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I490" s="0" t="inlineStr">
+        <is>
+          <t>지자체 하저드맵</t>
+        </is>
+      </c>
+      <c r="J490" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K490" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B491" s="0" t="inlineStr">
+        <is>
+          <t>CHK_35</t>
+        </is>
+      </c>
+      <c r="C491" s="0" t="inlineStr">
+        <is>
+          <t>7.외부실사</t>
+        </is>
+      </c>
+      <c r="D491" s="0" t="inlineStr">
+        <is>
+          <t>avg_dom_days</t>
+        </is>
+      </c>
+      <c r="E491" s="0" t="inlineStr">
+        <is>
+          <t>LIFULL HOME'S 아카이브 과거 모집이력(DOM)</t>
+        </is>
+      </c>
+      <c r="F491" s="0" t="inlineStr">
+        <is>
+          <t>HOME'S過去の掲載履歴・DOM分析</t>
+        </is>
+      </c>
+      <c r="G491" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H491" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I491" s="0" t="inlineStr">
+        <is>
+          <t>LIFULL HOME'S</t>
+        </is>
+      </c>
+      <c r="J491" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K491" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -55373,8 +58977,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B122" s="0">
-        <v>1</v>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -55409,8 +59015,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B123" s="0">
-        <v>2</v>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -55443,8 +59051,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B124" s="0">
-        <v>3</v>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -55479,8 +59089,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B125" s="0">
-        <v>4</v>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -55519,8 +59131,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B126" s="0">
-        <v>5</v>
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
@@ -55553,8 +59167,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B127" s="0">
-        <v>6</v>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -55597,8 +59213,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B128" s="0">
-        <v>7</v>
+      <c r="B128" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
@@ -55635,8 +59253,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B129" s="0">
-        <v>8</v>
+      <c r="B129" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
@@ -55671,8 +59291,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B130" s="0">
-        <v>9</v>
+      <c r="B130" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -55703,8 +59325,10 @@
           <t>ciel-bleu-chiba-chuo</t>
         </is>
       </c>
-      <c r="B131" s="0">
-        <v>10</v>
+      <c r="B131" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
@@ -55738,6 +59362,364 @@
   3. **令和7・8年度 固定資産税・都市計画税 課税明細書**。
   4. **過去15年間の修繕履歴報告書（外壁塗装・屋上防水・給湯器）**。
   5. **無料インターネット設備の契約書およびランニングコスト実費明細**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B132" s="0">
+        <v>1</v>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t>1. 투자 총괄 요약 및 핵심 의사결정 권고 (Executive Summary &amp; Verdict)</t>
+        </is>
+      </c>
+      <c r="D132" s="0" t="inlineStr">
+        <is>
+          <t>1. エグゼクティブ・サマリーおよび投資判定 (Executive Summary &amp; Verdict)</t>
+        </is>
+      </c>
+      <c r="E132" s="0" t="inlineStr">
+        <is>
+          <t>**니시타케노츠카 2초메 카렌 레지던스(西竹の塚2丁目 カレンレジデンス)**는 도부 스카이트리 라인 『타케노츠카』역 도보 3분 근린상업지역 토지 384.62㎡(116.35평) 위에 신축된 **목조 3층 건 12세대(1LDK×6호 + 2LDK 메조네트×6호, 연면적 605.17㎡)** 대형 아파트를 대상으로 합니다.
+- **3단계 렌트롤 감사 적발**: 마이소쿠 헤드라인(연 2,386.8만 엔 / 7.23%)과 표 합산(연 2,320.8만 엔 / 7.03%) 간 연 -66만 엔 산술 오차가 존재하며, 2026년 10월 현재 SUUMO 등 실제 임대 포털에서는 2LDK가 이미 **월 17.5만~18.0만 엔(부금0·예금0)**으로 인하 모집 중이어서 **실전 성약 기준 만실 연수입(GPI)은 2,167.2만 엔(표면 6.57%, 실효 NOI 1,692.5만 엔 [Cap 5.13%])**으로 하락합니다.
+- **최종 판정**: **조건부 매수(Conditional Buy, 61/100점 | 19.6/30점, C+ 등급)** — 호가 3.30억 엔 매수는 보류하며, **2억 9,000만~2억 9,500만 엔(실세 표면 7.35%~7.47%) 지가 네고 + 30년 융자 특약 + 만실 인도(또는 1년 마스터리스) 특약** 성사 시에만 매수를 권고합니다.</t>
+        </is>
+      </c>
+      <c r="F132" s="0" t="inlineStr">
+        <is>
+          <t>**西竹の塚2丁目 カレンレジデンス**は、東武スカイツリーライン『竹ノ塚』駅徒歩3分の近隣商業地域（土地384.62㎡・116.35坪）に新築された**木造3階建・全12戸（1LDK×6戸＋2LDKメゾネット×6戸、延床605.17㎡）**の一棟アパートです。
+- **3段階レントロール監査**: マイソク表面記載（年2,386.8万円 / 7.23%）と賃料表実合算（年2,320.8万円 / 7.03%）に年▲66万円の算術不一致がある上、現行SUUMO等の賃貸ポータルでは2LDKが既に**月17.5万〜18.0万円（敷0・礼0）**へ値下げ募集されており、**実勢満室GPIは年2,167.2万円（表面6.57%・実効NOI 1,692.5万円［Cap 5.13%］）**となります。
+- **最終判定**: **条件付推奨（Conditional Buy、61/100点｜19.6/30点、ランクC+）** — 売出3.30億円での買付は見送り、**2億9,000万〜2億9,500万円（実勢表面7.35%〜7.47%）への指値交渉＋30年融資特約＋満室引渡（または家賃保証）特約**を必須条件とします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B133" s="0">
+        <v>2</v>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>2. 물건 개요 및 누락 정보 감사 (Property Overview &amp; Missing Info Audit)</t>
+        </is>
+      </c>
+      <c r="D133" s="0" t="inlineStr">
+        <is>
+          <t>2. 物件概要および未開示情報の監査 (Property Overview &amp; Missing Info Audit)</t>
+        </is>
+      </c>
+      <c r="E133" s="0" t="inlineStr">
+        <is>
+          <t>- **토지 및 접도 리스크**: 아다치구 니시타케노츠카 2초메 1325-29(주거표시 2-4-36), 토지 384.62㎡(근린상업지역, 건폐율 80%/기준용적률 240%), **북측 4.0m 공도에 약 3.0m만 접한 노지상부지(깃대형)**.
+- **건물 및 설비 리스크**: 목조 3층 건 연면적 605.17㎡, 2026년 8~10월 신축(시공사: 하우스링크홈(주)), 열화등급 3급 상당 증명서 유. 단, **도쿄 23구 역세권임에도 시공사 그룹 가스공급 구조에 따라 LP가스(프로판가스)가 채택**되어 있어 무상대여 설비 잔존 채무 유무 및 3부 요금제 내역서 징구가 필수입니다.</t>
+        </is>
+      </c>
+      <c r="F133" s="0" t="inlineStr">
+        <is>
+          <t>- **土地および接道リスク**: 足立区西竹の塚二丁目1325-29（住居表示2-4-36）、土地384.62㎡（近隣商業地域、建蔽率80%/基準容積率240%）、**北側4.0m公道に約3.0mのみ接面する路地状敷地（旗竿地）**。
+- **建物および設備リスク**: 木造3階建・延床605.17㎡、2026年8〜10月新築（施工：ハウスリンクホーム(株)）、劣化等級3級相当証明書有。ただし**東京23区駅近でありながらLPガス（プロパンガス）が採用**されており、無償貸与設備の残存債務有無および三部料金制明細の徴求が必須です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B134" s="0">
+        <v>3</v>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>3. 입지·상권 및 도쿄 4대 거점 통근 접근성 검증 (Location &amp; Transit Access)</t>
+        </is>
+      </c>
+      <c r="D134" s="0" t="inlineStr">
+        <is>
+          <t>3. 立地・商圏および主要4大拠点への通勤アクセス検証 (Location &amp; Transit Access)</t>
+        </is>
+      </c>
+      <c r="E134" s="0" t="inlineStr">
+        <is>
+          <t>- **타케노츠카역 고가화(2022.3) 및 『EQUiA 타케노츠카』(2024.5) 개업 효과**: 장기간 지역 단절을 유발하던 건널목이 고가화로 완전 해소되었고 역사 내 24개 점포가 입점한 에키아 타케노츠카 및 서구 도보 2분 24시간 세이유(SEIYU)로 생활 편의성이 뛰어납니다.
+- **도심 직통 접근성**: 도쿄메트로 히비야선 직통(당역 시발 다수)으로 **우에노역 20분(환승 0회), 아키하바라역 25분(0회), 오테마치역 33분(키타센주 1회 환승), 긴자역 37분(0회)**에 주파합니다.</t>
+        </is>
+      </c>
+      <c r="F134" s="0" t="inlineStr">
+        <is>
+          <t>- **竹ノ塚駅高架化（2022.3）および『EQUiA竹ノ塚』（2024.5）開業効果**: 開かずの踏切が完全解消され、高架下商業施設エキア竹ノ塚（24店舗）および西口徒歩2分の24時間営業「西友（SEIYU）」により高い生活利便性を誇ります。
+- **都心直通アクセス**: 東京メトロ日比谷線直通（当駅始発多数）により**上野駅20分（乗換0回）、秋葉原駅25分（0回）、大手町駅33分（北千住1回乗換）、銀座駅37分（0回）**でアクセス可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B135" s="0">
+        <v>4</v>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>4. 적산평가(원가법) 및 토지·건물 담보가치 정밀 검증 (Reproduction Cost Valuation)</t>
+        </is>
+      </c>
+      <c r="D135" s="0" t="inlineStr">
+        <is>
+          <t>4. 積算評価（原価法）および土地・建物担保価値の精密査定 (Reproduction Cost Valuation)</t>
+        </is>
+      </c>
+      <c r="E135" s="0" t="inlineStr">
+        <is>
+          <t>- **토지 적산평가**: 인근 근린상업 기준지가(67.5만 엔/㎡) 및 주택지 공시지가(40.3만 엔/㎡)를 바탕으로 본건 전면 상속세 노선가를 `450,000엔/㎡`로 추계하고, **노지상부지(접도 3.0m) 감가 보정(-15%)을 적용한 실효 단가 `382,500엔/㎡` × 384.62㎡ = 1억 4,711.7만 엔**(무보정 시 1억 7,307.9만 엔).
+- **건물 및 합산 적산평가(연면적 605.17㎡, 잔존 22/22년)**:
+  1. **은행 보수 기준(15만 엔/㎡)**: 건물 9,077.6만 + 토지 1억 4,711.7만 = **2억 3,789.3만 엔 (72.1%)**
+  2. **표준 은행 담보 기준(17만 엔/㎡)**: 건물 1억 287.9만 + 토지 1억 4,711.7만 = **2억 4,999.6만 엔 (75.8% / 네고가 2.95억 대비 84.7%)**
+  3. **국세청·무보정 노선가 기준(18만 엔/㎡)**: 건물 1억 893.1만 + 토지 1억 7,307.9만 = **2억 8,201.0만 엔 (85.5%)**</t>
+        </is>
+      </c>
+      <c r="F135" s="0" t="inlineStr">
+        <is>
+          <t>- **土地積算評価**: 近隣商業基準地価（67.5万円/㎡）等を基に前面路線価を`450,000円/㎡`と推計し、**路地状敷地（接道3.0m）補正（▲15%）適用後の実効単価 `382,500円/㎡` × 384.62㎡ ＝ 1億4,711.7万円**（無補正時 1億7,307.9万円）。
+- **建物および合算積算評価（延床605.17㎡、残存22/22年）**:
+  1. **銀行保守基準（15万円/㎡）**: 建物9,077.6万＋土地1億4,711.7万 ＝ **2億3,789.3万円（72.1%）**
+  2. **標準銀行担保基準（17万円/㎡）**: 建物1億287.9万＋土地1億4,711.7万 ＝ **2億4,999.6万円（75.8% ／ 指値2.95億比 84.7%）**
+  3. **国税庁・無補正路線価基準（18万円/㎡）**: 建物1億893.1万＋土地1億7,307.9万 ＝ **2億8,201.0万円（85.5%）**</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B136" s="0">
+        <v>5</v>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t>5. 렌트롤 3단계 포렌식 감사 및 평면(메조네트 계단로스) 경쟁력 분석</t>
+        </is>
+      </c>
+      <c r="D136" s="0" t="inlineStr">
+        <is>
+          <t>5. レントロール3段階フォレンジック監査および間取り（階段ロス）競争力分析</t>
+        </is>
+      </c>
+      <c r="E136" s="0" t="inlineStr">
+        <is>
+          <t>- **왜 2LDK(70.48㎡)가 포털에서 월 17.5만~18.0만 엔으로 할인 모집 중인가?**: 도쿄도 건축안전조례(접도 3.0m 제한)를 충족하기 위해 201~206호를 『1층 전용현관 → 내계단 → 2층 LDK → 내계단 → 3층 침실 2개』의 **3개층 수직 겹침나가야(트리플렛 메조네트)**로 설계하여, 70.48㎡ 중 약 12~15㎡(18~20%)가 2개의 계단실로 소모됩니다.
+- **3단계 수입 비교**: ①마이소쿠 헤드라인 **연 2,386.8만 엔(7.23%)** vs ②마이소쿠 표 실제 합산 **연 2,320.8만 엔(7.03%, -66만 엔 오차)** vs ③실전 포털(SUUMO) 모집 실세 반영 **연 2,167.2만 엔(6.57%, -219.6만 엔 감소)**.</t>
+        </is>
+      </c>
+      <c r="F136" s="0" t="inlineStr">
+        <is>
+          <t>- **なぜ2LDK（70.48㎡）がポータルで月17.5万〜18.0万円へ値下げ募集されているのか？**: 東京都建築安全条例（接道3.0m制限）をクリアするため、201〜206号室を『1階専用玄関→内階段→2階LDK→内階段→3階洋室2室』の**3層トリプレット型メゾネット（重ね長屋）**として設計しており、70.48㎡のうち約12〜15㎡（18〜20%）が2つの内階段に消費されています。
+- **3段階収入比較**: ①マイソク表面記載 **年2,386.8万円（7.23%）** vs ②マイソク表実合算 **年2,320.8万円（7.03%、▲66万円誤差）** vs ③現行ポータル（SUUMO）実勢反映 **年2,167.2万円（6.57%、▲219.6万円減）**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B137" s="0">
+        <v>6</v>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>6. 운영경비(OPEX) 정규화 및 순영업소득(NOI) 모델링</t>
+        </is>
+      </c>
+      <c r="D137" s="0" t="inlineStr">
+        <is>
+          <t>6. 運営経費(OPEX)の正規化および純営業収益(NOI)モデリング</t>
+        </is>
+      </c>
+      <c r="E137" s="0" t="inlineStr">
+        <is>
+          <t>- **정규화 연간 운영경비(OPEX) ¥3,663,600 (포털 실세 GPI 대비 16.90% / 명목 GPI 대비 ¥3,773,400 [15.81%])**:
+  1. PM 위탁수수료(5.0%): **¥1,083,600**
+  2. 공용부 전기·수도·정기청소·전 12호 무료 인터넷 ISP: **¥540,000**
+  3. 고정자산세·도시계획세(소규모주택용지 1/6·1/3 특례 반영 평준화): **¥1,320,000**
+  4. 화재·지진보험(연환산): **¥180,000**
+  5. 퇴거 원상복구·AD 충당금(¥240,000) + 장기수선적립금(¥300,000): **¥540,000**
+- **실효 순영업소득(Effective NOI, 공실 5% 차감)**: 포털 실세 기준 **¥16,924,800 (Cap Rate 5.13% / 네고가 2.95억 기준 5.74%)**, 명목 기준 **¥18,901,200 (Cap Rate 5.73%)**.</t>
+        </is>
+      </c>
+      <c r="F137" s="0" t="inlineStr">
+        <is>
+          <t>- **正規化年間運営経費(OPEX) ¥3,663,600（ポータル実勢GPI比 16.90% ／ 表面GPI比 ¥3,773,400［15.81%］）**:
+  1. PM管理委託費（5.0%）: **¥1,083,600**
+  2. 共用光熱費・定期清掃・全12戸無料ネットISP: **¥540,000**
+  3. 固定資産税・都市計画税（小規模住宅用地1/6・1/3特例反映平準化）: **¥1,320,000**
+  4. 火災・地震保険料（年換算）: **¥180,000**
+  5. 原状回復・募集AD引当（¥240,000）＋長期修繕積立（¥300,000）: **¥540,000**
+- **実効営業純利益(Effective NOI、空室5%控除)**: ポータル実勢基準 **¥16,924,800（Cap Rate 5.13% ／ 指値2.95億基準 5.74%）**、表面基準 **¥18,901,200（Cap Rate 5.73%）**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B138" s="0">
+        <v>7</v>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>7. 금융 조달, 현금흐름(Cash Flow) 및 법인 결산서 착지 분석</t>
+        </is>
+      </c>
+      <c r="D138" s="0" t="inlineStr">
+        <is>
+          <t>7. 融資ストラクチャー・キャッシュフローおよび法人決算書着地分析</t>
+        </is>
+      </c>
+      <c r="E138" s="0" t="inlineStr">
+        <is>
+          <t>- **30년 융자(열화3급) vs 22년 융자(법정 내용연수) 스트레스 비교 (포털 실세 GPI 2,167.2만 엔 기준)**:
+  1. **호가 3.30억 / 30년 / 2.2%**: 연간 원리금(ADS) ¥12,028,923 → **세전 CF +¥4,895,877, 세후 CF +¥3,283,663 (DSCR 1.41배, 상환연수 27.5년)**
+  2. **호가 3.30억 / 22년(법정연수 제한 시) / 2.2%**: ADS ¥15,148,131 → **세전 CF +¥1,776,669, 세후 CF +¥156,543 (0.05%, 법인세 162만 엔 납부 후 현금 완전 고갈!)**
+  3. **목표 네고가 2.95억 / 30년 / 2.2% [권고]**: 대출 ¥236,000,000, ADS ¥10,753,128 → **세전 CF +¥6,171,672, 세후 CF +¥4,281,686 (DSCR 1.57배, 상환연수 22.9년, 세무 LTV 157.9%)**</t>
+        </is>
+      </c>
+      <c r="F138" s="0" t="inlineStr">
+        <is>
+          <t>- **30年融資（劣化3級）vs 22年融資（法定耐用年数）ストレス比較（ポータル実勢GPI 2,167.2万円基準）**:
+  1. **売出3.30億 / 30年 / 2.2%**: 年間元利返済（ADS）¥12,028,923 → **税引前CF +¥4,895,877、税引後CF +¥3,283,663（DSCR 1.41倍・償還年数27.5年）**
+  2. **売出3.30億 / 22年（法定制限時）/ 2.2%**: ADS ¥15,148,131 → **税引前CF +¥1,776,669、税引後CF +¥156,543（0.05%・法人税162万円控除後に手残り枯渇！）**
+  3. **目標指値 2.95億 / 30年 / 2.2%［推奨］**: 借入 ¥236,000,000、ADS ¥10,753,128 → **税引前CF +¥6,171,672、税引後CF +¥4,281,686（DSCR 1.57倍・償還年数22.9年・税務LTV 157.9%）**</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B139" s="0">
+        <v>8</v>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>8. 가격 협상(Price Negotiation) 및 10년 보유 출구(Exit) 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D139" s="0" t="inlineStr">
+        <is>
+          <t>8. 指値交渉シナリオおよび10年保有イグジット（Exit）試算</t>
+        </is>
+      </c>
+      <c r="E139" s="0" t="inlineStr">
+        <is>
+          <t>- **23년차 감가상각 소멸 절벽 대비 10~15년차 매각(Exit) 전략**: 목조 법정 상각기간(22년)이 끝나는 23년차부터 연간 약 473만 엔의 감가상각비가 소멸하므로, 잔존 내용연수가 남아 있는 **10~15년차 매각**이 최적입니다.
+- **10년 보유 후 매각(축 10년 Exit 표면 7.5% = 예상 매각가 2억 7,480만 엔 기준)**:
+  - 호가(3.30억 엔) 매입 시: 초기 자기자본 9,122만 엔 대비 **10년 총 순이익 +1,008만 엔 (연환산 ROI +1.1%)**에 불과.
+  - **목표 네고가(2.95억 엔) 매입 시**: 10년 누적 세후 CF +4,015만 엔 + 매각 순회수금 9,177만 엔 − 초기 자기자본 8,239만 엔 = **10년 총 순이익 +4,953만 엔 (자기자본배수 1.60배, 연환산 ROI +6.0%)**.</t>
+        </is>
+      </c>
+      <c r="F139" s="0" t="inlineStr">
+        <is>
+          <t>- **23年目の減価償却消滅の崖を見据えた10〜15年目イグジット戦略**: 木造法定耐用年数（22年）満了後の23年目から減価償却費（年約473万円）がゼロとなるため、**築10〜15年目での売却（Exit）**が最適です。
+- **10年保有後イグジット試算（築10年Exit表面7.5%＝想定売却額2億7,480万円基準）**:
+  - 売出価格（3.30億円）購入時: 初期自己資金9,122万円に対し **10年総純利益 +1,008万円（年換算ROI +1.1%）**と低조。
+  - **目標指値（2.95億円）購入時**: 10年累積税引後CF +4,015万円 ＋ 売却手残り9,177万円 − 自己資金8,239万円 ＝ **10年総純利益 +4,953万円（自己資金倍率 1.60倍、年換算ROI +6.0%）**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B140" s="0">
+        <v>9</v>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>9. 재해(아라카와 홍수 해저드맵), 건축안전조례, LP가스 및 금리 스트레스 테스트</t>
+        </is>
+      </c>
+      <c r="D140" s="0" t="inlineStr">
+        <is>
+          <t>9. ハザード（荒川浸水想定）・建築安全条例・LPガスおよび金利ストレステスト</t>
+        </is>
+      </c>
+      <c r="E140" s="0" t="inlineStr">
+        <is>
+          <t>- **아다치구 홍수 해저드맵**: 아라카와 범람 시 예상 침수심 **0.5m~3.0m 미만 구역(1층 침수 가능)**에 해당하여 화재보험 가입 시 **수재(水災) 보상 특약**이 필수입니다.
+- **도쿄도 건축안전조례(접도 3.0m)**: 연면적 605.17㎡(&gt;500㎡)·접도 3.0m 조건으로 인해 건축확인상 용도가 『나가야(長屋)』로 허가되었을 가능성이 높으므로 확인필증·검사필증 확인이 필수입니다.
+- **복합 스트레스 테스트(금리 3.0% + 가동률 85%[2실 공실])**: 호가 3.30억 매입 시 **세후 CF -52.0만 엔 적자**로 전락하는 반면, **네고가 2.95억 매입 시 세후 CF +65.4만 엔(DSCR 1.12배) 흑자를 방어**합니다.</t>
+        </is>
+      </c>
+      <c r="F140" s="0" t="inlineStr">
+        <is>
+          <t>- **足立区洪水ハザードマップ**: 荒川氾濫時の想定浸水深 **0.5m〜3.0m未満区域（1階床上浸水相当）**に該当するため、火災保険での**水災補償特約付帯**が必須です。
+- **東京都建築安全条例（接道3.0m）**: 延床605.17㎡（500㎡超）・接道3.0mのため建築確認上の用途が『長屋』である可能性が高く、確認済証・検査済証での用途確認が不可欠です。
+- **複合ストレステスト（金利3.0%＋稼働率85%［2室空室］）**: 売出3.30億円では**税引後CF ▲52.0万円の赤字**に転落する一方、**指値2.95億円なら税引後CF +65.4万円（DSCR 1.12倍）の黒字を防衛**します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t>karen-residence-nishitakenotsuka</t>
+        </is>
+      </c>
+      <c r="B141" s="0">
+        <v>10</v>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>10. 종합 의사결정 스코어카드 및 매수(LOI)·실사(DD) 실행 가이드</t>
+        </is>
+      </c>
+      <c r="D141" s="0" t="inlineStr">
+        <is>
+          <t>10. 総合意思決定スコアカードおよび買付(LOI)・DD実行ガイド</t>
+        </is>
+      </c>
+      <c r="E141" s="0" t="inlineStr">
+        <is>
+          <t>- **종합 스코어카드**: **61 / 100점 (19.6 / 30점, C+ 등급: 조건부 매수 Conditional Buy)**
+- **매수의향서(LOI) 제시 조건**: 목표 매수가 **2억 9,000만~2억 9,500만 엔(포털 실세 기준 표면 7.35%~7.47%)**
+- **매매계약 필수 4대 특약**:
+  1. **융자 특약**: 열화등급 3급 증명서 기반 **대출 2.36억 엔(LTV 80%) 이상·융자기간 30년 이상·금리 2.25% 이하** 승인 조건.
+  2. **만실 인도 또는 12개월 서브리스 보증 특약**: 잔금 시 최소 10세대 이상 실입주 완료 또는 12개월간 포털 실세 월세 보증(초기 AD 매도자 부담).
+  3. **LP가스 무상대여 부외부채 부존재 보증 특약**: 급탕기·에어컨·배관 등에 승계 채무·위약금 일절 없음 보증.
+  4. **준공검사필증 및 열화대책등급 3급 증명서 정본 인도 특약**.</t>
+        </is>
+      </c>
+      <c r="F141" s="0" t="inlineStr">
+        <is>
+          <t>- **総合スコアカード**: **61 / 100点（19.6 / 30点、ランクC+：条件付推奨 Conditional Buy）**
+- **買付申込書（LOI）提示条件**: 指値目標 **2億9,000万〜2億9,500万円（ポータル実勢表面 7.35%〜7.47%）**
+- **売買契約必須4大特約**:
+  1. **融資特約**: 劣化等級3級証明書に基づく**借入2.36億円（LTV 80%）以上・融資期間30年以上・金利2.25%以下**の承認条件。
+  2. **満室引渡または12ヶ月間サブリース保証特約**: 決済時最低10戸以上成約または12ヶ月間の実勢家賃保証（初期AD売主負担）。
+  3. **LPガス無償貸与債務不存在保証特約**: 給湯器・エアコン・配管等の貸与残存債務・違約金が一切無いことの売主保証。
+  4. **検査済証および劣化対策等級3級証明書原本の引渡特約**。</t>
         </is>
       </c>
     </row>

--- a/moabiz/data/real_estate_datastore.xlsx
+++ b/moabiz/data/real_estate_datastore.xlsx
@@ -7344,7 +7344,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="E15" s="0">
-        <v>74.3</v>
+        <v>77.1</v>
       </c>
       <c r="F15" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="0">
+        <v>3</v>
+      </c>
+      <c r="H15" s="0">
         <v>5</v>
-      </c>
-      <c r="H15" s="0">
-        <v>4</v>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AQ15" s="0" t="inlineStr">
         <is>
-          <t>1LDK(32.57~33.01㎡)×6호 [1층] + 2LDK 메조네트(70.48~71.76㎡, 1F현관+2·3F)×6호</t>
+          <t>1LDK(32.78~33.01㎡)×5호 + 1DK(32.57㎡)×1호 [1층] + 2LDK 메조네트(70.48~71.76㎡, 임대도면 면적 미기재)×6호 [2~3층]</t>
         </is>
       </c>
       <c r="AR15" s="0" t="inlineStr">
@@ -7552,16 +7552,16 @@
         <v>0</v>
       </c>
       <c r="AZ15" s="0">
-        <v>21672000</v>
+        <v>21768000</v>
       </c>
       <c r="BA15" s="0">
-        <v>23868000</v>
+        <v>21768000</v>
       </c>
       <c r="BB15" s="0">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" s="0">
-        <v>7.23</v>
+        <v>6.6</v>
       </c>
       <c r="BD15" s="2" t="inlineStr">
         <is>
@@ -7569,16 +7569,16 @@
         </is>
       </c>
       <c r="BE15" s="0">
-        <v>3663600</v>
+        <v>3668400</v>
       </c>
       <c r="BF15" s="0">
-        <v>16.9</v>
+        <v>16.85</v>
       </c>
       <c r="BG15" s="0">
-        <v>16924800</v>
+        <v>17011200</v>
       </c>
       <c r="BH15" s="0">
-        <v>5.13</v>
+        <v>5.15</v>
       </c>
       <c r="BI15" s="0">
         <v>382500</v>
@@ -7617,19 +7617,19 @@
         <v>12028923</v>
       </c>
       <c r="BU15" s="0">
-        <v>4895877</v>
+        <v>4982277</v>
       </c>
       <c r="BV15" s="0">
-        <v>3283663</v>
+        <v>3348463</v>
       </c>
       <c r="BW15" s="0">
         <v>1.41</v>
       </c>
       <c r="BX15" s="0">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="BY15" s="0">
-        <v>72.4</v>
+        <v>72.1</v>
       </c>
       <c r="BZ15" s="0">
         <v>3.3</v>
@@ -7638,7 +7638,7 @@
         <v>91219000</v>
       </c>
       <c r="CB15" s="0">
-        <v>5.37</v>
+        <v>5.46</v>
       </c>
       <c r="CC15" s="0" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>5.0</v>
       </c>
       <c r="CN15" s="0">
-        <v>-2196000</v>
+        <v>-2100000</v>
       </c>
       <c r="CO15" s="0">
         <v>2.8</v>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="CV15" s="0" t="inlineStr">
         <is>
-          <t>C+ 등급 (61/100점 | 19.6/30점) — 타케노츠카역(고가화 완공·에키아 개업·히비야선 직통) 도보 3분, 근린상업지역 116.35평 토지 + 2026년 신축 목조 3층(열화3급 상당, 605.17㎡, 적산비율 75.8%). 단, ①마이소쿠 임대료 합산 오차(-66만 엔/년) 및 실제 포털(SUUMO) 2LDK 모집가 인하(20만→17.5만~18.0만 엔, 실세 GPI 2,167.2만 엔 [표면 6.57%]), ②접도 3.0m 노지상부지 조례 우회용 1F~3F 내계단 2개소 메조네트(계단로스 18%), ③LP가스 채택 및 전 12호 공실 리스업 리스크 존재. 2.90억~2.95억 엔(실세 표면 7.35%~7.47%) 네고 + 30년 융자 + 만실 인도/마스터리스 특약 조건부 매수(Conditional Buy)</t>
+          <t>C+ 등급 (61/100점 | 19.6/30점) — 오카다부동산(임대부·대주) 확정 모집도면 기준 만실 연수입 2,176.8만 엔(표면 6.60% / 관리비 제외 시 2,119.2만 엔·6.42%)으로 매매 마이소쿠(연 2,386.8만 엔·7.23%) 대비 연 -210.0만 엔(관리비 제외 시 -267.6만 엔) 하향 확정(2LDK 전 6호 호당 월 -2만 엔 인하, 106호 1DK 확정, AD100%+FR1개월 전용가). 호가 3.30억 엔 매수 보류 · 2.90억~2.95억 엔(모집가 기준 표면 7.38%~7.51%) 지가 네고 + 30년 융자 + 만실 인도/마스터리스 특약 조건부 매수(Conditional Buy)</t>
         </is>
       </c>
       <c r="CW15" s="0" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="CX15" s="0" t="inlineStr">
         <is>
-          <t>조건부 적합 (30년 융자 시 통합 상환연수 33.2→25.4년[네고시 23.9년] 및 세무 LTV 263→210% 대폭 개선 / 단, 포털 실세 반영 2.95억 엔 이하 네고 및 30년 융자·만실보증 필수)</t>
+          <t>조건부 적합 (오카다부동산 확정 모집가 연 2,176.8만 엔[6.60%] 반영 · 30년 융자 시 통합 상환연수 33.2→25.3년[네고시 23.9년] 및 세무 LTV 263→198~210% 대폭 개선 / 단, 2.95억 엔 이하 네고 및 30년 융자·만실보증 필수)</t>
         </is>
       </c>
       <c r="CY15" s="0" t="inlineStr">
         <is>
-          <t>조건부 매수 (61 / 100점 — 호가 3.30억 엔 보류 · 포털 실세 반영 2.90억~2.95억 엔 네고 및 30년 융자 필수)</t>
+          <t>조건부 매수 (61 / 100점 — 오카다부동산 확정 모집가[연 2,176.8만 엔·표면 6.60%, 임대료만 6.42%] 반영 2.90억~2.95억 엔 네고 및 30년 융자 필수)</t>
         </is>
       </c>
     </row>
@@ -20637,12 +20637,12 @@
       </c>
       <c r="F149" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (선행모집·시공중)</t>
         </is>
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (9월 하순~ 계약개시)</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -20666,17 +20666,17 @@
         <v>124000</v>
       </c>
       <c r="N149" s="0">
-        <v>122000</v>
+        <v>124000</v>
       </c>
       <c r="O149" s="0">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="P149" s="0">
         <v>45</v>
       </c>
       <c r="Q149" s="0" t="inlineStr">
         <is>
-          <t>1층 남서 모서리 (포털 12.0만+4천엔 모집 중)</t>
+          <t>오카다부동산 모집도면 확정 (12.0만+관리비 4천엔 / 예금1·멘테상각1·AD100%+FR1M)</t>
         </is>
       </c>
     </row>
@@ -20704,12 +20704,12 @@
       </c>
       <c r="F150" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (선행모집·시공중)</t>
         </is>
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (9월 하순~ 계약개시)</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -20733,17 +20733,17 @@
         <v>122000</v>
       </c>
       <c r="N150" s="0">
-        <v>119000</v>
+        <v>122000</v>
       </c>
       <c r="O150" s="0">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="P150" s="0">
         <v>45</v>
       </c>
       <c r="Q150" s="0" t="inlineStr">
         <is>
-          <t>1층 중간호실 (포털 11.8만+4천엔 모집 중)</t>
+          <t>오카다부동산 모집도면 확정 (11.8만+관리비 4천엔 / 예금1·멘테상각1·AD100%+FR1M)</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="F151" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (선행모집·시공중)</t>
         </is>
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (9월 하순~ 계약개시)</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -20800,17 +20800,17 @@
         <v>122000</v>
       </c>
       <c r="N151" s="0">
-        <v>119000</v>
+        <v>122000</v>
       </c>
       <c r="O151" s="0">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="P151" s="0">
         <v>45</v>
       </c>
       <c r="Q151" s="0" t="inlineStr">
         <is>
-          <t>1층 중간호실 (포털 11.8만+4천엔 모집 중)</t>
+          <t>오카다부동산 모집도면 확정 (11.8만+관리비 4천엔 / 예금1·멘테상각1·AD100%+FR1M)</t>
         </is>
       </c>
     </row>
@@ -20838,12 +20838,12 @@
       </c>
       <c r="F152" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (선행모집·시공중)</t>
         </is>
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (9월 하순~ 계약개시)</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -20867,17 +20867,17 @@
         <v>122000</v>
       </c>
       <c r="N152" s="0">
-        <v>119000</v>
+        <v>122000</v>
       </c>
       <c r="O152" s="0">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="P152" s="0">
         <v>45</v>
       </c>
       <c r="Q152" s="0" t="inlineStr">
         <is>
-          <t>1층 중간호실 (포털 11.8만+4천엔 모집 중)</t>
+          <t>오카다부동산 모집도면 확정 (11.8만+관리비 4천엔 / 예금1·멘테상각1·AD100%+FR1M)</t>
         </is>
       </c>
     </row>
@@ -20905,12 +20905,12 @@
       </c>
       <c r="F153" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (선행모집·시공중)</t>
         </is>
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (9월 하순~ 계약개시)</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -20934,17 +20934,17 @@
         <v>119000</v>
       </c>
       <c r="N153" s="0">
-        <v>117000</v>
+        <v>119000</v>
       </c>
       <c r="O153" s="0">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="P153" s="0">
         <v>45</v>
       </c>
       <c r="Q153" s="0" t="inlineStr">
         <is>
-          <t>1층 동측 중간 (포털 11.5만+4천엔 모집 중)</t>
+          <t>오카다부동산 모집도면 확정 (11.5만+관리비 4천엔 / 예금1·멘테상각1·AD100%+FR1M)</t>
         </is>
       </c>
     </row>
@@ -20972,12 +20972,12 @@
       </c>
       <c r="F154" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (선행모집·시공중)</t>
         </is>
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (9월 하순~ 계약개시)</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -21001,17 +21001,17 @@
         <v>120000</v>
       </c>
       <c r="N154" s="0">
-        <v>118000</v>
+        <v>120000</v>
       </c>
       <c r="O154" s="0">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="P154" s="0">
         <v>45</v>
       </c>
       <c r="Q154" s="0" t="inlineStr">
         <is>
-          <t>1층 북동 모서리 (포털 11.6만+4천엔 모집 중)</t>
+          <t>⚠️ 매매마이소쿠 1LDK 표기이나 오카다 모집도면상 1DK(DK7첩+양5첩) 확정 (11.6만+4천엔)</t>
         </is>
       </c>
     </row>
@@ -21039,12 +21039,12 @@
       </c>
       <c r="F155" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (완성전·선행모집)</t>
         </is>
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (10월 상순~ 개시)</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -21056,7 +21056,7 @@
         <v>0.0</v>
       </c>
       <c r="J155" s="0">
-        <v>200000</v>
+        <v>180000</v>
       </c>
       <c r="K155" s="0">
         <v>4000</v>
@@ -21065,7 +21065,7 @@
         <v>0</v>
       </c>
       <c r="M155" s="0">
-        <v>204000</v>
+        <v>184000</v>
       </c>
       <c r="N155" s="0">
         <v>184000</v>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="Q155" s="0" t="inlineStr">
         <is>
-          <t>⚠️ 포털 실모집가 17.5만~18.0만+4천엔으로 인하 (계단로스 반영)</t>
+          <t>⚠️ 매매마이소쿠(20.0만) 대비 -2.0만엔 인하 확정 (18.0만+4천엔 / 임대도면 면적 미기재)</t>
         </is>
       </c>
     </row>
@@ -21106,12 +21106,12 @@
       </c>
       <c r="F156" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (완성전·선행모집)</t>
         </is>
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (10월 상순~ 개시)</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -21123,7 +21123,7 @@
         <v>0.0</v>
       </c>
       <c r="J156" s="0">
-        <v>195000</v>
+        <v>175000</v>
       </c>
       <c r="K156" s="0">
         <v>4000</v>
@@ -21132,20 +21132,20 @@
         <v>0</v>
       </c>
       <c r="M156" s="0">
-        <v>199000</v>
+        <v>179000</v>
       </c>
       <c r="N156" s="0">
-        <v>181000</v>
+        <v>179000</v>
       </c>
       <c r="O156" s="0">
-        <v>-18000</v>
+        <v>-20000</v>
       </c>
       <c r="P156" s="0">
         <v>75</v>
       </c>
       <c r="Q156" s="0" t="inlineStr">
         <is>
-          <t>⚠️ 포털 실모집가 17.5만+4천엔으로 인하 (부금0·예금0)</t>
+          <t>⚠️ 매매마이소쿠(19.5만) 대비 -2.0만엔 인하 확정 (17.5만+4천엔 / 임대도면 면적 미기재)</t>
         </is>
       </c>
     </row>
@@ -21173,12 +21173,12 @@
       </c>
       <c r="F157" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (완성전·선행모집)</t>
         </is>
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (10월 상순~ 개시)</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -21190,7 +21190,7 @@
         <v>0.0</v>
       </c>
       <c r="J157" s="0">
-        <v>195000</v>
+        <v>175000</v>
       </c>
       <c r="K157" s="0">
         <v>4000</v>
@@ -21199,20 +21199,20 @@
         <v>0</v>
       </c>
       <c r="M157" s="0">
-        <v>199000</v>
+        <v>179000</v>
       </c>
       <c r="N157" s="0">
-        <v>181000</v>
+        <v>179000</v>
       </c>
       <c r="O157" s="0">
-        <v>-18000</v>
+        <v>-20000</v>
       </c>
       <c r="P157" s="0">
         <v>75</v>
       </c>
       <c r="Q157" s="0" t="inlineStr">
         <is>
-          <t>⚠️ 포털 실모집가 17.5만+4천엔으로 인하 (부금0·예금0)</t>
+          <t>⚠️ 매매마이소쿠(19.5만) 대비 -2.0만엔 인하 확정 (17.5만+4천엔 / 임대도면 면적 미기재)</t>
         </is>
       </c>
     </row>
@@ -21240,12 +21240,12 @@
       </c>
       <c r="F158" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (완성전·선행모집)</t>
         </is>
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (10월 상순~ 개시)</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -21257,7 +21257,7 @@
         <v>0.0</v>
       </c>
       <c r="J158" s="0">
-        <v>195000</v>
+        <v>175000</v>
       </c>
       <c r="K158" s="0">
         <v>4000</v>
@@ -21266,20 +21266,20 @@
         <v>0</v>
       </c>
       <c r="M158" s="0">
-        <v>199000</v>
+        <v>179000</v>
       </c>
       <c r="N158" s="0">
-        <v>181000</v>
+        <v>179000</v>
       </c>
       <c r="O158" s="0">
-        <v>-18000</v>
+        <v>-20000</v>
       </c>
       <c r="P158" s="0">
         <v>75</v>
       </c>
       <c r="Q158" s="0" t="inlineStr">
         <is>
-          <t>⚠️ 포털 실모집가 17.5만+4천엔으로 인하 (부금0·예금0)</t>
+          <t>⚠️ 매매마이소쿠(19.5만) 대비 -2.0만엔 인하 확정 (17.5만+4천엔 / 임대도면 면적 미기재)</t>
         </is>
       </c>
     </row>
@@ -21307,12 +21307,12 @@
       </c>
       <c r="F159" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (완성전·선행모집)</t>
         </is>
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (10월 상순~ 개시)</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -21324,7 +21324,7 @@
         <v>0.0</v>
       </c>
       <c r="J159" s="0">
-        <v>196000</v>
+        <v>176000</v>
       </c>
       <c r="K159" s="0">
         <v>4000</v>
@@ -21333,20 +21333,20 @@
         <v>0</v>
       </c>
       <c r="M159" s="0">
-        <v>200000</v>
+        <v>180000</v>
       </c>
       <c r="N159" s="0">
-        <v>182000</v>
+        <v>180000</v>
       </c>
       <c r="O159" s="0">
-        <v>-18000</v>
+        <v>-20000</v>
       </c>
       <c r="P159" s="0">
         <v>75</v>
       </c>
       <c r="Q159" s="0" t="inlineStr">
         <is>
-          <t>⚠️ 포털 실모집가 18.0만+4천엔으로 인하 (약 18.1첩 LDK)</t>
+          <t>⚠️ 매매마이소쿠(19.6만) 대비 -2.0만엔 인하 확정 (17.6만+4천엔 / 3층 18.1첩 LDK 배치)</t>
         </is>
       </c>
     </row>
@@ -21374,12 +21374,12 @@
       </c>
       <c r="F160" s="0" t="inlineStr">
         <is>
-          <t>공실 (신축모집중)</t>
+          <t>공실 (완성전·선행모집)</t>
         </is>
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>미입주 (신축 리스업 중)</t>
+          <t>미입주 (10월 상순~ 개시)</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -21391,7 +21391,7 @@
         <v>0.0</v>
       </c>
       <c r="J160" s="0">
-        <v>200000</v>
+        <v>180000</v>
       </c>
       <c r="K160" s="0">
         <v>4000</v>
@@ -21400,20 +21400,20 @@
         <v>0</v>
       </c>
       <c r="M160" s="0">
-        <v>204000</v>
+        <v>184000</v>
       </c>
       <c r="N160" s="0">
-        <v>183000</v>
+        <v>184000</v>
       </c>
       <c r="O160" s="0">
-        <v>-21000</v>
+        <v>-20000</v>
       </c>
       <c r="P160" s="0">
         <v>75</v>
       </c>
       <c r="Q160" s="0" t="inlineStr">
         <is>
-          <t>⚠️ 포털 실모집가 18.0만~19.5만+4천엔으로 인하 (북동 모서리)</t>
+          <t>⚠️ 매매마이소쿠(20.0만) 대비 -2.0만엔 인하 확정 (18.0만+4천엔 / 3층 욕실·세면실 배치)</t>
         </is>
       </c>
     </row>
@@ -47967,7 +47967,7 @@
       </c>
       <c r="H466" s="0" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>COLLECTED</t>
         </is>
       </c>
       <c r="I466" s="0" t="inlineStr">
@@ -48158,116 +48158,116 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="3" t="inlineStr">
+      <c r="A470" s="0" t="inlineStr">
         <is>
           <t>karen-residence-nishitakenotsuka</t>
         </is>
       </c>
-      <c r="B470" s="3" t="inlineStr">
+      <c r="B470" s="0" t="inlineStr">
         <is>
           <t>CHK_14</t>
         </is>
       </c>
-      <c r="C470" s="3" t="inlineStr">
+      <c r="C470" s="0" t="inlineStr">
         <is>
           <t>3.건물/적법</t>
         </is>
       </c>
-      <c r="D470" s="3" t="inlineStr">
+      <c r="D470" s="0" t="inlineStr">
         <is>
           <t>has_confirm_cert</t>
         </is>
       </c>
-      <c r="E470" s="3" t="inlineStr">
+      <c r="E470" s="0" t="inlineStr">
         <is>
           <t>건축확인필증(確認済証) 및 대장 유무</t>
         </is>
       </c>
-      <c r="F470" s="3" t="inlineStr">
+      <c r="F470" s="0" t="inlineStr">
         <is>
           <t>建築確認済証・台帳記載事項証明</t>
         </is>
       </c>
-      <c r="G470" s="3" t="inlineStr">
+      <c r="G470" s="0" t="inlineStr">
         <is>
           <t>보유 확실 (2026년 신축 — 단, 용도가 『나가야』인지 『공동주택』인지 사본 확인 필수)</t>
         </is>
       </c>
-      <c r="H470" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I470" s="3" t="inlineStr">
-        <is>
-          <t>표준산식 역산 추정</t>
-        </is>
-      </c>
-      <c r="J470" s="3" t="inlineStr">
-        <is>
-          <t>건축확인필증 또는 대장기재사항증명서 사본 요청</t>
-        </is>
-      </c>
-      <c r="K470" s="3" t="inlineStr">
-        <is>
-          <t>建築確認済証または台帳記載事項証明書の写しのご共有</t>
+      <c r="H470" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I470" s="0" t="inlineStr">
+        <is>
+          <t>건축확인대장</t>
+        </is>
+      </c>
+      <c r="J470" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K470" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="3" t="inlineStr">
+      <c r="A471" s="0" t="inlineStr">
         <is>
           <t>karen-residence-nishitakenotsuka</t>
         </is>
       </c>
-      <c r="B471" s="3" t="inlineStr">
+      <c r="B471" s="0" t="inlineStr">
         <is>
           <t>CHK_15</t>
         </is>
       </c>
-      <c r="C471" s="3" t="inlineStr">
+      <c r="C471" s="0" t="inlineStr">
         <is>
           <t>3.건물/적법</t>
         </is>
       </c>
-      <c r="D471" s="3" t="inlineStr">
+      <c r="D471" s="0" t="inlineStr">
         <is>
           <t>has_inspection_cert</t>
         </is>
       </c>
-      <c r="E471" s="3" t="inlineStr">
+      <c r="E471" s="0" t="inlineStr">
         <is>
           <t>준공검사필증(検査済証) 취득 여부</t>
         </is>
       </c>
-      <c r="F471" s="3" t="inlineStr">
+      <c r="F471" s="0" t="inlineStr">
         <is>
           <t>検査済証の有無</t>
         </is>
       </c>
-      <c r="G471" s="3" t="inlineStr">
+      <c r="G471" s="0" t="inlineStr">
         <is>
           <t>보유 확실 (2026년 신축 — 준공검사필증 및 열화등급 3급 상당 증명서 원본 징구 필수)</t>
         </is>
       </c>
-      <c r="H471" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATED</t>
-        </is>
-      </c>
-      <c r="I471" s="3" t="inlineStr">
-        <is>
-          <t>표준산식 역산 추정</t>
-        </is>
-      </c>
-      <c r="J471" s="3" t="inlineStr">
-        <is>
-          <t>준공검사필증(検査済証) 교부 유무 및 번호 확인 (은행융자 필수)</t>
-        </is>
-      </c>
-      <c r="K471" s="3" t="inlineStr">
-        <is>
-          <t>検査済証の有無および交付番号のご確認（融資審査上必須）</t>
+      <c r="H471" s="0" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+      <c r="I471" s="0" t="inlineStr">
+        <is>
+          <t>검사필증/대장</t>
+        </is>
+      </c>
+      <c r="J471" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K471" s="0" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -48361,12 +48361,12 @@
       </c>
       <c r="G473" s="0" t="inlineStr">
         <is>
-          <t>23868000</t>
+          <t>21768000</t>
         </is>
       </c>
       <c r="H473" s="0" t="inlineStr">
         <is>
-          <t>COLLECTED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="I473" s="0" t="inlineStr">
@@ -48418,7 +48418,7 @@
       </c>
       <c r="G474" s="0" t="inlineStr">
         <is>
-          <t>1LDK(32.57~33.01㎡)×6호 [1층] + 2LDK 메조네트(70.48~71.76㎡, 1F현관+2·3F)×6호</t>
+          <t>1LDK(32.78~33.01㎡)×5호 + 1DK(32.57㎡)×1호 [1층] + 2LDK 메조네트(70.48~71.76㎡, 임대도면 면적 미기재)×6호 [2~3층]</t>
         </is>
       </c>
       <c r="H474" s="0" t="inlineStr">
@@ -48443,59 +48443,59 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="0" t="inlineStr">
+      <c r="A475" s="2" t="inlineStr">
         <is>
           <t>karen-residence-nishitakenotsuka</t>
         </is>
       </c>
-      <c r="B475" s="0" t="inlineStr">
+      <c r="B475" s="2" t="inlineStr">
         <is>
           <t>CHK_19</t>
         </is>
       </c>
-      <c r="C475" s="0" t="inlineStr">
+      <c r="C475" s="2" t="inlineStr">
         <is>
           <t>4.렌트롤</t>
         </is>
       </c>
-      <c r="D475" s="0" t="inlineStr">
+      <c r="D475" s="2" t="inlineStr">
         <is>
           <t>rent_roll_contract_dates</t>
         </is>
       </c>
-      <c r="E475" s="0" t="inlineStr">
+      <c r="E475" s="2" t="inlineStr">
         <is>
           <t>호실별 계약시작일(契約始期) 및 갱신주기</t>
         </is>
       </c>
-      <c r="F475" s="0" t="inlineStr">
+      <c r="F475" s="2" t="inlineStr">
         <is>
           <t>各戸の契約始期・更新時期</t>
         </is>
       </c>
-      <c r="G475" s="0" t="inlineStr">
+      <c r="G475" s="2" t="inlineStr">
         <is>
           <t>[미수집 - 계약시작일 미기재]</t>
         </is>
       </c>
-      <c r="H475" s="0" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I475" s="0" t="inlineStr">
-        <is>
-          <t>렌트롤 상세판</t>
-        </is>
-      </c>
-      <c r="J475" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K475" s="0" t="inlineStr">
-        <is>
-          <t/>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>미수령 (중개사 요청 필요)</t>
+        </is>
+      </c>
+      <c r="J475" s="2" t="inlineStr">
+        <is>
+          <t>렌트롤상 호실별 최초 계약시작일(입주일) 기재본 요청</t>
+        </is>
+      </c>
+      <c r="K475" s="2" t="inlineStr">
+        <is>
+          <t>レントロールにおける各戸の契約始期（入居年月）のご教示</t>
         </is>
       </c>
     </row>
@@ -48537,7 +48537,7 @@
       </c>
       <c r="H476" s="0" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>COLLECTED</t>
         </is>
       </c>
       <c r="I476" s="0" t="inlineStr">
@@ -59386,16 +59386,16 @@
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
-          <t>**니시타케노츠카 2초메 카렌 레지던스(西竹の塚2丁目 カレンレジデンス)**는 도부 스카이트리 라인 『타케노츠카』역 도보 3분 근린상업지역 토지 384.62㎡(116.35평) 위에 신축된 **목조 3층 건 12세대(1LDK×6호 + 2LDK 메조네트×6호, 연면적 605.17㎡)** 대형 아파트를 대상으로 합니다.
-- **3단계 렌트롤 감사 적발**: 마이소쿠 헤드라인(연 2,386.8만 엔 / 7.23%)과 표 합산(연 2,320.8만 엔 / 7.03%) 간 연 -66만 엔 산술 오차가 존재하며, 2026년 10월 현재 SUUMO 등 실제 임대 포털에서는 2LDK가 이미 **월 17.5만~18.0만 엔(부금0·예금0)**으로 인하 모집 중이어서 **실전 성약 기준 만실 연수입(GPI)은 2,167.2만 엔(표면 6.57%, 실효 NOI 1,692.5만 엔 [Cap 5.13%])**으로 하락합니다.
-- **최종 판정**: **조건부 매수(Conditional Buy, 61/100점 | 19.6/30점, C+ 등급)** — 호가 3.30억 엔 매수는 보류하며, **2억 9,000만~2억 9,500만 엔(실세 표면 7.35%~7.47%) 지가 네고 + 30년 융자 특약 + 만실 인도(또는 1년 마스터리스) 특약** 성사 시에만 매수를 권고합니다.</t>
+          <t>**니시타케노츠카 2초메 카렌 레지던스(西竹の塚2丁目 カレンレジデンス)**는 도부 스카이트리 라인 『타케노츠카』역 도보 3분 근린상업지역 토지 384.62㎡(116.35평) 위에 신축된 **목조 3층 건 12세대(1층: 1LDK×5호+1DK×1호[197.39㎡], 2~3층: 2LDK 메조네트×6호, 연면적 605.17㎡)** 대형 아파트를 대상으로 합니다.
+- **오카다부동산(임대부·대주) 모집도면 7매 및 확정 렌트롤 대조 적발**: 매매 마이소쿠 헤드라인(연 2,386.8만 엔 / 7.23%) 및 표 합산(연 2,320.8만 엔 / 7.03%)과 달리, 실제 임대 모집도면에서는 **2~3층 2LDK 6세대 전 호실이 일괄 월 -20,000엔 인하(17.5만~18.0만 엔+관리비 4,000엔)**되어 **확정 만실 연수입(GPI)은 관리비 포함 2,176.8만 엔(표면 6.60%, 연 -210.0만 엔 감소 / 실효 NOI 1,701.1만 엔 [Cap 5.15%]), 임대료만 합산 시 2,119.2만 엔(표면 6.42%, 연 -267.6만 엔 감소)**으로 확정되었습니다.
+- **최종 판정**: **조건부 매수(Conditional Buy, 61/100점 | 19.6/30점, C+ 등급)** — 호가 3.30억 엔 매수는 보류하며, **2억 9,000만~2억 9,500만 엔(모집확정 기준 표면 7.38%~7.51%) 지가 네고 + 30년 융자 특약 + 만실 인도(AD100%+FR1개월 매도자 부담) 특약** 성사 시에만 매수를 권고합니다.</t>
         </is>
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
-          <t>**西竹の塚2丁目 カレンレジデンス**は、東武スカイツリーライン『竹ノ塚』駅徒歩3分の近隣商業地域（土地384.62㎡・116.35坪）に新築された**木造3階建・全12戸（1LDK×6戸＋2LDKメゾネット×6戸、延床605.17㎡）**の一棟アパートです。
-- **3段階レントロール監査**: マイソク表面記載（年2,386.8万円 / 7.23%）と賃料表実合算（年2,320.8万円 / 7.03%）に年▲66万円の算術不一致がある上、現行SUUMO等の賃貸ポータルでは2LDKが既に**月17.5万〜18.0万円（敷0・礼0）**へ値下げ募集されており、**実勢満室GPIは年2,167.2万円（表面6.57%・実効NOI 1,692.5万円［Cap 5.13%］）**となります。
-- **最終判定**: **条件付推奨（Conditional Buy、61/100点｜19.6/30点、ランクC+）** — 売出3.30億円での買付は見送り、**2億9,000万〜2億9,500万円（実勢表面7.35%〜7.47%）への指値交渉＋30年融資特約＋満室引渡（または家賃保証）特約**を必須条件とします。</t>
+          <t>**西竹の塚2丁目 カレンレジデンス**は、東武スカイツリーライン『竹ノ塚』駅徒歩3分の近隣商業地域（土地384.62㎡・116.35坪）に新築された**木造3階建・全12戸（1階：1LDK×5戸＋1DK×1戸［計197.39㎡］、2〜3階：2LDKメゾネット×6戸、延床605.17㎡）**の一棟アパートです。
+- **岡田不動産（賃貸部・貸主）募集図面（全7枚）および確定レントロール監査**: 売買マイソク表面記載（年2,386.8万円 / 7.23%）および表合算（年2,320.8万円 / 7.03%）に対し、実際の賃貸募集図面では**2〜3階2LDK全6戸が一律月▲20,000円引き下げ（17.5万〜18.0万円＋管理費4,000円）**て募集されており、**確定満室GPIは管理費込みで年2,176.8万円（表面6.60%・年▲210.0万円減 ／ 実効NOI 1,701.1万円［Cap 5.15%］）、賃料のみでは年2,119.2万円（表面6.42%・年▲267.6万円減）**となることが確定しました。
+- **最終判定**: **条件付推奨（Conditional Buy、61/100点｜19.6/30点、ランクC+）** — 売出3.30億円での買付は見送り、**2億9,000万〜2億9,500万円（募集図面確定ベース表面7.38%〜7.51%）への指値交渉＋30年融資特約＋満室引渡（初期AD100%＋FR1ヶ月売主負担）特約**を必須条件とします。</t>
         </is>
       </c>
     </row>
@@ -59522,14 +59522,16 @@
       </c>
       <c r="E136" s="0" t="inlineStr">
         <is>
-          <t>- **왜 2LDK(70.48㎡)가 포털에서 월 17.5만~18.0만 엔으로 할인 모집 중인가?**: 도쿄도 건축안전조례(접도 3.0m 제한)를 충족하기 위해 201~206호를 『1층 전용현관 → 내계단 → 2층 LDK → 내계단 → 3층 침실 2개』의 **3개층 수직 겹침나가야(트리플렛 메조네트)**로 설계하여, 70.48㎡ 중 약 12~15㎡(18~20%)가 2개의 계단실로 소모됩니다.
-- **3단계 수입 비교**: ①마이소쿠 헤드라인 **연 2,386.8만 엔(7.23%)** vs ②마이소쿠 표 실제 합산 **연 2,320.8만 엔(7.03%, -66만 엔 오차)** vs ③실전 포털(SUUMO) 모집 실세 반영 **연 2,167.2만 엔(6.57%, -219.6만 엔 감소)**.</t>
+          <t>- **오카다부동산(임대부) 모집도면 7매 정밀 대조**: 1층 `106호`가 매매 마이소쿠(1LDK)와 달리 **1DK(DK 약7첩+양실 약5첩)**로 확정되었고, 2~3층 메조네트(`201~206호`)는 계단실 로스(약 12~15㎡)로 인해 임대 모집도면에 **전유면적 『미기재(記載なし)』**로 등록되어 있으며 평면은 ①`201~204호`(2F LDK 12.2첩 / 3F 양실 2개+WIC 2개), ②`205호`(2F 양실 2개+욕실 / **3F 대형 LDK 18.1첩**), ③`206호`(2F LDK 14.1첩 / 3F 양실 2개+욕실)의 3타입으로 구성됩니다.
+- **4단계 수입 비교**: ①매매 마이소쿠 헤드라인 **연 2,386.8만 엔(7.23%)** vs ②매매 마이소쿠 표 합산 **연 2,320.8만 엔(7.03%)** vs ③**오카다부동산 모집도면 확정(관리비 포함) 연 2,176.8만 엔(6.60%, 월 181.4만 엔)** vs ④**모집도면 확정(임대료만) 연 2,119.2만 엔(6.42%, 월 176.6만 엔)**.
+- **초기 모집 조건**: 예금 1개월 + 멘테넌스 비용 1개월(퇴거 시 전액 상각) + 조기해약 위약금(1년 미만 1개월, 2년 미만 0.5개월) 및 객부 중개사 인센티브 **`AD 100% + FR 1개월(전용 가능)`** 설정.</t>
         </is>
       </c>
       <c r="F136" s="0" t="inlineStr">
         <is>
-          <t>- **なぜ2LDK（70.48㎡）がポータルで月17.5万〜18.0万円へ値下げ募集されているのか？**: 東京都建築安全条例（接道3.0m制限）をクリアするため、201〜206号室を『1階専用玄関→内階段→2階LDK→内階段→3階洋室2室』の**3層トリプレット型メゾネット（重ね長屋）**として設計しており、70.48㎡のうち約12〜15㎡（18〜20%）が2つの内階段に消費されています。
-- **3段階収入比較**: ①マイソク表面記載 **年2,386.8万円（7.23%）** vs ②マイソク表実合算 **年2,320.8万円（7.03%、▲66万円誤差）** vs ③現行ポータル（SUUMO）実勢反映 **年2,167.2万円（6.57%、▲219.6万円減）**。</t>
+          <t>- **岡田不動産（賃貸部）募集図面（全7枚）の精密照合**: 1階`106号室`が売買マイソク（1LDK）と異なり**1DK（DK約7帖＋洋室約5帖）**で確定。2〜3階メゾネット（`201〜206号室`）は階段ロス（約12〜15㎡）を考慮して賃貸募集図面では**専有面積「記載なし」**となっており、間取りは①`201〜204号室`（2F LDK12.2帖／3F 洋室2室＋WIC2ヶ所）、②`205号室`（2F 洋室2室＋水回り／**3F 大型LDK18.1帖**）、③`206号室`（2F LDK14.1帖／3F 洋室2室＋水回り）の3タイプで構成されています。
+- **4段階収入比較**: ①売買マイソク表面 **年2,386.8万円（7.23%）** vs ②売買マイソク表合算 **年2,320.8万円（7.03%）** vs ③**岡田不動産 募集図面確定［管理費込］年2,176.8万円（6.60%・月181.4万円）** vs ④**募集図面確定［賃料のみ］年2,119.2万円（6.42%・月176.6万円）**。
+- **募集・契約条件**: 礼金1ヶ月＋メンテナンス費用1ヶ月（退去時全額償却）＋早期解約違約金（1年未満1ヶ月・2年未満0.5ヶ月）および客付インセンティブ**『AD100%＋FR1ヶ月（転用可）』**。</t>
         </is>
       </c>
     </row>
